--- a/report/bao-cao.xlsx
+++ b/report/bao-cao.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HXuan\BaocaoGiaingan\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B4A278-9038-4882-9E31-F7D21547A648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F48674-6CAF-4726-8F26-2B51D5319317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{BF3132C5-3821-4F06-A909-D3A92B5D6441}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{BF3132C5-3821-4F06-A909-D3A92B5D6441}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,9 +30,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1405,21 +1402,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1453,29 +1459,20 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1818,69 +1815,68 @@
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
     <col min="2" max="2" width="33" style="154" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" style="118" customWidth="1"/>
-    <col min="4" max="11" width="8.5703125" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="11.5703125" style="118" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" hidden="1" customWidth="1"/>
-    <col min="16" max="17" width="10.5703125" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="9.5703125" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="17.42578125" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="16.42578125" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="11.140625" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" hidden="1" customWidth="1"/>
+    <col min="4" max="11" width="8.5703125" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" style="118" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" customWidth="1"/>
+    <col min="16" max="17" width="10.5703125" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" customWidth="1"/>
+    <col min="19" max="19" width="17.42578125" customWidth="1"/>
+    <col min="20" max="20" width="16.42578125" customWidth="1"/>
+    <col min="21" max="21" width="11.140625" customWidth="1"/>
+    <col min="22" max="22" width="8.5703125" customWidth="1"/>
     <col min="23" max="23" width="14.140625" customWidth="1"/>
-    <col min="24" max="24" width="10" style="155" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="11.140625" style="155" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="11.140625" style="155" customWidth="1"/>
+    <col min="24" max="24" width="10" style="155" customWidth="1"/>
+    <col min="25" max="26" width="11.140625" style="155" customWidth="1"/>
     <col min="27" max="27" width="11.42578125" customWidth="1"/>
     <col min="28" max="28" width="10.5703125" customWidth="1"/>
     <col min="29" max="29" width="10.85546875" style="47" customWidth="1"/>
     <col min="30" max="30" width="12.5703125" style="47" customWidth="1"/>
     <col min="31" max="31" width="11.140625" style="47" customWidth="1"/>
     <col min="32" max="32" width="9.5703125" customWidth="1"/>
-    <col min="33" max="34" width="14.5703125" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="15.5703125" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="11.42578125" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="12.140625" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="17.5703125" hidden="1" customWidth="1"/>
-    <col min="39" max="39" width="12.42578125" hidden="1" customWidth="1"/>
-    <col min="40" max="40" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="33" max="34" width="14.5703125" customWidth="1"/>
+    <col min="35" max="35" width="15.5703125" customWidth="1"/>
+    <col min="36" max="36" width="11.42578125" customWidth="1"/>
+    <col min="37" max="37" width="12.140625" customWidth="1"/>
+    <col min="38" max="38" width="17.5703125" customWidth="1"/>
+    <col min="39" max="39" width="12.42578125" customWidth="1"/>
+    <col min="40" max="40" width="15.85546875" customWidth="1"/>
     <col min="41" max="41" width="15" style="118" customWidth="1"/>
     <col min="42" max="44" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="179" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="180"/>
-      <c r="C1" s="180"/>
-      <c r="D1" s="180"/>
-      <c r="E1" s="180"/>
-      <c r="F1" s="180"/>
-      <c r="G1" s="180"/>
-      <c r="H1" s="180"/>
-      <c r="I1" s="180"/>
-      <c r="J1" s="180"/>
-      <c r="K1" s="180"/>
-      <c r="L1" s="180"/>
-      <c r="M1" s="180"/>
-      <c r="N1" s="180"/>
-      <c r="O1" s="180"/>
-      <c r="P1" s="180"/>
-      <c r="Q1" s="180"/>
-      <c r="R1" s="180"/>
-      <c r="S1" s="180"/>
-      <c r="T1" s="180"/>
-      <c r="U1" s="180"/>
-      <c r="V1" s="180"/>
-      <c r="W1" s="180"/>
-      <c r="X1" s="180"/>
-      <c r="Y1" s="180"/>
-      <c r="Z1" s="180"/>
-      <c r="AA1" s="180"/>
-      <c r="AB1" s="180"/>
+      <c r="A1" s="161" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="162"/>
+      <c r="G1" s="162"/>
+      <c r="H1" s="162"/>
+      <c r="I1" s="162"/>
+      <c r="J1" s="162"/>
+      <c r="K1" s="162"/>
+      <c r="L1" s="162"/>
+      <c r="M1" s="162"/>
+      <c r="N1" s="162"/>
+      <c r="O1" s="162"/>
+      <c r="P1" s="162"/>
+      <c r="Q1" s="162"/>
+      <c r="R1" s="162"/>
+      <c r="S1" s="162"/>
+      <c r="T1" s="162"/>
+      <c r="U1" s="162"/>
+      <c r="V1" s="162"/>
+      <c r="W1" s="162"/>
+      <c r="X1" s="162"/>
+      <c r="Y1" s="162"/>
+      <c r="Z1" s="162"/>
+      <c r="AA1" s="162"/>
+      <c r="AB1" s="162"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
@@ -1900,36 +1896,36 @@
       </c>
     </row>
     <row r="2" spans="1:44" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="181" t="s">
+      <c r="A2" s="163" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="180"/>
-      <c r="C2" s="180"/>
-      <c r="D2" s="180"/>
-      <c r="E2" s="180"/>
-      <c r="F2" s="180"/>
-      <c r="G2" s="180"/>
-      <c r="H2" s="180"/>
-      <c r="I2" s="180"/>
-      <c r="J2" s="180"/>
-      <c r="K2" s="180"/>
-      <c r="L2" s="180"/>
-      <c r="M2" s="180"/>
-      <c r="N2" s="180"/>
-      <c r="O2" s="180"/>
-      <c r="P2" s="180"/>
-      <c r="Q2" s="180"/>
-      <c r="R2" s="180"/>
-      <c r="S2" s="180"/>
-      <c r="T2" s="180"/>
-      <c r="U2" s="180"/>
-      <c r="V2" s="180"/>
-      <c r="W2" s="180"/>
-      <c r="X2" s="180"/>
-      <c r="Y2" s="180"/>
-      <c r="Z2" s="180"/>
-      <c r="AA2" s="180"/>
-      <c r="AB2" s="180"/>
+      <c r="B2" s="162"/>
+      <c r="C2" s="162"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="162"/>
+      <c r="F2" s="162"/>
+      <c r="G2" s="162"/>
+      <c r="H2" s="162"/>
+      <c r="I2" s="162"/>
+      <c r="J2" s="162"/>
+      <c r="K2" s="162"/>
+      <c r="L2" s="162"/>
+      <c r="M2" s="162"/>
+      <c r="N2" s="162"/>
+      <c r="O2" s="162"/>
+      <c r="P2" s="162"/>
+      <c r="Q2" s="162"/>
+      <c r="R2" s="162"/>
+      <c r="S2" s="162"/>
+      <c r="T2" s="162"/>
+      <c r="U2" s="162"/>
+      <c r="V2" s="162"/>
+      <c r="W2" s="162"/>
+      <c r="X2" s="162"/>
+      <c r="Y2" s="162"/>
+      <c r="Z2" s="162"/>
+      <c r="AA2" s="162"/>
+      <c r="AB2" s="162"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
       <c r="AE2" s="1"/>
@@ -1988,94 +1984,94 @@
       <c r="AO3" s="5"/>
     </row>
     <row r="4" spans="1:44" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="182" t="s">
+      <c r="A4" s="164" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="180"/>
-      <c r="C4" s="180"/>
-      <c r="D4" s="180"/>
-      <c r="E4" s="180"/>
-      <c r="F4" s="180"/>
-      <c r="G4" s="180"/>
-      <c r="H4" s="180"/>
-      <c r="I4" s="180"/>
-      <c r="J4" s="180"/>
-      <c r="K4" s="180"/>
-      <c r="L4" s="180"/>
-      <c r="M4" s="180"/>
-      <c r="N4" s="180"/>
-      <c r="O4" s="180"/>
-      <c r="P4" s="180"/>
-      <c r="Q4" s="180"/>
-      <c r="R4" s="180"/>
-      <c r="S4" s="180"/>
-      <c r="T4" s="180"/>
-      <c r="U4" s="180"/>
-      <c r="V4" s="180"/>
-      <c r="W4" s="180"/>
-      <c r="X4" s="180"/>
-      <c r="Y4" s="180"/>
-      <c r="Z4" s="180"/>
-      <c r="AA4" s="180"/>
-      <c r="AB4" s="180"/>
-      <c r="AC4" s="180"/>
-      <c r="AD4" s="180"/>
-      <c r="AE4" s="180"/>
-      <c r="AF4" s="180"/>
-      <c r="AG4" s="180"/>
-      <c r="AH4" s="180"/>
-      <c r="AI4" s="180"/>
-      <c r="AJ4" s="180"/>
-      <c r="AK4" s="180"/>
-      <c r="AL4" s="180"/>
-      <c r="AM4" s="180"/>
-      <c r="AN4" s="180"/>
-      <c r="AO4" s="180"/>
+      <c r="B4" s="162"/>
+      <c r="C4" s="162"/>
+      <c r="D4" s="162"/>
+      <c r="E4" s="162"/>
+      <c r="F4" s="162"/>
+      <c r="G4" s="162"/>
+      <c r="H4" s="162"/>
+      <c r="I4" s="162"/>
+      <c r="J4" s="162"/>
+      <c r="K4" s="162"/>
+      <c r="L4" s="162"/>
+      <c r="M4" s="162"/>
+      <c r="N4" s="162"/>
+      <c r="O4" s="162"/>
+      <c r="P4" s="162"/>
+      <c r="Q4" s="162"/>
+      <c r="R4" s="162"/>
+      <c r="S4" s="162"/>
+      <c r="T4" s="162"/>
+      <c r="U4" s="162"/>
+      <c r="V4" s="162"/>
+      <c r="W4" s="162"/>
+      <c r="X4" s="162"/>
+      <c r="Y4" s="162"/>
+      <c r="Z4" s="162"/>
+      <c r="AA4" s="162"/>
+      <c r="AB4" s="162"/>
+      <c r="AC4" s="162"/>
+      <c r="AD4" s="162"/>
+      <c r="AE4" s="162"/>
+      <c r="AF4" s="162"/>
+      <c r="AG4" s="162"/>
+      <c r="AH4" s="162"/>
+      <c r="AI4" s="162"/>
+      <c r="AJ4" s="162"/>
+      <c r="AK4" s="162"/>
+      <c r="AL4" s="162"/>
+      <c r="AM4" s="162"/>
+      <c r="AN4" s="162"/>
+      <c r="AO4" s="162"/>
     </row>
     <row r="5" spans="1:44" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="183" t="s">
+      <c r="A5" s="165" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="180"/>
-      <c r="C5" s="180"/>
-      <c r="D5" s="180"/>
-      <c r="E5" s="180"/>
-      <c r="F5" s="180"/>
-      <c r="G5" s="180"/>
-      <c r="H5" s="180"/>
-      <c r="I5" s="180"/>
-      <c r="J5" s="180"/>
-      <c r="K5" s="180"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="180"/>
-      <c r="N5" s="180"/>
-      <c r="O5" s="180"/>
-      <c r="P5" s="180"/>
-      <c r="Q5" s="180"/>
-      <c r="R5" s="180"/>
-      <c r="S5" s="180"/>
-      <c r="T5" s="180"/>
-      <c r="U5" s="180"/>
-      <c r="V5" s="180"/>
-      <c r="W5" s="180"/>
-      <c r="X5" s="180"/>
-      <c r="Y5" s="180"/>
-      <c r="Z5" s="180"/>
-      <c r="AA5" s="180"/>
-      <c r="AB5" s="180"/>
-      <c r="AC5" s="180"/>
-      <c r="AD5" s="180"/>
-      <c r="AE5" s="180"/>
-      <c r="AF5" s="180"/>
-      <c r="AG5" s="180"/>
-      <c r="AH5" s="180"/>
-      <c r="AI5" s="180"/>
-      <c r="AJ5" s="180"/>
-      <c r="AK5" s="180"/>
-      <c r="AL5" s="180"/>
-      <c r="AM5" s="180"/>
-      <c r="AN5" s="180"/>
-      <c r="AO5" s="180"/>
+      <c r="B5" s="162"/>
+      <c r="C5" s="162"/>
+      <c r="D5" s="162"/>
+      <c r="E5" s="162"/>
+      <c r="F5" s="162"/>
+      <c r="G5" s="162"/>
+      <c r="H5" s="162"/>
+      <c r="I5" s="162"/>
+      <c r="J5" s="162"/>
+      <c r="K5" s="162"/>
+      <c r="L5" s="162"/>
+      <c r="M5" s="162"/>
+      <c r="N5" s="162"/>
+      <c r="O5" s="162"/>
+      <c r="P5" s="162"/>
+      <c r="Q5" s="162"/>
+      <c r="R5" s="162"/>
+      <c r="S5" s="162"/>
+      <c r="T5" s="162"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="162"/>
+      <c r="W5" s="162"/>
+      <c r="X5" s="162"/>
+      <c r="Y5" s="162"/>
+      <c r="Z5" s="162"/>
+      <c r="AA5" s="162"/>
+      <c r="AB5" s="162"/>
+      <c r="AC5" s="162"/>
+      <c r="AD5" s="162"/>
+      <c r="AE5" s="162"/>
+      <c r="AF5" s="162"/>
+      <c r="AG5" s="162"/>
+      <c r="AH5" s="162"/>
+      <c r="AI5" s="162"/>
+      <c r="AJ5" s="162"/>
+      <c r="AK5" s="162"/>
+      <c r="AL5" s="162"/>
+      <c r="AM5" s="162"/>
+      <c r="AN5" s="162"/>
+      <c r="AO5" s="162"/>
     </row>
     <row r="6" spans="1:44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16"/>
@@ -2111,18 +2107,18 @@
       <c r="AC6" s="16"/>
       <c r="AD6" s="16"/>
       <c r="AE6" s="16"/>
-      <c r="AF6" s="184" t="s">
+      <c r="AF6" s="166" t="s">
         <v>6</v>
       </c>
-      <c r="AG6" s="185"/>
-      <c r="AH6" s="185"/>
-      <c r="AI6" s="185"/>
-      <c r="AJ6" s="185"/>
-      <c r="AK6" s="185"/>
-      <c r="AL6" s="185"/>
-      <c r="AM6" s="185"/>
-      <c r="AN6" s="185"/>
-      <c r="AO6" s="185"/>
+      <c r="AG6" s="167"/>
+      <c r="AH6" s="167"/>
+      <c r="AI6" s="167"/>
+      <c r="AJ6" s="167"/>
+      <c r="AK6" s="167"/>
+      <c r="AL6" s="167"/>
+      <c r="AM6" s="167"/>
+      <c r="AN6" s="167"/>
+      <c r="AO6" s="167"/>
     </row>
     <row r="7" spans="1:44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="159" t="s">
@@ -2131,7 +2127,7 @@
       <c r="B7" s="159" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="187" t="s">
+      <c r="C7" s="169" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="159" t="s">
@@ -2158,7 +2154,7 @@
       <c r="K7" s="159" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="168" t="s">
+      <c r="L7" s="171" t="s">
         <v>18</v>
       </c>
       <c r="M7" s="159" t="s">
@@ -2167,26 +2163,26 @@
       <c r="N7" s="159" t="s">
         <v>20</v>
       </c>
-      <c r="O7" s="170" t="s">
+      <c r="O7" s="173" t="s">
         <v>21</v>
       </c>
-      <c r="P7" s="171"/>
-      <c r="Q7" s="171"/>
-      <c r="R7" s="171"/>
-      <c r="S7" s="171"/>
-      <c r="T7" s="171"/>
-      <c r="U7" s="171"/>
-      <c r="V7" s="172"/>
+      <c r="P7" s="174"/>
+      <c r="Q7" s="174"/>
+      <c r="R7" s="174"/>
+      <c r="S7" s="174"/>
+      <c r="T7" s="174"/>
+      <c r="U7" s="174"/>
+      <c r="V7" s="175"/>
       <c r="W7" s="159" t="s">
         <v>22</v>
       </c>
-      <c r="X7" s="165" t="s">
+      <c r="X7" s="182" t="s">
         <v>23</v>
       </c>
-      <c r="Y7" s="165" t="s">
+      <c r="Y7" s="182" t="s">
         <v>24</v>
       </c>
-      <c r="Z7" s="166" t="s">
+      <c r="Z7" s="183" t="s">
         <v>25</v>
       </c>
       <c r="AA7" s="159" t="s">
@@ -2195,30 +2191,30 @@
       <c r="AB7" s="159" t="s">
         <v>27</v>
       </c>
-      <c r="AC7" s="167" t="s">
+      <c r="AC7" s="184" t="s">
         <v>28</v>
       </c>
-      <c r="AD7" s="167"/>
-      <c r="AE7" s="167"/>
-      <c r="AF7" s="164" t="s">
+      <c r="AD7" s="184"/>
+      <c r="AE7" s="184"/>
+      <c r="AF7" s="170" t="s">
         <v>29</v>
       </c>
-      <c r="AG7" s="161" t="s">
+      <c r="AG7" s="185" t="s">
         <v>30</v>
       </c>
-      <c r="AH7" s="161" t="s">
+      <c r="AH7" s="185" t="s">
         <v>31</v>
       </c>
-      <c r="AI7" s="161" t="s">
+      <c r="AI7" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="AJ7" s="161" t="s">
+      <c r="AJ7" s="185" t="s">
         <v>33</v>
       </c>
-      <c r="AK7" s="164" t="s">
+      <c r="AK7" s="170" t="s">
         <v>34</v>
       </c>
-      <c r="AL7" s="164" t="s">
+      <c r="AL7" s="170" t="s">
         <v>35</v>
       </c>
       <c r="AM7" s="159" t="s">
@@ -2227,14 +2223,14 @@
       <c r="AN7" s="159" t="s">
         <v>37</v>
       </c>
-      <c r="AO7" s="161" t="s">
+      <c r="AO7" s="185" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="160"/>
-      <c r="B8" s="186"/>
-      <c r="C8" s="187"/>
+      <c r="B8" s="168"/>
+      <c r="C8" s="169"/>
       <c r="D8" s="160"/>
       <c r="E8" s="160"/>
       <c r="F8" s="160"/>
@@ -2245,39 +2241,39 @@
       <c r="K8" s="160"/>
       <c r="L8" s="160"/>
       <c r="M8" s="160"/>
-      <c r="N8" s="169"/>
-      <c r="O8" s="173"/>
-      <c r="P8" s="174"/>
-      <c r="Q8" s="174"/>
-      <c r="R8" s="174"/>
-      <c r="S8" s="174"/>
-      <c r="T8" s="174"/>
-      <c r="U8" s="174"/>
-      <c r="V8" s="175"/>
+      <c r="N8" s="172"/>
+      <c r="O8" s="176"/>
+      <c r="P8" s="177"/>
+      <c r="Q8" s="177"/>
+      <c r="R8" s="177"/>
+      <c r="S8" s="177"/>
+      <c r="T8" s="177"/>
+      <c r="U8" s="177"/>
+      <c r="V8" s="178"/>
       <c r="W8" s="160"/>
       <c r="X8" s="160"/>
       <c r="Y8" s="160"/>
       <c r="Z8" s="160"/>
       <c r="AA8" s="160"/>
       <c r="AB8" s="160"/>
-      <c r="AC8" s="167"/>
-      <c r="AD8" s="167"/>
-      <c r="AE8" s="167"/>
+      <c r="AC8" s="184"/>
+      <c r="AD8" s="184"/>
+      <c r="AE8" s="184"/>
       <c r="AF8" s="160"/>
-      <c r="AG8" s="163"/>
-      <c r="AH8" s="163"/>
-      <c r="AI8" s="161"/>
-      <c r="AJ8" s="163"/>
+      <c r="AG8" s="187"/>
+      <c r="AH8" s="187"/>
+      <c r="AI8" s="185"/>
+      <c r="AJ8" s="187"/>
       <c r="AK8" s="160"/>
-      <c r="AL8" s="164"/>
+      <c r="AL8" s="170"/>
       <c r="AM8" s="160"/>
       <c r="AN8" s="159"/>
-      <c r="AO8" s="162"/>
+      <c r="AO8" s="186"/>
     </row>
     <row r="9" spans="1:44" ht="104.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="160"/>
-      <c r="B9" s="186"/>
-      <c r="C9" s="187"/>
+      <c r="B9" s="168"/>
+      <c r="C9" s="169"/>
       <c r="D9" s="160"/>
       <c r="E9" s="160"/>
       <c r="F9" s="160"/>
@@ -2288,15 +2284,15 @@
       <c r="K9" s="160"/>
       <c r="L9" s="160"/>
       <c r="M9" s="160"/>
-      <c r="N9" s="169"/>
-      <c r="O9" s="176"/>
-      <c r="P9" s="177"/>
-      <c r="Q9" s="177"/>
-      <c r="R9" s="177"/>
-      <c r="S9" s="177"/>
-      <c r="T9" s="177"/>
-      <c r="U9" s="177"/>
-      <c r="V9" s="178"/>
+      <c r="N9" s="172"/>
+      <c r="O9" s="179"/>
+      <c r="P9" s="180"/>
+      <c r="Q9" s="180"/>
+      <c r="R9" s="180"/>
+      <c r="S9" s="180"/>
+      <c r="T9" s="180"/>
+      <c r="U9" s="180"/>
+      <c r="V9" s="181"/>
       <c r="W9" s="160"/>
       <c r="X9" s="160"/>
       <c r="Y9" s="160"/>
@@ -2313,15 +2309,15 @@
         <v>41</v>
       </c>
       <c r="AF9" s="160"/>
-      <c r="AG9" s="163"/>
-      <c r="AH9" s="163"/>
-      <c r="AI9" s="161"/>
-      <c r="AJ9" s="163"/>
+      <c r="AG9" s="187"/>
+      <c r="AH9" s="187"/>
+      <c r="AI9" s="185"/>
+      <c r="AJ9" s="187"/>
       <c r="AK9" s="160"/>
-      <c r="AL9" s="164"/>
+      <c r="AL9" s="170"/>
       <c r="AM9" s="160"/>
       <c r="AN9" s="159"/>
-      <c r="AO9" s="162"/>
+      <c r="AO9" s="186"/>
       <c r="AP9">
         <f>Z11/W11</f>
         <v>0.64927786254388997</v>
@@ -8886,6 +8882,27 @@
     <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AO7:AO9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AE8"/>
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A2:AB2"/>
@@ -8902,27 +8919,6 @@
     <mergeCell ref="H7:H9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:J9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AE8"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AO7:AO9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AL7:AL9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/report/bao-cao.xlsx
+++ b/report/bao-cao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HXuan\BaocaoGiaingan\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F48674-6CAF-4726-8F26-2B51D5319317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57579E4D-776A-462F-BCF0-6623A7763D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{BF3132C5-3821-4F06-A909-D3A92B5D6441}"/>
   </bookViews>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="156">
   <si>
     <t xml:space="preserve">          UBND PHƯỜNG BÌNH THẠNH</t>
   </si>
@@ -510,6 +508,9 @@
   </si>
   <si>
     <t>Nguyễn Phi Hoàng</t>
+  </si>
+  <si>
+    <t>Cán Bộ Kỹ Thuật</t>
   </si>
 </sst>
 </file>
@@ -813,7 +814,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -860,6 +861,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor rgb="FFB4C6E7"/>
       </patternFill>
     </fill>
   </fills>
@@ -998,7 +1011,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1140,9 +1153,6 @@
     <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1371,7 +1381,6 @@
     <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="40" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1473,6 +1482,28 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1809,16 +1840,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F12D5F66-05D5-4ED1-A0A9-0ABADD06F7DE}">
-  <dimension ref="A1:AR983"/>
+  <dimension ref="A1:AS983"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
-    <col min="2" max="2" width="33" style="154" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" style="118" customWidth="1"/>
-    <col min="4" max="11" width="8.5703125" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" customWidth="1"/>
-    <col min="14" max="14" width="11.5703125" style="118" customWidth="1"/>
+    <col min="2" max="2" width="33" style="152" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" style="117" customWidth="1"/>
+    <col min="4" max="11" width="8.5703125" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" style="117" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="13.140625" customWidth="1"/>
     <col min="16" max="17" width="10.5703125" customWidth="1"/>
     <col min="18" max="18" width="9.5703125" customWidth="1"/>
@@ -1827,8 +1858,9 @@
     <col min="21" max="21" width="11.140625" customWidth="1"/>
     <col min="22" max="22" width="8.5703125" customWidth="1"/>
     <col min="23" max="23" width="14.140625" customWidth="1"/>
-    <col min="24" max="24" width="10" style="155" customWidth="1"/>
-    <col min="25" max="26" width="11.140625" style="155" customWidth="1"/>
+    <col min="24" max="24" width="10" style="153" customWidth="1"/>
+    <col min="25" max="25" width="11.140625" style="193" customWidth="1"/>
+    <col min="26" max="26" width="11.140625" style="153" customWidth="1"/>
     <col min="27" max="27" width="11.42578125" customWidth="1"/>
     <col min="28" max="28" width="10.5703125" customWidth="1"/>
     <col min="29" max="29" width="10.85546875" style="47" customWidth="1"/>
@@ -1842,41 +1874,41 @@
     <col min="38" max="38" width="17.5703125" customWidth="1"/>
     <col min="39" max="39" width="12.42578125" customWidth="1"/>
     <col min="40" max="40" width="15.85546875" customWidth="1"/>
-    <col min="41" max="41" width="15" style="118" customWidth="1"/>
+    <col min="41" max="41" width="15" style="117" customWidth="1"/>
     <col min="42" max="44" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="161" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="162"/>
-      <c r="G1" s="162"/>
-      <c r="H1" s="162"/>
-      <c r="I1" s="162"/>
-      <c r="J1" s="162"/>
-      <c r="K1" s="162"/>
-      <c r="L1" s="162"/>
-      <c r="M1" s="162"/>
-      <c r="N1" s="162"/>
-      <c r="O1" s="162"/>
-      <c r="P1" s="162"/>
-      <c r="Q1" s="162"/>
-      <c r="R1" s="162"/>
-      <c r="S1" s="162"/>
-      <c r="T1" s="162"/>
-      <c r="U1" s="162"/>
-      <c r="V1" s="162"/>
-      <c r="W1" s="162"/>
-      <c r="X1" s="162"/>
-      <c r="Y1" s="162"/>
-      <c r="Z1" s="162"/>
-      <c r="AA1" s="162"/>
-      <c r="AB1" s="162"/>
+    <row r="1" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="159" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
+      <c r="J1" s="160"/>
+      <c r="K1" s="160"/>
+      <c r="L1" s="160"/>
+      <c r="M1" s="160"/>
+      <c r="N1" s="160"/>
+      <c r="O1" s="160"/>
+      <c r="P1" s="160"/>
+      <c r="Q1" s="160"/>
+      <c r="R1" s="160"/>
+      <c r="S1" s="160"/>
+      <c r="T1" s="160"/>
+      <c r="U1" s="160"/>
+      <c r="V1" s="160"/>
+      <c r="W1" s="160"/>
+      <c r="X1" s="160"/>
+      <c r="Y1" s="194"/>
+      <c r="Z1" s="160"/>
+      <c r="AA1" s="160"/>
+      <c r="AB1" s="160"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
@@ -1895,37 +1927,37 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:44" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="163" t="s">
+    <row r="2" spans="1:45" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="161" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="162"/>
-      <c r="C2" s="162"/>
-      <c r="D2" s="162"/>
-      <c r="E2" s="162"/>
-      <c r="F2" s="162"/>
-      <c r="G2" s="162"/>
-      <c r="H2" s="162"/>
-      <c r="I2" s="162"/>
-      <c r="J2" s="162"/>
-      <c r="K2" s="162"/>
-      <c r="L2" s="162"/>
-      <c r="M2" s="162"/>
-      <c r="N2" s="162"/>
-      <c r="O2" s="162"/>
-      <c r="P2" s="162"/>
-      <c r="Q2" s="162"/>
-      <c r="R2" s="162"/>
-      <c r="S2" s="162"/>
-      <c r="T2" s="162"/>
-      <c r="U2" s="162"/>
-      <c r="V2" s="162"/>
-      <c r="W2" s="162"/>
-      <c r="X2" s="162"/>
-      <c r="Y2" s="162"/>
-      <c r="Z2" s="162"/>
-      <c r="AA2" s="162"/>
-      <c r="AB2" s="162"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
+      <c r="M2" s="160"/>
+      <c r="N2" s="160"/>
+      <c r="O2" s="160"/>
+      <c r="P2" s="160"/>
+      <c r="Q2" s="160"/>
+      <c r="R2" s="160"/>
+      <c r="S2" s="160"/>
+      <c r="T2" s="160"/>
+      <c r="U2" s="160"/>
+      <c r="V2" s="160"/>
+      <c r="W2" s="160"/>
+      <c r="X2" s="160"/>
+      <c r="Y2" s="194"/>
+      <c r="Z2" s="160"/>
+      <c r="AA2" s="160"/>
+      <c r="AB2" s="160"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
       <c r="AE2" s="1"/>
@@ -1940,7 +1972,7 @@
       <c r="AN2" s="4"/>
       <c r="AO2" s="6"/>
     </row>
-    <row r="3" spans="1:44" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="9"/>
@@ -1965,7 +1997,7 @@
       <c r="V3" s="12"/>
       <c r="W3" s="14"/>
       <c r="X3" s="15"/>
-      <c r="Y3" s="15"/>
+      <c r="Y3" s="195"/>
       <c r="Z3" s="15"/>
       <c r="AA3" s="16"/>
       <c r="AB3" s="16"/>
@@ -1983,97 +2015,97 @@
       <c r="AN3" s="4"/>
       <c r="AO3" s="5"/>
     </row>
-    <row r="4" spans="1:44" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="164" t="s">
+    <row r="4" spans="1:45" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="162" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="162"/>
-      <c r="C4" s="162"/>
-      <c r="D4" s="162"/>
-      <c r="E4" s="162"/>
-      <c r="F4" s="162"/>
-      <c r="G4" s="162"/>
-      <c r="H4" s="162"/>
-      <c r="I4" s="162"/>
-      <c r="J4" s="162"/>
-      <c r="K4" s="162"/>
-      <c r="L4" s="162"/>
-      <c r="M4" s="162"/>
-      <c r="N4" s="162"/>
-      <c r="O4" s="162"/>
-      <c r="P4" s="162"/>
-      <c r="Q4" s="162"/>
-      <c r="R4" s="162"/>
-      <c r="S4" s="162"/>
-      <c r="T4" s="162"/>
-      <c r="U4" s="162"/>
-      <c r="V4" s="162"/>
-      <c r="W4" s="162"/>
-      <c r="X4" s="162"/>
-      <c r="Y4" s="162"/>
-      <c r="Z4" s="162"/>
-      <c r="AA4" s="162"/>
-      <c r="AB4" s="162"/>
-      <c r="AC4" s="162"/>
-      <c r="AD4" s="162"/>
-      <c r="AE4" s="162"/>
-      <c r="AF4" s="162"/>
-      <c r="AG4" s="162"/>
-      <c r="AH4" s="162"/>
-      <c r="AI4" s="162"/>
-      <c r="AJ4" s="162"/>
-      <c r="AK4" s="162"/>
-      <c r="AL4" s="162"/>
-      <c r="AM4" s="162"/>
-      <c r="AN4" s="162"/>
-      <c r="AO4" s="162"/>
+      <c r="B4" s="160"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="160"/>
+      <c r="E4" s="160"/>
+      <c r="F4" s="160"/>
+      <c r="G4" s="160"/>
+      <c r="H4" s="160"/>
+      <c r="I4" s="160"/>
+      <c r="J4" s="160"/>
+      <c r="K4" s="160"/>
+      <c r="L4" s="160"/>
+      <c r="M4" s="160"/>
+      <c r="N4" s="160"/>
+      <c r="O4" s="160"/>
+      <c r="P4" s="160"/>
+      <c r="Q4" s="160"/>
+      <c r="R4" s="160"/>
+      <c r="S4" s="160"/>
+      <c r="T4" s="160"/>
+      <c r="U4" s="160"/>
+      <c r="V4" s="160"/>
+      <c r="W4" s="160"/>
+      <c r="X4" s="160"/>
+      <c r="Y4" s="194"/>
+      <c r="Z4" s="160"/>
+      <c r="AA4" s="160"/>
+      <c r="AB4" s="160"/>
+      <c r="AC4" s="160"/>
+      <c r="AD4" s="160"/>
+      <c r="AE4" s="160"/>
+      <c r="AF4" s="160"/>
+      <c r="AG4" s="160"/>
+      <c r="AH4" s="160"/>
+      <c r="AI4" s="160"/>
+      <c r="AJ4" s="160"/>
+      <c r="AK4" s="160"/>
+      <c r="AL4" s="160"/>
+      <c r="AM4" s="160"/>
+      <c r="AN4" s="160"/>
+      <c r="AO4" s="160"/>
     </row>
-    <row r="5" spans="1:44" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="165" t="s">
+    <row r="5" spans="1:45" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A5" s="163" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="162"/>
-      <c r="C5" s="162"/>
-      <c r="D5" s="162"/>
-      <c r="E5" s="162"/>
-      <c r="F5" s="162"/>
-      <c r="G5" s="162"/>
-      <c r="H5" s="162"/>
-      <c r="I5" s="162"/>
-      <c r="J5" s="162"/>
-      <c r="K5" s="162"/>
-      <c r="L5" s="162"/>
-      <c r="M5" s="162"/>
-      <c r="N5" s="162"/>
-      <c r="O5" s="162"/>
-      <c r="P5" s="162"/>
-      <c r="Q5" s="162"/>
-      <c r="R5" s="162"/>
-      <c r="S5" s="162"/>
-      <c r="T5" s="162"/>
-      <c r="U5" s="162"/>
-      <c r="V5" s="162"/>
-      <c r="W5" s="162"/>
-      <c r="X5" s="162"/>
-      <c r="Y5" s="162"/>
-      <c r="Z5" s="162"/>
-      <c r="AA5" s="162"/>
-      <c r="AB5" s="162"/>
-      <c r="AC5" s="162"/>
-      <c r="AD5" s="162"/>
-      <c r="AE5" s="162"/>
-      <c r="AF5" s="162"/>
-      <c r="AG5" s="162"/>
-      <c r="AH5" s="162"/>
-      <c r="AI5" s="162"/>
-      <c r="AJ5" s="162"/>
-      <c r="AK5" s="162"/>
-      <c r="AL5" s="162"/>
-      <c r="AM5" s="162"/>
-      <c r="AN5" s="162"/>
-      <c r="AO5" s="162"/>
+      <c r="B5" s="160"/>
+      <c r="C5" s="160"/>
+      <c r="D5" s="160"/>
+      <c r="E5" s="160"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="160"/>
+      <c r="H5" s="160"/>
+      <c r="I5" s="160"/>
+      <c r="J5" s="160"/>
+      <c r="K5" s="160"/>
+      <c r="L5" s="160"/>
+      <c r="M5" s="160"/>
+      <c r="N5" s="160"/>
+      <c r="O5" s="160"/>
+      <c r="P5" s="160"/>
+      <c r="Q5" s="160"/>
+      <c r="R5" s="160"/>
+      <c r="S5" s="160"/>
+      <c r="T5" s="160"/>
+      <c r="U5" s="160"/>
+      <c r="V5" s="160"/>
+      <c r="W5" s="160"/>
+      <c r="X5" s="160"/>
+      <c r="Y5" s="194"/>
+      <c r="Z5" s="160"/>
+      <c r="AA5" s="160"/>
+      <c r="AB5" s="160"/>
+      <c r="AC5" s="160"/>
+      <c r="AD5" s="160"/>
+      <c r="AE5" s="160"/>
+      <c r="AF5" s="160"/>
+      <c r="AG5" s="160"/>
+      <c r="AH5" s="160"/>
+      <c r="AI5" s="160"/>
+      <c r="AJ5" s="160"/>
+      <c r="AK5" s="160"/>
+      <c r="AL5" s="160"/>
+      <c r="AM5" s="160"/>
+      <c r="AN5" s="160"/>
+      <c r="AO5" s="160"/>
     </row>
-    <row r="6" spans="1:44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16"/>
       <c r="B6" s="17"/>
       <c r="C6" s="18"/>
@@ -2100,205 +2132,209 @@
       <c r="X6" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="Y6" s="15"/>
+      <c r="Y6" s="195"/>
       <c r="Z6" s="24"/>
       <c r="AA6" s="25"/>
       <c r="AB6" s="16"/>
       <c r="AC6" s="16"/>
       <c r="AD6" s="16"/>
       <c r="AE6" s="16"/>
-      <c r="AF6" s="166" t="s">
+      <c r="AF6" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="AG6" s="167"/>
-      <c r="AH6" s="167"/>
-      <c r="AI6" s="167"/>
-      <c r="AJ6" s="167"/>
-      <c r="AK6" s="167"/>
-      <c r="AL6" s="167"/>
-      <c r="AM6" s="167"/>
-      <c r="AN6" s="167"/>
-      <c r="AO6" s="167"/>
+      <c r="AG6" s="165"/>
+      <c r="AH6" s="165"/>
+      <c r="AI6" s="165"/>
+      <c r="AJ6" s="165"/>
+      <c r="AK6" s="165"/>
+      <c r="AL6" s="165"/>
+      <c r="AM6" s="165"/>
+      <c r="AN6" s="165"/>
+      <c r="AO6" s="165"/>
     </row>
-    <row r="7" spans="1:44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="159" t="s">
+    <row r="7" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="157" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="159" t="s">
+      <c r="B7" s="157" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="169" t="s">
+      <c r="C7" s="167" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="159" t="s">
+      <c r="D7" s="157" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="159" t="s">
+      <c r="E7" s="157" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="159" t="s">
+      <c r="F7" s="157" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="159" t="s">
+      <c r="G7" s="157" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="159" t="s">
+      <c r="H7" s="157" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="159" t="s">
+      <c r="I7" s="157" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="159" t="s">
+      <c r="J7" s="157" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="159" t="s">
+      <c r="K7" s="157" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="171" t="s">
+      <c r="L7" s="169" t="s">
         <v>18</v>
       </c>
-      <c r="M7" s="159" t="s">
+      <c r="M7" s="157" t="s">
         <v>19</v>
       </c>
-      <c r="N7" s="159" t="s">
+      <c r="N7" s="157" t="s">
         <v>20</v>
       </c>
-      <c r="O7" s="173" t="s">
+      <c r="O7" s="171" t="s">
         <v>21</v>
       </c>
-      <c r="P7" s="174"/>
-      <c r="Q7" s="174"/>
-      <c r="R7" s="174"/>
-      <c r="S7" s="174"/>
-      <c r="T7" s="174"/>
-      <c r="U7" s="174"/>
-      <c r="V7" s="175"/>
-      <c r="W7" s="159" t="s">
+      <c r="P7" s="172"/>
+      <c r="Q7" s="172"/>
+      <c r="R7" s="172"/>
+      <c r="S7" s="172"/>
+      <c r="T7" s="172"/>
+      <c r="U7" s="172"/>
+      <c r="V7" s="173"/>
+      <c r="W7" s="157" t="s">
         <v>22</v>
       </c>
-      <c r="X7" s="182" t="s">
+      <c r="X7" s="180" t="s">
         <v>23</v>
       </c>
-      <c r="Y7" s="182" t="s">
+      <c r="Y7" s="180" t="s">
         <v>24</v>
       </c>
-      <c r="Z7" s="183" t="s">
+      <c r="Z7" s="181" t="s">
         <v>25</v>
       </c>
-      <c r="AA7" s="159" t="s">
+      <c r="AA7" s="157" t="s">
         <v>26</v>
       </c>
-      <c r="AB7" s="159" t="s">
+      <c r="AB7" s="157" t="s">
         <v>27</v>
       </c>
-      <c r="AC7" s="184" t="s">
+      <c r="AC7" s="182" t="s">
         <v>28</v>
       </c>
-      <c r="AD7" s="184"/>
-      <c r="AE7" s="184"/>
-      <c r="AF7" s="170" t="s">
+      <c r="AD7" s="182"/>
+      <c r="AE7" s="182"/>
+      <c r="AF7" s="168" t="s">
         <v>29</v>
       </c>
-      <c r="AG7" s="185" t="s">
+      <c r="AG7" s="183" t="s">
         <v>30</v>
       </c>
-      <c r="AH7" s="185" t="s">
+      <c r="AH7" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="AI7" s="185" t="s">
+      <c r="AI7" s="183" t="s">
         <v>32</v>
       </c>
-      <c r="AJ7" s="185" t="s">
+      <c r="AJ7" s="183" t="s">
         <v>33</v>
       </c>
-      <c r="AK7" s="170" t="s">
+      <c r="AK7" s="168" t="s">
         <v>34</v>
       </c>
-      <c r="AL7" s="170" t="s">
+      <c r="AL7" s="168" t="s">
         <v>35</v>
       </c>
-      <c r="AM7" s="159" t="s">
+      <c r="AM7" s="157" t="s">
         <v>36</v>
       </c>
-      <c r="AN7" s="159" t="s">
+      <c r="AN7" s="157" t="s">
         <v>37</v>
       </c>
-      <c r="AO7" s="185" t="s">
+      <c r="AO7" s="157" t="s">
+        <v>155</v>
+      </c>
+      <c r="AS7" s="183" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="160"/>
-      <c r="B8" s="168"/>
-      <c r="C8" s="169"/>
-      <c r="D8" s="160"/>
-      <c r="E8" s="160"/>
-      <c r="F8" s="160"/>
-      <c r="G8" s="160"/>
-      <c r="H8" s="160"/>
-      <c r="I8" s="160"/>
-      <c r="J8" s="160"/>
-      <c r="K8" s="160"/>
-      <c r="L8" s="160"/>
-      <c r="M8" s="160"/>
-      <c r="N8" s="172"/>
-      <c r="O8" s="176"/>
-      <c r="P8" s="177"/>
-      <c r="Q8" s="177"/>
-      <c r="R8" s="177"/>
-      <c r="S8" s="177"/>
-      <c r="T8" s="177"/>
-      <c r="U8" s="177"/>
-      <c r="V8" s="178"/>
-      <c r="W8" s="160"/>
-      <c r="X8" s="160"/>
-      <c r="Y8" s="160"/>
-      <c r="Z8" s="160"/>
-      <c r="AA8" s="160"/>
-      <c r="AB8" s="160"/>
-      <c r="AC8" s="184"/>
-      <c r="AD8" s="184"/>
-      <c r="AE8" s="184"/>
-      <c r="AF8" s="160"/>
-      <c r="AG8" s="187"/>
-      <c r="AH8" s="187"/>
-      <c r="AI8" s="185"/>
-      <c r="AJ8" s="187"/>
-      <c r="AK8" s="160"/>
-      <c r="AL8" s="170"/>
-      <c r="AM8" s="160"/>
-      <c r="AN8" s="159"/>
-      <c r="AO8" s="186"/>
+    <row r="8" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="158"/>
+      <c r="B8" s="166"/>
+      <c r="C8" s="167"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="158"/>
+      <c r="F8" s="158"/>
+      <c r="G8" s="158"/>
+      <c r="H8" s="158"/>
+      <c r="I8" s="158"/>
+      <c r="J8" s="158"/>
+      <c r="K8" s="158"/>
+      <c r="L8" s="158"/>
+      <c r="M8" s="158"/>
+      <c r="N8" s="170"/>
+      <c r="O8" s="174"/>
+      <c r="P8" s="175"/>
+      <c r="Q8" s="175"/>
+      <c r="R8" s="175"/>
+      <c r="S8" s="175"/>
+      <c r="T8" s="175"/>
+      <c r="U8" s="175"/>
+      <c r="V8" s="176"/>
+      <c r="W8" s="158"/>
+      <c r="X8" s="158"/>
+      <c r="Y8" s="158"/>
+      <c r="Z8" s="158"/>
+      <c r="AA8" s="158"/>
+      <c r="AB8" s="158"/>
+      <c r="AC8" s="182"/>
+      <c r="AD8" s="182"/>
+      <c r="AE8" s="182"/>
+      <c r="AF8" s="158"/>
+      <c r="AG8" s="185"/>
+      <c r="AH8" s="185"/>
+      <c r="AI8" s="183"/>
+      <c r="AJ8" s="185"/>
+      <c r="AK8" s="158"/>
+      <c r="AL8" s="168"/>
+      <c r="AM8" s="158"/>
+      <c r="AN8" s="157"/>
+      <c r="AO8" s="157"/>
+      <c r="AS8" s="184"/>
     </row>
-    <row r="9" spans="1:44" ht="104.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="160"/>
-      <c r="B9" s="168"/>
-      <c r="C9" s="169"/>
-      <c r="D9" s="160"/>
-      <c r="E9" s="160"/>
-      <c r="F9" s="160"/>
-      <c r="G9" s="160"/>
-      <c r="H9" s="160"/>
-      <c r="I9" s="160"/>
-      <c r="J9" s="160"/>
-      <c r="K9" s="160"/>
-      <c r="L9" s="160"/>
-      <c r="M9" s="160"/>
-      <c r="N9" s="172"/>
-      <c r="O9" s="179"/>
-      <c r="P9" s="180"/>
-      <c r="Q9" s="180"/>
-      <c r="R9" s="180"/>
-      <c r="S9" s="180"/>
-      <c r="T9" s="180"/>
-      <c r="U9" s="180"/>
-      <c r="V9" s="181"/>
-      <c r="W9" s="160"/>
-      <c r="X9" s="160"/>
-      <c r="Y9" s="160"/>
-      <c r="Z9" s="160"/>
-      <c r="AA9" s="160"/>
-      <c r="AB9" s="160"/>
+    <row r="9" spans="1:45" ht="104.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="158"/>
+      <c r="B9" s="166"/>
+      <c r="C9" s="167"/>
+      <c r="D9" s="158"/>
+      <c r="E9" s="158"/>
+      <c r="F9" s="158"/>
+      <c r="G9" s="158"/>
+      <c r="H9" s="158"/>
+      <c r="I9" s="158"/>
+      <c r="J9" s="158"/>
+      <c r="K9" s="158"/>
+      <c r="L9" s="158"/>
+      <c r="M9" s="158"/>
+      <c r="N9" s="170"/>
+      <c r="O9" s="177"/>
+      <c r="P9" s="178"/>
+      <c r="Q9" s="178"/>
+      <c r="R9" s="178"/>
+      <c r="S9" s="178"/>
+      <c r="T9" s="178"/>
+      <c r="U9" s="178"/>
+      <c r="V9" s="179"/>
+      <c r="W9" s="158"/>
+      <c r="X9" s="158"/>
+      <c r="Y9" s="158"/>
+      <c r="Z9" s="158"/>
+      <c r="AA9" s="158"/>
+      <c r="AB9" s="158"/>
       <c r="AC9" s="26" t="s">
         <v>39</v>
       </c>
@@ -2308,25 +2344,26 @@
       <c r="AE9" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="AF9" s="160"/>
-      <c r="AG9" s="187"/>
-      <c r="AH9" s="187"/>
-      <c r="AI9" s="185"/>
-      <c r="AJ9" s="187"/>
-      <c r="AK9" s="160"/>
-      <c r="AL9" s="170"/>
-      <c r="AM9" s="160"/>
-      <c r="AN9" s="159"/>
-      <c r="AO9" s="186"/>
+      <c r="AF9" s="158"/>
+      <c r="AG9" s="185"/>
+      <c r="AH9" s="185"/>
+      <c r="AI9" s="183"/>
+      <c r="AJ9" s="185"/>
+      <c r="AK9" s="158"/>
+      <c r="AL9" s="168"/>
+      <c r="AM9" s="158"/>
+      <c r="AN9" s="157"/>
+      <c r="AO9" s="157"/>
       <c r="AP9">
         <f>Z11/W11</f>
-        <v>0.64927786254388997</v>
+        <v>0.6571510184673206</v>
       </c>
       <c r="AR9">
         <v>27</v>
       </c>
+      <c r="AS9" s="184"/>
     </row>
-    <row r="10" spans="1:44" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:45" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="27">
         <v>1</v>
       </c>
@@ -2375,7 +2412,7 @@
         <v>5</v>
       </c>
       <c r="X10" s="30"/>
-      <c r="Y10" s="30"/>
+      <c r="Y10" s="186"/>
       <c r="Z10" s="30">
         <v>6</v>
       </c>
@@ -2412,7 +2449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:44" s="47" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:45" s="47" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34"/>
       <c r="B11" s="35" t="s">
         <v>49</v>
@@ -2501,21 +2538,21 @@
       <c r="X11" s="37">
         <v>654048.10699999996</v>
       </c>
-      <c r="Y11" s="37">
+      <c r="Y11" s="187">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7931</v>
       </c>
       <c r="Z11" s="37">
         <f>SUBTOTAL(9,Z12:Z73)</f>
-        <v>654048.10699999996</v>
+        <v>661979.10699999996</v>
       </c>
       <c r="AA11" s="39">
         <f>Z11/W11</f>
-        <v>0.64927786254388997</v>
+        <v>0.6571510184673206</v>
       </c>
       <c r="AB11" s="39">
         <f>Z11/N11</f>
-        <v>0.73429147992635169</v>
+        <v>0.74319551261900485</v>
       </c>
       <c r="AC11" s="40">
         <f>SUM(AC12:AC73)</f>
@@ -2530,19 +2567,19 @@
       </c>
       <c r="AF11" s="37">
         <f>W11-Z11</f>
-        <v>353298.89300000004</v>
+        <v>345367.89300000004</v>
       </c>
       <c r="AG11" s="37">
         <f>X11-AA11</f>
-        <v>654047.45772213745</v>
+        <v>654047.44984898146</v>
       </c>
       <c r="AH11" s="37">
         <f>Y11-AB11</f>
-        <v>-0.73429147992635169</v>
+        <v>7930.2568044873806</v>
       </c>
       <c r="AI11" s="37">
         <f>Z11-AC11</f>
-        <v>597008.10699999996</v>
+        <v>604939.10699999996</v>
       </c>
       <c r="AJ11" s="41">
         <f>SUM(AJ12:AJ66)</f>
@@ -2550,28 +2587,28 @@
       </c>
       <c r="AK11" s="42">
         <f>W11-Z11-AJ11</f>
-        <v>28538.89300000004</v>
+        <v>20607.89300000004</v>
       </c>
       <c r="AL11" s="43">
         <f>(Z11+AJ11)/W11</f>
-        <v>0.97166925299822204</v>
+        <v>0.97954240892165256</v>
       </c>
       <c r="AM11" s="39"/>
       <c r="AN11" s="40">
         <f>SUM(AN12:AN66)</f>
-        <v>304793.70300000004</v>
+        <v>296862.70300000004</v>
       </c>
       <c r="AO11" s="44"/>
       <c r="AP11" s="45">
         <f>W11-Z11</f>
-        <v>353298.89300000004</v>
+        <v>345367.89300000004</v>
       </c>
       <c r="AQ11" s="46">
         <f>Z11+AC11</f>
-        <v>711088.10699999996</v>
+        <v>719019.10699999996</v>
       </c>
     </row>
-    <row r="12" spans="1:44" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:45" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="48" t="s">
         <v>50</v>
       </c>
@@ -2607,113 +2644,113 @@
       <c r="X12" s="58">
         <v>0</v>
       </c>
-      <c r="Y12" s="59"/>
-      <c r="Z12" s="60">
+      <c r="Y12" s="188"/>
+      <c r="Z12" s="59">
         <f>SUM(X12:Y12)</f>
         <v>0</v>
       </c>
-      <c r="AA12" s="61"/>
-      <c r="AB12" s="62"/>
-      <c r="AC12" s="62"/>
-      <c r="AD12" s="63"/>
-      <c r="AE12" s="62"/>
+      <c r="AA12" s="60"/>
+      <c r="AB12" s="61"/>
+      <c r="AC12" s="61"/>
+      <c r="AD12" s="62"/>
+      <c r="AE12" s="61"/>
       <c r="AF12" s="52"/>
-      <c r="AG12" s="64"/>
-      <c r="AH12" s="64"/>
-      <c r="AI12" s="65">
+      <c r="AG12" s="63"/>
+      <c r="AH12" s="63"/>
+      <c r="AI12" s="64">
         <f t="shared" ref="AI12:AI66" si="2">AF12-AG12</f>
         <v>0</v>
       </c>
-      <c r="AJ12" s="66"/>
+      <c r="AJ12" s="65"/>
       <c r="AK12" s="42">
         <f t="shared" ref="AK12:AK67" si="3">W12-Z12-AJ12</f>
         <v>0</v>
       </c>
       <c r="AL12" s="43"/>
-      <c r="AM12" s="66"/>
-      <c r="AN12" s="67"/>
-      <c r="AO12" s="105"/>
-      <c r="AP12" s="68">
+      <c r="AM12" s="65"/>
+      <c r="AN12" s="66"/>
+      <c r="AO12" s="104"/>
+      <c r="AP12" s="67">
         <f>Z11+AJ11</f>
-        <v>978808.10699999996</v>
+        <v>986739.10699999996</v>
       </c>
     </row>
-    <row r="13" spans="1:44" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="69">
+    <row r="13" spans="1:45" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="68">
         <v>1</v>
       </c>
-      <c r="B13" s="70" t="s">
+      <c r="B13" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="71" t="s">
+      <c r="C13" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="72">
+      <c r="D13" s="71">
         <v>10000</v>
       </c>
-      <c r="E13" s="72">
+      <c r="E13" s="71">
         <v>40000</v>
       </c>
-      <c r="F13" s="72">
+      <c r="F13" s="71">
         <v>21000</v>
       </c>
-      <c r="G13" s="72">
+      <c r="G13" s="71">
         <v>9000</v>
       </c>
-      <c r="H13" s="72">
+      <c r="H13" s="71">
         <v>1810</v>
       </c>
-      <c r="I13" s="72">
+      <c r="I13" s="71">
         <v>4000</v>
       </c>
-      <c r="J13" s="72">
+      <c r="J13" s="71">
         <v>1774</v>
       </c>
-      <c r="K13" s="72"/>
+      <c r="K13" s="71"/>
       <c r="L13" s="52">
         <v>70670</v>
       </c>
       <c r="M13" s="53">
         <v>0</v>
       </c>
-      <c r="N13" s="72">
-        <v>0</v>
-      </c>
-      <c r="O13" s="73">
+      <c r="N13" s="71">
+        <v>0</v>
+      </c>
+      <c r="O13" s="72">
         <v>60050</v>
       </c>
-      <c r="P13" s="73"/>
-      <c r="Q13" s="73"/>
-      <c r="R13" s="73"/>
-      <c r="S13" s="74"/>
-      <c r="T13" s="73"/>
-      <c r="U13" s="75">
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="73"/>
+      <c r="T13" s="72"/>
+      <c r="U13" s="74">
         <v>-60050</v>
       </c>
-      <c r="V13" s="76"/>
+      <c r="V13" s="75"/>
       <c r="W13" s="57">
         <f>SUM(O13:V13)</f>
         <v>0</v>
       </c>
-      <c r="X13" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="77"/>
-      <c r="Z13" s="60">
+      <c r="X13" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="189"/>
+      <c r="Z13" s="59">
         <f t="shared" ref="Z13:Z66" si="4">SUM(X13:Y13)</f>
         <v>0</v>
       </c>
-      <c r="AA13" s="78">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="79">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="80"/>
-      <c r="AD13" s="63">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="80">
+      <c r="AA13" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="78">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="79"/>
+      <c r="AD13" s="62">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="79">
         <f>AC13-AD13</f>
         <v>0</v>
       </c>
@@ -2721,13 +2758,13 @@
         <f t="shared" ref="AF13:AF73" si="5">W13-Z13</f>
         <v>0</v>
       </c>
-      <c r="AG13" s="81"/>
-      <c r="AH13" s="81"/>
-      <c r="AI13" s="65">
+      <c r="AG13" s="80"/>
+      <c r="AH13" s="80"/>
+      <c r="AI13" s="64">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AJ13" s="82"/>
+      <c r="AJ13" s="81"/>
       <c r="AK13" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2736,95 +2773,95 @@
         <f t="shared" ref="AL13:AL67" si="6">(Z13+AJ13)/W13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM13" s="83"/>
-      <c r="AN13" s="84">
+      <c r="AM13" s="82"/>
+      <c r="AN13" s="83">
         <f>W13-Z13</f>
         <v>0</v>
       </c>
-      <c r="AO13" s="156" t="s">
+      <c r="AO13" s="154" t="s">
         <v>148</v>
       </c>
-      <c r="AP13" s="85">
+      <c r="AP13" s="84">
         <f>Z11/W11</f>
-        <v>0.64927786254388997</v>
+        <v>0.6571510184673206</v>
       </c>
       <c r="AR13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:44" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="69">
+    <row r="14" spans="1:45" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="68">
         <v>2</v>
       </c>
-      <c r="B14" s="70" t="s">
+      <c r="B14" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="71" t="s">
+      <c r="C14" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="72">
+      <c r="D14" s="71">
         <v>200</v>
       </c>
-      <c r="E14" s="72">
+      <c r="E14" s="71">
         <v>1000</v>
       </c>
-      <c r="F14" s="72">
+      <c r="F14" s="71">
         <v>60000</v>
       </c>
-      <c r="G14" s="72">
+      <c r="G14" s="71">
         <v>3200</v>
       </c>
-      <c r="H14" s="72">
+      <c r="H14" s="71">
         <v>4000</v>
       </c>
-      <c r="I14" s="72">
+      <c r="I14" s="71">
         <v>1000</v>
       </c>
-      <c r="J14" s="72"/>
-      <c r="K14" s="72"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="71"/>
       <c r="L14" s="52"/>
       <c r="M14" s="53">
         <v>0</v>
       </c>
-      <c r="N14" s="72">
-        <v>0</v>
-      </c>
-      <c r="O14" s="73">
+      <c r="N14" s="71">
+        <v>0</v>
+      </c>
+      <c r="O14" s="72">
         <v>39020</v>
       </c>
-      <c r="P14" s="73"/>
-      <c r="Q14" s="73"/>
-      <c r="R14" s="73"/>
-      <c r="S14" s="74"/>
-      <c r="T14" s="73"/>
-      <c r="U14" s="75">
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="73"/>
+      <c r="T14" s="72"/>
+      <c r="U14" s="74">
         <v>-39020</v>
       </c>
-      <c r="V14" s="73"/>
+      <c r="V14" s="72"/>
       <c r="W14" s="57">
         <f>SUM(O14:V14)</f>
         <v>0</v>
       </c>
-      <c r="X14" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="77"/>
-      <c r="Z14" s="60">
+      <c r="X14" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="189"/>
+      <c r="Z14" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA14" s="78">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="79">
+      <c r="AA14" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="78">
         <f>0%</f>
         <v>0</v>
       </c>
-      <c r="AC14" s="80"/>
-      <c r="AD14" s="63">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="80">
+      <c r="AC14" s="79"/>
+      <c r="AD14" s="62">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="79">
         <f t="shared" ref="AE14:AE73" si="7">AC14-AD14</f>
         <v>0</v>
       </c>
@@ -2832,40 +2869,40 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG14" s="81"/>
-      <c r="AH14" s="81"/>
-      <c r="AI14" s="65">
+      <c r="AG14" s="80"/>
+      <c r="AH14" s="80"/>
+      <c r="AI14" s="64">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AJ14" s="86"/>
+      <c r="AJ14" s="85"/>
       <c r="AK14" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AL14" s="87">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="86"/>
-      <c r="AN14" s="84">
+      <c r="AL14" s="86">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="85"/>
+      <c r="AN14" s="83">
         <f>W14-Z14</f>
         <v>0</v>
       </c>
-      <c r="AO14" s="156" t="s">
+      <c r="AO14" s="154" t="s">
         <v>148</v>
       </c>
       <c r="AR14">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:44" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="88" t="s">
+    <row r="15" spans="1:45" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="87" t="s">
         <v>56</v>
       </c>
       <c r="B15" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="89"/>
+      <c r="C15" s="88"/>
       <c r="D15" s="54"/>
       <c r="E15" s="54"/>
       <c r="F15" s="54"/>
@@ -2880,30 +2917,30 @@
       </c>
       <c r="N15" s="54"/>
       <c r="O15" s="54"/>
-      <c r="P15" s="73"/>
-      <c r="Q15" s="73"/>
-      <c r="R15" s="73"/>
-      <c r="S15" s="74"/>
-      <c r="T15" s="73"/>
-      <c r="U15" s="73"/>
-      <c r="V15" s="73"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="73"/>
+      <c r="T15" s="72"/>
+      <c r="U15" s="72"/>
+      <c r="V15" s="72"/>
       <c r="W15" s="57">
         <f t="shared" ref="W15:W74" si="8">SUM(O15:V15)</f>
         <v>0</v>
       </c>
-      <c r="X15" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="77"/>
-      <c r="Z15" s="60">
+      <c r="X15" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="189"/>
+      <c r="Z15" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA15" s="78"/>
-      <c r="AB15" s="79"/>
-      <c r="AC15" s="80"/>
-      <c r="AD15" s="63"/>
-      <c r="AE15" s="80">
+      <c r="AA15" s="77"/>
+      <c r="AB15" s="78"/>
+      <c r="AC15" s="79"/>
+      <c r="AD15" s="62"/>
+      <c r="AE15" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -2911,89 +2948,89 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG15" s="81"/>
-      <c r="AH15" s="81"/>
-      <c r="AI15" s="65">
+      <c r="AG15" s="80"/>
+      <c r="AH15" s="80"/>
+      <c r="AI15" s="64">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AJ15" s="86"/>
+      <c r="AJ15" s="85"/>
       <c r="AK15" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AL15" s="43"/>
-      <c r="AM15" s="86"/>
-      <c r="AN15" s="81"/>
+      <c r="AM15" s="85"/>
+      <c r="AN15" s="80"/>
       <c r="AO15" s="54"/>
       <c r="AR15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:44" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="69">
+    <row r="16" spans="1:45" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="68">
         <v>3</v>
       </c>
-      <c r="B16" s="70" t="s">
+      <c r="B16" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="90" t="s">
+      <c r="C16" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="72"/>
-      <c r="E16" s="72"/>
-      <c r="F16" s="72"/>
-      <c r="G16" s="72"/>
-      <c r="H16" s="72"/>
-      <c r="I16" s="72"/>
-      <c r="J16" s="72">
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="71">
         <v>500</v>
       </c>
-      <c r="K16" s="72">
+      <c r="K16" s="71">
         <v>1302</v>
       </c>
       <c r="L16" s="52"/>
       <c r="M16" s="53">
         <v>1301.9340000000002</v>
       </c>
-      <c r="N16" s="72">
-        <v>0</v>
-      </c>
-      <c r="O16" s="73">
+      <c r="N16" s="71">
+        <v>0</v>
+      </c>
+      <c r="O16" s="72">
         <v>1000</v>
       </c>
-      <c r="P16" s="73"/>
-      <c r="Q16" s="73"/>
-      <c r="R16" s="73"/>
-      <c r="S16" s="73">
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72">
         <v>-1000</v>
       </c>
-      <c r="T16" s="73"/>
-      <c r="U16" s="73"/>
-      <c r="V16" s="73"/>
+      <c r="T16" s="72"/>
+      <c r="U16" s="72"/>
+      <c r="V16" s="72"/>
       <c r="W16" s="57">
         <f>SUM(O16:V16)</f>
         <v>0</v>
       </c>
-      <c r="X16" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="77"/>
-      <c r="Z16" s="60">
+      <c r="X16" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="189"/>
+      <c r="Z16" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA16" s="79">
+      <c r="AA16" s="78">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="AB16" s="79">
+      <c r="AB16" s="78">
         <f>0%</f>
         <v>0</v>
       </c>
-      <c r="AC16" s="80"/>
-      <c r="AD16" s="63"/>
-      <c r="AE16" s="80">
+      <c r="AC16" s="79"/>
+      <c r="AD16" s="62"/>
+      <c r="AE16" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3001,13 +3038,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG16" s="81"/>
-      <c r="AH16" s="81"/>
-      <c r="AI16" s="65">
+      <c r="AG16" s="80"/>
+      <c r="AH16" s="80"/>
+      <c r="AI16" s="64">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AJ16" s="86"/>
+      <c r="AJ16" s="85"/>
       <c r="AK16" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3016,12 +3053,12 @@
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM16" s="86"/>
-      <c r="AN16" s="81">
+      <c r="AM16" s="85"/>
+      <c r="AN16" s="80">
         <f t="shared" ref="AN16" si="9">W16-Z16</f>
         <v>0</v>
       </c>
-      <c r="AO16" s="157" t="s">
+      <c r="AO16" s="155" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3032,119 +3069,119 @@
       <c r="B17" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="90"/>
-      <c r="D17" s="72"/>
-      <c r="E17" s="72"/>
-      <c r="F17" s="72"/>
-      <c r="G17" s="72"/>
-      <c r="H17" s="72"/>
-      <c r="I17" s="72"/>
-      <c r="J17" s="72"/>
-      <c r="K17" s="72"/>
+      <c r="C17" s="89"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
       <c r="L17" s="52"/>
       <c r="M17" s="52"/>
-      <c r="N17" s="72"/>
-      <c r="O17" s="74"/>
-      <c r="P17" s="73"/>
-      <c r="Q17" s="73"/>
-      <c r="R17" s="73"/>
-      <c r="S17" s="74"/>
-      <c r="T17" s="73"/>
-      <c r="U17" s="73"/>
-      <c r="V17" s="73"/>
+      <c r="N17" s="71"/>
+      <c r="O17" s="73"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="73"/>
+      <c r="T17" s="72"/>
+      <c r="U17" s="72"/>
+      <c r="V17" s="72"/>
       <c r="W17" s="57"/>
-      <c r="X17" s="77"/>
-      <c r="Y17" s="77"/>
-      <c r="Z17" s="60"/>
-      <c r="AA17" s="79"/>
-      <c r="AB17" s="79"/>
-      <c r="AC17" s="80"/>
-      <c r="AD17" s="63"/>
-      <c r="AE17" s="80">
+      <c r="X17" s="76"/>
+      <c r="Y17" s="189"/>
+      <c r="Z17" s="59"/>
+      <c r="AA17" s="78"/>
+      <c r="AB17" s="78"/>
+      <c r="AC17" s="79"/>
+      <c r="AD17" s="62"/>
+      <c r="AE17" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AF17" s="52"/>
-      <c r="AG17" s="81"/>
-      <c r="AH17" s="81"/>
-      <c r="AI17" s="65">
+      <c r="AG17" s="80"/>
+      <c r="AH17" s="80"/>
+      <c r="AI17" s="64">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AJ17" s="86"/>
+      <c r="AJ17" s="85"/>
       <c r="AK17" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AL17" s="43"/>
-      <c r="AM17" s="86"/>
-      <c r="AN17" s="81"/>
+      <c r="AM17" s="85"/>
+      <c r="AN17" s="80"/>
       <c r="AO17" s="29"/>
     </row>
     <row r="18" spans="1:44" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="69">
+      <c r="A18" s="68">
         <v>4</v>
       </c>
-      <c r="B18" s="70" t="s">
+      <c r="B18" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="90" t="s">
+      <c r="C18" s="89" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="72"/>
-      <c r="J18" s="72">
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="71">
         <v>50</v>
       </c>
-      <c r="K18" s="72">
+      <c r="K18" s="71">
         <v>800</v>
       </c>
       <c r="L18" s="52"/>
       <c r="M18" s="53">
         <v>794.4</v>
       </c>
-      <c r="N18" s="91">
+      <c r="N18" s="90">
         <v>50</v>
       </c>
-      <c r="O18" s="73">
+      <c r="O18" s="72">
         <v>20</v>
       </c>
-      <c r="P18" s="73"/>
-      <c r="Q18" s="73"/>
-      <c r="R18" s="73"/>
-      <c r="S18" s="73">
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="72">
         <v>30</v>
       </c>
-      <c r="T18" s="73"/>
-      <c r="U18" s="75"/>
-      <c r="V18" s="76"/>
+      <c r="T18" s="72"/>
+      <c r="U18" s="74"/>
+      <c r="V18" s="75"/>
       <c r="W18" s="57">
         <f t="shared" si="8"/>
         <v>50</v>
       </c>
-      <c r="X18" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="77"/>
-      <c r="Z18" s="60">
+      <c r="X18" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="189"/>
+      <c r="Z18" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA18" s="79">
+      <c r="AA18" s="78">
         <f t="shared" ref="AA18:AA21" si="10">Z18/W18</f>
         <v>0</v>
       </c>
-      <c r="AB18" s="79">
+      <c r="AB18" s="78">
         <f t="shared" ref="AB18" si="11">Z18/N18</f>
         <v>0</v>
       </c>
-      <c r="AC18" s="80"/>
-      <c r="AD18" s="63"/>
-      <c r="AE18" s="80">
+      <c r="AC18" s="79"/>
+      <c r="AD18" s="62"/>
+      <c r="AE18" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3152,13 +3189,13 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="AG18" s="81"/>
-      <c r="AH18" s="81"/>
-      <c r="AI18" s="65">
+      <c r="AG18" s="80"/>
+      <c r="AH18" s="80"/>
+      <c r="AI18" s="64">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="AJ18" s="82"/>
+      <c r="AJ18" s="81"/>
       <c r="AK18" s="42">
         <f t="shared" si="3"/>
         <v>50</v>
@@ -3167,81 +3204,81 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM18" s="92"/>
-      <c r="AN18" s="93">
+      <c r="AM18" s="91"/>
+      <c r="AN18" s="92">
         <f>W18-Z18</f>
         <v>50</v>
       </c>
-      <c r="AO18" s="158" t="s">
+      <c r="AO18" s="156" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:44" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="69">
+      <c r="A19" s="68">
         <v>5</v>
       </c>
-      <c r="B19" s="70" t="s">
+      <c r="B19" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="90" t="s">
+      <c r="C19" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="72"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="72"/>
-      <c r="K19" s="72">
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="71">
         <v>970357</v>
       </c>
       <c r="L19" s="52"/>
       <c r="M19" s="53">
         <v>960094.85</v>
       </c>
-      <c r="N19" s="91">
+      <c r="N19" s="90">
         <v>7000</v>
       </c>
-      <c r="O19" s="73">
+      <c r="O19" s="72">
         <v>61243</v>
       </c>
-      <c r="P19" s="73"/>
-      <c r="Q19" s="73"/>
-      <c r="R19" s="73"/>
-      <c r="S19" s="73">
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="72">
         <v>-4967</v>
       </c>
-      <c r="T19" s="73"/>
-      <c r="U19" s="73">
+      <c r="T19" s="72"/>
+      <c r="U19" s="72">
         <v>-40565</v>
       </c>
-      <c r="V19" s="94"/>
+      <c r="V19" s="93"/>
       <c r="W19" s="57">
         <f t="shared" si="8"/>
         <v>15711</v>
       </c>
-      <c r="X19" s="77">
+      <c r="X19" s="76">
         <v>2246.1019999999999</v>
       </c>
-      <c r="Y19" s="77"/>
-      <c r="Z19" s="60">
+      <c r="Y19" s="189"/>
+      <c r="Z19" s="59">
         <f t="shared" si="4"/>
         <v>2246.1019999999999</v>
       </c>
-      <c r="AA19" s="79">
+      <c r="AA19" s="78">
         <f t="shared" si="10"/>
         <v>0.1429636560371714</v>
       </c>
-      <c r="AB19" s="79">
+      <c r="AB19" s="78">
         <f>Z19/W19</f>
         <v>0.1429636560371714</v>
       </c>
-      <c r="AC19" s="80">
+      <c r="AC19" s="79">
         <v>1600</v>
       </c>
-      <c r="AD19" s="63"/>
-      <c r="AE19" s="80">
+      <c r="AD19" s="62"/>
+      <c r="AE19" s="79">
         <f t="shared" si="7"/>
         <v>1600</v>
       </c>
@@ -3249,13 +3286,13 @@
         <f t="shared" si="5"/>
         <v>13464.898000000001</v>
       </c>
-      <c r="AG19" s="81"/>
-      <c r="AH19" s="81"/>
-      <c r="AI19" s="65">
+      <c r="AG19" s="80"/>
+      <c r="AH19" s="80"/>
+      <c r="AI19" s="64">
         <f t="shared" si="2"/>
         <v>13464.898000000001</v>
       </c>
-      <c r="AJ19" s="95" t="s">
+      <c r="AJ19" s="94" t="s">
         <v>66</v>
       </c>
       <c r="AK19" s="42">
@@ -3266,77 +3303,77 @@
         <f t="shared" si="6"/>
         <v>0.33391267264973584</v>
       </c>
-      <c r="AM19" s="96"/>
-      <c r="AN19" s="93">
+      <c r="AM19" s="95"/>
+      <c r="AN19" s="92">
         <f t="shared" ref="AN19:AN21" si="12">W19-Z19</f>
         <v>13464.898000000001</v>
       </c>
-      <c r="AO19" s="157" t="s">
+      <c r="AO19" s="155" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:44" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="69">
+      <c r="A20" s="68">
         <v>6</v>
       </c>
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="90">
+      <c r="C20" s="89">
         <v>8112228</v>
       </c>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="72"/>
-      <c r="I20" s="72"/>
-      <c r="J20" s="72"/>
-      <c r="K20" s="72">
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="71">
         <v>250</v>
       </c>
       <c r="L20" s="52"/>
       <c r="M20" s="53">
         <v>250</v>
       </c>
-      <c r="N20" s="91">
+      <c r="N20" s="90">
         <v>36800</v>
       </c>
-      <c r="O20" s="73">
+      <c r="O20" s="72">
         <v>36800</v>
       </c>
-      <c r="P20" s="73"/>
-      <c r="Q20" s="73"/>
-      <c r="R20" s="73"/>
-      <c r="S20" s="74"/>
-      <c r="T20" s="73"/>
-      <c r="U20" s="75"/>
-      <c r="V20" s="76"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="73"/>
+      <c r="T20" s="72"/>
+      <c r="U20" s="74"/>
+      <c r="V20" s="75"/>
       <c r="W20" s="57">
         <f t="shared" si="8"/>
         <v>36800</v>
       </c>
-      <c r="X20" s="77">
+      <c r="X20" s="76">
         <v>26478.066999999999</v>
       </c>
-      <c r="Y20" s="77"/>
-      <c r="Z20" s="60">
+      <c r="Y20" s="189"/>
+      <c r="Z20" s="59">
         <f>SUM(X20:Y20)</f>
         <v>26478.066999999999</v>
       </c>
-      <c r="AA20" s="79">
+      <c r="AA20" s="78">
         <f t="shared" si="10"/>
         <v>0.71951269021739128</v>
       </c>
-      <c r="AB20" s="79">
+      <c r="AB20" s="78">
         <f t="shared" ref="AB20" si="13">Z20/N20</f>
         <v>0.71951269021739128</v>
       </c>
-      <c r="AC20" s="80">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="63"/>
-      <c r="AE20" s="80">
+      <c r="AC20" s="79">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="62"/>
+      <c r="AE20" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3344,13 +3381,13 @@
         <f t="shared" si="5"/>
         <v>10321.933000000001</v>
       </c>
-      <c r="AG20" s="81"/>
-      <c r="AH20" s="81"/>
-      <c r="AI20" s="65">
+      <c r="AG20" s="80"/>
+      <c r="AH20" s="80"/>
+      <c r="AI20" s="64">
         <f t="shared" si="2"/>
         <v>10321.933000000001</v>
       </c>
-      <c r="AJ20" s="97">
+      <c r="AJ20" s="96">
         <v>20000</v>
       </c>
       <c r="AK20" s="42">
@@ -3361,83 +3398,83 @@
         <f t="shared" si="6"/>
         <v>1.2629909510869564</v>
       </c>
-      <c r="AM20" s="84"/>
-      <c r="AN20" s="93">
+      <c r="AM20" s="83"/>
+      <c r="AN20" s="92">
         <f t="shared" si="12"/>
         <v>10321.933000000001</v>
       </c>
-      <c r="AO20" s="157" t="s">
+      <c r="AO20" s="155" t="s">
         <v>149</v>
       </c>
-      <c r="AQ20" s="98">
+      <c r="AQ20" s="97">
         <f>Z20-24656</f>
         <v>1822.0669999999991</v>
       </c>
     </row>
     <row r="21" spans="1:44" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="69">
+      <c r="A21" s="68">
         <v>7</v>
       </c>
-      <c r="B21" s="70" t="s">
+      <c r="B21" s="69" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="90" t="s">
+      <c r="C21" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="72"/>
-      <c r="J21" s="72">
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="71">
         <v>50</v>
       </c>
-      <c r="K21" s="72">
+      <c r="K21" s="71">
         <v>2998</v>
       </c>
       <c r="L21" s="52"/>
       <c r="M21" s="53">
         <v>2248.2619999999997</v>
       </c>
-      <c r="N21" s="91">
+      <c r="N21" s="90">
         <v>3288</v>
       </c>
-      <c r="O21" s="73">
+      <c r="O21" s="72">
         <v>3288</v>
       </c>
-      <c r="P21" s="73"/>
-      <c r="Q21" s="73"/>
-      <c r="R21" s="73"/>
-      <c r="S21" s="74"/>
-      <c r="T21" s="73"/>
-      <c r="U21" s="75"/>
-      <c r="V21" s="76"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="73"/>
+      <c r="T21" s="72"/>
+      <c r="U21" s="74"/>
+      <c r="V21" s="75"/>
       <c r="W21" s="57">
         <f t="shared" si="8"/>
         <v>3288</v>
       </c>
-      <c r="X21" s="77">
+      <c r="X21" s="76">
         <v>2292.66</v>
       </c>
-      <c r="Y21" s="77"/>
-      <c r="Z21" s="60">
+      <c r="Y21" s="189"/>
+      <c r="Z21" s="59">
         <f t="shared" si="4"/>
         <v>2292.66</v>
       </c>
-      <c r="AA21" s="79">
+      <c r="AA21" s="78">
         <f t="shared" si="10"/>
         <v>0.69728102189781016</v>
       </c>
-      <c r="AB21" s="79">
+      <c r="AB21" s="78">
         <f>Z21/N21</f>
         <v>0.69728102189781016</v>
       </c>
-      <c r="AC21" s="80">
+      <c r="AC21" s="79">
         <v>863</v>
       </c>
-      <c r="AD21" s="63"/>
-      <c r="AE21" s="80">
+      <c r="AD21" s="62"/>
+      <c r="AE21" s="79">
         <f t="shared" si="7"/>
         <v>863</v>
       </c>
@@ -3445,13 +3482,13 @@
         <f t="shared" si="5"/>
         <v>995.34000000000015</v>
       </c>
-      <c r="AG21" s="81"/>
-      <c r="AH21" s="81"/>
-      <c r="AI21" s="65">
+      <c r="AG21" s="80"/>
+      <c r="AH21" s="80"/>
+      <c r="AI21" s="64">
         <f t="shared" si="2"/>
         <v>995.34000000000015</v>
       </c>
-      <c r="AJ21" s="99">
+      <c r="AJ21" s="98">
         <v>450</v>
       </c>
       <c r="AK21" s="42">
@@ -3462,15 +3499,15 @@
         <f t="shared" si="6"/>
         <v>0.83414233576642327</v>
       </c>
-      <c r="AM21" s="84"/>
-      <c r="AN21" s="93">
+      <c r="AM21" s="83"/>
+      <c r="AN21" s="92">
         <f t="shared" si="12"/>
         <v>995.34000000000015</v>
       </c>
-      <c r="AO21" s="158" t="s">
+      <c r="AO21" s="156" t="s">
         <v>150</v>
       </c>
-      <c r="AP21" s="98">
+      <c r="AP21" s="97">
         <f>Z21-38334</f>
         <v>-36041.339999999997</v>
       </c>
@@ -3479,61 +3516,61 @@
       </c>
     </row>
     <row r="22" spans="1:44" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="69">
+      <c r="A22" s="68">
         <v>8</v>
       </c>
-      <c r="B22" s="70" t="s">
+      <c r="B22" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="90" t="s">
+      <c r="C22" s="89" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="72"/>
-      <c r="K22" s="72"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="71"/>
       <c r="L22" s="52"/>
       <c r="M22" s="53"/>
-      <c r="N22" s="100">
+      <c r="N22" s="99">
         <v>6</v>
       </c>
-      <c r="O22" s="73"/>
-      <c r="P22" s="73"/>
-      <c r="Q22" s="73"/>
-      <c r="R22" s="73">
+      <c r="O22" s="72"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="72">
         <v>6</v>
       </c>
-      <c r="S22" s="73">
+      <c r="S22" s="72">
         <v>6</v>
       </c>
-      <c r="T22" s="73"/>
-      <c r="U22" s="75">
+      <c r="T22" s="72"/>
+      <c r="U22" s="74">
         <v>-6</v>
       </c>
-      <c r="V22" s="76"/>
+      <c r="V22" s="75"/>
       <c r="W22" s="57">
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="X22" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="77"/>
-      <c r="Z22" s="60">
+      <c r="X22" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="189"/>
+      <c r="Z22" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA22" s="79"/>
-      <c r="AB22" s="79"/>
-      <c r="AC22" s="101">
+      <c r="AA22" s="78"/>
+      <c r="AB22" s="78"/>
+      <c r="AC22" s="100">
         <v>6</v>
       </c>
-      <c r="AD22" s="63"/>
-      <c r="AE22" s="80">
+      <c r="AD22" s="62"/>
+      <c r="AE22" s="79">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
@@ -3541,75 +3578,75 @@
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="AG22" s="81"/>
-      <c r="AH22" s="81"/>
-      <c r="AI22" s="65"/>
-      <c r="AJ22" s="99"/>
+      <c r="AG22" s="80"/>
+      <c r="AH22" s="80"/>
+      <c r="AI22" s="64"/>
+      <c r="AJ22" s="98"/>
       <c r="AK22" s="42"/>
       <c r="AL22" s="43"/>
-      <c r="AM22" s="84"/>
-      <c r="AN22" s="93"/>
-      <c r="AO22" s="107" t="s">
+      <c r="AM22" s="83"/>
+      <c r="AN22" s="92"/>
+      <c r="AO22" s="106" t="s">
         <v>151</v>
       </c>
-      <c r="AP22" s="98"/>
+      <c r="AP22" s="97"/>
     </row>
     <row r="23" spans="1:44" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="69">
+      <c r="A23" s="68">
         <v>9</v>
       </c>
-      <c r="B23" s="70" t="s">
+      <c r="B23" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="90" t="s">
+      <c r="C23" s="89" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="72"/>
-      <c r="J23" s="72"/>
-      <c r="K23" s="72"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="71"/>
       <c r="L23" s="52"/>
       <c r="M23" s="53"/>
-      <c r="N23" s="100">
+      <c r="N23" s="99">
         <v>23</v>
       </c>
-      <c r="O23" s="73"/>
-      <c r="P23" s="73"/>
-      <c r="Q23" s="73"/>
-      <c r="R23" s="73">
+      <c r="O23" s="72"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="72">
         <v>23</v>
       </c>
-      <c r="S23" s="73">
+      <c r="S23" s="72">
         <v>23</v>
       </c>
-      <c r="T23" s="73"/>
-      <c r="U23" s="75">
+      <c r="T23" s="72"/>
+      <c r="U23" s="74">
         <v>-23</v>
       </c>
-      <c r="V23" s="76"/>
+      <c r="V23" s="75"/>
       <c r="W23" s="57">
         <f t="shared" si="8"/>
         <v>23</v>
       </c>
-      <c r="X23" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="77"/>
-      <c r="Z23" s="60">
+      <c r="X23" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="189"/>
+      <c r="Z23" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA23" s="79"/>
-      <c r="AB23" s="79"/>
-      <c r="AC23" s="101">
+      <c r="AA23" s="78"/>
+      <c r="AB23" s="78"/>
+      <c r="AC23" s="100">
         <v>23</v>
       </c>
-      <c r="AD23" s="63"/>
-      <c r="AE23" s="80">
+      <c r="AD23" s="62"/>
+      <c r="AE23" s="79">
         <f t="shared" si="7"/>
         <v>23</v>
       </c>
@@ -3617,71 +3654,71 @@
         <f t="shared" si="5"/>
         <v>23</v>
       </c>
-      <c r="AG23" s="81"/>
-      <c r="AH23" s="81"/>
-      <c r="AI23" s="65"/>
-      <c r="AJ23" s="99"/>
+      <c r="AG23" s="80"/>
+      <c r="AH23" s="80"/>
+      <c r="AI23" s="64"/>
+      <c r="AJ23" s="98"/>
       <c r="AK23" s="42"/>
       <c r="AL23" s="43"/>
-      <c r="AM23" s="84"/>
-      <c r="AN23" s="93"/>
-      <c r="AO23" s="107" t="s">
+      <c r="AM23" s="83"/>
+      <c r="AN23" s="92"/>
+      <c r="AO23" s="106" t="s">
         <v>151</v>
       </c>
-      <c r="AP23" s="98"/>
+      <c r="AP23" s="97"/>
     </row>
     <row r="24" spans="1:44" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="69">
+      <c r="A24" s="68">
         <v>10</v>
       </c>
-      <c r="B24" s="70" t="s">
+      <c r="B24" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="90" t="s">
+      <c r="C24" s="89" t="s">
         <v>75</v>
       </c>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="72"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="72"/>
-      <c r="K24" s="72"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="71"/>
       <c r="L24" s="52"/>
       <c r="M24" s="53"/>
-      <c r="N24" s="100">
+      <c r="N24" s="99">
         <v>4</v>
       </c>
-      <c r="O24" s="73"/>
-      <c r="P24" s="73"/>
-      <c r="Q24" s="73"/>
-      <c r="R24" s="73"/>
-      <c r="S24" s="73">
+      <c r="O24" s="72"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="72">
         <v>4</v>
       </c>
-      <c r="T24" s="73"/>
-      <c r="U24" s="75"/>
-      <c r="V24" s="76"/>
+      <c r="T24" s="72"/>
+      <c r="U24" s="74"/>
+      <c r="V24" s="75"/>
       <c r="W24" s="57">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="X24" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="77"/>
-      <c r="Z24" s="60">
+      <c r="X24" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="189"/>
+      <c r="Z24" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA24" s="79"/>
-      <c r="AB24" s="79"/>
-      <c r="AC24" s="101">
+      <c r="AA24" s="78"/>
+      <c r="AB24" s="78"/>
+      <c r="AC24" s="100">
         <v>4</v>
       </c>
-      <c r="AD24" s="63"/>
-      <c r="AE24" s="80">
+      <c r="AD24" s="62"/>
+      <c r="AE24" s="79">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
@@ -3689,69 +3726,69 @@
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="AG24" s="81"/>
-      <c r="AH24" s="81"/>
-      <c r="AI24" s="65"/>
-      <c r="AJ24" s="99"/>
+      <c r="AG24" s="80"/>
+      <c r="AH24" s="80"/>
+      <c r="AI24" s="64"/>
+      <c r="AJ24" s="98"/>
       <c r="AK24" s="42"/>
       <c r="AL24" s="43"/>
-      <c r="AM24" s="84"/>
-      <c r="AN24" s="93"/>
-      <c r="AO24" s="107" t="s">
+      <c r="AM24" s="83"/>
+      <c r="AN24" s="92"/>
+      <c r="AO24" s="106" t="s">
         <v>152</v>
       </c>
-      <c r="AP24" s="98"/>
+      <c r="AP24" s="97"/>
     </row>
     <row r="25" spans="1:44" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="69">
+      <c r="A25" s="68">
         <v>11</v>
       </c>
-      <c r="B25" s="70" t="s">
+      <c r="B25" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="90" t="s">
+      <c r="C25" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
-      <c r="F25" s="72"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="72"/>
-      <c r="J25" s="72"/>
-      <c r="K25" s="72"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="71"/>
       <c r="L25" s="52"/>
       <c r="M25" s="53"/>
-      <c r="N25" s="100">
+      <c r="N25" s="99">
         <v>6</v>
       </c>
-      <c r="O25" s="73"/>
-      <c r="P25" s="73"/>
-      <c r="Q25" s="73"/>
-      <c r="R25" s="73"/>
-      <c r="S25" s="73">
+      <c r="O25" s="72"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="72">
         <v>6</v>
       </c>
-      <c r="T25" s="73"/>
-      <c r="U25" s="75"/>
-      <c r="V25" s="76"/>
+      <c r="T25" s="72"/>
+      <c r="U25" s="74"/>
+      <c r="V25" s="75"/>
       <c r="W25" s="57">
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="X25" s="77">
+      <c r="X25" s="76">
         <v>5.04</v>
       </c>
-      <c r="Y25" s="77"/>
-      <c r="Z25" s="60">
+      <c r="Y25" s="189"/>
+      <c r="Z25" s="59">
         <f t="shared" si="4"/>
         <v>5.04</v>
       </c>
-      <c r="AA25" s="79"/>
-      <c r="AB25" s="79"/>
-      <c r="AC25" s="101"/>
-      <c r="AD25" s="63"/>
-      <c r="AE25" s="80">
+      <c r="AA25" s="78"/>
+      <c r="AB25" s="78"/>
+      <c r="AC25" s="100"/>
+      <c r="AD25" s="62"/>
+      <c r="AE25" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3759,71 +3796,71 @@
         <f t="shared" si="5"/>
         <v>0.96</v>
       </c>
-      <c r="AG25" s="81"/>
-      <c r="AH25" s="81"/>
-      <c r="AI25" s="65"/>
-      <c r="AJ25" s="99"/>
+      <c r="AG25" s="80"/>
+      <c r="AH25" s="80"/>
+      <c r="AI25" s="64"/>
+      <c r="AJ25" s="98"/>
       <c r="AK25" s="42"/>
       <c r="AL25" s="43"/>
-      <c r="AM25" s="84"/>
-      <c r="AN25" s="93"/>
-      <c r="AO25" s="158" t="s">
+      <c r="AM25" s="83"/>
+      <c r="AN25" s="92"/>
+      <c r="AO25" s="156" t="s">
         <v>150</v>
       </c>
-      <c r="AP25" s="98"/>
+      <c r="AP25" s="97"/>
     </row>
     <row r="26" spans="1:44" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="69">
+      <c r="A26" s="68">
         <v>12</v>
       </c>
-      <c r="B26" s="70" t="s">
+      <c r="B26" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="C26" s="90" t="s">
+      <c r="C26" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="72"/>
-      <c r="E26" s="72"/>
-      <c r="F26" s="72"/>
-      <c r="G26" s="72"/>
-      <c r="H26" s="72"/>
-      <c r="I26" s="72"/>
-      <c r="J26" s="72"/>
-      <c r="K26" s="72"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="71"/>
       <c r="L26" s="52"/>
       <c r="M26" s="53"/>
-      <c r="N26" s="100">
+      <c r="N26" s="99">
         <v>6</v>
       </c>
-      <c r="O26" s="73"/>
-      <c r="P26" s="73"/>
-      <c r="Q26" s="73"/>
-      <c r="R26" s="73"/>
-      <c r="S26" s="73">
+      <c r="O26" s="72"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="72">
         <v>6</v>
       </c>
-      <c r="T26" s="73"/>
-      <c r="U26" s="75"/>
-      <c r="V26" s="76"/>
+      <c r="T26" s="72"/>
+      <c r="U26" s="74"/>
+      <c r="V26" s="75"/>
       <c r="W26" s="57">
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="X26" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="77"/>
-      <c r="Z26" s="60">
+      <c r="X26" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="189"/>
+      <c r="Z26" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA26" s="79"/>
-      <c r="AB26" s="79"/>
-      <c r="AC26" s="101">
+      <c r="AA26" s="78"/>
+      <c r="AB26" s="78"/>
+      <c r="AC26" s="100">
         <v>6</v>
       </c>
-      <c r="AD26" s="63"/>
-      <c r="AE26" s="80">
+      <c r="AD26" s="62"/>
+      <c r="AE26" s="79">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
@@ -3831,71 +3868,71 @@
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="AG26" s="81"/>
-      <c r="AH26" s="81"/>
-      <c r="AI26" s="65"/>
-      <c r="AJ26" s="99"/>
+      <c r="AG26" s="80"/>
+      <c r="AH26" s="80"/>
+      <c r="AI26" s="64"/>
+      <c r="AJ26" s="98"/>
       <c r="AK26" s="42"/>
       <c r="AL26" s="43"/>
-      <c r="AM26" s="84"/>
-      <c r="AN26" s="93"/>
-      <c r="AO26" s="107" t="s">
+      <c r="AM26" s="83"/>
+      <c r="AN26" s="92"/>
+      <c r="AO26" s="106" t="s">
         <v>152</v>
       </c>
-      <c r="AP26" s="98"/>
+      <c r="AP26" s="97"/>
     </row>
     <row r="27" spans="1:44" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="69">
+      <c r="A27" s="68">
         <v>13</v>
       </c>
-      <c r="B27" s="70" t="s">
+      <c r="B27" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="C27" s="90" t="s">
+      <c r="C27" s="89" t="s">
         <v>81</v>
       </c>
-      <c r="D27" s="72"/>
-      <c r="E27" s="72"/>
-      <c r="F27" s="72"/>
-      <c r="G27" s="72"/>
-      <c r="H27" s="72"/>
-      <c r="I27" s="72"/>
-      <c r="J27" s="72"/>
-      <c r="K27" s="72"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="71"/>
       <c r="L27" s="52"/>
       <c r="M27" s="53"/>
-      <c r="N27" s="100">
+      <c r="N27" s="99">
         <v>4</v>
       </c>
-      <c r="O27" s="73"/>
-      <c r="P27" s="73"/>
-      <c r="Q27" s="73"/>
-      <c r="R27" s="73"/>
-      <c r="S27" s="73">
+      <c r="O27" s="72"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="72">
         <v>4</v>
       </c>
-      <c r="T27" s="73"/>
-      <c r="U27" s="75"/>
-      <c r="V27" s="76"/>
+      <c r="T27" s="72"/>
+      <c r="U27" s="74"/>
+      <c r="V27" s="75"/>
       <c r="W27" s="57">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="X27" s="77">
+      <c r="X27" s="76">
         <v>3.47</v>
       </c>
-      <c r="Y27" s="77"/>
-      <c r="Z27" s="60">
+      <c r="Y27" s="189"/>
+      <c r="Z27" s="59">
         <f t="shared" si="4"/>
         <v>3.47</v>
       </c>
-      <c r="AA27" s="79"/>
-      <c r="AB27" s="79"/>
-      <c r="AC27" s="101">
+      <c r="AA27" s="78"/>
+      <c r="AB27" s="78"/>
+      <c r="AC27" s="100">
         <v>1</v>
       </c>
-      <c r="AD27" s="63"/>
-      <c r="AE27" s="80">
+      <c r="AD27" s="62"/>
+      <c r="AE27" s="79">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
@@ -3903,71 +3940,71 @@
         <f t="shared" si="5"/>
         <v>0.5299999999999998</v>
       </c>
-      <c r="AG27" s="81"/>
-      <c r="AH27" s="81"/>
-      <c r="AI27" s="65"/>
-      <c r="AJ27" s="99"/>
+      <c r="AG27" s="80"/>
+      <c r="AH27" s="80"/>
+      <c r="AI27" s="64"/>
+      <c r="AJ27" s="98"/>
       <c r="AK27" s="42"/>
       <c r="AL27" s="43"/>
-      <c r="AM27" s="84"/>
-      <c r="AN27" s="93"/>
-      <c r="AO27" s="158" t="s">
+      <c r="AM27" s="83"/>
+      <c r="AN27" s="92"/>
+      <c r="AO27" s="156" t="s">
         <v>150</v>
       </c>
-      <c r="AP27" s="98"/>
+      <c r="AP27" s="97"/>
     </row>
     <row r="28" spans="1:44" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="69">
+      <c r="A28" s="68">
         <v>14</v>
       </c>
-      <c r="B28" s="102" t="s">
+      <c r="B28" s="101" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="90" t="s">
+      <c r="C28" s="89" t="s">
         <v>83</v>
       </c>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="72"/>
-      <c r="K28" s="72"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="71"/>
       <c r="L28" s="52"/>
       <c r="M28" s="53"/>
-      <c r="N28" s="103">
+      <c r="N28" s="102">
         <v>43</v>
       </c>
-      <c r="O28" s="73"/>
-      <c r="P28" s="73"/>
-      <c r="Q28" s="73"/>
-      <c r="R28" s="73"/>
-      <c r="S28" s="73">
+      <c r="O28" s="72"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="72">
         <v>43</v>
       </c>
-      <c r="T28" s="73"/>
-      <c r="U28" s="75"/>
-      <c r="V28" s="76"/>
+      <c r="T28" s="72"/>
+      <c r="U28" s="74"/>
+      <c r="V28" s="75"/>
       <c r="W28" s="57">
         <f t="shared" si="8"/>
         <v>43</v>
       </c>
-      <c r="X28" s="77">
+      <c r="X28" s="76">
         <v>6.7</v>
       </c>
-      <c r="Y28" s="77"/>
-      <c r="Z28" s="60">
+      <c r="Y28" s="189"/>
+      <c r="Z28" s="59">
         <f t="shared" si="4"/>
         <v>6.7</v>
       </c>
-      <c r="AA28" s="79"/>
-      <c r="AB28" s="79"/>
-      <c r="AC28" s="101">
+      <c r="AA28" s="78"/>
+      <c r="AB28" s="78"/>
+      <c r="AC28" s="100">
         <v>36</v>
       </c>
-      <c r="AD28" s="63"/>
-      <c r="AE28" s="80">
+      <c r="AD28" s="62"/>
+      <c r="AE28" s="79">
         <f t="shared" si="7"/>
         <v>36</v>
       </c>
@@ -3975,71 +4012,71 @@
         <f t="shared" si="5"/>
         <v>36.299999999999997</v>
       </c>
-      <c r="AG28" s="81"/>
-      <c r="AH28" s="81"/>
-      <c r="AI28" s="65"/>
-      <c r="AJ28" s="99"/>
+      <c r="AG28" s="80"/>
+      <c r="AH28" s="80"/>
+      <c r="AI28" s="64"/>
+      <c r="AJ28" s="98"/>
       <c r="AK28" s="42"/>
       <c r="AL28" s="43"/>
-      <c r="AM28" s="84"/>
-      <c r="AN28" s="93"/>
-      <c r="AO28" s="156" t="s">
+      <c r="AM28" s="83"/>
+      <c r="AN28" s="92"/>
+      <c r="AO28" s="154" t="s">
         <v>148</v>
       </c>
-      <c r="AP28" s="98"/>
+      <c r="AP28" s="97"/>
     </row>
     <row r="29" spans="1:44" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="69">
+      <c r="A29" s="68">
         <v>15</v>
       </c>
-      <c r="B29" s="102" t="s">
+      <c r="B29" s="101" t="s">
         <v>84</v>
       </c>
-      <c r="C29" s="90" t="s">
+      <c r="C29" s="89" t="s">
         <v>85</v>
       </c>
-      <c r="D29" s="72"/>
-      <c r="E29" s="72"/>
-      <c r="F29" s="72"/>
-      <c r="G29" s="72"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="72"/>
-      <c r="K29" s="72"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="71"/>
       <c r="L29" s="52"/>
       <c r="M29" s="53"/>
-      <c r="N29" s="100">
+      <c r="N29" s="99">
         <v>45</v>
       </c>
-      <c r="O29" s="73"/>
-      <c r="P29" s="73"/>
-      <c r="Q29" s="73"/>
-      <c r="R29" s="73"/>
-      <c r="S29" s="73">
+      <c r="O29" s="72"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="72">
         <v>45</v>
       </c>
-      <c r="T29" s="73"/>
-      <c r="U29" s="75"/>
-      <c r="V29" s="76"/>
+      <c r="T29" s="72"/>
+      <c r="U29" s="74"/>
+      <c r="V29" s="75"/>
       <c r="W29" s="57">
         <f t="shared" si="8"/>
         <v>45</v>
       </c>
-      <c r="X29" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="77"/>
-      <c r="Z29" s="60">
+      <c r="X29" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="189"/>
+      <c r="Z29" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA29" s="79"/>
-      <c r="AB29" s="79"/>
-      <c r="AC29" s="101">
+      <c r="AA29" s="78"/>
+      <c r="AB29" s="78"/>
+      <c r="AC29" s="100">
         <v>45</v>
       </c>
-      <c r="AD29" s="63"/>
-      <c r="AE29" s="80">
+      <c r="AD29" s="62"/>
+      <c r="AE29" s="79">
         <f t="shared" si="7"/>
         <v>45</v>
       </c>
@@ -4047,71 +4084,71 @@
         <f t="shared" si="5"/>
         <v>45</v>
       </c>
-      <c r="AG29" s="81"/>
-      <c r="AH29" s="81"/>
-      <c r="AI29" s="65"/>
-      <c r="AJ29" s="99"/>
+      <c r="AG29" s="80"/>
+      <c r="AH29" s="80"/>
+      <c r="AI29" s="64"/>
+      <c r="AJ29" s="98"/>
       <c r="AK29" s="42"/>
       <c r="AL29" s="43"/>
-      <c r="AM29" s="84"/>
-      <c r="AN29" s="93"/>
-      <c r="AO29" s="158" t="s">
+      <c r="AM29" s="83"/>
+      <c r="AN29" s="92"/>
+      <c r="AO29" s="156" t="s">
         <v>150</v>
       </c>
-      <c r="AP29" s="98"/>
+      <c r="AP29" s="97"/>
     </row>
     <row r="30" spans="1:44" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="69">
+      <c r="A30" s="68">
         <v>16</v>
       </c>
-      <c r="B30" s="102" t="s">
+      <c r="B30" s="101" t="s">
         <v>86</v>
       </c>
-      <c r="C30" s="90" t="s">
+      <c r="C30" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="D30" s="72"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="72"/>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="72"/>
-      <c r="K30" s="72"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="71"/>
       <c r="L30" s="52"/>
       <c r="M30" s="53"/>
-      <c r="N30" s="100">
+      <c r="N30" s="99">
         <v>74</v>
       </c>
-      <c r="O30" s="73"/>
-      <c r="P30" s="73"/>
-      <c r="Q30" s="73"/>
-      <c r="R30" s="73"/>
-      <c r="S30" s="73">
+      <c r="O30" s="72"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="72">
         <v>74</v>
       </c>
-      <c r="T30" s="73"/>
-      <c r="U30" s="75"/>
-      <c r="V30" s="76"/>
+      <c r="T30" s="72"/>
+      <c r="U30" s="74"/>
+      <c r="V30" s="75"/>
       <c r="W30" s="57">
         <f t="shared" si="8"/>
         <v>74</v>
       </c>
-      <c r="X30" s="77">
+      <c r="X30" s="76">
         <v>37.1</v>
       </c>
-      <c r="Y30" s="77"/>
-      <c r="Z30" s="60">
+      <c r="Y30" s="189"/>
+      <c r="Z30" s="59">
         <f t="shared" si="4"/>
         <v>37.1</v>
       </c>
-      <c r="AA30" s="79"/>
-      <c r="AB30" s="79"/>
-      <c r="AC30" s="101">
+      <c r="AA30" s="78"/>
+      <c r="AB30" s="78"/>
+      <c r="AC30" s="100">
         <v>37</v>
       </c>
-      <c r="AD30" s="63"/>
-      <c r="AE30" s="80">
+      <c r="AD30" s="62"/>
+      <c r="AE30" s="79">
         <f t="shared" si="7"/>
         <v>37</v>
       </c>
@@ -4119,71 +4156,71 @@
         <f t="shared" si="5"/>
         <v>36.9</v>
       </c>
-      <c r="AG30" s="81"/>
-      <c r="AH30" s="81"/>
-      <c r="AI30" s="65"/>
-      <c r="AJ30" s="99"/>
+      <c r="AG30" s="80"/>
+      <c r="AH30" s="80"/>
+      <c r="AI30" s="64"/>
+      <c r="AJ30" s="98"/>
       <c r="AK30" s="42"/>
       <c r="AL30" s="43"/>
-      <c r="AM30" s="84"/>
-      <c r="AN30" s="93"/>
-      <c r="AO30" s="158" t="s">
+      <c r="AM30" s="83"/>
+      <c r="AN30" s="92"/>
+      <c r="AO30" s="156" t="s">
         <v>150</v>
       </c>
-      <c r="AP30" s="98"/>
+      <c r="AP30" s="97"/>
     </row>
     <row r="31" spans="1:44" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="69">
+      <c r="A31" s="68">
         <v>17</v>
       </c>
-      <c r="B31" s="102" t="s">
+      <c r="B31" s="101" t="s">
         <v>88</v>
       </c>
-      <c r="C31" s="90" t="s">
+      <c r="C31" s="89" t="s">
         <v>89</v>
       </c>
-      <c r="D31" s="72"/>
-      <c r="E31" s="72"/>
-      <c r="F31" s="72"/>
-      <c r="G31" s="72"/>
-      <c r="H31" s="72"/>
-      <c r="I31" s="72"/>
-      <c r="J31" s="72"/>
-      <c r="K31" s="72"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="71"/>
       <c r="L31" s="52"/>
       <c r="M31" s="53"/>
-      <c r="N31" s="100">
+      <c r="N31" s="99">
         <v>4</v>
       </c>
-      <c r="O31" s="73"/>
-      <c r="P31" s="73"/>
-      <c r="Q31" s="73"/>
-      <c r="R31" s="73"/>
-      <c r="S31" s="73">
+      <c r="O31" s="72"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="72">
         <v>4</v>
       </c>
-      <c r="T31" s="73"/>
-      <c r="U31" s="75"/>
-      <c r="V31" s="76"/>
+      <c r="T31" s="72"/>
+      <c r="U31" s="74"/>
+      <c r="V31" s="75"/>
       <c r="W31" s="57">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="X31" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="77"/>
-      <c r="Z31" s="60">
+      <c r="X31" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="189"/>
+      <c r="Z31" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA31" s="79"/>
-      <c r="AB31" s="79"/>
-      <c r="AC31" s="101">
+      <c r="AA31" s="78"/>
+      <c r="AB31" s="78"/>
+      <c r="AC31" s="100">
         <v>4</v>
       </c>
-      <c r="AD31" s="63"/>
-      <c r="AE31" s="80">
+      <c r="AD31" s="62"/>
+      <c r="AE31" s="79">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
@@ -4191,71 +4228,71 @@
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="AG31" s="81"/>
-      <c r="AH31" s="81"/>
-      <c r="AI31" s="65"/>
-      <c r="AJ31" s="99"/>
+      <c r="AG31" s="80"/>
+      <c r="AH31" s="80"/>
+      <c r="AI31" s="64"/>
+      <c r="AJ31" s="98"/>
       <c r="AK31" s="42"/>
       <c r="AL31" s="43"/>
-      <c r="AM31" s="84"/>
-      <c r="AN31" s="93"/>
-      <c r="AO31" s="107" t="s">
+      <c r="AM31" s="83"/>
+      <c r="AN31" s="92"/>
+      <c r="AO31" s="106" t="s">
         <v>151</v>
       </c>
-      <c r="AP31" s="98"/>
+      <c r="AP31" s="97"/>
     </row>
     <row r="32" spans="1:44" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="69">
+      <c r="A32" s="68">
         <v>18</v>
       </c>
-      <c r="B32" s="102" t="s">
+      <c r="B32" s="101" t="s">
         <v>90</v>
       </c>
-      <c r="C32" s="90" t="s">
+      <c r="C32" s="89" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="72"/>
-      <c r="E32" s="72"/>
-      <c r="F32" s="72"/>
-      <c r="G32" s="72"/>
-      <c r="H32" s="72"/>
-      <c r="I32" s="72"/>
-      <c r="J32" s="72"/>
-      <c r="K32" s="72"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="71"/>
       <c r="L32" s="52"/>
       <c r="M32" s="53"/>
-      <c r="N32" s="100">
+      <c r="N32" s="99">
         <v>9</v>
       </c>
-      <c r="O32" s="73"/>
-      <c r="P32" s="73"/>
-      <c r="Q32" s="73"/>
-      <c r="R32" s="73"/>
-      <c r="S32" s="73">
+      <c r="O32" s="72"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="72">
         <v>9</v>
       </c>
-      <c r="T32" s="73"/>
-      <c r="U32" s="75"/>
-      <c r="V32" s="76"/>
+      <c r="T32" s="72"/>
+      <c r="U32" s="74"/>
+      <c r="V32" s="75"/>
       <c r="W32" s="57">
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="X32" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="77"/>
-      <c r="Z32" s="60">
+      <c r="X32" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="189"/>
+      <c r="Z32" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA32" s="79"/>
-      <c r="AB32" s="79"/>
-      <c r="AC32" s="101">
+      <c r="AA32" s="78"/>
+      <c r="AB32" s="78"/>
+      <c r="AC32" s="100">
         <v>9</v>
       </c>
-      <c r="AD32" s="63"/>
-      <c r="AE32" s="80">
+      <c r="AD32" s="62"/>
+      <c r="AE32" s="79">
         <f t="shared" si="7"/>
         <v>9</v>
       </c>
@@ -4263,71 +4300,71 @@
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="AG32" s="81"/>
-      <c r="AH32" s="81"/>
-      <c r="AI32" s="65"/>
-      <c r="AJ32" s="99"/>
+      <c r="AG32" s="80"/>
+      <c r="AH32" s="80"/>
+      <c r="AI32" s="64"/>
+      <c r="AJ32" s="98"/>
       <c r="AK32" s="42"/>
       <c r="AL32" s="43"/>
-      <c r="AM32" s="84"/>
-      <c r="AN32" s="93"/>
-      <c r="AO32" s="107" t="s">
+      <c r="AM32" s="83"/>
+      <c r="AN32" s="92"/>
+      <c r="AO32" s="106" t="s">
         <v>152</v>
       </c>
-      <c r="AP32" s="98"/>
+      <c r="AP32" s="97"/>
     </row>
     <row r="33" spans="1:44" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="69">
+      <c r="A33" s="68">
         <v>19</v>
       </c>
-      <c r="B33" s="102" t="s">
+      <c r="B33" s="101" t="s">
         <v>92</v>
       </c>
-      <c r="C33" s="90" t="s">
+      <c r="C33" s="89" t="s">
         <v>93</v>
       </c>
-      <c r="D33" s="72"/>
-      <c r="E33" s="72"/>
-      <c r="F33" s="72"/>
-      <c r="G33" s="72"/>
-      <c r="H33" s="72"/>
-      <c r="I33" s="72"/>
-      <c r="J33" s="72"/>
-      <c r="K33" s="72"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="71"/>
       <c r="L33" s="52"/>
       <c r="M33" s="53"/>
-      <c r="N33" s="100">
+      <c r="N33" s="99">
         <v>10</v>
       </c>
-      <c r="O33" s="73"/>
-      <c r="P33" s="73"/>
-      <c r="Q33" s="73"/>
-      <c r="R33" s="73"/>
-      <c r="S33" s="73">
+      <c r="O33" s="72"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="72">
         <v>10</v>
       </c>
-      <c r="T33" s="73"/>
-      <c r="U33" s="75"/>
-      <c r="V33" s="76"/>
+      <c r="T33" s="72"/>
+      <c r="U33" s="74"/>
+      <c r="V33" s="75"/>
       <c r="W33" s="57">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="X33" s="77">
+      <c r="X33" s="76">
         <v>8.5</v>
       </c>
-      <c r="Y33" s="77"/>
-      <c r="Z33" s="60">
+      <c r="Y33" s="189"/>
+      <c r="Z33" s="59">
         <f t="shared" si="4"/>
         <v>8.5</v>
       </c>
-      <c r="AA33" s="79"/>
-      <c r="AB33" s="79"/>
-      <c r="AC33" s="101">
+      <c r="AA33" s="78"/>
+      <c r="AB33" s="78"/>
+      <c r="AC33" s="100">
         <v>2</v>
       </c>
-      <c r="AD33" s="63"/>
-      <c r="AE33" s="80">
+      <c r="AD33" s="62"/>
+      <c r="AE33" s="79">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -4335,18 +4372,18 @@
         <f t="shared" si="5"/>
         <v>1.5</v>
       </c>
-      <c r="AG33" s="81"/>
-      <c r="AH33" s="81"/>
-      <c r="AI33" s="65"/>
-      <c r="AJ33" s="99"/>
+      <c r="AG33" s="80"/>
+      <c r="AH33" s="80"/>
+      <c r="AI33" s="64"/>
+      <c r="AJ33" s="98"/>
       <c r="AK33" s="42"/>
       <c r="AL33" s="43"/>
-      <c r="AM33" s="84"/>
-      <c r="AN33" s="93"/>
-      <c r="AO33" s="158" t="s">
+      <c r="AM33" s="83"/>
+      <c r="AN33" s="92"/>
+      <c r="AO33" s="156" t="s">
         <v>150</v>
       </c>
-      <c r="AP33" s="98"/>
+      <c r="AP33" s="97"/>
     </row>
     <row r="34" spans="1:44" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="48" t="s">
@@ -4355,35 +4392,35 @@
       <c r="B34" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="C34" s="104"/>
-      <c r="D34" s="105"/>
-      <c r="E34" s="105"/>
-      <c r="F34" s="105"/>
-      <c r="G34" s="105"/>
-      <c r="H34" s="105"/>
-      <c r="I34" s="105"/>
-      <c r="J34" s="105"/>
-      <c r="K34" s="105"/>
+      <c r="C34" s="103"/>
+      <c r="D34" s="104"/>
+      <c r="E34" s="104"/>
+      <c r="F34" s="104"/>
+      <c r="G34" s="104"/>
+      <c r="H34" s="104"/>
+      <c r="I34" s="104"/>
+      <c r="J34" s="104"/>
+      <c r="K34" s="104"/>
       <c r="L34" s="52"/>
       <c r="M34" s="53"/>
-      <c r="N34" s="105"/>
+      <c r="N34" s="104"/>
       <c r="O34" s="54"/>
-      <c r="P34" s="73"/>
-      <c r="Q34" s="73"/>
-      <c r="R34" s="73"/>
-      <c r="S34" s="74"/>
-      <c r="T34" s="73"/>
-      <c r="U34" s="73"/>
-      <c r="V34" s="73"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="73"/>
+      <c r="T34" s="72"/>
+      <c r="U34" s="72"/>
+      <c r="V34" s="72"/>
       <c r="W34" s="57"/>
-      <c r="X34" s="77"/>
-      <c r="Y34" s="77"/>
-      <c r="Z34" s="60"/>
-      <c r="AA34" s="79"/>
-      <c r="AB34" s="79"/>
-      <c r="AC34" s="101"/>
-      <c r="AD34" s="63"/>
-      <c r="AE34" s="80">
+      <c r="X34" s="76"/>
+      <c r="Y34" s="189"/>
+      <c r="Z34" s="59"/>
+      <c r="AA34" s="78"/>
+      <c r="AB34" s="78"/>
+      <c r="AC34" s="100"/>
+      <c r="AD34" s="62"/>
+      <c r="AE34" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4391,42 +4428,42 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG34" s="81"/>
-      <c r="AH34" s="81"/>
-      <c r="AI34" s="65">
+      <c r="AG34" s="80"/>
+      <c r="AH34" s="80"/>
+      <c r="AI34" s="64">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AJ34" s="86"/>
+      <c r="AJ34" s="85"/>
       <c r="AK34" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AL34" s="43"/>
-      <c r="AM34" s="86"/>
-      <c r="AN34" s="81"/>
-      <c r="AO34" s="88"/>
+      <c r="AM34" s="85"/>
+      <c r="AN34" s="80"/>
+      <c r="AO34" s="87"/>
     </row>
     <row r="35" spans="1:44" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="69">
+      <c r="A35" s="68">
         <v>20</v>
       </c>
-      <c r="B35" s="70" t="s">
+      <c r="B35" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="90" t="s">
+      <c r="C35" s="89" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="72"/>
-      <c r="H35" s="72"/>
-      <c r="I35" s="72"/>
-      <c r="J35" s="72">
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="71">
         <v>50</v>
       </c>
-      <c r="K35" s="72">
+      <c r="K35" s="71">
         <v>200</v>
       </c>
       <c r="L35" s="52"/>
@@ -4434,46 +4471,46 @@
         <f>200</f>
         <v>200</v>
       </c>
-      <c r="N35" s="91">
+      <c r="N35" s="90">
         <v>6515</v>
       </c>
-      <c r="O35" s="73">
+      <c r="O35" s="72">
         <v>8285</v>
       </c>
-      <c r="P35" s="73"/>
-      <c r="Q35" s="73"/>
-      <c r="R35" s="73"/>
-      <c r="S35" s="73">
+      <c r="P35" s="72"/>
+      <c r="Q35" s="72"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="72">
         <v>-1632</v>
       </c>
-      <c r="T35" s="73"/>
-      <c r="U35" s="75">
+      <c r="T35" s="72"/>
+      <c r="U35" s="74">
         <v>-138</v>
       </c>
-      <c r="V35" s="75"/>
+      <c r="V35" s="74"/>
       <c r="W35" s="57">
         <f t="shared" si="8"/>
         <v>6515</v>
       </c>
-      <c r="X35" s="77">
+      <c r="X35" s="76">
         <v>6002.44</v>
       </c>
-      <c r="Y35" s="77"/>
-      <c r="Z35" s="60">
+      <c r="Y35" s="189"/>
+      <c r="Z35" s="59">
         <f>SUM(X35:Y35)</f>
         <v>6002.44</v>
       </c>
-      <c r="AA35" s="79">
+      <c r="AA35" s="78">
         <f>Z35/W35</f>
         <v>0.92132617037605524</v>
       </c>
-      <c r="AB35" s="79">
+      <c r="AB35" s="78">
         <f>Z35/N35</f>
         <v>0.92132617037605524</v>
       </c>
-      <c r="AC35" s="101"/>
-      <c r="AD35" s="63"/>
-      <c r="AE35" s="80">
+      <c r="AC35" s="100"/>
+      <c r="AD35" s="62"/>
+      <c r="AE35" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4481,13 +4518,13 @@
         <f t="shared" si="5"/>
         <v>512.5600000000004</v>
       </c>
-      <c r="AG35" s="81"/>
-      <c r="AH35" s="81"/>
-      <c r="AI35" s="65">
+      <c r="AG35" s="80"/>
+      <c r="AH35" s="80"/>
+      <c r="AI35" s="64">
         <f t="shared" si="2"/>
         <v>512.5600000000004</v>
       </c>
-      <c r="AJ35" s="82">
+      <c r="AJ35" s="81">
         <v>110</v>
       </c>
       <c r="AK35" s="42">
@@ -4498,75 +4535,75 @@
         <f t="shared" si="6"/>
         <v>0.93821028396009198</v>
       </c>
-      <c r="AM35" s="81"/>
-      <c r="AN35" s="81">
+      <c r="AM35" s="80"/>
+      <c r="AN35" s="80">
         <f>W35-Z35</f>
         <v>512.5600000000004</v>
       </c>
-      <c r="AO35" s="157" t="s">
+      <c r="AO35" s="155" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:44" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="69">
+      <c r="A36" s="68">
         <v>21</v>
       </c>
-      <c r="B36" s="70" t="s">
+      <c r="B36" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="C36" s="90">
+      <c r="C36" s="89">
         <v>8112965</v>
       </c>
-      <c r="D36" s="72"/>
-      <c r="E36" s="72"/>
-      <c r="F36" s="72"/>
-      <c r="G36" s="72"/>
-      <c r="H36" s="72"/>
-      <c r="I36" s="72"/>
-      <c r="J36" s="72"/>
-      <c r="K36" s="72">
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="71">
         <v>200</v>
       </c>
       <c r="L36" s="52"/>
       <c r="M36" s="53">
         <v>170</v>
       </c>
-      <c r="N36" s="91">
+      <c r="N36" s="90">
         <v>1208</v>
       </c>
-      <c r="O36" s="73">
+      <c r="O36" s="72">
         <v>1208</v>
       </c>
-      <c r="P36" s="73"/>
-      <c r="Q36" s="73"/>
-      <c r="R36" s="73"/>
-      <c r="S36" s="74"/>
-      <c r="T36" s="73"/>
-      <c r="U36" s="75"/>
-      <c r="V36" s="76"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="73"/>
+      <c r="T36" s="72"/>
+      <c r="U36" s="74"/>
+      <c r="V36" s="75"/>
       <c r="W36" s="57">
         <f t="shared" si="8"/>
         <v>1208</v>
       </c>
-      <c r="X36" s="77">
+      <c r="X36" s="76">
         <v>936.10699999999997</v>
       </c>
-      <c r="Y36" s="77"/>
-      <c r="Z36" s="60">
+      <c r="Y36" s="189"/>
+      <c r="Z36" s="59">
         <f t="shared" si="4"/>
         <v>936.10699999999997</v>
       </c>
-      <c r="AA36" s="79">
+      <c r="AA36" s="78">
         <f t="shared" ref="AA36:AA60" si="14">Z36/W36</f>
         <v>0.7749230132450331</v>
       </c>
-      <c r="AB36" s="79">
+      <c r="AB36" s="78">
         <f t="shared" ref="AB36:AB60" si="15">Z36/N36</f>
         <v>0.7749230132450331</v>
       </c>
-      <c r="AC36" s="101"/>
-      <c r="AD36" s="63"/>
-      <c r="AE36" s="80">
+      <c r="AC36" s="100"/>
+      <c r="AD36" s="62"/>
+      <c r="AE36" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4574,13 +4611,13 @@
         <f t="shared" si="5"/>
         <v>271.89300000000003</v>
       </c>
-      <c r="AG36" s="81"/>
-      <c r="AH36" s="81"/>
-      <c r="AI36" s="65">
+      <c r="AG36" s="80"/>
+      <c r="AH36" s="80"/>
+      <c r="AI36" s="64">
         <f t="shared" si="2"/>
         <v>271.89300000000003</v>
       </c>
-      <c r="AJ36" s="82"/>
+      <c r="AJ36" s="81"/>
       <c r="AK36" s="42">
         <f t="shared" si="3"/>
         <v>271.89300000000003</v>
@@ -4589,85 +4626,85 @@
         <f t="shared" si="6"/>
         <v>0.7749230132450331</v>
       </c>
-      <c r="AM36" s="86"/>
-      <c r="AN36" s="81">
+      <c r="AM36" s="85"/>
+      <c r="AN36" s="80">
         <f t="shared" ref="AN36:AN61" si="16">W36-Z36</f>
         <v>271.89300000000003</v>
       </c>
-      <c r="AO36" s="156" t="s">
+      <c r="AO36" s="154" t="s">
         <v>148</v>
       </c>
-      <c r="AQ36" s="68">
+      <c r="AQ36" s="67">
         <f>X36-261</f>
         <v>675.10699999999997</v>
       </c>
     </row>
     <row r="37" spans="1:44" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="69">
+      <c r="A37" s="68">
         <v>22</v>
       </c>
-      <c r="B37" s="70" t="s">
+      <c r="B37" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="C37" s="90">
+      <c r="C37" s="89">
         <v>8100887</v>
       </c>
-      <c r="D37" s="72"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="72"/>
-      <c r="H37" s="72"/>
-      <c r="I37" s="72"/>
-      <c r="J37" s="72"/>
-      <c r="K37" s="72">
+      <c r="D37" s="71"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="71"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="71"/>
+      <c r="K37" s="71">
         <v>5221</v>
       </c>
       <c r="L37" s="52"/>
       <c r="M37" s="53">
         <v>1558.6</v>
       </c>
-      <c r="N37" s="91">
+      <c r="N37" s="90">
         <v>12500</v>
       </c>
-      <c r="O37" s="73">
+      <c r="O37" s="72">
         <v>5000</v>
       </c>
-      <c r="P37" s="73"/>
-      <c r="Q37" s="73"/>
-      <c r="R37" s="73"/>
-      <c r="S37" s="73">
+      <c r="P37" s="72"/>
+      <c r="Q37" s="72"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="72">
         <v>11500</v>
       </c>
-      <c r="T37" s="73"/>
-      <c r="U37" s="75">
+      <c r="T37" s="72"/>
+      <c r="U37" s="74">
         <v>-2000</v>
       </c>
-      <c r="V37" s="76"/>
+      <c r="V37" s="75"/>
       <c r="W37" s="57">
         <f t="shared" si="8"/>
         <v>14500</v>
       </c>
-      <c r="X37" s="77">
+      <c r="X37" s="76">
         <v>9615.2000000000007</v>
       </c>
-      <c r="Y37" s="77"/>
-      <c r="Z37" s="60">
+      <c r="Y37" s="189"/>
+      <c r="Z37" s="59">
         <f t="shared" si="4"/>
         <v>9615.2000000000007</v>
       </c>
-      <c r="AA37" s="61">
+      <c r="AA37" s="60">
         <f>Z37/W37</f>
         <v>0.66311724137931038</v>
       </c>
-      <c r="AB37" s="61">
+      <c r="AB37" s="60">
         <f t="shared" si="15"/>
         <v>0.76921600000000001</v>
       </c>
-      <c r="AC37" s="101">
+      <c r="AC37" s="100">
         <v>3500</v>
       </c>
-      <c r="AD37" s="63"/>
-      <c r="AE37" s="80">
+      <c r="AD37" s="62"/>
+      <c r="AE37" s="79">
         <f t="shared" si="7"/>
         <v>3500</v>
       </c>
@@ -4675,13 +4712,13 @@
         <f t="shared" si="5"/>
         <v>4884.7999999999993</v>
       </c>
-      <c r="AG37" s="81"/>
-      <c r="AH37" s="81"/>
-      <c r="AI37" s="65">
+      <c r="AG37" s="80"/>
+      <c r="AH37" s="80"/>
+      <c r="AI37" s="64">
         <f t="shared" si="2"/>
         <v>4884.7999999999993</v>
       </c>
-      <c r="AJ37" s="82">
+      <c r="AJ37" s="81">
         <v>1000</v>
       </c>
       <c r="AK37" s="42">
@@ -4692,176 +4729,178 @@
         <f t="shared" si="6"/>
         <v>0.73208275862068972</v>
       </c>
-      <c r="AM37" s="86"/>
-      <c r="AN37" s="81">
+      <c r="AM37" s="85"/>
+      <c r="AN37" s="80">
         <f t="shared" si="16"/>
         <v>4884.7999999999993</v>
       </c>
-      <c r="AO37" s="158" t="s">
+      <c r="AO37" s="156" t="s">
         <v>150</v>
       </c>
-      <c r="AP37" s="106"/>
-      <c r="AQ37" s="68"/>
+      <c r="AP37" s="105"/>
+      <c r="AQ37" s="67"/>
     </row>
     <row r="38" spans="1:44" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="69">
+      <c r="A38" s="68">
         <v>23</v>
       </c>
-      <c r="B38" s="70" t="s">
+      <c r="B38" s="69" t="s">
         <v>100</v>
       </c>
-      <c r="C38" s="90">
+      <c r="C38" s="89">
         <v>8101114</v>
       </c>
-      <c r="D38" s="72"/>
-      <c r="E38" s="72"/>
-      <c r="F38" s="72"/>
-      <c r="G38" s="72"/>
-      <c r="H38" s="72"/>
-      <c r="I38" s="72"/>
-      <c r="J38" s="72"/>
-      <c r="K38" s="72">
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="71">
         <v>1000</v>
       </c>
       <c r="L38" s="52"/>
       <c r="M38" s="53">
         <v>983.19999999999993</v>
       </c>
-      <c r="N38" s="91">
+      <c r="N38" s="90">
         <v>44117</v>
       </c>
-      <c r="O38" s="73">
+      <c r="O38" s="72">
         <v>44117</v>
       </c>
-      <c r="P38" s="73"/>
-      <c r="Q38" s="73"/>
-      <c r="R38" s="73"/>
-      <c r="S38" s="74"/>
-      <c r="T38" s="73"/>
-      <c r="U38" s="75"/>
-      <c r="V38" s="76"/>
+      <c r="P38" s="72"/>
+      <c r="Q38" s="72"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="73"/>
+      <c r="T38" s="72"/>
+      <c r="U38" s="74"/>
+      <c r="V38" s="75"/>
       <c r="W38" s="57">
         <f t="shared" si="8"/>
         <v>44117</v>
       </c>
-      <c r="X38" s="77">
+      <c r="X38" s="76">
         <v>20539.23</v>
       </c>
-      <c r="Y38" s="77"/>
-      <c r="Z38" s="60">
+      <c r="Y38" s="189">
+        <v>7931</v>
+      </c>
+      <c r="Z38" s="59">
         <f t="shared" si="4"/>
-        <v>20539.23</v>
-      </c>
-      <c r="AA38" s="79">
+        <v>28470.23</v>
+      </c>
+      <c r="AA38" s="78">
         <f t="shared" si="14"/>
-        <v>0.46556270825305435</v>
-      </c>
-      <c r="AB38" s="79">
+        <v>0.64533467824194757</v>
+      </c>
+      <c r="AB38" s="78">
         <f t="shared" si="15"/>
-        <v>0.46556270825305435</v>
-      </c>
-      <c r="AC38" s="101">
+        <v>0.64533467824194757</v>
+      </c>
+      <c r="AC38" s="100">
         <f>7900</f>
         <v>7900</v>
       </c>
-      <c r="AD38" s="63"/>
-      <c r="AE38" s="80">
+      <c r="AD38" s="62"/>
+      <c r="AE38" s="79">
         <f t="shared" si="7"/>
         <v>7900</v>
       </c>
       <c r="AF38" s="52">
         <f t="shared" si="5"/>
-        <v>23577.77</v>
-      </c>
-      <c r="AG38" s="81"/>
-      <c r="AH38" s="81"/>
-      <c r="AI38" s="65">
+        <v>15646.77</v>
+      </c>
+      <c r="AG38" s="80"/>
+      <c r="AH38" s="80"/>
+      <c r="AI38" s="64">
         <f t="shared" si="2"/>
-        <v>23577.77</v>
-      </c>
-      <c r="AJ38" s="82">
+        <v>15646.77</v>
+      </c>
+      <c r="AJ38" s="81">
         <v>5000</v>
       </c>
       <c r="AK38" s="42">
         <f t="shared" si="3"/>
-        <v>18577.77</v>
+        <v>10646.77</v>
       </c>
       <c r="AL38" s="43">
         <f t="shared" si="6"/>
-        <v>0.57889770383298955</v>
-      </c>
-      <c r="AM38" s="107"/>
-      <c r="AN38" s="81">
+        <v>0.75866967382188266</v>
+      </c>
+      <c r="AM38" s="106"/>
+      <c r="AN38" s="80">
         <f t="shared" si="16"/>
-        <v>23577.77</v>
-      </c>
-      <c r="AO38" s="156" t="s">
+        <v>15646.77</v>
+      </c>
+      <c r="AO38" s="154" t="s">
         <v>148</v>
       </c>
-      <c r="AQ38" s="68"/>
+      <c r="AQ38" s="67"/>
     </row>
     <row r="39" spans="1:44" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="69">
+      <c r="A39" s="68">
         <v>24</v>
       </c>
-      <c r="B39" s="70" t="s">
+      <c r="B39" s="69" t="s">
         <v>101</v>
       </c>
-      <c r="C39" s="90">
+      <c r="C39" s="89">
         <v>8100889</v>
       </c>
-      <c r="D39" s="72"/>
-      <c r="E39" s="72"/>
-      <c r="F39" s="72"/>
-      <c r="G39" s="72"/>
-      <c r="H39" s="72"/>
-      <c r="I39" s="72"/>
-      <c r="J39" s="72"/>
-      <c r="K39" s="72">
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71">
         <v>1100</v>
       </c>
       <c r="L39" s="52"/>
       <c r="M39" s="53">
         <v>1097.5700000000002</v>
       </c>
-      <c r="N39" s="91">
+      <c r="N39" s="90">
         <v>48719</v>
       </c>
-      <c r="O39" s="73">
+      <c r="O39" s="72">
         <v>50419</v>
       </c>
-      <c r="P39" s="73"/>
-      <c r="Q39" s="73"/>
-      <c r="R39" s="73"/>
-      <c r="S39" s="74"/>
-      <c r="T39" s="73"/>
-      <c r="U39" s="73"/>
-      <c r="V39" s="94"/>
+      <c r="P39" s="72"/>
+      <c r="Q39" s="72"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="73"/>
+      <c r="T39" s="72"/>
+      <c r="U39" s="72"/>
+      <c r="V39" s="93"/>
       <c r="W39" s="57">
         <f t="shared" si="8"/>
         <v>50419</v>
       </c>
-      <c r="X39" s="77">
+      <c r="X39" s="76">
         <v>22155.989999999998</v>
       </c>
-      <c r="Y39" s="77"/>
-      <c r="Z39" s="60">
+      <c r="Y39" s="189"/>
+      <c r="Z39" s="59">
         <f>SUM(X39:Y39)</f>
         <v>22155.989999999998</v>
       </c>
-      <c r="AA39" s="79">
+      <c r="AA39" s="78">
         <f t="shared" si="14"/>
         <v>0.43943731529780433</v>
       </c>
-      <c r="AB39" s="79">
+      <c r="AB39" s="78">
         <f t="shared" si="15"/>
         <v>0.45477103388821605</v>
       </c>
-      <c r="AC39" s="101">
+      <c r="AC39" s="100">
         <v>10000</v>
       </c>
-      <c r="AD39" s="63"/>
-      <c r="AE39" s="80">
+      <c r="AD39" s="62"/>
+      <c r="AE39" s="79">
         <f t="shared" si="7"/>
         <v>10000</v>
       </c>
@@ -4869,13 +4908,13 @@
         <f t="shared" si="5"/>
         <v>28263.010000000002</v>
       </c>
-      <c r="AG39" s="81"/>
-      <c r="AH39" s="81"/>
-      <c r="AI39" s="65">
+      <c r="AG39" s="80"/>
+      <c r="AH39" s="80"/>
+      <c r="AI39" s="64">
         <f t="shared" si="2"/>
         <v>28263.010000000002</v>
       </c>
-      <c r="AJ39" s="82">
+      <c r="AJ39" s="81">
         <v>3200</v>
       </c>
       <c r="AK39" s="42">
@@ -4886,81 +4925,81 @@
         <f t="shared" si="6"/>
         <v>0.50290545230964512</v>
       </c>
-      <c r="AM39" s="86"/>
-      <c r="AN39" s="81">
+      <c r="AM39" s="85"/>
+      <c r="AN39" s="80">
         <f t="shared" si="16"/>
         <v>28263.010000000002</v>
       </c>
-      <c r="AO39" s="107" t="s">
+      <c r="AO39" s="106" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="40" spans="1:44" ht="46.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="69">
+      <c r="A40" s="68">
         <v>25</v>
       </c>
-      <c r="B40" s="70" t="s">
+      <c r="B40" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="C40" s="90">
+      <c r="C40" s="89">
         <v>8111370</v>
       </c>
-      <c r="D40" s="72"/>
-      <c r="E40" s="72"/>
-      <c r="F40" s="72"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="72"/>
-      <c r="I40" s="72"/>
-      <c r="J40" s="72"/>
-      <c r="K40" s="72">
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="71"/>
+      <c r="K40" s="71">
         <v>1100</v>
       </c>
       <c r="L40" s="52"/>
       <c r="M40" s="53">
         <v>931.3</v>
       </c>
-      <c r="N40" s="91">
+      <c r="N40" s="90">
         <v>60438</v>
       </c>
-      <c r="O40" s="73">
+      <c r="O40" s="72">
         <v>70000</v>
       </c>
-      <c r="P40" s="73"/>
-      <c r="Q40" s="73">
+      <c r="P40" s="72"/>
+      <c r="Q40" s="72">
         <v>-4562</v>
       </c>
-      <c r="R40" s="73"/>
-      <c r="S40" s="73">
+      <c r="R40" s="72"/>
+      <c r="S40" s="72">
         <v>-5000</v>
       </c>
-      <c r="T40" s="73"/>
-      <c r="U40" s="73"/>
-      <c r="V40" s="94"/>
+      <c r="T40" s="72"/>
+      <c r="U40" s="72"/>
+      <c r="V40" s="93"/>
       <c r="W40" s="57">
         <f t="shared" si="8"/>
         <v>60438</v>
       </c>
-      <c r="X40" s="77">
+      <c r="X40" s="76">
         <v>36775</v>
       </c>
-      <c r="Y40" s="77"/>
-      <c r="Z40" s="60">
+      <c r="Y40" s="189"/>
+      <c r="Z40" s="59">
         <f t="shared" si="4"/>
         <v>36775</v>
       </c>
-      <c r="AA40" s="79">
+      <c r="AA40" s="78">
         <f t="shared" si="14"/>
         <v>0.60847480062212511</v>
       </c>
-      <c r="AB40" s="79">
+      <c r="AB40" s="78">
         <f t="shared" si="15"/>
         <v>0.60847480062212511</v>
       </c>
-      <c r="AC40" s="101">
+      <c r="AC40" s="100">
         <v>10000</v>
       </c>
-      <c r="AD40" s="63"/>
-      <c r="AE40" s="80">
+      <c r="AD40" s="62"/>
+      <c r="AE40" s="79">
         <f t="shared" si="7"/>
         <v>10000</v>
       </c>
@@ -4968,13 +5007,13 @@
         <f t="shared" si="5"/>
         <v>23663</v>
       </c>
-      <c r="AG40" s="81"/>
-      <c r="AH40" s="81"/>
-      <c r="AI40" s="65">
+      <c r="AG40" s="80"/>
+      <c r="AH40" s="80"/>
+      <c r="AI40" s="64">
         <f t="shared" si="2"/>
         <v>23663</v>
       </c>
-      <c r="AJ40" s="82">
+      <c r="AJ40" s="81">
         <v>15000</v>
       </c>
       <c r="AK40" s="42">
@@ -4985,77 +5024,77 @@
         <f t="shared" si="6"/>
         <v>0.856663026572686</v>
       </c>
-      <c r="AM40" s="81"/>
-      <c r="AN40" s="81">
+      <c r="AM40" s="80"/>
+      <c r="AN40" s="80">
         <f t="shared" si="16"/>
         <v>23663</v>
       </c>
-      <c r="AO40" s="158" t="s">
+      <c r="AO40" s="156" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:44" ht="40.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="69">
+      <c r="A41" s="68">
         <v>26</v>
       </c>
-      <c r="B41" s="70" t="s">
+      <c r="B41" s="69" t="s">
         <v>103</v>
       </c>
-      <c r="C41" s="90">
+      <c r="C41" s="89">
         <v>8111981</v>
       </c>
-      <c r="D41" s="72"/>
-      <c r="E41" s="72"/>
-      <c r="F41" s="72"/>
-      <c r="G41" s="72"/>
-      <c r="H41" s="72"/>
-      <c r="I41" s="72"/>
-      <c r="J41" s="72"/>
-      <c r="K41" s="72">
+      <c r="D41" s="71"/>
+      <c r="E41" s="71"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="71"/>
+      <c r="I41" s="71"/>
+      <c r="J41" s="71"/>
+      <c r="K41" s="71">
         <v>300</v>
       </c>
       <c r="L41" s="52"/>
       <c r="M41" s="53">
         <v>272</v>
       </c>
-      <c r="N41" s="91">
+      <c r="N41" s="90">
         <v>420</v>
       </c>
-      <c r="O41" s="73">
+      <c r="O41" s="72">
         <v>20</v>
       </c>
-      <c r="P41" s="73"/>
-      <c r="Q41" s="73"/>
-      <c r="R41" s="73"/>
-      <c r="S41" s="73">
+      <c r="P41" s="72"/>
+      <c r="Q41" s="72"/>
+      <c r="R41" s="72"/>
+      <c r="S41" s="72">
         <v>400</v>
       </c>
-      <c r="T41" s="73"/>
-      <c r="U41" s="73"/>
-      <c r="V41" s="94"/>
+      <c r="T41" s="72"/>
+      <c r="U41" s="72"/>
+      <c r="V41" s="93"/>
       <c r="W41" s="57">
         <f t="shared" si="8"/>
         <v>420</v>
       </c>
-      <c r="X41" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="77"/>
-      <c r="Z41" s="60">
+      <c r="X41" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="189"/>
+      <c r="Z41" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA41" s="79">
+      <c r="AA41" s="78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB41" s="79">
+      <c r="AB41" s="78">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC41" s="101"/>
-      <c r="AD41" s="63"/>
-      <c r="AE41" s="80">
+      <c r="AC41" s="100"/>
+      <c r="AD41" s="62"/>
+      <c r="AE41" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -5063,13 +5102,13 @@
         <f t="shared" si="5"/>
         <v>420</v>
       </c>
-      <c r="AG41" s="81"/>
-      <c r="AH41" s="81"/>
-      <c r="AI41" s="65">
+      <c r="AG41" s="80"/>
+      <c r="AH41" s="80"/>
+      <c r="AI41" s="64">
         <f t="shared" si="2"/>
         <v>420</v>
       </c>
-      <c r="AJ41" s="82"/>
+      <c r="AJ41" s="81"/>
       <c r="AK41" s="42">
         <f t="shared" si="3"/>
         <v>420</v>
@@ -5078,79 +5117,79 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM41" s="108"/>
-      <c r="AN41" s="81">
+      <c r="AM41" s="107"/>
+      <c r="AN41" s="80">
         <f t="shared" si="16"/>
         <v>420</v>
       </c>
-      <c r="AO41" s="158" t="s">
+      <c r="AO41" s="156" t="s">
         <v>150</v>
       </c>
-      <c r="AP41" s="98">
+      <c r="AP41" s="97">
         <f>AP40-Z40</f>
         <v>-36775</v>
       </c>
     </row>
     <row r="42" spans="1:44" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="69">
+      <c r="A42" s="68">
         <v>27</v>
       </c>
-      <c r="B42" s="70" t="s">
+      <c r="B42" s="69" t="s">
         <v>104</v>
       </c>
-      <c r="C42" s="90">
+      <c r="C42" s="89">
         <v>8112964</v>
       </c>
-      <c r="D42" s="72"/>
-      <c r="E42" s="72"/>
-      <c r="F42" s="72"/>
-      <c r="G42" s="72"/>
-      <c r="H42" s="72"/>
-      <c r="I42" s="72"/>
-      <c r="J42" s="72"/>
-      <c r="K42" s="72">
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="71">
         <v>340</v>
       </c>
       <c r="L42" s="52"/>
       <c r="M42" s="53">
         <v>339.3</v>
       </c>
-      <c r="N42" s="91">
+      <c r="N42" s="90">
         <v>125</v>
       </c>
-      <c r="O42" s="73">
+      <c r="O42" s="72">
         <v>125</v>
       </c>
-      <c r="P42" s="73"/>
-      <c r="Q42" s="73"/>
-      <c r="R42" s="73"/>
-      <c r="S42" s="74"/>
-      <c r="T42" s="73"/>
-      <c r="U42" s="73"/>
-      <c r="V42" s="94"/>
+      <c r="P42" s="72"/>
+      <c r="Q42" s="72"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="73"/>
+      <c r="T42" s="72"/>
+      <c r="U42" s="72"/>
+      <c r="V42" s="93"/>
       <c r="W42" s="57">
         <f t="shared" si="8"/>
         <v>125</v>
       </c>
-      <c r="X42" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="77"/>
-      <c r="Z42" s="60">
+      <c r="X42" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="189"/>
+      <c r="Z42" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA42" s="79">
+      <c r="AA42" s="78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB42" s="79">
+      <c r="AB42" s="78">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC42" s="101"/>
-      <c r="AD42" s="63"/>
-      <c r="AE42" s="80">
+      <c r="AC42" s="100"/>
+      <c r="AD42" s="62"/>
+      <c r="AE42" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -5158,13 +5197,13 @@
         <f t="shared" si="5"/>
         <v>125</v>
       </c>
-      <c r="AG42" s="81"/>
-      <c r="AH42" s="81"/>
-      <c r="AI42" s="65">
+      <c r="AG42" s="80"/>
+      <c r="AH42" s="80"/>
+      <c r="AI42" s="64">
         <f t="shared" si="2"/>
         <v>125</v>
       </c>
-      <c r="AJ42" s="82"/>
+      <c r="AJ42" s="81"/>
       <c r="AK42" s="42">
         <f t="shared" si="3"/>
         <v>125</v>
@@ -5173,15 +5212,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM42" s="81"/>
-      <c r="AN42" s="81">
+      <c r="AM42" s="80"/>
+      <c r="AN42" s="80">
         <f t="shared" si="16"/>
         <v>125</v>
       </c>
-      <c r="AO42" s="107" t="s">
+      <c r="AO42" s="106" t="s">
         <v>152</v>
       </c>
-      <c r="AP42" s="98">
+      <c r="AP42" s="97">
         <f>Z42-13579</f>
         <v>-13579</v>
       </c>
@@ -5191,65 +5230,65 @@
       </c>
     </row>
     <row r="43" spans="1:44" ht="40.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="69">
+      <c r="A43" s="68">
         <v>28</v>
       </c>
-      <c r="B43" s="70" t="s">
+      <c r="B43" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="C43" s="90">
+      <c r="C43" s="89">
         <v>8112963</v>
       </c>
-      <c r="D43" s="72"/>
-      <c r="E43" s="72"/>
-      <c r="F43" s="72"/>
-      <c r="G43" s="72"/>
-      <c r="H43" s="72"/>
-      <c r="I43" s="72"/>
-      <c r="J43" s="72"/>
-      <c r="K43" s="72">
+      <c r="D43" s="71"/>
+      <c r="E43" s="71"/>
+      <c r="F43" s="71"/>
+      <c r="G43" s="71"/>
+      <c r="H43" s="71"/>
+      <c r="I43" s="71"/>
+      <c r="J43" s="71"/>
+      <c r="K43" s="71">
         <v>210</v>
       </c>
       <c r="L43" s="52"/>
       <c r="M43" s="53">
         <v>209.78</v>
       </c>
-      <c r="N43" s="72">
-        <v>0</v>
-      </c>
-      <c r="O43" s="73">
+      <c r="N43" s="71">
+        <v>0</v>
+      </c>
+      <c r="O43" s="72">
         <v>7575</v>
       </c>
-      <c r="P43" s="73"/>
-      <c r="Q43" s="73"/>
-      <c r="R43" s="73"/>
-      <c r="S43" s="74"/>
-      <c r="T43" s="73"/>
-      <c r="U43" s="75">
+      <c r="P43" s="72"/>
+      <c r="Q43" s="72"/>
+      <c r="R43" s="72"/>
+      <c r="S43" s="73"/>
+      <c r="T43" s="72"/>
+      <c r="U43" s="74">
         <v>-7575</v>
       </c>
-      <c r="V43" s="75"/>
+      <c r="V43" s="74"/>
       <c r="W43" s="57">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X43" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="77"/>
-      <c r="Z43" s="60">
+      <c r="X43" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="189"/>
+      <c r="Z43" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA43" s="109">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="79">
-        <v>0</v>
-      </c>
-      <c r="AC43" s="101"/>
-      <c r="AD43" s="63"/>
-      <c r="AE43" s="80">
+      <c r="AA43" s="108">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="78">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="100"/>
+      <c r="AD43" s="62"/>
+      <c r="AE43" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -5257,96 +5296,96 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG43" s="81"/>
-      <c r="AH43" s="81"/>
-      <c r="AI43" s="65">
+      <c r="AG43" s="80"/>
+      <c r="AH43" s="80"/>
+      <c r="AI43" s="64">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AJ43" s="82"/>
+      <c r="AJ43" s="81"/>
       <c r="AK43" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AL43" s="87" t="e">
+      <c r="AL43" s="86" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM43" s="81"/>
-      <c r="AN43" s="81">
+      <c r="AM43" s="80"/>
+      <c r="AN43" s="80">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AO43" s="157" t="s">
+      <c r="AO43" s="155" t="s">
         <v>149</v>
       </c>
-      <c r="AQ43" s="98">
+      <c r="AQ43" s="97">
         <f>AQ42-Z42</f>
         <v>13104</v>
       </c>
     </row>
     <row r="44" spans="1:44" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="69">
+      <c r="A44" s="68">
         <v>29</v>
       </c>
-      <c r="B44" s="70" t="s">
+      <c r="B44" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="C44" s="90" t="s">
+      <c r="C44" s="89" t="s">
         <v>107</v>
       </c>
-      <c r="D44" s="72"/>
-      <c r="E44" s="72"/>
-      <c r="F44" s="72"/>
-      <c r="G44" s="72"/>
-      <c r="H44" s="72"/>
-      <c r="I44" s="72"/>
-      <c r="J44" s="72">
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="71">
         <v>50</v>
       </c>
-      <c r="K44" s="72">
+      <c r="K44" s="71">
         <v>954</v>
       </c>
       <c r="L44" s="52"/>
       <c r="M44" s="53">
         <v>898.03700000000003</v>
       </c>
-      <c r="N44" s="91">
+      <c r="N44" s="90">
         <v>34000</v>
       </c>
-      <c r="O44" s="73">
+      <c r="O44" s="72">
         <v>34000</v>
       </c>
-      <c r="P44" s="73"/>
-      <c r="Q44" s="73"/>
-      <c r="R44" s="73"/>
-      <c r="S44" s="74"/>
-      <c r="T44" s="73"/>
-      <c r="U44" s="73"/>
-      <c r="V44" s="73"/>
+      <c r="P44" s="72"/>
+      <c r="Q44" s="72"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="73"/>
+      <c r="T44" s="72"/>
+      <c r="U44" s="72"/>
+      <c r="V44" s="72"/>
       <c r="W44" s="57">
         <f t="shared" si="8"/>
         <v>34000</v>
       </c>
-      <c r="X44" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="77"/>
-      <c r="Z44" s="60">
+      <c r="X44" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="189"/>
+      <c r="Z44" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA44" s="79">
+      <c r="AA44" s="78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB44" s="79">
+      <c r="AB44" s="78">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC44" s="101"/>
-      <c r="AD44" s="63"/>
-      <c r="AE44" s="80">
+      <c r="AC44" s="100"/>
+      <c r="AD44" s="62"/>
+      <c r="AE44" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -5354,13 +5393,13 @@
         <f t="shared" si="5"/>
         <v>34000</v>
       </c>
-      <c r="AG44" s="81"/>
-      <c r="AH44" s="81"/>
-      <c r="AI44" s="65">
+      <c r="AG44" s="80"/>
+      <c r="AH44" s="80"/>
+      <c r="AI44" s="64">
         <f t="shared" si="2"/>
         <v>34000</v>
       </c>
-      <c r="AJ44" s="82"/>
+      <c r="AJ44" s="81"/>
       <c r="AK44" s="42">
         <f t="shared" si="3"/>
         <v>34000</v>
@@ -5369,12 +5408,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM44" s="86"/>
-      <c r="AN44" s="81">
+      <c r="AM44" s="85"/>
+      <c r="AN44" s="80">
         <f t="shared" si="16"/>
         <v>34000</v>
       </c>
-      <c r="AO44" s="156" t="s">
+      <c r="AO44" s="154" t="s">
         <v>148</v>
       </c>
       <c r="AP44">
@@ -5382,67 +5421,67 @@
       </c>
     </row>
     <row r="45" spans="1:44" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="69">
+      <c r="A45" s="68">
         <v>30</v>
       </c>
-      <c r="B45" s="70" t="s">
+      <c r="B45" s="69" t="s">
         <v>108</v>
       </c>
-      <c r="C45" s="90">
+      <c r="C45" s="89">
         <v>8111982</v>
       </c>
-      <c r="D45" s="72"/>
-      <c r="E45" s="72"/>
-      <c r="F45" s="72"/>
-      <c r="G45" s="72"/>
-      <c r="H45" s="72"/>
-      <c r="I45" s="72"/>
-      <c r="J45" s="72"/>
-      <c r="K45" s="72">
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="71">
         <v>300</v>
       </c>
       <c r="L45" s="52"/>
       <c r="M45" s="53">
         <v>264.39999999999998</v>
       </c>
-      <c r="N45" s="91">
+      <c r="N45" s="90">
         <v>191</v>
       </c>
-      <c r="O45" s="73">
+      <c r="O45" s="72">
         <v>21</v>
       </c>
-      <c r="P45" s="73"/>
-      <c r="Q45" s="73"/>
-      <c r="R45" s="73"/>
-      <c r="S45" s="73">
+      <c r="P45" s="72"/>
+      <c r="Q45" s="72"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="72">
         <v>170</v>
       </c>
-      <c r="T45" s="73"/>
-      <c r="U45" s="73"/>
-      <c r="V45" s="73"/>
+      <c r="T45" s="72"/>
+      <c r="U45" s="72"/>
+      <c r="V45" s="72"/>
       <c r="W45" s="57">
         <f t="shared" si="8"/>
         <v>191</v>
       </c>
-      <c r="X45" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="77"/>
-      <c r="Z45" s="60">
+      <c r="X45" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="189"/>
+      <c r="Z45" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA45" s="79">
+      <c r="AA45" s="78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB45" s="79">
+      <c r="AB45" s="78">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC45" s="101"/>
-      <c r="AD45" s="63"/>
-      <c r="AE45" s="80">
+      <c r="AC45" s="100"/>
+      <c r="AD45" s="62"/>
+      <c r="AE45" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -5450,13 +5489,13 @@
         <f t="shared" si="5"/>
         <v>191</v>
       </c>
-      <c r="AG45" s="81"/>
-      <c r="AH45" s="81"/>
-      <c r="AI45" s="65">
+      <c r="AG45" s="80"/>
+      <c r="AH45" s="80"/>
+      <c r="AI45" s="64">
         <f t="shared" si="2"/>
         <v>191</v>
       </c>
-      <c r="AJ45" s="82"/>
+      <c r="AJ45" s="81"/>
       <c r="AK45" s="42">
         <f t="shared" si="3"/>
         <v>191</v>
@@ -5465,15 +5504,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM45" s="81"/>
-      <c r="AN45" s="81">
+      <c r="AM45" s="80"/>
+      <c r="AN45" s="80">
         <f t="shared" si="16"/>
         <v>191</v>
       </c>
-      <c r="AO45" s="158" t="s">
+      <c r="AO45" s="156" t="s">
         <v>150</v>
       </c>
-      <c r="AP45" s="68">
+      <c r="AP45" s="67">
         <f>10338</f>
         <v>10338</v>
       </c>
@@ -5482,65 +5521,65 @@
       </c>
     </row>
     <row r="46" spans="1:44" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="69">
+      <c r="A46" s="68">
         <v>31</v>
       </c>
-      <c r="B46" s="70" t="s">
+      <c r="B46" s="69" t="s">
         <v>109</v>
       </c>
-      <c r="C46" s="90">
+      <c r="C46" s="89">
         <v>8101113</v>
       </c>
-      <c r="D46" s="72"/>
-      <c r="E46" s="72"/>
-      <c r="F46" s="72"/>
-      <c r="G46" s="72"/>
-      <c r="H46" s="72"/>
-      <c r="I46" s="72"/>
-      <c r="J46" s="72"/>
-      <c r="K46" s="72">
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="71">
         <v>1014</v>
       </c>
       <c r="L46" s="52"/>
       <c r="M46" s="53">
         <v>331.15</v>
       </c>
-      <c r="N46" s="91">
+      <c r="N46" s="90">
         <v>33</v>
       </c>
-      <c r="O46" s="73">
+      <c r="O46" s="72">
         <v>33</v>
       </c>
-      <c r="P46" s="73"/>
-      <c r="Q46" s="73"/>
-      <c r="R46" s="73"/>
-      <c r="S46" s="74"/>
-      <c r="T46" s="73"/>
-      <c r="U46" s="75"/>
-      <c r="V46" s="76"/>
+      <c r="P46" s="72"/>
+      <c r="Q46" s="72"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="73"/>
+      <c r="T46" s="72"/>
+      <c r="U46" s="74"/>
+      <c r="V46" s="75"/>
       <c r="W46" s="57">
         <f t="shared" si="8"/>
         <v>33</v>
       </c>
-      <c r="X46" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="77"/>
-      <c r="Z46" s="60">
+      <c r="X46" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="189"/>
+      <c r="Z46" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA46" s="79">
+      <c r="AA46" s="78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB46" s="79">
+      <c r="AB46" s="78">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC46" s="101"/>
-      <c r="AD46" s="63"/>
-      <c r="AE46" s="80">
+      <c r="AC46" s="100"/>
+      <c r="AD46" s="62"/>
+      <c r="AE46" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -5548,13 +5587,13 @@
         <f t="shared" si="5"/>
         <v>33</v>
       </c>
-      <c r="AG46" s="81"/>
-      <c r="AH46" s="81"/>
-      <c r="AI46" s="65">
+      <c r="AG46" s="80"/>
+      <c r="AH46" s="80"/>
+      <c r="AI46" s="64">
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="AJ46" s="82"/>
+      <c r="AJ46" s="81"/>
       <c r="AK46" s="42">
         <f t="shared" si="3"/>
         <v>33</v>
@@ -5563,12 +5602,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM46" s="86"/>
-      <c r="AN46" s="81">
+      <c r="AM46" s="85"/>
+      <c r="AN46" s="80">
         <f t="shared" si="16"/>
         <v>33</v>
       </c>
-      <c r="AO46" s="107" t="s">
+      <c r="AO46" s="106" t="s">
         <v>151</v>
       </c>
       <c r="AR46">
@@ -5576,65 +5615,65 @@
       </c>
     </row>
     <row r="47" spans="1:44" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="69">
+      <c r="A47" s="68">
         <v>32</v>
       </c>
-      <c r="B47" s="70" t="s">
+      <c r="B47" s="69" t="s">
         <v>110</v>
       </c>
-      <c r="C47" s="90">
+      <c r="C47" s="89">
         <v>8101117</v>
       </c>
-      <c r="D47" s="72"/>
-      <c r="E47" s="72"/>
-      <c r="F47" s="72"/>
-      <c r="G47" s="72"/>
-      <c r="H47" s="72"/>
-      <c r="I47" s="72"/>
-      <c r="J47" s="72"/>
-      <c r="K47" s="72">
+      <c r="D47" s="71"/>
+      <c r="E47" s="71"/>
+      <c r="F47" s="71"/>
+      <c r="G47" s="71"/>
+      <c r="H47" s="71"/>
+      <c r="I47" s="71"/>
+      <c r="J47" s="71"/>
+      <c r="K47" s="71">
         <v>500</v>
       </c>
       <c r="L47" s="52"/>
       <c r="M47" s="53">
         <v>115.9</v>
       </c>
-      <c r="N47" s="91">
+      <c r="N47" s="90">
         <v>10</v>
       </c>
-      <c r="O47" s="73">
+      <c r="O47" s="72">
         <v>10</v>
       </c>
-      <c r="P47" s="73"/>
-      <c r="Q47" s="73"/>
-      <c r="R47" s="73"/>
-      <c r="S47" s="74"/>
-      <c r="T47" s="73"/>
-      <c r="U47" s="75"/>
-      <c r="V47" s="76"/>
+      <c r="P47" s="72"/>
+      <c r="Q47" s="72"/>
+      <c r="R47" s="72"/>
+      <c r="S47" s="73"/>
+      <c r="T47" s="72"/>
+      <c r="U47" s="74"/>
+      <c r="V47" s="75"/>
       <c r="W47" s="57">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="X47" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="77"/>
-      <c r="Z47" s="60">
+      <c r="X47" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="189"/>
+      <c r="Z47" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA47" s="79">
+      <c r="AA47" s="78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB47" s="79">
+      <c r="AB47" s="78">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC47" s="80"/>
-      <c r="AD47" s="63"/>
-      <c r="AE47" s="80">
+      <c r="AC47" s="79"/>
+      <c r="AD47" s="62"/>
+      <c r="AE47" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -5642,13 +5681,13 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="AG47" s="81"/>
-      <c r="AH47" s="81"/>
-      <c r="AI47" s="65">
+      <c r="AG47" s="80"/>
+      <c r="AH47" s="80"/>
+      <c r="AI47" s="64">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="AJ47" s="82"/>
+      <c r="AJ47" s="81"/>
       <c r="AK47" s="42">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -5657,75 +5696,75 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM47" s="86"/>
-      <c r="AN47" s="81">
+      <c r="AM47" s="85"/>
+      <c r="AN47" s="80">
         <f t="shared" si="16"/>
         <v>10</v>
       </c>
-      <c r="AO47" s="158" t="s">
+      <c r="AO47" s="156" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:44" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="69">
+      <c r="A48" s="68">
         <v>33</v>
       </c>
-      <c r="B48" s="70" t="s">
+      <c r="B48" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="C48" s="90">
+      <c r="C48" s="89">
         <v>8100890</v>
       </c>
-      <c r="D48" s="72"/>
-      <c r="E48" s="72"/>
-      <c r="F48" s="72"/>
-      <c r="G48" s="72"/>
-      <c r="H48" s="72"/>
-      <c r="I48" s="72"/>
-      <c r="J48" s="72"/>
-      <c r="K48" s="72">
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="71"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="71">
         <v>1000</v>
       </c>
       <c r="L48" s="52"/>
       <c r="M48" s="53">
         <v>173.7</v>
       </c>
-      <c r="N48" s="91">
+      <c r="N48" s="90">
         <v>10</v>
       </c>
-      <c r="O48" s="73">
+      <c r="O48" s="72">
         <v>10</v>
       </c>
-      <c r="P48" s="73"/>
-      <c r="Q48" s="73"/>
-      <c r="R48" s="73"/>
-      <c r="S48" s="74"/>
-      <c r="T48" s="73"/>
-      <c r="U48" s="73"/>
-      <c r="V48" s="73"/>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="72"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="73"/>
+      <c r="T48" s="72"/>
+      <c r="U48" s="72"/>
+      <c r="V48" s="72"/>
       <c r="W48" s="57">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="X48" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y48" s="77"/>
-      <c r="Z48" s="60">
+      <c r="X48" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="189"/>
+      <c r="Z48" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA48" s="79">
+      <c r="AA48" s="78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB48" s="79">
+      <c r="AB48" s="78">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC48" s="80"/>
-      <c r="AD48" s="63"/>
-      <c r="AE48" s="80">
+      <c r="AC48" s="79"/>
+      <c r="AD48" s="62"/>
+      <c r="AE48" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -5733,13 +5772,13 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="AG48" s="81"/>
-      <c r="AH48" s="81"/>
-      <c r="AI48" s="65">
+      <c r="AG48" s="80"/>
+      <c r="AH48" s="80"/>
+      <c r="AI48" s="64">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="AJ48" s="82"/>
+      <c r="AJ48" s="81"/>
       <c r="AK48" s="42">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -5748,75 +5787,75 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM48" s="81"/>
-      <c r="AN48" s="81">
+      <c r="AM48" s="80"/>
+      <c r="AN48" s="80">
         <f t="shared" si="16"/>
         <v>10</v>
       </c>
-      <c r="AO48" s="107" t="s">
+      <c r="AO48" s="106" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="49" spans="1:44" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="69">
+      <c r="A49" s="68">
         <v>34</v>
       </c>
-      <c r="B49" s="70" t="s">
+      <c r="B49" s="69" t="s">
         <v>112</v>
       </c>
-      <c r="C49" s="90">
+      <c r="C49" s="89">
         <v>8101116</v>
       </c>
-      <c r="D49" s="72"/>
-      <c r="E49" s="72"/>
-      <c r="F49" s="72"/>
-      <c r="G49" s="72"/>
-      <c r="H49" s="72"/>
-      <c r="I49" s="72"/>
-      <c r="J49" s="72"/>
-      <c r="K49" s="72">
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="71"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="71">
         <v>700</v>
       </c>
       <c r="L49" s="52"/>
       <c r="M49" s="53">
         <v>239.99999999999997</v>
       </c>
-      <c r="N49" s="91">
+      <c r="N49" s="90">
         <v>20</v>
       </c>
-      <c r="O49" s="73">
+      <c r="O49" s="72">
         <v>20</v>
       </c>
-      <c r="P49" s="73"/>
-      <c r="Q49" s="73"/>
-      <c r="R49" s="73"/>
-      <c r="S49" s="74"/>
-      <c r="T49" s="73"/>
-      <c r="U49" s="75"/>
-      <c r="V49" s="76"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="73"/>
+      <c r="T49" s="72"/>
+      <c r="U49" s="74"/>
+      <c r="V49" s="75"/>
       <c r="W49" s="57">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="X49" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="77"/>
-      <c r="Z49" s="60">
+      <c r="X49" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="189"/>
+      <c r="Z49" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA49" s="79">
+      <c r="AA49" s="78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB49" s="79">
+      <c r="AB49" s="78">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC49" s="80"/>
-      <c r="AD49" s="63"/>
-      <c r="AE49" s="80">
+      <c r="AC49" s="79"/>
+      <c r="AD49" s="62"/>
+      <c r="AE49" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -5824,13 +5863,13 @@
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="AG49" s="81"/>
-      <c r="AH49" s="81"/>
-      <c r="AI49" s="65">
+      <c r="AG49" s="80"/>
+      <c r="AH49" s="80"/>
+      <c r="AI49" s="64">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="AJ49" s="82"/>
+      <c r="AJ49" s="81"/>
       <c r="AK49" s="42">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -5839,75 +5878,75 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM49" s="86"/>
-      <c r="AN49" s="81">
+      <c r="AM49" s="85"/>
+      <c r="AN49" s="80">
         <f t="shared" si="16"/>
         <v>20</v>
       </c>
-      <c r="AO49" s="156" t="s">
+      <c r="AO49" s="154" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:44" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="69">
+      <c r="A50" s="68">
         <v>35</v>
       </c>
-      <c r="B50" s="70" t="s">
+      <c r="B50" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="C50" s="90">
+      <c r="C50" s="89">
         <v>8101115</v>
       </c>
-      <c r="D50" s="72"/>
-      <c r="E50" s="72"/>
-      <c r="F50" s="72"/>
-      <c r="G50" s="72"/>
-      <c r="H50" s="72"/>
-      <c r="I50" s="72"/>
-      <c r="J50" s="72"/>
-      <c r="K50" s="72">
+      <c r="D50" s="71"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="71"/>
+      <c r="I50" s="71"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="71">
         <v>1556</v>
       </c>
       <c r="L50" s="52"/>
       <c r="M50" s="53">
         <v>306.99099999999999</v>
       </c>
-      <c r="N50" s="91">
+      <c r="N50" s="90">
         <v>47</v>
       </c>
-      <c r="O50" s="73">
+      <c r="O50" s="72">
         <v>50</v>
       </c>
-      <c r="P50" s="73"/>
-      <c r="Q50" s="73"/>
-      <c r="R50" s="73"/>
-      <c r="S50" s="74"/>
-      <c r="T50" s="73"/>
-      <c r="U50" s="75"/>
-      <c r="V50" s="76"/>
+      <c r="P50" s="72"/>
+      <c r="Q50" s="72"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="73"/>
+      <c r="T50" s="72"/>
+      <c r="U50" s="74"/>
+      <c r="V50" s="75"/>
       <c r="W50" s="57">
         <f t="shared" si="8"/>
         <v>50</v>
       </c>
-      <c r="X50" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="77"/>
-      <c r="Z50" s="60">
+      <c r="X50" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="189"/>
+      <c r="Z50" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA50" s="79">
+      <c r="AA50" s="78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB50" s="79">
+      <c r="AB50" s="78">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC50" s="80"/>
-      <c r="AD50" s="63"/>
-      <c r="AE50" s="80">
+      <c r="AC50" s="79"/>
+      <c r="AD50" s="62"/>
+      <c r="AE50" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -5915,13 +5954,13 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="AG50" s="81"/>
-      <c r="AH50" s="81"/>
-      <c r="AI50" s="65">
+      <c r="AG50" s="80"/>
+      <c r="AH50" s="80"/>
+      <c r="AI50" s="64">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="AJ50" s="82"/>
+      <c r="AJ50" s="81"/>
       <c r="AK50" s="42">
         <f t="shared" si="3"/>
         <v>50</v>
@@ -5930,75 +5969,75 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM50" s="86"/>
-      <c r="AN50" s="81">
+      <c r="AM50" s="85"/>
+      <c r="AN50" s="80">
         <f t="shared" si="16"/>
         <v>50</v>
       </c>
-      <c r="AO50" s="156" t="s">
+      <c r="AO50" s="154" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:44" ht="60" x14ac:dyDescent="0.25">
-      <c r="A51" s="69">
+      <c r="A51" s="68">
         <v>36</v>
       </c>
-      <c r="B51" s="70" t="s">
+      <c r="B51" s="69" t="s">
         <v>114</v>
       </c>
-      <c r="C51" s="90">
+      <c r="C51" s="89">
         <v>8101736</v>
       </c>
-      <c r="D51" s="72"/>
-      <c r="E51" s="72"/>
-      <c r="F51" s="72"/>
-      <c r="G51" s="72"/>
-      <c r="H51" s="72"/>
-      <c r="I51" s="72"/>
-      <c r="J51" s="72"/>
-      <c r="K51" s="72">
+      <c r="D51" s="71"/>
+      <c r="E51" s="71"/>
+      <c r="F51" s="71"/>
+      <c r="G51" s="71"/>
+      <c r="H51" s="71"/>
+      <c r="I51" s="71"/>
+      <c r="J51" s="71"/>
+      <c r="K51" s="71">
         <v>3750</v>
       </c>
       <c r="L51" s="52"/>
       <c r="M51" s="53">
         <v>507.4</v>
       </c>
-      <c r="N51" s="91">
+      <c r="N51" s="90">
         <v>50</v>
       </c>
-      <c r="O51" s="73">
+      <c r="O51" s="72">
         <v>50</v>
       </c>
-      <c r="P51" s="73"/>
-      <c r="Q51" s="73"/>
-      <c r="R51" s="73"/>
-      <c r="S51" s="74"/>
-      <c r="T51" s="73"/>
-      <c r="U51" s="75"/>
-      <c r="V51" s="76"/>
+      <c r="P51" s="72"/>
+      <c r="Q51" s="72"/>
+      <c r="R51" s="72"/>
+      <c r="S51" s="73"/>
+      <c r="T51" s="72"/>
+      <c r="U51" s="74"/>
+      <c r="V51" s="75"/>
       <c r="W51" s="57">
         <f>SUM(O51:V51)</f>
         <v>50</v>
       </c>
-      <c r="X51" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y51" s="77"/>
-      <c r="Z51" s="60">
+      <c r="X51" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="189"/>
+      <c r="Z51" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA51" s="79">
+      <c r="AA51" s="78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB51" s="79">
+      <c r="AB51" s="78">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC51" s="80"/>
-      <c r="AD51" s="63"/>
-      <c r="AE51" s="80">
+      <c r="AC51" s="79"/>
+      <c r="AD51" s="62"/>
+      <c r="AE51" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -6006,13 +6045,13 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="AG51" s="81"/>
-      <c r="AH51" s="81"/>
-      <c r="AI51" s="65">
+      <c r="AG51" s="80"/>
+      <c r="AH51" s="80"/>
+      <c r="AI51" s="64">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="AJ51" s="82"/>
+      <c r="AJ51" s="81"/>
       <c r="AK51" s="42">
         <f t="shared" si="3"/>
         <v>50</v>
@@ -6021,75 +6060,75 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM51" s="86"/>
-      <c r="AN51" s="81">
+      <c r="AM51" s="85"/>
+      <c r="AN51" s="80">
         <f t="shared" si="16"/>
         <v>50</v>
       </c>
-      <c r="AO51" s="158" t="s">
+      <c r="AO51" s="156" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="52" spans="1:44" ht="45" x14ac:dyDescent="0.25">
-      <c r="A52" s="69">
+      <c r="A52" s="68">
         <v>37</v>
       </c>
-      <c r="B52" s="70" t="s">
+      <c r="B52" s="69" t="s">
         <v>115</v>
       </c>
-      <c r="C52" s="90">
+      <c r="C52" s="89">
         <v>8112949</v>
       </c>
-      <c r="D52" s="72"/>
-      <c r="E52" s="72"/>
-      <c r="F52" s="72"/>
-      <c r="G52" s="72"/>
-      <c r="H52" s="72"/>
-      <c r="I52" s="72"/>
-      <c r="J52" s="72"/>
-      <c r="K52" s="72">
+      <c r="D52" s="71"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="71"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="71">
         <v>250</v>
       </c>
       <c r="L52" s="52"/>
       <c r="M52" s="53">
         <v>182.3</v>
       </c>
-      <c r="N52" s="91">
+      <c r="N52" s="90">
         <v>15</v>
       </c>
-      <c r="O52" s="73">
+      <c r="O52" s="72">
         <v>15</v>
       </c>
-      <c r="P52" s="73"/>
-      <c r="Q52" s="73"/>
-      <c r="R52" s="73"/>
-      <c r="S52" s="74"/>
-      <c r="T52" s="73"/>
-      <c r="U52" s="75"/>
-      <c r="V52" s="75"/>
+      <c r="P52" s="72"/>
+      <c r="Q52" s="72"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="73"/>
+      <c r="T52" s="72"/>
+      <c r="U52" s="74"/>
+      <c r="V52" s="74"/>
       <c r="W52" s="57">
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="X52" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="77"/>
-      <c r="Z52" s="60">
+      <c r="X52" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="189"/>
+      <c r="Z52" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA52" s="79">
+      <c r="AA52" s="78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB52" s="79">
+      <c r="AB52" s="78">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC52" s="80"/>
-      <c r="AD52" s="63"/>
-      <c r="AE52" s="80">
+      <c r="AC52" s="79"/>
+      <c r="AD52" s="62"/>
+      <c r="AE52" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -6097,13 +6136,13 @@
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="AG52" s="81"/>
-      <c r="AH52" s="81"/>
-      <c r="AI52" s="65">
+      <c r="AG52" s="80"/>
+      <c r="AH52" s="80"/>
+      <c r="AI52" s="64">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="AJ52" s="82"/>
+      <c r="AJ52" s="81"/>
       <c r="AK52" s="42">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -6112,75 +6151,75 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM52" s="86"/>
-      <c r="AN52" s="81">
+      <c r="AM52" s="85"/>
+      <c r="AN52" s="80">
         <f t="shared" si="16"/>
         <v>15</v>
       </c>
-      <c r="AO52" s="158" t="s">
+      <c r="AO52" s="156" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:44" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="69">
+      <c r="A53" s="68">
         <v>38</v>
       </c>
-      <c r="B53" s="70" t="s">
+      <c r="B53" s="69" t="s">
         <v>116</v>
       </c>
-      <c r="C53" s="90">
+      <c r="C53" s="89">
         <v>8111980</v>
       </c>
-      <c r="D53" s="72"/>
-      <c r="E53" s="72"/>
-      <c r="F53" s="72"/>
-      <c r="G53" s="72"/>
-      <c r="H53" s="72"/>
-      <c r="I53" s="72"/>
-      <c r="J53" s="72"/>
-      <c r="K53" s="72">
+      <c r="D53" s="71"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="71"/>
+      <c r="H53" s="71"/>
+      <c r="I53" s="71"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="71">
         <v>418</v>
       </c>
       <c r="L53" s="52"/>
       <c r="M53" s="53">
         <v>359.4</v>
       </c>
-      <c r="N53" s="91">
+      <c r="N53" s="90">
         <v>33</v>
       </c>
-      <c r="O53" s="73">
+      <c r="O53" s="72">
         <v>33</v>
       </c>
-      <c r="P53" s="73"/>
-      <c r="Q53" s="73"/>
-      <c r="R53" s="73"/>
-      <c r="S53" s="74"/>
-      <c r="T53" s="73"/>
-      <c r="U53" s="75"/>
-      <c r="V53" s="75"/>
+      <c r="P53" s="72"/>
+      <c r="Q53" s="72"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="73"/>
+      <c r="T53" s="72"/>
+      <c r="U53" s="74"/>
+      <c r="V53" s="74"/>
       <c r="W53" s="57">
         <f t="shared" si="8"/>
         <v>33</v>
       </c>
-      <c r="X53" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y53" s="77"/>
-      <c r="Z53" s="60">
+      <c r="X53" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="189"/>
+      <c r="Z53" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA53" s="79">
+      <c r="AA53" s="78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB53" s="79">
+      <c r="AB53" s="78">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC53" s="80"/>
-      <c r="AD53" s="63"/>
-      <c r="AE53" s="80">
+      <c r="AC53" s="79"/>
+      <c r="AD53" s="62"/>
+      <c r="AE53" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -6188,13 +6227,13 @@
         <f t="shared" si="5"/>
         <v>33</v>
       </c>
-      <c r="AG53" s="81"/>
-      <c r="AH53" s="81"/>
-      <c r="AI53" s="65">
+      <c r="AG53" s="80"/>
+      <c r="AH53" s="80"/>
+      <c r="AI53" s="64">
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="AJ53" s="82"/>
+      <c r="AJ53" s="81"/>
       <c r="AK53" s="42">
         <f t="shared" si="3"/>
         <v>33</v>
@@ -6203,75 +6242,75 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM53" s="86"/>
-      <c r="AN53" s="81">
+      <c r="AM53" s="85"/>
+      <c r="AN53" s="80">
         <f t="shared" si="16"/>
         <v>33</v>
       </c>
-      <c r="AO53" s="107" t="s">
+      <c r="AO53" s="106" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="54" spans="1:44" ht="86.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="69">
+      <c r="A54" s="68">
         <v>39</v>
       </c>
-      <c r="B54" s="70" t="s">
+      <c r="B54" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="C54" s="90">
+      <c r="C54" s="89">
         <v>8113485</v>
       </c>
-      <c r="D54" s="72"/>
-      <c r="E54" s="72"/>
-      <c r="F54" s="72"/>
-      <c r="G54" s="72"/>
-      <c r="H54" s="72"/>
-      <c r="I54" s="72"/>
-      <c r="J54" s="72"/>
-      <c r="K54" s="72">
+      <c r="D54" s="71"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="71">
         <v>500</v>
       </c>
       <c r="L54" s="52"/>
       <c r="M54" s="53">
         <v>442</v>
       </c>
-      <c r="N54" s="91">
+      <c r="N54" s="90">
         <v>50</v>
       </c>
-      <c r="O54" s="73">
+      <c r="O54" s="72">
         <v>50</v>
       </c>
-      <c r="P54" s="73"/>
-      <c r="Q54" s="73"/>
-      <c r="R54" s="73"/>
-      <c r="S54" s="74"/>
-      <c r="T54" s="73"/>
-      <c r="U54" s="73"/>
-      <c r="V54" s="94"/>
+      <c r="P54" s="72"/>
+      <c r="Q54" s="72"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="73"/>
+      <c r="T54" s="72"/>
+      <c r="U54" s="72"/>
+      <c r="V54" s="93"/>
       <c r="W54" s="57">
         <f t="shared" si="8"/>
         <v>50</v>
       </c>
-      <c r="X54" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y54" s="77"/>
-      <c r="Z54" s="60">
+      <c r="X54" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="189"/>
+      <c r="Z54" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA54" s="79">
+      <c r="AA54" s="78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB54" s="79">
+      <c r="AB54" s="78">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC54" s="80"/>
-      <c r="AD54" s="63"/>
-      <c r="AE54" s="80">
+      <c r="AC54" s="79"/>
+      <c r="AD54" s="62"/>
+      <c r="AE54" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -6279,13 +6318,13 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="AG54" s="81"/>
-      <c r="AH54" s="81"/>
-      <c r="AI54" s="65">
+      <c r="AG54" s="80"/>
+      <c r="AH54" s="80"/>
+      <c r="AI54" s="64">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="AJ54" s="82"/>
+      <c r="AJ54" s="81"/>
       <c r="AK54" s="42">
         <f t="shared" si="3"/>
         <v>50</v>
@@ -6294,75 +6333,75 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM54" s="86"/>
-      <c r="AN54" s="81">
+      <c r="AM54" s="85"/>
+      <c r="AN54" s="80">
         <f t="shared" si="16"/>
         <v>50</v>
       </c>
-      <c r="AO54" s="158" t="s">
+      <c r="AO54" s="156" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:44" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="69">
+      <c r="A55" s="68">
         <v>40</v>
       </c>
-      <c r="B55" s="70" t="s">
+      <c r="B55" s="69" t="s">
         <v>118</v>
       </c>
-      <c r="C55" s="90">
+      <c r="C55" s="89">
         <v>8113487</v>
       </c>
-      <c r="D55" s="72"/>
-      <c r="E55" s="72"/>
-      <c r="F55" s="72"/>
-      <c r="G55" s="72"/>
-      <c r="H55" s="72"/>
-      <c r="I55" s="72"/>
-      <c r="J55" s="72"/>
-      <c r="K55" s="72">
+      <c r="D55" s="71"/>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="71"/>
+      <c r="I55" s="71"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="71">
         <v>2000</v>
       </c>
       <c r="L55" s="52"/>
       <c r="M55" s="53">
         <v>229</v>
       </c>
-      <c r="N55" s="91">
+      <c r="N55" s="90">
         <v>37</v>
       </c>
-      <c r="O55" s="73">
+      <c r="O55" s="72">
         <v>50</v>
       </c>
-      <c r="P55" s="73"/>
-      <c r="Q55" s="73"/>
-      <c r="R55" s="73"/>
-      <c r="S55" s="74"/>
-      <c r="T55" s="73"/>
-      <c r="U55" s="75"/>
-      <c r="V55" s="76"/>
+      <c r="P55" s="72"/>
+      <c r="Q55" s="72"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="73"/>
+      <c r="T55" s="72"/>
+      <c r="U55" s="74"/>
+      <c r="V55" s="75"/>
       <c r="W55" s="57">
         <f t="shared" si="8"/>
         <v>50</v>
       </c>
-      <c r="X55" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y55" s="77"/>
-      <c r="Z55" s="60">
+      <c r="X55" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="189"/>
+      <c r="Z55" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA55" s="79">
+      <c r="AA55" s="78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB55" s="79">
+      <c r="AB55" s="78">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC55" s="80"/>
-      <c r="AD55" s="63"/>
-      <c r="AE55" s="80">
+      <c r="AC55" s="79"/>
+      <c r="AD55" s="62"/>
+      <c r="AE55" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -6370,13 +6409,13 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="AG55" s="81"/>
-      <c r="AH55" s="81"/>
-      <c r="AI55" s="65">
+      <c r="AG55" s="80"/>
+      <c r="AH55" s="80"/>
+      <c r="AI55" s="64">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="AJ55" s="82"/>
+      <c r="AJ55" s="81"/>
       <c r="AK55" s="42">
         <f t="shared" si="3"/>
         <v>50</v>
@@ -6385,75 +6424,75 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM55" s="86"/>
-      <c r="AN55" s="81">
+      <c r="AM55" s="85"/>
+      <c r="AN55" s="80">
         <f t="shared" si="16"/>
         <v>50</v>
       </c>
-      <c r="AO55" s="156" t="s">
+      <c r="AO55" s="154" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="56" spans="1:44" ht="46.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="69">
+      <c r="A56" s="68">
         <v>41</v>
       </c>
-      <c r="B56" s="70" t="s">
+      <c r="B56" s="69" t="s">
         <v>119</v>
       </c>
-      <c r="C56" s="90">
+      <c r="C56" s="89">
         <v>8112948</v>
       </c>
-      <c r="D56" s="72"/>
-      <c r="E56" s="72"/>
-      <c r="F56" s="72"/>
-      <c r="G56" s="72"/>
-      <c r="H56" s="72"/>
-      <c r="I56" s="72"/>
-      <c r="J56" s="72"/>
-      <c r="K56" s="72">
+      <c r="D56" s="71"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="71"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="71">
         <v>284</v>
       </c>
       <c r="L56" s="52"/>
       <c r="M56" s="53">
         <v>129.5</v>
       </c>
-      <c r="N56" s="91">
+      <c r="N56" s="90">
         <v>6</v>
       </c>
-      <c r="O56" s="73">
+      <c r="O56" s="72">
         <v>6</v>
       </c>
-      <c r="P56" s="73"/>
-      <c r="Q56" s="73"/>
-      <c r="R56" s="73"/>
-      <c r="S56" s="74"/>
-      <c r="T56" s="73"/>
-      <c r="U56" s="75"/>
-      <c r="V56" s="75"/>
+      <c r="P56" s="72"/>
+      <c r="Q56" s="72"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="73"/>
+      <c r="T56" s="72"/>
+      <c r="U56" s="74"/>
+      <c r="V56" s="74"/>
       <c r="W56" s="57">
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="X56" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y56" s="77"/>
-      <c r="Z56" s="60">
+      <c r="X56" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="189"/>
+      <c r="Z56" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA56" s="79">
+      <c r="AA56" s="78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB56" s="79">
+      <c r="AB56" s="78">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC56" s="80"/>
-      <c r="AD56" s="63"/>
-      <c r="AE56" s="80">
+      <c r="AC56" s="79"/>
+      <c r="AD56" s="62"/>
+      <c r="AE56" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -6461,13 +6500,13 @@
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="AG56" s="81"/>
-      <c r="AH56" s="81"/>
-      <c r="AI56" s="65">
+      <c r="AG56" s="80"/>
+      <c r="AH56" s="80"/>
+      <c r="AI56" s="64">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="AJ56" s="82"/>
+      <c r="AJ56" s="81"/>
       <c r="AK56" s="42">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -6476,75 +6515,75 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM56" s="86"/>
-      <c r="AN56" s="81">
+      <c r="AM56" s="85"/>
+      <c r="AN56" s="80">
         <f t="shared" si="16"/>
         <v>6</v>
       </c>
-      <c r="AO56" s="107" t="s">
+      <c r="AO56" s="106" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="57" spans="1:44" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="69">
+      <c r="A57" s="68">
         <v>42</v>
       </c>
-      <c r="B57" s="70" t="s">
+      <c r="B57" s="69" t="s">
         <v>120</v>
       </c>
-      <c r="C57" s="90">
+      <c r="C57" s="89">
         <v>8118634</v>
       </c>
-      <c r="D57" s="72"/>
-      <c r="E57" s="72"/>
-      <c r="F57" s="72"/>
-      <c r="G57" s="72"/>
-      <c r="H57" s="72"/>
-      <c r="I57" s="72"/>
-      <c r="J57" s="72"/>
-      <c r="K57" s="72">
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="71">
         <v>460</v>
       </c>
       <c r="L57" s="52"/>
       <c r="M57" s="53">
         <v>388.14</v>
       </c>
-      <c r="N57" s="91">
+      <c r="N57" s="90">
         <v>23</v>
       </c>
-      <c r="O57" s="73">
+      <c r="O57" s="72">
         <v>23</v>
       </c>
-      <c r="P57" s="73"/>
-      <c r="Q57" s="73"/>
-      <c r="R57" s="73"/>
-      <c r="S57" s="74"/>
-      <c r="T57" s="73"/>
-      <c r="U57" s="75"/>
-      <c r="V57" s="75"/>
+      <c r="P57" s="72"/>
+      <c r="Q57" s="72"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="73"/>
+      <c r="T57" s="72"/>
+      <c r="U57" s="74"/>
+      <c r="V57" s="74"/>
       <c r="W57" s="57">
         <f t="shared" si="8"/>
         <v>23</v>
       </c>
-      <c r="X57" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="77"/>
-      <c r="Z57" s="60">
+      <c r="X57" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="189"/>
+      <c r="Z57" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA57" s="79">
+      <c r="AA57" s="78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB57" s="79">
+      <c r="AB57" s="78">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC57" s="80"/>
-      <c r="AD57" s="63"/>
-      <c r="AE57" s="80">
+      <c r="AC57" s="79"/>
+      <c r="AD57" s="62"/>
+      <c r="AE57" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -6552,13 +6591,13 @@
         <f t="shared" si="5"/>
         <v>23</v>
       </c>
-      <c r="AG57" s="81"/>
-      <c r="AH57" s="81"/>
-      <c r="AI57" s="65">
+      <c r="AG57" s="80"/>
+      <c r="AH57" s="80"/>
+      <c r="AI57" s="64">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="AJ57" s="82"/>
+      <c r="AJ57" s="81"/>
       <c r="AK57" s="42">
         <f t="shared" si="3"/>
         <v>23</v>
@@ -6567,75 +6606,75 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM57" s="86"/>
-      <c r="AN57" s="81">
+      <c r="AM57" s="85"/>
+      <c r="AN57" s="80">
         <f t="shared" si="16"/>
         <v>23</v>
       </c>
-      <c r="AO57" s="107" t="s">
+      <c r="AO57" s="106" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="58" spans="1:44" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="69">
+      <c r="A58" s="68">
         <v>43</v>
       </c>
-      <c r="B58" s="70" t="s">
+      <c r="B58" s="69" t="s">
         <v>121</v>
       </c>
-      <c r="C58" s="90">
+      <c r="C58" s="89">
         <v>8111984</v>
       </c>
-      <c r="D58" s="72"/>
-      <c r="E58" s="72"/>
-      <c r="F58" s="72"/>
-      <c r="G58" s="72"/>
-      <c r="H58" s="72"/>
-      <c r="I58" s="72"/>
-      <c r="J58" s="72"/>
-      <c r="K58" s="72">
+      <c r="D58" s="71"/>
+      <c r="E58" s="71"/>
+      <c r="F58" s="71"/>
+      <c r="G58" s="71"/>
+      <c r="H58" s="71"/>
+      <c r="I58" s="71"/>
+      <c r="J58" s="71"/>
+      <c r="K58" s="71">
         <v>3000</v>
       </c>
       <c r="L58" s="52"/>
       <c r="M58" s="53">
         <v>531</v>
       </c>
-      <c r="N58" s="91">
+      <c r="N58" s="90">
         <v>25</v>
       </c>
-      <c r="O58" s="73">
+      <c r="O58" s="72">
         <v>25</v>
       </c>
-      <c r="P58" s="73"/>
-      <c r="Q58" s="73"/>
-      <c r="R58" s="73"/>
-      <c r="S58" s="74"/>
-      <c r="T58" s="73"/>
-      <c r="U58" s="75"/>
-      <c r="V58" s="76"/>
+      <c r="P58" s="72"/>
+      <c r="Q58" s="72"/>
+      <c r="R58" s="72"/>
+      <c r="S58" s="73"/>
+      <c r="T58" s="72"/>
+      <c r="U58" s="74"/>
+      <c r="V58" s="75"/>
       <c r="W58" s="57">
         <f t="shared" si="8"/>
         <v>25</v>
       </c>
-      <c r="X58" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="77"/>
-      <c r="Z58" s="60">
+      <c r="X58" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="189"/>
+      <c r="Z58" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA58" s="79">
+      <c r="AA58" s="78">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AB58" s="79">
+      <c r="AB58" s="78">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC58" s="80"/>
-      <c r="AD58" s="63"/>
-      <c r="AE58" s="80">
+      <c r="AC58" s="79"/>
+      <c r="AD58" s="62"/>
+      <c r="AE58" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -6643,13 +6682,13 @@
         <f t="shared" si="5"/>
         <v>25</v>
       </c>
-      <c r="AG58" s="81"/>
-      <c r="AH58" s="81"/>
-      <c r="AI58" s="65">
+      <c r="AG58" s="80"/>
+      <c r="AH58" s="80"/>
+      <c r="AI58" s="64">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="AJ58" s="82"/>
+      <c r="AJ58" s="81"/>
       <c r="AK58" s="42">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -6658,73 +6697,73 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM58" s="86"/>
-      <c r="AN58" s="81">
+      <c r="AM58" s="85"/>
+      <c r="AN58" s="80">
         <f t="shared" si="16"/>
         <v>25</v>
       </c>
-      <c r="AO58" s="158" t="s">
+      <c r="AO58" s="156" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:44" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="69">
+      <c r="A59" s="68">
         <v>44</v>
       </c>
-      <c r="B59" s="70" t="s">
+      <c r="B59" s="69" t="s">
         <v>122</v>
       </c>
-      <c r="C59" s="90">
+      <c r="C59" s="89">
         <v>8111979</v>
       </c>
-      <c r="D59" s="72"/>
-      <c r="E59" s="72"/>
-      <c r="F59" s="72"/>
-      <c r="G59" s="72"/>
-      <c r="H59" s="72"/>
-      <c r="I59" s="72"/>
-      <c r="J59" s="72"/>
-      <c r="K59" s="72">
+      <c r="D59" s="71"/>
+      <c r="E59" s="71"/>
+      <c r="F59" s="71"/>
+      <c r="G59" s="71"/>
+      <c r="H59" s="71"/>
+      <c r="I59" s="71"/>
+      <c r="J59" s="71"/>
+      <c r="K59" s="71">
         <v>3000</v>
       </c>
       <c r="L59" s="52"/>
       <c r="M59" s="53">
         <v>547.70000000000005</v>
       </c>
-      <c r="N59" s="91">
+      <c r="N59" s="90">
         <v>265</v>
       </c>
-      <c r="O59" s="73"/>
-      <c r="P59" s="73"/>
-      <c r="Q59" s="73"/>
-      <c r="R59" s="73"/>
-      <c r="S59" s="73">
+      <c r="O59" s="72"/>
+      <c r="P59" s="72"/>
+      <c r="Q59" s="72"/>
+      <c r="R59" s="72"/>
+      <c r="S59" s="72">
         <v>265</v>
       </c>
-      <c r="T59" s="73"/>
-      <c r="U59" s="73"/>
-      <c r="V59" s="94"/>
+      <c r="T59" s="72"/>
+      <c r="U59" s="72"/>
+      <c r="V59" s="93"/>
       <c r="W59" s="57">
         <f t="shared" si="8"/>
         <v>265</v>
       </c>
-      <c r="X59" s="77">
-        <v>0</v>
-      </c>
-      <c r="Y59" s="77"/>
-      <c r="Z59" s="60">
+      <c r="X59" s="76">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="189"/>
+      <c r="Z59" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA59" s="79">
-        <v>0</v>
-      </c>
-      <c r="AB59" s="79">
-        <v>0</v>
-      </c>
-      <c r="AC59" s="80"/>
-      <c r="AD59" s="63"/>
-      <c r="AE59" s="80">
+      <c r="AA59" s="78">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="78">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="79"/>
+      <c r="AD59" s="62"/>
+      <c r="AE59" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -6732,13 +6771,13 @@
         <f t="shared" si="5"/>
         <v>265</v>
       </c>
-      <c r="AG59" s="81"/>
-      <c r="AH59" s="81"/>
-      <c r="AI59" s="65">
+      <c r="AG59" s="80"/>
+      <c r="AH59" s="80"/>
+      <c r="AI59" s="64">
         <f t="shared" si="2"/>
         <v>265</v>
       </c>
-      <c r="AJ59" s="82"/>
+      <c r="AJ59" s="81"/>
       <c r="AK59" s="42">
         <f t="shared" si="3"/>
         <v>265</v>
@@ -6747,77 +6786,77 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM59" s="86"/>
-      <c r="AN59" s="81">
+      <c r="AM59" s="85"/>
+      <c r="AN59" s="80">
         <f t="shared" si="16"/>
         <v>265</v>
       </c>
-      <c r="AO59" s="158" t="s">
+      <c r="AO59" s="156" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:44" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="69">
+      <c r="A60" s="68">
         <v>45</v>
       </c>
-      <c r="B60" s="70" t="s">
+      <c r="B60" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="C60" s="90">
+      <c r="C60" s="89">
         <v>8113209</v>
       </c>
-      <c r="D60" s="72"/>
-      <c r="E60" s="72"/>
-      <c r="F60" s="72"/>
-      <c r="G60" s="72"/>
-      <c r="H60" s="72"/>
-      <c r="I60" s="72"/>
-      <c r="J60" s="72"/>
-      <c r="K60" s="72">
+      <c r="D60" s="71"/>
+      <c r="E60" s="71"/>
+      <c r="F60" s="71"/>
+      <c r="G60" s="71"/>
+      <c r="H60" s="71"/>
+      <c r="I60" s="71"/>
+      <c r="J60" s="71"/>
+      <c r="K60" s="71">
         <v>300</v>
       </c>
       <c r="L60" s="52"/>
       <c r="M60" s="53">
         <v>267.56</v>
       </c>
-      <c r="N60" s="91">
+      <c r="N60" s="90">
         <v>61775</v>
       </c>
-      <c r="O60" s="73">
+      <c r="O60" s="72">
         <v>61775</v>
       </c>
-      <c r="P60" s="73"/>
-      <c r="Q60" s="73"/>
-      <c r="R60" s="73"/>
-      <c r="S60" s="74"/>
-      <c r="T60" s="73"/>
-      <c r="U60" s="75"/>
-      <c r="V60" s="76"/>
+      <c r="P60" s="72"/>
+      <c r="Q60" s="72"/>
+      <c r="R60" s="72"/>
+      <c r="S60" s="73"/>
+      <c r="T60" s="72"/>
+      <c r="U60" s="74"/>
+      <c r="V60" s="75"/>
       <c r="W60" s="57">
         <f t="shared" si="8"/>
         <v>61775</v>
       </c>
-      <c r="X60" s="77">
+      <c r="X60" s="76">
         <v>28362.960999999999</v>
       </c>
-      <c r="Y60" s="77"/>
-      <c r="Z60" s="60">
+      <c r="Y60" s="189"/>
+      <c r="Z60" s="59">
         <f t="shared" si="4"/>
         <v>28362.960999999999</v>
       </c>
-      <c r="AA60" s="79">
+      <c r="AA60" s="78">
         <f t="shared" si="14"/>
         <v>0.45913332254148115</v>
       </c>
-      <c r="AB60" s="79">
+      <c r="AB60" s="78">
         <f t="shared" si="15"/>
         <v>0.45913332254148115</v>
       </c>
-      <c r="AC60" s="80">
+      <c r="AC60" s="79">
         <v>6000</v>
       </c>
-      <c r="AD60" s="63"/>
-      <c r="AE60" s="80">
+      <c r="AD60" s="62"/>
+      <c r="AE60" s="79">
         <f t="shared" si="7"/>
         <v>6000</v>
       </c>
@@ -6825,13 +6864,13 @@
         <f t="shared" si="5"/>
         <v>33412.039000000004</v>
       </c>
-      <c r="AG60" s="81"/>
-      <c r="AH60" s="81"/>
-      <c r="AI60" s="65">
+      <c r="AG60" s="80"/>
+      <c r="AH60" s="80"/>
+      <c r="AI60" s="64">
         <f t="shared" si="2"/>
         <v>33412.039000000004</v>
       </c>
-      <c r="AJ60" s="82">
+      <c r="AJ60" s="81">
         <v>10000</v>
       </c>
       <c r="AK60" s="42">
@@ -6842,77 +6881,77 @@
         <f t="shared" si="6"/>
         <v>0.62101110481586397</v>
       </c>
-      <c r="AM60" s="86"/>
-      <c r="AN60" s="81">
+      <c r="AM60" s="85"/>
+      <c r="AN60" s="80">
         <f t="shared" si="16"/>
         <v>33412.039000000004</v>
       </c>
-      <c r="AO60" s="156" t="s">
+      <c r="AO60" s="154" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="61" spans="1:44" ht="45" x14ac:dyDescent="0.25">
-      <c r="A61" s="69">
+      <c r="A61" s="68">
         <v>46</v>
       </c>
-      <c r="B61" s="70" t="s">
+      <c r="B61" s="69" t="s">
         <v>124</v>
       </c>
-      <c r="C61" s="90">
+      <c r="C61" s="89">
         <v>8100888</v>
       </c>
-      <c r="D61" s="72"/>
-      <c r="E61" s="72"/>
-      <c r="F61" s="72"/>
-      <c r="G61" s="72"/>
-      <c r="H61" s="72"/>
-      <c r="I61" s="72"/>
-      <c r="J61" s="72"/>
-      <c r="K61" s="72">
+      <c r="D61" s="71"/>
+      <c r="E61" s="71"/>
+      <c r="F61" s="71"/>
+      <c r="G61" s="71"/>
+      <c r="H61" s="71"/>
+      <c r="I61" s="71"/>
+      <c r="J61" s="71"/>
+      <c r="K61" s="71">
         <v>1983</v>
       </c>
       <c r="L61" s="52"/>
       <c r="M61" s="53">
         <v>1530</v>
       </c>
-      <c r="N61" s="91">
+      <c r="N61" s="90">
         <v>507784</v>
       </c>
-      <c r="O61" s="73">
+      <c r="O61" s="72">
         <v>745850</v>
       </c>
-      <c r="P61" s="73"/>
-      <c r="Q61" s="73"/>
-      <c r="R61" s="73"/>
-      <c r="S61" s="74"/>
-      <c r="T61" s="73"/>
-      <c r="U61" s="75">
+      <c r="P61" s="72"/>
+      <c r="Q61" s="72"/>
+      <c r="R61" s="72"/>
+      <c r="S61" s="73"/>
+      <c r="T61" s="72"/>
+      <c r="U61" s="74">
         <v>-118066</v>
       </c>
-      <c r="V61" s="76"/>
+      <c r="V61" s="75"/>
       <c r="W61" s="57">
         <f t="shared" si="8"/>
         <v>627784</v>
       </c>
-      <c r="X61" s="77">
+      <c r="X61" s="76">
         <v>497783.54</v>
       </c>
-      <c r="Y61" s="77"/>
-      <c r="Z61" s="60">
+      <c r="Y61" s="189"/>
+      <c r="Z61" s="59">
         <f t="shared" si="4"/>
         <v>497783.54</v>
       </c>
-      <c r="AA61" s="79">
+      <c r="AA61" s="78">
         <f>Z61/W61</f>
         <v>0.79292167369668543</v>
       </c>
-      <c r="AB61" s="79">
+      <c r="AB61" s="78">
         <f>Z61/N61</f>
         <v>0.98030568115576699</v>
       </c>
-      <c r="AC61" s="80"/>
-      <c r="AD61" s="63"/>
-      <c r="AE61" s="80">
+      <c r="AC61" s="79"/>
+      <c r="AD61" s="62"/>
+      <c r="AE61" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -6920,13 +6959,13 @@
         <f t="shared" si="5"/>
         <v>130000.46000000002</v>
       </c>
-      <c r="AG61" s="81"/>
-      <c r="AH61" s="81"/>
-      <c r="AI61" s="65">
+      <c r="AG61" s="80"/>
+      <c r="AH61" s="80"/>
+      <c r="AI61" s="64">
         <f t="shared" si="2"/>
         <v>130000.46000000002</v>
       </c>
-      <c r="AJ61" s="82">
+      <c r="AJ61" s="81">
         <v>270000</v>
       </c>
       <c r="AK61" s="42">
@@ -6937,18 +6976,18 @@
         <f t="shared" si="6"/>
         <v>1.2230059064901304</v>
       </c>
-      <c r="AM61" s="86"/>
-      <c r="AN61" s="81">
+      <c r="AM61" s="85"/>
+      <c r="AN61" s="80">
         <f t="shared" si="16"/>
         <v>130000.46000000002</v>
       </c>
-      <c r="AO61" s="158" t="s">
+      <c r="AO61" s="156" t="s">
         <v>150</v>
       </c>
-      <c r="AQ61" s="110">
+      <c r="AQ61" s="109">
         <v>167340</v>
       </c>
-      <c r="AR61" s="106">
+      <c r="AR61" s="105">
         <v>167340</v>
       </c>
     </row>
@@ -6959,38 +6998,38 @@
       <c r="B62" s="49" t="s">
         <v>126</v>
       </c>
-      <c r="C62" s="111"/>
-      <c r="D62" s="105"/>
-      <c r="E62" s="105"/>
-      <c r="F62" s="105"/>
-      <c r="G62" s="105"/>
-      <c r="H62" s="105"/>
-      <c r="I62" s="105"/>
-      <c r="J62" s="105"/>
-      <c r="K62" s="105"/>
+      <c r="C62" s="110"/>
+      <c r="D62" s="104"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="104"/>
+      <c r="G62" s="104"/>
+      <c r="H62" s="104"/>
+      <c r="I62" s="104"/>
+      <c r="J62" s="104"/>
+      <c r="K62" s="104"/>
       <c r="L62" s="52"/>
       <c r="M62" s="53"/>
-      <c r="N62" s="105"/>
-      <c r="O62" s="105"/>
-      <c r="P62" s="105"/>
-      <c r="Q62" s="105"/>
-      <c r="R62" s="105"/>
-      <c r="S62" s="74"/>
-      <c r="T62" s="105"/>
-      <c r="U62" s="105"/>
-      <c r="V62" s="105"/>
+      <c r="N62" s="104"/>
+      <c r="O62" s="104"/>
+      <c r="P62" s="104"/>
+      <c r="Q62" s="104"/>
+      <c r="R62" s="104"/>
+      <c r="S62" s="73"/>
+      <c r="T62" s="104"/>
+      <c r="U62" s="104"/>
+      <c r="V62" s="104"/>
       <c r="W62" s="57">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X62" s="77"/>
-      <c r="Y62" s="77"/>
-      <c r="Z62" s="60"/>
-      <c r="AA62" s="79"/>
-      <c r="AB62" s="79"/>
-      <c r="AC62" s="80"/>
-      <c r="AD62" s="112"/>
-      <c r="AE62" s="80">
+      <c r="X62" s="76"/>
+      <c r="Y62" s="189"/>
+      <c r="Z62" s="59"/>
+      <c r="AA62" s="78"/>
+      <c r="AB62" s="78"/>
+      <c r="AC62" s="79"/>
+      <c r="AD62" s="111"/>
+      <c r="AE62" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -6998,97 +7037,97 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG62" s="81"/>
-      <c r="AH62" s="81"/>
-      <c r="AI62" s="65">
+      <c r="AG62" s="80"/>
+      <c r="AH62" s="80"/>
+      <c r="AI62" s="64">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AJ62" s="82"/>
+      <c r="AJ62" s="81"/>
       <c r="AK62" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AL62" s="43"/>
-      <c r="AM62" s="86"/>
-      <c r="AN62" s="86"/>
+      <c r="AM62" s="85"/>
+      <c r="AN62" s="85"/>
       <c r="AO62" s="48"/>
-      <c r="AQ62" s="113">
+      <c r="AQ62" s="112">
         <f>AQ61-Z61</f>
         <v>-330443.53999999998</v>
       </c>
-      <c r="AR62" s="114">
+      <c r="AR62" s="113">
         <f>AR61-Z61</f>
         <v>-330443.53999999998</v>
       </c>
     </row>
     <row r="63" spans="1:44" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="69">
+      <c r="A63" s="68">
         <v>1</v>
       </c>
-      <c r="B63" s="70" t="s">
+      <c r="B63" s="69" t="s">
         <v>127</v>
       </c>
-      <c r="C63" s="115" t="s">
+      <c r="C63" s="114" t="s">
         <v>128</v>
       </c>
-      <c r="D63" s="72"/>
-      <c r="E63" s="72"/>
-      <c r="F63" s="72"/>
-      <c r="G63" s="72"/>
-      <c r="H63" s="72"/>
-      <c r="I63" s="72"/>
-      <c r="J63" s="72">
+      <c r="D63" s="71"/>
+      <c r="E63" s="71"/>
+      <c r="F63" s="71"/>
+      <c r="G63" s="71"/>
+      <c r="H63" s="71"/>
+      <c r="I63" s="71"/>
+      <c r="J63" s="71">
         <v>5354</v>
       </c>
-      <c r="K63" s="72">
+      <c r="K63" s="71">
         <v>19662</v>
       </c>
       <c r="L63" s="52"/>
       <c r="M63" s="53">
         <v>19661.934000000001</v>
       </c>
-      <c r="N63" s="91">
+      <c r="N63" s="90">
         <v>5992</v>
       </c>
-      <c r="O63" s="73"/>
-      <c r="P63" s="73">
+      <c r="O63" s="72"/>
+      <c r="P63" s="72">
         <v>100</v>
       </c>
-      <c r="Q63" s="73"/>
-      <c r="R63" s="73">
+      <c r="Q63" s="72"/>
+      <c r="R63" s="72">
         <v>700</v>
       </c>
-      <c r="S63" s="74"/>
-      <c r="T63" s="73"/>
-      <c r="U63" s="73">
+      <c r="S63" s="73"/>
+      <c r="T63" s="72"/>
+      <c r="U63" s="72">
         <v>5992</v>
       </c>
-      <c r="V63" s="73"/>
+      <c r="V63" s="72"/>
       <c r="W63" s="57">
         <f t="shared" si="8"/>
         <v>6792</v>
       </c>
-      <c r="X63" s="77">
+      <c r="X63" s="76">
         <v>100</v>
       </c>
-      <c r="Y63" s="77"/>
-      <c r="Z63" s="60">
+      <c r="Y63" s="189"/>
+      <c r="Z63" s="59">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AA63" s="116">
+      <c r="AA63" s="115">
         <f>Z63/W63</f>
         <v>1.4723203769140165E-2</v>
       </c>
-      <c r="AB63" s="79">
-        <v>0</v>
-      </c>
-      <c r="AC63" s="80">
+      <c r="AB63" s="78">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="79">
         <v>3000</v>
       </c>
-      <c r="AD63" s="116"/>
-      <c r="AE63" s="80">
+      <c r="AD63" s="115"/>
+      <c r="AE63" s="79">
         <f t="shared" si="7"/>
         <v>3000</v>
       </c>
@@ -7096,13 +7135,13 @@
         <f t="shared" si="5"/>
         <v>6692</v>
       </c>
-      <c r="AG63" s="81"/>
-      <c r="AH63" s="81"/>
-      <c r="AI63" s="65">
+      <c r="AG63" s="80"/>
+      <c r="AH63" s="80"/>
+      <c r="AI63" s="64">
         <f t="shared" si="2"/>
         <v>6692</v>
       </c>
-      <c r="AJ63" s="82"/>
+      <c r="AJ63" s="81"/>
       <c r="AK63" s="42">
         <f t="shared" si="3"/>
         <v>6692</v>
@@ -7111,86 +7150,86 @@
         <f t="shared" si="6"/>
         <v>1.4723203769140165E-2</v>
       </c>
-      <c r="AM63" s="86"/>
-      <c r="AN63" s="86"/>
-      <c r="AO63" s="117" t="s">
+      <c r="AM63" s="85"/>
+      <c r="AN63" s="85"/>
+      <c r="AO63" s="116" t="s">
         <v>153</v>
       </c>
-      <c r="AR63" s="118">
+      <c r="AR63" s="117">
         <f>383-60</f>
         <v>323</v>
       </c>
     </row>
     <row r="64" spans="1:44" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="69">
+      <c r="A64" s="68">
         <v>2</v>
       </c>
-      <c r="B64" s="70" t="s">
+      <c r="B64" s="69" t="s">
         <v>129</v>
       </c>
-      <c r="C64" s="115" t="s">
+      <c r="C64" s="114" t="s">
         <v>130</v>
       </c>
-      <c r="D64" s="72"/>
-      <c r="E64" s="72">
+      <c r="D64" s="71"/>
+      <c r="E64" s="71">
         <v>7500</v>
       </c>
-      <c r="F64" s="72">
+      <c r="F64" s="71">
         <v>2600</v>
       </c>
-      <c r="G64" s="72"/>
-      <c r="H64" s="72"/>
-      <c r="I64" s="72"/>
-      <c r="J64" s="72">
+      <c r="G64" s="71"/>
+      <c r="H64" s="71"/>
+      <c r="I64" s="71"/>
+      <c r="J64" s="71">
         <v>6090</v>
       </c>
-      <c r="K64" s="72">
+      <c r="K64" s="71">
         <v>19816</v>
       </c>
       <c r="L64" s="52"/>
-      <c r="M64" s="72"/>
-      <c r="N64" s="91">
+      <c r="M64" s="71"/>
+      <c r="N64" s="90">
         <v>6500</v>
       </c>
-      <c r="O64" s="73"/>
-      <c r="P64" s="73">
+      <c r="O64" s="72"/>
+      <c r="P64" s="72">
         <v>100</v>
       </c>
-      <c r="Q64" s="73"/>
-      <c r="R64" s="73">
+      <c r="Q64" s="72"/>
+      <c r="R64" s="72">
         <v>1000</v>
       </c>
-      <c r="S64" s="74"/>
-      <c r="T64" s="73"/>
-      <c r="U64" s="75">
+      <c r="S64" s="73"/>
+      <c r="T64" s="72"/>
+      <c r="U64" s="74">
         <v>3000</v>
       </c>
-      <c r="V64" s="76"/>
+      <c r="V64" s="75"/>
       <c r="W64" s="57">
         <f t="shared" si="8"/>
         <v>4100</v>
       </c>
-      <c r="X64" s="77">
+      <c r="X64" s="76">
         <v>100</v>
       </c>
-      <c r="Y64" s="77"/>
-      <c r="Z64" s="60">
+      <c r="Y64" s="189"/>
+      <c r="Z64" s="59">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AA64" s="116">
+      <c r="AA64" s="115">
         <f t="shared" ref="AA64:AA66" si="17">Z64/W64</f>
         <v>2.4390243902439025E-2</v>
       </c>
-      <c r="AB64" s="79">
-        <v>0</v>
-      </c>
-      <c r="AC64" s="80">
+      <c r="AB64" s="78">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="79">
         <f>423+37</f>
         <v>460</v>
       </c>
-      <c r="AD64" s="116"/>
-      <c r="AE64" s="80">
+      <c r="AD64" s="115"/>
+      <c r="AE64" s="79">
         <f t="shared" si="7"/>
         <v>460</v>
       </c>
@@ -7198,13 +7237,13 @@
         <f t="shared" si="5"/>
         <v>4000</v>
       </c>
-      <c r="AG64" s="81"/>
-      <c r="AH64" s="81"/>
-      <c r="AI64" s="65">
+      <c r="AG64" s="80"/>
+      <c r="AH64" s="80"/>
+      <c r="AI64" s="64">
         <f t="shared" si="2"/>
         <v>4000</v>
       </c>
-      <c r="AJ64" s="82"/>
+      <c r="AJ64" s="81"/>
       <c r="AK64" s="42">
         <f t="shared" si="3"/>
         <v>4000</v>
@@ -7213,80 +7252,80 @@
         <f t="shared" si="6"/>
         <v>2.4390243902439025E-2</v>
       </c>
-      <c r="AM64" s="86"/>
-      <c r="AN64" s="86"/>
-      <c r="AO64" s="117" t="s">
+      <c r="AM64" s="85"/>
+      <c r="AN64" s="85"/>
+      <c r="AO64" s="116" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="65" spans="1:41" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="69">
+      <c r="A65" s="68">
         <v>3</v>
       </c>
-      <c r="B65" s="70" t="s">
+      <c r="B65" s="69" t="s">
         <v>131</v>
       </c>
-      <c r="C65" s="115" t="s">
+      <c r="C65" s="114" t="s">
         <v>132</v>
       </c>
-      <c r="D65" s="72"/>
-      <c r="E65" s="72">
+      <c r="D65" s="71"/>
+      <c r="E65" s="71">
         <v>6200</v>
       </c>
-      <c r="F65" s="72">
+      <c r="F65" s="71">
         <v>4220</v>
       </c>
-      <c r="G65" s="72"/>
-      <c r="H65" s="72">
+      <c r="G65" s="71"/>
+      <c r="H65" s="71">
         <v>3960</v>
       </c>
-      <c r="I65" s="72"/>
-      <c r="J65" s="72"/>
-      <c r="K65" s="72">
+      <c r="I65" s="71"/>
+      <c r="J65" s="71"/>
+      <c r="K65" s="71">
         <v>5251</v>
       </c>
       <c r="L65" s="52"/>
-      <c r="M65" s="72"/>
-      <c r="N65" s="91">
+      <c r="M65" s="71"/>
+      <c r="N65" s="90">
         <v>6000</v>
       </c>
-      <c r="O65" s="73"/>
-      <c r="P65" s="73">
+      <c r="O65" s="72"/>
+      <c r="P65" s="72">
         <v>100</v>
       </c>
-      <c r="Q65" s="73"/>
-      <c r="R65" s="73">
+      <c r="Q65" s="72"/>
+      <c r="R65" s="72">
         <v>1000</v>
       </c>
-      <c r="S65" s="74"/>
-      <c r="T65" s="73"/>
-      <c r="U65" s="75"/>
-      <c r="V65" s="75"/>
+      <c r="S65" s="73"/>
+      <c r="T65" s="72"/>
+      <c r="U65" s="74"/>
+      <c r="V65" s="74"/>
       <c r="W65" s="57">
         <f t="shared" si="8"/>
         <v>1100</v>
       </c>
-      <c r="X65" s="77">
+      <c r="X65" s="76">
         <v>100</v>
       </c>
-      <c r="Y65" s="77"/>
-      <c r="Z65" s="60">
+      <c r="Y65" s="189"/>
+      <c r="Z65" s="59">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AA65" s="116">
+      <c r="AA65" s="115">
         <f t="shared" si="17"/>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="AB65" s="79">
-        <v>0</v>
-      </c>
-      <c r="AC65" s="80">
+      <c r="AB65" s="78">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="79">
         <f>448+26</f>
         <v>474</v>
       </c>
-      <c r="AD65" s="116"/>
-      <c r="AE65" s="80">
+      <c r="AD65" s="115"/>
+      <c r="AE65" s="79">
         <f t="shared" si="7"/>
         <v>474</v>
       </c>
@@ -7294,13 +7333,13 @@
         <f t="shared" si="5"/>
         <v>1000</v>
       </c>
-      <c r="AG65" s="81"/>
-      <c r="AH65" s="81"/>
-      <c r="AI65" s="65">
+      <c r="AG65" s="80"/>
+      <c r="AH65" s="80"/>
+      <c r="AI65" s="64">
         <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="AJ65" s="82"/>
+      <c r="AJ65" s="81"/>
       <c r="AK65" s="42">
         <f t="shared" si="3"/>
         <v>1000</v>
@@ -7309,76 +7348,76 @@
         <f t="shared" si="6"/>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="AM65" s="81"/>
-      <c r="AN65" s="81"/>
-      <c r="AO65" s="117" t="s">
+      <c r="AM65" s="80"/>
+      <c r="AN65" s="80"/>
+      <c r="AO65" s="116" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="66" spans="1:41" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="69">
+      <c r="A66" s="68">
         <v>4</v>
       </c>
-      <c r="B66" s="70" t="s">
+      <c r="B66" s="69" t="s">
         <v>133</v>
       </c>
-      <c r="C66" s="115" t="s">
+      <c r="C66" s="114" t="s">
         <v>134</v>
       </c>
-      <c r="D66" s="72"/>
-      <c r="E66" s="72"/>
-      <c r="F66" s="72"/>
-      <c r="G66" s="72"/>
-      <c r="H66" s="72">
+      <c r="D66" s="71"/>
+      <c r="E66" s="71"/>
+      <c r="F66" s="71"/>
+      <c r="G66" s="71"/>
+      <c r="H66" s="71">
         <v>103</v>
       </c>
-      <c r="I66" s="72"/>
-      <c r="J66" s="72">
+      <c r="I66" s="71"/>
+      <c r="J66" s="71">
         <v>1500</v>
       </c>
-      <c r="K66" s="72"/>
+      <c r="K66" s="71"/>
       <c r="L66" s="52"/>
-      <c r="M66" s="72"/>
-      <c r="N66" s="91">
+      <c r="M66" s="71"/>
+      <c r="N66" s="90">
         <v>10000</v>
       </c>
-      <c r="O66" s="73"/>
-      <c r="P66" s="73">
+      <c r="O66" s="72"/>
+      <c r="P66" s="72">
         <v>100</v>
       </c>
-      <c r="Q66" s="73"/>
-      <c r="R66" s="73">
+      <c r="Q66" s="72"/>
+      <c r="R66" s="72">
         <v>600</v>
       </c>
-      <c r="S66" s="74"/>
-      <c r="T66" s="73"/>
-      <c r="U66" s="73">
+      <c r="S66" s="73"/>
+      <c r="T66" s="72"/>
+      <c r="U66" s="72">
         <f>100-100</f>
         <v>0</v>
       </c>
-      <c r="V66" s="73"/>
+      <c r="V66" s="72"/>
       <c r="W66" s="57">
         <f t="shared" si="8"/>
         <v>700</v>
       </c>
-      <c r="X66" s="77">
+      <c r="X66" s="76">
         <v>100</v>
       </c>
-      <c r="Y66" s="77"/>
-      <c r="Z66" s="60">
+      <c r="Y66" s="189"/>
+      <c r="Z66" s="59">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AA66" s="116">
+      <c r="AA66" s="115">
         <f t="shared" si="17"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AB66" s="79">
-        <v>0</v>
-      </c>
-      <c r="AC66" s="80"/>
-      <c r="AD66" s="116"/>
-      <c r="AE66" s="80">
+      <c r="AB66" s="78">
+        <v>0</v>
+      </c>
+      <c r="AC66" s="79"/>
+      <c r="AD66" s="115"/>
+      <c r="AE66" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -7386,13 +7425,13 @@
         <f t="shared" si="5"/>
         <v>600</v>
       </c>
-      <c r="AG66" s="81"/>
-      <c r="AH66" s="81"/>
-      <c r="AI66" s="65">
+      <c r="AG66" s="80"/>
+      <c r="AH66" s="80"/>
+      <c r="AI66" s="64">
         <f t="shared" si="2"/>
         <v>600</v>
       </c>
-      <c r="AJ66" s="82"/>
+      <c r="AJ66" s="81"/>
       <c r="AK66" s="42">
         <f t="shared" si="3"/>
         <v>600</v>
@@ -7401,73 +7440,73 @@
         <f t="shared" si="6"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AM66" s="86"/>
-      <c r="AN66" s="86"/>
-      <c r="AO66" s="156" t="s">
+      <c r="AM66" s="85"/>
+      <c r="AN66" s="85"/>
+      <c r="AO66" s="154" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="67" spans="1:41" ht="61.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="69">
+      <c r="A67" s="68">
         <v>5</v>
       </c>
-      <c r="B67" s="70" t="s">
+      <c r="B67" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="C67" s="115" t="s">
+      <c r="C67" s="114" t="s">
         <v>136</v>
       </c>
-      <c r="D67" s="119"/>
-      <c r="E67" s="119"/>
-      <c r="F67" s="119"/>
-      <c r="G67" s="119"/>
-      <c r="H67" s="119"/>
-      <c r="I67" s="119"/>
-      <c r="J67" s="119"/>
-      <c r="K67" s="119"/>
-      <c r="L67" s="119"/>
-      <c r="M67" s="119"/>
-      <c r="N67" s="91">
+      <c r="D67" s="118"/>
+      <c r="E67" s="118"/>
+      <c r="F67" s="118"/>
+      <c r="G67" s="118"/>
+      <c r="H67" s="118"/>
+      <c r="I67" s="118"/>
+      <c r="J67" s="118"/>
+      <c r="K67" s="118"/>
+      <c r="L67" s="118"/>
+      <c r="M67" s="118"/>
+      <c r="N67" s="90">
         <v>4600</v>
       </c>
-      <c r="O67" s="120"/>
-      <c r="P67" s="73">
+      <c r="O67" s="119"/>
+      <c r="P67" s="72">
         <v>100</v>
       </c>
-      <c r="Q67" s="119"/>
-      <c r="R67" s="73">
+      <c r="Q67" s="118"/>
+      <c r="R67" s="72">
         <v>250</v>
       </c>
-      <c r="S67" s="119"/>
-      <c r="T67" s="119"/>
-      <c r="U67" s="121">
+      <c r="S67" s="118"/>
+      <c r="T67" s="118"/>
+      <c r="U67" s="120">
         <v>4250</v>
       </c>
-      <c r="V67" s="119"/>
+      <c r="V67" s="118"/>
       <c r="W67" s="57">
         <f t="shared" si="8"/>
         <v>4600</v>
       </c>
-      <c r="X67" s="77">
+      <c r="X67" s="76">
         <v>100</v>
       </c>
-      <c r="Y67" s="122"/>
-      <c r="Z67" s="122">
+      <c r="Y67" s="190"/>
+      <c r="Z67" s="121">
         <f>SUM(X67:Y67)</f>
         <v>100</v>
       </c>
-      <c r="AA67" s="123">
+      <c r="AA67" s="122">
         <f>Z67/W67</f>
         <v>2.1739130434782608E-2</v>
       </c>
-      <c r="AB67" s="79">
-        <v>0</v>
-      </c>
-      <c r="AC67" s="80">
+      <c r="AB67" s="78">
+        <v>0</v>
+      </c>
+      <c r="AC67" s="79">
         <v>320</v>
       </c>
-      <c r="AD67" s="116"/>
-      <c r="AE67" s="80">
+      <c r="AD67" s="115"/>
+      <c r="AE67" s="79">
         <f t="shared" si="7"/>
         <v>320</v>
       </c>
@@ -7475,85 +7514,85 @@
         <f t="shared" si="5"/>
         <v>4500</v>
       </c>
-      <c r="AG67" s="119"/>
-      <c r="AH67" s="119"/>
-      <c r="AI67" s="119"/>
-      <c r="AJ67" s="119"/>
-      <c r="AK67" s="119">
+      <c r="AG67" s="118"/>
+      <c r="AH67" s="118"/>
+      <c r="AI67" s="118"/>
+      <c r="AJ67" s="118"/>
+      <c r="AK67" s="118">
         <f t="shared" si="3"/>
         <v>4500</v>
       </c>
-      <c r="AL67" s="119">
+      <c r="AL67" s="118">
         <f t="shared" si="6"/>
         <v>2.1739130434782608E-2</v>
       </c>
-      <c r="AM67" s="119"/>
-      <c r="AN67" s="119"/>
-      <c r="AO67" s="117" t="s">
+      <c r="AM67" s="118"/>
+      <c r="AN67" s="118"/>
+      <c r="AO67" s="116" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="68" spans="1:41" ht="135.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="69">
+      <c r="A68" s="68">
         <v>6</v>
       </c>
-      <c r="B68" s="70" t="s">
+      <c r="B68" s="69" t="s">
         <v>137</v>
       </c>
-      <c r="C68" s="124" t="s">
+      <c r="C68" s="123" t="s">
         <v>138</v>
       </c>
-      <c r="D68" s="119"/>
-      <c r="E68" s="119"/>
-      <c r="F68" s="119"/>
-      <c r="G68" s="119"/>
-      <c r="H68" s="119"/>
-      <c r="I68" s="119"/>
-      <c r="J68" s="119"/>
-      <c r="K68" s="119"/>
-      <c r="L68" s="119"/>
-      <c r="M68" s="119"/>
-      <c r="N68" s="91">
+      <c r="D68" s="118"/>
+      <c r="E68" s="118"/>
+      <c r="F68" s="118"/>
+      <c r="G68" s="118"/>
+      <c r="H68" s="118"/>
+      <c r="I68" s="118"/>
+      <c r="J68" s="118"/>
+      <c r="K68" s="118"/>
+      <c r="L68" s="118"/>
+      <c r="M68" s="118"/>
+      <c r="N68" s="90">
         <v>11400</v>
       </c>
-      <c r="O68" s="125"/>
-      <c r="P68" s="126">
+      <c r="O68" s="124"/>
+      <c r="P68" s="125">
         <v>100</v>
       </c>
-      <c r="Q68" s="127"/>
-      <c r="R68" s="73">
+      <c r="Q68" s="126"/>
+      <c r="R68" s="72">
         <v>600</v>
       </c>
-      <c r="S68" s="127"/>
-      <c r="T68" s="127"/>
-      <c r="U68" s="128">
+      <c r="S68" s="126"/>
+      <c r="T68" s="126"/>
+      <c r="U68" s="127">
         <v>10700</v>
       </c>
-      <c r="V68" s="127"/>
+      <c r="V68" s="126"/>
       <c r="W68" s="57">
         <f t="shared" si="8"/>
         <v>11400</v>
       </c>
-      <c r="X68" s="77">
+      <c r="X68" s="76">
         <v>100</v>
       </c>
-      <c r="Y68" s="129"/>
-      <c r="Z68" s="129">
+      <c r="Y68" s="191"/>
+      <c r="Z68" s="128">
         <f>SUM(X68:Y68)</f>
         <v>100</v>
       </c>
-      <c r="AA68" s="130">
+      <c r="AA68" s="129">
         <f>Z68/W68</f>
         <v>8.771929824561403E-3</v>
       </c>
-      <c r="AB68" s="131">
-        <v>0</v>
-      </c>
-      <c r="AC68" s="80">
+      <c r="AB68" s="130">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="79">
         <v>4500</v>
       </c>
-      <c r="AD68" s="132"/>
-      <c r="AE68" s="80">
+      <c r="AD68" s="131"/>
+      <c r="AE68" s="79">
         <f t="shared" si="7"/>
         <v>4500</v>
       </c>
@@ -7561,79 +7600,79 @@
         <f t="shared" si="5"/>
         <v>11300</v>
       </c>
-      <c r="AG68" s="119"/>
-      <c r="AH68" s="119"/>
-      <c r="AI68" s="119"/>
-      <c r="AJ68" s="119"/>
-      <c r="AK68" s="119"/>
-      <c r="AL68" s="119"/>
-      <c r="AM68" s="119"/>
-      <c r="AN68" s="119"/>
-      <c r="AO68" s="157" t="s">
+      <c r="AG68" s="118"/>
+      <c r="AH68" s="118"/>
+      <c r="AI68" s="118"/>
+      <c r="AJ68" s="118"/>
+      <c r="AK68" s="118"/>
+      <c r="AL68" s="118"/>
+      <c r="AM68" s="118"/>
+      <c r="AN68" s="118"/>
+      <c r="AO68" s="155" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="69" spans="1:41" s="110" customFormat="1" ht="76.349999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="69">
+    <row r="69" spans="1:41" s="109" customFormat="1" ht="76.349999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="68">
         <v>7</v>
       </c>
-      <c r="B69" s="133" t="s">
+      <c r="B69" s="132" t="s">
         <v>139</v>
       </c>
-      <c r="C69" s="115" t="s">
+      <c r="C69" s="114" t="s">
         <v>140</v>
       </c>
-      <c r="D69" s="134"/>
-      <c r="E69" s="134"/>
-      <c r="F69" s="134"/>
-      <c r="G69" s="134"/>
-      <c r="H69" s="134"/>
-      <c r="I69" s="134"/>
-      <c r="J69" s="134"/>
-      <c r="K69" s="134"/>
-      <c r="L69" s="134"/>
-      <c r="M69" s="134"/>
-      <c r="N69" s="91">
+      <c r="D69" s="133"/>
+      <c r="E69" s="133"/>
+      <c r="F69" s="133"/>
+      <c r="G69" s="133"/>
+      <c r="H69" s="133"/>
+      <c r="I69" s="133"/>
+      <c r="J69" s="133"/>
+      <c r="K69" s="133"/>
+      <c r="L69" s="133"/>
+      <c r="M69" s="133"/>
+      <c r="N69" s="90">
         <v>10967</v>
       </c>
-      <c r="O69" s="135"/>
-      <c r="P69" s="73">
+      <c r="O69" s="134"/>
+      <c r="P69" s="72">
         <v>100</v>
       </c>
-      <c r="Q69" s="136"/>
-      <c r="R69" s="73">
+      <c r="Q69" s="135"/>
+      <c r="R69" s="72">
         <v>600</v>
       </c>
-      <c r="S69" s="136"/>
-      <c r="T69" s="136"/>
-      <c r="U69" s="137">
+      <c r="S69" s="135"/>
+      <c r="T69" s="135"/>
+      <c r="U69" s="136">
         <v>10267</v>
       </c>
-      <c r="V69" s="136"/>
+      <c r="V69" s="135"/>
       <c r="W69" s="57">
         <f t="shared" si="8"/>
         <v>10967</v>
       </c>
-      <c r="X69" s="77">
+      <c r="X69" s="76">
         <v>100</v>
       </c>
-      <c r="Y69" s="122"/>
-      <c r="Z69" s="122">
+      <c r="Y69" s="190"/>
+      <c r="Z69" s="121">
         <f>SUM(X69:Y69)</f>
         <v>100</v>
       </c>
-      <c r="AA69" s="138">
+      <c r="AA69" s="137">
         <f>Z69/W69</f>
         <v>9.1182638825567618E-3</v>
       </c>
-      <c r="AB69" s="79">
-        <v>0</v>
-      </c>
-      <c r="AC69" s="80">
+      <c r="AB69" s="78">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="79">
         <v>4300</v>
       </c>
-      <c r="AD69" s="139"/>
-      <c r="AE69" s="80">
+      <c r="AD69" s="138"/>
+      <c r="AE69" s="79">
         <f t="shared" si="7"/>
         <v>4300</v>
       </c>
@@ -7641,79 +7680,79 @@
         <f t="shared" si="5"/>
         <v>10867</v>
       </c>
-      <c r="AG69" s="134"/>
-      <c r="AH69" s="134"/>
-      <c r="AI69" s="134"/>
-      <c r="AJ69" s="134"/>
-      <c r="AK69" s="134"/>
-      <c r="AL69" s="134"/>
-      <c r="AM69" s="134"/>
-      <c r="AN69" s="134"/>
-      <c r="AO69" s="157" t="s">
+      <c r="AG69" s="133"/>
+      <c r="AH69" s="133"/>
+      <c r="AI69" s="133"/>
+      <c r="AJ69" s="133"/>
+      <c r="AK69" s="133"/>
+      <c r="AL69" s="133"/>
+      <c r="AM69" s="133"/>
+      <c r="AN69" s="133"/>
+      <c r="AO69" s="155" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="70" spans="1:41" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="69">
+      <c r="A70" s="68">
         <v>8</v>
       </c>
-      <c r="B70" s="133" t="s">
+      <c r="B70" s="132" t="s">
         <v>141</v>
       </c>
-      <c r="C70" s="115" t="s">
+      <c r="C70" s="114" t="s">
         <v>142</v>
       </c>
-      <c r="D70" s="119"/>
-      <c r="E70" s="119"/>
-      <c r="F70" s="119"/>
-      <c r="G70" s="119"/>
-      <c r="H70" s="119"/>
-      <c r="I70" s="119"/>
-      <c r="J70" s="119"/>
-      <c r="K70" s="119"/>
-      <c r="L70" s="119"/>
-      <c r="M70" s="119"/>
-      <c r="N70" s="91">
+      <c r="D70" s="118"/>
+      <c r="E70" s="118"/>
+      <c r="F70" s="118"/>
+      <c r="G70" s="118"/>
+      <c r="H70" s="118"/>
+      <c r="I70" s="118"/>
+      <c r="J70" s="118"/>
+      <c r="K70" s="118"/>
+      <c r="L70" s="118"/>
+      <c r="M70" s="118"/>
+      <c r="N70" s="90">
         <v>7073</v>
       </c>
-      <c r="O70" s="120"/>
-      <c r="P70" s="73">
+      <c r="O70" s="119"/>
+      <c r="P70" s="72">
         <v>100</v>
       </c>
-      <c r="Q70" s="127"/>
-      <c r="R70" s="73">
+      <c r="Q70" s="126"/>
+      <c r="R70" s="72">
         <v>450</v>
       </c>
-      <c r="S70" s="127"/>
-      <c r="T70" s="127"/>
-      <c r="U70" s="137">
+      <c r="S70" s="126"/>
+      <c r="T70" s="126"/>
+      <c r="U70" s="136">
         <v>6523</v>
       </c>
-      <c r="V70" s="127"/>
+      <c r="V70" s="126"/>
       <c r="W70" s="57">
         <f t="shared" si="8"/>
         <v>7073</v>
       </c>
-      <c r="X70" s="77">
+      <c r="X70" s="76">
         <v>100</v>
       </c>
-      <c r="Y70" s="140"/>
-      <c r="Z70" s="122">
+      <c r="Y70" s="192"/>
+      <c r="Z70" s="121">
         <f>SUM(X70:Y70)</f>
         <v>100</v>
       </c>
-      <c r="AA70" s="138">
+      <c r="AA70" s="137">
         <f>Z70/W70</f>
         <v>1.4138272303124559E-2</v>
       </c>
-      <c r="AB70" s="79">
-        <v>0</v>
-      </c>
-      <c r="AC70" s="80">
+      <c r="AB70" s="78">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="79">
         <v>3950</v>
       </c>
-      <c r="AD70" s="139"/>
-      <c r="AE70" s="80">
+      <c r="AD70" s="138"/>
+      <c r="AE70" s="79">
         <f t="shared" si="7"/>
         <v>3950</v>
       </c>
@@ -7721,63 +7760,63 @@
         <f t="shared" si="5"/>
         <v>6973</v>
       </c>
-      <c r="AG70" s="119"/>
-      <c r="AH70" s="119"/>
-      <c r="AI70" s="119"/>
-      <c r="AJ70" s="119"/>
-      <c r="AK70" s="119"/>
-      <c r="AL70" s="119"/>
-      <c r="AM70" s="119"/>
-      <c r="AN70" s="119"/>
-      <c r="AO70" s="117" t="s">
+      <c r="AG70" s="118"/>
+      <c r="AH70" s="118"/>
+      <c r="AI70" s="118"/>
+      <c r="AJ70" s="118"/>
+      <c r="AK70" s="118"/>
+      <c r="AL70" s="118"/>
+      <c r="AM70" s="118"/>
+      <c r="AN70" s="118"/>
+      <c r="AO70" s="116" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="71" spans="1:41" s="151" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="69">
+    <row r="71" spans="1:41" s="149" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="68">
         <v>9</v>
       </c>
-      <c r="B71" s="141" t="s">
+      <c r="B71" s="140" t="s">
         <v>143</v>
       </c>
-      <c r="C71" s="142" t="s">
+      <c r="C71" s="141" t="s">
         <v>144</v>
       </c>
-      <c r="D71" s="143"/>
-      <c r="E71" s="143"/>
-      <c r="F71" s="143"/>
-      <c r="G71" s="143"/>
-      <c r="H71" s="143"/>
-      <c r="I71" s="143"/>
-      <c r="J71" s="143"/>
-      <c r="K71" s="143"/>
-      <c r="L71" s="143"/>
-      <c r="M71" s="143"/>
-      <c r="N71" s="91">
+      <c r="D71" s="142"/>
+      <c r="E71" s="142"/>
+      <c r="F71" s="142"/>
+      <c r="G71" s="142"/>
+      <c r="H71" s="142"/>
+      <c r="I71" s="142"/>
+      <c r="J71" s="142"/>
+      <c r="K71" s="142"/>
+      <c r="L71" s="142"/>
+      <c r="M71" s="142"/>
+      <c r="N71" s="90">
         <v>600</v>
       </c>
-      <c r="O71" s="144"/>
-      <c r="P71" s="73"/>
-      <c r="Q71" s="145"/>
-      <c r="R71" s="73">
+      <c r="O71" s="143"/>
+      <c r="P71" s="72"/>
+      <c r="Q71" s="144"/>
+      <c r="R71" s="72">
         <v>600</v>
       </c>
-      <c r="S71" s="145"/>
-      <c r="T71" s="145"/>
-      <c r="U71" s="146"/>
-      <c r="V71" s="145"/>
+      <c r="S71" s="144"/>
+      <c r="T71" s="144"/>
+      <c r="U71" s="145"/>
+      <c r="V71" s="144"/>
       <c r="W71" s="57">
         <f t="shared" si="8"/>
         <v>600</v>
       </c>
-      <c r="X71" s="147"/>
-      <c r="Y71" s="148"/>
-      <c r="Z71" s="149"/>
-      <c r="AA71" s="150"/>
-      <c r="AB71" s="79"/>
-      <c r="AC71" s="80"/>
-      <c r="AD71" s="139"/>
-      <c r="AE71" s="80">
+      <c r="X71" s="146"/>
+      <c r="Y71" s="192"/>
+      <c r="Z71" s="147"/>
+      <c r="AA71" s="148"/>
+      <c r="AB71" s="78"/>
+      <c r="AC71" s="79"/>
+      <c r="AD71" s="138"/>
+      <c r="AE71" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -7785,63 +7824,63 @@
         <f t="shared" si="5"/>
         <v>600</v>
       </c>
-      <c r="AG71" s="143"/>
-      <c r="AH71" s="143"/>
-      <c r="AI71" s="143"/>
-      <c r="AJ71" s="143"/>
-      <c r="AK71" s="143"/>
-      <c r="AL71" s="143"/>
-      <c r="AM71" s="143"/>
-      <c r="AN71" s="143"/>
-      <c r="AO71" s="158" t="s">
+      <c r="AG71" s="142"/>
+      <c r="AH71" s="142"/>
+      <c r="AI71" s="142"/>
+      <c r="AJ71" s="142"/>
+      <c r="AK71" s="142"/>
+      <c r="AL71" s="142"/>
+      <c r="AM71" s="142"/>
+      <c r="AN71" s="142"/>
+      <c r="AO71" s="156" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="72" spans="1:41" s="151" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="69">
+    <row r="72" spans="1:41" s="149" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="68">
         <v>10</v>
       </c>
-      <c r="B72" s="141" t="s">
+      <c r="B72" s="140" t="s">
         <v>145</v>
       </c>
-      <c r="C72" s="142" t="s">
+      <c r="C72" s="141" t="s">
         <v>146</v>
       </c>
-      <c r="D72" s="143"/>
-      <c r="E72" s="143"/>
-      <c r="F72" s="143"/>
-      <c r="G72" s="143"/>
-      <c r="H72" s="143"/>
-      <c r="I72" s="143"/>
-      <c r="J72" s="143"/>
-      <c r="K72" s="143"/>
-      <c r="L72" s="143"/>
-      <c r="M72" s="143"/>
-      <c r="N72" s="91">
+      <c r="D72" s="142"/>
+      <c r="E72" s="142"/>
+      <c r="F72" s="142"/>
+      <c r="G72" s="142"/>
+      <c r="H72" s="142"/>
+      <c r="I72" s="142"/>
+      <c r="J72" s="142"/>
+      <c r="K72" s="142"/>
+      <c r="L72" s="142"/>
+      <c r="M72" s="142"/>
+      <c r="N72" s="90">
         <v>800</v>
       </c>
-      <c r="O72" s="144"/>
-      <c r="P72" s="73"/>
-      <c r="Q72" s="145"/>
-      <c r="R72" s="73">
+      <c r="O72" s="143"/>
+      <c r="P72" s="72"/>
+      <c r="Q72" s="144"/>
+      <c r="R72" s="72">
         <v>800</v>
       </c>
-      <c r="S72" s="145"/>
-      <c r="T72" s="145"/>
-      <c r="U72" s="146"/>
-      <c r="V72" s="145"/>
+      <c r="S72" s="144"/>
+      <c r="T72" s="144"/>
+      <c r="U72" s="145"/>
+      <c r="V72" s="144"/>
       <c r="W72" s="57">
         <f t="shared" si="8"/>
         <v>800</v>
       </c>
-      <c r="X72" s="147"/>
-      <c r="Y72" s="148"/>
-      <c r="Z72" s="149"/>
-      <c r="AA72" s="150"/>
-      <c r="AB72" s="79"/>
-      <c r="AC72" s="80"/>
-      <c r="AD72" s="139"/>
-      <c r="AE72" s="80">
+      <c r="X72" s="146"/>
+      <c r="Y72" s="192"/>
+      <c r="Z72" s="147"/>
+      <c r="AA72" s="148"/>
+      <c r="AB72" s="78"/>
+      <c r="AC72" s="79"/>
+      <c r="AD72" s="138"/>
+      <c r="AE72" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -7849,63 +7888,63 @@
         <f t="shared" si="5"/>
         <v>800</v>
       </c>
-      <c r="AG72" s="143"/>
-      <c r="AH72" s="143"/>
-      <c r="AI72" s="143"/>
-      <c r="AJ72" s="143"/>
-      <c r="AK72" s="143"/>
-      <c r="AL72" s="143"/>
-      <c r="AM72" s="143"/>
-      <c r="AN72" s="143"/>
-      <c r="AO72" s="158" t="s">
+      <c r="AG72" s="142"/>
+      <c r="AH72" s="142"/>
+      <c r="AI72" s="142"/>
+      <c r="AJ72" s="142"/>
+      <c r="AK72" s="142"/>
+      <c r="AL72" s="142"/>
+      <c r="AM72" s="142"/>
+      <c r="AN72" s="142"/>
+      <c r="AO72" s="156" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="73" spans="1:41" s="151" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="69">
+    <row r="73" spans="1:41" s="149" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="68">
         <v>11</v>
       </c>
-      <c r="B73" s="141" t="s">
+      <c r="B73" s="140" t="s">
         <v>147</v>
       </c>
-      <c r="C73" s="142" t="s">
+      <c r="C73" s="141" t="s">
         <v>144</v>
       </c>
-      <c r="D73" s="143"/>
-      <c r="E73" s="143"/>
-      <c r="F73" s="143"/>
-      <c r="G73" s="143"/>
-      <c r="H73" s="143"/>
-      <c r="I73" s="143"/>
-      <c r="J73" s="143"/>
-      <c r="K73" s="143"/>
-      <c r="L73" s="143"/>
-      <c r="M73" s="143"/>
-      <c r="N73" s="91">
+      <c r="D73" s="142"/>
+      <c r="E73" s="142"/>
+      <c r="F73" s="142"/>
+      <c r="G73" s="142"/>
+      <c r="H73" s="142"/>
+      <c r="I73" s="142"/>
+      <c r="J73" s="142"/>
+      <c r="K73" s="142"/>
+      <c r="L73" s="142"/>
+      <c r="M73" s="142"/>
+      <c r="N73" s="90">
         <v>1000</v>
       </c>
-      <c r="O73" s="144"/>
-      <c r="P73" s="73"/>
-      <c r="Q73" s="145"/>
-      <c r="R73" s="73">
+      <c r="O73" s="143"/>
+      <c r="P73" s="72"/>
+      <c r="Q73" s="144"/>
+      <c r="R73" s="72">
         <v>1000</v>
       </c>
-      <c r="S73" s="145"/>
-      <c r="T73" s="145"/>
-      <c r="U73" s="146"/>
-      <c r="V73" s="145"/>
+      <c r="S73" s="144"/>
+      <c r="T73" s="144"/>
+      <c r="U73" s="145"/>
+      <c r="V73" s="144"/>
       <c r="W73" s="57">
         <f t="shared" si="8"/>
         <v>1000</v>
       </c>
-      <c r="X73" s="147"/>
-      <c r="Y73" s="148"/>
-      <c r="Z73" s="149"/>
-      <c r="AA73" s="150"/>
-      <c r="AB73" s="79"/>
-      <c r="AC73" s="80"/>
-      <c r="AD73" s="139"/>
-      <c r="AE73" s="80">
+      <c r="X73" s="146"/>
+      <c r="Y73" s="192"/>
+      <c r="Z73" s="147"/>
+      <c r="AA73" s="148"/>
+      <c r="AB73" s="78"/>
+      <c r="AC73" s="79"/>
+      <c r="AD73" s="138"/>
+      <c r="AE73" s="79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -7913,63 +7952,63 @@
         <f t="shared" si="5"/>
         <v>1000</v>
       </c>
-      <c r="AG73" s="143"/>
-      <c r="AH73" s="143"/>
-      <c r="AI73" s="143"/>
-      <c r="AJ73" s="143"/>
-      <c r="AK73" s="143"/>
-      <c r="AL73" s="143"/>
-      <c r="AM73" s="143"/>
-      <c r="AN73" s="143"/>
-      <c r="AO73" s="158" t="s">
+      <c r="AG73" s="142"/>
+      <c r="AH73" s="142"/>
+      <c r="AI73" s="142"/>
+      <c r="AJ73" s="142"/>
+      <c r="AK73" s="142"/>
+      <c r="AL73" s="142"/>
+      <c r="AM73" s="142"/>
+      <c r="AN73" s="142"/>
+      <c r="AO73" s="156" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="119"/>
-      <c r="B74" s="152"/>
-      <c r="C74" s="120"/>
-      <c r="D74" s="119"/>
-      <c r="E74" s="119"/>
-      <c r="F74" s="119"/>
-      <c r="G74" s="119"/>
-      <c r="H74" s="119"/>
-      <c r="I74" s="119"/>
-      <c r="J74" s="119"/>
-      <c r="K74" s="119"/>
-      <c r="L74" s="119"/>
-      <c r="M74" s="119"/>
-      <c r="N74" s="120"/>
-      <c r="O74" s="119"/>
-      <c r="P74" s="119"/>
-      <c r="Q74" s="119"/>
-      <c r="R74" s="119"/>
-      <c r="S74" s="119"/>
-      <c r="T74" s="119"/>
-      <c r="U74" s="119"/>
-      <c r="V74" s="119"/>
+      <c r="A74" s="118"/>
+      <c r="B74" s="150"/>
+      <c r="C74" s="119"/>
+      <c r="D74" s="118"/>
+      <c r="E74" s="118"/>
+      <c r="F74" s="118"/>
+      <c r="G74" s="118"/>
+      <c r="H74" s="118"/>
+      <c r="I74" s="118"/>
+      <c r="J74" s="118"/>
+      <c r="K74" s="118"/>
+      <c r="L74" s="118"/>
+      <c r="M74" s="118"/>
+      <c r="N74" s="119"/>
+      <c r="O74" s="118"/>
+      <c r="P74" s="118"/>
+      <c r="Q74" s="118"/>
+      <c r="R74" s="118"/>
+      <c r="S74" s="118"/>
+      <c r="T74" s="118"/>
+      <c r="U74" s="118"/>
+      <c r="V74" s="118"/>
       <c r="W74" s="57">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X74" s="140"/>
-      <c r="Y74" s="140"/>
-      <c r="Z74" s="140"/>
-      <c r="AA74" s="119"/>
-      <c r="AB74" s="119"/>
-      <c r="AC74" s="153"/>
-      <c r="AD74" s="143"/>
-      <c r="AE74" s="143"/>
-      <c r="AF74" s="119"/>
-      <c r="AG74" s="119"/>
-      <c r="AH74" s="119"/>
-      <c r="AI74" s="119"/>
-      <c r="AJ74" s="119"/>
-      <c r="AK74" s="119"/>
-      <c r="AL74" s="119"/>
-      <c r="AM74" s="119"/>
-      <c r="AN74" s="119"/>
-      <c r="AO74" s="144"/>
+      <c r="X74" s="139"/>
+      <c r="Y74" s="192"/>
+      <c r="Z74" s="139"/>
+      <c r="AA74" s="118"/>
+      <c r="AB74" s="118"/>
+      <c r="AC74" s="151"/>
+      <c r="AD74" s="142"/>
+      <c r="AE74" s="142"/>
+      <c r="AF74" s="118"/>
+      <c r="AG74" s="118"/>
+      <c r="AH74" s="118"/>
+      <c r="AI74" s="118"/>
+      <c r="AJ74" s="118"/>
+      <c r="AK74" s="118"/>
+      <c r="AL74" s="118"/>
+      <c r="AM74" s="118"/>
+      <c r="AN74" s="118"/>
+      <c r="AO74" s="143"/>
     </row>
     <row r="75" spans="1:41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="76" spans="1:41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8881,10 +8920,11 @@
     <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="38">
+    <mergeCell ref="AO7:AO9"/>
     <mergeCell ref="AM7:AM9"/>
     <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AO7:AO9"/>
+    <mergeCell ref="AS7:AS9"/>
     <mergeCell ref="AG7:AG9"/>
     <mergeCell ref="AH7:AH9"/>
     <mergeCell ref="AI7:AI9"/>
@@ -8920,6 +8960,7 @@
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:J9"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/report/bao-cao.xlsx
+++ b/report/bao-cao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HXuan\BaocaoGiaingan\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57579E4D-776A-462F-BCF0-6623A7763D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2AC359-70EC-4C7C-834D-4C08B773BFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{BF3132C5-3821-4F06-A909-D3A92B5D6441}"/>
   </bookViews>
@@ -48,9 +48,6 @@
     <t>BÁO CÁO TÌNH HÌNH THỰC HIỆN CÔNG TÁC GIẢI NGÂN - VỐN ĐẦU TƯ CÔNG NĂM 2026</t>
   </si>
   <si>
-    <t>(Tính đến ngày 04/09/2026)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -511,6 +508,9 @@
   </si>
   <si>
     <t>Cán Bộ Kỹ Thuật</t>
+  </si>
+  <si>
+    <t>(Tính đến ngày 10/09/2026)</t>
   </si>
 </sst>
 </file>
@@ -1407,14 +1407,84 @@
     <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1434,76 +1504,6 @@
     <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1859,7 +1859,7 @@
     <col min="22" max="22" width="8.5703125" customWidth="1"/>
     <col min="23" max="23" width="14.140625" customWidth="1"/>
     <col min="24" max="24" width="10" style="153" customWidth="1"/>
-    <col min="25" max="25" width="11.140625" style="193" customWidth="1"/>
+    <col min="25" max="25" width="11.140625" style="164" customWidth="1"/>
     <col min="26" max="26" width="11.140625" style="153" customWidth="1"/>
     <col min="27" max="27" width="11.42578125" customWidth="1"/>
     <col min="28" max="28" width="10.5703125" customWidth="1"/>
@@ -1879,36 +1879,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="159" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
-      <c r="K1" s="160"/>
-      <c r="L1" s="160"/>
-      <c r="M1" s="160"/>
-      <c r="N1" s="160"/>
-      <c r="O1" s="160"/>
-      <c r="P1" s="160"/>
-      <c r="Q1" s="160"/>
-      <c r="R1" s="160"/>
-      <c r="S1" s="160"/>
-      <c r="T1" s="160"/>
-      <c r="U1" s="160"/>
-      <c r="V1" s="160"/>
-      <c r="W1" s="160"/>
-      <c r="X1" s="160"/>
-      <c r="Y1" s="194"/>
-      <c r="Z1" s="160"/>
-      <c r="AA1" s="160"/>
-      <c r="AB1" s="160"/>
+      <c r="A1" s="186" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
+      <c r="K1" s="187"/>
+      <c r="L1" s="187"/>
+      <c r="M1" s="187"/>
+      <c r="N1" s="187"/>
+      <c r="O1" s="187"/>
+      <c r="P1" s="187"/>
+      <c r="Q1" s="187"/>
+      <c r="R1" s="187"/>
+      <c r="S1" s="187"/>
+      <c r="T1" s="187"/>
+      <c r="U1" s="187"/>
+      <c r="V1" s="187"/>
+      <c r="W1" s="187"/>
+      <c r="X1" s="187"/>
+      <c r="Y1" s="188"/>
+      <c r="Z1" s="187"/>
+      <c r="AA1" s="187"/>
+      <c r="AB1" s="187"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
@@ -1928,36 +1928,36 @@
       </c>
     </row>
     <row r="2" spans="1:45" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="161" t="s">
+      <c r="A2" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="160"/>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
-      <c r="K2" s="160"/>
-      <c r="L2" s="160"/>
-      <c r="M2" s="160"/>
-      <c r="N2" s="160"/>
-      <c r="O2" s="160"/>
-      <c r="P2" s="160"/>
-      <c r="Q2" s="160"/>
-      <c r="R2" s="160"/>
-      <c r="S2" s="160"/>
-      <c r="T2" s="160"/>
-      <c r="U2" s="160"/>
-      <c r="V2" s="160"/>
-      <c r="W2" s="160"/>
-      <c r="X2" s="160"/>
-      <c r="Y2" s="194"/>
-      <c r="Z2" s="160"/>
-      <c r="AA2" s="160"/>
-      <c r="AB2" s="160"/>
+      <c r="B2" s="187"/>
+      <c r="C2" s="187"/>
+      <c r="D2" s="187"/>
+      <c r="E2" s="187"/>
+      <c r="F2" s="187"/>
+      <c r="G2" s="187"/>
+      <c r="H2" s="187"/>
+      <c r="I2" s="187"/>
+      <c r="J2" s="187"/>
+      <c r="K2" s="187"/>
+      <c r="L2" s="187"/>
+      <c r="M2" s="187"/>
+      <c r="N2" s="187"/>
+      <c r="O2" s="187"/>
+      <c r="P2" s="187"/>
+      <c r="Q2" s="187"/>
+      <c r="R2" s="187"/>
+      <c r="S2" s="187"/>
+      <c r="T2" s="187"/>
+      <c r="U2" s="187"/>
+      <c r="V2" s="187"/>
+      <c r="W2" s="187"/>
+      <c r="X2" s="187"/>
+      <c r="Y2" s="188"/>
+      <c r="Z2" s="187"/>
+      <c r="AA2" s="187"/>
+      <c r="AB2" s="187"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
       <c r="AE2" s="1"/>
@@ -1997,7 +1997,7 @@
       <c r="V3" s="12"/>
       <c r="W3" s="14"/>
       <c r="X3" s="15"/>
-      <c r="Y3" s="195"/>
+      <c r="Y3" s="165"/>
       <c r="Z3" s="15"/>
       <c r="AA3" s="16"/>
       <c r="AB3" s="16"/>
@@ -2016,94 +2016,94 @@
       <c r="AO3" s="5"/>
     </row>
     <row r="4" spans="1:45" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="162" t="s">
+      <c r="A4" s="190" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="160"/>
-      <c r="C4" s="160"/>
-      <c r="D4" s="160"/>
-      <c r="E4" s="160"/>
-      <c r="F4" s="160"/>
-      <c r="G4" s="160"/>
-      <c r="H4" s="160"/>
-      <c r="I4" s="160"/>
-      <c r="J4" s="160"/>
-      <c r="K4" s="160"/>
-      <c r="L4" s="160"/>
-      <c r="M4" s="160"/>
-      <c r="N4" s="160"/>
-      <c r="O4" s="160"/>
-      <c r="P4" s="160"/>
-      <c r="Q4" s="160"/>
-      <c r="R4" s="160"/>
-      <c r="S4" s="160"/>
-      <c r="T4" s="160"/>
-      <c r="U4" s="160"/>
-      <c r="V4" s="160"/>
-      <c r="W4" s="160"/>
-      <c r="X4" s="160"/>
-      <c r="Y4" s="194"/>
-      <c r="Z4" s="160"/>
-      <c r="AA4" s="160"/>
-      <c r="AB4" s="160"/>
-      <c r="AC4" s="160"/>
-      <c r="AD4" s="160"/>
-      <c r="AE4" s="160"/>
-      <c r="AF4" s="160"/>
-      <c r="AG4" s="160"/>
-      <c r="AH4" s="160"/>
-      <c r="AI4" s="160"/>
-      <c r="AJ4" s="160"/>
-      <c r="AK4" s="160"/>
-      <c r="AL4" s="160"/>
-      <c r="AM4" s="160"/>
-      <c r="AN4" s="160"/>
-      <c r="AO4" s="160"/>
+      <c r="B4" s="187"/>
+      <c r="C4" s="187"/>
+      <c r="D4" s="187"/>
+      <c r="E4" s="187"/>
+      <c r="F4" s="187"/>
+      <c r="G4" s="187"/>
+      <c r="H4" s="187"/>
+      <c r="I4" s="187"/>
+      <c r="J4" s="187"/>
+      <c r="K4" s="187"/>
+      <c r="L4" s="187"/>
+      <c r="M4" s="187"/>
+      <c r="N4" s="187"/>
+      <c r="O4" s="187"/>
+      <c r="P4" s="187"/>
+      <c r="Q4" s="187"/>
+      <c r="R4" s="187"/>
+      <c r="S4" s="187"/>
+      <c r="T4" s="187"/>
+      <c r="U4" s="187"/>
+      <c r="V4" s="187"/>
+      <c r="W4" s="187"/>
+      <c r="X4" s="187"/>
+      <c r="Y4" s="188"/>
+      <c r="Z4" s="187"/>
+      <c r="AA4" s="187"/>
+      <c r="AB4" s="187"/>
+      <c r="AC4" s="187"/>
+      <c r="AD4" s="187"/>
+      <c r="AE4" s="187"/>
+      <c r="AF4" s="187"/>
+      <c r="AG4" s="187"/>
+      <c r="AH4" s="187"/>
+      <c r="AI4" s="187"/>
+      <c r="AJ4" s="187"/>
+      <c r="AK4" s="187"/>
+      <c r="AL4" s="187"/>
+      <c r="AM4" s="187"/>
+      <c r="AN4" s="187"/>
+      <c r="AO4" s="187"/>
     </row>
     <row r="5" spans="1:45" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="163" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="160"/>
-      <c r="C5" s="160"/>
-      <c r="D5" s="160"/>
-      <c r="E5" s="160"/>
-      <c r="F5" s="160"/>
-      <c r="G5" s="160"/>
-      <c r="H5" s="160"/>
-      <c r="I5" s="160"/>
-      <c r="J5" s="160"/>
-      <c r="K5" s="160"/>
-      <c r="L5" s="160"/>
-      <c r="M5" s="160"/>
-      <c r="N5" s="160"/>
-      <c r="O5" s="160"/>
-      <c r="P5" s="160"/>
-      <c r="Q5" s="160"/>
-      <c r="R5" s="160"/>
-      <c r="S5" s="160"/>
-      <c r="T5" s="160"/>
-      <c r="U5" s="160"/>
-      <c r="V5" s="160"/>
-      <c r="W5" s="160"/>
-      <c r="X5" s="160"/>
-      <c r="Y5" s="194"/>
-      <c r="Z5" s="160"/>
-      <c r="AA5" s="160"/>
-      <c r="AB5" s="160"/>
-      <c r="AC5" s="160"/>
-      <c r="AD5" s="160"/>
-      <c r="AE5" s="160"/>
-      <c r="AF5" s="160"/>
-      <c r="AG5" s="160"/>
-      <c r="AH5" s="160"/>
-      <c r="AI5" s="160"/>
-      <c r="AJ5" s="160"/>
-      <c r="AK5" s="160"/>
-      <c r="AL5" s="160"/>
-      <c r="AM5" s="160"/>
-      <c r="AN5" s="160"/>
-      <c r="AO5" s="160"/>
+      <c r="A5" s="191" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5" s="187"/>
+      <c r="C5" s="187"/>
+      <c r="D5" s="187"/>
+      <c r="E5" s="187"/>
+      <c r="F5" s="187"/>
+      <c r="G5" s="187"/>
+      <c r="H5" s="187"/>
+      <c r="I5" s="187"/>
+      <c r="J5" s="187"/>
+      <c r="K5" s="187"/>
+      <c r="L5" s="187"/>
+      <c r="M5" s="187"/>
+      <c r="N5" s="187"/>
+      <c r="O5" s="187"/>
+      <c r="P5" s="187"/>
+      <c r="Q5" s="187"/>
+      <c r="R5" s="187"/>
+      <c r="S5" s="187"/>
+      <c r="T5" s="187"/>
+      <c r="U5" s="187"/>
+      <c r="V5" s="187"/>
+      <c r="W5" s="187"/>
+      <c r="X5" s="187"/>
+      <c r="Y5" s="188"/>
+      <c r="Z5" s="187"/>
+      <c r="AA5" s="187"/>
+      <c r="AB5" s="187"/>
+      <c r="AC5" s="187"/>
+      <c r="AD5" s="187"/>
+      <c r="AE5" s="187"/>
+      <c r="AF5" s="187"/>
+      <c r="AG5" s="187"/>
+      <c r="AH5" s="187"/>
+      <c r="AI5" s="187"/>
+      <c r="AJ5" s="187"/>
+      <c r="AK5" s="187"/>
+      <c r="AL5" s="187"/>
+      <c r="AM5" s="187"/>
+      <c r="AN5" s="187"/>
+      <c r="AO5" s="187"/>
     </row>
     <row r="6" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16"/>
@@ -2130,230 +2130,230 @@
       <c r="V6" s="21"/>
       <c r="W6" s="23"/>
       <c r="X6" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y6" s="195"/>
+        <v>4</v>
+      </c>
+      <c r="Y6" s="165"/>
       <c r="Z6" s="24"/>
       <c r="AA6" s="25"/>
       <c r="AB6" s="16"/>
       <c r="AC6" s="16"/>
       <c r="AD6" s="16"/>
       <c r="AE6" s="16"/>
-      <c r="AF6" s="164" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG6" s="165"/>
-      <c r="AH6" s="165"/>
-      <c r="AI6" s="165"/>
-      <c r="AJ6" s="165"/>
-      <c r="AK6" s="165"/>
-      <c r="AL6" s="165"/>
-      <c r="AM6" s="165"/>
-      <c r="AN6" s="165"/>
-      <c r="AO6" s="165"/>
+      <c r="AF6" s="192" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG6" s="193"/>
+      <c r="AH6" s="193"/>
+      <c r="AI6" s="193"/>
+      <c r="AJ6" s="193"/>
+      <c r="AK6" s="193"/>
+      <c r="AL6" s="193"/>
+      <c r="AM6" s="193"/>
+      <c r="AN6" s="193"/>
+      <c r="AO6" s="193"/>
     </row>
     <row r="7" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="157" t="s">
+      <c r="A7" s="166" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="157" t="s">
+      <c r="C7" s="195" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="167" t="s">
+      <c r="D7" s="166" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="157" t="s">
+      <c r="E7" s="166" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="157" t="s">
+      <c r="F7" s="166" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="157" t="s">
+      <c r="G7" s="166" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="157" t="s">
+      <c r="H7" s="166" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="157" t="s">
+      <c r="I7" s="166" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="157" t="s">
+      <c r="J7" s="166" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="157" t="s">
+      <c r="K7" s="166" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="157" t="s">
+      <c r="L7" s="172" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="169" t="s">
+      <c r="M7" s="166" t="s">
         <v>18</v>
       </c>
-      <c r="M7" s="157" t="s">
+      <c r="N7" s="166" t="s">
         <v>19</v>
       </c>
-      <c r="N7" s="157" t="s">
+      <c r="O7" s="174" t="s">
         <v>20</v>
       </c>
-      <c r="O7" s="171" t="s">
+      <c r="P7" s="175"/>
+      <c r="Q7" s="175"/>
+      <c r="R7" s="175"/>
+      <c r="S7" s="175"/>
+      <c r="T7" s="175"/>
+      <c r="U7" s="175"/>
+      <c r="V7" s="176"/>
+      <c r="W7" s="166" t="s">
         <v>21</v>
       </c>
-      <c r="P7" s="172"/>
-      <c r="Q7" s="172"/>
-      <c r="R7" s="172"/>
-      <c r="S7" s="172"/>
-      <c r="T7" s="172"/>
-      <c r="U7" s="172"/>
-      <c r="V7" s="173"/>
-      <c r="W7" s="157" t="s">
+      <c r="X7" s="183" t="s">
         <v>22</v>
       </c>
-      <c r="X7" s="180" t="s">
+      <c r="Y7" s="183" t="s">
         <v>23</v>
       </c>
-      <c r="Y7" s="180" t="s">
+      <c r="Z7" s="184" t="s">
         <v>24</v>
       </c>
-      <c r="Z7" s="181" t="s">
+      <c r="AA7" s="166" t="s">
         <v>25</v>
       </c>
-      <c r="AA7" s="157" t="s">
+      <c r="AB7" s="166" t="s">
         <v>26</v>
       </c>
-      <c r="AB7" s="157" t="s">
+      <c r="AC7" s="185" t="s">
         <v>27</v>
       </c>
-      <c r="AC7" s="182" t="s">
+      <c r="AD7" s="185"/>
+      <c r="AE7" s="185"/>
+      <c r="AF7" s="171" t="s">
         <v>28</v>
       </c>
-      <c r="AD7" s="182"/>
-      <c r="AE7" s="182"/>
-      <c r="AF7" s="168" t="s">
+      <c r="AG7" s="168" t="s">
         <v>29</v>
       </c>
-      <c r="AG7" s="183" t="s">
+      <c r="AH7" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="AH7" s="183" t="s">
+      <c r="AI7" s="168" t="s">
         <v>31</v>
       </c>
-      <c r="AI7" s="183" t="s">
+      <c r="AJ7" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="AJ7" s="183" t="s">
+      <c r="AK7" s="171" t="s">
         <v>33</v>
       </c>
-      <c r="AK7" s="168" t="s">
+      <c r="AL7" s="171" t="s">
         <v>34</v>
       </c>
-      <c r="AL7" s="168" t="s">
+      <c r="AM7" s="166" t="s">
         <v>35</v>
       </c>
-      <c r="AM7" s="157" t="s">
+      <c r="AN7" s="166" t="s">
         <v>36</v>
       </c>
-      <c r="AN7" s="157" t="s">
+      <c r="AO7" s="166" t="s">
+        <v>154</v>
+      </c>
+      <c r="AS7" s="168" t="s">
         <v>37</v>
-      </c>
-      <c r="AO7" s="157" t="s">
-        <v>155</v>
-      </c>
-      <c r="AS7" s="183" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="158"/>
-      <c r="B8" s="166"/>
-      <c r="C8" s="167"/>
-      <c r="D8" s="158"/>
-      <c r="E8" s="158"/>
-      <c r="F8" s="158"/>
-      <c r="G8" s="158"/>
-      <c r="H8" s="158"/>
-      <c r="I8" s="158"/>
-      <c r="J8" s="158"/>
-      <c r="K8" s="158"/>
-      <c r="L8" s="158"/>
-      <c r="M8" s="158"/>
-      <c r="N8" s="170"/>
-      <c r="O8" s="174"/>
-      <c r="P8" s="175"/>
-      <c r="Q8" s="175"/>
-      <c r="R8" s="175"/>
-      <c r="S8" s="175"/>
-      <c r="T8" s="175"/>
-      <c r="U8" s="175"/>
-      <c r="V8" s="176"/>
-      <c r="W8" s="158"/>
-      <c r="X8" s="158"/>
-      <c r="Y8" s="158"/>
-      <c r="Z8" s="158"/>
-      <c r="AA8" s="158"/>
-      <c r="AB8" s="158"/>
-      <c r="AC8" s="182"/>
-      <c r="AD8" s="182"/>
-      <c r="AE8" s="182"/>
-      <c r="AF8" s="158"/>
-      <c r="AG8" s="185"/>
-      <c r="AH8" s="185"/>
-      <c r="AI8" s="183"/>
-      <c r="AJ8" s="185"/>
-      <c r="AK8" s="158"/>
-      <c r="AL8" s="168"/>
-      <c r="AM8" s="158"/>
-      <c r="AN8" s="157"/>
-      <c r="AO8" s="157"/>
-      <c r="AS8" s="184"/>
+      <c r="A8" s="167"/>
+      <c r="B8" s="194"/>
+      <c r="C8" s="195"/>
+      <c r="D8" s="167"/>
+      <c r="E8" s="167"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="167"/>
+      <c r="H8" s="167"/>
+      <c r="I8" s="167"/>
+      <c r="J8" s="167"/>
+      <c r="K8" s="167"/>
+      <c r="L8" s="167"/>
+      <c r="M8" s="167"/>
+      <c r="N8" s="173"/>
+      <c r="O8" s="177"/>
+      <c r="P8" s="178"/>
+      <c r="Q8" s="178"/>
+      <c r="R8" s="178"/>
+      <c r="S8" s="178"/>
+      <c r="T8" s="178"/>
+      <c r="U8" s="178"/>
+      <c r="V8" s="179"/>
+      <c r="W8" s="167"/>
+      <c r="X8" s="167"/>
+      <c r="Y8" s="167"/>
+      <c r="Z8" s="167"/>
+      <c r="AA8" s="167"/>
+      <c r="AB8" s="167"/>
+      <c r="AC8" s="185"/>
+      <c r="AD8" s="185"/>
+      <c r="AE8" s="185"/>
+      <c r="AF8" s="167"/>
+      <c r="AG8" s="170"/>
+      <c r="AH8" s="170"/>
+      <c r="AI8" s="168"/>
+      <c r="AJ8" s="170"/>
+      <c r="AK8" s="167"/>
+      <c r="AL8" s="171"/>
+      <c r="AM8" s="167"/>
+      <c r="AN8" s="166"/>
+      <c r="AO8" s="166"/>
+      <c r="AS8" s="169"/>
     </row>
     <row r="9" spans="1:45" ht="104.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="158"/>
-      <c r="B9" s="166"/>
-      <c r="C9" s="167"/>
-      <c r="D9" s="158"/>
-      <c r="E9" s="158"/>
-      <c r="F9" s="158"/>
-      <c r="G9" s="158"/>
-      <c r="H9" s="158"/>
-      <c r="I9" s="158"/>
-      <c r="J9" s="158"/>
-      <c r="K9" s="158"/>
-      <c r="L9" s="158"/>
-      <c r="M9" s="158"/>
-      <c r="N9" s="170"/>
-      <c r="O9" s="177"/>
-      <c r="P9" s="178"/>
-      <c r="Q9" s="178"/>
-      <c r="R9" s="178"/>
-      <c r="S9" s="178"/>
-      <c r="T9" s="178"/>
-      <c r="U9" s="178"/>
-      <c r="V9" s="179"/>
-      <c r="W9" s="158"/>
-      <c r="X9" s="158"/>
-      <c r="Y9" s="158"/>
-      <c r="Z9" s="158"/>
-      <c r="AA9" s="158"/>
-      <c r="AB9" s="158"/>
+      <c r="A9" s="167"/>
+      <c r="B9" s="194"/>
+      <c r="C9" s="195"/>
+      <c r="D9" s="167"/>
+      <c r="E9" s="167"/>
+      <c r="F9" s="167"/>
+      <c r="G9" s="167"/>
+      <c r="H9" s="167"/>
+      <c r="I9" s="167"/>
+      <c r="J9" s="167"/>
+      <c r="K9" s="167"/>
+      <c r="L9" s="167"/>
+      <c r="M9" s="167"/>
+      <c r="N9" s="173"/>
+      <c r="O9" s="180"/>
+      <c r="P9" s="181"/>
+      <c r="Q9" s="181"/>
+      <c r="R9" s="181"/>
+      <c r="S9" s="181"/>
+      <c r="T9" s="181"/>
+      <c r="U9" s="181"/>
+      <c r="V9" s="182"/>
+      <c r="W9" s="167"/>
+      <c r="X9" s="167"/>
+      <c r="Y9" s="167"/>
+      <c r="Z9" s="167"/>
+      <c r="AA9" s="167"/>
+      <c r="AB9" s="167"/>
       <c r="AC9" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD9" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="AD9" s="26" t="s">
+      <c r="AE9" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="AE9" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="AF9" s="158"/>
-      <c r="AG9" s="185"/>
-      <c r="AH9" s="185"/>
-      <c r="AI9" s="183"/>
-      <c r="AJ9" s="185"/>
-      <c r="AK9" s="158"/>
-      <c r="AL9" s="168"/>
-      <c r="AM9" s="158"/>
-      <c r="AN9" s="157"/>
-      <c r="AO9" s="157"/>
+      <c r="AF9" s="167"/>
+      <c r="AG9" s="170"/>
+      <c r="AH9" s="170"/>
+      <c r="AI9" s="168"/>
+      <c r="AJ9" s="170"/>
+      <c r="AK9" s="167"/>
+      <c r="AL9" s="171"/>
+      <c r="AM9" s="167"/>
+      <c r="AN9" s="166"/>
+      <c r="AO9" s="166"/>
       <c r="AP9">
         <f>Z11/W11</f>
         <v>0.6571510184673206</v>
@@ -2361,7 +2361,7 @@
       <c r="AR9">
         <v>27</v>
       </c>
-      <c r="AS9" s="184"/>
+      <c r="AS9" s="169"/>
     </row>
     <row r="10" spans="1:45" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="27">
@@ -2387,32 +2387,32 @@
         <v>4</v>
       </c>
       <c r="O10" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="P10" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="P10" s="29" t="s">
+      <c r="Q10" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="Q10" s="29" t="s">
+      <c r="R10" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="R10" s="29" t="s">
+      <c r="S10" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="S10" s="29" t="s">
+      <c r="T10" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="T10" s="29" t="s">
+      <c r="U10" s="29" t="s">
         <v>47</v>
-      </c>
-      <c r="U10" s="29" t="s">
-        <v>48</v>
       </c>
       <c r="V10" s="29"/>
       <c r="W10" s="27">
         <v>5</v>
       </c>
       <c r="X10" s="30"/>
-      <c r="Y10" s="186"/>
+      <c r="Y10" s="157"/>
       <c r="Z10" s="30">
         <v>6</v>
       </c>
@@ -2452,7 +2452,7 @@
     <row r="11" spans="1:45" s="47" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34"/>
       <c r="B11" s="35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" s="36"/>
       <c r="D11" s="37">
@@ -2538,7 +2538,7 @@
       <c r="X11" s="37">
         <v>654048.10699999996</v>
       </c>
-      <c r="Y11" s="187">
+      <c r="Y11" s="158">
         <f t="shared" si="1"/>
         <v>7931</v>
       </c>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="12" spans="1:45" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="49" t="s">
         <v>50</v>
-      </c>
-      <c r="B12" s="49" t="s">
-        <v>51</v>
       </c>
       <c r="C12" s="50"/>
       <c r="D12" s="51"/>
@@ -2644,7 +2644,7 @@
       <c r="X12" s="58">
         <v>0</v>
       </c>
-      <c r="Y12" s="188"/>
+      <c r="Y12" s="159"/>
       <c r="Z12" s="59">
         <f>SUM(X12:Y12)</f>
         <v>0</v>
@@ -2680,10 +2680,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="69" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="70" t="s">
         <v>52</v>
-      </c>
-      <c r="C13" s="70" t="s">
-        <v>53</v>
       </c>
       <c r="D13" s="71">
         <v>10000</v>
@@ -2735,7 +2735,7 @@
       <c r="X13" s="76">
         <v>0</v>
       </c>
-      <c r="Y13" s="189"/>
+      <c r="Y13" s="160"/>
       <c r="Z13" s="59">
         <f t="shared" ref="Z13:Z66" si="4">SUM(X13:Y13)</f>
         <v>0</v>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="AO13" s="154" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AP13" s="84">
         <f>Z11/W11</f>
@@ -2794,10 +2794,10 @@
         <v>2</v>
       </c>
       <c r="B14" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="70" t="s">
         <v>54</v>
-      </c>
-      <c r="C14" s="70" t="s">
-        <v>55</v>
       </c>
       <c r="D14" s="71">
         <v>200</v>
@@ -2845,7 +2845,7 @@
       <c r="X14" s="76">
         <v>0</v>
       </c>
-      <c r="Y14" s="189"/>
+      <c r="Y14" s="160"/>
       <c r="Z14" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -2889,7 +2889,7 @@
         <v>0</v>
       </c>
       <c r="AO14" s="154" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AR14">
         <v>28</v>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="15" spans="1:45" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="87" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="49" t="s">
         <v>56</v>
-      </c>
-      <c r="B15" s="49" t="s">
-        <v>57</v>
       </c>
       <c r="C15" s="88"/>
       <c r="D15" s="54"/>
@@ -2931,7 +2931,7 @@
       <c r="X15" s="76">
         <v>0</v>
       </c>
-      <c r="Y15" s="189"/>
+      <c r="Y15" s="160"/>
       <c r="Z15" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -2972,10 +2972,10 @@
         <v>3</v>
       </c>
       <c r="B16" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="89" t="s">
         <v>58</v>
-      </c>
-      <c r="C16" s="89" t="s">
-        <v>59</v>
       </c>
       <c r="D16" s="71"/>
       <c r="E16" s="71"/>
@@ -3015,7 +3015,7 @@
       <c r="X16" s="76">
         <v>0</v>
       </c>
-      <c r="Y16" s="189"/>
+      <c r="Y16" s="160"/>
       <c r="Z16" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="AO16" s="155" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:44" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="49" t="s">
         <v>60</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>61</v>
       </c>
       <c r="C17" s="89"/>
       <c r="D17" s="71"/>
@@ -3091,7 +3091,7 @@
       <c r="V17" s="72"/>
       <c r="W17" s="57"/>
       <c r="X17" s="76"/>
-      <c r="Y17" s="189"/>
+      <c r="Y17" s="160"/>
       <c r="Z17" s="59"/>
       <c r="AA17" s="78"/>
       <c r="AB17" s="78"/>
@@ -3123,10 +3123,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="89" t="s">
         <v>62</v>
-      </c>
-      <c r="C18" s="89" t="s">
-        <v>63</v>
       </c>
       <c r="D18" s="71"/>
       <c r="E18" s="71"/>
@@ -3166,7 +3166,7 @@
       <c r="X18" s="76">
         <v>0</v>
       </c>
-      <c r="Y18" s="189"/>
+      <c r="Y18" s="160"/>
       <c r="Z18" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3210,7 +3210,7 @@
         <v>50</v>
       </c>
       <c r="AO18" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:44" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3218,10 +3218,10 @@
         <v>5</v>
       </c>
       <c r="B19" s="69" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="89" t="s">
         <v>64</v>
-      </c>
-      <c r="C19" s="89" t="s">
-        <v>65</v>
       </c>
       <c r="D19" s="71"/>
       <c r="E19" s="71"/>
@@ -3261,7 +3261,7 @@
       <c r="X19" s="76">
         <v>2246.1019999999999</v>
       </c>
-      <c r="Y19" s="189"/>
+      <c r="Y19" s="160"/>
       <c r="Z19" s="59">
         <f t="shared" si="4"/>
         <v>2246.1019999999999</v>
@@ -3293,7 +3293,7 @@
         <v>13464.898000000001</v>
       </c>
       <c r="AJ19" s="94" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AK19" s="42">
         <f t="shared" si="3"/>
@@ -3309,7 +3309,7 @@
         <v>13464.898000000001</v>
       </c>
       <c r="AO19" s="155" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:44" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -3317,7 +3317,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="69" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C20" s="89">
         <v>8112228</v>
@@ -3356,7 +3356,7 @@
       <c r="X20" s="76">
         <v>26478.066999999999</v>
       </c>
-      <c r="Y20" s="189"/>
+      <c r="Y20" s="160"/>
       <c r="Z20" s="59">
         <f>SUM(X20:Y20)</f>
         <v>26478.066999999999</v>
@@ -3404,7 +3404,7 @@
         <v>10321.933000000001</v>
       </c>
       <c r="AO20" s="155" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AQ20" s="97">
         <f>Z20-24656</f>
@@ -3416,10 +3416,10 @@
         <v>7</v>
       </c>
       <c r="B21" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="89" t="s">
         <v>68</v>
-      </c>
-      <c r="C21" s="89" t="s">
-        <v>69</v>
       </c>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
@@ -3457,7 +3457,7 @@
       <c r="X21" s="76">
         <v>2292.66</v>
       </c>
-      <c r="Y21" s="189"/>
+      <c r="Y21" s="160"/>
       <c r="Z21" s="59">
         <f t="shared" si="4"/>
         <v>2292.66</v>
@@ -3505,7 +3505,7 @@
         <v>995.34000000000015</v>
       </c>
       <c r="AO21" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AP21" s="97">
         <f>Z21-38334</f>
@@ -3520,10 +3520,10 @@
         <v>8</v>
       </c>
       <c r="B22" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="89" t="s">
         <v>70</v>
-      </c>
-      <c r="C22" s="89" t="s">
-        <v>71</v>
       </c>
       <c r="D22" s="71"/>
       <c r="E22" s="71"/>
@@ -3559,7 +3559,7 @@
       <c r="X22" s="76">
         <v>0</v>
       </c>
-      <c r="Y22" s="189"/>
+      <c r="Y22" s="160"/>
       <c r="Z22" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3587,7 +3587,7 @@
       <c r="AM22" s="83"/>
       <c r="AN22" s="92"/>
       <c r="AO22" s="106" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AP22" s="97"/>
     </row>
@@ -3596,10 +3596,10 @@
         <v>9</v>
       </c>
       <c r="B23" s="69" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="89" t="s">
         <v>72</v>
-      </c>
-      <c r="C23" s="89" t="s">
-        <v>73</v>
       </c>
       <c r="D23" s="71"/>
       <c r="E23" s="71"/>
@@ -3635,7 +3635,7 @@
       <c r="X23" s="76">
         <v>0</v>
       </c>
-      <c r="Y23" s="189"/>
+      <c r="Y23" s="160"/>
       <c r="Z23" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3663,7 +3663,7 @@
       <c r="AM23" s="83"/>
       <c r="AN23" s="92"/>
       <c r="AO23" s="106" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AP23" s="97"/>
     </row>
@@ -3672,10 +3672,10 @@
         <v>10</v>
       </c>
       <c r="B24" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="89" t="s">
         <v>74</v>
-      </c>
-      <c r="C24" s="89" t="s">
-        <v>75</v>
       </c>
       <c r="D24" s="71"/>
       <c r="E24" s="71"/>
@@ -3707,7 +3707,7 @@
       <c r="X24" s="76">
         <v>0</v>
       </c>
-      <c r="Y24" s="189"/>
+      <c r="Y24" s="160"/>
       <c r="Z24" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3735,7 +3735,7 @@
       <c r="AM24" s="83"/>
       <c r="AN24" s="92"/>
       <c r="AO24" s="106" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AP24" s="97"/>
     </row>
@@ -3744,10 +3744,10 @@
         <v>11</v>
       </c>
       <c r="B25" s="69" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="89" t="s">
         <v>76</v>
-      </c>
-      <c r="C25" s="89" t="s">
-        <v>77</v>
       </c>
       <c r="D25" s="71"/>
       <c r="E25" s="71"/>
@@ -3779,7 +3779,7 @@
       <c r="X25" s="76">
         <v>5.04</v>
       </c>
-      <c r="Y25" s="189"/>
+      <c r="Y25" s="160"/>
       <c r="Z25" s="59">
         <f t="shared" si="4"/>
         <v>5.04</v>
@@ -3805,7 +3805,7 @@
       <c r="AM25" s="83"/>
       <c r="AN25" s="92"/>
       <c r="AO25" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AP25" s="97"/>
     </row>
@@ -3814,10 +3814,10 @@
         <v>12</v>
       </c>
       <c r="B26" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="89" t="s">
         <v>78</v>
-      </c>
-      <c r="C26" s="89" t="s">
-        <v>79</v>
       </c>
       <c r="D26" s="71"/>
       <c r="E26" s="71"/>
@@ -3849,7 +3849,7 @@
       <c r="X26" s="76">
         <v>0</v>
       </c>
-      <c r="Y26" s="189"/>
+      <c r="Y26" s="160"/>
       <c r="Z26" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3877,7 +3877,7 @@
       <c r="AM26" s="83"/>
       <c r="AN26" s="92"/>
       <c r="AO26" s="106" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AP26" s="97"/>
     </row>
@@ -3886,10 +3886,10 @@
         <v>13</v>
       </c>
       <c r="B27" s="69" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="89" t="s">
         <v>80</v>
-      </c>
-      <c r="C27" s="89" t="s">
-        <v>81</v>
       </c>
       <c r="D27" s="71"/>
       <c r="E27" s="71"/>
@@ -3921,7 +3921,7 @@
       <c r="X27" s="76">
         <v>3.47</v>
       </c>
-      <c r="Y27" s="189"/>
+      <c r="Y27" s="160"/>
       <c r="Z27" s="59">
         <f t="shared" si="4"/>
         <v>3.47</v>
@@ -3949,7 +3949,7 @@
       <c r="AM27" s="83"/>
       <c r="AN27" s="92"/>
       <c r="AO27" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AP27" s="97"/>
     </row>
@@ -3958,10 +3958,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="101" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="89" t="s">
         <v>82</v>
-      </c>
-      <c r="C28" s="89" t="s">
-        <v>83</v>
       </c>
       <c r="D28" s="71"/>
       <c r="E28" s="71"/>
@@ -3993,7 +3993,7 @@
       <c r="X28" s="76">
         <v>6.7</v>
       </c>
-      <c r="Y28" s="189"/>
+      <c r="Y28" s="160"/>
       <c r="Z28" s="59">
         <f t="shared" si="4"/>
         <v>6.7</v>
@@ -4021,7 +4021,7 @@
       <c r="AM28" s="83"/>
       <c r="AN28" s="92"/>
       <c r="AO28" s="154" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AP28" s="97"/>
     </row>
@@ -4030,10 +4030,10 @@
         <v>15</v>
       </c>
       <c r="B29" s="101" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" s="89" t="s">
         <v>84</v>
-      </c>
-      <c r="C29" s="89" t="s">
-        <v>85</v>
       </c>
       <c r="D29" s="71"/>
       <c r="E29" s="71"/>
@@ -4065,7 +4065,7 @@
       <c r="X29" s="76">
         <v>0</v>
       </c>
-      <c r="Y29" s="189"/>
+      <c r="Y29" s="160"/>
       <c r="Z29" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -4093,7 +4093,7 @@
       <c r="AM29" s="83"/>
       <c r="AN29" s="92"/>
       <c r="AO29" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AP29" s="97"/>
     </row>
@@ -4102,10 +4102,10 @@
         <v>16</v>
       </c>
       <c r="B30" s="101" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" s="89" t="s">
         <v>86</v>
-      </c>
-      <c r="C30" s="89" t="s">
-        <v>87</v>
       </c>
       <c r="D30" s="71"/>
       <c r="E30" s="71"/>
@@ -4137,7 +4137,7 @@
       <c r="X30" s="76">
         <v>37.1</v>
       </c>
-      <c r="Y30" s="189"/>
+      <c r="Y30" s="160"/>
       <c r="Z30" s="59">
         <f t="shared" si="4"/>
         <v>37.1</v>
@@ -4165,7 +4165,7 @@
       <c r="AM30" s="83"/>
       <c r="AN30" s="92"/>
       <c r="AO30" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AP30" s="97"/>
     </row>
@@ -4174,10 +4174,10 @@
         <v>17</v>
       </c>
       <c r="B31" s="101" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="89" t="s">
         <v>88</v>
-      </c>
-      <c r="C31" s="89" t="s">
-        <v>89</v>
       </c>
       <c r="D31" s="71"/>
       <c r="E31" s="71"/>
@@ -4209,7 +4209,7 @@
       <c r="X31" s="76">
         <v>0</v>
       </c>
-      <c r="Y31" s="189"/>
+      <c r="Y31" s="160"/>
       <c r="Z31" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -4237,7 +4237,7 @@
       <c r="AM31" s="83"/>
       <c r="AN31" s="92"/>
       <c r="AO31" s="106" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AP31" s="97"/>
     </row>
@@ -4246,10 +4246,10 @@
         <v>18</v>
       </c>
       <c r="B32" s="101" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="89" t="s">
         <v>90</v>
-      </c>
-      <c r="C32" s="89" t="s">
-        <v>91</v>
       </c>
       <c r="D32" s="71"/>
       <c r="E32" s="71"/>
@@ -4281,7 +4281,7 @@
       <c r="X32" s="76">
         <v>0</v>
       </c>
-      <c r="Y32" s="189"/>
+      <c r="Y32" s="160"/>
       <c r="Z32" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -4309,7 +4309,7 @@
       <c r="AM32" s="83"/>
       <c r="AN32" s="92"/>
       <c r="AO32" s="106" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AP32" s="97"/>
     </row>
@@ -4318,10 +4318,10 @@
         <v>19</v>
       </c>
       <c r="B33" s="101" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" s="89" t="s">
         <v>92</v>
-      </c>
-      <c r="C33" s="89" t="s">
-        <v>93</v>
       </c>
       <c r="D33" s="71"/>
       <c r="E33" s="71"/>
@@ -4353,7 +4353,7 @@
       <c r="X33" s="76">
         <v>8.5</v>
       </c>
-      <c r="Y33" s="189"/>
+      <c r="Y33" s="160"/>
       <c r="Z33" s="59">
         <f t="shared" si="4"/>
         <v>8.5</v>
@@ -4381,16 +4381,16 @@
       <c r="AM33" s="83"/>
       <c r="AN33" s="92"/>
       <c r="AO33" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AP33" s="97"/>
     </row>
     <row r="34" spans="1:44" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="49" t="s">
         <v>94</v>
-      </c>
-      <c r="B34" s="49" t="s">
-        <v>95</v>
       </c>
       <c r="C34" s="103"/>
       <c r="D34" s="104"/>
@@ -4414,7 +4414,7 @@
       <c r="V34" s="72"/>
       <c r="W34" s="57"/>
       <c r="X34" s="76"/>
-      <c r="Y34" s="189"/>
+      <c r="Y34" s="160"/>
       <c r="Z34" s="59"/>
       <c r="AA34" s="78"/>
       <c r="AB34" s="78"/>
@@ -4449,10 +4449,10 @@
         <v>20</v>
       </c>
       <c r="B35" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="89" t="s">
         <v>96</v>
-      </c>
-      <c r="C35" s="89" t="s">
-        <v>97</v>
       </c>
       <c r="D35" s="71"/>
       <c r="E35" s="71"/>
@@ -4495,7 +4495,7 @@
       <c r="X35" s="76">
         <v>6002.44</v>
       </c>
-      <c r="Y35" s="189"/>
+      <c r="Y35" s="160"/>
       <c r="Z35" s="59">
         <f>SUM(X35:Y35)</f>
         <v>6002.44</v>
@@ -4541,7 +4541,7 @@
         <v>512.5600000000004</v>
       </c>
       <c r="AO35" s="155" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:44" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4549,7 +4549,7 @@
         <v>21</v>
       </c>
       <c r="B36" s="69" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C36" s="89">
         <v>8112965</v>
@@ -4588,7 +4588,7 @@
       <c r="X36" s="76">
         <v>936.10699999999997</v>
       </c>
-      <c r="Y36" s="189"/>
+      <c r="Y36" s="160"/>
       <c r="Z36" s="59">
         <f t="shared" si="4"/>
         <v>936.10699999999997</v>
@@ -4632,7 +4632,7 @@
         <v>271.89300000000003</v>
       </c>
       <c r="AO36" s="154" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AQ36" s="67">
         <f>X36-261</f>
@@ -4644,7 +4644,7 @@
         <v>22</v>
       </c>
       <c r="B37" s="69" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C37" s="89">
         <v>8100887</v>
@@ -4687,7 +4687,7 @@
       <c r="X37" s="76">
         <v>9615.2000000000007</v>
       </c>
-      <c r="Y37" s="189"/>
+      <c r="Y37" s="160"/>
       <c r="Z37" s="59">
         <f t="shared" si="4"/>
         <v>9615.2000000000007</v>
@@ -4735,7 +4735,7 @@
         <v>4884.7999999999993</v>
       </c>
       <c r="AO37" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AP37" s="105"/>
       <c r="AQ37" s="67"/>
@@ -4745,7 +4745,7 @@
         <v>23</v>
       </c>
       <c r="B38" s="69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C38" s="89">
         <v>8101114</v>
@@ -4784,7 +4784,7 @@
       <c r="X38" s="76">
         <v>20539.23</v>
       </c>
-      <c r="Y38" s="189">
+      <c r="Y38" s="160">
         <v>7931</v>
       </c>
       <c r="Z38" s="59">
@@ -4835,7 +4835,7 @@
         <v>15646.77</v>
       </c>
       <c r="AO38" s="154" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AQ38" s="67"/>
     </row>
@@ -4844,7 +4844,7 @@
         <v>24</v>
       </c>
       <c r="B39" s="69" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C39" s="89">
         <v>8100889</v>
@@ -4883,7 +4883,7 @@
       <c r="X39" s="76">
         <v>22155.989999999998</v>
       </c>
-      <c r="Y39" s="189"/>
+      <c r="Y39" s="160"/>
       <c r="Z39" s="59">
         <f>SUM(X39:Y39)</f>
         <v>22155.989999999998</v>
@@ -4931,7 +4931,7 @@
         <v>28263.010000000002</v>
       </c>
       <c r="AO39" s="106" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:44" ht="46.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -4939,7 +4939,7 @@
         <v>25</v>
       </c>
       <c r="B40" s="69" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C40" s="89">
         <v>8111370</v>
@@ -4982,7 +4982,7 @@
       <c r="X40" s="76">
         <v>36775</v>
       </c>
-      <c r="Y40" s="189"/>
+      <c r="Y40" s="160"/>
       <c r="Z40" s="59">
         <f t="shared" si="4"/>
         <v>36775</v>
@@ -5030,7 +5030,7 @@
         <v>23663</v>
       </c>
       <c r="AO40" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:44" ht="40.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -5038,7 +5038,7 @@
         <v>26</v>
       </c>
       <c r="B41" s="69" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C41" s="89">
         <v>8111981</v>
@@ -5079,7 +5079,7 @@
       <c r="X41" s="76">
         <v>0</v>
       </c>
-      <c r="Y41" s="189"/>
+      <c r="Y41" s="160"/>
       <c r="Z41" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -5123,7 +5123,7 @@
         <v>420</v>
       </c>
       <c r="AO41" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AP41" s="97">
         <f>AP40-Z40</f>
@@ -5135,7 +5135,7 @@
         <v>27</v>
       </c>
       <c r="B42" s="69" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C42" s="89">
         <v>8112964</v>
@@ -5174,7 +5174,7 @@
       <c r="X42" s="76">
         <v>0</v>
       </c>
-      <c r="Y42" s="189"/>
+      <c r="Y42" s="160"/>
       <c r="Z42" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -5218,7 +5218,7 @@
         <v>125</v>
       </c>
       <c r="AO42" s="106" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AP42" s="97">
         <f>Z42-13579</f>
@@ -5234,7 +5234,7 @@
         <v>28</v>
       </c>
       <c r="B43" s="69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C43" s="89">
         <v>8112963</v>
@@ -5275,7 +5275,7 @@
       <c r="X43" s="76">
         <v>0</v>
       </c>
-      <c r="Y43" s="189"/>
+      <c r="Y43" s="160"/>
       <c r="Z43" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -5317,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="AO43" s="155" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AQ43" s="97">
         <f>AQ42-Z42</f>
@@ -5329,10 +5329,10 @@
         <v>29</v>
       </c>
       <c r="B44" s="69" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" s="89" t="s">
         <v>106</v>
-      </c>
-      <c r="C44" s="89" t="s">
-        <v>107</v>
       </c>
       <c r="D44" s="71"/>
       <c r="E44" s="71"/>
@@ -5370,7 +5370,7 @@
       <c r="X44" s="76">
         <v>0</v>
       </c>
-      <c r="Y44" s="189"/>
+      <c r="Y44" s="160"/>
       <c r="Z44" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -5414,7 +5414,7 @@
         <v>34000</v>
       </c>
       <c r="AO44" s="154" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AP44">
         <v>24869</v>
@@ -5425,7 +5425,7 @@
         <v>30</v>
       </c>
       <c r="B45" s="69" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C45" s="89">
         <v>8111982</v>
@@ -5466,7 +5466,7 @@
       <c r="X45" s="76">
         <v>0</v>
       </c>
-      <c r="Y45" s="189"/>
+      <c r="Y45" s="160"/>
       <c r="Z45" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -5510,7 +5510,7 @@
         <v>191</v>
       </c>
       <c r="AO45" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AP45" s="67">
         <f>10338</f>
@@ -5525,7 +5525,7 @@
         <v>31</v>
       </c>
       <c r="B46" s="69" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C46" s="89">
         <v>8101113</v>
@@ -5564,7 +5564,7 @@
       <c r="X46" s="76">
         <v>0</v>
       </c>
-      <c r="Y46" s="189"/>
+      <c r="Y46" s="160"/>
       <c r="Z46" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -5608,7 +5608,7 @@
         <v>33</v>
       </c>
       <c r="AO46" s="106" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AR46">
         <v>55</v>
@@ -5619,7 +5619,7 @@
         <v>32</v>
       </c>
       <c r="B47" s="69" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C47" s="89">
         <v>8101117</v>
@@ -5658,7 +5658,7 @@
       <c r="X47" s="76">
         <v>0</v>
       </c>
-      <c r="Y47" s="189"/>
+      <c r="Y47" s="160"/>
       <c r="Z47" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -5702,7 +5702,7 @@
         <v>10</v>
       </c>
       <c r="AO47" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="48" spans="1:44" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5710,7 +5710,7 @@
         <v>33</v>
       </c>
       <c r="B48" s="69" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C48" s="89">
         <v>8100890</v>
@@ -5749,7 +5749,7 @@
       <c r="X48" s="76">
         <v>0</v>
       </c>
-      <c r="Y48" s="189"/>
+      <c r="Y48" s="160"/>
       <c r="Z48" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -5793,7 +5793,7 @@
         <v>10</v>
       </c>
       <c r="AO48" s="106" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="49" spans="1:44" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -5801,7 +5801,7 @@
         <v>34</v>
       </c>
       <c r="B49" s="69" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C49" s="89">
         <v>8101116</v>
@@ -5840,7 +5840,7 @@
       <c r="X49" s="76">
         <v>0</v>
       </c>
-      <c r="Y49" s="189"/>
+      <c r="Y49" s="160"/>
       <c r="Z49" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -5884,7 +5884,7 @@
         <v>20</v>
       </c>
       <c r="AO49" s="154" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="50" spans="1:44" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5892,7 +5892,7 @@
         <v>35</v>
       </c>
       <c r="B50" s="69" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C50" s="89">
         <v>8101115</v>
@@ -5931,7 +5931,7 @@
       <c r="X50" s="76">
         <v>0</v>
       </c>
-      <c r="Y50" s="189"/>
+      <c r="Y50" s="160"/>
       <c r="Z50" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -5975,7 +5975,7 @@
         <v>50</v>
       </c>
       <c r="AO50" s="154" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="51" spans="1:44" ht="60" x14ac:dyDescent="0.25">
@@ -5983,7 +5983,7 @@
         <v>36</v>
       </c>
       <c r="B51" s="69" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C51" s="89">
         <v>8101736</v>
@@ -6022,7 +6022,7 @@
       <c r="X51" s="76">
         <v>0</v>
       </c>
-      <c r="Y51" s="189"/>
+      <c r="Y51" s="160"/>
       <c r="Z51" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -6066,7 +6066,7 @@
         <v>50</v>
       </c>
       <c r="AO51" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="1:44" ht="45" x14ac:dyDescent="0.25">
@@ -6074,7 +6074,7 @@
         <v>37</v>
       </c>
       <c r="B52" s="69" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C52" s="89">
         <v>8112949</v>
@@ -6113,7 +6113,7 @@
       <c r="X52" s="76">
         <v>0</v>
       </c>
-      <c r="Y52" s="189"/>
+      <c r="Y52" s="160"/>
       <c r="Z52" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -6157,7 +6157,7 @@
         <v>15</v>
       </c>
       <c r="AO52" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:44" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6165,7 +6165,7 @@
         <v>38</v>
       </c>
       <c r="B53" s="69" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C53" s="89">
         <v>8111980</v>
@@ -6204,7 +6204,7 @@
       <c r="X53" s="76">
         <v>0</v>
       </c>
-      <c r="Y53" s="189"/>
+      <c r="Y53" s="160"/>
       <c r="Z53" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -6248,7 +6248,7 @@
         <v>33</v>
       </c>
       <c r="AO53" s="106" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:44" ht="86.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6256,7 +6256,7 @@
         <v>39</v>
       </c>
       <c r="B54" s="69" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C54" s="89">
         <v>8113485</v>
@@ -6295,7 +6295,7 @@
       <c r="X54" s="76">
         <v>0</v>
       </c>
-      <c r="Y54" s="189"/>
+      <c r="Y54" s="160"/>
       <c r="Z54" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -6339,7 +6339,7 @@
         <v>50</v>
       </c>
       <c r="AO54" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:44" ht="48" customHeight="1" x14ac:dyDescent="0.25">
@@ -6347,7 +6347,7 @@
         <v>40</v>
       </c>
       <c r="B55" s="69" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C55" s="89">
         <v>8113487</v>
@@ -6386,7 +6386,7 @@
       <c r="X55" s="76">
         <v>0</v>
       </c>
-      <c r="Y55" s="189"/>
+      <c r="Y55" s="160"/>
       <c r="Z55" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>50</v>
       </c>
       <c r="AO55" s="154" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="56" spans="1:44" ht="46.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -6438,7 +6438,7 @@
         <v>41</v>
       </c>
       <c r="B56" s="69" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C56" s="89">
         <v>8112948</v>
@@ -6477,7 +6477,7 @@
       <c r="X56" s="76">
         <v>0</v>
       </c>
-      <c r="Y56" s="189"/>
+      <c r="Y56" s="160"/>
       <c r="Z56" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -6521,7 +6521,7 @@
         <v>6</v>
       </c>
       <c r="AO56" s="106" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" spans="1:44" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6529,7 +6529,7 @@
         <v>42</v>
       </c>
       <c r="B57" s="69" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C57" s="89">
         <v>8118634</v>
@@ -6568,7 +6568,7 @@
       <c r="X57" s="76">
         <v>0</v>
       </c>
-      <c r="Y57" s="189"/>
+      <c r="Y57" s="160"/>
       <c r="Z57" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>23</v>
       </c>
       <c r="AO57" s="106" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:44" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6620,7 +6620,7 @@
         <v>43</v>
       </c>
       <c r="B58" s="69" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C58" s="89">
         <v>8111984</v>
@@ -6659,7 +6659,7 @@
       <c r="X58" s="76">
         <v>0</v>
       </c>
-      <c r="Y58" s="189"/>
+      <c r="Y58" s="160"/>
       <c r="Z58" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -6703,7 +6703,7 @@
         <v>25</v>
       </c>
       <c r="AO58" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:44" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6711,7 +6711,7 @@
         <v>44</v>
       </c>
       <c r="B59" s="69" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C59" s="89">
         <v>8111979</v>
@@ -6750,7 +6750,7 @@
       <c r="X59" s="76">
         <v>0</v>
       </c>
-      <c r="Y59" s="189"/>
+      <c r="Y59" s="160"/>
       <c r="Z59" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -6792,7 +6792,7 @@
         <v>265</v>
       </c>
       <c r="AO59" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="60" spans="1:44" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6800,7 +6800,7 @@
         <v>45</v>
       </c>
       <c r="B60" s="69" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C60" s="89">
         <v>8113209</v>
@@ -6839,7 +6839,7 @@
       <c r="X60" s="76">
         <v>28362.960999999999</v>
       </c>
-      <c r="Y60" s="189"/>
+      <c r="Y60" s="160"/>
       <c r="Z60" s="59">
         <f t="shared" si="4"/>
         <v>28362.960999999999</v>
@@ -6887,7 +6887,7 @@
         <v>33412.039000000004</v>
       </c>
       <c r="AO60" s="154" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="61" spans="1:44" ht="45" x14ac:dyDescent="0.25">
@@ -6895,7 +6895,7 @@
         <v>46</v>
       </c>
       <c r="B61" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C61" s="89">
         <v>8100888</v>
@@ -6936,7 +6936,7 @@
       <c r="X61" s="76">
         <v>497783.54</v>
       </c>
-      <c r="Y61" s="189"/>
+      <c r="Y61" s="160"/>
       <c r="Z61" s="59">
         <f t="shared" si="4"/>
         <v>497783.54</v>
@@ -6982,7 +6982,7 @@
         <v>130000.46000000002</v>
       </c>
       <c r="AO61" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AQ61" s="109">
         <v>167340</v>
@@ -6993,10 +6993,10 @@
     </row>
     <row r="62" spans="1:44" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="B62" s="49" t="s">
         <v>125</v>
-      </c>
-      <c r="B62" s="49" t="s">
-        <v>126</v>
       </c>
       <c r="C62" s="110"/>
       <c r="D62" s="104"/>
@@ -7023,7 +7023,7 @@
         <v>0</v>
       </c>
       <c r="X62" s="76"/>
-      <c r="Y62" s="189"/>
+      <c r="Y62" s="160"/>
       <c r="Z62" s="59"/>
       <c r="AA62" s="78"/>
       <c r="AB62" s="78"/>
@@ -7066,10 +7066,10 @@
         <v>1</v>
       </c>
       <c r="B63" s="69" t="s">
+        <v>126</v>
+      </c>
+      <c r="C63" s="114" t="s">
         <v>127</v>
-      </c>
-      <c r="C63" s="114" t="s">
-        <v>128</v>
       </c>
       <c r="D63" s="71"/>
       <c r="E63" s="71"/>
@@ -7111,7 +7111,7 @@
       <c r="X63" s="76">
         <v>100</v>
       </c>
-      <c r="Y63" s="189"/>
+      <c r="Y63" s="160"/>
       <c r="Z63" s="59">
         <f t="shared" si="4"/>
         <v>100</v>
@@ -7153,7 +7153,7 @@
       <c r="AM63" s="85"/>
       <c r="AN63" s="85"/>
       <c r="AO63" s="116" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AR63" s="117">
         <f>383-60</f>
@@ -7165,10 +7165,10 @@
         <v>2</v>
       </c>
       <c r="B64" s="69" t="s">
+        <v>128</v>
+      </c>
+      <c r="C64" s="114" t="s">
         <v>129</v>
-      </c>
-      <c r="C64" s="114" t="s">
-        <v>130</v>
       </c>
       <c r="D64" s="71"/>
       <c r="E64" s="71">
@@ -7212,7 +7212,7 @@
       <c r="X64" s="76">
         <v>100</v>
       </c>
-      <c r="Y64" s="189"/>
+      <c r="Y64" s="160"/>
       <c r="Z64" s="59">
         <f t="shared" si="4"/>
         <v>100</v>
@@ -7255,7 +7255,7 @@
       <c r="AM64" s="85"/>
       <c r="AN64" s="85"/>
       <c r="AO64" s="116" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:41" ht="48" customHeight="1" x14ac:dyDescent="0.25">
@@ -7263,10 +7263,10 @@
         <v>3</v>
       </c>
       <c r="B65" s="69" t="s">
+        <v>130</v>
+      </c>
+      <c r="C65" s="114" t="s">
         <v>131</v>
-      </c>
-      <c r="C65" s="114" t="s">
-        <v>132</v>
       </c>
       <c r="D65" s="71"/>
       <c r="E65" s="71">
@@ -7308,7 +7308,7 @@
       <c r="X65" s="76">
         <v>100</v>
       </c>
-      <c r="Y65" s="189"/>
+      <c r="Y65" s="160"/>
       <c r="Z65" s="59">
         <f t="shared" si="4"/>
         <v>100</v>
@@ -7351,7 +7351,7 @@
       <c r="AM65" s="80"/>
       <c r="AN65" s="80"/>
       <c r="AO65" s="116" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="66" spans="1:41" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7359,10 +7359,10 @@
         <v>4</v>
       </c>
       <c r="B66" s="69" t="s">
+        <v>132</v>
+      </c>
+      <c r="C66" s="114" t="s">
         <v>133</v>
-      </c>
-      <c r="C66" s="114" t="s">
-        <v>134</v>
       </c>
       <c r="D66" s="71"/>
       <c r="E66" s="71"/>
@@ -7403,7 +7403,7 @@
       <c r="X66" s="76">
         <v>100</v>
       </c>
-      <c r="Y66" s="189"/>
+      <c r="Y66" s="160"/>
       <c r="Z66" s="59">
         <f t="shared" si="4"/>
         <v>100</v>
@@ -7443,7 +7443,7 @@
       <c r="AM66" s="85"/>
       <c r="AN66" s="85"/>
       <c r="AO66" s="154" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="67" spans="1:41" ht="61.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -7451,10 +7451,10 @@
         <v>5</v>
       </c>
       <c r="B67" s="69" t="s">
+        <v>134</v>
+      </c>
+      <c r="C67" s="114" t="s">
         <v>135</v>
-      </c>
-      <c r="C67" s="114" t="s">
-        <v>136</v>
       </c>
       <c r="D67" s="118"/>
       <c r="E67" s="118"/>
@@ -7490,7 +7490,7 @@
       <c r="X67" s="76">
         <v>100</v>
       </c>
-      <c r="Y67" s="190"/>
+      <c r="Y67" s="161"/>
       <c r="Z67" s="121">
         <f>SUM(X67:Y67)</f>
         <v>100</v>
@@ -7529,7 +7529,7 @@
       <c r="AM67" s="118"/>
       <c r="AN67" s="118"/>
       <c r="AO67" s="116" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="68" spans="1:41" ht="135.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7537,10 +7537,10 @@
         <v>6</v>
       </c>
       <c r="B68" s="69" t="s">
+        <v>136</v>
+      </c>
+      <c r="C68" s="123" t="s">
         <v>137</v>
-      </c>
-      <c r="C68" s="123" t="s">
-        <v>138</v>
       </c>
       <c r="D68" s="118"/>
       <c r="E68" s="118"/>
@@ -7576,7 +7576,7 @@
       <c r="X68" s="76">
         <v>100</v>
       </c>
-      <c r="Y68" s="191"/>
+      <c r="Y68" s="162"/>
       <c r="Z68" s="128">
         <f>SUM(X68:Y68)</f>
         <v>100</v>
@@ -7609,7 +7609,7 @@
       <c r="AM68" s="118"/>
       <c r="AN68" s="118"/>
       <c r="AO68" s="155" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="69" spans="1:41" s="109" customFormat="1" ht="76.349999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -7617,10 +7617,10 @@
         <v>7</v>
       </c>
       <c r="B69" s="132" t="s">
+        <v>138</v>
+      </c>
+      <c r="C69" s="114" t="s">
         <v>139</v>
-      </c>
-      <c r="C69" s="114" t="s">
-        <v>140</v>
       </c>
       <c r="D69" s="133"/>
       <c r="E69" s="133"/>
@@ -7656,7 +7656,7 @@
       <c r="X69" s="76">
         <v>100</v>
       </c>
-      <c r="Y69" s="190"/>
+      <c r="Y69" s="161"/>
       <c r="Z69" s="121">
         <f>SUM(X69:Y69)</f>
         <v>100</v>
@@ -7689,7 +7689,7 @@
       <c r="AM69" s="133"/>
       <c r="AN69" s="133"/>
       <c r="AO69" s="155" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="70" spans="1:41" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -7697,10 +7697,10 @@
         <v>8</v>
       </c>
       <c r="B70" s="132" t="s">
+        <v>140</v>
+      </c>
+      <c r="C70" s="114" t="s">
         <v>141</v>
-      </c>
-      <c r="C70" s="114" t="s">
-        <v>142</v>
       </c>
       <c r="D70" s="118"/>
       <c r="E70" s="118"/>
@@ -7736,7 +7736,7 @@
       <c r="X70" s="76">
         <v>100</v>
       </c>
-      <c r="Y70" s="192"/>
+      <c r="Y70" s="163"/>
       <c r="Z70" s="121">
         <f>SUM(X70:Y70)</f>
         <v>100</v>
@@ -7769,7 +7769,7 @@
       <c r="AM70" s="118"/>
       <c r="AN70" s="118"/>
       <c r="AO70" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="71" spans="1:41" s="149" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -7777,10 +7777,10 @@
         <v>9</v>
       </c>
       <c r="B71" s="140" t="s">
+        <v>142</v>
+      </c>
+      <c r="C71" s="141" t="s">
         <v>143</v>
-      </c>
-      <c r="C71" s="141" t="s">
-        <v>144</v>
       </c>
       <c r="D71" s="142"/>
       <c r="E71" s="142"/>
@@ -7810,7 +7810,7 @@
         <v>600</v>
       </c>
       <c r="X71" s="146"/>
-      <c r="Y71" s="192"/>
+      <c r="Y71" s="163"/>
       <c r="Z71" s="147"/>
       <c r="AA71" s="148"/>
       <c r="AB71" s="78"/>
@@ -7833,7 +7833,7 @@
       <c r="AM71" s="142"/>
       <c r="AN71" s="142"/>
       <c r="AO71" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:41" s="149" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -7841,10 +7841,10 @@
         <v>10</v>
       </c>
       <c r="B72" s="140" t="s">
+        <v>144</v>
+      </c>
+      <c r="C72" s="141" t="s">
         <v>145</v>
-      </c>
-      <c r="C72" s="141" t="s">
-        <v>146</v>
       </c>
       <c r="D72" s="142"/>
       <c r="E72" s="142"/>
@@ -7874,7 +7874,7 @@
         <v>800</v>
       </c>
       <c r="X72" s="146"/>
-      <c r="Y72" s="192"/>
+      <c r="Y72" s="163"/>
       <c r="Z72" s="147"/>
       <c r="AA72" s="148"/>
       <c r="AB72" s="78"/>
@@ -7897,7 +7897,7 @@
       <c r="AM72" s="142"/>
       <c r="AN72" s="142"/>
       <c r="AO72" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:41" s="149" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -7905,10 +7905,10 @@
         <v>11</v>
       </c>
       <c r="B73" s="140" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C73" s="141" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D73" s="142"/>
       <c r="E73" s="142"/>
@@ -7938,7 +7938,7 @@
         <v>1000</v>
       </c>
       <c r="X73" s="146"/>
-      <c r="Y73" s="192"/>
+      <c r="Y73" s="163"/>
       <c r="Z73" s="147"/>
       <c r="AA73" s="148"/>
       <c r="AB73" s="78"/>
@@ -7961,7 +7961,7 @@
       <c r="AM73" s="142"/>
       <c r="AN73" s="142"/>
       <c r="AO73" s="156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74" spans="1:41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="X74" s="139"/>
-      <c r="Y74" s="192"/>
+      <c r="Y74" s="163"/>
       <c r="Z74" s="139"/>
       <c r="AA74" s="118"/>
       <c r="AB74" s="118"/>
@@ -8921,28 +8921,6 @@
     <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="AO7:AO9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AS7:AS9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AE8"/>
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A2:AB2"/>
@@ -8959,6 +8937,28 @@
     <mergeCell ref="H7:H9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:J9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AE8"/>
+    <mergeCell ref="AO7:AO9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AS7:AS9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AL7:AL9"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId1"/>

--- a/report/bao-cao.xlsx
+++ b/report/bao-cao.xlsx
@@ -1432,54 +1432,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1504,6 +1456,54 @@
     <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1879,36 +1879,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="186" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="187"/>
-      <c r="C1" s="187"/>
-      <c r="D1" s="187"/>
-      <c r="E1" s="187"/>
-      <c r="F1" s="187"/>
-      <c r="G1" s="187"/>
-      <c r="H1" s="187"/>
-      <c r="I1" s="187"/>
-      <c r="J1" s="187"/>
-      <c r="K1" s="187"/>
-      <c r="L1" s="187"/>
-      <c r="M1" s="187"/>
-      <c r="N1" s="187"/>
-      <c r="O1" s="187"/>
-      <c r="P1" s="187"/>
-      <c r="Q1" s="187"/>
-      <c r="R1" s="187"/>
-      <c r="S1" s="187"/>
-      <c r="T1" s="187"/>
-      <c r="U1" s="187"/>
-      <c r="V1" s="187"/>
-      <c r="W1" s="187"/>
-      <c r="X1" s="187"/>
-      <c r="Y1" s="188"/>
-      <c r="Z1" s="187"/>
-      <c r="AA1" s="187"/>
-      <c r="AB1" s="187"/>
+      <c r="A1" s="168" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="169"/>
+      <c r="H1" s="169"/>
+      <c r="I1" s="169"/>
+      <c r="J1" s="169"/>
+      <c r="K1" s="169"/>
+      <c r="L1" s="169"/>
+      <c r="M1" s="169"/>
+      <c r="N1" s="169"/>
+      <c r="O1" s="169"/>
+      <c r="P1" s="169"/>
+      <c r="Q1" s="169"/>
+      <c r="R1" s="169"/>
+      <c r="S1" s="169"/>
+      <c r="T1" s="169"/>
+      <c r="U1" s="169"/>
+      <c r="V1" s="169"/>
+      <c r="W1" s="169"/>
+      <c r="X1" s="169"/>
+      <c r="Y1" s="170"/>
+      <c r="Z1" s="169"/>
+      <c r="AA1" s="169"/>
+      <c r="AB1" s="169"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
@@ -1928,36 +1928,36 @@
       </c>
     </row>
     <row r="2" spans="1:45" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="189" t="s">
+      <c r="A2" s="171" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="187"/>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="187"/>
-      <c r="I2" s="187"/>
-      <c r="J2" s="187"/>
-      <c r="K2" s="187"/>
-      <c r="L2" s="187"/>
-      <c r="M2" s="187"/>
-      <c r="N2" s="187"/>
-      <c r="O2" s="187"/>
-      <c r="P2" s="187"/>
-      <c r="Q2" s="187"/>
-      <c r="R2" s="187"/>
-      <c r="S2" s="187"/>
-      <c r="T2" s="187"/>
-      <c r="U2" s="187"/>
-      <c r="V2" s="187"/>
-      <c r="W2" s="187"/>
-      <c r="X2" s="187"/>
-      <c r="Y2" s="188"/>
-      <c r="Z2" s="187"/>
-      <c r="AA2" s="187"/>
-      <c r="AB2" s="187"/>
+      <c r="B2" s="169"/>
+      <c r="C2" s="169"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="169"/>
+      <c r="H2" s="169"/>
+      <c r="I2" s="169"/>
+      <c r="J2" s="169"/>
+      <c r="K2" s="169"/>
+      <c r="L2" s="169"/>
+      <c r="M2" s="169"/>
+      <c r="N2" s="169"/>
+      <c r="O2" s="169"/>
+      <c r="P2" s="169"/>
+      <c r="Q2" s="169"/>
+      <c r="R2" s="169"/>
+      <c r="S2" s="169"/>
+      <c r="T2" s="169"/>
+      <c r="U2" s="169"/>
+      <c r="V2" s="169"/>
+      <c r="W2" s="169"/>
+      <c r="X2" s="169"/>
+      <c r="Y2" s="170"/>
+      <c r="Z2" s="169"/>
+      <c r="AA2" s="169"/>
+      <c r="AB2" s="169"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
       <c r="AE2" s="1"/>
@@ -2016,94 +2016,94 @@
       <c r="AO3" s="5"/>
     </row>
     <row r="4" spans="1:45" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="190" t="s">
+      <c r="A4" s="172" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="187"/>
-      <c r="C4" s="187"/>
-      <c r="D4" s="187"/>
-      <c r="E4" s="187"/>
-      <c r="F4" s="187"/>
-      <c r="G4" s="187"/>
-      <c r="H4" s="187"/>
-      <c r="I4" s="187"/>
-      <c r="J4" s="187"/>
-      <c r="K4" s="187"/>
-      <c r="L4" s="187"/>
-      <c r="M4" s="187"/>
-      <c r="N4" s="187"/>
-      <c r="O4" s="187"/>
-      <c r="P4" s="187"/>
-      <c r="Q4" s="187"/>
-      <c r="R4" s="187"/>
-      <c r="S4" s="187"/>
-      <c r="T4" s="187"/>
-      <c r="U4" s="187"/>
-      <c r="V4" s="187"/>
-      <c r="W4" s="187"/>
-      <c r="X4" s="187"/>
-      <c r="Y4" s="188"/>
-      <c r="Z4" s="187"/>
-      <c r="AA4" s="187"/>
-      <c r="AB4" s="187"/>
-      <c r="AC4" s="187"/>
-      <c r="AD4" s="187"/>
-      <c r="AE4" s="187"/>
-      <c r="AF4" s="187"/>
-      <c r="AG4" s="187"/>
-      <c r="AH4" s="187"/>
-      <c r="AI4" s="187"/>
-      <c r="AJ4" s="187"/>
-      <c r="AK4" s="187"/>
-      <c r="AL4" s="187"/>
-      <c r="AM4" s="187"/>
-      <c r="AN4" s="187"/>
-      <c r="AO4" s="187"/>
+      <c r="B4" s="169"/>
+      <c r="C4" s="169"/>
+      <c r="D4" s="169"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="169"/>
+      <c r="G4" s="169"/>
+      <c r="H4" s="169"/>
+      <c r="I4" s="169"/>
+      <c r="J4" s="169"/>
+      <c r="K4" s="169"/>
+      <c r="L4" s="169"/>
+      <c r="M4" s="169"/>
+      <c r="N4" s="169"/>
+      <c r="O4" s="169"/>
+      <c r="P4" s="169"/>
+      <c r="Q4" s="169"/>
+      <c r="R4" s="169"/>
+      <c r="S4" s="169"/>
+      <c r="T4" s="169"/>
+      <c r="U4" s="169"/>
+      <c r="V4" s="169"/>
+      <c r="W4" s="169"/>
+      <c r="X4" s="169"/>
+      <c r="Y4" s="170"/>
+      <c r="Z4" s="169"/>
+      <c r="AA4" s="169"/>
+      <c r="AB4" s="169"/>
+      <c r="AC4" s="169"/>
+      <c r="AD4" s="169"/>
+      <c r="AE4" s="169"/>
+      <c r="AF4" s="169"/>
+      <c r="AG4" s="169"/>
+      <c r="AH4" s="169"/>
+      <c r="AI4" s="169"/>
+      <c r="AJ4" s="169"/>
+      <c r="AK4" s="169"/>
+      <c r="AL4" s="169"/>
+      <c r="AM4" s="169"/>
+      <c r="AN4" s="169"/>
+      <c r="AO4" s="169"/>
     </row>
     <row r="5" spans="1:45" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="191" t="s">
+      <c r="A5" s="173" t="s">
         <v>155</v>
       </c>
-      <c r="B5" s="187"/>
-      <c r="C5" s="187"/>
-      <c r="D5" s="187"/>
-      <c r="E5" s="187"/>
-      <c r="F5" s="187"/>
-      <c r="G5" s="187"/>
-      <c r="H5" s="187"/>
-      <c r="I5" s="187"/>
-      <c r="J5" s="187"/>
-      <c r="K5" s="187"/>
-      <c r="L5" s="187"/>
-      <c r="M5" s="187"/>
-      <c r="N5" s="187"/>
-      <c r="O5" s="187"/>
-      <c r="P5" s="187"/>
-      <c r="Q5" s="187"/>
-      <c r="R5" s="187"/>
-      <c r="S5" s="187"/>
-      <c r="T5" s="187"/>
-      <c r="U5" s="187"/>
-      <c r="V5" s="187"/>
-      <c r="W5" s="187"/>
-      <c r="X5" s="187"/>
-      <c r="Y5" s="188"/>
-      <c r="Z5" s="187"/>
-      <c r="AA5" s="187"/>
-      <c r="AB5" s="187"/>
-      <c r="AC5" s="187"/>
-      <c r="AD5" s="187"/>
-      <c r="AE5" s="187"/>
-      <c r="AF5" s="187"/>
-      <c r="AG5" s="187"/>
-      <c r="AH5" s="187"/>
-      <c r="AI5" s="187"/>
-      <c r="AJ5" s="187"/>
-      <c r="AK5" s="187"/>
-      <c r="AL5" s="187"/>
-      <c r="AM5" s="187"/>
-      <c r="AN5" s="187"/>
-      <c r="AO5" s="187"/>
+      <c r="B5" s="169"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="169"/>
+      <c r="E5" s="169"/>
+      <c r="F5" s="169"/>
+      <c r="G5" s="169"/>
+      <c r="H5" s="169"/>
+      <c r="I5" s="169"/>
+      <c r="J5" s="169"/>
+      <c r="K5" s="169"/>
+      <c r="L5" s="169"/>
+      <c r="M5" s="169"/>
+      <c r="N5" s="169"/>
+      <c r="O5" s="169"/>
+      <c r="P5" s="169"/>
+      <c r="Q5" s="169"/>
+      <c r="R5" s="169"/>
+      <c r="S5" s="169"/>
+      <c r="T5" s="169"/>
+      <c r="U5" s="169"/>
+      <c r="V5" s="169"/>
+      <c r="W5" s="169"/>
+      <c r="X5" s="169"/>
+      <c r="Y5" s="170"/>
+      <c r="Z5" s="169"/>
+      <c r="AA5" s="169"/>
+      <c r="AB5" s="169"/>
+      <c r="AC5" s="169"/>
+      <c r="AD5" s="169"/>
+      <c r="AE5" s="169"/>
+      <c r="AF5" s="169"/>
+      <c r="AG5" s="169"/>
+      <c r="AH5" s="169"/>
+      <c r="AI5" s="169"/>
+      <c r="AJ5" s="169"/>
+      <c r="AK5" s="169"/>
+      <c r="AL5" s="169"/>
+      <c r="AM5" s="169"/>
+      <c r="AN5" s="169"/>
+      <c r="AO5" s="169"/>
     </row>
     <row r="6" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16"/>
@@ -2139,18 +2139,18 @@
       <c r="AC6" s="16"/>
       <c r="AD6" s="16"/>
       <c r="AE6" s="16"/>
-      <c r="AF6" s="192" t="s">
+      <c r="AF6" s="174" t="s">
         <v>5</v>
       </c>
-      <c r="AG6" s="193"/>
-      <c r="AH6" s="193"/>
-      <c r="AI6" s="193"/>
-      <c r="AJ6" s="193"/>
-      <c r="AK6" s="193"/>
-      <c r="AL6" s="193"/>
-      <c r="AM6" s="193"/>
-      <c r="AN6" s="193"/>
-      <c r="AO6" s="193"/>
+      <c r="AG6" s="175"/>
+      <c r="AH6" s="175"/>
+      <c r="AI6" s="175"/>
+      <c r="AJ6" s="175"/>
+      <c r="AK6" s="175"/>
+      <c r="AL6" s="175"/>
+      <c r="AM6" s="175"/>
+      <c r="AN6" s="175"/>
+      <c r="AO6" s="175"/>
     </row>
     <row r="7" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="166" t="s">
@@ -2159,7 +2159,7 @@
       <c r="B7" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="195" t="s">
+      <c r="C7" s="177" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="166" t="s">
@@ -2186,7 +2186,7 @@
       <c r="K7" s="166" t="s">
         <v>16</v>
       </c>
-      <c r="L7" s="172" t="s">
+      <c r="L7" s="179" t="s">
         <v>17</v>
       </c>
       <c r="M7" s="166" t="s">
@@ -2195,26 +2195,26 @@
       <c r="N7" s="166" t="s">
         <v>19</v>
       </c>
-      <c r="O7" s="174" t="s">
+      <c r="O7" s="181" t="s">
         <v>20</v>
       </c>
-      <c r="P7" s="175"/>
-      <c r="Q7" s="175"/>
-      <c r="R7" s="175"/>
-      <c r="S7" s="175"/>
-      <c r="T7" s="175"/>
-      <c r="U7" s="175"/>
-      <c r="V7" s="176"/>
+      <c r="P7" s="182"/>
+      <c r="Q7" s="182"/>
+      <c r="R7" s="182"/>
+      <c r="S7" s="182"/>
+      <c r="T7" s="182"/>
+      <c r="U7" s="182"/>
+      <c r="V7" s="183"/>
       <c r="W7" s="166" t="s">
         <v>21</v>
       </c>
-      <c r="X7" s="183" t="s">
+      <c r="X7" s="190" t="s">
         <v>22</v>
       </c>
-      <c r="Y7" s="183" t="s">
+      <c r="Y7" s="190" t="s">
         <v>23</v>
       </c>
-      <c r="Z7" s="184" t="s">
+      <c r="Z7" s="191" t="s">
         <v>24</v>
       </c>
       <c r="AA7" s="166" t="s">
@@ -2223,30 +2223,30 @@
       <c r="AB7" s="166" t="s">
         <v>26</v>
       </c>
-      <c r="AC7" s="185" t="s">
+      <c r="AC7" s="192" t="s">
         <v>27</v>
       </c>
-      <c r="AD7" s="185"/>
-      <c r="AE7" s="185"/>
-      <c r="AF7" s="171" t="s">
+      <c r="AD7" s="192"/>
+      <c r="AE7" s="192"/>
+      <c r="AF7" s="178" t="s">
         <v>28</v>
       </c>
-      <c r="AG7" s="168" t="s">
+      <c r="AG7" s="193" t="s">
         <v>29</v>
       </c>
-      <c r="AH7" s="168" t="s">
+      <c r="AH7" s="193" t="s">
         <v>30</v>
       </c>
-      <c r="AI7" s="168" t="s">
+      <c r="AI7" s="193" t="s">
         <v>31</v>
       </c>
-      <c r="AJ7" s="168" t="s">
+      <c r="AJ7" s="193" t="s">
         <v>32</v>
       </c>
-      <c r="AK7" s="171" t="s">
+      <c r="AK7" s="178" t="s">
         <v>33</v>
       </c>
-      <c r="AL7" s="171" t="s">
+      <c r="AL7" s="178" t="s">
         <v>34</v>
       </c>
       <c r="AM7" s="166" t="s">
@@ -2258,14 +2258,14 @@
       <c r="AO7" s="166" t="s">
         <v>154</v>
       </c>
-      <c r="AS7" s="168" t="s">
+      <c r="AS7" s="193" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="167"/>
-      <c r="B8" s="194"/>
-      <c r="C8" s="195"/>
+      <c r="B8" s="176"/>
+      <c r="C8" s="177"/>
       <c r="D8" s="167"/>
       <c r="E8" s="167"/>
       <c r="F8" s="167"/>
@@ -2276,40 +2276,40 @@
       <c r="K8" s="167"/>
       <c r="L8" s="167"/>
       <c r="M8" s="167"/>
-      <c r="N8" s="173"/>
-      <c r="O8" s="177"/>
-      <c r="P8" s="178"/>
-      <c r="Q8" s="178"/>
-      <c r="R8" s="178"/>
-      <c r="S8" s="178"/>
-      <c r="T8" s="178"/>
-      <c r="U8" s="178"/>
-      <c r="V8" s="179"/>
+      <c r="N8" s="180"/>
+      <c r="O8" s="184"/>
+      <c r="P8" s="185"/>
+      <c r="Q8" s="185"/>
+      <c r="R8" s="185"/>
+      <c r="S8" s="185"/>
+      <c r="T8" s="185"/>
+      <c r="U8" s="185"/>
+      <c r="V8" s="186"/>
       <c r="W8" s="167"/>
       <c r="X8" s="167"/>
       <c r="Y8" s="167"/>
       <c r="Z8" s="167"/>
       <c r="AA8" s="167"/>
       <c r="AB8" s="167"/>
-      <c r="AC8" s="185"/>
-      <c r="AD8" s="185"/>
-      <c r="AE8" s="185"/>
+      <c r="AC8" s="192"/>
+      <c r="AD8" s="192"/>
+      <c r="AE8" s="192"/>
       <c r="AF8" s="167"/>
-      <c r="AG8" s="170"/>
-      <c r="AH8" s="170"/>
-      <c r="AI8" s="168"/>
-      <c r="AJ8" s="170"/>
+      <c r="AG8" s="195"/>
+      <c r="AH8" s="195"/>
+      <c r="AI8" s="193"/>
+      <c r="AJ8" s="195"/>
       <c r="AK8" s="167"/>
-      <c r="AL8" s="171"/>
+      <c r="AL8" s="178"/>
       <c r="AM8" s="167"/>
       <c r="AN8" s="166"/>
       <c r="AO8" s="166"/>
-      <c r="AS8" s="169"/>
+      <c r="AS8" s="194"/>
     </row>
     <row r="9" spans="1:45" ht="104.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="167"/>
-      <c r="B9" s="194"/>
-      <c r="C9" s="195"/>
+      <c r="B9" s="176"/>
+      <c r="C9" s="177"/>
       <c r="D9" s="167"/>
       <c r="E9" s="167"/>
       <c r="F9" s="167"/>
@@ -2320,15 +2320,15 @@
       <c r="K9" s="167"/>
       <c r="L9" s="167"/>
       <c r="M9" s="167"/>
-      <c r="N9" s="173"/>
-      <c r="O9" s="180"/>
-      <c r="P9" s="181"/>
-      <c r="Q9" s="181"/>
-      <c r="R9" s="181"/>
-      <c r="S9" s="181"/>
-      <c r="T9" s="181"/>
-      <c r="U9" s="181"/>
-      <c r="V9" s="182"/>
+      <c r="N9" s="180"/>
+      <c r="O9" s="187"/>
+      <c r="P9" s="188"/>
+      <c r="Q9" s="188"/>
+      <c r="R9" s="188"/>
+      <c r="S9" s="188"/>
+      <c r="T9" s="188"/>
+      <c r="U9" s="188"/>
+      <c r="V9" s="189"/>
       <c r="W9" s="167"/>
       <c r="X9" s="167"/>
       <c r="Y9" s="167"/>
@@ -2345,12 +2345,12 @@
         <v>40</v>
       </c>
       <c r="AF9" s="167"/>
-      <c r="AG9" s="170"/>
-      <c r="AH9" s="170"/>
-      <c r="AI9" s="168"/>
-      <c r="AJ9" s="170"/>
+      <c r="AG9" s="195"/>
+      <c r="AH9" s="195"/>
+      <c r="AI9" s="193"/>
+      <c r="AJ9" s="195"/>
       <c r="AK9" s="167"/>
-      <c r="AL9" s="171"/>
+      <c r="AL9" s="178"/>
       <c r="AM9" s="167"/>
       <c r="AN9" s="166"/>
       <c r="AO9" s="166"/>
@@ -2361,7 +2361,7 @@
       <c r="AR9">
         <v>27</v>
       </c>
-      <c r="AS9" s="169"/>
+      <c r="AS9" s="194"/>
     </row>
     <row r="10" spans="1:45" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="27">
@@ -8921,6 +8921,28 @@
     <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="AO7:AO9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AS7:AS9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AE8"/>
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A2:AB2"/>
@@ -8937,28 +8959,6 @@
     <mergeCell ref="H7:H9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:J9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AE8"/>
-    <mergeCell ref="AO7:AO9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AS7:AS9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AL7:AL9"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId1"/>

--- a/report/bao-cao.xlsx
+++ b/report/bao-cao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HXuan\BaocaoGiaingan\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B95CFE-643B-4345-BC04-6DD2274A5818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A48B8B6-9A71-4FA7-81E5-C85FB2BFF850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="0" windowWidth="12570" windowHeight="12900" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="0" windowWidth="15900" windowHeight="12900" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="bc" sheetId="1" state="hidden" r:id="rId1"/>
@@ -1649,7 +1649,7 @@
     <xf numFmtId="164" fontId="60" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="60" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="347">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2335,9 +2335,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="73" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2448,49 +2445,21 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="54" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="63" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="77" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2506,10 +2475,12 @@
     <xf numFmtId="0" fontId="59" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2537,24 +2508,50 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="63" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2818,36 +2815,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="340" t="s">
+      <c r="A1" s="341" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="320"/>
-      <c r="C1" s="321"/>
-      <c r="D1" s="320"/>
-      <c r="E1" s="320"/>
-      <c r="F1" s="320"/>
-      <c r="G1" s="320"/>
-      <c r="H1" s="320"/>
-      <c r="I1" s="320"/>
-      <c r="J1" s="320"/>
-      <c r="K1" s="320"/>
-      <c r="L1" s="320"/>
-      <c r="M1" s="320"/>
-      <c r="N1" s="320"/>
-      <c r="O1" s="320"/>
-      <c r="P1" s="320"/>
-      <c r="Q1" s="320"/>
-      <c r="R1" s="320"/>
-      <c r="S1" s="320"/>
-      <c r="T1" s="320"/>
-      <c r="U1" s="320"/>
-      <c r="V1" s="320"/>
-      <c r="W1" s="320"/>
-      <c r="X1" s="320"/>
-      <c r="Y1" s="320"/>
-      <c r="Z1" s="320"/>
-      <c r="AA1" s="320"/>
-      <c r="AB1" s="322"/>
+      <c r="B1" s="311"/>
+      <c r="C1" s="312"/>
+      <c r="D1" s="311"/>
+      <c r="E1" s="311"/>
+      <c r="F1" s="311"/>
+      <c r="G1" s="311"/>
+      <c r="H1" s="311"/>
+      <c r="I1" s="311"/>
+      <c r="J1" s="311"/>
+      <c r="K1" s="311"/>
+      <c r="L1" s="311"/>
+      <c r="M1" s="311"/>
+      <c r="N1" s="311"/>
+      <c r="O1" s="311"/>
+      <c r="P1" s="311"/>
+      <c r="Q1" s="311"/>
+      <c r="R1" s="311"/>
+      <c r="S1" s="311"/>
+      <c r="T1" s="311"/>
+      <c r="U1" s="311"/>
+      <c r="V1" s="311"/>
+      <c r="W1" s="311"/>
+      <c r="X1" s="311"/>
+      <c r="Y1" s="311"/>
+      <c r="Z1" s="311"/>
+      <c r="AA1" s="311"/>
+      <c r="AB1" s="313"/>
       <c r="AC1" s="17"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="2"/>
@@ -2863,36 +2860,36 @@
       <c r="AM1" s="3"/>
     </row>
     <row r="2" spans="1:42" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="323" t="s">
+      <c r="A2" s="314" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="320"/>
-      <c r="C2" s="321"/>
-      <c r="D2" s="320"/>
-      <c r="E2" s="320"/>
-      <c r="F2" s="320"/>
-      <c r="G2" s="320"/>
-      <c r="H2" s="320"/>
-      <c r="I2" s="320"/>
-      <c r="J2" s="320"/>
-      <c r="K2" s="320"/>
-      <c r="L2" s="320"/>
-      <c r="M2" s="320"/>
-      <c r="N2" s="320"/>
-      <c r="O2" s="320"/>
-      <c r="P2" s="320"/>
-      <c r="Q2" s="320"/>
-      <c r="R2" s="320"/>
-      <c r="S2" s="320"/>
-      <c r="T2" s="320"/>
-      <c r="U2" s="320"/>
-      <c r="V2" s="320"/>
-      <c r="W2" s="320"/>
-      <c r="X2" s="320"/>
-      <c r="Y2" s="320"/>
-      <c r="Z2" s="320"/>
-      <c r="AA2" s="320"/>
-      <c r="AB2" s="322"/>
+      <c r="B2" s="311"/>
+      <c r="C2" s="312"/>
+      <c r="D2" s="311"/>
+      <c r="E2" s="311"/>
+      <c r="F2" s="311"/>
+      <c r="G2" s="311"/>
+      <c r="H2" s="311"/>
+      <c r="I2" s="311"/>
+      <c r="J2" s="311"/>
+      <c r="K2" s="311"/>
+      <c r="L2" s="311"/>
+      <c r="M2" s="311"/>
+      <c r="N2" s="311"/>
+      <c r="O2" s="311"/>
+      <c r="P2" s="311"/>
+      <c r="Q2" s="311"/>
+      <c r="R2" s="311"/>
+      <c r="S2" s="311"/>
+      <c r="T2" s="311"/>
+      <c r="U2" s="311"/>
+      <c r="V2" s="311"/>
+      <c r="W2" s="311"/>
+      <c r="X2" s="311"/>
+      <c r="Y2" s="311"/>
+      <c r="Z2" s="311"/>
+      <c r="AA2" s="311"/>
+      <c r="AB2" s="313"/>
       <c r="AC2" s="17"/>
       <c r="AD2" s="1"/>
       <c r="AE2" s="2"/>
@@ -2947,90 +2944,90 @@
       <c r="AM3" s="3"/>
     </row>
     <row r="4" spans="1:42" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="324" t="s">
+      <c r="A4" s="315" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="320"/>
-      <c r="C4" s="321"/>
-      <c r="D4" s="320"/>
-      <c r="E4" s="320"/>
-      <c r="F4" s="320"/>
-      <c r="G4" s="320"/>
-      <c r="H4" s="320"/>
-      <c r="I4" s="320"/>
-      <c r="J4" s="320"/>
-      <c r="K4" s="320"/>
-      <c r="L4" s="320"/>
-      <c r="M4" s="320"/>
-      <c r="N4" s="320"/>
-      <c r="O4" s="320"/>
-      <c r="P4" s="320"/>
-      <c r="Q4" s="320"/>
-      <c r="R4" s="320"/>
-      <c r="S4" s="320"/>
-      <c r="T4" s="320"/>
-      <c r="U4" s="320"/>
-      <c r="V4" s="320"/>
-      <c r="W4" s="320"/>
-      <c r="X4" s="320"/>
-      <c r="Y4" s="320"/>
-      <c r="Z4" s="320"/>
-      <c r="AA4" s="320"/>
-      <c r="AB4" s="320"/>
-      <c r="AC4" s="321"/>
-      <c r="AD4" s="320"/>
-      <c r="AE4" s="320"/>
-      <c r="AF4" s="321"/>
-      <c r="AG4" s="321"/>
-      <c r="AH4" s="320"/>
-      <c r="AI4" s="321"/>
-      <c r="AJ4" s="321"/>
-      <c r="AK4" s="320"/>
-      <c r="AL4" s="321"/>
-      <c r="AM4" s="322"/>
+      <c r="B4" s="311"/>
+      <c r="C4" s="312"/>
+      <c r="D4" s="311"/>
+      <c r="E4" s="311"/>
+      <c r="F4" s="311"/>
+      <c r="G4" s="311"/>
+      <c r="H4" s="311"/>
+      <c r="I4" s="311"/>
+      <c r="J4" s="311"/>
+      <c r="K4" s="311"/>
+      <c r="L4" s="311"/>
+      <c r="M4" s="311"/>
+      <c r="N4" s="311"/>
+      <c r="O4" s="311"/>
+      <c r="P4" s="311"/>
+      <c r="Q4" s="311"/>
+      <c r="R4" s="311"/>
+      <c r="S4" s="311"/>
+      <c r="T4" s="311"/>
+      <c r="U4" s="311"/>
+      <c r="V4" s="311"/>
+      <c r="W4" s="311"/>
+      <c r="X4" s="311"/>
+      <c r="Y4" s="311"/>
+      <c r="Z4" s="311"/>
+      <c r="AA4" s="311"/>
+      <c r="AB4" s="311"/>
+      <c r="AC4" s="312"/>
+      <c r="AD4" s="311"/>
+      <c r="AE4" s="311"/>
+      <c r="AF4" s="312"/>
+      <c r="AG4" s="312"/>
+      <c r="AH4" s="311"/>
+      <c r="AI4" s="312"/>
+      <c r="AJ4" s="312"/>
+      <c r="AK4" s="311"/>
+      <c r="AL4" s="312"/>
+      <c r="AM4" s="313"/>
     </row>
     <row r="5" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="325" t="s">
+      <c r="A5" s="316" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="320"/>
-      <c r="C5" s="321"/>
-      <c r="D5" s="320"/>
-      <c r="E5" s="320"/>
-      <c r="F5" s="320"/>
-      <c r="G5" s="320"/>
-      <c r="H5" s="320"/>
-      <c r="I5" s="320"/>
-      <c r="J5" s="320"/>
-      <c r="K5" s="320"/>
-      <c r="L5" s="320"/>
-      <c r="M5" s="320"/>
-      <c r="N5" s="320"/>
-      <c r="O5" s="320"/>
-      <c r="P5" s="320"/>
-      <c r="Q5" s="320"/>
-      <c r="R5" s="320"/>
-      <c r="S5" s="320"/>
-      <c r="T5" s="320"/>
-      <c r="U5" s="320"/>
-      <c r="V5" s="320"/>
-      <c r="W5" s="320"/>
-      <c r="X5" s="320"/>
-      <c r="Y5" s="320"/>
-      <c r="Z5" s="320"/>
-      <c r="AA5" s="320"/>
-      <c r="AB5" s="320"/>
-      <c r="AC5" s="321"/>
-      <c r="AD5" s="320"/>
-      <c r="AE5" s="320"/>
-      <c r="AF5" s="321"/>
-      <c r="AG5" s="321"/>
-      <c r="AH5" s="320"/>
-      <c r="AI5" s="321"/>
-      <c r="AJ5" s="321"/>
-      <c r="AK5" s="320"/>
-      <c r="AL5" s="321"/>
-      <c r="AM5" s="322"/>
+      <c r="B5" s="311"/>
+      <c r="C5" s="312"/>
+      <c r="D5" s="311"/>
+      <c r="E5" s="311"/>
+      <c r="F5" s="311"/>
+      <c r="G5" s="311"/>
+      <c r="H5" s="311"/>
+      <c r="I5" s="311"/>
+      <c r="J5" s="311"/>
+      <c r="K5" s="311"/>
+      <c r="L5" s="311"/>
+      <c r="M5" s="311"/>
+      <c r="N5" s="311"/>
+      <c r="O5" s="311"/>
+      <c r="P5" s="311"/>
+      <c r="Q5" s="311"/>
+      <c r="R5" s="311"/>
+      <c r="S5" s="311"/>
+      <c r="T5" s="311"/>
+      <c r="U5" s="311"/>
+      <c r="V5" s="311"/>
+      <c r="W5" s="311"/>
+      <c r="X5" s="311"/>
+      <c r="Y5" s="311"/>
+      <c r="Z5" s="311"/>
+      <c r="AA5" s="311"/>
+      <c r="AB5" s="311"/>
+      <c r="AC5" s="312"/>
+      <c r="AD5" s="311"/>
+      <c r="AE5" s="311"/>
+      <c r="AF5" s="312"/>
+      <c r="AG5" s="312"/>
+      <c r="AH5" s="311"/>
+      <c r="AI5" s="312"/>
+      <c r="AJ5" s="312"/>
+      <c r="AK5" s="311"/>
+      <c r="AL5" s="312"/>
+      <c r="AM5" s="313"/>
     </row>
     <row r="6" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -3065,202 +3062,202 @@
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
       <c r="AD6" s="342"/>
-      <c r="AE6" s="321"/>
-      <c r="AF6" s="321"/>
-      <c r="AG6" s="321"/>
-      <c r="AH6" s="321"/>
-      <c r="AI6" s="321"/>
-      <c r="AJ6" s="321"/>
-      <c r="AK6" s="321"/>
-      <c r="AL6" s="321"/>
-      <c r="AM6" s="321"/>
+      <c r="AE6" s="312"/>
+      <c r="AF6" s="312"/>
+      <c r="AG6" s="312"/>
+      <c r="AH6" s="312"/>
+      <c r="AI6" s="312"/>
+      <c r="AJ6" s="312"/>
+      <c r="AK6" s="312"/>
+      <c r="AL6" s="312"/>
+      <c r="AM6" s="312"/>
     </row>
     <row r="7" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="305" t="s">
+      <c r="A7" s="303" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="305" t="s">
+      <c r="B7" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="308" t="s">
+      <c r="C7" s="330" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="305" t="s">
+      <c r="D7" s="303" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="305" t="s">
+      <c r="E7" s="303" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="305" t="s">
+      <c r="F7" s="303" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="305" t="s">
+      <c r="G7" s="303" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="305" t="s">
+      <c r="H7" s="303" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="305" t="s">
+      <c r="I7" s="303" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="305" t="s">
+      <c r="J7" s="303" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="305" t="s">
+      <c r="K7" s="303" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="326" t="s">
+      <c r="L7" s="318" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="305" t="s">
+      <c r="M7" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="305" t="s">
+      <c r="N7" s="303" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="328" t="s">
+      <c r="O7" s="319" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="329"/>
-      <c r="Q7" s="329"/>
-      <c r="R7" s="329"/>
-      <c r="S7" s="329"/>
-      <c r="T7" s="329"/>
-      <c r="U7" s="329"/>
-      <c r="V7" s="330"/>
-      <c r="W7" s="305" t="s">
+      <c r="P7" s="320"/>
+      <c r="Q7" s="320"/>
+      <c r="R7" s="320"/>
+      <c r="S7" s="320"/>
+      <c r="T7" s="320"/>
+      <c r="U7" s="320"/>
+      <c r="V7" s="321"/>
+      <c r="W7" s="303" t="s">
         <v>139</v>
       </c>
-      <c r="X7" s="341" t="s">
+      <c r="X7" s="340" t="s">
         <v>13</v>
       </c>
-      <c r="Y7" s="341" t="s">
+      <c r="Y7" s="340" t="s">
         <v>14</v>
       </c>
-      <c r="Z7" s="311" t="s">
+      <c r="Z7" s="308" t="s">
         <v>150</v>
       </c>
-      <c r="AA7" s="305" t="s">
+      <c r="AA7" s="303" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="305" t="s">
+      <c r="AB7" s="303" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="305" t="s">
+      <c r="AC7" s="303" t="s">
         <v>134</v>
       </c>
-      <c r="AD7" s="311" t="s">
+      <c r="AD7" s="308" t="s">
         <v>17</v>
       </c>
-      <c r="AE7" s="337" t="s">
+      <c r="AE7" s="305" t="s">
         <v>107</v>
       </c>
-      <c r="AF7" s="337" t="s">
+      <c r="AF7" s="305" t="s">
         <v>108</v>
       </c>
-      <c r="AG7" s="337" t="s">
+      <c r="AG7" s="305" t="s">
         <v>106</v>
       </c>
-      <c r="AH7" s="339" t="s">
+      <c r="AH7" s="307" t="s">
         <v>147</v>
       </c>
-      <c r="AI7" s="311" t="s">
+      <c r="AI7" s="308" t="s">
         <v>136</v>
       </c>
-      <c r="AJ7" s="311" t="s">
+      <c r="AJ7" s="308" t="s">
         <v>137</v>
       </c>
-      <c r="AK7" s="305" t="s">
+      <c r="AK7" s="303" t="s">
         <v>135</v>
       </c>
-      <c r="AL7" s="305" t="s">
+      <c r="AL7" s="303" t="s">
         <v>146</v>
       </c>
-      <c r="AM7" s="305" t="s">
+      <c r="AM7" s="303" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="306"/>
-      <c r="B8" s="306"/>
-      <c r="C8" s="308"/>
-      <c r="D8" s="306"/>
-      <c r="E8" s="306"/>
-      <c r="F8" s="306"/>
-      <c r="G8" s="306"/>
-      <c r="H8" s="306"/>
-      <c r="I8" s="306"/>
-      <c r="J8" s="306"/>
-      <c r="K8" s="306"/>
-      <c r="L8" s="306"/>
-      <c r="M8" s="306"/>
-      <c r="N8" s="306"/>
-      <c r="O8" s="331"/>
-      <c r="P8" s="332"/>
-      <c r="Q8" s="332"/>
-      <c r="R8" s="332"/>
-      <c r="S8" s="332"/>
-      <c r="T8" s="332"/>
-      <c r="U8" s="332"/>
-      <c r="V8" s="333"/>
-      <c r="W8" s="306"/>
-      <c r="X8" s="306"/>
-      <c r="Y8" s="306"/>
-      <c r="Z8" s="306"/>
-      <c r="AA8" s="306"/>
-      <c r="AB8" s="306"/>
-      <c r="AC8" s="305"/>
-      <c r="AD8" s="306"/>
-      <c r="AE8" s="338"/>
-      <c r="AF8" s="338"/>
-      <c r="AG8" s="339"/>
-      <c r="AH8" s="338"/>
-      <c r="AI8" s="306"/>
-      <c r="AJ8" s="311"/>
-      <c r="AK8" s="306"/>
-      <c r="AL8" s="305"/>
-      <c r="AM8" s="306"/>
+      <c r="A8" s="309"/>
+      <c r="B8" s="309"/>
+      <c r="C8" s="330"/>
+      <c r="D8" s="309"/>
+      <c r="E8" s="309"/>
+      <c r="F8" s="309"/>
+      <c r="G8" s="309"/>
+      <c r="H8" s="309"/>
+      <c r="I8" s="309"/>
+      <c r="J8" s="309"/>
+      <c r="K8" s="309"/>
+      <c r="L8" s="309"/>
+      <c r="M8" s="309"/>
+      <c r="N8" s="309"/>
+      <c r="O8" s="322"/>
+      <c r="P8" s="323"/>
+      <c r="Q8" s="323"/>
+      <c r="R8" s="323"/>
+      <c r="S8" s="323"/>
+      <c r="T8" s="323"/>
+      <c r="U8" s="323"/>
+      <c r="V8" s="324"/>
+      <c r="W8" s="309"/>
+      <c r="X8" s="309"/>
+      <c r="Y8" s="309"/>
+      <c r="Z8" s="309"/>
+      <c r="AA8" s="309"/>
+      <c r="AB8" s="309"/>
+      <c r="AC8" s="303"/>
+      <c r="AD8" s="309"/>
+      <c r="AE8" s="306"/>
+      <c r="AF8" s="306"/>
+      <c r="AG8" s="307"/>
+      <c r="AH8" s="306"/>
+      <c r="AI8" s="309"/>
+      <c r="AJ8" s="308"/>
+      <c r="AK8" s="309"/>
+      <c r="AL8" s="303"/>
+      <c r="AM8" s="309"/>
     </row>
     <row r="9" spans="1:42" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="306"/>
-      <c r="B9" s="306"/>
-      <c r="C9" s="308"/>
-      <c r="D9" s="306"/>
-      <c r="E9" s="306"/>
-      <c r="F9" s="306"/>
-      <c r="G9" s="306"/>
-      <c r="H9" s="306"/>
-      <c r="I9" s="306"/>
-      <c r="J9" s="306"/>
-      <c r="K9" s="306"/>
-      <c r="L9" s="306"/>
-      <c r="M9" s="306"/>
-      <c r="N9" s="306"/>
-      <c r="O9" s="334"/>
-      <c r="P9" s="335"/>
-      <c r="Q9" s="335"/>
-      <c r="R9" s="335"/>
-      <c r="S9" s="335"/>
-      <c r="T9" s="335"/>
-      <c r="U9" s="335"/>
-      <c r="V9" s="336"/>
-      <c r="W9" s="306"/>
-      <c r="X9" s="306"/>
-      <c r="Y9" s="306"/>
-      <c r="Z9" s="306"/>
-      <c r="AA9" s="306"/>
-      <c r="AB9" s="306"/>
-      <c r="AC9" s="305"/>
-      <c r="AD9" s="306"/>
-      <c r="AE9" s="338"/>
-      <c r="AF9" s="338"/>
-      <c r="AG9" s="339"/>
-      <c r="AH9" s="338"/>
-      <c r="AI9" s="306"/>
-      <c r="AJ9" s="311"/>
-      <c r="AK9" s="306"/>
-      <c r="AL9" s="305"/>
-      <c r="AM9" s="306"/>
+      <c r="A9" s="309"/>
+      <c r="B9" s="309"/>
+      <c r="C9" s="330"/>
+      <c r="D9" s="309"/>
+      <c r="E9" s="309"/>
+      <c r="F9" s="309"/>
+      <c r="G9" s="309"/>
+      <c r="H9" s="309"/>
+      <c r="I9" s="309"/>
+      <c r="J9" s="309"/>
+      <c r="K9" s="309"/>
+      <c r="L9" s="309"/>
+      <c r="M9" s="309"/>
+      <c r="N9" s="309"/>
+      <c r="O9" s="325"/>
+      <c r="P9" s="326"/>
+      <c r="Q9" s="326"/>
+      <c r="R9" s="326"/>
+      <c r="S9" s="326"/>
+      <c r="T9" s="326"/>
+      <c r="U9" s="326"/>
+      <c r="V9" s="327"/>
+      <c r="W9" s="309"/>
+      <c r="X9" s="309"/>
+      <c r="Y9" s="309"/>
+      <c r="Z9" s="309"/>
+      <c r="AA9" s="309"/>
+      <c r="AB9" s="309"/>
+      <c r="AC9" s="303"/>
+      <c r="AD9" s="309"/>
+      <c r="AE9" s="306"/>
+      <c r="AF9" s="306"/>
+      <c r="AG9" s="307"/>
+      <c r="AH9" s="306"/>
+      <c r="AI9" s="309"/>
+      <c r="AJ9" s="308"/>
+      <c r="AK9" s="309"/>
+      <c r="AL9" s="303"/>
+      <c r="AM9" s="309"/>
       <c r="AP9">
         <v>27</v>
       </c>
@@ -8709,47 +8706,47 @@
       </c>
     </row>
     <row r="77" spans="1:42" ht="29.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="343" t="s">
+      <c r="A77" s="339" t="s">
         <v>145</v>
       </c>
-      <c r="B77" s="306"/>
-      <c r="C77" s="306"/>
-      <c r="D77" s="306"/>
-      <c r="E77" s="306"/>
-      <c r="F77" s="306"/>
-      <c r="G77" s="306"/>
-      <c r="H77" s="306"/>
-      <c r="I77" s="306"/>
-      <c r="J77" s="306"/>
-      <c r="K77" s="306"/>
-      <c r="L77" s="306"/>
-      <c r="M77" s="306"/>
-      <c r="N77" s="306"/>
-      <c r="O77" s="306"/>
-      <c r="P77" s="306"/>
-      <c r="Q77" s="306"/>
-      <c r="R77" s="306"/>
-      <c r="S77" s="306"/>
-      <c r="T77" s="306"/>
-      <c r="U77" s="306"/>
-      <c r="V77" s="306"/>
-      <c r="W77" s="306"/>
-      <c r="X77" s="306"/>
-      <c r="Y77" s="306"/>
-      <c r="Z77" s="306"/>
-      <c r="AA77" s="306"/>
-      <c r="AB77" s="306"/>
-      <c r="AC77" s="306"/>
-      <c r="AD77" s="306"/>
-      <c r="AE77" s="306"/>
-      <c r="AF77" s="306"/>
-      <c r="AG77" s="306"/>
-      <c r="AH77" s="306"/>
-      <c r="AI77" s="306"/>
-      <c r="AJ77" s="306"/>
-      <c r="AK77" s="306"/>
-      <c r="AL77" s="306"/>
-      <c r="AM77" s="306"/>
+      <c r="B77" s="309"/>
+      <c r="C77" s="309"/>
+      <c r="D77" s="309"/>
+      <c r="E77" s="309"/>
+      <c r="F77" s="309"/>
+      <c r="G77" s="309"/>
+      <c r="H77" s="309"/>
+      <c r="I77" s="309"/>
+      <c r="J77" s="309"/>
+      <c r="K77" s="309"/>
+      <c r="L77" s="309"/>
+      <c r="M77" s="309"/>
+      <c r="N77" s="309"/>
+      <c r="O77" s="309"/>
+      <c r="P77" s="309"/>
+      <c r="Q77" s="309"/>
+      <c r="R77" s="309"/>
+      <c r="S77" s="309"/>
+      <c r="T77" s="309"/>
+      <c r="U77" s="309"/>
+      <c r="V77" s="309"/>
+      <c r="W77" s="309"/>
+      <c r="X77" s="309"/>
+      <c r="Y77" s="309"/>
+      <c r="Z77" s="309"/>
+      <c r="AA77" s="309"/>
+      <c r="AB77" s="309"/>
+      <c r="AC77" s="309"/>
+      <c r="AD77" s="309"/>
+      <c r="AE77" s="309"/>
+      <c r="AF77" s="309"/>
+      <c r="AG77" s="309"/>
+      <c r="AH77" s="309"/>
+      <c r="AI77" s="309"/>
+      <c r="AJ77" s="309"/>
+      <c r="AK77" s="309"/>
+      <c r="AL77" s="309"/>
+      <c r="AM77" s="309"/>
     </row>
     <row r="78" spans="1:42" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="81"/>
@@ -9849,6 +9846,28 @@
   </sheetData>
   <autoFilter ref="A10:AP80" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="38">
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AC9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="A2:AB2"/>
+    <mergeCell ref="A4:AM4"/>
+    <mergeCell ref="A5:AM5"/>
+    <mergeCell ref="AD7:AD9"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="AD6:AM6"/>
     <mergeCell ref="A77:AM77"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="D7:D9"/>
@@ -9865,28 +9884,6 @@
     <mergeCell ref="AI7:AI9"/>
     <mergeCell ref="AJ7:AJ9"/>
     <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="A2:AB2"/>
-    <mergeCell ref="A4:AM4"/>
-    <mergeCell ref="A5:AM5"/>
-    <mergeCell ref="AD7:AD9"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="AD6:AM6"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AC9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="O7:V9"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.27559055118110237" top="0.47244094488188981" bottom="0.31496062992125984" header="0" footer="0"/>
   <pageSetup scale="80" orientation="landscape" r:id="rId1"/>
@@ -9935,36 +9932,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="340" t="s">
+      <c r="A1" s="341" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="320"/>
-      <c r="C1" s="321"/>
-      <c r="D1" s="320"/>
-      <c r="E1" s="320"/>
-      <c r="F1" s="320"/>
-      <c r="G1" s="320"/>
-      <c r="H1" s="320"/>
-      <c r="I1" s="320"/>
-      <c r="J1" s="320"/>
-      <c r="K1" s="320"/>
-      <c r="L1" s="320"/>
-      <c r="M1" s="320"/>
-      <c r="N1" s="320"/>
-      <c r="O1" s="320"/>
-      <c r="P1" s="320"/>
-      <c r="Q1" s="320"/>
-      <c r="R1" s="320"/>
-      <c r="S1" s="320"/>
-      <c r="T1" s="320"/>
-      <c r="U1" s="320"/>
-      <c r="V1" s="320"/>
-      <c r="W1" s="320"/>
-      <c r="X1" s="320"/>
-      <c r="Y1" s="320"/>
-      <c r="Z1" s="320"/>
-      <c r="AA1" s="320"/>
-      <c r="AB1" s="322"/>
+      <c r="B1" s="311"/>
+      <c r="C1" s="312"/>
+      <c r="D1" s="311"/>
+      <c r="E1" s="311"/>
+      <c r="F1" s="311"/>
+      <c r="G1" s="311"/>
+      <c r="H1" s="311"/>
+      <c r="I1" s="311"/>
+      <c r="J1" s="311"/>
+      <c r="K1" s="311"/>
+      <c r="L1" s="311"/>
+      <c r="M1" s="311"/>
+      <c r="N1" s="311"/>
+      <c r="O1" s="311"/>
+      <c r="P1" s="311"/>
+      <c r="Q1" s="311"/>
+      <c r="R1" s="311"/>
+      <c r="S1" s="311"/>
+      <c r="T1" s="311"/>
+      <c r="U1" s="311"/>
+      <c r="V1" s="311"/>
+      <c r="W1" s="311"/>
+      <c r="X1" s="311"/>
+      <c r="Y1" s="311"/>
+      <c r="Z1" s="311"/>
+      <c r="AA1" s="311"/>
+      <c r="AB1" s="313"/>
       <c r="AC1" s="17"/>
       <c r="AD1" s="17"/>
       <c r="AE1" s="1"/>
@@ -9981,36 +9978,36 @@
       <c r="AN1" s="160"/>
     </row>
     <row r="2" spans="1:43" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="323" t="s">
+      <c r="A2" s="314" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="320"/>
-      <c r="C2" s="321"/>
-      <c r="D2" s="320"/>
-      <c r="E2" s="320"/>
-      <c r="F2" s="320"/>
-      <c r="G2" s="320"/>
-      <c r="H2" s="320"/>
-      <c r="I2" s="320"/>
-      <c r="J2" s="320"/>
-      <c r="K2" s="320"/>
-      <c r="L2" s="320"/>
-      <c r="M2" s="320"/>
-      <c r="N2" s="320"/>
-      <c r="O2" s="320"/>
-      <c r="P2" s="320"/>
-      <c r="Q2" s="320"/>
-      <c r="R2" s="320"/>
-      <c r="S2" s="320"/>
-      <c r="T2" s="320"/>
-      <c r="U2" s="320"/>
-      <c r="V2" s="320"/>
-      <c r="W2" s="320"/>
-      <c r="X2" s="320"/>
-      <c r="Y2" s="320"/>
-      <c r="Z2" s="320"/>
-      <c r="AA2" s="320"/>
-      <c r="AB2" s="322"/>
+      <c r="B2" s="311"/>
+      <c r="C2" s="312"/>
+      <c r="D2" s="311"/>
+      <c r="E2" s="311"/>
+      <c r="F2" s="311"/>
+      <c r="G2" s="311"/>
+      <c r="H2" s="311"/>
+      <c r="I2" s="311"/>
+      <c r="J2" s="311"/>
+      <c r="K2" s="311"/>
+      <c r="L2" s="311"/>
+      <c r="M2" s="311"/>
+      <c r="N2" s="311"/>
+      <c r="O2" s="311"/>
+      <c r="P2" s="311"/>
+      <c r="Q2" s="311"/>
+      <c r="R2" s="311"/>
+      <c r="S2" s="311"/>
+      <c r="T2" s="311"/>
+      <c r="U2" s="311"/>
+      <c r="V2" s="311"/>
+      <c r="W2" s="311"/>
+      <c r="X2" s="311"/>
+      <c r="Y2" s="311"/>
+      <c r="Z2" s="311"/>
+      <c r="AA2" s="311"/>
+      <c r="AB2" s="313"/>
       <c r="AC2" s="17"/>
       <c r="AD2" s="17"/>
       <c r="AE2" s="1"/>
@@ -10067,92 +10064,92 @@
       <c r="AN3" s="160"/>
     </row>
     <row r="4" spans="1:43" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="324" t="s">
+      <c r="A4" s="315" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="320"/>
-      <c r="C4" s="321"/>
-      <c r="D4" s="320"/>
-      <c r="E4" s="320"/>
-      <c r="F4" s="320"/>
-      <c r="G4" s="320"/>
-      <c r="H4" s="320"/>
-      <c r="I4" s="320"/>
-      <c r="J4" s="320"/>
-      <c r="K4" s="320"/>
-      <c r="L4" s="320"/>
-      <c r="M4" s="320"/>
-      <c r="N4" s="320"/>
-      <c r="O4" s="320"/>
-      <c r="P4" s="320"/>
-      <c r="Q4" s="320"/>
-      <c r="R4" s="320"/>
-      <c r="S4" s="320"/>
-      <c r="T4" s="320"/>
-      <c r="U4" s="320"/>
-      <c r="V4" s="320"/>
-      <c r="W4" s="320"/>
-      <c r="X4" s="320"/>
-      <c r="Y4" s="320"/>
-      <c r="Z4" s="320"/>
-      <c r="AA4" s="320"/>
-      <c r="AB4" s="320"/>
-      <c r="AC4" s="321"/>
-      <c r="AD4" s="321"/>
-      <c r="AE4" s="320"/>
-      <c r="AF4" s="320"/>
-      <c r="AG4" s="321"/>
-      <c r="AH4" s="321"/>
-      <c r="AI4" s="320"/>
-      <c r="AJ4" s="321"/>
-      <c r="AK4" s="321"/>
-      <c r="AL4" s="320"/>
-      <c r="AM4" s="321"/>
-      <c r="AN4" s="322"/>
+      <c r="B4" s="311"/>
+      <c r="C4" s="312"/>
+      <c r="D4" s="311"/>
+      <c r="E4" s="311"/>
+      <c r="F4" s="311"/>
+      <c r="G4" s="311"/>
+      <c r="H4" s="311"/>
+      <c r="I4" s="311"/>
+      <c r="J4" s="311"/>
+      <c r="K4" s="311"/>
+      <c r="L4" s="311"/>
+      <c r="M4" s="311"/>
+      <c r="N4" s="311"/>
+      <c r="O4" s="311"/>
+      <c r="P4" s="311"/>
+      <c r="Q4" s="311"/>
+      <c r="R4" s="311"/>
+      <c r="S4" s="311"/>
+      <c r="T4" s="311"/>
+      <c r="U4" s="311"/>
+      <c r="V4" s="311"/>
+      <c r="W4" s="311"/>
+      <c r="X4" s="311"/>
+      <c r="Y4" s="311"/>
+      <c r="Z4" s="311"/>
+      <c r="AA4" s="311"/>
+      <c r="AB4" s="311"/>
+      <c r="AC4" s="312"/>
+      <c r="AD4" s="312"/>
+      <c r="AE4" s="311"/>
+      <c r="AF4" s="311"/>
+      <c r="AG4" s="312"/>
+      <c r="AH4" s="312"/>
+      <c r="AI4" s="311"/>
+      <c r="AJ4" s="312"/>
+      <c r="AK4" s="312"/>
+      <c r="AL4" s="311"/>
+      <c r="AM4" s="312"/>
+      <c r="AN4" s="313"/>
     </row>
     <row r="5" spans="1:43" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="325" t="s">
+      <c r="A5" s="316" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="320"/>
-      <c r="C5" s="321"/>
-      <c r="D5" s="320"/>
-      <c r="E5" s="320"/>
-      <c r="F5" s="320"/>
-      <c r="G5" s="320"/>
-      <c r="H5" s="320"/>
-      <c r="I5" s="320"/>
-      <c r="J5" s="320"/>
-      <c r="K5" s="320"/>
-      <c r="L5" s="320"/>
-      <c r="M5" s="320"/>
-      <c r="N5" s="320"/>
-      <c r="O5" s="320"/>
-      <c r="P5" s="320"/>
-      <c r="Q5" s="320"/>
-      <c r="R5" s="320"/>
-      <c r="S5" s="320"/>
-      <c r="T5" s="320"/>
-      <c r="U5" s="320"/>
-      <c r="V5" s="320"/>
-      <c r="W5" s="320"/>
-      <c r="X5" s="320"/>
-      <c r="Y5" s="320"/>
-      <c r="Z5" s="320"/>
-      <c r="AA5" s="320"/>
-      <c r="AB5" s="320"/>
-      <c r="AC5" s="321"/>
-      <c r="AD5" s="321"/>
-      <c r="AE5" s="320"/>
-      <c r="AF5" s="320"/>
-      <c r="AG5" s="321"/>
-      <c r="AH5" s="321"/>
-      <c r="AI5" s="320"/>
-      <c r="AJ5" s="321"/>
-      <c r="AK5" s="321"/>
-      <c r="AL5" s="320"/>
-      <c r="AM5" s="321"/>
-      <c r="AN5" s="322"/>
+      <c r="B5" s="311"/>
+      <c r="C5" s="312"/>
+      <c r="D5" s="311"/>
+      <c r="E5" s="311"/>
+      <c r="F5" s="311"/>
+      <c r="G5" s="311"/>
+      <c r="H5" s="311"/>
+      <c r="I5" s="311"/>
+      <c r="J5" s="311"/>
+      <c r="K5" s="311"/>
+      <c r="L5" s="311"/>
+      <c r="M5" s="311"/>
+      <c r="N5" s="311"/>
+      <c r="O5" s="311"/>
+      <c r="P5" s="311"/>
+      <c r="Q5" s="311"/>
+      <c r="R5" s="311"/>
+      <c r="S5" s="311"/>
+      <c r="T5" s="311"/>
+      <c r="U5" s="311"/>
+      <c r="V5" s="311"/>
+      <c r="W5" s="311"/>
+      <c r="X5" s="311"/>
+      <c r="Y5" s="311"/>
+      <c r="Z5" s="311"/>
+      <c r="AA5" s="311"/>
+      <c r="AB5" s="311"/>
+      <c r="AC5" s="312"/>
+      <c r="AD5" s="312"/>
+      <c r="AE5" s="311"/>
+      <c r="AF5" s="311"/>
+      <c r="AG5" s="312"/>
+      <c r="AH5" s="312"/>
+      <c r="AI5" s="311"/>
+      <c r="AJ5" s="312"/>
+      <c r="AK5" s="312"/>
+      <c r="AL5" s="311"/>
+      <c r="AM5" s="312"/>
+      <c r="AN5" s="313"/>
     </row>
     <row r="6" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -10187,212 +10184,212 @@
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
       <c r="AD6" s="11"/>
-      <c r="AE6" s="344" t="s">
+      <c r="AE6" s="343" t="s">
         <v>151</v>
       </c>
-      <c r="AF6" s="345"/>
-      <c r="AG6" s="345"/>
-      <c r="AH6" s="345"/>
-      <c r="AI6" s="345"/>
-      <c r="AJ6" s="345"/>
-      <c r="AK6" s="345"/>
-      <c r="AL6" s="345"/>
-      <c r="AM6" s="345"/>
-      <c r="AN6" s="345"/>
+      <c r="AF6" s="344"/>
+      <c r="AG6" s="344"/>
+      <c r="AH6" s="344"/>
+      <c r="AI6" s="344"/>
+      <c r="AJ6" s="344"/>
+      <c r="AK6" s="344"/>
+      <c r="AL6" s="344"/>
+      <c r="AM6" s="344"/>
+      <c r="AN6" s="344"/>
     </row>
     <row r="7" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="305" t="s">
+      <c r="A7" s="303" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="305" t="s">
+      <c r="B7" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="308" t="s">
+      <c r="C7" s="330" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="305" t="s">
+      <c r="D7" s="303" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="305" t="s">
+      <c r="E7" s="303" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="305" t="s">
+      <c r="F7" s="303" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="305" t="s">
+      <c r="G7" s="303" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="305" t="s">
+      <c r="H7" s="303" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="305" t="s">
+      <c r="I7" s="303" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="305" t="s">
+      <c r="J7" s="303" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="305" t="s">
+      <c r="K7" s="303" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="326" t="s">
+      <c r="L7" s="318" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="305" t="s">
+      <c r="M7" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="305" t="s">
+      <c r="N7" s="303" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="328" t="s">
+      <c r="O7" s="319" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="329"/>
-      <c r="Q7" s="329"/>
-      <c r="R7" s="329"/>
-      <c r="S7" s="329"/>
-      <c r="T7" s="329"/>
-      <c r="U7" s="329"/>
-      <c r="V7" s="330"/>
-      <c r="W7" s="305" t="s">
+      <c r="P7" s="320"/>
+      <c r="Q7" s="320"/>
+      <c r="R7" s="320"/>
+      <c r="S7" s="320"/>
+      <c r="T7" s="320"/>
+      <c r="U7" s="320"/>
+      <c r="V7" s="321"/>
+      <c r="W7" s="303" t="s">
         <v>139</v>
       </c>
-      <c r="X7" s="309" t="s">
+      <c r="X7" s="317" t="s">
         <v>13</v>
       </c>
-      <c r="Y7" s="309" t="s">
+      <c r="Y7" s="317" t="s">
         <v>184</v>
       </c>
-      <c r="Z7" s="310" t="s">
+      <c r="Z7" s="331" t="s">
         <v>175</v>
       </c>
-      <c r="AA7" s="305" t="s">
+      <c r="AA7" s="303" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="305" t="s">
+      <c r="AB7" s="303" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="328" t="s">
+      <c r="AC7" s="319" t="s">
         <v>155</v>
       </c>
-      <c r="AD7" s="330"/>
-      <c r="AE7" s="311" t="s">
+      <c r="AD7" s="321"/>
+      <c r="AE7" s="308" t="s">
         <v>17</v>
       </c>
-      <c r="AF7" s="337" t="s">
+      <c r="AF7" s="305" t="s">
         <v>107</v>
       </c>
-      <c r="AG7" s="337" t="s">
+      <c r="AG7" s="305" t="s">
         <v>108</v>
       </c>
-      <c r="AH7" s="337" t="s">
+      <c r="AH7" s="305" t="s">
         <v>106</v>
       </c>
-      <c r="AI7" s="339" t="s">
+      <c r="AI7" s="307" t="s">
         <v>147</v>
       </c>
-      <c r="AJ7" s="311" t="s">
+      <c r="AJ7" s="308" t="s">
         <v>136</v>
       </c>
-      <c r="AK7" s="311" t="s">
+      <c r="AK7" s="308" t="s">
         <v>137</v>
       </c>
-      <c r="AL7" s="305" t="s">
+      <c r="AL7" s="303" t="s">
         <v>135</v>
       </c>
-      <c r="AM7" s="305" t="s">
+      <c r="AM7" s="303" t="s">
         <v>146</v>
       </c>
-      <c r="AN7" s="305" t="s">
+      <c r="AN7" s="303" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="306"/>
-      <c r="B8" s="306"/>
-      <c r="C8" s="308"/>
-      <c r="D8" s="306"/>
-      <c r="E8" s="306"/>
-      <c r="F8" s="306"/>
-      <c r="G8" s="306"/>
-      <c r="H8" s="306"/>
-      <c r="I8" s="306"/>
-      <c r="J8" s="306"/>
-      <c r="K8" s="306"/>
-      <c r="L8" s="306"/>
-      <c r="M8" s="306"/>
-      <c r="N8" s="306"/>
-      <c r="O8" s="331"/>
-      <c r="P8" s="332"/>
-      <c r="Q8" s="332"/>
-      <c r="R8" s="332"/>
-      <c r="S8" s="332"/>
-      <c r="T8" s="332"/>
-      <c r="U8" s="332"/>
-      <c r="V8" s="333"/>
-      <c r="W8" s="306"/>
-      <c r="X8" s="306"/>
-      <c r="Y8" s="306"/>
-      <c r="Z8" s="306"/>
-      <c r="AA8" s="306"/>
-      <c r="AB8" s="306"/>
-      <c r="AC8" s="334"/>
-      <c r="AD8" s="336"/>
-      <c r="AE8" s="306"/>
-      <c r="AF8" s="338"/>
-      <c r="AG8" s="338"/>
-      <c r="AH8" s="339"/>
-      <c r="AI8" s="338"/>
-      <c r="AJ8" s="306"/>
-      <c r="AK8" s="311"/>
-      <c r="AL8" s="306"/>
-      <c r="AM8" s="305"/>
-      <c r="AN8" s="327"/>
+      <c r="A8" s="309"/>
+      <c r="B8" s="309"/>
+      <c r="C8" s="330"/>
+      <c r="D8" s="309"/>
+      <c r="E8" s="309"/>
+      <c r="F8" s="309"/>
+      <c r="G8" s="309"/>
+      <c r="H8" s="309"/>
+      <c r="I8" s="309"/>
+      <c r="J8" s="309"/>
+      <c r="K8" s="309"/>
+      <c r="L8" s="309"/>
+      <c r="M8" s="309"/>
+      <c r="N8" s="309"/>
+      <c r="O8" s="322"/>
+      <c r="P8" s="323"/>
+      <c r="Q8" s="323"/>
+      <c r="R8" s="323"/>
+      <c r="S8" s="323"/>
+      <c r="T8" s="323"/>
+      <c r="U8" s="323"/>
+      <c r="V8" s="324"/>
+      <c r="W8" s="309"/>
+      <c r="X8" s="309"/>
+      <c r="Y8" s="309"/>
+      <c r="Z8" s="309"/>
+      <c r="AA8" s="309"/>
+      <c r="AB8" s="309"/>
+      <c r="AC8" s="325"/>
+      <c r="AD8" s="327"/>
+      <c r="AE8" s="309"/>
+      <c r="AF8" s="306"/>
+      <c r="AG8" s="306"/>
+      <c r="AH8" s="307"/>
+      <c r="AI8" s="306"/>
+      <c r="AJ8" s="309"/>
+      <c r="AK8" s="308"/>
+      <c r="AL8" s="309"/>
+      <c r="AM8" s="303"/>
+      <c r="AN8" s="304"/>
     </row>
     <row r="9" spans="1:43" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="306"/>
-      <c r="B9" s="306"/>
-      <c r="C9" s="308"/>
-      <c r="D9" s="306"/>
-      <c r="E9" s="306"/>
-      <c r="F9" s="306"/>
-      <c r="G9" s="306"/>
-      <c r="H9" s="306"/>
-      <c r="I9" s="306"/>
-      <c r="J9" s="306"/>
-      <c r="K9" s="306"/>
-      <c r="L9" s="306"/>
-      <c r="M9" s="306"/>
-      <c r="N9" s="306"/>
-      <c r="O9" s="334"/>
-      <c r="P9" s="335"/>
-      <c r="Q9" s="335"/>
-      <c r="R9" s="335"/>
-      <c r="S9" s="335"/>
-      <c r="T9" s="335"/>
-      <c r="U9" s="335"/>
-      <c r="V9" s="336"/>
-      <c r="W9" s="306"/>
-      <c r="X9" s="306"/>
-      <c r="Y9" s="306"/>
-      <c r="Z9" s="306"/>
-      <c r="AA9" s="306"/>
-      <c r="AB9" s="306"/>
+      <c r="A9" s="309"/>
+      <c r="B9" s="309"/>
+      <c r="C9" s="330"/>
+      <c r="D9" s="309"/>
+      <c r="E9" s="309"/>
+      <c r="F9" s="309"/>
+      <c r="G9" s="309"/>
+      <c r="H9" s="309"/>
+      <c r="I9" s="309"/>
+      <c r="J9" s="309"/>
+      <c r="K9" s="309"/>
+      <c r="L9" s="309"/>
+      <c r="M9" s="309"/>
+      <c r="N9" s="309"/>
+      <c r="O9" s="325"/>
+      <c r="P9" s="326"/>
+      <c r="Q9" s="326"/>
+      <c r="R9" s="326"/>
+      <c r="S9" s="326"/>
+      <c r="T9" s="326"/>
+      <c r="U9" s="326"/>
+      <c r="V9" s="327"/>
+      <c r="W9" s="309"/>
+      <c r="X9" s="309"/>
+      <c r="Y9" s="309"/>
+      <c r="Z9" s="309"/>
+      <c r="AA9" s="309"/>
+      <c r="AB9" s="309"/>
       <c r="AC9" s="201" t="s">
         <v>153</v>
       </c>
       <c r="AD9" s="178" t="s">
         <v>154</v>
       </c>
-      <c r="AE9" s="306"/>
-      <c r="AF9" s="338"/>
-      <c r="AG9" s="338"/>
-      <c r="AH9" s="339"/>
-      <c r="AI9" s="338"/>
-      <c r="AJ9" s="306"/>
-      <c r="AK9" s="311"/>
-      <c r="AL9" s="306"/>
-      <c r="AM9" s="305"/>
-      <c r="AN9" s="327"/>
+      <c r="AE9" s="309"/>
+      <c r="AF9" s="306"/>
+      <c r="AG9" s="306"/>
+      <c r="AH9" s="307"/>
+      <c r="AI9" s="306"/>
+      <c r="AJ9" s="309"/>
+      <c r="AK9" s="308"/>
+      <c r="AL9" s="309"/>
+      <c r="AM9" s="303"/>
+      <c r="AN9" s="304"/>
       <c r="AO9">
         <f>Z11/W11</f>
         <v>0.50632226325372287</v>
@@ -15662,27 +15659,6 @@
   </sheetData>
   <autoFilter ref="A10:AQ54" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AD8"/>
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A2:AB2"/>
@@ -15699,6 +15675,27 @@
     <mergeCell ref="H7:H9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:J9"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AD8"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
   </mergeCells>
   <pageMargins left="0.17" right="0.15748031496062992" top="0.41" bottom="0.23622047244094491" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
@@ -15747,36 +15744,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="340" t="s">
+      <c r="A1" s="341" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="320"/>
-      <c r="C1" s="321"/>
-      <c r="D1" s="320"/>
-      <c r="E1" s="320"/>
-      <c r="F1" s="320"/>
-      <c r="G1" s="320"/>
-      <c r="H1" s="320"/>
-      <c r="I1" s="320"/>
-      <c r="J1" s="320"/>
-      <c r="K1" s="320"/>
-      <c r="L1" s="320"/>
-      <c r="M1" s="320"/>
-      <c r="N1" s="320"/>
-      <c r="O1" s="320"/>
-      <c r="P1" s="320"/>
-      <c r="Q1" s="320"/>
-      <c r="R1" s="320"/>
-      <c r="S1" s="320"/>
-      <c r="T1" s="320"/>
-      <c r="U1" s="320"/>
-      <c r="V1" s="320"/>
-      <c r="W1" s="320"/>
-      <c r="X1" s="320"/>
-      <c r="Y1" s="320"/>
-      <c r="Z1" s="320"/>
-      <c r="AA1" s="320"/>
-      <c r="AB1" s="322"/>
+      <c r="B1" s="311"/>
+      <c r="C1" s="312"/>
+      <c r="D1" s="311"/>
+      <c r="E1" s="311"/>
+      <c r="F1" s="311"/>
+      <c r="G1" s="311"/>
+      <c r="H1" s="311"/>
+      <c r="I1" s="311"/>
+      <c r="J1" s="311"/>
+      <c r="K1" s="311"/>
+      <c r="L1" s="311"/>
+      <c r="M1" s="311"/>
+      <c r="N1" s="311"/>
+      <c r="O1" s="311"/>
+      <c r="P1" s="311"/>
+      <c r="Q1" s="311"/>
+      <c r="R1" s="311"/>
+      <c r="S1" s="311"/>
+      <c r="T1" s="311"/>
+      <c r="U1" s="311"/>
+      <c r="V1" s="311"/>
+      <c r="W1" s="311"/>
+      <c r="X1" s="311"/>
+      <c r="Y1" s="311"/>
+      <c r="Z1" s="311"/>
+      <c r="AA1" s="311"/>
+      <c r="AB1" s="313"/>
       <c r="AC1" s="17"/>
       <c r="AD1" s="17"/>
       <c r="AE1" s="1"/>
@@ -15793,36 +15790,36 @@
       <c r="AN1" s="160"/>
     </row>
     <row r="2" spans="1:43" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="323" t="s">
+      <c r="A2" s="314" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="320"/>
-      <c r="C2" s="321"/>
-      <c r="D2" s="320"/>
-      <c r="E2" s="320"/>
-      <c r="F2" s="320"/>
-      <c r="G2" s="320"/>
-      <c r="H2" s="320"/>
-      <c r="I2" s="320"/>
-      <c r="J2" s="320"/>
-      <c r="K2" s="320"/>
-      <c r="L2" s="320"/>
-      <c r="M2" s="320"/>
-      <c r="N2" s="320"/>
-      <c r="O2" s="320"/>
-      <c r="P2" s="320"/>
-      <c r="Q2" s="320"/>
-      <c r="R2" s="320"/>
-      <c r="S2" s="320"/>
-      <c r="T2" s="320"/>
-      <c r="U2" s="320"/>
-      <c r="V2" s="320"/>
-      <c r="W2" s="320"/>
-      <c r="X2" s="320"/>
-      <c r="Y2" s="320"/>
-      <c r="Z2" s="320"/>
-      <c r="AA2" s="320"/>
-      <c r="AB2" s="322"/>
+      <c r="B2" s="311"/>
+      <c r="C2" s="312"/>
+      <c r="D2" s="311"/>
+      <c r="E2" s="311"/>
+      <c r="F2" s="311"/>
+      <c r="G2" s="311"/>
+      <c r="H2" s="311"/>
+      <c r="I2" s="311"/>
+      <c r="J2" s="311"/>
+      <c r="K2" s="311"/>
+      <c r="L2" s="311"/>
+      <c r="M2" s="311"/>
+      <c r="N2" s="311"/>
+      <c r="O2" s="311"/>
+      <c r="P2" s="311"/>
+      <c r="Q2" s="311"/>
+      <c r="R2" s="311"/>
+      <c r="S2" s="311"/>
+      <c r="T2" s="311"/>
+      <c r="U2" s="311"/>
+      <c r="V2" s="311"/>
+      <c r="W2" s="311"/>
+      <c r="X2" s="311"/>
+      <c r="Y2" s="311"/>
+      <c r="Z2" s="311"/>
+      <c r="AA2" s="311"/>
+      <c r="AB2" s="313"/>
       <c r="AC2" s="17"/>
       <c r="AD2" s="17"/>
       <c r="AE2" s="1"/>
@@ -15879,92 +15876,92 @@
       <c r="AN3" s="160"/>
     </row>
     <row r="4" spans="1:43" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="324" t="s">
+      <c r="A4" s="315" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="320"/>
-      <c r="C4" s="321"/>
-      <c r="D4" s="320"/>
-      <c r="E4" s="320"/>
-      <c r="F4" s="320"/>
-      <c r="G4" s="320"/>
-      <c r="H4" s="320"/>
-      <c r="I4" s="320"/>
-      <c r="J4" s="320"/>
-      <c r="K4" s="320"/>
-      <c r="L4" s="320"/>
-      <c r="M4" s="320"/>
-      <c r="N4" s="320"/>
-      <c r="O4" s="320"/>
-      <c r="P4" s="320"/>
-      <c r="Q4" s="320"/>
-      <c r="R4" s="320"/>
-      <c r="S4" s="320"/>
-      <c r="T4" s="320"/>
-      <c r="U4" s="320"/>
-      <c r="V4" s="320"/>
-      <c r="W4" s="320"/>
-      <c r="X4" s="320"/>
-      <c r="Y4" s="320"/>
-      <c r="Z4" s="320"/>
-      <c r="AA4" s="320"/>
-      <c r="AB4" s="320"/>
-      <c r="AC4" s="321"/>
-      <c r="AD4" s="321"/>
-      <c r="AE4" s="320"/>
-      <c r="AF4" s="320"/>
-      <c r="AG4" s="321"/>
-      <c r="AH4" s="321"/>
-      <c r="AI4" s="320"/>
-      <c r="AJ4" s="321"/>
-      <c r="AK4" s="321"/>
-      <c r="AL4" s="320"/>
-      <c r="AM4" s="321"/>
-      <c r="AN4" s="322"/>
+      <c r="B4" s="311"/>
+      <c r="C4" s="312"/>
+      <c r="D4" s="311"/>
+      <c r="E4" s="311"/>
+      <c r="F4" s="311"/>
+      <c r="G4" s="311"/>
+      <c r="H4" s="311"/>
+      <c r="I4" s="311"/>
+      <c r="J4" s="311"/>
+      <c r="K4" s="311"/>
+      <c r="L4" s="311"/>
+      <c r="M4" s="311"/>
+      <c r="N4" s="311"/>
+      <c r="O4" s="311"/>
+      <c r="P4" s="311"/>
+      <c r="Q4" s="311"/>
+      <c r="R4" s="311"/>
+      <c r="S4" s="311"/>
+      <c r="T4" s="311"/>
+      <c r="U4" s="311"/>
+      <c r="V4" s="311"/>
+      <c r="W4" s="311"/>
+      <c r="X4" s="311"/>
+      <c r="Y4" s="311"/>
+      <c r="Z4" s="311"/>
+      <c r="AA4" s="311"/>
+      <c r="AB4" s="311"/>
+      <c r="AC4" s="312"/>
+      <c r="AD4" s="312"/>
+      <c r="AE4" s="311"/>
+      <c r="AF4" s="311"/>
+      <c r="AG4" s="312"/>
+      <c r="AH4" s="312"/>
+      <c r="AI4" s="311"/>
+      <c r="AJ4" s="312"/>
+      <c r="AK4" s="312"/>
+      <c r="AL4" s="311"/>
+      <c r="AM4" s="312"/>
+      <c r="AN4" s="313"/>
     </row>
     <row r="5" spans="1:43" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="325" t="s">
+      <c r="A5" s="316" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="320"/>
-      <c r="C5" s="321"/>
-      <c r="D5" s="320"/>
-      <c r="E5" s="320"/>
-      <c r="F5" s="320"/>
-      <c r="G5" s="320"/>
-      <c r="H5" s="320"/>
-      <c r="I5" s="320"/>
-      <c r="J5" s="320"/>
-      <c r="K5" s="320"/>
-      <c r="L5" s="320"/>
-      <c r="M5" s="320"/>
-      <c r="N5" s="320"/>
-      <c r="O5" s="320"/>
-      <c r="P5" s="320"/>
-      <c r="Q5" s="320"/>
-      <c r="R5" s="320"/>
-      <c r="S5" s="320"/>
-      <c r="T5" s="320"/>
-      <c r="U5" s="320"/>
-      <c r="V5" s="320"/>
-      <c r="W5" s="320"/>
-      <c r="X5" s="320"/>
-      <c r="Y5" s="320"/>
-      <c r="Z5" s="320"/>
-      <c r="AA5" s="320"/>
-      <c r="AB5" s="320"/>
-      <c r="AC5" s="321"/>
-      <c r="AD5" s="321"/>
-      <c r="AE5" s="320"/>
-      <c r="AF5" s="320"/>
-      <c r="AG5" s="321"/>
-      <c r="AH5" s="321"/>
-      <c r="AI5" s="320"/>
-      <c r="AJ5" s="321"/>
-      <c r="AK5" s="321"/>
-      <c r="AL5" s="320"/>
-      <c r="AM5" s="321"/>
-      <c r="AN5" s="322"/>
+      <c r="B5" s="311"/>
+      <c r="C5" s="312"/>
+      <c r="D5" s="311"/>
+      <c r="E5" s="311"/>
+      <c r="F5" s="311"/>
+      <c r="G5" s="311"/>
+      <c r="H5" s="311"/>
+      <c r="I5" s="311"/>
+      <c r="J5" s="311"/>
+      <c r="K5" s="311"/>
+      <c r="L5" s="311"/>
+      <c r="M5" s="311"/>
+      <c r="N5" s="311"/>
+      <c r="O5" s="311"/>
+      <c r="P5" s="311"/>
+      <c r="Q5" s="311"/>
+      <c r="R5" s="311"/>
+      <c r="S5" s="311"/>
+      <c r="T5" s="311"/>
+      <c r="U5" s="311"/>
+      <c r="V5" s="311"/>
+      <c r="W5" s="311"/>
+      <c r="X5" s="311"/>
+      <c r="Y5" s="311"/>
+      <c r="Z5" s="311"/>
+      <c r="AA5" s="311"/>
+      <c r="AB5" s="311"/>
+      <c r="AC5" s="312"/>
+      <c r="AD5" s="312"/>
+      <c r="AE5" s="311"/>
+      <c r="AF5" s="311"/>
+      <c r="AG5" s="312"/>
+      <c r="AH5" s="312"/>
+      <c r="AI5" s="311"/>
+      <c r="AJ5" s="312"/>
+      <c r="AK5" s="312"/>
+      <c r="AL5" s="311"/>
+      <c r="AM5" s="312"/>
+      <c r="AN5" s="313"/>
     </row>
     <row r="6" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -15999,212 +15996,212 @@
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
       <c r="AD6" s="11"/>
-      <c r="AE6" s="344" t="s">
+      <c r="AE6" s="343" t="s">
         <v>151</v>
       </c>
-      <c r="AF6" s="345"/>
-      <c r="AG6" s="345"/>
-      <c r="AH6" s="345"/>
-      <c r="AI6" s="345"/>
-      <c r="AJ6" s="345"/>
-      <c r="AK6" s="345"/>
-      <c r="AL6" s="345"/>
-      <c r="AM6" s="345"/>
-      <c r="AN6" s="345"/>
+      <c r="AF6" s="344"/>
+      <c r="AG6" s="344"/>
+      <c r="AH6" s="344"/>
+      <c r="AI6" s="344"/>
+      <c r="AJ6" s="344"/>
+      <c r="AK6" s="344"/>
+      <c r="AL6" s="344"/>
+      <c r="AM6" s="344"/>
+      <c r="AN6" s="344"/>
     </row>
     <row r="7" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="305" t="s">
+      <c r="A7" s="303" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="346" t="s">
+      <c r="B7" s="345" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="308" t="s">
+      <c r="C7" s="330" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="305" t="s">
+      <c r="D7" s="303" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="305" t="s">
+      <c r="E7" s="303" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="305" t="s">
+      <c r="F7" s="303" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="305" t="s">
+      <c r="G7" s="303" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="305" t="s">
+      <c r="H7" s="303" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="305" t="s">
+      <c r="I7" s="303" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="305" t="s">
+      <c r="J7" s="303" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="305" t="s">
+      <c r="K7" s="303" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="326" t="s">
+      <c r="L7" s="318" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="305" t="s">
+      <c r="M7" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="305" t="s">
+      <c r="N7" s="303" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="328" t="s">
+      <c r="O7" s="319" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="329"/>
-      <c r="Q7" s="329"/>
-      <c r="R7" s="329"/>
-      <c r="S7" s="329"/>
-      <c r="T7" s="329"/>
-      <c r="U7" s="329"/>
-      <c r="V7" s="330"/>
-      <c r="W7" s="305" t="s">
+      <c r="P7" s="320"/>
+      <c r="Q7" s="320"/>
+      <c r="R7" s="320"/>
+      <c r="S7" s="320"/>
+      <c r="T7" s="320"/>
+      <c r="U7" s="320"/>
+      <c r="V7" s="321"/>
+      <c r="W7" s="303" t="s">
         <v>139</v>
       </c>
-      <c r="X7" s="309" t="s">
+      <c r="X7" s="317" t="s">
         <v>13</v>
       </c>
-      <c r="Y7" s="309" t="s">
+      <c r="Y7" s="317" t="s">
         <v>184</v>
       </c>
-      <c r="Z7" s="310" t="s">
+      <c r="Z7" s="331" t="s">
         <v>175</v>
       </c>
-      <c r="AA7" s="305" t="s">
+      <c r="AA7" s="303" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="305" t="s">
+      <c r="AB7" s="303" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="328" t="s">
+      <c r="AC7" s="319" t="s">
         <v>155</v>
       </c>
-      <c r="AD7" s="330"/>
-      <c r="AE7" s="311" t="s">
+      <c r="AD7" s="321"/>
+      <c r="AE7" s="308" t="s">
         <v>17</v>
       </c>
-      <c r="AF7" s="337" t="s">
+      <c r="AF7" s="305" t="s">
         <v>107</v>
       </c>
-      <c r="AG7" s="337" t="s">
+      <c r="AG7" s="305" t="s">
         <v>108</v>
       </c>
-      <c r="AH7" s="337" t="s">
+      <c r="AH7" s="305" t="s">
         <v>106</v>
       </c>
-      <c r="AI7" s="339" t="s">
+      <c r="AI7" s="307" t="s">
         <v>147</v>
       </c>
-      <c r="AJ7" s="311" t="s">
+      <c r="AJ7" s="308" t="s">
         <v>136</v>
       </c>
-      <c r="AK7" s="311" t="s">
+      <c r="AK7" s="308" t="s">
         <v>137</v>
       </c>
-      <c r="AL7" s="305" t="s">
+      <c r="AL7" s="303" t="s">
         <v>135</v>
       </c>
-      <c r="AM7" s="305" t="s">
+      <c r="AM7" s="303" t="s">
         <v>146</v>
       </c>
-      <c r="AN7" s="305" t="s">
+      <c r="AN7" s="303" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="306"/>
-      <c r="B8" s="347"/>
-      <c r="C8" s="308"/>
-      <c r="D8" s="306"/>
-      <c r="E8" s="306"/>
-      <c r="F8" s="306"/>
-      <c r="G8" s="306"/>
-      <c r="H8" s="306"/>
-      <c r="I8" s="306"/>
-      <c r="J8" s="306"/>
-      <c r="K8" s="306"/>
-      <c r="L8" s="306"/>
-      <c r="M8" s="306"/>
-      <c r="N8" s="306"/>
-      <c r="O8" s="331"/>
-      <c r="P8" s="332"/>
-      <c r="Q8" s="332"/>
-      <c r="R8" s="332"/>
-      <c r="S8" s="332"/>
-      <c r="T8" s="332"/>
-      <c r="U8" s="332"/>
-      <c r="V8" s="333"/>
-      <c r="W8" s="306"/>
-      <c r="X8" s="306"/>
-      <c r="Y8" s="306"/>
-      <c r="Z8" s="306"/>
-      <c r="AA8" s="306"/>
-      <c r="AB8" s="306"/>
-      <c r="AC8" s="334"/>
-      <c r="AD8" s="336"/>
-      <c r="AE8" s="306"/>
-      <c r="AF8" s="338"/>
-      <c r="AG8" s="338"/>
-      <c r="AH8" s="339"/>
-      <c r="AI8" s="338"/>
-      <c r="AJ8" s="306"/>
-      <c r="AK8" s="311"/>
-      <c r="AL8" s="306"/>
-      <c r="AM8" s="305"/>
-      <c r="AN8" s="327"/>
+      <c r="A8" s="309"/>
+      <c r="B8" s="346"/>
+      <c r="C8" s="330"/>
+      <c r="D8" s="309"/>
+      <c r="E8" s="309"/>
+      <c r="F8" s="309"/>
+      <c r="G8" s="309"/>
+      <c r="H8" s="309"/>
+      <c r="I8" s="309"/>
+      <c r="J8" s="309"/>
+      <c r="K8" s="309"/>
+      <c r="L8" s="309"/>
+      <c r="M8" s="309"/>
+      <c r="N8" s="309"/>
+      <c r="O8" s="322"/>
+      <c r="P8" s="323"/>
+      <c r="Q8" s="323"/>
+      <c r="R8" s="323"/>
+      <c r="S8" s="323"/>
+      <c r="T8" s="323"/>
+      <c r="U8" s="323"/>
+      <c r="V8" s="324"/>
+      <c r="W8" s="309"/>
+      <c r="X8" s="309"/>
+      <c r="Y8" s="309"/>
+      <c r="Z8" s="309"/>
+      <c r="AA8" s="309"/>
+      <c r="AB8" s="309"/>
+      <c r="AC8" s="325"/>
+      <c r="AD8" s="327"/>
+      <c r="AE8" s="309"/>
+      <c r="AF8" s="306"/>
+      <c r="AG8" s="306"/>
+      <c r="AH8" s="307"/>
+      <c r="AI8" s="306"/>
+      <c r="AJ8" s="309"/>
+      <c r="AK8" s="308"/>
+      <c r="AL8" s="309"/>
+      <c r="AM8" s="303"/>
+      <c r="AN8" s="304"/>
     </row>
     <row r="9" spans="1:43" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="306"/>
-      <c r="B9" s="347"/>
-      <c r="C9" s="308"/>
-      <c r="D9" s="306"/>
-      <c r="E9" s="306"/>
-      <c r="F9" s="306"/>
-      <c r="G9" s="306"/>
-      <c r="H9" s="306"/>
-      <c r="I9" s="306"/>
-      <c r="J9" s="306"/>
-      <c r="K9" s="306"/>
-      <c r="L9" s="306"/>
-      <c r="M9" s="306"/>
-      <c r="N9" s="306"/>
-      <c r="O9" s="334"/>
-      <c r="P9" s="335"/>
-      <c r="Q9" s="335"/>
-      <c r="R9" s="335"/>
-      <c r="S9" s="335"/>
-      <c r="T9" s="335"/>
-      <c r="U9" s="335"/>
-      <c r="V9" s="336"/>
-      <c r="W9" s="306"/>
-      <c r="X9" s="306"/>
-      <c r="Y9" s="306"/>
-      <c r="Z9" s="306"/>
-      <c r="AA9" s="306"/>
-      <c r="AB9" s="306"/>
+      <c r="A9" s="309"/>
+      <c r="B9" s="346"/>
+      <c r="C9" s="330"/>
+      <c r="D9" s="309"/>
+      <c r="E9" s="309"/>
+      <c r="F9" s="309"/>
+      <c r="G9" s="309"/>
+      <c r="H9" s="309"/>
+      <c r="I9" s="309"/>
+      <c r="J9" s="309"/>
+      <c r="K9" s="309"/>
+      <c r="L9" s="309"/>
+      <c r="M9" s="309"/>
+      <c r="N9" s="309"/>
+      <c r="O9" s="325"/>
+      <c r="P9" s="326"/>
+      <c r="Q9" s="326"/>
+      <c r="R9" s="326"/>
+      <c r="S9" s="326"/>
+      <c r="T9" s="326"/>
+      <c r="U9" s="326"/>
+      <c r="V9" s="327"/>
+      <c r="W9" s="309"/>
+      <c r="X9" s="309"/>
+      <c r="Y9" s="309"/>
+      <c r="Z9" s="309"/>
+      <c r="AA9" s="309"/>
+      <c r="AB9" s="309"/>
       <c r="AC9" s="201" t="s">
         <v>153</v>
       </c>
       <c r="AD9" s="178" t="s">
         <v>154</v>
       </c>
-      <c r="AE9" s="306"/>
-      <c r="AF9" s="338"/>
-      <c r="AG9" s="338"/>
-      <c r="AH9" s="339"/>
-      <c r="AI9" s="338"/>
-      <c r="AJ9" s="306"/>
-      <c r="AK9" s="311"/>
-      <c r="AL9" s="306"/>
-      <c r="AM9" s="305"/>
-      <c r="AN9" s="327"/>
+      <c r="AE9" s="309"/>
+      <c r="AF9" s="306"/>
+      <c r="AG9" s="306"/>
+      <c r="AH9" s="307"/>
+      <c r="AI9" s="306"/>
+      <c r="AJ9" s="309"/>
+      <c r="AK9" s="308"/>
+      <c r="AL9" s="309"/>
+      <c r="AM9" s="303"/>
+      <c r="AN9" s="304"/>
       <c r="AO9">
         <f>Z11/W11</f>
         <v>0.50320398224028773</v>
@@ -22378,6 +22375,27 @@
   </sheetData>
   <autoFilter ref="A10:AQ73" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="37">
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AD8"/>
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A2:AB2"/>
@@ -22394,27 +22412,6 @@
     <mergeCell ref="H7:H9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:J9"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AD8"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
   </mergeCells>
   <pageMargins left="0.17" right="0.15748031496062992" top="0.41" bottom="0.23622047244094491" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
@@ -22432,7 +22429,7 @@
     <col min="4" max="11" width="8.7109375" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="12.140625" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="10.7109375" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" style="268" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" style="267" customWidth="1"/>
     <col min="15" max="15" width="13.140625" customWidth="1"/>
     <col min="16" max="16" width="10.7109375" customWidth="1"/>
     <col min="17" max="17" width="10.5703125" customWidth="1"/>
@@ -22459,49 +22456,49 @@
     <col min="41" max="41" width="17.5703125" customWidth="1"/>
     <col min="42" max="42" width="12.28515625" customWidth="1"/>
     <col min="43" max="43" width="12.140625" customWidth="1"/>
-    <col min="44" max="44" width="15" style="268" customWidth="1"/>
+    <col min="44" max="44" width="15" style="267" customWidth="1"/>
     <col min="45" max="45" width="13.140625" customWidth="1"/>
     <col min="46" max="48" width="0" hidden="1" customWidth="1"/>
     <col min="51" max="51" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="319" t="s">
+      <c r="A1" s="310" t="s">
         <v>206</v>
       </c>
-      <c r="B1" s="320"/>
-      <c r="C1" s="321"/>
-      <c r="D1" s="320"/>
-      <c r="E1" s="320"/>
-      <c r="F1" s="320"/>
-      <c r="G1" s="320"/>
-      <c r="H1" s="320"/>
-      <c r="I1" s="320"/>
-      <c r="J1" s="320"/>
-      <c r="K1" s="320"/>
-      <c r="L1" s="320"/>
-      <c r="M1" s="320"/>
-      <c r="N1" s="320"/>
-      <c r="O1" s="320"/>
-      <c r="P1" s="320"/>
-      <c r="Q1" s="320"/>
-      <c r="R1" s="320"/>
-      <c r="S1" s="320"/>
-      <c r="T1" s="320"/>
-      <c r="U1" s="320"/>
-      <c r="V1" s="320"/>
-      <c r="W1" s="320"/>
-      <c r="X1" s="320"/>
-      <c r="Y1" s="320"/>
-      <c r="Z1" s="321"/>
-      <c r="AA1" s="320"/>
-      <c r="AB1" s="320"/>
-      <c r="AC1" s="322"/>
-      <c r="AD1" s="262"/>
-      <c r="AE1" s="262"/>
-      <c r="AF1" s="262"/>
-      <c r="AG1" s="262"/>
-      <c r="AH1" s="262"/>
+      <c r="B1" s="311"/>
+      <c r="C1" s="312"/>
+      <c r="D1" s="311"/>
+      <c r="E1" s="311"/>
+      <c r="F1" s="311"/>
+      <c r="G1" s="311"/>
+      <c r="H1" s="311"/>
+      <c r="I1" s="311"/>
+      <c r="J1" s="311"/>
+      <c r="K1" s="311"/>
+      <c r="L1" s="311"/>
+      <c r="M1" s="311"/>
+      <c r="N1" s="311"/>
+      <c r="O1" s="311"/>
+      <c r="P1" s="311"/>
+      <c r="Q1" s="311"/>
+      <c r="R1" s="311"/>
+      <c r="S1" s="311"/>
+      <c r="T1" s="311"/>
+      <c r="U1" s="311"/>
+      <c r="V1" s="311"/>
+      <c r="W1" s="311"/>
+      <c r="X1" s="311"/>
+      <c r="Y1" s="311"/>
+      <c r="Z1" s="312"/>
+      <c r="AA1" s="311"/>
+      <c r="AB1" s="311"/>
+      <c r="AC1" s="313"/>
+      <c r="AD1" s="261"/>
+      <c r="AE1" s="261"/>
+      <c r="AF1" s="261"/>
+      <c r="AG1" s="261"/>
+      <c r="AH1" s="261"/>
       <c r="AI1" s="1"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
@@ -22513,48 +22510,48 @@
       </c>
       <c r="AP1" s="3"/>
       <c r="AQ1" s="3"/>
-      <c r="AR1" s="296" t="s">
+      <c r="AR1" s="295" t="s">
         <v>227</v>
       </c>
       <c r="AS1" s="160"/>
     </row>
     <row r="2" spans="1:51" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="323" t="s">
+      <c r="A2" s="314" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="320"/>
-      <c r="C2" s="321"/>
-      <c r="D2" s="320"/>
-      <c r="E2" s="320"/>
-      <c r="F2" s="320"/>
-      <c r="G2" s="320"/>
-      <c r="H2" s="320"/>
-      <c r="I2" s="320"/>
-      <c r="J2" s="320"/>
-      <c r="K2" s="320"/>
-      <c r="L2" s="320"/>
-      <c r="M2" s="320"/>
-      <c r="N2" s="320"/>
-      <c r="O2" s="320"/>
-      <c r="P2" s="320"/>
-      <c r="Q2" s="320"/>
-      <c r="R2" s="320"/>
-      <c r="S2" s="320"/>
-      <c r="T2" s="320"/>
-      <c r="U2" s="320"/>
-      <c r="V2" s="320"/>
-      <c r="W2" s="320"/>
-      <c r="X2" s="320"/>
-      <c r="Y2" s="320"/>
-      <c r="Z2" s="321"/>
-      <c r="AA2" s="320"/>
-      <c r="AB2" s="320"/>
-      <c r="AC2" s="322"/>
-      <c r="AD2" s="262"/>
-      <c r="AE2" s="262"/>
-      <c r="AF2" s="262"/>
-      <c r="AG2" s="262"/>
-      <c r="AH2" s="262"/>
+      <c r="B2" s="311"/>
+      <c r="C2" s="312"/>
+      <c r="D2" s="311"/>
+      <c r="E2" s="311"/>
+      <c r="F2" s="311"/>
+      <c r="G2" s="311"/>
+      <c r="H2" s="311"/>
+      <c r="I2" s="311"/>
+      <c r="J2" s="311"/>
+      <c r="K2" s="311"/>
+      <c r="L2" s="311"/>
+      <c r="M2" s="311"/>
+      <c r="N2" s="311"/>
+      <c r="O2" s="311"/>
+      <c r="P2" s="311"/>
+      <c r="Q2" s="311"/>
+      <c r="R2" s="311"/>
+      <c r="S2" s="311"/>
+      <c r="T2" s="311"/>
+      <c r="U2" s="311"/>
+      <c r="V2" s="311"/>
+      <c r="W2" s="311"/>
+      <c r="X2" s="311"/>
+      <c r="Y2" s="311"/>
+      <c r="Z2" s="312"/>
+      <c r="AA2" s="311"/>
+      <c r="AB2" s="311"/>
+      <c r="AC2" s="313"/>
+      <c r="AD2" s="261"/>
+      <c r="AE2" s="261"/>
+      <c r="AF2" s="261"/>
+      <c r="AG2" s="261"/>
+      <c r="AH2" s="261"/>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
@@ -22564,7 +22561,7 @@
       <c r="AO2" s="3"/>
       <c r="AP2" s="3"/>
       <c r="AQ2" s="3"/>
-      <c r="AR2" s="297"/>
+      <c r="AR2" s="296"/>
       <c r="AS2" s="161"/>
     </row>
     <row r="3" spans="1:51" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -22611,106 +22608,106 @@
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
       <c r="AQ3" s="3"/>
-      <c r="AR3" s="296"/>
+      <c r="AR3" s="295"/>
       <c r="AS3" s="160"/>
     </row>
     <row r="4" spans="1:51" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="324" t="s">
+      <c r="A4" s="315" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="320"/>
-      <c r="C4" s="321"/>
-      <c r="D4" s="320"/>
-      <c r="E4" s="320"/>
-      <c r="F4" s="320"/>
-      <c r="G4" s="320"/>
-      <c r="H4" s="320"/>
-      <c r="I4" s="320"/>
-      <c r="J4" s="320"/>
-      <c r="K4" s="320"/>
-      <c r="L4" s="320"/>
-      <c r="M4" s="320"/>
-      <c r="N4" s="320"/>
-      <c r="O4" s="320"/>
-      <c r="P4" s="320"/>
-      <c r="Q4" s="320"/>
-      <c r="R4" s="320"/>
-      <c r="S4" s="320"/>
-      <c r="T4" s="320"/>
-      <c r="U4" s="320"/>
-      <c r="V4" s="320"/>
-      <c r="W4" s="320"/>
-      <c r="X4" s="320"/>
-      <c r="Y4" s="320"/>
-      <c r="Z4" s="321"/>
-      <c r="AA4" s="320"/>
-      <c r="AB4" s="320"/>
-      <c r="AC4" s="320"/>
-      <c r="AD4" s="321"/>
-      <c r="AE4" s="321"/>
-      <c r="AF4" s="321"/>
-      <c r="AG4" s="321"/>
-      <c r="AH4" s="321"/>
-      <c r="AI4" s="320"/>
-      <c r="AJ4" s="320"/>
-      <c r="AK4" s="321"/>
-      <c r="AL4" s="321"/>
-      <c r="AM4" s="320"/>
-      <c r="AN4" s="321"/>
-      <c r="AO4" s="321"/>
-      <c r="AP4" s="320"/>
-      <c r="AQ4" s="321"/>
-      <c r="AR4" s="321"/>
-      <c r="AS4" s="322"/>
+      <c r="B4" s="311"/>
+      <c r="C4" s="312"/>
+      <c r="D4" s="311"/>
+      <c r="E4" s="311"/>
+      <c r="F4" s="311"/>
+      <c r="G4" s="311"/>
+      <c r="H4" s="311"/>
+      <c r="I4" s="311"/>
+      <c r="J4" s="311"/>
+      <c r="K4" s="311"/>
+      <c r="L4" s="311"/>
+      <c r="M4" s="311"/>
+      <c r="N4" s="311"/>
+      <c r="O4" s="311"/>
+      <c r="P4" s="311"/>
+      <c r="Q4" s="311"/>
+      <c r="R4" s="311"/>
+      <c r="S4" s="311"/>
+      <c r="T4" s="311"/>
+      <c r="U4" s="311"/>
+      <c r="V4" s="311"/>
+      <c r="W4" s="311"/>
+      <c r="X4" s="311"/>
+      <c r="Y4" s="311"/>
+      <c r="Z4" s="312"/>
+      <c r="AA4" s="311"/>
+      <c r="AB4" s="311"/>
+      <c r="AC4" s="311"/>
+      <c r="AD4" s="312"/>
+      <c r="AE4" s="312"/>
+      <c r="AF4" s="312"/>
+      <c r="AG4" s="312"/>
+      <c r="AH4" s="312"/>
+      <c r="AI4" s="311"/>
+      <c r="AJ4" s="311"/>
+      <c r="AK4" s="312"/>
+      <c r="AL4" s="312"/>
+      <c r="AM4" s="311"/>
+      <c r="AN4" s="312"/>
+      <c r="AO4" s="312"/>
+      <c r="AP4" s="311"/>
+      <c r="AQ4" s="312"/>
+      <c r="AR4" s="312"/>
+      <c r="AS4" s="313"/>
     </row>
     <row r="5" spans="1:51" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="325" t="s">
+      <c r="A5" s="316" t="s">
         <v>224</v>
       </c>
-      <c r="B5" s="320"/>
-      <c r="C5" s="321"/>
-      <c r="D5" s="320"/>
-      <c r="E5" s="320"/>
-      <c r="F5" s="320"/>
-      <c r="G5" s="320"/>
-      <c r="H5" s="320"/>
-      <c r="I5" s="320"/>
-      <c r="J5" s="320"/>
-      <c r="K5" s="320"/>
-      <c r="L5" s="320"/>
-      <c r="M5" s="320"/>
-      <c r="N5" s="320"/>
-      <c r="O5" s="320"/>
-      <c r="P5" s="320"/>
-      <c r="Q5" s="320"/>
-      <c r="R5" s="320"/>
-      <c r="S5" s="320"/>
-      <c r="T5" s="320"/>
-      <c r="U5" s="320"/>
-      <c r="V5" s="320"/>
-      <c r="W5" s="320"/>
-      <c r="X5" s="320"/>
-      <c r="Y5" s="320"/>
-      <c r="Z5" s="321"/>
-      <c r="AA5" s="320"/>
-      <c r="AB5" s="320"/>
-      <c r="AC5" s="320"/>
-      <c r="AD5" s="321"/>
-      <c r="AE5" s="321"/>
-      <c r="AF5" s="321"/>
-      <c r="AG5" s="321"/>
-      <c r="AH5" s="321"/>
-      <c r="AI5" s="320"/>
-      <c r="AJ5" s="320"/>
-      <c r="AK5" s="321"/>
-      <c r="AL5" s="321"/>
-      <c r="AM5" s="320"/>
-      <c r="AN5" s="321"/>
-      <c r="AO5" s="321"/>
-      <c r="AP5" s="320"/>
-      <c r="AQ5" s="321"/>
-      <c r="AR5" s="321"/>
-      <c r="AS5" s="322"/>
+      <c r="B5" s="311"/>
+      <c r="C5" s="312"/>
+      <c r="D5" s="311"/>
+      <c r="E5" s="311"/>
+      <c r="F5" s="311"/>
+      <c r="G5" s="311"/>
+      <c r="H5" s="311"/>
+      <c r="I5" s="311"/>
+      <c r="J5" s="311"/>
+      <c r="K5" s="311"/>
+      <c r="L5" s="311"/>
+      <c r="M5" s="311"/>
+      <c r="N5" s="311"/>
+      <c r="O5" s="311"/>
+      <c r="P5" s="311"/>
+      <c r="Q5" s="311"/>
+      <c r="R5" s="311"/>
+      <c r="S5" s="311"/>
+      <c r="T5" s="311"/>
+      <c r="U5" s="311"/>
+      <c r="V5" s="311"/>
+      <c r="W5" s="311"/>
+      <c r="X5" s="311"/>
+      <c r="Y5" s="311"/>
+      <c r="Z5" s="312"/>
+      <c r="AA5" s="311"/>
+      <c r="AB5" s="311"/>
+      <c r="AC5" s="311"/>
+      <c r="AD5" s="312"/>
+      <c r="AE5" s="312"/>
+      <c r="AF5" s="312"/>
+      <c r="AG5" s="312"/>
+      <c r="AH5" s="312"/>
+      <c r="AI5" s="311"/>
+      <c r="AJ5" s="311"/>
+      <c r="AK5" s="312"/>
+      <c r="AL5" s="312"/>
+      <c r="AM5" s="311"/>
+      <c r="AN5" s="312"/>
+      <c r="AO5" s="312"/>
+      <c r="AP5" s="311"/>
+      <c r="AQ5" s="312"/>
+      <c r="AR5" s="312"/>
+      <c r="AS5" s="313"/>
     </row>
     <row r="6" spans="1:51" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -22746,241 +22743,241 @@
       <c r="AC6" s="11"/>
       <c r="AD6" s="11"/>
       <c r="AE6" s="11"/>
-      <c r="AF6" s="304" t="s">
+      <c r="AF6" s="328" t="s">
         <v>151</v>
       </c>
-      <c r="AG6" s="304"/>
-      <c r="AH6" s="304"/>
-      <c r="AI6" s="304"/>
-      <c r="AJ6" s="304"/>
-      <c r="AK6" s="304"/>
-      <c r="AL6" s="304"/>
-      <c r="AM6" s="304"/>
-      <c r="AN6" s="304"/>
-      <c r="AO6" s="304"/>
-      <c r="AP6" s="304"/>
-      <c r="AQ6" s="304"/>
-      <c r="AR6" s="304"/>
-      <c r="AS6" s="304"/>
+      <c r="AG6" s="328"/>
+      <c r="AH6" s="328"/>
+      <c r="AI6" s="328"/>
+      <c r="AJ6" s="328"/>
+      <c r="AK6" s="328"/>
+      <c r="AL6" s="328"/>
+      <c r="AM6" s="328"/>
+      <c r="AN6" s="328"/>
+      <c r="AO6" s="328"/>
+      <c r="AP6" s="328"/>
+      <c r="AQ6" s="328"/>
+      <c r="AR6" s="328"/>
+      <c r="AS6" s="328"/>
     </row>
     <row r="7" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="305" t="s">
+      <c r="A7" s="303" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="305" t="s">
+      <c r="B7" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="308" t="s">
+      <c r="C7" s="330" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="305" t="s">
+      <c r="D7" s="303" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="305" t="s">
+      <c r="E7" s="303" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="305" t="s">
+      <c r="F7" s="303" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="305" t="s">
+      <c r="G7" s="303" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="305" t="s">
+      <c r="H7" s="303" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="305" t="s">
+      <c r="I7" s="303" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="305" t="s">
+      <c r="J7" s="303" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="305" t="s">
+      <c r="K7" s="303" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="326" t="s">
+      <c r="L7" s="318" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="305" t="s">
+      <c r="M7" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="305" t="s">
+      <c r="N7" s="303" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="328" t="s">
+      <c r="O7" s="319" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="329"/>
-      <c r="Q7" s="329"/>
-      <c r="R7" s="329"/>
-      <c r="S7" s="329"/>
-      <c r="T7" s="329"/>
-      <c r="U7" s="329"/>
-      <c r="V7" s="330"/>
-      <c r="W7" s="305" t="s">
+      <c r="P7" s="320"/>
+      <c r="Q7" s="320"/>
+      <c r="R7" s="320"/>
+      <c r="S7" s="320"/>
+      <c r="T7" s="320"/>
+      <c r="U7" s="320"/>
+      <c r="V7" s="321"/>
+      <c r="W7" s="303" t="s">
         <v>202</v>
       </c>
-      <c r="X7" s="309" t="s">
+      <c r="X7" s="317" t="s">
         <v>13</v>
       </c>
-      <c r="Y7" s="309" t="s">
+      <c r="Y7" s="317" t="s">
         <v>221</v>
       </c>
-      <c r="Z7" s="316" t="s">
+      <c r="Z7" s="336" t="s">
         <v>222</v>
       </c>
-      <c r="AA7" s="310" t="s">
+      <c r="AA7" s="331" t="s">
         <v>223</v>
       </c>
-      <c r="AB7" s="305" t="s">
+      <c r="AB7" s="303" t="s">
         <v>15</v>
       </c>
-      <c r="AC7" s="305" t="s">
+      <c r="AC7" s="303" t="s">
         <v>16</v>
       </c>
-      <c r="AD7" s="312" t="s">
+      <c r="AD7" s="332" t="s">
         <v>211</v>
       </c>
-      <c r="AE7" s="312"/>
-      <c r="AF7" s="312"/>
-      <c r="AG7" s="313" t="s">
+      <c r="AE7" s="332"/>
+      <c r="AF7" s="332"/>
+      <c r="AG7" s="333" t="s">
         <v>215</v>
       </c>
-      <c r="AH7" s="313" t="s">
+      <c r="AH7" s="333" t="s">
         <v>219</v>
       </c>
-      <c r="AI7" s="311" t="s">
+      <c r="AI7" s="308" t="s">
         <v>17</v>
       </c>
-      <c r="AJ7" s="337" t="s">
+      <c r="AJ7" s="305" t="s">
         <v>107</v>
       </c>
-      <c r="AK7" s="337" t="s">
+      <c r="AK7" s="305" t="s">
         <v>108</v>
       </c>
-      <c r="AL7" s="337" t="s">
+      <c r="AL7" s="305" t="s">
         <v>106</v>
       </c>
-      <c r="AM7" s="339" t="s">
+      <c r="AM7" s="307" t="s">
         <v>147</v>
       </c>
-      <c r="AN7" s="311" t="s">
+      <c r="AN7" s="308" t="s">
         <v>136</v>
       </c>
-      <c r="AO7" s="311" t="s">
+      <c r="AO7" s="308" t="s">
         <v>137</v>
       </c>
-      <c r="AP7" s="305" t="s">
+      <c r="AP7" s="303" t="s">
         <v>135</v>
       </c>
-      <c r="AQ7" s="305" t="s">
+      <c r="AQ7" s="303" t="s">
         <v>146</v>
       </c>
-      <c r="AR7" s="305" t="s">
+      <c r="AR7" s="303" t="s">
         <v>228</v>
       </c>
-      <c r="AS7" s="305" t="s">
+      <c r="AS7" s="303" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A8" s="306"/>
-      <c r="B8" s="307"/>
-      <c r="C8" s="308"/>
-      <c r="D8" s="306"/>
-      <c r="E8" s="306"/>
-      <c r="F8" s="306"/>
-      <c r="G8" s="306"/>
-      <c r="H8" s="306"/>
-      <c r="I8" s="306"/>
-      <c r="J8" s="306"/>
-      <c r="K8" s="306"/>
-      <c r="L8" s="306"/>
-      <c r="M8" s="306"/>
-      <c r="N8" s="327"/>
-      <c r="O8" s="331"/>
-      <c r="P8" s="332"/>
-      <c r="Q8" s="332"/>
-      <c r="R8" s="332"/>
-      <c r="S8" s="332"/>
-      <c r="T8" s="332"/>
-      <c r="U8" s="332"/>
-      <c r="V8" s="333"/>
-      <c r="W8" s="306"/>
-      <c r="X8" s="306"/>
-      <c r="Y8" s="306"/>
-      <c r="Z8" s="317"/>
-      <c r="AA8" s="306"/>
-      <c r="AB8" s="306"/>
-      <c r="AC8" s="306"/>
-      <c r="AD8" s="312"/>
-      <c r="AE8" s="312"/>
-      <c r="AF8" s="312"/>
-      <c r="AG8" s="314"/>
-      <c r="AH8" s="314"/>
-      <c r="AI8" s="306"/>
-      <c r="AJ8" s="338"/>
-      <c r="AK8" s="338"/>
-      <c r="AL8" s="339"/>
-      <c r="AM8" s="338"/>
-      <c r="AN8" s="306"/>
-      <c r="AO8" s="311"/>
-      <c r="AP8" s="306"/>
-      <c r="AQ8" s="305"/>
-      <c r="AR8" s="305"/>
-      <c r="AS8" s="327"/>
+      <c r="A8" s="309"/>
+      <c r="B8" s="329"/>
+      <c r="C8" s="330"/>
+      <c r="D8" s="309"/>
+      <c r="E8" s="309"/>
+      <c r="F8" s="309"/>
+      <c r="G8" s="309"/>
+      <c r="H8" s="309"/>
+      <c r="I8" s="309"/>
+      <c r="J8" s="309"/>
+      <c r="K8" s="309"/>
+      <c r="L8" s="309"/>
+      <c r="M8" s="309"/>
+      <c r="N8" s="304"/>
+      <c r="O8" s="322"/>
+      <c r="P8" s="323"/>
+      <c r="Q8" s="323"/>
+      <c r="R8" s="323"/>
+      <c r="S8" s="323"/>
+      <c r="T8" s="323"/>
+      <c r="U8" s="323"/>
+      <c r="V8" s="324"/>
+      <c r="W8" s="309"/>
+      <c r="X8" s="309"/>
+      <c r="Y8" s="309"/>
+      <c r="Z8" s="337"/>
+      <c r="AA8" s="309"/>
+      <c r="AB8" s="309"/>
+      <c r="AC8" s="309"/>
+      <c r="AD8" s="332"/>
+      <c r="AE8" s="332"/>
+      <c r="AF8" s="332"/>
+      <c r="AG8" s="334"/>
+      <c r="AH8" s="334"/>
+      <c r="AI8" s="309"/>
+      <c r="AJ8" s="306"/>
+      <c r="AK8" s="306"/>
+      <c r="AL8" s="307"/>
+      <c r="AM8" s="306"/>
+      <c r="AN8" s="309"/>
+      <c r="AO8" s="308"/>
+      <c r="AP8" s="309"/>
+      <c r="AQ8" s="303"/>
+      <c r="AR8" s="303"/>
+      <c r="AS8" s="304"/>
     </row>
     <row r="9" spans="1:51" ht="104.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="306"/>
-      <c r="B9" s="307"/>
-      <c r="C9" s="308"/>
-      <c r="D9" s="306"/>
-      <c r="E9" s="306"/>
-      <c r="F9" s="306"/>
-      <c r="G9" s="306"/>
-      <c r="H9" s="306"/>
-      <c r="I9" s="306"/>
-      <c r="J9" s="306"/>
-      <c r="K9" s="306"/>
-      <c r="L9" s="306"/>
-      <c r="M9" s="306"/>
-      <c r="N9" s="327"/>
-      <c r="O9" s="334"/>
-      <c r="P9" s="335"/>
-      <c r="Q9" s="335"/>
-      <c r="R9" s="335"/>
-      <c r="S9" s="335"/>
-      <c r="T9" s="335"/>
-      <c r="U9" s="335"/>
-      <c r="V9" s="336"/>
-      <c r="W9" s="306"/>
-      <c r="X9" s="306"/>
-      <c r="Y9" s="306"/>
-      <c r="Z9" s="318"/>
-      <c r="AA9" s="306"/>
-      <c r="AB9" s="306"/>
-      <c r="AC9" s="306"/>
-      <c r="AD9" s="265" t="s">
+      <c r="A9" s="309"/>
+      <c r="B9" s="329"/>
+      <c r="C9" s="330"/>
+      <c r="D9" s="309"/>
+      <c r="E9" s="309"/>
+      <c r="F9" s="309"/>
+      <c r="G9" s="309"/>
+      <c r="H9" s="309"/>
+      <c r="I9" s="309"/>
+      <c r="J9" s="309"/>
+      <c r="K9" s="309"/>
+      <c r="L9" s="309"/>
+      <c r="M9" s="309"/>
+      <c r="N9" s="304"/>
+      <c r="O9" s="325"/>
+      <c r="P9" s="326"/>
+      <c r="Q9" s="326"/>
+      <c r="R9" s="326"/>
+      <c r="S9" s="326"/>
+      <c r="T9" s="326"/>
+      <c r="U9" s="326"/>
+      <c r="V9" s="327"/>
+      <c r="W9" s="309"/>
+      <c r="X9" s="309"/>
+      <c r="Y9" s="309"/>
+      <c r="Z9" s="338"/>
+      <c r="AA9" s="309"/>
+      <c r="AB9" s="309"/>
+      <c r="AC9" s="309"/>
+      <c r="AD9" s="264" t="s">
         <v>212</v>
       </c>
-      <c r="AE9" s="265" t="s">
+      <c r="AE9" s="264" t="s">
         <v>214</v>
       </c>
-      <c r="AF9" s="265" t="s">
+      <c r="AF9" s="264" t="s">
         <v>213</v>
       </c>
-      <c r="AG9" s="315"/>
-      <c r="AH9" s="315"/>
-      <c r="AI9" s="306"/>
-      <c r="AJ9" s="338"/>
-      <c r="AK9" s="338"/>
-      <c r="AL9" s="339"/>
-      <c r="AM9" s="338"/>
-      <c r="AN9" s="306"/>
-      <c r="AO9" s="311"/>
-      <c r="AP9" s="306"/>
-      <c r="AQ9" s="305"/>
-      <c r="AR9" s="305"/>
-      <c r="AS9" s="327"/>
+      <c r="AG9" s="335"/>
+      <c r="AH9" s="335"/>
+      <c r="AI9" s="309"/>
+      <c r="AJ9" s="306"/>
+      <c r="AK9" s="306"/>
+      <c r="AL9" s="307"/>
+      <c r="AM9" s="306"/>
+      <c r="AN9" s="309"/>
+      <c r="AO9" s="308"/>
+      <c r="AP9" s="309"/>
+      <c r="AQ9" s="303"/>
+      <c r="AR9" s="303"/>
+      <c r="AS9" s="304"/>
       <c r="AT9">
         <f>AA12/W12</f>
         <v>0.7450786614439131</v>
@@ -23051,17 +23048,17 @@
       <c r="AC10" s="28">
         <v>8</v>
       </c>
-      <c r="AD10" s="263">
+      <c r="AD10" s="262">
         <v>9</v>
       </c>
-      <c r="AE10" s="263">
+      <c r="AE10" s="262">
         <v>10</v>
       </c>
-      <c r="AF10" s="263">
+      <c r="AF10" s="262">
         <v>11</v>
       </c>
-      <c r="AG10" s="263"/>
-      <c r="AH10" s="263"/>
+      <c r="AG10" s="262"/>
+      <c r="AH10" s="262"/>
       <c r="AI10" s="243">
         <v>12</v>
       </c>
@@ -23082,7 +23079,7 @@
     </row>
     <row r="11" spans="1:51" ht="22.15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28"/>
-      <c r="B11" s="283" t="s">
+      <c r="B11" s="282" t="s">
         <v>225</v>
       </c>
       <c r="C11" s="103"/>
@@ -23096,66 +23093,66 @@
       <c r="K11" s="28"/>
       <c r="L11" s="28"/>
       <c r="M11" s="28"/>
-      <c r="N11" s="288">
+      <c r="N11" s="287">
         <f>N12</f>
         <v>890720</v>
       </c>
-      <c r="O11" s="289"/>
-      <c r="P11" s="290"/>
-      <c r="Q11" s="290"/>
-      <c r="R11" s="290"/>
-      <c r="S11" s="290"/>
-      <c r="T11" s="290"/>
-      <c r="U11" s="290"/>
-      <c r="V11" s="290"/>
-      <c r="W11" s="288">
+      <c r="O11" s="288"/>
+      <c r="P11" s="289"/>
+      <c r="Q11" s="289"/>
+      <c r="R11" s="289"/>
+      <c r="S11" s="289"/>
+      <c r="T11" s="289"/>
+      <c r="U11" s="289"/>
+      <c r="V11" s="289"/>
+      <c r="W11" s="287">
         <f>W12+39020</f>
         <v>1007347</v>
       </c>
-      <c r="X11" s="291"/>
-      <c r="Y11" s="291"/>
-      <c r="Z11" s="291"/>
-      <c r="AA11" s="292">
+      <c r="X11" s="290"/>
+      <c r="Y11" s="290"/>
+      <c r="Z11" s="290"/>
+      <c r="AA11" s="291">
         <f>AA12</f>
         <v>721479.78500000003</v>
       </c>
-      <c r="AB11" s="293">
+      <c r="AB11" s="292">
         <f>AA11/W11</f>
         <v>0.71621773331334693</v>
       </c>
-      <c r="AC11" s="294">
+      <c r="AC11" s="293">
         <f>AC12</f>
         <v>0.80999616602299263</v>
       </c>
-      <c r="AD11" s="295">
+      <c r="AD11" s="294">
         <f>AD12</f>
         <v>57013</v>
       </c>
-      <c r="AE11" s="295">
+      <c r="AE11" s="294">
         <f>AE12</f>
         <v>67533.5</v>
       </c>
-      <c r="AF11" s="295">
+      <c r="AF11" s="294">
         <f>AF12</f>
         <v>-10520.5</v>
       </c>
-      <c r="AG11" s="284"/>
-      <c r="AH11" s="284"/>
-      <c r="AI11" s="285"/>
-      <c r="AJ11" s="282"/>
-      <c r="AK11" s="282"/>
-      <c r="AL11" s="282"/>
-      <c r="AM11" s="286"/>
-      <c r="AN11" s="282"/>
-      <c r="AO11" s="282"/>
-      <c r="AP11" s="282"/>
-      <c r="AQ11" s="282"/>
-      <c r="AR11" s="298"/>
-      <c r="AS11" s="282"/>
+      <c r="AG11" s="283"/>
+      <c r="AH11" s="283"/>
+      <c r="AI11" s="284"/>
+      <c r="AJ11" s="281"/>
+      <c r="AK11" s="281"/>
+      <c r="AL11" s="281"/>
+      <c r="AM11" s="285"/>
+      <c r="AN11" s="281"/>
+      <c r="AO11" s="281"/>
+      <c r="AP11" s="281"/>
+      <c r="AQ11" s="281"/>
+      <c r="AR11" s="297"/>
+      <c r="AS11" s="281"/>
     </row>
     <row r="12" spans="1:51" s="102" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="96"/>
-      <c r="B12" s="283" t="s">
+      <c r="B12" s="282" t="s">
         <v>226</v>
       </c>
       <c r="C12" s="104"/>
@@ -23199,7 +23196,7 @@
         <f>SUBTOTAL(9,M13:M67)</f>
         <v>997557.30800000019</v>
       </c>
-      <c r="N12" s="266">
+      <c r="N12" s="265">
         <f>SUBTOTAL(9,N13:N74)</f>
         <v>890720</v>
       </c>
@@ -23484,16 +23481,16 @@
       <c r="AC14" s="63">
         <v>0</v>
       </c>
-      <c r="AD14" s="270"/>
+      <c r="AD14" s="269"/>
       <c r="AE14" s="177">
         <v>0</v>
       </c>
-      <c r="AF14" s="270">
+      <c r="AF14" s="269">
         <f>AD14-AE14</f>
         <v>0</v>
       </c>
-      <c r="AG14" s="270"/>
-      <c r="AH14" s="270"/>
+      <c r="AG14" s="269"/>
+      <c r="AH14" s="269"/>
       <c r="AI14" s="33">
         <f>W14-AA14</f>
         <v>0</v>
@@ -23518,7 +23515,7 @@
         <f>W14-AA14</f>
         <v>0</v>
       </c>
-      <c r="AR14" s="299" t="s">
+      <c r="AR14" s="298" t="s">
         <v>229</v>
       </c>
       <c r="AS14" s="141" t="s">
@@ -23605,16 +23602,16 @@
         <f>0%</f>
         <v>0</v>
       </c>
-      <c r="AD15" s="270"/>
+      <c r="AD15" s="269"/>
       <c r="AE15" s="177">
         <v>0</v>
       </c>
-      <c r="AF15" s="270">
+      <c r="AF15" s="269">
         <f t="shared" ref="AF15:AF74" si="5">AD15-AE15</f>
         <v>0</v>
       </c>
-      <c r="AG15" s="270"/>
-      <c r="AH15" s="270"/>
+      <c r="AG15" s="269"/>
+      <c r="AH15" s="269"/>
       <c r="AI15" s="33">
         <f>W15-AA15</f>
         <v>0</v>
@@ -23638,7 +23635,7 @@
         <f>W15-AA15</f>
         <v>0</v>
       </c>
-      <c r="AR15" s="299" t="s">
+      <c r="AR15" s="298" t="s">
         <v>229</v>
       </c>
       <c r="AS15" s="141" t="s">
@@ -23695,14 +23692,14 @@
       </c>
       <c r="AB16" s="154"/>
       <c r="AC16" s="63"/>
-      <c r="AD16" s="270"/>
+      <c r="AD16" s="269"/>
       <c r="AE16" s="177"/>
-      <c r="AF16" s="270">
+      <c r="AF16" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG16" s="270"/>
-      <c r="AH16" s="270"/>
+      <c r="AG16" s="269"/>
+      <c r="AH16" s="269"/>
       <c r="AI16" s="33">
         <f>W16-AA16</f>
         <v>0</v>
@@ -23792,14 +23789,14 @@
         <f>0%</f>
         <v>0</v>
       </c>
-      <c r="AD17" s="270"/>
+      <c r="AD17" s="269"/>
       <c r="AE17" s="177"/>
-      <c r="AF17" s="270">
+      <c r="AF17" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG17" s="270"/>
-      <c r="AH17" s="270"/>
+      <c r="AG17" s="269"/>
+      <c r="AH17" s="269"/>
       <c r="AI17" s="33">
         <f>W17-AA17</f>
         <v>0</v>
@@ -23824,7 +23821,7 @@
         <f t="shared" ref="AQ17" si="7">W17-AA17</f>
         <v>0</v>
       </c>
-      <c r="AR17" s="300" t="s">
+      <c r="AR17" s="299" t="s">
         <v>230</v>
       </c>
       <c r="AS17" s="144" t="s">
@@ -23868,14 +23865,14 @@
       </c>
       <c r="AB18" s="63"/>
       <c r="AC18" s="63"/>
-      <c r="AD18" s="270"/>
+      <c r="AD18" s="269"/>
       <c r="AE18" s="177"/>
-      <c r="AF18" s="270">
+      <c r="AF18" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG18" s="270"/>
-      <c r="AH18" s="270"/>
+      <c r="AG18" s="269"/>
+      <c r="AH18" s="269"/>
       <c r="AI18" s="33"/>
       <c r="AJ18" s="64"/>
       <c r="AK18" s="64"/>
@@ -23951,25 +23948,25 @@
         <v>50</v>
       </c>
       <c r="AB19" s="63">
-        <f t="shared" ref="AB19:AB22" si="8">AA19/W19</f>
+        <f t="shared" ref="AB19:AB74" si="8">AA19/W19</f>
         <v>1</v>
       </c>
       <c r="AC19" s="63">
         <f t="shared" ref="AC19" si="9">AA19/N19</f>
         <v>1</v>
       </c>
-      <c r="AD19" s="270"/>
+      <c r="AD19" s="269"/>
       <c r="AE19" s="177">
         <v>50</v>
       </c>
-      <c r="AF19" s="270">
+      <c r="AF19" s="269">
         <f t="shared" si="5"/>
         <v>-50</v>
       </c>
-      <c r="AG19" s="270" t="s">
+      <c r="AG19" s="269" t="s">
         <v>216</v>
       </c>
-      <c r="AH19" s="270">
+      <c r="AH19" s="269">
         <v>50</v>
       </c>
       <c r="AI19" s="33">
@@ -23996,7 +23993,7 @@
         <f>W19-AA19</f>
         <v>0</v>
       </c>
-      <c r="AR19" s="301" t="s">
+      <c r="AR19" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS19" s="166"/>
@@ -24065,20 +24062,20 @@
         <f>AA20/W20</f>
         <v>0.24731729361593788</v>
       </c>
-      <c r="AD20" s="270">
+      <c r="AD20" s="269">
         <v>1600</v>
       </c>
       <c r="AE20" s="177">
         <v>1639</v>
       </c>
-      <c r="AF20" s="270">
+      <c r="AF20" s="269">
         <f t="shared" si="5"/>
         <v>-39</v>
       </c>
-      <c r="AG20" s="270" t="s">
+      <c r="AG20" s="269" t="s">
         <v>217</v>
       </c>
-      <c r="AH20" s="270">
+      <c r="AH20" s="269">
         <v>1600</v>
       </c>
       <c r="AI20" s="33">
@@ -24107,7 +24104,7 @@
         <f t="shared" ref="AQ20:AQ22" si="11">W20-AA20</f>
         <v>11825.398000000001</v>
       </c>
-      <c r="AR20" s="300" t="s">
+      <c r="AR20" s="299" t="s">
         <v>230</v>
       </c>
       <c r="AS20" s="147" t="s">
@@ -24176,19 +24173,19 @@
         <f t="shared" ref="AC21" si="12">AA21/N21</f>
         <v>0.80421377717391307</v>
       </c>
-      <c r="AD21" s="270">
+      <c r="AD21" s="269">
         <v>0</v>
       </c>
       <c r="AE21" s="177">
         <f>100+3017</f>
         <v>3117</v>
       </c>
-      <c r="AF21" s="270">
+      <c r="AF21" s="269">
         <f t="shared" si="5"/>
         <v>-3117</v>
       </c>
-      <c r="AG21" s="270"/>
-      <c r="AH21" s="270"/>
+      <c r="AG21" s="269"/>
+      <c r="AH21" s="269"/>
       <c r="AI21" s="33">
         <f t="shared" si="10"/>
         <v>7204.9330000000009</v>
@@ -24215,7 +24212,7 @@
         <f t="shared" si="11"/>
         <v>7204.9330000000009</v>
       </c>
-      <c r="AR21" s="300" t="s">
+      <c r="AR21" s="299" t="s">
         <v>230</v>
       </c>
       <c r="AS21" s="169"/>
@@ -24286,20 +24283,20 @@
         <f>AA22/N22</f>
         <v>0.95975060827250602</v>
       </c>
-      <c r="AD22" s="270">
+      <c r="AD22" s="269">
         <v>863</v>
       </c>
       <c r="AE22" s="177">
         <v>863</v>
       </c>
-      <c r="AF22" s="270">
+      <c r="AF22" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG22" s="270" t="s">
+      <c r="AG22" s="269" t="s">
         <v>217</v>
       </c>
-      <c r="AH22" s="270">
+      <c r="AH22" s="269">
         <v>863</v>
       </c>
       <c r="AI22" s="33">
@@ -24328,7 +24325,7 @@
         <f t="shared" si="11"/>
         <v>132.34000000000015</v>
       </c>
-      <c r="AR22" s="301" t="s">
+      <c r="AR22" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS22" s="167"/>
@@ -24390,16 +24387,19 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB23" s="63"/>
+      <c r="AB23" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AC23" s="63"/>
-      <c r="AD23" s="271"/>
+      <c r="AD23" s="270"/>
       <c r="AE23" s="177"/>
-      <c r="AF23" s="270">
+      <c r="AF23" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG23" s="270"/>
-      <c r="AH23" s="270"/>
+      <c r="AG23" s="269"/>
+      <c r="AH23" s="269"/>
       <c r="AI23" s="33">
         <f t="shared" si="10"/>
         <v>6</v>
@@ -24468,16 +24468,19 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB24" s="63"/>
+      <c r="AB24" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AC24" s="63"/>
-      <c r="AD24" s="271"/>
+      <c r="AD24" s="270"/>
       <c r="AE24" s="177"/>
-      <c r="AF24" s="270">
+      <c r="AF24" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG24" s="270"/>
-      <c r="AH24" s="270"/>
+      <c r="AG24" s="269"/>
+      <c r="AH24" s="269"/>
       <c r="AI24" s="33">
         <f t="shared" si="10"/>
         <v>23</v>
@@ -24533,7 +24536,7 @@
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="X25" s="279">
+      <c r="X25" s="278">
         <v>3.2639999999999998</v>
       </c>
       <c r="Y25" s="210"/>
@@ -24542,20 +24545,23 @@
         <f t="shared" si="4"/>
         <v>3.2639999999999998</v>
       </c>
-      <c r="AB25" s="63"/>
+      <c r="AB25" s="63">
+        <f t="shared" si="8"/>
+        <v>0.81599999999999995</v>
+      </c>
       <c r="AC25" s="63"/>
-      <c r="AD25" s="271">
+      <c r="AD25" s="270">
         <v>4</v>
       </c>
       <c r="AE25" s="210">
         <v>4</v>
       </c>
-      <c r="AF25" s="270">
+      <c r="AF25" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG25" s="270"/>
-      <c r="AH25" s="270"/>
+      <c r="AG25" s="269"/>
+      <c r="AH25" s="269"/>
       <c r="AI25" s="33">
         <f t="shared" si="10"/>
         <v>0.73600000000000021</v>
@@ -24620,20 +24626,23 @@
         <f t="shared" si="4"/>
         <v>5.54</v>
       </c>
-      <c r="AB26" s="63"/>
+      <c r="AB26" s="63">
+        <f t="shared" si="8"/>
+        <v>0.92333333333333334</v>
+      </c>
       <c r="AC26" s="63"/>
-      <c r="AD26" s="271">
+      <c r="AD26" s="270">
         <v>1</v>
       </c>
       <c r="AE26" s="210">
         <v>0.5</v>
       </c>
-      <c r="AF26" s="270">
+      <c r="AF26" s="269">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="AG26" s="270"/>
-      <c r="AH26" s="270"/>
+      <c r="AG26" s="269"/>
+      <c r="AH26" s="269"/>
       <c r="AI26" s="33">
         <f t="shared" si="10"/>
         <v>0.45999999999999996</v>
@@ -24646,7 +24655,7 @@
       <c r="AO26" s="126"/>
       <c r="AP26" s="77"/>
       <c r="AQ26" s="157"/>
-      <c r="AR26" s="301" t="s">
+      <c r="AR26" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS26" s="167"/>
@@ -24689,7 +24698,7 @@
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="X27" s="279">
+      <c r="X27" s="278">
         <v>5.1639999999999997</v>
       </c>
       <c r="Y27" s="210"/>
@@ -24698,20 +24707,23 @@
         <f t="shared" si="4"/>
         <v>5.1639999999999997</v>
       </c>
-      <c r="AB27" s="63"/>
+      <c r="AB27" s="63">
+        <f t="shared" si="8"/>
+        <v>0.86066666666666658</v>
+      </c>
       <c r="AC27" s="63"/>
-      <c r="AD27" s="271">
+      <c r="AD27" s="270">
         <v>6</v>
       </c>
       <c r="AE27" s="210">
         <v>6</v>
       </c>
-      <c r="AF27" s="270">
+      <c r="AF27" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG27" s="270"/>
-      <c r="AH27" s="270"/>
+      <c r="AG27" s="269"/>
+      <c r="AH27" s="269"/>
       <c r="AI27" s="33">
         <f t="shared" si="10"/>
         <v>0.8360000000000003</v>
@@ -24767,7 +24779,7 @@
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="X28" s="280">
+      <c r="X28" s="279">
         <v>3.97</v>
       </c>
       <c r="Y28" s="210"/>
@@ -24776,20 +24788,23 @@
         <f t="shared" si="4"/>
         <v>3.97</v>
       </c>
-      <c r="AB28" s="63"/>
+      <c r="AB28" s="63">
+        <f t="shared" si="8"/>
+        <v>0.99250000000000005</v>
+      </c>
       <c r="AC28" s="63"/>
-      <c r="AD28" s="271">
+      <c r="AD28" s="270">
         <v>1</v>
       </c>
-      <c r="AE28" s="281">
+      <c r="AE28" s="280">
         <v>1</v>
       </c>
-      <c r="AF28" s="270">
+      <c r="AF28" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG28" s="270"/>
-      <c r="AH28" s="270"/>
+      <c r="AG28" s="269"/>
+      <c r="AH28" s="269"/>
       <c r="AI28" s="33">
         <f t="shared" si="10"/>
         <v>2.9999999999999805E-2</v>
@@ -24802,7 +24817,7 @@
       <c r="AO28" s="126"/>
       <c r="AP28" s="77"/>
       <c r="AQ28" s="157"/>
-      <c r="AR28" s="301" t="s">
+      <c r="AR28" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS28" s="167"/>
@@ -24828,7 +24843,7 @@
       <c r="K29" s="59"/>
       <c r="L29" s="33"/>
       <c r="M29" s="34"/>
-      <c r="N29" s="287">
+      <c r="N29" s="286">
         <v>43</v>
       </c>
       <c r="O29" s="35"/>
@@ -24845,7 +24860,7 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="X29" s="278">
+      <c r="X29" s="277">
         <v>42.15</v>
       </c>
       <c r="Y29" s="210"/>
@@ -24854,20 +24869,23 @@
         <f t="shared" si="4"/>
         <v>42.15</v>
       </c>
-      <c r="AB29" s="63"/>
+      <c r="AB29" s="63">
+        <f t="shared" si="8"/>
+        <v>0.9802325581395348</v>
+      </c>
       <c r="AC29" s="63"/>
-      <c r="AD29" s="271">
+      <c r="AD29" s="270">
         <v>36</v>
       </c>
       <c r="AE29" s="210">
         <v>36</v>
       </c>
-      <c r="AF29" s="270">
+      <c r="AF29" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG29" s="270"/>
-      <c r="AH29" s="270"/>
+      <c r="AG29" s="269"/>
+      <c r="AH29" s="269"/>
       <c r="AI29" s="33">
         <f t="shared" si="10"/>
         <v>0.85000000000000142</v>
@@ -24880,12 +24898,12 @@
       <c r="AO29" s="126"/>
       <c r="AP29" s="77"/>
       <c r="AQ29" s="157"/>
-      <c r="AR29" s="299" t="s">
+      <c r="AR29" s="298" t="s">
         <v>229</v>
       </c>
       <c r="AS29" s="167"/>
       <c r="AT29" s="18"/>
-      <c r="AY29" s="269"/>
+      <c r="AY29" s="268"/>
     </row>
     <row r="30" spans="1:51" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="30">
@@ -24933,20 +24951,23 @@
         <f t="shared" si="4"/>
         <v>44.32</v>
       </c>
-      <c r="AB30" s="63"/>
+      <c r="AB30" s="63">
+        <f t="shared" si="8"/>
+        <v>0.98488888888888892</v>
+      </c>
       <c r="AC30" s="63"/>
-      <c r="AD30" s="271">
+      <c r="AD30" s="270">
         <v>45</v>
       </c>
       <c r="AE30" s="210">
         <v>44.32</v>
       </c>
-      <c r="AF30" s="270">
+      <c r="AF30" s="269">
         <f t="shared" si="5"/>
         <v>0.67999999999999972</v>
       </c>
-      <c r="AG30" s="270"/>
-      <c r="AH30" s="270"/>
+      <c r="AG30" s="269"/>
+      <c r="AH30" s="269"/>
       <c r="AI30" s="33">
         <f t="shared" si="10"/>
         <v>0.67999999999999972</v>
@@ -24959,7 +24980,7 @@
       <c r="AO30" s="126"/>
       <c r="AP30" s="77"/>
       <c r="AQ30" s="157"/>
-      <c r="AR30" s="301" t="s">
+      <c r="AR30" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS30" s="167"/>
@@ -25011,20 +25032,23 @@
         <f t="shared" si="4"/>
         <v>73.800000000000011</v>
       </c>
-      <c r="AB31" s="63"/>
+      <c r="AB31" s="63">
+        <f t="shared" si="8"/>
+        <v>0.99729729729729744</v>
+      </c>
       <c r="AC31" s="63"/>
-      <c r="AD31" s="271">
+      <c r="AD31" s="270">
         <v>37</v>
       </c>
       <c r="AE31" s="210">
         <v>36.700000000000003</v>
       </c>
-      <c r="AF31" s="270">
+      <c r="AF31" s="269">
         <f t="shared" si="5"/>
         <v>0.29999999999999716</v>
       </c>
-      <c r="AG31" s="270"/>
-      <c r="AH31" s="270"/>
+      <c r="AG31" s="269"/>
+      <c r="AH31" s="269"/>
       <c r="AI31" s="33">
         <f t="shared" si="10"/>
         <v>0.19999999999998863</v>
@@ -25037,7 +25061,7 @@
       <c r="AO31" s="126"/>
       <c r="AP31" s="77"/>
       <c r="AQ31" s="157"/>
-      <c r="AR31" s="301" t="s">
+      <c r="AR31" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS31" s="167"/>
@@ -25080,7 +25104,7 @@
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="X32" s="279">
+      <c r="X32" s="278">
         <v>3.28</v>
       </c>
       <c r="Y32" s="210"/>
@@ -25089,20 +25113,23 @@
         <f t="shared" si="4"/>
         <v>3.28</v>
       </c>
-      <c r="AB32" s="63"/>
+      <c r="AB32" s="63">
+        <f t="shared" si="8"/>
+        <v>0.82</v>
+      </c>
       <c r="AC32" s="63"/>
-      <c r="AD32" s="271">
+      <c r="AD32" s="270">
         <v>4</v>
       </c>
       <c r="AE32" s="210">
         <v>3.28</v>
       </c>
-      <c r="AF32" s="270">
+      <c r="AF32" s="269">
         <f t="shared" si="5"/>
         <v>0.7200000000000002</v>
       </c>
-      <c r="AG32" s="270"/>
-      <c r="AH32" s="270"/>
+      <c r="AG32" s="269"/>
+      <c r="AH32" s="269"/>
       <c r="AI32" s="33">
         <f t="shared" si="10"/>
         <v>0.7200000000000002</v>
@@ -25167,20 +25194,23 @@
         <f t="shared" si="4"/>
         <v>8.6999999999999993</v>
       </c>
-      <c r="AB33" s="63"/>
+      <c r="AB33" s="63">
+        <f t="shared" si="8"/>
+        <v>0.96666666666666656</v>
+      </c>
       <c r="AC33" s="63"/>
-      <c r="AD33" s="271">
+      <c r="AD33" s="270">
         <v>9</v>
       </c>
       <c r="AE33" s="210">
         <v>8.6999999999999993</v>
       </c>
-      <c r="AF33" s="270">
+      <c r="AF33" s="269">
         <f t="shared" si="5"/>
         <v>0.30000000000000071</v>
       </c>
-      <c r="AG33" s="270"/>
-      <c r="AH33" s="270"/>
+      <c r="AG33" s="269"/>
+      <c r="AH33" s="269"/>
       <c r="AI33" s="33">
         <f t="shared" si="10"/>
         <v>0.30000000000000071</v>
@@ -25245,20 +25275,23 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="AB34" s="63"/>
+      <c r="AB34" s="63">
+        <f t="shared" si="8"/>
+        <v>0.9</v>
+      </c>
       <c r="AC34" s="63"/>
-      <c r="AD34" s="271">
+      <c r="AD34" s="270">
         <v>2</v>
       </c>
       <c r="AE34" s="210">
         <v>1</v>
       </c>
-      <c r="AF34" s="270">
+      <c r="AF34" s="269">
         <f>AD34-AE34</f>
         <v>1</v>
       </c>
-      <c r="AG34" s="270"/>
-      <c r="AH34" s="270"/>
+      <c r="AG34" s="269"/>
+      <c r="AH34" s="269"/>
       <c r="AI34" s="33">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -25271,7 +25304,7 @@
       <c r="AO34" s="126"/>
       <c r="AP34" s="77"/>
       <c r="AQ34" s="157"/>
-      <c r="AR34" s="301" t="s">
+      <c r="AR34" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS34" s="167"/>
@@ -25312,16 +25345,19 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB35" s="63"/>
+      <c r="AB35" s="63" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AC35" s="63"/>
-      <c r="AD35" s="271"/>
+      <c r="AD35" s="270"/>
       <c r="AE35" s="177"/>
-      <c r="AF35" s="270">
+      <c r="AF35" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG35" s="270"/>
-      <c r="AH35" s="270"/>
+      <c r="AG35" s="269"/>
+      <c r="AH35" s="269"/>
       <c r="AI35" s="33">
         <f t="shared" si="10"/>
         <v>0</v>
@@ -25340,7 +25376,7 @@
       <c r="AO35" s="126"/>
       <c r="AP35" s="67"/>
       <c r="AQ35" s="64"/>
-      <c r="AR35" s="302"/>
+      <c r="AR35" s="301"/>
       <c r="AS35" s="170"/>
     </row>
     <row r="36" spans="1:49" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -25403,23 +25439,23 @@
         <v>6453.44</v>
       </c>
       <c r="AB36" s="63">
-        <f>AA36/W36</f>
+        <f t="shared" si="8"/>
         <v>0.99055103607060624</v>
       </c>
       <c r="AC36" s="63">
         <f>AA36/N36</f>
         <v>0.99055103607060624</v>
       </c>
-      <c r="AD36" s="271"/>
+      <c r="AD36" s="270"/>
       <c r="AE36" s="177">
         <v>450</v>
       </c>
-      <c r="AF36" s="270">
+      <c r="AF36" s="269">
         <f t="shared" si="5"/>
         <v>-450</v>
       </c>
-      <c r="AG36" s="270"/>
-      <c r="AH36" s="270"/>
+      <c r="AG36" s="269"/>
+      <c r="AH36" s="269"/>
       <c r="AI36" s="33">
         <f t="shared" si="10"/>
         <v>61.5600000000004</v>
@@ -25446,7 +25482,7 @@
         <f>W36-AA36</f>
         <v>61.5600000000004</v>
       </c>
-      <c r="AR36" s="300" t="s">
+      <c r="AR36" s="299" t="s">
         <v>230</v>
       </c>
       <c r="AS36" s="168"/>
@@ -25506,21 +25542,21 @@
         <v>936.10699999999997</v>
       </c>
       <c r="AB37" s="63">
-        <f t="shared" ref="AB37:AB61" si="15">AA37/W37</f>
+        <f t="shared" si="8"/>
         <v>0.7749230132450331</v>
       </c>
       <c r="AC37" s="63">
-        <f t="shared" ref="AC37:AC61" si="16">AA37/N37</f>
+        <f t="shared" ref="AC37:AC61" si="15">AA37/N37</f>
         <v>0.7749230132450331</v>
       </c>
-      <c r="AD37" s="271"/>
+      <c r="AD37" s="270"/>
       <c r="AE37" s="177"/>
-      <c r="AF37" s="270">
+      <c r="AF37" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG37" s="270"/>
-      <c r="AH37" s="270"/>
+      <c r="AG37" s="269"/>
+      <c r="AH37" s="269"/>
       <c r="AI37" s="33">
         <f t="shared" si="10"/>
         <v>271.89300000000003</v>
@@ -25542,10 +25578,10 @@
       </c>
       <c r="AP37" s="67"/>
       <c r="AQ37" s="64">
-        <f t="shared" ref="AQ37:AQ62" si="17">W37-AA37</f>
+        <f t="shared" ref="AQ37:AQ62" si="16">W37-AA37</f>
         <v>271.89300000000003</v>
       </c>
-      <c r="AR37" s="299" t="s">
+      <c r="AR37" s="298" t="s">
         <v>229</v>
       </c>
       <c r="AS37" s="169"/>
@@ -25608,24 +25644,24 @@
         <f t="shared" si="4"/>
         <v>9615.2000000000007</v>
       </c>
-      <c r="AB38" s="39">
-        <f>AA38/W38</f>
+      <c r="AB38" s="63">
+        <f t="shared" si="8"/>
         <v>0.66311724137931038</v>
       </c>
       <c r="AC38" s="39">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0.76921600000000001</v>
       </c>
-      <c r="AD38" s="271">
+      <c r="AD38" s="270">
         <v>3500</v>
       </c>
       <c r="AE38" s="177"/>
-      <c r="AF38" s="270">
+      <c r="AF38" s="269">
         <f t="shared" si="5"/>
         <v>3500</v>
       </c>
-      <c r="AG38" s="270"/>
-      <c r="AH38" s="270"/>
+      <c r="AG38" s="269"/>
+      <c r="AH38" s="269"/>
       <c r="AI38" s="33">
         <f t="shared" si="10"/>
         <v>4884.7999999999993</v>
@@ -25649,10 +25685,10 @@
       </c>
       <c r="AP38" s="67"/>
       <c r="AQ38" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>4884.7999999999993</v>
       </c>
-      <c r="AR38" s="301" t="s">
+      <c r="AR38" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS38" s="167"/>
@@ -25717,14 +25753,14 @@
         <v>28818.329999999998</v>
       </c>
       <c r="AB39" s="63">
+        <f t="shared" si="8"/>
+        <v>0.73672137433852281</v>
+      </c>
+      <c r="AC39" s="63">
         <f t="shared" si="15"/>
-        <v>0.73672137433852281</v>
-      </c>
-      <c r="AC39" s="63">
-        <f t="shared" si="16"/>
         <v>0.65322506063422259</v>
       </c>
-      <c r="AD39" s="271">
+      <c r="AD39" s="270">
         <f>7900</f>
         <v>7900</v>
       </c>
@@ -25732,14 +25768,14 @@
         <f>7931+148+200</f>
         <v>8279</v>
       </c>
-      <c r="AF39" s="270">
+      <c r="AF39" s="269">
         <f t="shared" si="5"/>
         <v>-379</v>
       </c>
-      <c r="AG39" s="270" t="s">
+      <c r="AG39" s="269" t="s">
         <v>220</v>
       </c>
-      <c r="AH39" s="270">
+      <c r="AH39" s="269">
         <v>148</v>
       </c>
       <c r="AI39" s="33">
@@ -25765,10 +25801,10 @@
       </c>
       <c r="AP39" s="122"/>
       <c r="AQ39" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>10298.670000000002</v>
       </c>
-      <c r="AR39" s="299" t="s">
+      <c r="AR39" s="298" t="s">
         <v>229</v>
       </c>
       <c r="AS39" s="166"/>
@@ -25827,28 +25863,28 @@
         <v>33629.99</v>
       </c>
       <c r="AB40" s="63">
+        <f t="shared" si="8"/>
+        <v>0.66701025407088599</v>
+      </c>
+      <c r="AC40" s="63">
         <f t="shared" si="15"/>
-        <v>0.66701025407088599</v>
-      </c>
-      <c r="AC40" s="63">
-        <f t="shared" si="16"/>
         <v>0.69028489911533486</v>
       </c>
-      <c r="AD40" s="271">
+      <c r="AD40" s="270">
         <v>10000</v>
       </c>
       <c r="AE40" s="177">
         <f>80+11394</f>
         <v>11474</v>
       </c>
-      <c r="AF40" s="270">
+      <c r="AF40" s="269">
         <f t="shared" si="5"/>
         <v>-1474</v>
       </c>
-      <c r="AG40" s="270" t="s">
+      <c r="AG40" s="269" t="s">
         <v>218</v>
       </c>
-      <c r="AH40" s="270">
+      <c r="AH40" s="269">
         <v>11382</v>
       </c>
       <c r="AI40" s="33">
@@ -25874,7 +25910,7 @@
       </c>
       <c r="AP40" s="67"/>
       <c r="AQ40" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>16789.010000000002</v>
       </c>
       <c r="AR40" s="122" t="s">
@@ -25940,26 +25976,26 @@
         <v>48007.9</v>
       </c>
       <c r="AB41" s="63">
+        <f t="shared" si="8"/>
+        <v>0.79433303550746226</v>
+      </c>
+      <c r="AC41" s="63">
         <f t="shared" si="15"/>
         <v>0.79433303550746226</v>
       </c>
-      <c r="AC41" s="63">
-        <f t="shared" si="16"/>
-        <v>0.79433303550746226</v>
-      </c>
-      <c r="AD41" s="271">
+      <c r="AD41" s="270">
         <v>10000</v>
       </c>
       <c r="AE41" s="177">
         <f>10933+300</f>
         <v>11233</v>
       </c>
-      <c r="AF41" s="270">
+      <c r="AF41" s="269">
         <f t="shared" si="5"/>
         <v>-1233</v>
       </c>
-      <c r="AG41" s="270"/>
-      <c r="AH41" s="270"/>
+      <c r="AG41" s="269"/>
+      <c r="AH41" s="269"/>
       <c r="AI41" s="33">
         <f t="shared" si="10"/>
         <v>12430.099999999999</v>
@@ -25983,10 +26019,10 @@
       </c>
       <c r="AP41" s="64"/>
       <c r="AQ41" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>12430.099999999999</v>
       </c>
-      <c r="AR41" s="301" t="s">
+      <c r="AR41" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS41" s="169"/>
@@ -26048,21 +26084,21 @@
         <v>0</v>
       </c>
       <c r="AB42" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AC42" s="63">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC42" s="63">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AD42" s="271"/>
+      <c r="AD42" s="270"/>
       <c r="AE42" s="177"/>
-      <c r="AF42" s="270">
+      <c r="AF42" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG42" s="270"/>
-      <c r="AH42" s="270"/>
+      <c r="AG42" s="269"/>
+      <c r="AH42" s="269"/>
       <c r="AI42" s="33">
         <f t="shared" si="10"/>
         <v>420</v>
@@ -26084,10 +26120,10 @@
       </c>
       <c r="AP42" s="128"/>
       <c r="AQ42" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>420</v>
       </c>
-      <c r="AR42" s="301" t="s">
+      <c r="AR42" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS42" s="169"/>
@@ -26150,21 +26186,21 @@
         <v>0</v>
       </c>
       <c r="AB43" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AC43" s="63">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC43" s="63">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AD43" s="271"/>
+      <c r="AD43" s="270"/>
       <c r="AE43" s="177"/>
-      <c r="AF43" s="270">
+      <c r="AF43" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG43" s="270"/>
-      <c r="AH43" s="270"/>
+      <c r="AG43" s="269"/>
+      <c r="AH43" s="269"/>
       <c r="AI43" s="33">
         <f t="shared" si="10"/>
         <v>125</v>
@@ -26186,7 +26222,7 @@
       </c>
       <c r="AP43" s="64"/>
       <c r="AQ43" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>125</v>
       </c>
       <c r="AR43" s="122" t="s">
@@ -26254,20 +26290,21 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB44" s="78">
-        <v>0</v>
+      <c r="AB44" s="63" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="AC44" s="63">
         <v>0</v>
       </c>
-      <c r="AD44" s="271"/>
+      <c r="AD44" s="270"/>
       <c r="AE44" s="177"/>
-      <c r="AF44" s="270">
+      <c r="AF44" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG44" s="270"/>
-      <c r="AH44" s="270"/>
+      <c r="AG44" s="269"/>
+      <c r="AH44" s="269"/>
       <c r="AI44" s="33">
         <f t="shared" si="10"/>
         <v>0</v>
@@ -26289,10 +26326,10 @@
       </c>
       <c r="AP44" s="64"/>
       <c r="AQ44" s="64">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AR44" s="300" t="s">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AR44" s="299" t="s">
         <v>230</v>
       </c>
       <c r="AS44" s="174" t="s">
@@ -26357,21 +26394,22 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB45" s="78">
-        <v>0</v>
+      <c r="AB45" s="63" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="AC45" s="63">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AD45" s="271"/>
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AD45" s="270"/>
       <c r="AE45" s="177"/>
-      <c r="AF45" s="270">
+      <c r="AF45" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG45" s="270"/>
-      <c r="AH45" s="270"/>
+      <c r="AG45" s="269"/>
+      <c r="AH45" s="269"/>
       <c r="AI45" s="33">
         <f t="shared" si="10"/>
         <v>0</v>
@@ -26393,10 +26431,10 @@
       </c>
       <c r="AP45" s="67"/>
       <c r="AQ45" s="64">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AR45" s="299" t="s">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AR45" s="298" t="s">
         <v>229</v>
       </c>
       <c r="AS45" s="166"/>
@@ -26457,21 +26495,21 @@
         <v>0</v>
       </c>
       <c r="AB46" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AC46" s="63">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC46" s="63">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AD46" s="271"/>
+      <c r="AD46" s="270"/>
       <c r="AE46" s="177"/>
-      <c r="AF46" s="270">
+      <c r="AF46" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG46" s="270"/>
-      <c r="AH46" s="270"/>
+      <c r="AG46" s="269"/>
+      <c r="AH46" s="269"/>
       <c r="AI46" s="33">
         <f t="shared" si="10"/>
         <v>191</v>
@@ -26493,10 +26531,10 @@
       </c>
       <c r="AP46" s="64"/>
       <c r="AQ46" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>191</v>
       </c>
-      <c r="AR46" s="301" t="s">
+      <c r="AR46" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS46" s="167"/>
@@ -26559,21 +26597,21 @@
         <v>0</v>
       </c>
       <c r="AB47" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AC47" s="63">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC47" s="63">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AD47" s="271"/>
+      <c r="AD47" s="270"/>
       <c r="AE47" s="177"/>
-      <c r="AF47" s="270">
+      <c r="AF47" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG47" s="270"/>
-      <c r="AH47" s="270"/>
+      <c r="AG47" s="269"/>
+      <c r="AH47" s="269"/>
       <c r="AI47" s="33">
         <f t="shared" si="10"/>
         <v>33</v>
@@ -26595,7 +26633,7 @@
       </c>
       <c r="AP47" s="67"/>
       <c r="AQ47" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>33</v>
       </c>
       <c r="AR47" s="122" t="s">
@@ -26657,21 +26695,21 @@
         <v>0</v>
       </c>
       <c r="AB48" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AC48" s="63">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC48" s="63">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AD48" s="270"/>
+      <c r="AD48" s="269"/>
       <c r="AE48" s="177"/>
-      <c r="AF48" s="270">
+      <c r="AF48" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG48" s="270"/>
-      <c r="AH48" s="270"/>
+      <c r="AG48" s="269"/>
+      <c r="AH48" s="269"/>
       <c r="AI48" s="33">
         <f t="shared" si="10"/>
         <v>10</v>
@@ -26693,10 +26731,10 @@
       </c>
       <c r="AP48" s="67"/>
       <c r="AQ48" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>10</v>
       </c>
-      <c r="AR48" s="301" t="s">
+      <c r="AR48" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS48" s="166"/>
@@ -26752,21 +26790,21 @@
         <v>0</v>
       </c>
       <c r="AB49" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AC49" s="63">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC49" s="63">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AD49" s="270"/>
+      <c r="AD49" s="269"/>
       <c r="AE49" s="177"/>
-      <c r="AF49" s="270">
+      <c r="AF49" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG49" s="270"/>
-      <c r="AH49" s="270"/>
+      <c r="AG49" s="269"/>
+      <c r="AH49" s="269"/>
       <c r="AI49" s="33">
         <f t="shared" si="10"/>
         <v>10</v>
@@ -26788,7 +26826,7 @@
       </c>
       <c r="AP49" s="64"/>
       <c r="AQ49" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>10</v>
       </c>
       <c r="AR49" s="122" t="s">
@@ -26847,21 +26885,21 @@
         <v>0</v>
       </c>
       <c r="AB50" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AC50" s="63">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC50" s="63">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AD50" s="270"/>
+      <c r="AD50" s="269"/>
       <c r="AE50" s="177"/>
-      <c r="AF50" s="270">
+      <c r="AF50" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG50" s="270"/>
-      <c r="AH50" s="270"/>
+      <c r="AG50" s="269"/>
+      <c r="AH50" s="269"/>
       <c r="AI50" s="33">
         <f t="shared" si="10"/>
         <v>20</v>
@@ -26883,10 +26921,10 @@
       </c>
       <c r="AP50" s="67"/>
       <c r="AQ50" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
-      <c r="AR50" s="299" t="s">
+      <c r="AR50" s="298" t="s">
         <v>229</v>
       </c>
       <c r="AS50" s="166"/>
@@ -26942,23 +26980,23 @@
         <v>0</v>
       </c>
       <c r="AB51" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AC51" s="63">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC51" s="63">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AD51" s="270"/>
+      <c r="AD51" s="269"/>
       <c r="AE51" s="177"/>
-      <c r="AF51" s="270">
+      <c r="AF51" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG51" s="270"/>
-      <c r="AH51" s="270"/>
+      <c r="AG51" s="269"/>
+      <c r="AH51" s="269"/>
       <c r="AI51" s="33">
-        <f t="shared" ref="AI51:AI74" si="18">W51-AA51</f>
+        <f t="shared" ref="AI51:AI74" si="17">W51-AA51</f>
         <v>50</v>
       </c>
       <c r="AJ51" s="64"/>
@@ -26978,10 +27016,10 @@
       </c>
       <c r="AP51" s="67"/>
       <c r="AQ51" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>50</v>
       </c>
-      <c r="AR51" s="299" t="s">
+      <c r="AR51" s="298" t="s">
         <v>229</v>
       </c>
       <c r="AS51" s="166"/>
@@ -27039,25 +27077,25 @@
         <v>0</v>
       </c>
       <c r="AB52" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AC52" s="63">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC52" s="63">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AD52" s="270"/>
+      <c r="AD52" s="269"/>
       <c r="AE52" s="177">
         <v>0</v>
       </c>
-      <c r="AF52" s="270">
+      <c r="AF52" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG52" s="270"/>
-      <c r="AH52" s="270"/>
+      <c r="AG52" s="269"/>
+      <c r="AH52" s="269"/>
       <c r="AI52" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>50</v>
       </c>
       <c r="AJ52" s="64"/>
@@ -27077,10 +27115,10 @@
       </c>
       <c r="AP52" s="67"/>
       <c r="AQ52" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>50</v>
       </c>
-      <c r="AR52" s="301" t="s">
+      <c r="AR52" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS52" s="171"/>
@@ -27140,23 +27178,23 @@
         <v>0</v>
       </c>
       <c r="AB53" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AC53" s="63">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC53" s="63">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AD53" s="270"/>
+      <c r="AD53" s="269"/>
       <c r="AE53" s="177"/>
-      <c r="AF53" s="270">
+      <c r="AF53" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG53" s="270"/>
-      <c r="AH53" s="270"/>
+      <c r="AG53" s="269"/>
+      <c r="AH53" s="269"/>
       <c r="AI53" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>15</v>
       </c>
       <c r="AJ53" s="64"/>
@@ -27176,10 +27214,10 @@
       </c>
       <c r="AP53" s="67"/>
       <c r="AQ53" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>15</v>
       </c>
-      <c r="AR53" s="301" t="s">
+      <c r="AR53" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS53" s="167"/>
@@ -27239,23 +27277,23 @@
         <v>0</v>
       </c>
       <c r="AB54" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AC54" s="63">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC54" s="63">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AD54" s="270"/>
+      <c r="AD54" s="269"/>
       <c r="AE54" s="177"/>
-      <c r="AF54" s="270">
+      <c r="AF54" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG54" s="270"/>
-      <c r="AH54" s="270"/>
+      <c r="AG54" s="269"/>
+      <c r="AH54" s="269"/>
       <c r="AI54" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>33</v>
       </c>
       <c r="AJ54" s="64"/>
@@ -27275,7 +27313,7 @@
       </c>
       <c r="AP54" s="67"/>
       <c r="AQ54" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>33</v>
       </c>
       <c r="AR54" s="122" t="s">
@@ -27334,23 +27372,23 @@
         <v>0</v>
       </c>
       <c r="AB55" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AC55" s="63">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC55" s="63">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AD55" s="270"/>
+      <c r="AD55" s="269"/>
       <c r="AE55" s="177"/>
-      <c r="AF55" s="270">
+      <c r="AF55" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG55" s="270"/>
-      <c r="AH55" s="270"/>
+      <c r="AG55" s="269"/>
+      <c r="AH55" s="269"/>
       <c r="AI55" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>50</v>
       </c>
       <c r="AJ55" s="64"/>
@@ -27370,10 +27408,10 @@
       </c>
       <c r="AP55" s="67"/>
       <c r="AQ55" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>50</v>
       </c>
-      <c r="AR55" s="301" t="s">
+      <c r="AR55" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS55" s="167"/>
@@ -27429,23 +27467,23 @@
         <v>0</v>
       </c>
       <c r="AB56" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AC56" s="63">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC56" s="63">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AD56" s="270"/>
+      <c r="AD56" s="269"/>
       <c r="AE56" s="177"/>
-      <c r="AF56" s="270">
+      <c r="AF56" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG56" s="270"/>
-      <c r="AH56" s="270"/>
+      <c r="AG56" s="269"/>
+      <c r="AH56" s="269"/>
       <c r="AI56" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>50</v>
       </c>
       <c r="AJ56" s="64"/>
@@ -27465,10 +27503,10 @@
       </c>
       <c r="AP56" s="67"/>
       <c r="AQ56" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>50</v>
       </c>
-      <c r="AR56" s="299" t="s">
+      <c r="AR56" s="298" t="s">
         <v>229</v>
       </c>
       <c r="AS56" s="167"/>
@@ -27524,23 +27562,23 @@
         <v>0</v>
       </c>
       <c r="AB57" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AC57" s="63">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC57" s="63">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AD57" s="270"/>
+      <c r="AD57" s="269"/>
       <c r="AE57" s="177"/>
-      <c r="AF57" s="270">
+      <c r="AF57" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG57" s="270"/>
-      <c r="AH57" s="270"/>
+      <c r="AG57" s="269"/>
+      <c r="AH57" s="269"/>
       <c r="AI57" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>6</v>
       </c>
       <c r="AJ57" s="64"/>
@@ -27560,7 +27598,7 @@
       </c>
       <c r="AP57" s="67"/>
       <c r="AQ57" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>6</v>
       </c>
       <c r="AR57" s="122" t="s">
@@ -27619,23 +27657,23 @@
         <v>0</v>
       </c>
       <c r="AB58" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AC58" s="63">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC58" s="63">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AD58" s="270"/>
+      <c r="AD58" s="269"/>
       <c r="AE58" s="177"/>
-      <c r="AF58" s="270">
+      <c r="AF58" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG58" s="270"/>
-      <c r="AH58" s="270"/>
+      <c r="AG58" s="269"/>
+      <c r="AH58" s="269"/>
       <c r="AI58" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>23</v>
       </c>
       <c r="AJ58" s="64"/>
@@ -27655,7 +27693,7 @@
       </c>
       <c r="AP58" s="67"/>
       <c r="AQ58" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="AR58" s="122" t="s">
@@ -27714,23 +27752,23 @@
         <v>0</v>
       </c>
       <c r="AB59" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AC59" s="63">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC59" s="63">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AD59" s="270"/>
+      <c r="AD59" s="269"/>
       <c r="AE59" s="177"/>
-      <c r="AF59" s="270">
+      <c r="AF59" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG59" s="270"/>
-      <c r="AH59" s="270"/>
+      <c r="AG59" s="269"/>
+      <c r="AH59" s="269"/>
       <c r="AI59" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>25</v>
       </c>
       <c r="AJ59" s="64"/>
@@ -27750,10 +27788,10 @@
       </c>
       <c r="AP59" s="67"/>
       <c r="AQ59" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>25</v>
       </c>
-      <c r="AR59" s="301" t="s">
+      <c r="AR59" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS59" s="167"/>
@@ -27809,23 +27847,24 @@
         <v>0</v>
       </c>
       <c r="AB60" s="63">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AC60" s="63">
         <v>0</v>
       </c>
-      <c r="AD60" s="270"/>
+      <c r="AD60" s="269"/>
       <c r="AE60" s="177"/>
-      <c r="AF60" s="270">
+      <c r="AF60" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG60" s="270"/>
-      <c r="AH60" s="270">
+      <c r="AG60" s="269"/>
+      <c r="AH60" s="269">
         <v>265</v>
       </c>
       <c r="AI60" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>265</v>
       </c>
       <c r="AJ60" s="64"/>
@@ -27845,10 +27884,10 @@
       </c>
       <c r="AP60" s="67"/>
       <c r="AQ60" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>265</v>
       </c>
-      <c r="AR60" s="301" t="s">
+      <c r="AR60" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS60" s="167"/>
@@ -27910,27 +27949,27 @@
         <v>33820.960999999996</v>
       </c>
       <c r="AB61" s="63">
+        <f t="shared" si="8"/>
+        <v>0.54748621610683923</v>
+      </c>
+      <c r="AC61" s="63">
         <f t="shared" si="15"/>
         <v>0.54748621610683923</v>
       </c>
-      <c r="AC61" s="63">
-        <f t="shared" si="16"/>
-        <v>0.54748621610683923</v>
-      </c>
-      <c r="AD61" s="270">
+      <c r="AD61" s="269">
         <v>6000</v>
       </c>
       <c r="AE61" s="177">
         <v>5458</v>
       </c>
-      <c r="AF61" s="270">
+      <c r="AF61" s="269">
         <f t="shared" si="5"/>
         <v>542</v>
       </c>
-      <c r="AG61" s="270"/>
-      <c r="AH61" s="270"/>
+      <c r="AG61" s="269"/>
+      <c r="AH61" s="269"/>
       <c r="AI61" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>27954.039000000004</v>
       </c>
       <c r="AJ61" s="64"/>
@@ -27952,10 +27991,10 @@
       </c>
       <c r="AP61" s="67"/>
       <c r="AQ61" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>27954.039000000004</v>
       </c>
-      <c r="AR61" s="299" t="s">
+      <c r="AR61" s="298" t="s">
         <v>229</v>
       </c>
       <c r="AS61" s="167"/>
@@ -28016,23 +28055,23 @@
         <v>497783.54</v>
       </c>
       <c r="AB62" s="63">
-        <f>AA62/W62</f>
+        <f t="shared" si="8"/>
         <v>0.79292167369668543</v>
       </c>
       <c r="AC62" s="63">
         <f>AA62/N62</f>
         <v>0.98030568115576699</v>
       </c>
-      <c r="AD62" s="270"/>
+      <c r="AD62" s="269"/>
       <c r="AE62" s="177"/>
-      <c r="AF62" s="270">
+      <c r="AF62" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG62" s="270"/>
-      <c r="AH62" s="270"/>
+      <c r="AG62" s="269"/>
+      <c r="AH62" s="269"/>
       <c r="AI62" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>130000.46000000002</v>
       </c>
       <c r="AJ62" s="64"/>
@@ -28054,10 +28093,10 @@
       </c>
       <c r="AP62" s="67"/>
       <c r="AQ62" s="64">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>130000.46000000002</v>
       </c>
-      <c r="AR62" s="301" t="s">
+      <c r="AR62" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS62" s="147" t="s">
@@ -28112,18 +28151,21 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB63" s="63"/>
+      <c r="AB63" s="63" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AC63" s="63"/>
-      <c r="AD63" s="270"/>
+      <c r="AD63" s="269"/>
       <c r="AE63" s="114"/>
-      <c r="AF63" s="270">
+      <c r="AF63" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG63" s="270"/>
-      <c r="AH63" s="270"/>
+      <c r="AG63" s="269"/>
+      <c r="AH63" s="269"/>
       <c r="AI63" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AJ63" s="64"/>
@@ -28140,7 +28182,7 @@
       <c r="AO63" s="126"/>
       <c r="AP63" s="67"/>
       <c r="AQ63" s="67"/>
-      <c r="AR63" s="303"/>
+      <c r="AR63" s="302"/>
       <c r="AS63" s="172"/>
       <c r="AU63" s="21">
         <f>AU62-AA62</f>
@@ -28209,27 +28251,27 @@
         <f t="shared" si="4"/>
         <v>3567</v>
       </c>
-      <c r="AB64" s="186">
-        <f>AA64/W64</f>
+      <c r="AB64" s="63">
+        <f t="shared" si="8"/>
         <v>0.52517667844522964</v>
       </c>
       <c r="AC64" s="63">
         <v>0</v>
       </c>
-      <c r="AD64" s="270">
+      <c r="AD64" s="269">
         <v>3000</v>
       </c>
-      <c r="AE64" s="270">
+      <c r="AE64" s="269">
         <v>3467</v>
       </c>
-      <c r="AF64" s="270">
+      <c r="AF64" s="269">
         <f t="shared" si="5"/>
         <v>-467</v>
       </c>
-      <c r="AG64" s="270"/>
-      <c r="AH64" s="270"/>
+      <c r="AG64" s="269"/>
+      <c r="AH64" s="269"/>
       <c r="AI64" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>3225</v>
       </c>
       <c r="AJ64" s="64"/>
@@ -28319,28 +28361,28 @@
         <f t="shared" si="4"/>
         <v>3484</v>
       </c>
-      <c r="AB65" s="186">
-        <f t="shared" ref="AB65:AB67" si="19">AA65/W65</f>
+      <c r="AB65" s="63">
+        <f t="shared" si="8"/>
         <v>0.84975609756097559</v>
       </c>
       <c r="AC65" s="63">
         <v>0</v>
       </c>
-      <c r="AD65" s="270">
+      <c r="AD65" s="269">
         <f>423+37</f>
         <v>460</v>
       </c>
-      <c r="AE65" s="270">
+      <c r="AE65" s="269">
         <v>3384</v>
       </c>
-      <c r="AF65" s="270">
+      <c r="AF65" s="269">
         <f t="shared" si="5"/>
         <v>-2924</v>
       </c>
-      <c r="AG65" s="270"/>
-      <c r="AH65" s="270"/>
+      <c r="AG65" s="269"/>
+      <c r="AH65" s="269"/>
       <c r="AI65" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>616</v>
       </c>
       <c r="AJ65" s="64"/>
@@ -28424,28 +28466,28 @@
         <f t="shared" si="4"/>
         <v>574.29999999999995</v>
       </c>
-      <c r="AB66" s="186">
-        <f t="shared" si="19"/>
+      <c r="AB66" s="63">
+        <f t="shared" si="8"/>
         <v>0.52209090909090905</v>
       </c>
       <c r="AC66" s="63">
         <v>0</v>
       </c>
-      <c r="AD66" s="270">
+      <c r="AD66" s="269">
         <f>448+26</f>
         <v>474</v>
       </c>
-      <c r="AE66" s="270">
+      <c r="AE66" s="269">
         <v>474</v>
       </c>
-      <c r="AF66" s="270">
+      <c r="AF66" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG66" s="270"/>
-      <c r="AH66" s="270"/>
+      <c r="AG66" s="269"/>
+      <c r="AH66" s="269"/>
       <c r="AI66" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>525.70000000000005</v>
       </c>
       <c r="AJ66" s="64"/>
@@ -28527,25 +28569,25 @@
         <f t="shared" si="4"/>
         <v>684</v>
       </c>
-      <c r="AB67" s="186">
-        <f t="shared" si="19"/>
+      <c r="AB67" s="63">
+        <f t="shared" si="8"/>
         <v>0.97714285714285709</v>
       </c>
       <c r="AC67" s="63">
         <v>0</v>
       </c>
-      <c r="AD67" s="270"/>
-      <c r="AE67" s="270">
+      <c r="AD67" s="269"/>
+      <c r="AE67" s="269">
         <v>584</v>
       </c>
-      <c r="AF67" s="270">
+      <c r="AF67" s="269">
         <f t="shared" si="5"/>
         <v>-584</v>
       </c>
-      <c r="AG67" s="270"/>
-      <c r="AH67" s="270"/>
+      <c r="AG67" s="269"/>
+      <c r="AH67" s="269"/>
       <c r="AI67" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>16</v>
       </c>
       <c r="AJ67" s="64"/>
@@ -28565,7 +28607,7 @@
       </c>
       <c r="AP67" s="67"/>
       <c r="AQ67" s="67"/>
-      <c r="AR67" s="299" t="s">
+      <c r="AR67" s="298" t="s">
         <v>229</v>
       </c>
       <c r="AS67" s="173"/>
@@ -28603,7 +28645,7 @@
       </c>
       <c r="S68" s="179"/>
       <c r="T68" s="179"/>
-      <c r="U68" s="272">
+      <c r="U68" s="271">
         <v>4250</v>
       </c>
       <c r="V68" s="179"/>
@@ -28615,7 +28657,7 @@
         <v>100</v>
       </c>
       <c r="Y68" s="211"/>
-      <c r="Z68" s="276">
+      <c r="Z68" s="275">
         <f>1679.8+17.7+303</f>
         <v>2000.5</v>
       </c>
@@ -28623,27 +28665,27 @@
         <f t="shared" si="4"/>
         <v>2100.5</v>
       </c>
-      <c r="AB68" s="187">
-        <f>AA68/W68</f>
+      <c r="AB68" s="63">
+        <f t="shared" si="8"/>
         <v>0.45663043478260867</v>
       </c>
       <c r="AC68" s="63">
         <v>0</v>
       </c>
-      <c r="AD68" s="270">
+      <c r="AD68" s="269">
         <v>320</v>
       </c>
-      <c r="AE68" s="270">
+      <c r="AE68" s="269">
         <v>2001</v>
       </c>
-      <c r="AF68" s="270">
+      <c r="AF68" s="269">
         <f t="shared" si="5"/>
         <v>-1681</v>
       </c>
-      <c r="AG68" s="270"/>
-      <c r="AH68" s="270"/>
+      <c r="AG68" s="269"/>
+      <c r="AH68" s="269"/>
       <c r="AI68" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>2499.5</v>
       </c>
       <c r="AJ68" s="179"/>
@@ -28702,7 +28744,7 @@
       </c>
       <c r="S69" s="181"/>
       <c r="T69" s="181"/>
-      <c r="U69" s="273">
+      <c r="U69" s="272">
         <v>10700</v>
       </c>
       <c r="V69" s="181"/>
@@ -28714,7 +28756,7 @@
         <v>100</v>
       </c>
       <c r="Y69" s="212"/>
-      <c r="Z69" s="277">
+      <c r="Z69" s="276">
         <f>4936+741</f>
         <v>5677</v>
       </c>
@@ -28722,27 +28764,27 @@
         <f t="shared" si="4"/>
         <v>5777</v>
       </c>
-      <c r="AB69" s="197">
-        <f>AA69/W69</f>
+      <c r="AB69" s="63">
+        <f t="shared" si="8"/>
         <v>0.50675438596491229</v>
       </c>
       <c r="AC69" s="198">
         <v>0</v>
       </c>
-      <c r="AD69" s="270">
+      <c r="AD69" s="269">
         <v>4500</v>
       </c>
-      <c r="AE69" s="270">
+      <c r="AE69" s="269">
         <v>5677</v>
       </c>
-      <c r="AF69" s="270">
+      <c r="AF69" s="269">
         <f t="shared" si="5"/>
         <v>-1177</v>
       </c>
-      <c r="AG69" s="270"/>
-      <c r="AH69" s="270"/>
+      <c r="AG69" s="269"/>
+      <c r="AH69" s="269"/>
       <c r="AI69" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>5623</v>
       </c>
       <c r="AJ69" s="179"/>
@@ -28753,7 +28795,7 @@
       <c r="AO69" s="179"/>
       <c r="AP69" s="179"/>
       <c r="AQ69" s="179"/>
-      <c r="AR69" s="300" t="s">
+      <c r="AR69" s="299" t="s">
         <v>230</v>
       </c>
       <c r="AS69" s="200"/>
@@ -28791,7 +28833,7 @@
       </c>
       <c r="S70" s="182"/>
       <c r="T70" s="182"/>
-      <c r="U70" s="274">
+      <c r="U70" s="273">
         <v>10267</v>
       </c>
       <c r="V70" s="182"/>
@@ -28803,34 +28845,34 @@
         <v>100</v>
       </c>
       <c r="Y70" s="211"/>
-      <c r="Z70" s="276">
+      <c r="Z70" s="275">
         <v>5291</v>
       </c>
       <c r="AA70" s="209">
         <f t="shared" si="4"/>
         <v>5391</v>
       </c>
-      <c r="AB70" s="189">
-        <f>AA70/W70</f>
+      <c r="AB70" s="63">
+        <f t="shared" si="8"/>
         <v>0.49156560590863502</v>
       </c>
       <c r="AC70" s="63">
         <v>0</v>
       </c>
-      <c r="AD70" s="270">
+      <c r="AD70" s="269">
         <v>4300</v>
       </c>
-      <c r="AE70" s="270">
+      <c r="AE70" s="269">
         <v>5291</v>
       </c>
-      <c r="AF70" s="270">
+      <c r="AF70" s="269">
         <f t="shared" si="5"/>
         <v>-991</v>
       </c>
-      <c r="AG70" s="270"/>
-      <c r="AH70" s="270"/>
+      <c r="AG70" s="269"/>
+      <c r="AH70" s="269"/>
       <c r="AI70" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>5576</v>
       </c>
       <c r="AJ70" s="184"/>
@@ -28841,7 +28883,7 @@
       <c r="AO70" s="184"/>
       <c r="AP70" s="184"/>
       <c r="AQ70" s="184"/>
-      <c r="AR70" s="300" t="s">
+      <c r="AR70" s="299" t="s">
         <v>230</v>
       </c>
       <c r="AS70" s="173"/>
@@ -28879,7 +28921,7 @@
       </c>
       <c r="S71" s="181"/>
       <c r="T71" s="181"/>
-      <c r="U71" s="274">
+      <c r="U71" s="273">
         <v>6523</v>
       </c>
       <c r="V71" s="181"/>
@@ -28891,34 +28933,34 @@
         <v>100</v>
       </c>
       <c r="Y71" s="213"/>
-      <c r="Z71" s="276">
+      <c r="Z71" s="275">
         <v>3851</v>
       </c>
       <c r="AA71" s="209">
         <f t="shared" si="4"/>
         <v>3951</v>
       </c>
-      <c r="AB71" s="189">
-        <f>AA71/W71</f>
+      <c r="AB71" s="63">
+        <f t="shared" si="8"/>
         <v>0.55860313869645128</v>
       </c>
       <c r="AC71" s="63">
         <v>0</v>
       </c>
-      <c r="AD71" s="270">
+      <c r="AD71" s="269">
         <v>3951</v>
       </c>
-      <c r="AE71" s="270">
+      <c r="AE71" s="269">
         <v>3951</v>
       </c>
-      <c r="AF71" s="270">
+      <c r="AF71" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG71" s="270"/>
-      <c r="AH71" s="270"/>
+      <c r="AG71" s="269"/>
+      <c r="AH71" s="269"/>
       <c r="AI71" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>3122</v>
       </c>
       <c r="AJ71" s="179"/>
@@ -28965,7 +29007,7 @@
       </c>
       <c r="S72" s="258"/>
       <c r="T72" s="258"/>
-      <c r="U72" s="275"/>
+      <c r="U72" s="274"/>
       <c r="V72" s="258"/>
       <c r="W72" s="32">
         <f t="shared" si="6"/>
@@ -28978,18 +29020,21 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB72" s="261"/>
+      <c r="AB72" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AC72" s="63"/>
-      <c r="AD72" s="270"/>
-      <c r="AE72" s="270"/>
-      <c r="AF72" s="270">
+      <c r="AD72" s="269"/>
+      <c r="AE72" s="269"/>
+      <c r="AF72" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG72" s="270"/>
-      <c r="AH72" s="270"/>
+      <c r="AG72" s="269"/>
+      <c r="AH72" s="269"/>
       <c r="AI72" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>600</v>
       </c>
       <c r="AJ72" s="256"/>
@@ -29000,7 +29045,7 @@
       <c r="AO72" s="256"/>
       <c r="AP72" s="256"/>
       <c r="AQ72" s="256"/>
-      <c r="AR72" s="301" t="s">
+      <c r="AR72" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS72" s="173"/>
@@ -29036,7 +29081,7 @@
       </c>
       <c r="S73" s="258"/>
       <c r="T73" s="258"/>
-      <c r="U73" s="275"/>
+      <c r="U73" s="274"/>
       <c r="V73" s="258"/>
       <c r="W73" s="32">
         <f t="shared" si="6"/>
@@ -29049,18 +29094,21 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB73" s="261"/>
+      <c r="AB73" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AC73" s="63"/>
-      <c r="AD73" s="270"/>
-      <c r="AE73" s="270"/>
-      <c r="AF73" s="270">
+      <c r="AD73" s="269"/>
+      <c r="AE73" s="269"/>
+      <c r="AF73" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG73" s="270"/>
-      <c r="AH73" s="270"/>
+      <c r="AG73" s="269"/>
+      <c r="AH73" s="269"/>
       <c r="AI73" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>800</v>
       </c>
       <c r="AJ73" s="256"/>
@@ -29071,7 +29119,7 @@
       <c r="AO73" s="256"/>
       <c r="AP73" s="256"/>
       <c r="AQ73" s="256"/>
-      <c r="AR73" s="301" t="s">
+      <c r="AR73" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS73" s="173"/>
@@ -29107,7 +29155,7 @@
       </c>
       <c r="S74" s="258"/>
       <c r="T74" s="258"/>
-      <c r="U74" s="275"/>
+      <c r="U74" s="274"/>
       <c r="V74" s="258"/>
       <c r="W74" s="32">
         <f t="shared" si="6"/>
@@ -29120,18 +29168,21 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB74" s="261"/>
+      <c r="AB74" s="63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AC74" s="63"/>
-      <c r="AD74" s="270"/>
-      <c r="AE74" s="270"/>
-      <c r="AF74" s="270">
+      <c r="AD74" s="269"/>
+      <c r="AE74" s="269"/>
+      <c r="AF74" s="269">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG74" s="270"/>
-      <c r="AH74" s="270"/>
+      <c r="AG74" s="269"/>
+      <c r="AH74" s="269"/>
       <c r="AI74" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>1000</v>
       </c>
       <c r="AJ74" s="256"/>
@@ -29142,7 +29193,7 @@
       <c r="AO74" s="256"/>
       <c r="AP74" s="256"/>
       <c r="AQ74" s="256"/>
-      <c r="AR74" s="301" t="s">
+      <c r="AR74" s="300" t="s">
         <v>231</v>
       </c>
       <c r="AS74" s="173"/>
@@ -29161,7 +29212,7 @@
       <c r="K75" s="179"/>
       <c r="L75" s="179"/>
       <c r="M75" s="179"/>
-      <c r="N75" s="267"/>
+      <c r="N75" s="266"/>
       <c r="O75" s="179"/>
       <c r="P75" s="179"/>
       <c r="Q75" s="179"/>
@@ -29180,7 +29231,7 @@
       <c r="AA75" s="213"/>
       <c r="AB75" s="179"/>
       <c r="AC75" s="179"/>
-      <c r="AD75" s="264"/>
+      <c r="AD75" s="263"/>
       <c r="AE75" s="256"/>
       <c r="AF75" s="256"/>
       <c r="AG75" s="256"/>
@@ -30114,15 +30165,22 @@
   </sheetData>
   <autoFilter ref="A10:AV74" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="41">
-    <mergeCell ref="AQ7:AQ9"/>
-    <mergeCell ref="AS7:AS9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AO7:AO9"/>
-    <mergeCell ref="AR7:AR9"/>
+    <mergeCell ref="AF6:AS6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AC9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AD7:AF8"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AP7:AP9"/>
     <mergeCell ref="A1:AC1"/>
     <mergeCell ref="A2:AC2"/>
     <mergeCell ref="A4:AS4"/>
@@ -30139,22 +30197,15 @@
     <mergeCell ref="N7:N9"/>
     <mergeCell ref="O7:V9"/>
     <mergeCell ref="W7:W9"/>
-    <mergeCell ref="AF6:AS6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AC9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AD7:AF8"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AP7:AP9"/>
+    <mergeCell ref="AQ7:AQ9"/>
+    <mergeCell ref="AS7:AS9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AO7:AO9"/>
+    <mergeCell ref="AR7:AR9"/>
   </mergeCells>
   <pageMargins left="0.55000000000000004" right="0.15748031496062992" top="0.39370078740157483" bottom="0.23622047244094491" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" r:id="rId1"/>

--- a/report/bao-cao.xlsx
+++ b/report/bao-cao.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A48B8B6-9A71-4FA7-81E5-C85FB2BFF850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="0" windowWidth="15900" windowHeight="12900" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="bc" sheetId="1" state="hidden" r:id="rId1"/>
@@ -2445,21 +2445,49 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="54" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="63" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="77" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2475,12 +2503,10 @@
     <xf numFmtId="0" fontId="59" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2508,50 +2534,24 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="63" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2815,36 +2815,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="341" t="s">
+      <c r="A1" s="339" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="311"/>
-      <c r="C1" s="312"/>
-      <c r="D1" s="311"/>
-      <c r="E1" s="311"/>
-      <c r="F1" s="311"/>
-      <c r="G1" s="311"/>
-      <c r="H1" s="311"/>
-      <c r="I1" s="311"/>
-      <c r="J1" s="311"/>
-      <c r="K1" s="311"/>
-      <c r="L1" s="311"/>
-      <c r="M1" s="311"/>
-      <c r="N1" s="311"/>
-      <c r="O1" s="311"/>
-      <c r="P1" s="311"/>
-      <c r="Q1" s="311"/>
-      <c r="R1" s="311"/>
-      <c r="S1" s="311"/>
-      <c r="T1" s="311"/>
-      <c r="U1" s="311"/>
-      <c r="V1" s="311"/>
-      <c r="W1" s="311"/>
-      <c r="X1" s="311"/>
-      <c r="Y1" s="311"/>
-      <c r="Z1" s="311"/>
-      <c r="AA1" s="311"/>
-      <c r="AB1" s="313"/>
+      <c r="B1" s="319"/>
+      <c r="C1" s="320"/>
+      <c r="D1" s="319"/>
+      <c r="E1" s="319"/>
+      <c r="F1" s="319"/>
+      <c r="G1" s="319"/>
+      <c r="H1" s="319"/>
+      <c r="I1" s="319"/>
+      <c r="J1" s="319"/>
+      <c r="K1" s="319"/>
+      <c r="L1" s="319"/>
+      <c r="M1" s="319"/>
+      <c r="N1" s="319"/>
+      <c r="O1" s="319"/>
+      <c r="P1" s="319"/>
+      <c r="Q1" s="319"/>
+      <c r="R1" s="319"/>
+      <c r="S1" s="319"/>
+      <c r="T1" s="319"/>
+      <c r="U1" s="319"/>
+      <c r="V1" s="319"/>
+      <c r="W1" s="319"/>
+      <c r="X1" s="319"/>
+      <c r="Y1" s="319"/>
+      <c r="Z1" s="319"/>
+      <c r="AA1" s="319"/>
+      <c r="AB1" s="321"/>
       <c r="AC1" s="17"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="2"/>
@@ -2860,36 +2860,36 @@
       <c r="AM1" s="3"/>
     </row>
     <row r="2" spans="1:42" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="314" t="s">
+      <c r="A2" s="322" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="311"/>
-      <c r="C2" s="312"/>
-      <c r="D2" s="311"/>
-      <c r="E2" s="311"/>
-      <c r="F2" s="311"/>
-      <c r="G2" s="311"/>
-      <c r="H2" s="311"/>
-      <c r="I2" s="311"/>
-      <c r="J2" s="311"/>
-      <c r="K2" s="311"/>
-      <c r="L2" s="311"/>
-      <c r="M2" s="311"/>
-      <c r="N2" s="311"/>
-      <c r="O2" s="311"/>
-      <c r="P2" s="311"/>
-      <c r="Q2" s="311"/>
-      <c r="R2" s="311"/>
-      <c r="S2" s="311"/>
-      <c r="T2" s="311"/>
-      <c r="U2" s="311"/>
-      <c r="V2" s="311"/>
-      <c r="W2" s="311"/>
-      <c r="X2" s="311"/>
-      <c r="Y2" s="311"/>
-      <c r="Z2" s="311"/>
-      <c r="AA2" s="311"/>
-      <c r="AB2" s="313"/>
+      <c r="B2" s="319"/>
+      <c r="C2" s="320"/>
+      <c r="D2" s="319"/>
+      <c r="E2" s="319"/>
+      <c r="F2" s="319"/>
+      <c r="G2" s="319"/>
+      <c r="H2" s="319"/>
+      <c r="I2" s="319"/>
+      <c r="J2" s="319"/>
+      <c r="K2" s="319"/>
+      <c r="L2" s="319"/>
+      <c r="M2" s="319"/>
+      <c r="N2" s="319"/>
+      <c r="O2" s="319"/>
+      <c r="P2" s="319"/>
+      <c r="Q2" s="319"/>
+      <c r="R2" s="319"/>
+      <c r="S2" s="319"/>
+      <c r="T2" s="319"/>
+      <c r="U2" s="319"/>
+      <c r="V2" s="319"/>
+      <c r="W2" s="319"/>
+      <c r="X2" s="319"/>
+      <c r="Y2" s="319"/>
+      <c r="Z2" s="319"/>
+      <c r="AA2" s="319"/>
+      <c r="AB2" s="321"/>
       <c r="AC2" s="17"/>
       <c r="AD2" s="1"/>
       <c r="AE2" s="2"/>
@@ -2944,90 +2944,90 @@
       <c r="AM3" s="3"/>
     </row>
     <row r="4" spans="1:42" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="315" t="s">
+      <c r="A4" s="323" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="311"/>
-      <c r="C4" s="312"/>
-      <c r="D4" s="311"/>
-      <c r="E4" s="311"/>
-      <c r="F4" s="311"/>
-      <c r="G4" s="311"/>
-      <c r="H4" s="311"/>
-      <c r="I4" s="311"/>
-      <c r="J4" s="311"/>
-      <c r="K4" s="311"/>
-      <c r="L4" s="311"/>
-      <c r="M4" s="311"/>
-      <c r="N4" s="311"/>
-      <c r="O4" s="311"/>
-      <c r="P4" s="311"/>
-      <c r="Q4" s="311"/>
-      <c r="R4" s="311"/>
-      <c r="S4" s="311"/>
-      <c r="T4" s="311"/>
-      <c r="U4" s="311"/>
-      <c r="V4" s="311"/>
-      <c r="W4" s="311"/>
-      <c r="X4" s="311"/>
-      <c r="Y4" s="311"/>
-      <c r="Z4" s="311"/>
-      <c r="AA4" s="311"/>
-      <c r="AB4" s="311"/>
-      <c r="AC4" s="312"/>
-      <c r="AD4" s="311"/>
-      <c r="AE4" s="311"/>
-      <c r="AF4" s="312"/>
-      <c r="AG4" s="312"/>
-      <c r="AH4" s="311"/>
-      <c r="AI4" s="312"/>
-      <c r="AJ4" s="312"/>
-      <c r="AK4" s="311"/>
-      <c r="AL4" s="312"/>
-      <c r="AM4" s="313"/>
+      <c r="B4" s="319"/>
+      <c r="C4" s="320"/>
+      <c r="D4" s="319"/>
+      <c r="E4" s="319"/>
+      <c r="F4" s="319"/>
+      <c r="G4" s="319"/>
+      <c r="H4" s="319"/>
+      <c r="I4" s="319"/>
+      <c r="J4" s="319"/>
+      <c r="K4" s="319"/>
+      <c r="L4" s="319"/>
+      <c r="M4" s="319"/>
+      <c r="N4" s="319"/>
+      <c r="O4" s="319"/>
+      <c r="P4" s="319"/>
+      <c r="Q4" s="319"/>
+      <c r="R4" s="319"/>
+      <c r="S4" s="319"/>
+      <c r="T4" s="319"/>
+      <c r="U4" s="319"/>
+      <c r="V4" s="319"/>
+      <c r="W4" s="319"/>
+      <c r="X4" s="319"/>
+      <c r="Y4" s="319"/>
+      <c r="Z4" s="319"/>
+      <c r="AA4" s="319"/>
+      <c r="AB4" s="319"/>
+      <c r="AC4" s="320"/>
+      <c r="AD4" s="319"/>
+      <c r="AE4" s="319"/>
+      <c r="AF4" s="320"/>
+      <c r="AG4" s="320"/>
+      <c r="AH4" s="319"/>
+      <c r="AI4" s="320"/>
+      <c r="AJ4" s="320"/>
+      <c r="AK4" s="319"/>
+      <c r="AL4" s="320"/>
+      <c r="AM4" s="321"/>
     </row>
     <row r="5" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="316" t="s">
+      <c r="A5" s="324" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="311"/>
-      <c r="C5" s="312"/>
-      <c r="D5" s="311"/>
-      <c r="E5" s="311"/>
-      <c r="F5" s="311"/>
-      <c r="G5" s="311"/>
-      <c r="H5" s="311"/>
-      <c r="I5" s="311"/>
-      <c r="J5" s="311"/>
-      <c r="K5" s="311"/>
-      <c r="L5" s="311"/>
-      <c r="M5" s="311"/>
-      <c r="N5" s="311"/>
-      <c r="O5" s="311"/>
-      <c r="P5" s="311"/>
-      <c r="Q5" s="311"/>
-      <c r="R5" s="311"/>
-      <c r="S5" s="311"/>
-      <c r="T5" s="311"/>
-      <c r="U5" s="311"/>
-      <c r="V5" s="311"/>
-      <c r="W5" s="311"/>
-      <c r="X5" s="311"/>
-      <c r="Y5" s="311"/>
-      <c r="Z5" s="311"/>
-      <c r="AA5" s="311"/>
-      <c r="AB5" s="311"/>
-      <c r="AC5" s="312"/>
-      <c r="AD5" s="311"/>
-      <c r="AE5" s="311"/>
-      <c r="AF5" s="312"/>
-      <c r="AG5" s="312"/>
-      <c r="AH5" s="311"/>
-      <c r="AI5" s="312"/>
-      <c r="AJ5" s="312"/>
-      <c r="AK5" s="311"/>
-      <c r="AL5" s="312"/>
-      <c r="AM5" s="313"/>
+      <c r="B5" s="319"/>
+      <c r="C5" s="320"/>
+      <c r="D5" s="319"/>
+      <c r="E5" s="319"/>
+      <c r="F5" s="319"/>
+      <c r="G5" s="319"/>
+      <c r="H5" s="319"/>
+      <c r="I5" s="319"/>
+      <c r="J5" s="319"/>
+      <c r="K5" s="319"/>
+      <c r="L5" s="319"/>
+      <c r="M5" s="319"/>
+      <c r="N5" s="319"/>
+      <c r="O5" s="319"/>
+      <c r="P5" s="319"/>
+      <c r="Q5" s="319"/>
+      <c r="R5" s="319"/>
+      <c r="S5" s="319"/>
+      <c r="T5" s="319"/>
+      <c r="U5" s="319"/>
+      <c r="V5" s="319"/>
+      <c r="W5" s="319"/>
+      <c r="X5" s="319"/>
+      <c r="Y5" s="319"/>
+      <c r="Z5" s="319"/>
+      <c r="AA5" s="319"/>
+      <c r="AB5" s="319"/>
+      <c r="AC5" s="320"/>
+      <c r="AD5" s="319"/>
+      <c r="AE5" s="319"/>
+      <c r="AF5" s="320"/>
+      <c r="AG5" s="320"/>
+      <c r="AH5" s="319"/>
+      <c r="AI5" s="320"/>
+      <c r="AJ5" s="320"/>
+      <c r="AK5" s="319"/>
+      <c r="AL5" s="320"/>
+      <c r="AM5" s="321"/>
     </row>
     <row r="6" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -3061,71 +3061,71 @@
       <c r="AA6" s="16"/>
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
-      <c r="AD6" s="342"/>
-      <c r="AE6" s="312"/>
-      <c r="AF6" s="312"/>
-      <c r="AG6" s="312"/>
-      <c r="AH6" s="312"/>
-      <c r="AI6" s="312"/>
-      <c r="AJ6" s="312"/>
-      <c r="AK6" s="312"/>
-      <c r="AL6" s="312"/>
-      <c r="AM6" s="312"/>
+      <c r="AD6" s="341"/>
+      <c r="AE6" s="320"/>
+      <c r="AF6" s="320"/>
+      <c r="AG6" s="320"/>
+      <c r="AH6" s="320"/>
+      <c r="AI6" s="320"/>
+      <c r="AJ6" s="320"/>
+      <c r="AK6" s="320"/>
+      <c r="AL6" s="320"/>
+      <c r="AM6" s="320"/>
     </row>
     <row r="7" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="303" t="s">
+      <c r="A7" s="304" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="303" t="s">
+      <c r="B7" s="304" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="330" t="s">
+      <c r="C7" s="307" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="303" t="s">
+      <c r="D7" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="303" t="s">
+      <c r="E7" s="304" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="303" t="s">
+      <c r="F7" s="304" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="303" t="s">
+      <c r="G7" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="303" t="s">
+      <c r="H7" s="304" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="303" t="s">
+      <c r="I7" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="303" t="s">
+      <c r="J7" s="304" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="303" t="s">
+      <c r="K7" s="304" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="318" t="s">
+      <c r="L7" s="325" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="303" t="s">
+      <c r="M7" s="304" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="303" t="s">
+      <c r="N7" s="304" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="319" t="s">
+      <c r="O7" s="327" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="320"/>
-      <c r="Q7" s="320"/>
-      <c r="R7" s="320"/>
-      <c r="S7" s="320"/>
-      <c r="T7" s="320"/>
-      <c r="U7" s="320"/>
-      <c r="V7" s="321"/>
-      <c r="W7" s="303" t="s">
+      <c r="P7" s="328"/>
+      <c r="Q7" s="328"/>
+      <c r="R7" s="328"/>
+      <c r="S7" s="328"/>
+      <c r="T7" s="328"/>
+      <c r="U7" s="328"/>
+      <c r="V7" s="329"/>
+      <c r="W7" s="304" t="s">
         <v>139</v>
       </c>
       <c r="X7" s="340" t="s">
@@ -3134,130 +3134,130 @@
       <c r="Y7" s="340" t="s">
         <v>14</v>
       </c>
-      <c r="Z7" s="308" t="s">
+      <c r="Z7" s="310" t="s">
         <v>150</v>
       </c>
-      <c r="AA7" s="303" t="s">
+      <c r="AA7" s="304" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="303" t="s">
+      <c r="AB7" s="304" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="303" t="s">
+      <c r="AC7" s="304" t="s">
         <v>134</v>
       </c>
-      <c r="AD7" s="308" t="s">
+      <c r="AD7" s="310" t="s">
         <v>17</v>
       </c>
-      <c r="AE7" s="305" t="s">
+      <c r="AE7" s="336" t="s">
         <v>107</v>
       </c>
-      <c r="AF7" s="305" t="s">
+      <c r="AF7" s="336" t="s">
         <v>108</v>
       </c>
-      <c r="AG7" s="305" t="s">
+      <c r="AG7" s="336" t="s">
         <v>106</v>
       </c>
-      <c r="AH7" s="307" t="s">
+      <c r="AH7" s="338" t="s">
         <v>147</v>
       </c>
-      <c r="AI7" s="308" t="s">
+      <c r="AI7" s="310" t="s">
         <v>136</v>
       </c>
-      <c r="AJ7" s="308" t="s">
+      <c r="AJ7" s="310" t="s">
         <v>137</v>
       </c>
-      <c r="AK7" s="303" t="s">
+      <c r="AK7" s="304" t="s">
         <v>135</v>
       </c>
-      <c r="AL7" s="303" t="s">
+      <c r="AL7" s="304" t="s">
         <v>146</v>
       </c>
-      <c r="AM7" s="303" t="s">
+      <c r="AM7" s="304" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="309"/>
-      <c r="B8" s="309"/>
-      <c r="C8" s="330"/>
-      <c r="D8" s="309"/>
-      <c r="E8" s="309"/>
-      <c r="F8" s="309"/>
-      <c r="G8" s="309"/>
-      <c r="H8" s="309"/>
-      <c r="I8" s="309"/>
-      <c r="J8" s="309"/>
-      <c r="K8" s="309"/>
-      <c r="L8" s="309"/>
-      <c r="M8" s="309"/>
-      <c r="N8" s="309"/>
-      <c r="O8" s="322"/>
-      <c r="P8" s="323"/>
-      <c r="Q8" s="323"/>
-      <c r="R8" s="323"/>
-      <c r="S8" s="323"/>
-      <c r="T8" s="323"/>
-      <c r="U8" s="323"/>
-      <c r="V8" s="324"/>
-      <c r="W8" s="309"/>
-      <c r="X8" s="309"/>
-      <c r="Y8" s="309"/>
-      <c r="Z8" s="309"/>
-      <c r="AA8" s="309"/>
-      <c r="AB8" s="309"/>
-      <c r="AC8" s="303"/>
-      <c r="AD8" s="309"/>
-      <c r="AE8" s="306"/>
-      <c r="AF8" s="306"/>
-      <c r="AG8" s="307"/>
-      <c r="AH8" s="306"/>
-      <c r="AI8" s="309"/>
-      <c r="AJ8" s="308"/>
-      <c r="AK8" s="309"/>
-      <c r="AL8" s="303"/>
-      <c r="AM8" s="309"/>
+      <c r="A8" s="305"/>
+      <c r="B8" s="305"/>
+      <c r="C8" s="307"/>
+      <c r="D8" s="305"/>
+      <c r="E8" s="305"/>
+      <c r="F8" s="305"/>
+      <c r="G8" s="305"/>
+      <c r="H8" s="305"/>
+      <c r="I8" s="305"/>
+      <c r="J8" s="305"/>
+      <c r="K8" s="305"/>
+      <c r="L8" s="305"/>
+      <c r="M8" s="305"/>
+      <c r="N8" s="305"/>
+      <c r="O8" s="330"/>
+      <c r="P8" s="331"/>
+      <c r="Q8" s="331"/>
+      <c r="R8" s="331"/>
+      <c r="S8" s="331"/>
+      <c r="T8" s="331"/>
+      <c r="U8" s="331"/>
+      <c r="V8" s="332"/>
+      <c r="W8" s="305"/>
+      <c r="X8" s="305"/>
+      <c r="Y8" s="305"/>
+      <c r="Z8" s="305"/>
+      <c r="AA8" s="305"/>
+      <c r="AB8" s="305"/>
+      <c r="AC8" s="304"/>
+      <c r="AD8" s="305"/>
+      <c r="AE8" s="337"/>
+      <c r="AF8" s="337"/>
+      <c r="AG8" s="338"/>
+      <c r="AH8" s="337"/>
+      <c r="AI8" s="305"/>
+      <c r="AJ8" s="310"/>
+      <c r="AK8" s="305"/>
+      <c r="AL8" s="304"/>
+      <c r="AM8" s="305"/>
     </row>
     <row r="9" spans="1:42" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="309"/>
-      <c r="B9" s="309"/>
-      <c r="C9" s="330"/>
-      <c r="D9" s="309"/>
-      <c r="E9" s="309"/>
-      <c r="F9" s="309"/>
-      <c r="G9" s="309"/>
-      <c r="H9" s="309"/>
-      <c r="I9" s="309"/>
-      <c r="J9" s="309"/>
-      <c r="K9" s="309"/>
-      <c r="L9" s="309"/>
-      <c r="M9" s="309"/>
-      <c r="N9" s="309"/>
-      <c r="O9" s="325"/>
-      <c r="P9" s="326"/>
-      <c r="Q9" s="326"/>
-      <c r="R9" s="326"/>
-      <c r="S9" s="326"/>
-      <c r="T9" s="326"/>
-      <c r="U9" s="326"/>
-      <c r="V9" s="327"/>
-      <c r="W9" s="309"/>
-      <c r="X9" s="309"/>
-      <c r="Y9" s="309"/>
-      <c r="Z9" s="309"/>
-      <c r="AA9" s="309"/>
-      <c r="AB9" s="309"/>
-      <c r="AC9" s="303"/>
-      <c r="AD9" s="309"/>
-      <c r="AE9" s="306"/>
-      <c r="AF9" s="306"/>
-      <c r="AG9" s="307"/>
-      <c r="AH9" s="306"/>
-      <c r="AI9" s="309"/>
-      <c r="AJ9" s="308"/>
-      <c r="AK9" s="309"/>
-      <c r="AL9" s="303"/>
-      <c r="AM9" s="309"/>
+      <c r="A9" s="305"/>
+      <c r="B9" s="305"/>
+      <c r="C9" s="307"/>
+      <c r="D9" s="305"/>
+      <c r="E9" s="305"/>
+      <c r="F9" s="305"/>
+      <c r="G9" s="305"/>
+      <c r="H9" s="305"/>
+      <c r="I9" s="305"/>
+      <c r="J9" s="305"/>
+      <c r="K9" s="305"/>
+      <c r="L9" s="305"/>
+      <c r="M9" s="305"/>
+      <c r="N9" s="305"/>
+      <c r="O9" s="333"/>
+      <c r="P9" s="334"/>
+      <c r="Q9" s="334"/>
+      <c r="R9" s="334"/>
+      <c r="S9" s="334"/>
+      <c r="T9" s="334"/>
+      <c r="U9" s="334"/>
+      <c r="V9" s="335"/>
+      <c r="W9" s="305"/>
+      <c r="X9" s="305"/>
+      <c r="Y9" s="305"/>
+      <c r="Z9" s="305"/>
+      <c r="AA9" s="305"/>
+      <c r="AB9" s="305"/>
+      <c r="AC9" s="304"/>
+      <c r="AD9" s="305"/>
+      <c r="AE9" s="337"/>
+      <c r="AF9" s="337"/>
+      <c r="AG9" s="338"/>
+      <c r="AH9" s="337"/>
+      <c r="AI9" s="305"/>
+      <c r="AJ9" s="310"/>
+      <c r="AK9" s="305"/>
+      <c r="AL9" s="304"/>
+      <c r="AM9" s="305"/>
       <c r="AP9">
         <v>27</v>
       </c>
@@ -8706,47 +8706,47 @@
       </c>
     </row>
     <row r="77" spans="1:42" ht="29.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="339" t="s">
+      <c r="A77" s="342" t="s">
         <v>145</v>
       </c>
-      <c r="B77" s="309"/>
-      <c r="C77" s="309"/>
-      <c r="D77" s="309"/>
-      <c r="E77" s="309"/>
-      <c r="F77" s="309"/>
-      <c r="G77" s="309"/>
-      <c r="H77" s="309"/>
-      <c r="I77" s="309"/>
-      <c r="J77" s="309"/>
-      <c r="K77" s="309"/>
-      <c r="L77" s="309"/>
-      <c r="M77" s="309"/>
-      <c r="N77" s="309"/>
-      <c r="O77" s="309"/>
-      <c r="P77" s="309"/>
-      <c r="Q77" s="309"/>
-      <c r="R77" s="309"/>
-      <c r="S77" s="309"/>
-      <c r="T77" s="309"/>
-      <c r="U77" s="309"/>
-      <c r="V77" s="309"/>
-      <c r="W77" s="309"/>
-      <c r="X77" s="309"/>
-      <c r="Y77" s="309"/>
-      <c r="Z77" s="309"/>
-      <c r="AA77" s="309"/>
-      <c r="AB77" s="309"/>
-      <c r="AC77" s="309"/>
-      <c r="AD77" s="309"/>
-      <c r="AE77" s="309"/>
-      <c r="AF77" s="309"/>
-      <c r="AG77" s="309"/>
-      <c r="AH77" s="309"/>
-      <c r="AI77" s="309"/>
-      <c r="AJ77" s="309"/>
-      <c r="AK77" s="309"/>
-      <c r="AL77" s="309"/>
-      <c r="AM77" s="309"/>
+      <c r="B77" s="305"/>
+      <c r="C77" s="305"/>
+      <c r="D77" s="305"/>
+      <c r="E77" s="305"/>
+      <c r="F77" s="305"/>
+      <c r="G77" s="305"/>
+      <c r="H77" s="305"/>
+      <c r="I77" s="305"/>
+      <c r="J77" s="305"/>
+      <c r="K77" s="305"/>
+      <c r="L77" s="305"/>
+      <c r="M77" s="305"/>
+      <c r="N77" s="305"/>
+      <c r="O77" s="305"/>
+      <c r="P77" s="305"/>
+      <c r="Q77" s="305"/>
+      <c r="R77" s="305"/>
+      <c r="S77" s="305"/>
+      <c r="T77" s="305"/>
+      <c r="U77" s="305"/>
+      <c r="V77" s="305"/>
+      <c r="W77" s="305"/>
+      <c r="X77" s="305"/>
+      <c r="Y77" s="305"/>
+      <c r="Z77" s="305"/>
+      <c r="AA77" s="305"/>
+      <c r="AB77" s="305"/>
+      <c r="AC77" s="305"/>
+      <c r="AD77" s="305"/>
+      <c r="AE77" s="305"/>
+      <c r="AF77" s="305"/>
+      <c r="AG77" s="305"/>
+      <c r="AH77" s="305"/>
+      <c r="AI77" s="305"/>
+      <c r="AJ77" s="305"/>
+      <c r="AK77" s="305"/>
+      <c r="AL77" s="305"/>
+      <c r="AM77" s="305"/>
     </row>
     <row r="78" spans="1:42" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="81"/>
@@ -9846,12 +9846,22 @@
   </sheetData>
   <autoFilter ref="A10:AP80" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="38">
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AC9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="A77:AM77"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:J9"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="A7:A9"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A2:AB2"/>
     <mergeCell ref="A4:AM4"/>
@@ -9868,22 +9878,12 @@
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="X7:X9"/>
     <mergeCell ref="AD6:AM6"/>
-    <mergeCell ref="A77:AM77"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:J9"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AC9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="O7:V9"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.27559055118110237" top="0.47244094488188981" bottom="0.31496062992125984" header="0" footer="0"/>
   <pageSetup scale="80" orientation="landscape" r:id="rId1"/>
@@ -9932,36 +9932,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="341" t="s">
+      <c r="A1" s="339" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="311"/>
-      <c r="C1" s="312"/>
-      <c r="D1" s="311"/>
-      <c r="E1" s="311"/>
-      <c r="F1" s="311"/>
-      <c r="G1" s="311"/>
-      <c r="H1" s="311"/>
-      <c r="I1" s="311"/>
-      <c r="J1" s="311"/>
-      <c r="K1" s="311"/>
-      <c r="L1" s="311"/>
-      <c r="M1" s="311"/>
-      <c r="N1" s="311"/>
-      <c r="O1" s="311"/>
-      <c r="P1" s="311"/>
-      <c r="Q1" s="311"/>
-      <c r="R1" s="311"/>
-      <c r="S1" s="311"/>
-      <c r="T1" s="311"/>
-      <c r="U1" s="311"/>
-      <c r="V1" s="311"/>
-      <c r="W1" s="311"/>
-      <c r="X1" s="311"/>
-      <c r="Y1" s="311"/>
-      <c r="Z1" s="311"/>
-      <c r="AA1" s="311"/>
-      <c r="AB1" s="313"/>
+      <c r="B1" s="319"/>
+      <c r="C1" s="320"/>
+      <c r="D1" s="319"/>
+      <c r="E1" s="319"/>
+      <c r="F1" s="319"/>
+      <c r="G1" s="319"/>
+      <c r="H1" s="319"/>
+      <c r="I1" s="319"/>
+      <c r="J1" s="319"/>
+      <c r="K1" s="319"/>
+      <c r="L1" s="319"/>
+      <c r="M1" s="319"/>
+      <c r="N1" s="319"/>
+      <c r="O1" s="319"/>
+      <c r="P1" s="319"/>
+      <c r="Q1" s="319"/>
+      <c r="R1" s="319"/>
+      <c r="S1" s="319"/>
+      <c r="T1" s="319"/>
+      <c r="U1" s="319"/>
+      <c r="V1" s="319"/>
+      <c r="W1" s="319"/>
+      <c r="X1" s="319"/>
+      <c r="Y1" s="319"/>
+      <c r="Z1" s="319"/>
+      <c r="AA1" s="319"/>
+      <c r="AB1" s="321"/>
       <c r="AC1" s="17"/>
       <c r="AD1" s="17"/>
       <c r="AE1" s="1"/>
@@ -9978,36 +9978,36 @@
       <c r="AN1" s="160"/>
     </row>
     <row r="2" spans="1:43" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="314" t="s">
+      <c r="A2" s="322" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="311"/>
-      <c r="C2" s="312"/>
-      <c r="D2" s="311"/>
-      <c r="E2" s="311"/>
-      <c r="F2" s="311"/>
-      <c r="G2" s="311"/>
-      <c r="H2" s="311"/>
-      <c r="I2" s="311"/>
-      <c r="J2" s="311"/>
-      <c r="K2" s="311"/>
-      <c r="L2" s="311"/>
-      <c r="M2" s="311"/>
-      <c r="N2" s="311"/>
-      <c r="O2" s="311"/>
-      <c r="P2" s="311"/>
-      <c r="Q2" s="311"/>
-      <c r="R2" s="311"/>
-      <c r="S2" s="311"/>
-      <c r="T2" s="311"/>
-      <c r="U2" s="311"/>
-      <c r="V2" s="311"/>
-      <c r="W2" s="311"/>
-      <c r="X2" s="311"/>
-      <c r="Y2" s="311"/>
-      <c r="Z2" s="311"/>
-      <c r="AA2" s="311"/>
-      <c r="AB2" s="313"/>
+      <c r="B2" s="319"/>
+      <c r="C2" s="320"/>
+      <c r="D2" s="319"/>
+      <c r="E2" s="319"/>
+      <c r="F2" s="319"/>
+      <c r="G2" s="319"/>
+      <c r="H2" s="319"/>
+      <c r="I2" s="319"/>
+      <c r="J2" s="319"/>
+      <c r="K2" s="319"/>
+      <c r="L2" s="319"/>
+      <c r="M2" s="319"/>
+      <c r="N2" s="319"/>
+      <c r="O2" s="319"/>
+      <c r="P2" s="319"/>
+      <c r="Q2" s="319"/>
+      <c r="R2" s="319"/>
+      <c r="S2" s="319"/>
+      <c r="T2" s="319"/>
+      <c r="U2" s="319"/>
+      <c r="V2" s="319"/>
+      <c r="W2" s="319"/>
+      <c r="X2" s="319"/>
+      <c r="Y2" s="319"/>
+      <c r="Z2" s="319"/>
+      <c r="AA2" s="319"/>
+      <c r="AB2" s="321"/>
       <c r="AC2" s="17"/>
       <c r="AD2" s="17"/>
       <c r="AE2" s="1"/>
@@ -10064,92 +10064,92 @@
       <c r="AN3" s="160"/>
     </row>
     <row r="4" spans="1:43" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="315" t="s">
+      <c r="A4" s="323" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="311"/>
-      <c r="C4" s="312"/>
-      <c r="D4" s="311"/>
-      <c r="E4" s="311"/>
-      <c r="F4" s="311"/>
-      <c r="G4" s="311"/>
-      <c r="H4" s="311"/>
-      <c r="I4" s="311"/>
-      <c r="J4" s="311"/>
-      <c r="K4" s="311"/>
-      <c r="L4" s="311"/>
-      <c r="M4" s="311"/>
-      <c r="N4" s="311"/>
-      <c r="O4" s="311"/>
-      <c r="P4" s="311"/>
-      <c r="Q4" s="311"/>
-      <c r="R4" s="311"/>
-      <c r="S4" s="311"/>
-      <c r="T4" s="311"/>
-      <c r="U4" s="311"/>
-      <c r="V4" s="311"/>
-      <c r="W4" s="311"/>
-      <c r="X4" s="311"/>
-      <c r="Y4" s="311"/>
-      <c r="Z4" s="311"/>
-      <c r="AA4" s="311"/>
-      <c r="AB4" s="311"/>
-      <c r="AC4" s="312"/>
-      <c r="AD4" s="312"/>
-      <c r="AE4" s="311"/>
-      <c r="AF4" s="311"/>
-      <c r="AG4" s="312"/>
-      <c r="AH4" s="312"/>
-      <c r="AI4" s="311"/>
-      <c r="AJ4" s="312"/>
-      <c r="AK4" s="312"/>
-      <c r="AL4" s="311"/>
-      <c r="AM4" s="312"/>
-      <c r="AN4" s="313"/>
+      <c r="B4" s="319"/>
+      <c r="C4" s="320"/>
+      <c r="D4" s="319"/>
+      <c r="E4" s="319"/>
+      <c r="F4" s="319"/>
+      <c r="G4" s="319"/>
+      <c r="H4" s="319"/>
+      <c r="I4" s="319"/>
+      <c r="J4" s="319"/>
+      <c r="K4" s="319"/>
+      <c r="L4" s="319"/>
+      <c r="M4" s="319"/>
+      <c r="N4" s="319"/>
+      <c r="O4" s="319"/>
+      <c r="P4" s="319"/>
+      <c r="Q4" s="319"/>
+      <c r="R4" s="319"/>
+      <c r="S4" s="319"/>
+      <c r="T4" s="319"/>
+      <c r="U4" s="319"/>
+      <c r="V4" s="319"/>
+      <c r="W4" s="319"/>
+      <c r="X4" s="319"/>
+      <c r="Y4" s="319"/>
+      <c r="Z4" s="319"/>
+      <c r="AA4" s="319"/>
+      <c r="AB4" s="319"/>
+      <c r="AC4" s="320"/>
+      <c r="AD4" s="320"/>
+      <c r="AE4" s="319"/>
+      <c r="AF4" s="319"/>
+      <c r="AG4" s="320"/>
+      <c r="AH4" s="320"/>
+      <c r="AI4" s="319"/>
+      <c r="AJ4" s="320"/>
+      <c r="AK4" s="320"/>
+      <c r="AL4" s="319"/>
+      <c r="AM4" s="320"/>
+      <c r="AN4" s="321"/>
     </row>
     <row r="5" spans="1:43" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="316" t="s">
+      <c r="A5" s="324" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="311"/>
-      <c r="C5" s="312"/>
-      <c r="D5" s="311"/>
-      <c r="E5" s="311"/>
-      <c r="F5" s="311"/>
-      <c r="G5" s="311"/>
-      <c r="H5" s="311"/>
-      <c r="I5" s="311"/>
-      <c r="J5" s="311"/>
-      <c r="K5" s="311"/>
-      <c r="L5" s="311"/>
-      <c r="M5" s="311"/>
-      <c r="N5" s="311"/>
-      <c r="O5" s="311"/>
-      <c r="P5" s="311"/>
-      <c r="Q5" s="311"/>
-      <c r="R5" s="311"/>
-      <c r="S5" s="311"/>
-      <c r="T5" s="311"/>
-      <c r="U5" s="311"/>
-      <c r="V5" s="311"/>
-      <c r="W5" s="311"/>
-      <c r="X5" s="311"/>
-      <c r="Y5" s="311"/>
-      <c r="Z5" s="311"/>
-      <c r="AA5" s="311"/>
-      <c r="AB5" s="311"/>
-      <c r="AC5" s="312"/>
-      <c r="AD5" s="312"/>
-      <c r="AE5" s="311"/>
-      <c r="AF5" s="311"/>
-      <c r="AG5" s="312"/>
-      <c r="AH5" s="312"/>
-      <c r="AI5" s="311"/>
-      <c r="AJ5" s="312"/>
-      <c r="AK5" s="312"/>
-      <c r="AL5" s="311"/>
-      <c r="AM5" s="312"/>
-      <c r="AN5" s="313"/>
+      <c r="B5" s="319"/>
+      <c r="C5" s="320"/>
+      <c r="D5" s="319"/>
+      <c r="E5" s="319"/>
+      <c r="F5" s="319"/>
+      <c r="G5" s="319"/>
+      <c r="H5" s="319"/>
+      <c r="I5" s="319"/>
+      <c r="J5" s="319"/>
+      <c r="K5" s="319"/>
+      <c r="L5" s="319"/>
+      <c r="M5" s="319"/>
+      <c r="N5" s="319"/>
+      <c r="O5" s="319"/>
+      <c r="P5" s="319"/>
+      <c r="Q5" s="319"/>
+      <c r="R5" s="319"/>
+      <c r="S5" s="319"/>
+      <c r="T5" s="319"/>
+      <c r="U5" s="319"/>
+      <c r="V5" s="319"/>
+      <c r="W5" s="319"/>
+      <c r="X5" s="319"/>
+      <c r="Y5" s="319"/>
+      <c r="Z5" s="319"/>
+      <c r="AA5" s="319"/>
+      <c r="AB5" s="319"/>
+      <c r="AC5" s="320"/>
+      <c r="AD5" s="320"/>
+      <c r="AE5" s="319"/>
+      <c r="AF5" s="319"/>
+      <c r="AG5" s="320"/>
+      <c r="AH5" s="320"/>
+      <c r="AI5" s="319"/>
+      <c r="AJ5" s="320"/>
+      <c r="AK5" s="320"/>
+      <c r="AL5" s="319"/>
+      <c r="AM5" s="320"/>
+      <c r="AN5" s="321"/>
     </row>
     <row r="6" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -10198,198 +10198,198 @@
       <c r="AN6" s="344"/>
     </row>
     <row r="7" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="303" t="s">
+      <c r="A7" s="304" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="303" t="s">
+      <c r="B7" s="304" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="330" t="s">
+      <c r="C7" s="307" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="303" t="s">
+      <c r="D7" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="303" t="s">
+      <c r="E7" s="304" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="303" t="s">
+      <c r="F7" s="304" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="303" t="s">
+      <c r="G7" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="303" t="s">
+      <c r="H7" s="304" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="303" t="s">
+      <c r="I7" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="303" t="s">
+      <c r="J7" s="304" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="303" t="s">
+      <c r="K7" s="304" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="318" t="s">
+      <c r="L7" s="325" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="303" t="s">
+      <c r="M7" s="304" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="303" t="s">
+      <c r="N7" s="304" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="319" t="s">
+      <c r="O7" s="327" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="320"/>
-      <c r="Q7" s="320"/>
-      <c r="R7" s="320"/>
-      <c r="S7" s="320"/>
-      <c r="T7" s="320"/>
-      <c r="U7" s="320"/>
-      <c r="V7" s="321"/>
-      <c r="W7" s="303" t="s">
+      <c r="P7" s="328"/>
+      <c r="Q7" s="328"/>
+      <c r="R7" s="328"/>
+      <c r="S7" s="328"/>
+      <c r="T7" s="328"/>
+      <c r="U7" s="328"/>
+      <c r="V7" s="329"/>
+      <c r="W7" s="304" t="s">
         <v>139</v>
       </c>
-      <c r="X7" s="317" t="s">
+      <c r="X7" s="308" t="s">
         <v>13</v>
       </c>
-      <c r="Y7" s="317" t="s">
+      <c r="Y7" s="308" t="s">
         <v>184</v>
       </c>
-      <c r="Z7" s="331" t="s">
+      <c r="Z7" s="309" t="s">
         <v>175</v>
       </c>
-      <c r="AA7" s="303" t="s">
+      <c r="AA7" s="304" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="303" t="s">
+      <c r="AB7" s="304" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="319" t="s">
+      <c r="AC7" s="327" t="s">
         <v>155</v>
       </c>
-      <c r="AD7" s="321"/>
-      <c r="AE7" s="308" t="s">
+      <c r="AD7" s="329"/>
+      <c r="AE7" s="310" t="s">
         <v>17</v>
       </c>
-      <c r="AF7" s="305" t="s">
+      <c r="AF7" s="336" t="s">
         <v>107</v>
       </c>
-      <c r="AG7" s="305" t="s">
+      <c r="AG7" s="336" t="s">
         <v>108</v>
       </c>
-      <c r="AH7" s="305" t="s">
+      <c r="AH7" s="336" t="s">
         <v>106</v>
       </c>
-      <c r="AI7" s="307" t="s">
+      <c r="AI7" s="338" t="s">
         <v>147</v>
       </c>
-      <c r="AJ7" s="308" t="s">
+      <c r="AJ7" s="310" t="s">
         <v>136</v>
       </c>
-      <c r="AK7" s="308" t="s">
+      <c r="AK7" s="310" t="s">
         <v>137</v>
       </c>
-      <c r="AL7" s="303" t="s">
+      <c r="AL7" s="304" t="s">
         <v>135</v>
       </c>
-      <c r="AM7" s="303" t="s">
+      <c r="AM7" s="304" t="s">
         <v>146</v>
       </c>
-      <c r="AN7" s="303" t="s">
+      <c r="AN7" s="304" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="309"/>
-      <c r="B8" s="309"/>
-      <c r="C8" s="330"/>
-      <c r="D8" s="309"/>
-      <c r="E8" s="309"/>
-      <c r="F8" s="309"/>
-      <c r="G8" s="309"/>
-      <c r="H8" s="309"/>
-      <c r="I8" s="309"/>
-      <c r="J8" s="309"/>
-      <c r="K8" s="309"/>
-      <c r="L8" s="309"/>
-      <c r="M8" s="309"/>
-      <c r="N8" s="309"/>
-      <c r="O8" s="322"/>
-      <c r="P8" s="323"/>
-      <c r="Q8" s="323"/>
-      <c r="R8" s="323"/>
-      <c r="S8" s="323"/>
-      <c r="T8" s="323"/>
-      <c r="U8" s="323"/>
-      <c r="V8" s="324"/>
-      <c r="W8" s="309"/>
-      <c r="X8" s="309"/>
-      <c r="Y8" s="309"/>
-      <c r="Z8" s="309"/>
-      <c r="AA8" s="309"/>
-      <c r="AB8" s="309"/>
-      <c r="AC8" s="325"/>
-      <c r="AD8" s="327"/>
-      <c r="AE8" s="309"/>
-      <c r="AF8" s="306"/>
-      <c r="AG8" s="306"/>
-      <c r="AH8" s="307"/>
-      <c r="AI8" s="306"/>
-      <c r="AJ8" s="309"/>
-      <c r="AK8" s="308"/>
-      <c r="AL8" s="309"/>
-      <c r="AM8" s="303"/>
-      <c r="AN8" s="304"/>
+      <c r="A8" s="305"/>
+      <c r="B8" s="305"/>
+      <c r="C8" s="307"/>
+      <c r="D8" s="305"/>
+      <c r="E8" s="305"/>
+      <c r="F8" s="305"/>
+      <c r="G8" s="305"/>
+      <c r="H8" s="305"/>
+      <c r="I8" s="305"/>
+      <c r="J8" s="305"/>
+      <c r="K8" s="305"/>
+      <c r="L8" s="305"/>
+      <c r="M8" s="305"/>
+      <c r="N8" s="305"/>
+      <c r="O8" s="330"/>
+      <c r="P8" s="331"/>
+      <c r="Q8" s="331"/>
+      <c r="R8" s="331"/>
+      <c r="S8" s="331"/>
+      <c r="T8" s="331"/>
+      <c r="U8" s="331"/>
+      <c r="V8" s="332"/>
+      <c r="W8" s="305"/>
+      <c r="X8" s="305"/>
+      <c r="Y8" s="305"/>
+      <c r="Z8" s="305"/>
+      <c r="AA8" s="305"/>
+      <c r="AB8" s="305"/>
+      <c r="AC8" s="333"/>
+      <c r="AD8" s="335"/>
+      <c r="AE8" s="305"/>
+      <c r="AF8" s="337"/>
+      <c r="AG8" s="337"/>
+      <c r="AH8" s="338"/>
+      <c r="AI8" s="337"/>
+      <c r="AJ8" s="305"/>
+      <c r="AK8" s="310"/>
+      <c r="AL8" s="305"/>
+      <c r="AM8" s="304"/>
+      <c r="AN8" s="326"/>
     </row>
     <row r="9" spans="1:43" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="309"/>
-      <c r="B9" s="309"/>
-      <c r="C9" s="330"/>
-      <c r="D9" s="309"/>
-      <c r="E9" s="309"/>
-      <c r="F9" s="309"/>
-      <c r="G9" s="309"/>
-      <c r="H9" s="309"/>
-      <c r="I9" s="309"/>
-      <c r="J9" s="309"/>
-      <c r="K9" s="309"/>
-      <c r="L9" s="309"/>
-      <c r="M9" s="309"/>
-      <c r="N9" s="309"/>
-      <c r="O9" s="325"/>
-      <c r="P9" s="326"/>
-      <c r="Q9" s="326"/>
-      <c r="R9" s="326"/>
-      <c r="S9" s="326"/>
-      <c r="T9" s="326"/>
-      <c r="U9" s="326"/>
-      <c r="V9" s="327"/>
-      <c r="W9" s="309"/>
-      <c r="X9" s="309"/>
-      <c r="Y9" s="309"/>
-      <c r="Z9" s="309"/>
-      <c r="AA9" s="309"/>
-      <c r="AB9" s="309"/>
+      <c r="A9" s="305"/>
+      <c r="B9" s="305"/>
+      <c r="C9" s="307"/>
+      <c r="D9" s="305"/>
+      <c r="E9" s="305"/>
+      <c r="F9" s="305"/>
+      <c r="G9" s="305"/>
+      <c r="H9" s="305"/>
+      <c r="I9" s="305"/>
+      <c r="J9" s="305"/>
+      <c r="K9" s="305"/>
+      <c r="L9" s="305"/>
+      <c r="M9" s="305"/>
+      <c r="N9" s="305"/>
+      <c r="O9" s="333"/>
+      <c r="P9" s="334"/>
+      <c r="Q9" s="334"/>
+      <c r="R9" s="334"/>
+      <c r="S9" s="334"/>
+      <c r="T9" s="334"/>
+      <c r="U9" s="334"/>
+      <c r="V9" s="335"/>
+      <c r="W9" s="305"/>
+      <c r="X9" s="305"/>
+      <c r="Y9" s="305"/>
+      <c r="Z9" s="305"/>
+      <c r="AA9" s="305"/>
+      <c r="AB9" s="305"/>
       <c r="AC9" s="201" t="s">
         <v>153</v>
       </c>
       <c r="AD9" s="178" t="s">
         <v>154</v>
       </c>
-      <c r="AE9" s="309"/>
-      <c r="AF9" s="306"/>
-      <c r="AG9" s="306"/>
-      <c r="AH9" s="307"/>
-      <c r="AI9" s="306"/>
-      <c r="AJ9" s="309"/>
-      <c r="AK9" s="308"/>
-      <c r="AL9" s="309"/>
-      <c r="AM9" s="303"/>
-      <c r="AN9" s="304"/>
+      <c r="AE9" s="305"/>
+      <c r="AF9" s="337"/>
+      <c r="AG9" s="337"/>
+      <c r="AH9" s="338"/>
+      <c r="AI9" s="337"/>
+      <c r="AJ9" s="305"/>
+      <c r="AK9" s="310"/>
+      <c r="AL9" s="305"/>
+      <c r="AM9" s="304"/>
+      <c r="AN9" s="326"/>
       <c r="AO9">
         <f>Z11/W11</f>
         <v>0.50632226325372287</v>
@@ -15659,6 +15659,27 @@
   </sheetData>
   <autoFilter ref="A10:AQ54" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="37">
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AD8"/>
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A2:AB2"/>
@@ -15675,27 +15696,6 @@
     <mergeCell ref="H7:H9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:J9"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AD8"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
   </mergeCells>
   <pageMargins left="0.17" right="0.15748031496062992" top="0.41" bottom="0.23622047244094491" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
@@ -15744,36 +15744,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="341" t="s">
+      <c r="A1" s="339" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="311"/>
-      <c r="C1" s="312"/>
-      <c r="D1" s="311"/>
-      <c r="E1" s="311"/>
-      <c r="F1" s="311"/>
-      <c r="G1" s="311"/>
-      <c r="H1" s="311"/>
-      <c r="I1" s="311"/>
-      <c r="J1" s="311"/>
-      <c r="K1" s="311"/>
-      <c r="L1" s="311"/>
-      <c r="M1" s="311"/>
-      <c r="N1" s="311"/>
-      <c r="O1" s="311"/>
-      <c r="P1" s="311"/>
-      <c r="Q1" s="311"/>
-      <c r="R1" s="311"/>
-      <c r="S1" s="311"/>
-      <c r="T1" s="311"/>
-      <c r="U1" s="311"/>
-      <c r="V1" s="311"/>
-      <c r="W1" s="311"/>
-      <c r="X1" s="311"/>
-      <c r="Y1" s="311"/>
-      <c r="Z1" s="311"/>
-      <c r="AA1" s="311"/>
-      <c r="AB1" s="313"/>
+      <c r="B1" s="319"/>
+      <c r="C1" s="320"/>
+      <c r="D1" s="319"/>
+      <c r="E1" s="319"/>
+      <c r="F1" s="319"/>
+      <c r="G1" s="319"/>
+      <c r="H1" s="319"/>
+      <c r="I1" s="319"/>
+      <c r="J1" s="319"/>
+      <c r="K1" s="319"/>
+      <c r="L1" s="319"/>
+      <c r="M1" s="319"/>
+      <c r="N1" s="319"/>
+      <c r="O1" s="319"/>
+      <c r="P1" s="319"/>
+      <c r="Q1" s="319"/>
+      <c r="R1" s="319"/>
+      <c r="S1" s="319"/>
+      <c r="T1" s="319"/>
+      <c r="U1" s="319"/>
+      <c r="V1" s="319"/>
+      <c r="W1" s="319"/>
+      <c r="X1" s="319"/>
+      <c r="Y1" s="319"/>
+      <c r="Z1" s="319"/>
+      <c r="AA1" s="319"/>
+      <c r="AB1" s="321"/>
       <c r="AC1" s="17"/>
       <c r="AD1" s="17"/>
       <c r="AE1" s="1"/>
@@ -15790,36 +15790,36 @@
       <c r="AN1" s="160"/>
     </row>
     <row r="2" spans="1:43" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="314" t="s">
+      <c r="A2" s="322" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="311"/>
-      <c r="C2" s="312"/>
-      <c r="D2" s="311"/>
-      <c r="E2" s="311"/>
-      <c r="F2" s="311"/>
-      <c r="G2" s="311"/>
-      <c r="H2" s="311"/>
-      <c r="I2" s="311"/>
-      <c r="J2" s="311"/>
-      <c r="K2" s="311"/>
-      <c r="L2" s="311"/>
-      <c r="M2" s="311"/>
-      <c r="N2" s="311"/>
-      <c r="O2" s="311"/>
-      <c r="P2" s="311"/>
-      <c r="Q2" s="311"/>
-      <c r="R2" s="311"/>
-      <c r="S2" s="311"/>
-      <c r="T2" s="311"/>
-      <c r="U2" s="311"/>
-      <c r="V2" s="311"/>
-      <c r="W2" s="311"/>
-      <c r="X2" s="311"/>
-      <c r="Y2" s="311"/>
-      <c r="Z2" s="311"/>
-      <c r="AA2" s="311"/>
-      <c r="AB2" s="313"/>
+      <c r="B2" s="319"/>
+      <c r="C2" s="320"/>
+      <c r="D2" s="319"/>
+      <c r="E2" s="319"/>
+      <c r="F2" s="319"/>
+      <c r="G2" s="319"/>
+      <c r="H2" s="319"/>
+      <c r="I2" s="319"/>
+      <c r="J2" s="319"/>
+      <c r="K2" s="319"/>
+      <c r="L2" s="319"/>
+      <c r="M2" s="319"/>
+      <c r="N2" s="319"/>
+      <c r="O2" s="319"/>
+      <c r="P2" s="319"/>
+      <c r="Q2" s="319"/>
+      <c r="R2" s="319"/>
+      <c r="S2" s="319"/>
+      <c r="T2" s="319"/>
+      <c r="U2" s="319"/>
+      <c r="V2" s="319"/>
+      <c r="W2" s="319"/>
+      <c r="X2" s="319"/>
+      <c r="Y2" s="319"/>
+      <c r="Z2" s="319"/>
+      <c r="AA2" s="319"/>
+      <c r="AB2" s="321"/>
       <c r="AC2" s="17"/>
       <c r="AD2" s="17"/>
       <c r="AE2" s="1"/>
@@ -15876,92 +15876,92 @@
       <c r="AN3" s="160"/>
     </row>
     <row r="4" spans="1:43" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="315" t="s">
+      <c r="A4" s="323" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="311"/>
-      <c r="C4" s="312"/>
-      <c r="D4" s="311"/>
-      <c r="E4" s="311"/>
-      <c r="F4" s="311"/>
-      <c r="G4" s="311"/>
-      <c r="H4" s="311"/>
-      <c r="I4" s="311"/>
-      <c r="J4" s="311"/>
-      <c r="K4" s="311"/>
-      <c r="L4" s="311"/>
-      <c r="M4" s="311"/>
-      <c r="N4" s="311"/>
-      <c r="O4" s="311"/>
-      <c r="P4" s="311"/>
-      <c r="Q4" s="311"/>
-      <c r="R4" s="311"/>
-      <c r="S4" s="311"/>
-      <c r="T4" s="311"/>
-      <c r="U4" s="311"/>
-      <c r="V4" s="311"/>
-      <c r="W4" s="311"/>
-      <c r="X4" s="311"/>
-      <c r="Y4" s="311"/>
-      <c r="Z4" s="311"/>
-      <c r="AA4" s="311"/>
-      <c r="AB4" s="311"/>
-      <c r="AC4" s="312"/>
-      <c r="AD4" s="312"/>
-      <c r="AE4" s="311"/>
-      <c r="AF4" s="311"/>
-      <c r="AG4" s="312"/>
-      <c r="AH4" s="312"/>
-      <c r="AI4" s="311"/>
-      <c r="AJ4" s="312"/>
-      <c r="AK4" s="312"/>
-      <c r="AL4" s="311"/>
-      <c r="AM4" s="312"/>
-      <c r="AN4" s="313"/>
+      <c r="B4" s="319"/>
+      <c r="C4" s="320"/>
+      <c r="D4" s="319"/>
+      <c r="E4" s="319"/>
+      <c r="F4" s="319"/>
+      <c r="G4" s="319"/>
+      <c r="H4" s="319"/>
+      <c r="I4" s="319"/>
+      <c r="J4" s="319"/>
+      <c r="K4" s="319"/>
+      <c r="L4" s="319"/>
+      <c r="M4" s="319"/>
+      <c r="N4" s="319"/>
+      <c r="O4" s="319"/>
+      <c r="P4" s="319"/>
+      <c r="Q4" s="319"/>
+      <c r="R4" s="319"/>
+      <c r="S4" s="319"/>
+      <c r="T4" s="319"/>
+      <c r="U4" s="319"/>
+      <c r="V4" s="319"/>
+      <c r="W4" s="319"/>
+      <c r="X4" s="319"/>
+      <c r="Y4" s="319"/>
+      <c r="Z4" s="319"/>
+      <c r="AA4" s="319"/>
+      <c r="AB4" s="319"/>
+      <c r="AC4" s="320"/>
+      <c r="AD4" s="320"/>
+      <c r="AE4" s="319"/>
+      <c r="AF4" s="319"/>
+      <c r="AG4" s="320"/>
+      <c r="AH4" s="320"/>
+      <c r="AI4" s="319"/>
+      <c r="AJ4" s="320"/>
+      <c r="AK4" s="320"/>
+      <c r="AL4" s="319"/>
+      <c r="AM4" s="320"/>
+      <c r="AN4" s="321"/>
     </row>
     <row r="5" spans="1:43" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="316" t="s">
+      <c r="A5" s="324" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="311"/>
-      <c r="C5" s="312"/>
-      <c r="D5" s="311"/>
-      <c r="E5" s="311"/>
-      <c r="F5" s="311"/>
-      <c r="G5" s="311"/>
-      <c r="H5" s="311"/>
-      <c r="I5" s="311"/>
-      <c r="J5" s="311"/>
-      <c r="K5" s="311"/>
-      <c r="L5" s="311"/>
-      <c r="M5" s="311"/>
-      <c r="N5" s="311"/>
-      <c r="O5" s="311"/>
-      <c r="P5" s="311"/>
-      <c r="Q5" s="311"/>
-      <c r="R5" s="311"/>
-      <c r="S5" s="311"/>
-      <c r="T5" s="311"/>
-      <c r="U5" s="311"/>
-      <c r="V5" s="311"/>
-      <c r="W5" s="311"/>
-      <c r="X5" s="311"/>
-      <c r="Y5" s="311"/>
-      <c r="Z5" s="311"/>
-      <c r="AA5" s="311"/>
-      <c r="AB5" s="311"/>
-      <c r="AC5" s="312"/>
-      <c r="AD5" s="312"/>
-      <c r="AE5" s="311"/>
-      <c r="AF5" s="311"/>
-      <c r="AG5" s="312"/>
-      <c r="AH5" s="312"/>
-      <c r="AI5" s="311"/>
-      <c r="AJ5" s="312"/>
-      <c r="AK5" s="312"/>
-      <c r="AL5" s="311"/>
-      <c r="AM5" s="312"/>
-      <c r="AN5" s="313"/>
+      <c r="B5" s="319"/>
+      <c r="C5" s="320"/>
+      <c r="D5" s="319"/>
+      <c r="E5" s="319"/>
+      <c r="F5" s="319"/>
+      <c r="G5" s="319"/>
+      <c r="H5" s="319"/>
+      <c r="I5" s="319"/>
+      <c r="J5" s="319"/>
+      <c r="K5" s="319"/>
+      <c r="L5" s="319"/>
+      <c r="M5" s="319"/>
+      <c r="N5" s="319"/>
+      <c r="O5" s="319"/>
+      <c r="P5" s="319"/>
+      <c r="Q5" s="319"/>
+      <c r="R5" s="319"/>
+      <c r="S5" s="319"/>
+      <c r="T5" s="319"/>
+      <c r="U5" s="319"/>
+      <c r="V5" s="319"/>
+      <c r="W5" s="319"/>
+      <c r="X5" s="319"/>
+      <c r="Y5" s="319"/>
+      <c r="Z5" s="319"/>
+      <c r="AA5" s="319"/>
+      <c r="AB5" s="319"/>
+      <c r="AC5" s="320"/>
+      <c r="AD5" s="320"/>
+      <c r="AE5" s="319"/>
+      <c r="AF5" s="319"/>
+      <c r="AG5" s="320"/>
+      <c r="AH5" s="320"/>
+      <c r="AI5" s="319"/>
+      <c r="AJ5" s="320"/>
+      <c r="AK5" s="320"/>
+      <c r="AL5" s="319"/>
+      <c r="AM5" s="320"/>
+      <c r="AN5" s="321"/>
     </row>
     <row r="6" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -16010,198 +16010,198 @@
       <c r="AN6" s="344"/>
     </row>
     <row r="7" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="303" t="s">
+      <c r="A7" s="304" t="s">
         <v>1</v>
       </c>
       <c r="B7" s="345" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="330" t="s">
+      <c r="C7" s="307" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="303" t="s">
+      <c r="D7" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="303" t="s">
+      <c r="E7" s="304" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="303" t="s">
+      <c r="F7" s="304" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="303" t="s">
+      <c r="G7" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="303" t="s">
+      <c r="H7" s="304" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="303" t="s">
+      <c r="I7" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="303" t="s">
+      <c r="J7" s="304" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="303" t="s">
+      <c r="K7" s="304" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="318" t="s">
+      <c r="L7" s="325" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="303" t="s">
+      <c r="M7" s="304" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="303" t="s">
+      <c r="N7" s="304" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="319" t="s">
+      <c r="O7" s="327" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="320"/>
-      <c r="Q7" s="320"/>
-      <c r="R7" s="320"/>
-      <c r="S7" s="320"/>
-      <c r="T7" s="320"/>
-      <c r="U7" s="320"/>
-      <c r="V7" s="321"/>
-      <c r="W7" s="303" t="s">
+      <c r="P7" s="328"/>
+      <c r="Q7" s="328"/>
+      <c r="R7" s="328"/>
+      <c r="S7" s="328"/>
+      <c r="T7" s="328"/>
+      <c r="U7" s="328"/>
+      <c r="V7" s="329"/>
+      <c r="W7" s="304" t="s">
         <v>139</v>
       </c>
-      <c r="X7" s="317" t="s">
+      <c r="X7" s="308" t="s">
         <v>13</v>
       </c>
-      <c r="Y7" s="317" t="s">
+      <c r="Y7" s="308" t="s">
         <v>184</v>
       </c>
-      <c r="Z7" s="331" t="s">
+      <c r="Z7" s="309" t="s">
         <v>175</v>
       </c>
-      <c r="AA7" s="303" t="s">
+      <c r="AA7" s="304" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="303" t="s">
+      <c r="AB7" s="304" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="319" t="s">
+      <c r="AC7" s="327" t="s">
         <v>155</v>
       </c>
-      <c r="AD7" s="321"/>
-      <c r="AE7" s="308" t="s">
+      <c r="AD7" s="329"/>
+      <c r="AE7" s="310" t="s">
         <v>17</v>
       </c>
-      <c r="AF7" s="305" t="s">
+      <c r="AF7" s="336" t="s">
         <v>107</v>
       </c>
-      <c r="AG7" s="305" t="s">
+      <c r="AG7" s="336" t="s">
         <v>108</v>
       </c>
-      <c r="AH7" s="305" t="s">
+      <c r="AH7" s="336" t="s">
         <v>106</v>
       </c>
-      <c r="AI7" s="307" t="s">
+      <c r="AI7" s="338" t="s">
         <v>147</v>
       </c>
-      <c r="AJ7" s="308" t="s">
+      <c r="AJ7" s="310" t="s">
         <v>136</v>
       </c>
-      <c r="AK7" s="308" t="s">
+      <c r="AK7" s="310" t="s">
         <v>137</v>
       </c>
-      <c r="AL7" s="303" t="s">
+      <c r="AL7" s="304" t="s">
         <v>135</v>
       </c>
-      <c r="AM7" s="303" t="s">
+      <c r="AM7" s="304" t="s">
         <v>146</v>
       </c>
-      <c r="AN7" s="303" t="s">
+      <c r="AN7" s="304" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="309"/>
+      <c r="A8" s="305"/>
       <c r="B8" s="346"/>
-      <c r="C8" s="330"/>
-      <c r="D8" s="309"/>
-      <c r="E8" s="309"/>
-      <c r="F8" s="309"/>
-      <c r="G8" s="309"/>
-      <c r="H8" s="309"/>
-      <c r="I8" s="309"/>
-      <c r="J8" s="309"/>
-      <c r="K8" s="309"/>
-      <c r="L8" s="309"/>
-      <c r="M8" s="309"/>
-      <c r="N8" s="309"/>
-      <c r="O8" s="322"/>
-      <c r="P8" s="323"/>
-      <c r="Q8" s="323"/>
-      <c r="R8" s="323"/>
-      <c r="S8" s="323"/>
-      <c r="T8" s="323"/>
-      <c r="U8" s="323"/>
-      <c r="V8" s="324"/>
-      <c r="W8" s="309"/>
-      <c r="X8" s="309"/>
-      <c r="Y8" s="309"/>
-      <c r="Z8" s="309"/>
-      <c r="AA8" s="309"/>
-      <c r="AB8" s="309"/>
-      <c r="AC8" s="325"/>
-      <c r="AD8" s="327"/>
-      <c r="AE8" s="309"/>
-      <c r="AF8" s="306"/>
-      <c r="AG8" s="306"/>
-      <c r="AH8" s="307"/>
-      <c r="AI8" s="306"/>
-      <c r="AJ8" s="309"/>
-      <c r="AK8" s="308"/>
-      <c r="AL8" s="309"/>
-      <c r="AM8" s="303"/>
-      <c r="AN8" s="304"/>
+      <c r="C8" s="307"/>
+      <c r="D8" s="305"/>
+      <c r="E8" s="305"/>
+      <c r="F8" s="305"/>
+      <c r="G8" s="305"/>
+      <c r="H8" s="305"/>
+      <c r="I8" s="305"/>
+      <c r="J8" s="305"/>
+      <c r="K8" s="305"/>
+      <c r="L8" s="305"/>
+      <c r="M8" s="305"/>
+      <c r="N8" s="305"/>
+      <c r="O8" s="330"/>
+      <c r="P8" s="331"/>
+      <c r="Q8" s="331"/>
+      <c r="R8" s="331"/>
+      <c r="S8" s="331"/>
+      <c r="T8" s="331"/>
+      <c r="U8" s="331"/>
+      <c r="V8" s="332"/>
+      <c r="W8" s="305"/>
+      <c r="X8" s="305"/>
+      <c r="Y8" s="305"/>
+      <c r="Z8" s="305"/>
+      <c r="AA8" s="305"/>
+      <c r="AB8" s="305"/>
+      <c r="AC8" s="333"/>
+      <c r="AD8" s="335"/>
+      <c r="AE8" s="305"/>
+      <c r="AF8" s="337"/>
+      <c r="AG8" s="337"/>
+      <c r="AH8" s="338"/>
+      <c r="AI8" s="337"/>
+      <c r="AJ8" s="305"/>
+      <c r="AK8" s="310"/>
+      <c r="AL8" s="305"/>
+      <c r="AM8" s="304"/>
+      <c r="AN8" s="326"/>
     </row>
     <row r="9" spans="1:43" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="309"/>
+      <c r="A9" s="305"/>
       <c r="B9" s="346"/>
-      <c r="C9" s="330"/>
-      <c r="D9" s="309"/>
-      <c r="E9" s="309"/>
-      <c r="F9" s="309"/>
-      <c r="G9" s="309"/>
-      <c r="H9" s="309"/>
-      <c r="I9" s="309"/>
-      <c r="J9" s="309"/>
-      <c r="K9" s="309"/>
-      <c r="L9" s="309"/>
-      <c r="M9" s="309"/>
-      <c r="N9" s="309"/>
-      <c r="O9" s="325"/>
-      <c r="P9" s="326"/>
-      <c r="Q9" s="326"/>
-      <c r="R9" s="326"/>
-      <c r="S9" s="326"/>
-      <c r="T9" s="326"/>
-      <c r="U9" s="326"/>
-      <c r="V9" s="327"/>
-      <c r="W9" s="309"/>
-      <c r="X9" s="309"/>
-      <c r="Y9" s="309"/>
-      <c r="Z9" s="309"/>
-      <c r="AA9" s="309"/>
-      <c r="AB9" s="309"/>
+      <c r="C9" s="307"/>
+      <c r="D9" s="305"/>
+      <c r="E9" s="305"/>
+      <c r="F9" s="305"/>
+      <c r="G9" s="305"/>
+      <c r="H9" s="305"/>
+      <c r="I9" s="305"/>
+      <c r="J9" s="305"/>
+      <c r="K9" s="305"/>
+      <c r="L9" s="305"/>
+      <c r="M9" s="305"/>
+      <c r="N9" s="305"/>
+      <c r="O9" s="333"/>
+      <c r="P9" s="334"/>
+      <c r="Q9" s="334"/>
+      <c r="R9" s="334"/>
+      <c r="S9" s="334"/>
+      <c r="T9" s="334"/>
+      <c r="U9" s="334"/>
+      <c r="V9" s="335"/>
+      <c r="W9" s="305"/>
+      <c r="X9" s="305"/>
+      <c r="Y9" s="305"/>
+      <c r="Z9" s="305"/>
+      <c r="AA9" s="305"/>
+      <c r="AB9" s="305"/>
       <c r="AC9" s="201" t="s">
         <v>153</v>
       </c>
       <c r="AD9" s="178" t="s">
         <v>154</v>
       </c>
-      <c r="AE9" s="309"/>
-      <c r="AF9" s="306"/>
-      <c r="AG9" s="306"/>
-      <c r="AH9" s="307"/>
-      <c r="AI9" s="306"/>
-      <c r="AJ9" s="309"/>
-      <c r="AK9" s="308"/>
-      <c r="AL9" s="309"/>
-      <c r="AM9" s="303"/>
-      <c r="AN9" s="304"/>
+      <c r="AE9" s="305"/>
+      <c r="AF9" s="337"/>
+      <c r="AG9" s="337"/>
+      <c r="AH9" s="338"/>
+      <c r="AI9" s="337"/>
+      <c r="AJ9" s="305"/>
+      <c r="AK9" s="310"/>
+      <c r="AL9" s="305"/>
+      <c r="AM9" s="304"/>
+      <c r="AN9" s="326"/>
       <c r="AO9">
         <f>Z11/W11</f>
         <v>0.50320398224028773</v>
@@ -22375,27 +22375,6 @@
   </sheetData>
   <autoFilter ref="A10:AQ73" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AD8"/>
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A2:AB2"/>
@@ -22412,6 +22391,27 @@
     <mergeCell ref="H7:H9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:J9"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AD8"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
   </mergeCells>
   <pageMargins left="0.17" right="0.15748031496062992" top="0.41" bottom="0.23622047244094491" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
@@ -22463,37 +22463,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="310" t="s">
+      <c r="A1" s="318" t="s">
         <v>206</v>
       </c>
-      <c r="B1" s="311"/>
-      <c r="C1" s="312"/>
-      <c r="D1" s="311"/>
-      <c r="E1" s="311"/>
-      <c r="F1" s="311"/>
-      <c r="G1" s="311"/>
-      <c r="H1" s="311"/>
-      <c r="I1" s="311"/>
-      <c r="J1" s="311"/>
-      <c r="K1" s="311"/>
-      <c r="L1" s="311"/>
-      <c r="M1" s="311"/>
-      <c r="N1" s="311"/>
-      <c r="O1" s="311"/>
-      <c r="P1" s="311"/>
-      <c r="Q1" s="311"/>
-      <c r="R1" s="311"/>
-      <c r="S1" s="311"/>
-      <c r="T1" s="311"/>
-      <c r="U1" s="311"/>
-      <c r="V1" s="311"/>
-      <c r="W1" s="311"/>
-      <c r="X1" s="311"/>
-      <c r="Y1" s="311"/>
-      <c r="Z1" s="312"/>
-      <c r="AA1" s="311"/>
-      <c r="AB1" s="311"/>
-      <c r="AC1" s="313"/>
+      <c r="B1" s="319"/>
+      <c r="C1" s="320"/>
+      <c r="D1" s="319"/>
+      <c r="E1" s="319"/>
+      <c r="F1" s="319"/>
+      <c r="G1" s="319"/>
+      <c r="H1" s="319"/>
+      <c r="I1" s="319"/>
+      <c r="J1" s="319"/>
+      <c r="K1" s="319"/>
+      <c r="L1" s="319"/>
+      <c r="M1" s="319"/>
+      <c r="N1" s="319"/>
+      <c r="O1" s="319"/>
+      <c r="P1" s="319"/>
+      <c r="Q1" s="319"/>
+      <c r="R1" s="319"/>
+      <c r="S1" s="319"/>
+      <c r="T1" s="319"/>
+      <c r="U1" s="319"/>
+      <c r="V1" s="319"/>
+      <c r="W1" s="319"/>
+      <c r="X1" s="319"/>
+      <c r="Y1" s="319"/>
+      <c r="Z1" s="320"/>
+      <c r="AA1" s="319"/>
+      <c r="AB1" s="319"/>
+      <c r="AC1" s="321"/>
       <c r="AD1" s="261"/>
       <c r="AE1" s="261"/>
       <c r="AF1" s="261"/>
@@ -22516,37 +22516,37 @@
       <c r="AS1" s="160"/>
     </row>
     <row r="2" spans="1:51" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="314" t="s">
+      <c r="A2" s="322" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="311"/>
-      <c r="C2" s="312"/>
-      <c r="D2" s="311"/>
-      <c r="E2" s="311"/>
-      <c r="F2" s="311"/>
-      <c r="G2" s="311"/>
-      <c r="H2" s="311"/>
-      <c r="I2" s="311"/>
-      <c r="J2" s="311"/>
-      <c r="K2" s="311"/>
-      <c r="L2" s="311"/>
-      <c r="M2" s="311"/>
-      <c r="N2" s="311"/>
-      <c r="O2" s="311"/>
-      <c r="P2" s="311"/>
-      <c r="Q2" s="311"/>
-      <c r="R2" s="311"/>
-      <c r="S2" s="311"/>
-      <c r="T2" s="311"/>
-      <c r="U2" s="311"/>
-      <c r="V2" s="311"/>
-      <c r="W2" s="311"/>
-      <c r="X2" s="311"/>
-      <c r="Y2" s="311"/>
-      <c r="Z2" s="312"/>
-      <c r="AA2" s="311"/>
-      <c r="AB2" s="311"/>
-      <c r="AC2" s="313"/>
+      <c r="B2" s="319"/>
+      <c r="C2" s="320"/>
+      <c r="D2" s="319"/>
+      <c r="E2" s="319"/>
+      <c r="F2" s="319"/>
+      <c r="G2" s="319"/>
+      <c r="H2" s="319"/>
+      <c r="I2" s="319"/>
+      <c r="J2" s="319"/>
+      <c r="K2" s="319"/>
+      <c r="L2" s="319"/>
+      <c r="M2" s="319"/>
+      <c r="N2" s="319"/>
+      <c r="O2" s="319"/>
+      <c r="P2" s="319"/>
+      <c r="Q2" s="319"/>
+      <c r="R2" s="319"/>
+      <c r="S2" s="319"/>
+      <c r="T2" s="319"/>
+      <c r="U2" s="319"/>
+      <c r="V2" s="319"/>
+      <c r="W2" s="319"/>
+      <c r="X2" s="319"/>
+      <c r="Y2" s="319"/>
+      <c r="Z2" s="320"/>
+      <c r="AA2" s="319"/>
+      <c r="AB2" s="319"/>
+      <c r="AC2" s="321"/>
       <c r="AD2" s="261"/>
       <c r="AE2" s="261"/>
       <c r="AF2" s="261"/>
@@ -22612,102 +22612,102 @@
       <c r="AS3" s="160"/>
     </row>
     <row r="4" spans="1:51" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="315" t="s">
+      <c r="A4" s="323" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="311"/>
-      <c r="C4" s="312"/>
-      <c r="D4" s="311"/>
-      <c r="E4" s="311"/>
-      <c r="F4" s="311"/>
-      <c r="G4" s="311"/>
-      <c r="H4" s="311"/>
-      <c r="I4" s="311"/>
-      <c r="J4" s="311"/>
-      <c r="K4" s="311"/>
-      <c r="L4" s="311"/>
-      <c r="M4" s="311"/>
-      <c r="N4" s="311"/>
-      <c r="O4" s="311"/>
-      <c r="P4" s="311"/>
-      <c r="Q4" s="311"/>
-      <c r="R4" s="311"/>
-      <c r="S4" s="311"/>
-      <c r="T4" s="311"/>
-      <c r="U4" s="311"/>
-      <c r="V4" s="311"/>
-      <c r="W4" s="311"/>
-      <c r="X4" s="311"/>
-      <c r="Y4" s="311"/>
-      <c r="Z4" s="312"/>
-      <c r="AA4" s="311"/>
-      <c r="AB4" s="311"/>
-      <c r="AC4" s="311"/>
-      <c r="AD4" s="312"/>
-      <c r="AE4" s="312"/>
-      <c r="AF4" s="312"/>
-      <c r="AG4" s="312"/>
-      <c r="AH4" s="312"/>
-      <c r="AI4" s="311"/>
-      <c r="AJ4" s="311"/>
-      <c r="AK4" s="312"/>
-      <c r="AL4" s="312"/>
-      <c r="AM4" s="311"/>
-      <c r="AN4" s="312"/>
-      <c r="AO4" s="312"/>
-      <c r="AP4" s="311"/>
-      <c r="AQ4" s="312"/>
-      <c r="AR4" s="312"/>
-      <c r="AS4" s="313"/>
+      <c r="B4" s="319"/>
+      <c r="C4" s="320"/>
+      <c r="D4" s="319"/>
+      <c r="E4" s="319"/>
+      <c r="F4" s="319"/>
+      <c r="G4" s="319"/>
+      <c r="H4" s="319"/>
+      <c r="I4" s="319"/>
+      <c r="J4" s="319"/>
+      <c r="K4" s="319"/>
+      <c r="L4" s="319"/>
+      <c r="M4" s="319"/>
+      <c r="N4" s="319"/>
+      <c r="O4" s="319"/>
+      <c r="P4" s="319"/>
+      <c r="Q4" s="319"/>
+      <c r="R4" s="319"/>
+      <c r="S4" s="319"/>
+      <c r="T4" s="319"/>
+      <c r="U4" s="319"/>
+      <c r="V4" s="319"/>
+      <c r="W4" s="319"/>
+      <c r="X4" s="319"/>
+      <c r="Y4" s="319"/>
+      <c r="Z4" s="320"/>
+      <c r="AA4" s="319"/>
+      <c r="AB4" s="319"/>
+      <c r="AC4" s="319"/>
+      <c r="AD4" s="320"/>
+      <c r="AE4" s="320"/>
+      <c r="AF4" s="320"/>
+      <c r="AG4" s="320"/>
+      <c r="AH4" s="320"/>
+      <c r="AI4" s="319"/>
+      <c r="AJ4" s="319"/>
+      <c r="AK4" s="320"/>
+      <c r="AL4" s="320"/>
+      <c r="AM4" s="319"/>
+      <c r="AN4" s="320"/>
+      <c r="AO4" s="320"/>
+      <c r="AP4" s="319"/>
+      <c r="AQ4" s="320"/>
+      <c r="AR4" s="320"/>
+      <c r="AS4" s="321"/>
     </row>
     <row r="5" spans="1:51" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="316" t="s">
+      <c r="A5" s="324" t="s">
         <v>224</v>
       </c>
-      <c r="B5" s="311"/>
-      <c r="C5" s="312"/>
-      <c r="D5" s="311"/>
-      <c r="E5" s="311"/>
-      <c r="F5" s="311"/>
-      <c r="G5" s="311"/>
-      <c r="H5" s="311"/>
-      <c r="I5" s="311"/>
-      <c r="J5" s="311"/>
-      <c r="K5" s="311"/>
-      <c r="L5" s="311"/>
-      <c r="M5" s="311"/>
-      <c r="N5" s="311"/>
-      <c r="O5" s="311"/>
-      <c r="P5" s="311"/>
-      <c r="Q5" s="311"/>
-      <c r="R5" s="311"/>
-      <c r="S5" s="311"/>
-      <c r="T5" s="311"/>
-      <c r="U5" s="311"/>
-      <c r="V5" s="311"/>
-      <c r="W5" s="311"/>
-      <c r="X5" s="311"/>
-      <c r="Y5" s="311"/>
-      <c r="Z5" s="312"/>
-      <c r="AA5" s="311"/>
-      <c r="AB5" s="311"/>
-      <c r="AC5" s="311"/>
-      <c r="AD5" s="312"/>
-      <c r="AE5" s="312"/>
-      <c r="AF5" s="312"/>
-      <c r="AG5" s="312"/>
-      <c r="AH5" s="312"/>
-      <c r="AI5" s="311"/>
-      <c r="AJ5" s="311"/>
-      <c r="AK5" s="312"/>
-      <c r="AL5" s="312"/>
-      <c r="AM5" s="311"/>
-      <c r="AN5" s="312"/>
-      <c r="AO5" s="312"/>
-      <c r="AP5" s="311"/>
-      <c r="AQ5" s="312"/>
-      <c r="AR5" s="312"/>
-      <c r="AS5" s="313"/>
+      <c r="B5" s="319"/>
+      <c r="C5" s="320"/>
+      <c r="D5" s="319"/>
+      <c r="E5" s="319"/>
+      <c r="F5" s="319"/>
+      <c r="G5" s="319"/>
+      <c r="H5" s="319"/>
+      <c r="I5" s="319"/>
+      <c r="J5" s="319"/>
+      <c r="K5" s="319"/>
+      <c r="L5" s="319"/>
+      <c r="M5" s="319"/>
+      <c r="N5" s="319"/>
+      <c r="O5" s="319"/>
+      <c r="P5" s="319"/>
+      <c r="Q5" s="319"/>
+      <c r="R5" s="319"/>
+      <c r="S5" s="319"/>
+      <c r="T5" s="319"/>
+      <c r="U5" s="319"/>
+      <c r="V5" s="319"/>
+      <c r="W5" s="319"/>
+      <c r="X5" s="319"/>
+      <c r="Y5" s="319"/>
+      <c r="Z5" s="320"/>
+      <c r="AA5" s="319"/>
+      <c r="AB5" s="319"/>
+      <c r="AC5" s="319"/>
+      <c r="AD5" s="320"/>
+      <c r="AE5" s="320"/>
+      <c r="AF5" s="320"/>
+      <c r="AG5" s="320"/>
+      <c r="AH5" s="320"/>
+      <c r="AI5" s="319"/>
+      <c r="AJ5" s="319"/>
+      <c r="AK5" s="320"/>
+      <c r="AL5" s="320"/>
+      <c r="AM5" s="319"/>
+      <c r="AN5" s="320"/>
+      <c r="AO5" s="320"/>
+      <c r="AP5" s="319"/>
+      <c r="AQ5" s="320"/>
+      <c r="AR5" s="320"/>
+      <c r="AS5" s="321"/>
     </row>
     <row r="6" spans="1:51" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -22743,219 +22743,219 @@
       <c r="AC6" s="11"/>
       <c r="AD6" s="11"/>
       <c r="AE6" s="11"/>
-      <c r="AF6" s="328" t="s">
+      <c r="AF6" s="303" t="s">
         <v>151</v>
       </c>
-      <c r="AG6" s="328"/>
-      <c r="AH6" s="328"/>
-      <c r="AI6" s="328"/>
-      <c r="AJ6" s="328"/>
-      <c r="AK6" s="328"/>
-      <c r="AL6" s="328"/>
-      <c r="AM6" s="328"/>
-      <c r="AN6" s="328"/>
-      <c r="AO6" s="328"/>
-      <c r="AP6" s="328"/>
-      <c r="AQ6" s="328"/>
-      <c r="AR6" s="328"/>
-      <c r="AS6" s="328"/>
+      <c r="AG6" s="303"/>
+      <c r="AH6" s="303"/>
+      <c r="AI6" s="303"/>
+      <c r="AJ6" s="303"/>
+      <c r="AK6" s="303"/>
+      <c r="AL6" s="303"/>
+      <c r="AM6" s="303"/>
+      <c r="AN6" s="303"/>
+      <c r="AO6" s="303"/>
+      <c r="AP6" s="303"/>
+      <c r="AQ6" s="303"/>
+      <c r="AR6" s="303"/>
+      <c r="AS6" s="303"/>
     </row>
     <row r="7" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="303" t="s">
+      <c r="A7" s="304" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="303" t="s">
+      <c r="B7" s="304" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="330" t="s">
+      <c r="C7" s="307" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="303" t="s">
+      <c r="D7" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="303" t="s">
+      <c r="E7" s="304" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="303" t="s">
+      <c r="F7" s="304" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="303" t="s">
+      <c r="G7" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="303" t="s">
+      <c r="H7" s="304" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="303" t="s">
+      <c r="I7" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="303" t="s">
+      <c r="J7" s="304" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="303" t="s">
+      <c r="K7" s="304" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="318" t="s">
+      <c r="L7" s="325" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="303" t="s">
+      <c r="M7" s="304" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="303" t="s">
+      <c r="N7" s="304" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="319" t="s">
+      <c r="O7" s="327" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="320"/>
-      <c r="Q7" s="320"/>
-      <c r="R7" s="320"/>
-      <c r="S7" s="320"/>
-      <c r="T7" s="320"/>
-      <c r="U7" s="320"/>
-      <c r="V7" s="321"/>
-      <c r="W7" s="303" t="s">
+      <c r="P7" s="328"/>
+      <c r="Q7" s="328"/>
+      <c r="R7" s="328"/>
+      <c r="S7" s="328"/>
+      <c r="T7" s="328"/>
+      <c r="U7" s="328"/>
+      <c r="V7" s="329"/>
+      <c r="W7" s="304" t="s">
         <v>202</v>
       </c>
-      <c r="X7" s="317" t="s">
+      <c r="X7" s="308" t="s">
         <v>13</v>
       </c>
-      <c r="Y7" s="317" t="s">
+      <c r="Y7" s="308" t="s">
         <v>221</v>
       </c>
-      <c r="Z7" s="336" t="s">
+      <c r="Z7" s="315" t="s">
         <v>222</v>
       </c>
-      <c r="AA7" s="331" t="s">
+      <c r="AA7" s="309" t="s">
         <v>223</v>
       </c>
-      <c r="AB7" s="303" t="s">
+      <c r="AB7" s="304" t="s">
         <v>15</v>
       </c>
-      <c r="AC7" s="303" t="s">
+      <c r="AC7" s="304" t="s">
         <v>16</v>
       </c>
-      <c r="AD7" s="332" t="s">
+      <c r="AD7" s="311" t="s">
         <v>211</v>
       </c>
-      <c r="AE7" s="332"/>
-      <c r="AF7" s="332"/>
-      <c r="AG7" s="333" t="s">
+      <c r="AE7" s="311"/>
+      <c r="AF7" s="311"/>
+      <c r="AG7" s="312" t="s">
         <v>215</v>
       </c>
-      <c r="AH7" s="333" t="s">
+      <c r="AH7" s="312" t="s">
         <v>219</v>
       </c>
-      <c r="AI7" s="308" t="s">
+      <c r="AI7" s="310" t="s">
         <v>17</v>
       </c>
-      <c r="AJ7" s="305" t="s">
+      <c r="AJ7" s="336" t="s">
         <v>107</v>
       </c>
-      <c r="AK7" s="305" t="s">
+      <c r="AK7" s="336" t="s">
         <v>108</v>
       </c>
-      <c r="AL7" s="305" t="s">
+      <c r="AL7" s="336" t="s">
         <v>106</v>
       </c>
-      <c r="AM7" s="307" t="s">
+      <c r="AM7" s="338" t="s">
         <v>147</v>
       </c>
-      <c r="AN7" s="308" t="s">
+      <c r="AN7" s="310" t="s">
         <v>136</v>
       </c>
-      <c r="AO7" s="308" t="s">
+      <c r="AO7" s="310" t="s">
         <v>137</v>
       </c>
-      <c r="AP7" s="303" t="s">
+      <c r="AP7" s="304" t="s">
         <v>135</v>
       </c>
-      <c r="AQ7" s="303" t="s">
+      <c r="AQ7" s="304" t="s">
         <v>146</v>
       </c>
-      <c r="AR7" s="303" t="s">
+      <c r="AR7" s="304" t="s">
         <v>228</v>
       </c>
-      <c r="AS7" s="303" t="s">
+      <c r="AS7" s="304" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A8" s="309"/>
-      <c r="B8" s="329"/>
-      <c r="C8" s="330"/>
-      <c r="D8" s="309"/>
-      <c r="E8" s="309"/>
-      <c r="F8" s="309"/>
-      <c r="G8" s="309"/>
-      <c r="H8" s="309"/>
-      <c r="I8" s="309"/>
-      <c r="J8" s="309"/>
-      <c r="K8" s="309"/>
-      <c r="L8" s="309"/>
-      <c r="M8" s="309"/>
-      <c r="N8" s="304"/>
-      <c r="O8" s="322"/>
-      <c r="P8" s="323"/>
-      <c r="Q8" s="323"/>
-      <c r="R8" s="323"/>
-      <c r="S8" s="323"/>
-      <c r="T8" s="323"/>
-      <c r="U8" s="323"/>
-      <c r="V8" s="324"/>
-      <c r="W8" s="309"/>
-      <c r="X8" s="309"/>
-      <c r="Y8" s="309"/>
-      <c r="Z8" s="337"/>
-      <c r="AA8" s="309"/>
-      <c r="AB8" s="309"/>
-      <c r="AC8" s="309"/>
-      <c r="AD8" s="332"/>
-      <c r="AE8" s="332"/>
-      <c r="AF8" s="332"/>
-      <c r="AG8" s="334"/>
-      <c r="AH8" s="334"/>
-      <c r="AI8" s="309"/>
-      <c r="AJ8" s="306"/>
-      <c r="AK8" s="306"/>
-      <c r="AL8" s="307"/>
-      <c r="AM8" s="306"/>
-      <c r="AN8" s="309"/>
-      <c r="AO8" s="308"/>
-      <c r="AP8" s="309"/>
-      <c r="AQ8" s="303"/>
-      <c r="AR8" s="303"/>
-      <c r="AS8" s="304"/>
+      <c r="A8" s="305"/>
+      <c r="B8" s="306"/>
+      <c r="C8" s="307"/>
+      <c r="D8" s="305"/>
+      <c r="E8" s="305"/>
+      <c r="F8" s="305"/>
+      <c r="G8" s="305"/>
+      <c r="H8" s="305"/>
+      <c r="I8" s="305"/>
+      <c r="J8" s="305"/>
+      <c r="K8" s="305"/>
+      <c r="L8" s="305"/>
+      <c r="M8" s="305"/>
+      <c r="N8" s="326"/>
+      <c r="O8" s="330"/>
+      <c r="P8" s="331"/>
+      <c r="Q8" s="331"/>
+      <c r="R8" s="331"/>
+      <c r="S8" s="331"/>
+      <c r="T8" s="331"/>
+      <c r="U8" s="331"/>
+      <c r="V8" s="332"/>
+      <c r="W8" s="305"/>
+      <c r="X8" s="305"/>
+      <c r="Y8" s="305"/>
+      <c r="Z8" s="316"/>
+      <c r="AA8" s="305"/>
+      <c r="AB8" s="305"/>
+      <c r="AC8" s="305"/>
+      <c r="AD8" s="311"/>
+      <c r="AE8" s="311"/>
+      <c r="AF8" s="311"/>
+      <c r="AG8" s="313"/>
+      <c r="AH8" s="313"/>
+      <c r="AI8" s="305"/>
+      <c r="AJ8" s="337"/>
+      <c r="AK8" s="337"/>
+      <c r="AL8" s="338"/>
+      <c r="AM8" s="337"/>
+      <c r="AN8" s="305"/>
+      <c r="AO8" s="310"/>
+      <c r="AP8" s="305"/>
+      <c r="AQ8" s="304"/>
+      <c r="AR8" s="304"/>
+      <c r="AS8" s="326"/>
     </row>
     <row r="9" spans="1:51" ht="104.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="309"/>
-      <c r="B9" s="329"/>
-      <c r="C9" s="330"/>
-      <c r="D9" s="309"/>
-      <c r="E9" s="309"/>
-      <c r="F9" s="309"/>
-      <c r="G9" s="309"/>
-      <c r="H9" s="309"/>
-      <c r="I9" s="309"/>
-      <c r="J9" s="309"/>
-      <c r="K9" s="309"/>
-      <c r="L9" s="309"/>
-      <c r="M9" s="309"/>
-      <c r="N9" s="304"/>
-      <c r="O9" s="325"/>
-      <c r="P9" s="326"/>
-      <c r="Q9" s="326"/>
-      <c r="R9" s="326"/>
-      <c r="S9" s="326"/>
-      <c r="T9" s="326"/>
-      <c r="U9" s="326"/>
-      <c r="V9" s="327"/>
-      <c r="W9" s="309"/>
-      <c r="X9" s="309"/>
-      <c r="Y9" s="309"/>
-      <c r="Z9" s="338"/>
-      <c r="AA9" s="309"/>
-      <c r="AB9" s="309"/>
-      <c r="AC9" s="309"/>
+      <c r="A9" s="305"/>
+      <c r="B9" s="306"/>
+      <c r="C9" s="307"/>
+      <c r="D9" s="305"/>
+      <c r="E9" s="305"/>
+      <c r="F9" s="305"/>
+      <c r="G9" s="305"/>
+      <c r="H9" s="305"/>
+      <c r="I9" s="305"/>
+      <c r="J9" s="305"/>
+      <c r="K9" s="305"/>
+      <c r="L9" s="305"/>
+      <c r="M9" s="305"/>
+      <c r="N9" s="326"/>
+      <c r="O9" s="333"/>
+      <c r="P9" s="334"/>
+      <c r="Q9" s="334"/>
+      <c r="R9" s="334"/>
+      <c r="S9" s="334"/>
+      <c r="T9" s="334"/>
+      <c r="U9" s="334"/>
+      <c r="V9" s="335"/>
+      <c r="W9" s="305"/>
+      <c r="X9" s="305"/>
+      <c r="Y9" s="305"/>
+      <c r="Z9" s="317"/>
+      <c r="AA9" s="305"/>
+      <c r="AB9" s="305"/>
+      <c r="AC9" s="305"/>
       <c r="AD9" s="264" t="s">
         <v>212</v>
       </c>
@@ -22965,19 +22965,19 @@
       <c r="AF9" s="264" t="s">
         <v>213</v>
       </c>
-      <c r="AG9" s="335"/>
-      <c r="AH9" s="335"/>
-      <c r="AI9" s="309"/>
-      <c r="AJ9" s="306"/>
-      <c r="AK9" s="306"/>
-      <c r="AL9" s="307"/>
-      <c r="AM9" s="306"/>
-      <c r="AN9" s="309"/>
-      <c r="AO9" s="308"/>
-      <c r="AP9" s="309"/>
-      <c r="AQ9" s="303"/>
-      <c r="AR9" s="303"/>
-      <c r="AS9" s="304"/>
+      <c r="AG9" s="314"/>
+      <c r="AH9" s="314"/>
+      <c r="AI9" s="305"/>
+      <c r="AJ9" s="337"/>
+      <c r="AK9" s="337"/>
+      <c r="AL9" s="338"/>
+      <c r="AM9" s="337"/>
+      <c r="AN9" s="305"/>
+      <c r="AO9" s="310"/>
+      <c r="AP9" s="305"/>
+      <c r="AQ9" s="304"/>
+      <c r="AR9" s="304"/>
+      <c r="AS9" s="326"/>
       <c r="AT9">
         <f>AA12/W12</f>
         <v>0.7450786614439131</v>
@@ -30165,6 +30165,31 @@
   </sheetData>
   <autoFilter ref="A10:AV74" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="41">
+    <mergeCell ref="AQ7:AQ9"/>
+    <mergeCell ref="AS7:AS9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AO7:AO9"/>
+    <mergeCell ref="AR7:AR9"/>
+    <mergeCell ref="A1:AC1"/>
+    <mergeCell ref="A2:AC2"/>
+    <mergeCell ref="A4:AS4"/>
+    <mergeCell ref="A5:AS5"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:J9"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="W7:W9"/>
     <mergeCell ref="AF6:AS6"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="B7:B9"/>
@@ -30181,31 +30206,6 @@
     <mergeCell ref="AH7:AH9"/>
     <mergeCell ref="Z7:Z9"/>
     <mergeCell ref="AP7:AP9"/>
-    <mergeCell ref="A1:AC1"/>
-    <mergeCell ref="A2:AC2"/>
-    <mergeCell ref="A4:AS4"/>
-    <mergeCell ref="A5:AS5"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:J9"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="AQ7:AQ9"/>
-    <mergeCell ref="AS7:AS9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AO7:AO9"/>
-    <mergeCell ref="AR7:AR9"/>
   </mergeCells>
   <pageMargins left="0.55000000000000004" right="0.15748031496062992" top="0.39370078740157483" bottom="0.23622047244094491" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" r:id="rId1"/>

--- a/report/bao-cao.xlsx
+++ b/report/bao-cao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HXuan\BaocaoGiaingan\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FA9573-D474-493D-BA5C-4796F006D8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72CDCCF-E769-4CB6-AED7-BC6811B5E1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,17 +16,17 @@
     <sheet name="bc" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="BAO CAO 30-06 (2)" sheetId="3" state="hidden" r:id="rId2"/>
     <sheet name="BAO CAO 30-06 (KHV mới)" sheetId="4" state="hidden" r:id="rId3"/>
-    <sheet name="BAO CAO 25-09-2026" sheetId="5" r:id="rId4"/>
+    <sheet name="BAO CAO 01-10-2026" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BAO CAO 25-09-2026'!$A$10:$AK$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BAO CAO 01-10-2026'!$A$10:$AK$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BAO CAO 30-06 (2)'!$A$10:$AQ$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BAO CAO 30-06 (KHV mới)'!$A$10:$AQ$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">bc!$A$10:$AP$80</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'BAO CAO 25-09-2026'!$A$1:$AH$77</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'BAO CAO 01-10-2026'!$A$1:$AH$77</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'BAO CAO 30-06 (2)'!$A$1:$AN$58</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'BAO CAO 30-06 (KHV mới)'!$A$1:$AN$79</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'BAO CAO 25-09-2026'!$7:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'BAO CAO 01-10-2026'!$7:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'BAO CAO 30-06 (2)'!$7:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'BAO CAO 30-06 (KHV mới)'!$7:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">bc!$7:$9</definedName>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="239">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -707,16 +707,7 @@
     <t>QĐ 5545 ngày 25/08/2028</t>
   </si>
   <si>
-    <t>Uớc chi trong tháng 9/2026</t>
-  </si>
-  <si>
-    <t>Ước chi tháng 09/2026</t>
-  </si>
-  <si>
     <t>Số còn chi trong tháng 09/2026</t>
-  </si>
-  <si>
-    <t>Số đã chi trong tháng 09/2026</t>
   </si>
   <si>
     <t>Hồ sơ A/C KT gửi thanh toán</t>
@@ -756,13 +747,25 @@
   </si>
   <si>
     <t>Số giải ngân
-trong tuần (từ ngày 19/09/2026 đến 25/09/2026</t>
+trong tuần (từ ngày 01/10/2026 đến 04/10/2026</t>
   </si>
   <si>
-    <t>(Tính đến ngày 25/09/2026)</t>
+    <t>Ước chi tháng 10/2026</t>
   </si>
   <si>
-    <t>TỔNG SỐ GIẢI NGÂN ĐẾN NGÀY BÁO CÁO NGÀY 25/09/2026</t>
+    <t>Số đã chi trong tháng 10/2026</t>
+  </si>
+  <si>
+    <t>Uớc chi trong tháng 10/2026</t>
+  </si>
+  <si>
+    <t>7507257</t>
+  </si>
+  <si>
+    <t>(Tính đến ngày 06/10/2026)</t>
+  </si>
+  <si>
+    <t>TỔNG SỐ GIẢI NGÂN ĐẾN NGÀY BÁO CÁO NGÀY 06/10/2026</t>
   </si>
   <si>
     <t>Cán bộ Kỹ thuật</t>
@@ -794,8 +797,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="10">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@"/>
     <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
@@ -1649,10 +1652,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="60" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="60" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="60" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="343">
+  <cellXfs count="344">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1994,7 +1997,7 @@
     <xf numFmtId="10" fontId="47" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="25" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2202,7 +2205,7 @@
     <xf numFmtId="0" fontId="64" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="65" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="65" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="65" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2334,9 +2337,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="60" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="70" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="73" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
@@ -2344,9 +2344,6 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2360,22 +2357,10 @@
     <xf numFmtId="171" fontId="29" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="29" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="29" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="29" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="171" fontId="29" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="70" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="70" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="70" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="171" fontId="70" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2406,9 +2391,6 @@
     <xf numFmtId="0" fontId="79" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="80" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2425,21 +2407,47 @@
     <xf numFmtId="171" fontId="25" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="71" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="54" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="70" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="28" fillId="12" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="42" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="29" fillId="9" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="77" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2458,6 +2466,7 @@
     <xf numFmtId="0" fontId="64" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2497,32 +2506,27 @@
     <xf numFmtId="167" fontId="63" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2533,9 +2537,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="47" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2551,6 +2552,9 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2804,36 +2808,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="331" t="s">
+      <c r="A1" s="329" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="304"/>
-      <c r="C1" s="305"/>
-      <c r="D1" s="304"/>
-      <c r="E1" s="304"/>
-      <c r="F1" s="304"/>
-      <c r="G1" s="304"/>
-      <c r="H1" s="304"/>
-      <c r="I1" s="304"/>
-      <c r="J1" s="304"/>
-      <c r="K1" s="304"/>
-      <c r="L1" s="304"/>
-      <c r="M1" s="304"/>
-      <c r="N1" s="304"/>
-      <c r="O1" s="304"/>
-      <c r="P1" s="304"/>
-      <c r="Q1" s="304"/>
-      <c r="R1" s="304"/>
-      <c r="S1" s="304"/>
-      <c r="T1" s="304"/>
-      <c r="U1" s="304"/>
-      <c r="V1" s="304"/>
-      <c r="W1" s="304"/>
-      <c r="X1" s="304"/>
-      <c r="Y1" s="304"/>
-      <c r="Z1" s="304"/>
-      <c r="AA1" s="304"/>
-      <c r="AB1" s="306"/>
+      <c r="B1" s="305"/>
+      <c r="C1" s="306"/>
+      <c r="D1" s="305"/>
+      <c r="E1" s="305"/>
+      <c r="F1" s="305"/>
+      <c r="G1" s="305"/>
+      <c r="H1" s="305"/>
+      <c r="I1" s="305"/>
+      <c r="J1" s="305"/>
+      <c r="K1" s="305"/>
+      <c r="L1" s="305"/>
+      <c r="M1" s="305"/>
+      <c r="N1" s="305"/>
+      <c r="O1" s="305"/>
+      <c r="P1" s="305"/>
+      <c r="Q1" s="305"/>
+      <c r="R1" s="305"/>
+      <c r="S1" s="305"/>
+      <c r="T1" s="305"/>
+      <c r="U1" s="305"/>
+      <c r="V1" s="305"/>
+      <c r="W1" s="305"/>
+      <c r="X1" s="305"/>
+      <c r="Y1" s="305"/>
+      <c r="Z1" s="305"/>
+      <c r="AA1" s="305"/>
+      <c r="AB1" s="307"/>
       <c r="AC1" s="17"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="2"/>
@@ -2849,36 +2853,36 @@
       <c r="AM1" s="3"/>
     </row>
     <row r="2" spans="1:42" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="307" t="s">
+      <c r="A2" s="308" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="304"/>
-      <c r="C2" s="305"/>
-      <c r="D2" s="304"/>
-      <c r="E2" s="304"/>
-      <c r="F2" s="304"/>
-      <c r="G2" s="304"/>
-      <c r="H2" s="304"/>
-      <c r="I2" s="304"/>
-      <c r="J2" s="304"/>
-      <c r="K2" s="304"/>
-      <c r="L2" s="304"/>
-      <c r="M2" s="304"/>
-      <c r="N2" s="304"/>
-      <c r="O2" s="304"/>
-      <c r="P2" s="304"/>
-      <c r="Q2" s="304"/>
-      <c r="R2" s="304"/>
-      <c r="S2" s="304"/>
-      <c r="T2" s="304"/>
-      <c r="U2" s="304"/>
-      <c r="V2" s="304"/>
-      <c r="W2" s="304"/>
-      <c r="X2" s="304"/>
-      <c r="Y2" s="304"/>
-      <c r="Z2" s="304"/>
-      <c r="AA2" s="304"/>
-      <c r="AB2" s="306"/>
+      <c r="B2" s="305"/>
+      <c r="C2" s="306"/>
+      <c r="D2" s="305"/>
+      <c r="E2" s="305"/>
+      <c r="F2" s="305"/>
+      <c r="G2" s="305"/>
+      <c r="H2" s="305"/>
+      <c r="I2" s="305"/>
+      <c r="J2" s="305"/>
+      <c r="K2" s="305"/>
+      <c r="L2" s="305"/>
+      <c r="M2" s="305"/>
+      <c r="N2" s="305"/>
+      <c r="O2" s="305"/>
+      <c r="P2" s="305"/>
+      <c r="Q2" s="305"/>
+      <c r="R2" s="305"/>
+      <c r="S2" s="305"/>
+      <c r="T2" s="305"/>
+      <c r="U2" s="305"/>
+      <c r="V2" s="305"/>
+      <c r="W2" s="305"/>
+      <c r="X2" s="305"/>
+      <c r="Y2" s="305"/>
+      <c r="Z2" s="305"/>
+      <c r="AA2" s="305"/>
+      <c r="AB2" s="307"/>
       <c r="AC2" s="17"/>
       <c r="AD2" s="1"/>
       <c r="AE2" s="2"/>
@@ -2933,90 +2937,90 @@
       <c r="AM3" s="3"/>
     </row>
     <row r="4" spans="1:42" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="308" t="s">
+      <c r="A4" s="309" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="304"/>
-      <c r="C4" s="305"/>
-      <c r="D4" s="304"/>
-      <c r="E4" s="304"/>
-      <c r="F4" s="304"/>
-      <c r="G4" s="304"/>
-      <c r="H4" s="304"/>
-      <c r="I4" s="304"/>
-      <c r="J4" s="304"/>
-      <c r="K4" s="304"/>
-      <c r="L4" s="304"/>
-      <c r="M4" s="304"/>
-      <c r="N4" s="304"/>
-      <c r="O4" s="304"/>
-      <c r="P4" s="304"/>
-      <c r="Q4" s="304"/>
-      <c r="R4" s="304"/>
-      <c r="S4" s="304"/>
-      <c r="T4" s="304"/>
-      <c r="U4" s="304"/>
-      <c r="V4" s="304"/>
-      <c r="W4" s="304"/>
-      <c r="X4" s="304"/>
-      <c r="Y4" s="304"/>
-      <c r="Z4" s="304"/>
-      <c r="AA4" s="304"/>
-      <c r="AB4" s="304"/>
-      <c r="AC4" s="305"/>
-      <c r="AD4" s="304"/>
-      <c r="AE4" s="304"/>
-      <c r="AF4" s="305"/>
-      <c r="AG4" s="305"/>
-      <c r="AH4" s="304"/>
-      <c r="AI4" s="305"/>
-      <c r="AJ4" s="305"/>
-      <c r="AK4" s="304"/>
-      <c r="AL4" s="305"/>
-      <c r="AM4" s="306"/>
+      <c r="B4" s="305"/>
+      <c r="C4" s="306"/>
+      <c r="D4" s="305"/>
+      <c r="E4" s="305"/>
+      <c r="F4" s="305"/>
+      <c r="G4" s="305"/>
+      <c r="H4" s="305"/>
+      <c r="I4" s="305"/>
+      <c r="J4" s="305"/>
+      <c r="K4" s="305"/>
+      <c r="L4" s="305"/>
+      <c r="M4" s="305"/>
+      <c r="N4" s="305"/>
+      <c r="O4" s="305"/>
+      <c r="P4" s="305"/>
+      <c r="Q4" s="305"/>
+      <c r="R4" s="305"/>
+      <c r="S4" s="305"/>
+      <c r="T4" s="305"/>
+      <c r="U4" s="305"/>
+      <c r="V4" s="305"/>
+      <c r="W4" s="305"/>
+      <c r="X4" s="305"/>
+      <c r="Y4" s="305"/>
+      <c r="Z4" s="305"/>
+      <c r="AA4" s="305"/>
+      <c r="AB4" s="305"/>
+      <c r="AC4" s="306"/>
+      <c r="AD4" s="305"/>
+      <c r="AE4" s="305"/>
+      <c r="AF4" s="306"/>
+      <c r="AG4" s="306"/>
+      <c r="AH4" s="305"/>
+      <c r="AI4" s="306"/>
+      <c r="AJ4" s="306"/>
+      <c r="AK4" s="305"/>
+      <c r="AL4" s="306"/>
+      <c r="AM4" s="307"/>
     </row>
     <row r="5" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="309" t="s">
+      <c r="A5" s="310" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="304"/>
-      <c r="C5" s="305"/>
-      <c r="D5" s="304"/>
-      <c r="E5" s="304"/>
-      <c r="F5" s="304"/>
-      <c r="G5" s="304"/>
-      <c r="H5" s="304"/>
-      <c r="I5" s="304"/>
-      <c r="J5" s="304"/>
-      <c r="K5" s="304"/>
-      <c r="L5" s="304"/>
-      <c r="M5" s="304"/>
-      <c r="N5" s="304"/>
-      <c r="O5" s="304"/>
-      <c r="P5" s="304"/>
-      <c r="Q5" s="304"/>
-      <c r="R5" s="304"/>
-      <c r="S5" s="304"/>
-      <c r="T5" s="304"/>
-      <c r="U5" s="304"/>
-      <c r="V5" s="304"/>
-      <c r="W5" s="304"/>
-      <c r="X5" s="304"/>
-      <c r="Y5" s="304"/>
-      <c r="Z5" s="304"/>
-      <c r="AA5" s="304"/>
-      <c r="AB5" s="304"/>
-      <c r="AC5" s="305"/>
-      <c r="AD5" s="304"/>
-      <c r="AE5" s="304"/>
-      <c r="AF5" s="305"/>
-      <c r="AG5" s="305"/>
-      <c r="AH5" s="304"/>
-      <c r="AI5" s="305"/>
-      <c r="AJ5" s="305"/>
-      <c r="AK5" s="304"/>
-      <c r="AL5" s="305"/>
-      <c r="AM5" s="306"/>
+      <c r="B5" s="305"/>
+      <c r="C5" s="306"/>
+      <c r="D5" s="305"/>
+      <c r="E5" s="305"/>
+      <c r="F5" s="305"/>
+      <c r="G5" s="305"/>
+      <c r="H5" s="305"/>
+      <c r="I5" s="305"/>
+      <c r="J5" s="305"/>
+      <c r="K5" s="305"/>
+      <c r="L5" s="305"/>
+      <c r="M5" s="305"/>
+      <c r="N5" s="305"/>
+      <c r="O5" s="305"/>
+      <c r="P5" s="305"/>
+      <c r="Q5" s="305"/>
+      <c r="R5" s="305"/>
+      <c r="S5" s="305"/>
+      <c r="T5" s="305"/>
+      <c r="U5" s="305"/>
+      <c r="V5" s="305"/>
+      <c r="W5" s="305"/>
+      <c r="X5" s="305"/>
+      <c r="Y5" s="305"/>
+      <c r="Z5" s="305"/>
+      <c r="AA5" s="305"/>
+      <c r="AB5" s="305"/>
+      <c r="AC5" s="306"/>
+      <c r="AD5" s="305"/>
+      <c r="AE5" s="305"/>
+      <c r="AF5" s="306"/>
+      <c r="AG5" s="306"/>
+      <c r="AH5" s="305"/>
+      <c r="AI5" s="306"/>
+      <c r="AJ5" s="306"/>
+      <c r="AK5" s="305"/>
+      <c r="AL5" s="306"/>
+      <c r="AM5" s="307"/>
     </row>
     <row r="6" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -3050,71 +3054,71 @@
       <c r="AA6" s="16"/>
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
-      <c r="AD6" s="332"/>
-      <c r="AE6" s="305"/>
-      <c r="AF6" s="305"/>
-      <c r="AG6" s="305"/>
-      <c r="AH6" s="305"/>
-      <c r="AI6" s="305"/>
-      <c r="AJ6" s="305"/>
-      <c r="AK6" s="305"/>
-      <c r="AL6" s="305"/>
-      <c r="AM6" s="305"/>
+      <c r="AD6" s="331"/>
+      <c r="AE6" s="306"/>
+      <c r="AF6" s="306"/>
+      <c r="AG6" s="306"/>
+      <c r="AH6" s="306"/>
+      <c r="AI6" s="306"/>
+      <c r="AJ6" s="306"/>
+      <c r="AK6" s="306"/>
+      <c r="AL6" s="306"/>
+      <c r="AM6" s="306"/>
     </row>
     <row r="7" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="296" t="s">
+      <c r="A7" s="303" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="296" t="s">
+      <c r="B7" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="322" t="s">
+      <c r="C7" s="324" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="296" t="s">
+      <c r="D7" s="303" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="296" t="s">
+      <c r="E7" s="303" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="296" t="s">
+      <c r="F7" s="303" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="296" t="s">
+      <c r="G7" s="303" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="296" t="s">
+      <c r="H7" s="303" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="296" t="s">
+      <c r="I7" s="303" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="296" t="s">
+      <c r="J7" s="303" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="296" t="s">
+      <c r="K7" s="303" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="329" t="s">
+      <c r="L7" s="333" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="296" t="s">
+      <c r="M7" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="296" t="s">
+      <c r="N7" s="303" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="311" t="s">
+      <c r="O7" s="313" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="312"/>
-      <c r="Q7" s="312"/>
-      <c r="R7" s="312"/>
-      <c r="S7" s="312"/>
-      <c r="T7" s="312"/>
-      <c r="U7" s="312"/>
-      <c r="V7" s="313"/>
-      <c r="W7" s="296" t="s">
+      <c r="P7" s="314"/>
+      <c r="Q7" s="314"/>
+      <c r="R7" s="314"/>
+      <c r="S7" s="314"/>
+      <c r="T7" s="314"/>
+      <c r="U7" s="314"/>
+      <c r="V7" s="315"/>
+      <c r="W7" s="303" t="s">
         <v>139</v>
       </c>
       <c r="X7" s="330" t="s">
@@ -3123,130 +3127,130 @@
       <c r="Y7" s="330" t="s">
         <v>14</v>
       </c>
-      <c r="Z7" s="301" t="s">
+      <c r="Z7" s="297" t="s">
         <v>150</v>
       </c>
-      <c r="AA7" s="296" t="s">
+      <c r="AA7" s="303" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="296" t="s">
+      <c r="AB7" s="303" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="296" t="s">
+      <c r="AC7" s="303" t="s">
         <v>134</v>
       </c>
-      <c r="AD7" s="301" t="s">
+      <c r="AD7" s="297" t="s">
         <v>17</v>
       </c>
-      <c r="AE7" s="298" t="s">
+      <c r="AE7" s="326" t="s">
         <v>107</v>
       </c>
-      <c r="AF7" s="298" t="s">
+      <c r="AF7" s="326" t="s">
         <v>108</v>
       </c>
-      <c r="AG7" s="298" t="s">
+      <c r="AG7" s="326" t="s">
         <v>106</v>
       </c>
-      <c r="AH7" s="300" t="s">
+      <c r="AH7" s="328" t="s">
         <v>147</v>
       </c>
-      <c r="AI7" s="301" t="s">
+      <c r="AI7" s="297" t="s">
         <v>136</v>
       </c>
-      <c r="AJ7" s="301" t="s">
+      <c r="AJ7" s="297" t="s">
         <v>137</v>
       </c>
-      <c r="AK7" s="296" t="s">
+      <c r="AK7" s="303" t="s">
         <v>135</v>
       </c>
-      <c r="AL7" s="296" t="s">
+      <c r="AL7" s="303" t="s">
         <v>146</v>
       </c>
-      <c r="AM7" s="296" t="s">
+      <c r="AM7" s="303" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="302"/>
-      <c r="B8" s="302"/>
-      <c r="C8" s="322"/>
-      <c r="D8" s="302"/>
-      <c r="E8" s="302"/>
-      <c r="F8" s="302"/>
-      <c r="G8" s="302"/>
-      <c r="H8" s="302"/>
-      <c r="I8" s="302"/>
-      <c r="J8" s="302"/>
-      <c r="K8" s="302"/>
-      <c r="L8" s="302"/>
-      <c r="M8" s="302"/>
-      <c r="N8" s="302"/>
-      <c r="O8" s="314"/>
-      <c r="P8" s="315"/>
-      <c r="Q8" s="315"/>
-      <c r="R8" s="315"/>
-      <c r="S8" s="315"/>
-      <c r="T8" s="315"/>
-      <c r="U8" s="315"/>
-      <c r="V8" s="316"/>
-      <c r="W8" s="302"/>
-      <c r="X8" s="302"/>
-      <c r="Y8" s="302"/>
-      <c r="Z8" s="302"/>
-      <c r="AA8" s="302"/>
-      <c r="AB8" s="302"/>
-      <c r="AC8" s="296"/>
-      <c r="AD8" s="302"/>
-      <c r="AE8" s="299"/>
-      <c r="AF8" s="299"/>
-      <c r="AG8" s="300"/>
-      <c r="AH8" s="299"/>
-      <c r="AI8" s="302"/>
-      <c r="AJ8" s="301"/>
-      <c r="AK8" s="302"/>
-      <c r="AL8" s="296"/>
-      <c r="AM8" s="302"/>
+      <c r="A8" s="298"/>
+      <c r="B8" s="298"/>
+      <c r="C8" s="324"/>
+      <c r="D8" s="298"/>
+      <c r="E8" s="298"/>
+      <c r="F8" s="298"/>
+      <c r="G8" s="298"/>
+      <c r="H8" s="298"/>
+      <c r="I8" s="298"/>
+      <c r="J8" s="298"/>
+      <c r="K8" s="298"/>
+      <c r="L8" s="298"/>
+      <c r="M8" s="298"/>
+      <c r="N8" s="298"/>
+      <c r="O8" s="316"/>
+      <c r="P8" s="317"/>
+      <c r="Q8" s="317"/>
+      <c r="R8" s="317"/>
+      <c r="S8" s="317"/>
+      <c r="T8" s="317"/>
+      <c r="U8" s="317"/>
+      <c r="V8" s="318"/>
+      <c r="W8" s="298"/>
+      <c r="X8" s="298"/>
+      <c r="Y8" s="298"/>
+      <c r="Z8" s="298"/>
+      <c r="AA8" s="298"/>
+      <c r="AB8" s="298"/>
+      <c r="AC8" s="303"/>
+      <c r="AD8" s="298"/>
+      <c r="AE8" s="327"/>
+      <c r="AF8" s="327"/>
+      <c r="AG8" s="328"/>
+      <c r="AH8" s="327"/>
+      <c r="AI8" s="298"/>
+      <c r="AJ8" s="297"/>
+      <c r="AK8" s="298"/>
+      <c r="AL8" s="303"/>
+      <c r="AM8" s="298"/>
     </row>
     <row r="9" spans="1:42" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="302"/>
-      <c r="B9" s="302"/>
-      <c r="C9" s="322"/>
-      <c r="D9" s="302"/>
-      <c r="E9" s="302"/>
-      <c r="F9" s="302"/>
-      <c r="G9" s="302"/>
-      <c r="H9" s="302"/>
-      <c r="I9" s="302"/>
-      <c r="J9" s="302"/>
-      <c r="K9" s="302"/>
-      <c r="L9" s="302"/>
-      <c r="M9" s="302"/>
-      <c r="N9" s="302"/>
-      <c r="O9" s="317"/>
-      <c r="P9" s="318"/>
-      <c r="Q9" s="318"/>
-      <c r="R9" s="318"/>
-      <c r="S9" s="318"/>
-      <c r="T9" s="318"/>
-      <c r="U9" s="318"/>
-      <c r="V9" s="319"/>
-      <c r="W9" s="302"/>
-      <c r="X9" s="302"/>
-      <c r="Y9" s="302"/>
-      <c r="Z9" s="302"/>
-      <c r="AA9" s="302"/>
-      <c r="AB9" s="302"/>
-      <c r="AC9" s="296"/>
-      <c r="AD9" s="302"/>
-      <c r="AE9" s="299"/>
-      <c r="AF9" s="299"/>
-      <c r="AG9" s="300"/>
-      <c r="AH9" s="299"/>
-      <c r="AI9" s="302"/>
-      <c r="AJ9" s="301"/>
-      <c r="AK9" s="302"/>
-      <c r="AL9" s="296"/>
-      <c r="AM9" s="302"/>
+      <c r="A9" s="298"/>
+      <c r="B9" s="298"/>
+      <c r="C9" s="324"/>
+      <c r="D9" s="298"/>
+      <c r="E9" s="298"/>
+      <c r="F9" s="298"/>
+      <c r="G9" s="298"/>
+      <c r="H9" s="298"/>
+      <c r="I9" s="298"/>
+      <c r="J9" s="298"/>
+      <c r="K9" s="298"/>
+      <c r="L9" s="298"/>
+      <c r="M9" s="298"/>
+      <c r="N9" s="298"/>
+      <c r="O9" s="319"/>
+      <c r="P9" s="320"/>
+      <c r="Q9" s="320"/>
+      <c r="R9" s="320"/>
+      <c r="S9" s="320"/>
+      <c r="T9" s="320"/>
+      <c r="U9" s="320"/>
+      <c r="V9" s="321"/>
+      <c r="W9" s="298"/>
+      <c r="X9" s="298"/>
+      <c r="Y9" s="298"/>
+      <c r="Z9" s="298"/>
+      <c r="AA9" s="298"/>
+      <c r="AB9" s="298"/>
+      <c r="AC9" s="303"/>
+      <c r="AD9" s="298"/>
+      <c r="AE9" s="327"/>
+      <c r="AF9" s="327"/>
+      <c r="AG9" s="328"/>
+      <c r="AH9" s="327"/>
+      <c r="AI9" s="298"/>
+      <c r="AJ9" s="297"/>
+      <c r="AK9" s="298"/>
+      <c r="AL9" s="303"/>
+      <c r="AM9" s="298"/>
       <c r="AP9">
         <v>27</v>
       </c>
@@ -8695,47 +8699,47 @@
       </c>
     </row>
     <row r="77" spans="1:42" ht="29.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="328" t="s">
+      <c r="A77" s="332" t="s">
         <v>145</v>
       </c>
-      <c r="B77" s="302"/>
-      <c r="C77" s="302"/>
-      <c r="D77" s="302"/>
-      <c r="E77" s="302"/>
-      <c r="F77" s="302"/>
-      <c r="G77" s="302"/>
-      <c r="H77" s="302"/>
-      <c r="I77" s="302"/>
-      <c r="J77" s="302"/>
-      <c r="K77" s="302"/>
-      <c r="L77" s="302"/>
-      <c r="M77" s="302"/>
-      <c r="N77" s="302"/>
-      <c r="O77" s="302"/>
-      <c r="P77" s="302"/>
-      <c r="Q77" s="302"/>
-      <c r="R77" s="302"/>
-      <c r="S77" s="302"/>
-      <c r="T77" s="302"/>
-      <c r="U77" s="302"/>
-      <c r="V77" s="302"/>
-      <c r="W77" s="302"/>
-      <c r="X77" s="302"/>
-      <c r="Y77" s="302"/>
-      <c r="Z77" s="302"/>
-      <c r="AA77" s="302"/>
-      <c r="AB77" s="302"/>
-      <c r="AC77" s="302"/>
-      <c r="AD77" s="302"/>
-      <c r="AE77" s="302"/>
-      <c r="AF77" s="302"/>
-      <c r="AG77" s="302"/>
-      <c r="AH77" s="302"/>
-      <c r="AI77" s="302"/>
-      <c r="AJ77" s="302"/>
-      <c r="AK77" s="302"/>
-      <c r="AL77" s="302"/>
-      <c r="AM77" s="302"/>
+      <c r="B77" s="298"/>
+      <c r="C77" s="298"/>
+      <c r="D77" s="298"/>
+      <c r="E77" s="298"/>
+      <c r="F77" s="298"/>
+      <c r="G77" s="298"/>
+      <c r="H77" s="298"/>
+      <c r="I77" s="298"/>
+      <c r="J77" s="298"/>
+      <c r="K77" s="298"/>
+      <c r="L77" s="298"/>
+      <c r="M77" s="298"/>
+      <c r="N77" s="298"/>
+      <c r="O77" s="298"/>
+      <c r="P77" s="298"/>
+      <c r="Q77" s="298"/>
+      <c r="R77" s="298"/>
+      <c r="S77" s="298"/>
+      <c r="T77" s="298"/>
+      <c r="U77" s="298"/>
+      <c r="V77" s="298"/>
+      <c r="W77" s="298"/>
+      <c r="X77" s="298"/>
+      <c r="Y77" s="298"/>
+      <c r="Z77" s="298"/>
+      <c r="AA77" s="298"/>
+      <c r="AB77" s="298"/>
+      <c r="AC77" s="298"/>
+      <c r="AD77" s="298"/>
+      <c r="AE77" s="298"/>
+      <c r="AF77" s="298"/>
+      <c r="AG77" s="298"/>
+      <c r="AH77" s="298"/>
+      <c r="AI77" s="298"/>
+      <c r="AJ77" s="298"/>
+      <c r="AK77" s="298"/>
+      <c r="AL77" s="298"/>
+      <c r="AM77" s="298"/>
     </row>
     <row r="78" spans="1:42" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="81"/>
@@ -9835,12 +9839,22 @@
   </sheetData>
   <autoFilter ref="A10:AP80" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="38">
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AC9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="A77:AM77"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:J9"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="A7:A9"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A2:AB2"/>
     <mergeCell ref="A4:AM4"/>
@@ -9857,22 +9871,12 @@
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="X7:X9"/>
     <mergeCell ref="AD6:AM6"/>
-    <mergeCell ref="A77:AM77"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:J9"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AC9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="O7:V9"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.27559055118110237" top="0.47244094488188981" bottom="0.31496062992125984" header="0" footer="0"/>
   <pageSetup scale="80" orientation="landscape" r:id="rId1"/>
@@ -9921,36 +9925,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="331" t="s">
+      <c r="A1" s="329" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="304"/>
-      <c r="C1" s="305"/>
-      <c r="D1" s="304"/>
-      <c r="E1" s="304"/>
-      <c r="F1" s="304"/>
-      <c r="G1" s="304"/>
-      <c r="H1" s="304"/>
-      <c r="I1" s="304"/>
-      <c r="J1" s="304"/>
-      <c r="K1" s="304"/>
-      <c r="L1" s="304"/>
-      <c r="M1" s="304"/>
-      <c r="N1" s="304"/>
-      <c r="O1" s="304"/>
-      <c r="P1" s="304"/>
-      <c r="Q1" s="304"/>
-      <c r="R1" s="304"/>
-      <c r="S1" s="304"/>
-      <c r="T1" s="304"/>
-      <c r="U1" s="304"/>
-      <c r="V1" s="304"/>
-      <c r="W1" s="304"/>
-      <c r="X1" s="304"/>
-      <c r="Y1" s="304"/>
-      <c r="Z1" s="304"/>
-      <c r="AA1" s="304"/>
-      <c r="AB1" s="306"/>
+      <c r="B1" s="305"/>
+      <c r="C1" s="306"/>
+      <c r="D1" s="305"/>
+      <c r="E1" s="305"/>
+      <c r="F1" s="305"/>
+      <c r="G1" s="305"/>
+      <c r="H1" s="305"/>
+      <c r="I1" s="305"/>
+      <c r="J1" s="305"/>
+      <c r="K1" s="305"/>
+      <c r="L1" s="305"/>
+      <c r="M1" s="305"/>
+      <c r="N1" s="305"/>
+      <c r="O1" s="305"/>
+      <c r="P1" s="305"/>
+      <c r="Q1" s="305"/>
+      <c r="R1" s="305"/>
+      <c r="S1" s="305"/>
+      <c r="T1" s="305"/>
+      <c r="U1" s="305"/>
+      <c r="V1" s="305"/>
+      <c r="W1" s="305"/>
+      <c r="X1" s="305"/>
+      <c r="Y1" s="305"/>
+      <c r="Z1" s="305"/>
+      <c r="AA1" s="305"/>
+      <c r="AB1" s="307"/>
       <c r="AC1" s="17"/>
       <c r="AD1" s="17"/>
       <c r="AE1" s="1"/>
@@ -9967,36 +9971,36 @@
       <c r="AN1" s="160"/>
     </row>
     <row r="2" spans="1:43" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="307" t="s">
+      <c r="A2" s="308" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="304"/>
-      <c r="C2" s="305"/>
-      <c r="D2" s="304"/>
-      <c r="E2" s="304"/>
-      <c r="F2" s="304"/>
-      <c r="G2" s="304"/>
-      <c r="H2" s="304"/>
-      <c r="I2" s="304"/>
-      <c r="J2" s="304"/>
-      <c r="K2" s="304"/>
-      <c r="L2" s="304"/>
-      <c r="M2" s="304"/>
-      <c r="N2" s="304"/>
-      <c r="O2" s="304"/>
-      <c r="P2" s="304"/>
-      <c r="Q2" s="304"/>
-      <c r="R2" s="304"/>
-      <c r="S2" s="304"/>
-      <c r="T2" s="304"/>
-      <c r="U2" s="304"/>
-      <c r="V2" s="304"/>
-      <c r="W2" s="304"/>
-      <c r="X2" s="304"/>
-      <c r="Y2" s="304"/>
-      <c r="Z2" s="304"/>
-      <c r="AA2" s="304"/>
-      <c r="AB2" s="306"/>
+      <c r="B2" s="305"/>
+      <c r="C2" s="306"/>
+      <c r="D2" s="305"/>
+      <c r="E2" s="305"/>
+      <c r="F2" s="305"/>
+      <c r="G2" s="305"/>
+      <c r="H2" s="305"/>
+      <c r="I2" s="305"/>
+      <c r="J2" s="305"/>
+      <c r="K2" s="305"/>
+      <c r="L2" s="305"/>
+      <c r="M2" s="305"/>
+      <c r="N2" s="305"/>
+      <c r="O2" s="305"/>
+      <c r="P2" s="305"/>
+      <c r="Q2" s="305"/>
+      <c r="R2" s="305"/>
+      <c r="S2" s="305"/>
+      <c r="T2" s="305"/>
+      <c r="U2" s="305"/>
+      <c r="V2" s="305"/>
+      <c r="W2" s="305"/>
+      <c r="X2" s="305"/>
+      <c r="Y2" s="305"/>
+      <c r="Z2" s="305"/>
+      <c r="AA2" s="305"/>
+      <c r="AB2" s="307"/>
       <c r="AC2" s="17"/>
       <c r="AD2" s="17"/>
       <c r="AE2" s="1"/>
@@ -10053,92 +10057,92 @@
       <c r="AN3" s="160"/>
     </row>
     <row r="4" spans="1:43" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="308" t="s">
+      <c r="A4" s="309" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="304"/>
-      <c r="C4" s="305"/>
-      <c r="D4" s="304"/>
-      <c r="E4" s="304"/>
-      <c r="F4" s="304"/>
-      <c r="G4" s="304"/>
-      <c r="H4" s="304"/>
-      <c r="I4" s="304"/>
-      <c r="J4" s="304"/>
-      <c r="K4" s="304"/>
-      <c r="L4" s="304"/>
-      <c r="M4" s="304"/>
-      <c r="N4" s="304"/>
-      <c r="O4" s="304"/>
-      <c r="P4" s="304"/>
-      <c r="Q4" s="304"/>
-      <c r="R4" s="304"/>
-      <c r="S4" s="304"/>
-      <c r="T4" s="304"/>
-      <c r="U4" s="304"/>
-      <c r="V4" s="304"/>
-      <c r="W4" s="304"/>
-      <c r="X4" s="304"/>
-      <c r="Y4" s="304"/>
-      <c r="Z4" s="304"/>
-      <c r="AA4" s="304"/>
-      <c r="AB4" s="304"/>
-      <c r="AC4" s="305"/>
-      <c r="AD4" s="305"/>
-      <c r="AE4" s="304"/>
-      <c r="AF4" s="304"/>
-      <c r="AG4" s="305"/>
-      <c r="AH4" s="305"/>
-      <c r="AI4" s="304"/>
-      <c r="AJ4" s="305"/>
-      <c r="AK4" s="305"/>
-      <c r="AL4" s="304"/>
-      <c r="AM4" s="305"/>
-      <c r="AN4" s="306"/>
+      <c r="B4" s="305"/>
+      <c r="C4" s="306"/>
+      <c r="D4" s="305"/>
+      <c r="E4" s="305"/>
+      <c r="F4" s="305"/>
+      <c r="G4" s="305"/>
+      <c r="H4" s="305"/>
+      <c r="I4" s="305"/>
+      <c r="J4" s="305"/>
+      <c r="K4" s="305"/>
+      <c r="L4" s="305"/>
+      <c r="M4" s="305"/>
+      <c r="N4" s="305"/>
+      <c r="O4" s="305"/>
+      <c r="P4" s="305"/>
+      <c r="Q4" s="305"/>
+      <c r="R4" s="305"/>
+      <c r="S4" s="305"/>
+      <c r="T4" s="305"/>
+      <c r="U4" s="305"/>
+      <c r="V4" s="305"/>
+      <c r="W4" s="305"/>
+      <c r="X4" s="305"/>
+      <c r="Y4" s="305"/>
+      <c r="Z4" s="305"/>
+      <c r="AA4" s="305"/>
+      <c r="AB4" s="305"/>
+      <c r="AC4" s="306"/>
+      <c r="AD4" s="306"/>
+      <c r="AE4" s="305"/>
+      <c r="AF4" s="305"/>
+      <c r="AG4" s="306"/>
+      <c r="AH4" s="306"/>
+      <c r="AI4" s="305"/>
+      <c r="AJ4" s="306"/>
+      <c r="AK4" s="306"/>
+      <c r="AL4" s="305"/>
+      <c r="AM4" s="306"/>
+      <c r="AN4" s="307"/>
     </row>
     <row r="5" spans="1:43" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="309" t="s">
+      <c r="A5" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="304"/>
-      <c r="C5" s="305"/>
-      <c r="D5" s="304"/>
-      <c r="E5" s="304"/>
-      <c r="F5" s="304"/>
-      <c r="G5" s="304"/>
-      <c r="H5" s="304"/>
-      <c r="I5" s="304"/>
-      <c r="J5" s="304"/>
-      <c r="K5" s="304"/>
-      <c r="L5" s="304"/>
-      <c r="M5" s="304"/>
-      <c r="N5" s="304"/>
-      <c r="O5" s="304"/>
-      <c r="P5" s="304"/>
-      <c r="Q5" s="304"/>
-      <c r="R5" s="304"/>
-      <c r="S5" s="304"/>
-      <c r="T5" s="304"/>
-      <c r="U5" s="304"/>
-      <c r="V5" s="304"/>
-      <c r="W5" s="304"/>
-      <c r="X5" s="304"/>
-      <c r="Y5" s="304"/>
-      <c r="Z5" s="304"/>
-      <c r="AA5" s="304"/>
-      <c r="AB5" s="304"/>
-      <c r="AC5" s="305"/>
-      <c r="AD5" s="305"/>
-      <c r="AE5" s="304"/>
-      <c r="AF5" s="304"/>
-      <c r="AG5" s="305"/>
-      <c r="AH5" s="305"/>
-      <c r="AI5" s="304"/>
-      <c r="AJ5" s="305"/>
-      <c r="AK5" s="305"/>
-      <c r="AL5" s="304"/>
-      <c r="AM5" s="305"/>
-      <c r="AN5" s="306"/>
+      <c r="B5" s="305"/>
+      <c r="C5" s="306"/>
+      <c r="D5" s="305"/>
+      <c r="E5" s="305"/>
+      <c r="F5" s="305"/>
+      <c r="G5" s="305"/>
+      <c r="H5" s="305"/>
+      <c r="I5" s="305"/>
+      <c r="J5" s="305"/>
+      <c r="K5" s="305"/>
+      <c r="L5" s="305"/>
+      <c r="M5" s="305"/>
+      <c r="N5" s="305"/>
+      <c r="O5" s="305"/>
+      <c r="P5" s="305"/>
+      <c r="Q5" s="305"/>
+      <c r="R5" s="305"/>
+      <c r="S5" s="305"/>
+      <c r="T5" s="305"/>
+      <c r="U5" s="305"/>
+      <c r="V5" s="305"/>
+      <c r="W5" s="305"/>
+      <c r="X5" s="305"/>
+      <c r="Y5" s="305"/>
+      <c r="Z5" s="305"/>
+      <c r="AA5" s="305"/>
+      <c r="AB5" s="305"/>
+      <c r="AC5" s="306"/>
+      <c r="AD5" s="306"/>
+      <c r="AE5" s="305"/>
+      <c r="AF5" s="305"/>
+      <c r="AG5" s="306"/>
+      <c r="AH5" s="306"/>
+      <c r="AI5" s="305"/>
+      <c r="AJ5" s="306"/>
+      <c r="AK5" s="306"/>
+      <c r="AL5" s="305"/>
+      <c r="AM5" s="306"/>
+      <c r="AN5" s="307"/>
     </row>
     <row r="6" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -10173,212 +10177,212 @@
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
       <c r="AD6" s="11"/>
-      <c r="AE6" s="333" t="s">
+      <c r="AE6" s="334" t="s">
         <v>151</v>
       </c>
-      <c r="AF6" s="334"/>
-      <c r="AG6" s="334"/>
-      <c r="AH6" s="334"/>
-      <c r="AI6" s="334"/>
-      <c r="AJ6" s="334"/>
-      <c r="AK6" s="334"/>
-      <c r="AL6" s="334"/>
-      <c r="AM6" s="334"/>
-      <c r="AN6" s="334"/>
+      <c r="AF6" s="335"/>
+      <c r="AG6" s="335"/>
+      <c r="AH6" s="335"/>
+      <c r="AI6" s="335"/>
+      <c r="AJ6" s="335"/>
+      <c r="AK6" s="335"/>
+      <c r="AL6" s="335"/>
+      <c r="AM6" s="335"/>
+      <c r="AN6" s="335"/>
     </row>
     <row r="7" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="296" t="s">
+      <c r="A7" s="303" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="296" t="s">
+      <c r="B7" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="322" t="s">
+      <c r="C7" s="324" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="296" t="s">
+      <c r="D7" s="303" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="296" t="s">
+      <c r="E7" s="303" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="296" t="s">
+      <c r="F7" s="303" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="296" t="s">
+      <c r="G7" s="303" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="296" t="s">
+      <c r="H7" s="303" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="296" t="s">
+      <c r="I7" s="303" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="296" t="s">
+      <c r="J7" s="303" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="296" t="s">
+      <c r="K7" s="303" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="329" t="s">
+      <c r="L7" s="333" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="296" t="s">
+      <c r="M7" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="296" t="s">
+      <c r="N7" s="303" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="311" t="s">
+      <c r="O7" s="313" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="312"/>
-      <c r="Q7" s="312"/>
-      <c r="R7" s="312"/>
-      <c r="S7" s="312"/>
-      <c r="T7" s="312"/>
-      <c r="U7" s="312"/>
-      <c r="V7" s="313"/>
-      <c r="W7" s="296" t="s">
+      <c r="P7" s="314"/>
+      <c r="Q7" s="314"/>
+      <c r="R7" s="314"/>
+      <c r="S7" s="314"/>
+      <c r="T7" s="314"/>
+      <c r="U7" s="314"/>
+      <c r="V7" s="315"/>
+      <c r="W7" s="303" t="s">
         <v>139</v>
       </c>
-      <c r="X7" s="310" t="s">
+      <c r="X7" s="311" t="s">
         <v>13</v>
       </c>
-      <c r="Y7" s="310" t="s">
+      <c r="Y7" s="311" t="s">
         <v>184</v>
       </c>
-      <c r="Z7" s="323" t="s">
+      <c r="Z7" s="325" t="s">
         <v>175</v>
       </c>
-      <c r="AA7" s="296" t="s">
+      <c r="AA7" s="303" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="296" t="s">
+      <c r="AB7" s="303" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="311" t="s">
+      <c r="AC7" s="313" t="s">
         <v>155</v>
       </c>
-      <c r="AD7" s="313"/>
-      <c r="AE7" s="301" t="s">
+      <c r="AD7" s="315"/>
+      <c r="AE7" s="297" t="s">
         <v>17</v>
       </c>
-      <c r="AF7" s="298" t="s">
+      <c r="AF7" s="326" t="s">
         <v>107</v>
       </c>
-      <c r="AG7" s="298" t="s">
+      <c r="AG7" s="326" t="s">
         <v>108</v>
       </c>
-      <c r="AH7" s="298" t="s">
+      <c r="AH7" s="326" t="s">
         <v>106</v>
       </c>
-      <c r="AI7" s="300" t="s">
+      <c r="AI7" s="328" t="s">
         <v>147</v>
       </c>
-      <c r="AJ7" s="301" t="s">
+      <c r="AJ7" s="297" t="s">
         <v>136</v>
       </c>
-      <c r="AK7" s="301" t="s">
+      <c r="AK7" s="297" t="s">
         <v>137</v>
       </c>
-      <c r="AL7" s="296" t="s">
+      <c r="AL7" s="303" t="s">
         <v>135</v>
       </c>
-      <c r="AM7" s="296" t="s">
+      <c r="AM7" s="303" t="s">
         <v>146</v>
       </c>
-      <c r="AN7" s="296" t="s">
+      <c r="AN7" s="303" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="302"/>
-      <c r="B8" s="302"/>
-      <c r="C8" s="322"/>
-      <c r="D8" s="302"/>
-      <c r="E8" s="302"/>
-      <c r="F8" s="302"/>
-      <c r="G8" s="302"/>
-      <c r="H8" s="302"/>
-      <c r="I8" s="302"/>
-      <c r="J8" s="302"/>
-      <c r="K8" s="302"/>
-      <c r="L8" s="302"/>
-      <c r="M8" s="302"/>
-      <c r="N8" s="302"/>
-      <c r="O8" s="314"/>
-      <c r="P8" s="315"/>
-      <c r="Q8" s="315"/>
-      <c r="R8" s="315"/>
-      <c r="S8" s="315"/>
-      <c r="T8" s="315"/>
-      <c r="U8" s="315"/>
-      <c r="V8" s="316"/>
-      <c r="W8" s="302"/>
-      <c r="X8" s="302"/>
-      <c r="Y8" s="302"/>
-      <c r="Z8" s="302"/>
-      <c r="AA8" s="302"/>
-      <c r="AB8" s="302"/>
-      <c r="AC8" s="317"/>
-      <c r="AD8" s="319"/>
-      <c r="AE8" s="302"/>
-      <c r="AF8" s="299"/>
-      <c r="AG8" s="299"/>
-      <c r="AH8" s="300"/>
-      <c r="AI8" s="299"/>
-      <c r="AJ8" s="302"/>
-      <c r="AK8" s="301"/>
-      <c r="AL8" s="302"/>
-      <c r="AM8" s="296"/>
-      <c r="AN8" s="297"/>
+      <c r="A8" s="298"/>
+      <c r="B8" s="298"/>
+      <c r="C8" s="324"/>
+      <c r="D8" s="298"/>
+      <c r="E8" s="298"/>
+      <c r="F8" s="298"/>
+      <c r="G8" s="298"/>
+      <c r="H8" s="298"/>
+      <c r="I8" s="298"/>
+      <c r="J8" s="298"/>
+      <c r="K8" s="298"/>
+      <c r="L8" s="298"/>
+      <c r="M8" s="298"/>
+      <c r="N8" s="298"/>
+      <c r="O8" s="316"/>
+      <c r="P8" s="317"/>
+      <c r="Q8" s="317"/>
+      <c r="R8" s="317"/>
+      <c r="S8" s="317"/>
+      <c r="T8" s="317"/>
+      <c r="U8" s="317"/>
+      <c r="V8" s="318"/>
+      <c r="W8" s="298"/>
+      <c r="X8" s="298"/>
+      <c r="Y8" s="298"/>
+      <c r="Z8" s="298"/>
+      <c r="AA8" s="298"/>
+      <c r="AB8" s="298"/>
+      <c r="AC8" s="319"/>
+      <c r="AD8" s="321"/>
+      <c r="AE8" s="298"/>
+      <c r="AF8" s="327"/>
+      <c r="AG8" s="327"/>
+      <c r="AH8" s="328"/>
+      <c r="AI8" s="327"/>
+      <c r="AJ8" s="298"/>
+      <c r="AK8" s="297"/>
+      <c r="AL8" s="298"/>
+      <c r="AM8" s="303"/>
+      <c r="AN8" s="312"/>
     </row>
     <row r="9" spans="1:43" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="302"/>
-      <c r="B9" s="302"/>
-      <c r="C9" s="322"/>
-      <c r="D9" s="302"/>
-      <c r="E9" s="302"/>
-      <c r="F9" s="302"/>
-      <c r="G9" s="302"/>
-      <c r="H9" s="302"/>
-      <c r="I9" s="302"/>
-      <c r="J9" s="302"/>
-      <c r="K9" s="302"/>
-      <c r="L9" s="302"/>
-      <c r="M9" s="302"/>
-      <c r="N9" s="302"/>
-      <c r="O9" s="317"/>
-      <c r="P9" s="318"/>
-      <c r="Q9" s="318"/>
-      <c r="R9" s="318"/>
-      <c r="S9" s="318"/>
-      <c r="T9" s="318"/>
-      <c r="U9" s="318"/>
-      <c r="V9" s="319"/>
-      <c r="W9" s="302"/>
-      <c r="X9" s="302"/>
-      <c r="Y9" s="302"/>
-      <c r="Z9" s="302"/>
-      <c r="AA9" s="302"/>
-      <c r="AB9" s="302"/>
+      <c r="A9" s="298"/>
+      <c r="B9" s="298"/>
+      <c r="C9" s="324"/>
+      <c r="D9" s="298"/>
+      <c r="E9" s="298"/>
+      <c r="F9" s="298"/>
+      <c r="G9" s="298"/>
+      <c r="H9" s="298"/>
+      <c r="I9" s="298"/>
+      <c r="J9" s="298"/>
+      <c r="K9" s="298"/>
+      <c r="L9" s="298"/>
+      <c r="M9" s="298"/>
+      <c r="N9" s="298"/>
+      <c r="O9" s="319"/>
+      <c r="P9" s="320"/>
+      <c r="Q9" s="320"/>
+      <c r="R9" s="320"/>
+      <c r="S9" s="320"/>
+      <c r="T9" s="320"/>
+      <c r="U9" s="320"/>
+      <c r="V9" s="321"/>
+      <c r="W9" s="298"/>
+      <c r="X9" s="298"/>
+      <c r="Y9" s="298"/>
+      <c r="Z9" s="298"/>
+      <c r="AA9" s="298"/>
+      <c r="AB9" s="298"/>
       <c r="AC9" s="201" t="s">
         <v>153</v>
       </c>
       <c r="AD9" s="178" t="s">
         <v>154</v>
       </c>
-      <c r="AE9" s="302"/>
-      <c r="AF9" s="299"/>
-      <c r="AG9" s="299"/>
-      <c r="AH9" s="300"/>
-      <c r="AI9" s="299"/>
-      <c r="AJ9" s="302"/>
-      <c r="AK9" s="301"/>
-      <c r="AL9" s="302"/>
-      <c r="AM9" s="296"/>
-      <c r="AN9" s="297"/>
+      <c r="AE9" s="298"/>
+      <c r="AF9" s="327"/>
+      <c r="AG9" s="327"/>
+      <c r="AH9" s="328"/>
+      <c r="AI9" s="327"/>
+      <c r="AJ9" s="298"/>
+      <c r="AK9" s="297"/>
+      <c r="AL9" s="298"/>
+      <c r="AM9" s="303"/>
+      <c r="AN9" s="312"/>
       <c r="AO9">
         <f>Z11/W11</f>
         <v>0.50632226325372287</v>
@@ -15648,6 +15652,27 @@
   </sheetData>
   <autoFilter ref="A10:AQ54" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="37">
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AD8"/>
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A2:AB2"/>
@@ -15664,27 +15689,6 @@
     <mergeCell ref="H7:H9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:J9"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AD8"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
   </mergeCells>
   <pageMargins left="0.17" right="0.15748031496062992" top="0.41" bottom="0.23622047244094491" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
@@ -15733,36 +15737,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="331" t="s">
+      <c r="A1" s="329" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="304"/>
-      <c r="C1" s="305"/>
-      <c r="D1" s="304"/>
-      <c r="E1" s="304"/>
-      <c r="F1" s="304"/>
-      <c r="G1" s="304"/>
-      <c r="H1" s="304"/>
-      <c r="I1" s="304"/>
-      <c r="J1" s="304"/>
-      <c r="K1" s="304"/>
-      <c r="L1" s="304"/>
-      <c r="M1" s="304"/>
-      <c r="N1" s="304"/>
-      <c r="O1" s="304"/>
-      <c r="P1" s="304"/>
-      <c r="Q1" s="304"/>
-      <c r="R1" s="304"/>
-      <c r="S1" s="304"/>
-      <c r="T1" s="304"/>
-      <c r="U1" s="304"/>
-      <c r="V1" s="304"/>
-      <c r="W1" s="304"/>
-      <c r="X1" s="304"/>
-      <c r="Y1" s="304"/>
-      <c r="Z1" s="304"/>
-      <c r="AA1" s="304"/>
-      <c r="AB1" s="306"/>
+      <c r="B1" s="305"/>
+      <c r="C1" s="306"/>
+      <c r="D1" s="305"/>
+      <c r="E1" s="305"/>
+      <c r="F1" s="305"/>
+      <c r="G1" s="305"/>
+      <c r="H1" s="305"/>
+      <c r="I1" s="305"/>
+      <c r="J1" s="305"/>
+      <c r="K1" s="305"/>
+      <c r="L1" s="305"/>
+      <c r="M1" s="305"/>
+      <c r="N1" s="305"/>
+      <c r="O1" s="305"/>
+      <c r="P1" s="305"/>
+      <c r="Q1" s="305"/>
+      <c r="R1" s="305"/>
+      <c r="S1" s="305"/>
+      <c r="T1" s="305"/>
+      <c r="U1" s="305"/>
+      <c r="V1" s="305"/>
+      <c r="W1" s="305"/>
+      <c r="X1" s="305"/>
+      <c r="Y1" s="305"/>
+      <c r="Z1" s="305"/>
+      <c r="AA1" s="305"/>
+      <c r="AB1" s="307"/>
       <c r="AC1" s="17"/>
       <c r="AD1" s="17"/>
       <c r="AE1" s="1"/>
@@ -15779,36 +15783,36 @@
       <c r="AN1" s="160"/>
     </row>
     <row r="2" spans="1:43" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="307" t="s">
+      <c r="A2" s="308" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="304"/>
-      <c r="C2" s="305"/>
-      <c r="D2" s="304"/>
-      <c r="E2" s="304"/>
-      <c r="F2" s="304"/>
-      <c r="G2" s="304"/>
-      <c r="H2" s="304"/>
-      <c r="I2" s="304"/>
-      <c r="J2" s="304"/>
-      <c r="K2" s="304"/>
-      <c r="L2" s="304"/>
-      <c r="M2" s="304"/>
-      <c r="N2" s="304"/>
-      <c r="O2" s="304"/>
-      <c r="P2" s="304"/>
-      <c r="Q2" s="304"/>
-      <c r="R2" s="304"/>
-      <c r="S2" s="304"/>
-      <c r="T2" s="304"/>
-      <c r="U2" s="304"/>
-      <c r="V2" s="304"/>
-      <c r="W2" s="304"/>
-      <c r="X2" s="304"/>
-      <c r="Y2" s="304"/>
-      <c r="Z2" s="304"/>
-      <c r="AA2" s="304"/>
-      <c r="AB2" s="306"/>
+      <c r="B2" s="305"/>
+      <c r="C2" s="306"/>
+      <c r="D2" s="305"/>
+      <c r="E2" s="305"/>
+      <c r="F2" s="305"/>
+      <c r="G2" s="305"/>
+      <c r="H2" s="305"/>
+      <c r="I2" s="305"/>
+      <c r="J2" s="305"/>
+      <c r="K2" s="305"/>
+      <c r="L2" s="305"/>
+      <c r="M2" s="305"/>
+      <c r="N2" s="305"/>
+      <c r="O2" s="305"/>
+      <c r="P2" s="305"/>
+      <c r="Q2" s="305"/>
+      <c r="R2" s="305"/>
+      <c r="S2" s="305"/>
+      <c r="T2" s="305"/>
+      <c r="U2" s="305"/>
+      <c r="V2" s="305"/>
+      <c r="W2" s="305"/>
+      <c r="X2" s="305"/>
+      <c r="Y2" s="305"/>
+      <c r="Z2" s="305"/>
+      <c r="AA2" s="305"/>
+      <c r="AB2" s="307"/>
       <c r="AC2" s="17"/>
       <c r="AD2" s="17"/>
       <c r="AE2" s="1"/>
@@ -15865,92 +15869,92 @@
       <c r="AN3" s="160"/>
     </row>
     <row r="4" spans="1:43" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="308" t="s">
+      <c r="A4" s="309" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="304"/>
-      <c r="C4" s="305"/>
-      <c r="D4" s="304"/>
-      <c r="E4" s="304"/>
-      <c r="F4" s="304"/>
-      <c r="G4" s="304"/>
-      <c r="H4" s="304"/>
-      <c r="I4" s="304"/>
-      <c r="J4" s="304"/>
-      <c r="K4" s="304"/>
-      <c r="L4" s="304"/>
-      <c r="M4" s="304"/>
-      <c r="N4" s="304"/>
-      <c r="O4" s="304"/>
-      <c r="P4" s="304"/>
-      <c r="Q4" s="304"/>
-      <c r="R4" s="304"/>
-      <c r="S4" s="304"/>
-      <c r="T4" s="304"/>
-      <c r="U4" s="304"/>
-      <c r="V4" s="304"/>
-      <c r="W4" s="304"/>
-      <c r="X4" s="304"/>
-      <c r="Y4" s="304"/>
-      <c r="Z4" s="304"/>
-      <c r="AA4" s="304"/>
-      <c r="AB4" s="304"/>
-      <c r="AC4" s="305"/>
-      <c r="AD4" s="305"/>
-      <c r="AE4" s="304"/>
-      <c r="AF4" s="304"/>
-      <c r="AG4" s="305"/>
-      <c r="AH4" s="305"/>
-      <c r="AI4" s="304"/>
-      <c r="AJ4" s="305"/>
-      <c r="AK4" s="305"/>
-      <c r="AL4" s="304"/>
-      <c r="AM4" s="305"/>
-      <c r="AN4" s="306"/>
+      <c r="B4" s="305"/>
+      <c r="C4" s="306"/>
+      <c r="D4" s="305"/>
+      <c r="E4" s="305"/>
+      <c r="F4" s="305"/>
+      <c r="G4" s="305"/>
+      <c r="H4" s="305"/>
+      <c r="I4" s="305"/>
+      <c r="J4" s="305"/>
+      <c r="K4" s="305"/>
+      <c r="L4" s="305"/>
+      <c r="M4" s="305"/>
+      <c r="N4" s="305"/>
+      <c r="O4" s="305"/>
+      <c r="P4" s="305"/>
+      <c r="Q4" s="305"/>
+      <c r="R4" s="305"/>
+      <c r="S4" s="305"/>
+      <c r="T4" s="305"/>
+      <c r="U4" s="305"/>
+      <c r="V4" s="305"/>
+      <c r="W4" s="305"/>
+      <c r="X4" s="305"/>
+      <c r="Y4" s="305"/>
+      <c r="Z4" s="305"/>
+      <c r="AA4" s="305"/>
+      <c r="AB4" s="305"/>
+      <c r="AC4" s="306"/>
+      <c r="AD4" s="306"/>
+      <c r="AE4" s="305"/>
+      <c r="AF4" s="305"/>
+      <c r="AG4" s="306"/>
+      <c r="AH4" s="306"/>
+      <c r="AI4" s="305"/>
+      <c r="AJ4" s="306"/>
+      <c r="AK4" s="306"/>
+      <c r="AL4" s="305"/>
+      <c r="AM4" s="306"/>
+      <c r="AN4" s="307"/>
     </row>
     <row r="5" spans="1:43" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="309" t="s">
+      <c r="A5" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="304"/>
-      <c r="C5" s="305"/>
-      <c r="D5" s="304"/>
-      <c r="E5" s="304"/>
-      <c r="F5" s="304"/>
-      <c r="G5" s="304"/>
-      <c r="H5" s="304"/>
-      <c r="I5" s="304"/>
-      <c r="J5" s="304"/>
-      <c r="K5" s="304"/>
-      <c r="L5" s="304"/>
-      <c r="M5" s="304"/>
-      <c r="N5" s="304"/>
-      <c r="O5" s="304"/>
-      <c r="P5" s="304"/>
-      <c r="Q5" s="304"/>
-      <c r="R5" s="304"/>
-      <c r="S5" s="304"/>
-      <c r="T5" s="304"/>
-      <c r="U5" s="304"/>
-      <c r="V5" s="304"/>
-      <c r="W5" s="304"/>
-      <c r="X5" s="304"/>
-      <c r="Y5" s="304"/>
-      <c r="Z5" s="304"/>
-      <c r="AA5" s="304"/>
-      <c r="AB5" s="304"/>
-      <c r="AC5" s="305"/>
-      <c r="AD5" s="305"/>
-      <c r="AE5" s="304"/>
-      <c r="AF5" s="304"/>
-      <c r="AG5" s="305"/>
-      <c r="AH5" s="305"/>
-      <c r="AI5" s="304"/>
-      <c r="AJ5" s="305"/>
-      <c r="AK5" s="305"/>
-      <c r="AL5" s="304"/>
-      <c r="AM5" s="305"/>
-      <c r="AN5" s="306"/>
+      <c r="B5" s="305"/>
+      <c r="C5" s="306"/>
+      <c r="D5" s="305"/>
+      <c r="E5" s="305"/>
+      <c r="F5" s="305"/>
+      <c r="G5" s="305"/>
+      <c r="H5" s="305"/>
+      <c r="I5" s="305"/>
+      <c r="J5" s="305"/>
+      <c r="K5" s="305"/>
+      <c r="L5" s="305"/>
+      <c r="M5" s="305"/>
+      <c r="N5" s="305"/>
+      <c r="O5" s="305"/>
+      <c r="P5" s="305"/>
+      <c r="Q5" s="305"/>
+      <c r="R5" s="305"/>
+      <c r="S5" s="305"/>
+      <c r="T5" s="305"/>
+      <c r="U5" s="305"/>
+      <c r="V5" s="305"/>
+      <c r="W5" s="305"/>
+      <c r="X5" s="305"/>
+      <c r="Y5" s="305"/>
+      <c r="Z5" s="305"/>
+      <c r="AA5" s="305"/>
+      <c r="AB5" s="305"/>
+      <c r="AC5" s="306"/>
+      <c r="AD5" s="306"/>
+      <c r="AE5" s="305"/>
+      <c r="AF5" s="305"/>
+      <c r="AG5" s="306"/>
+      <c r="AH5" s="306"/>
+      <c r="AI5" s="305"/>
+      <c r="AJ5" s="306"/>
+      <c r="AK5" s="306"/>
+      <c r="AL5" s="305"/>
+      <c r="AM5" s="306"/>
+      <c r="AN5" s="307"/>
     </row>
     <row r="6" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -15985,212 +15989,212 @@
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
       <c r="AD6" s="11"/>
-      <c r="AE6" s="333" t="s">
+      <c r="AE6" s="334" t="s">
         <v>151</v>
       </c>
-      <c r="AF6" s="334"/>
-      <c r="AG6" s="334"/>
-      <c r="AH6" s="334"/>
-      <c r="AI6" s="334"/>
-      <c r="AJ6" s="334"/>
-      <c r="AK6" s="334"/>
-      <c r="AL6" s="334"/>
-      <c r="AM6" s="334"/>
-      <c r="AN6" s="334"/>
+      <c r="AF6" s="335"/>
+      <c r="AG6" s="335"/>
+      <c r="AH6" s="335"/>
+      <c r="AI6" s="335"/>
+      <c r="AJ6" s="335"/>
+      <c r="AK6" s="335"/>
+      <c r="AL6" s="335"/>
+      <c r="AM6" s="335"/>
+      <c r="AN6" s="335"/>
     </row>
     <row r="7" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="296" t="s">
+      <c r="A7" s="303" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="335" t="s">
+      <c r="B7" s="336" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="322" t="s">
+      <c r="C7" s="324" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="296" t="s">
+      <c r="D7" s="303" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="296" t="s">
+      <c r="E7" s="303" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="296" t="s">
+      <c r="F7" s="303" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="296" t="s">
+      <c r="G7" s="303" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="296" t="s">
+      <c r="H7" s="303" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="296" t="s">
+      <c r="I7" s="303" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="296" t="s">
+      <c r="J7" s="303" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="296" t="s">
+      <c r="K7" s="303" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="329" t="s">
+      <c r="L7" s="333" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="296" t="s">
+      <c r="M7" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="296" t="s">
+      <c r="N7" s="303" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="311" t="s">
+      <c r="O7" s="313" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="312"/>
-      <c r="Q7" s="312"/>
-      <c r="R7" s="312"/>
-      <c r="S7" s="312"/>
-      <c r="T7" s="312"/>
-      <c r="U7" s="312"/>
-      <c r="V7" s="313"/>
-      <c r="W7" s="296" t="s">
+      <c r="P7" s="314"/>
+      <c r="Q7" s="314"/>
+      <c r="R7" s="314"/>
+      <c r="S7" s="314"/>
+      <c r="T7" s="314"/>
+      <c r="U7" s="314"/>
+      <c r="V7" s="315"/>
+      <c r="W7" s="303" t="s">
         <v>139</v>
       </c>
-      <c r="X7" s="310" t="s">
+      <c r="X7" s="311" t="s">
         <v>13</v>
       </c>
-      <c r="Y7" s="310" t="s">
+      <c r="Y7" s="311" t="s">
         <v>184</v>
       </c>
-      <c r="Z7" s="323" t="s">
+      <c r="Z7" s="325" t="s">
         <v>175</v>
       </c>
-      <c r="AA7" s="296" t="s">
+      <c r="AA7" s="303" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="296" t="s">
+      <c r="AB7" s="303" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="311" t="s">
+      <c r="AC7" s="313" t="s">
         <v>155</v>
       </c>
-      <c r="AD7" s="313"/>
-      <c r="AE7" s="301" t="s">
+      <c r="AD7" s="315"/>
+      <c r="AE7" s="297" t="s">
         <v>17</v>
       </c>
-      <c r="AF7" s="298" t="s">
+      <c r="AF7" s="326" t="s">
         <v>107</v>
       </c>
-      <c r="AG7" s="298" t="s">
+      <c r="AG7" s="326" t="s">
         <v>108</v>
       </c>
-      <c r="AH7" s="298" t="s">
+      <c r="AH7" s="326" t="s">
         <v>106</v>
       </c>
-      <c r="AI7" s="300" t="s">
+      <c r="AI7" s="328" t="s">
         <v>147</v>
       </c>
-      <c r="AJ7" s="301" t="s">
+      <c r="AJ7" s="297" t="s">
         <v>136</v>
       </c>
-      <c r="AK7" s="301" t="s">
+      <c r="AK7" s="297" t="s">
         <v>137</v>
       </c>
-      <c r="AL7" s="296" t="s">
+      <c r="AL7" s="303" t="s">
         <v>135</v>
       </c>
-      <c r="AM7" s="296" t="s">
+      <c r="AM7" s="303" t="s">
         <v>146</v>
       </c>
-      <c r="AN7" s="296" t="s">
+      <c r="AN7" s="303" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="302"/>
-      <c r="B8" s="336"/>
-      <c r="C8" s="322"/>
-      <c r="D8" s="302"/>
-      <c r="E8" s="302"/>
-      <c r="F8" s="302"/>
-      <c r="G8" s="302"/>
-      <c r="H8" s="302"/>
-      <c r="I8" s="302"/>
-      <c r="J8" s="302"/>
-      <c r="K8" s="302"/>
-      <c r="L8" s="302"/>
-      <c r="M8" s="302"/>
-      <c r="N8" s="302"/>
-      <c r="O8" s="314"/>
-      <c r="P8" s="315"/>
-      <c r="Q8" s="315"/>
-      <c r="R8" s="315"/>
-      <c r="S8" s="315"/>
-      <c r="T8" s="315"/>
-      <c r="U8" s="315"/>
-      <c r="V8" s="316"/>
-      <c r="W8" s="302"/>
-      <c r="X8" s="302"/>
-      <c r="Y8" s="302"/>
-      <c r="Z8" s="302"/>
-      <c r="AA8" s="302"/>
-      <c r="AB8" s="302"/>
-      <c r="AC8" s="317"/>
-      <c r="AD8" s="319"/>
-      <c r="AE8" s="302"/>
-      <c r="AF8" s="299"/>
-      <c r="AG8" s="299"/>
-      <c r="AH8" s="300"/>
-      <c r="AI8" s="299"/>
-      <c r="AJ8" s="302"/>
-      <c r="AK8" s="301"/>
-      <c r="AL8" s="302"/>
-      <c r="AM8" s="296"/>
-      <c r="AN8" s="297"/>
+      <c r="A8" s="298"/>
+      <c r="B8" s="337"/>
+      <c r="C8" s="324"/>
+      <c r="D8" s="298"/>
+      <c r="E8" s="298"/>
+      <c r="F8" s="298"/>
+      <c r="G8" s="298"/>
+      <c r="H8" s="298"/>
+      <c r="I8" s="298"/>
+      <c r="J8" s="298"/>
+      <c r="K8" s="298"/>
+      <c r="L8" s="298"/>
+      <c r="M8" s="298"/>
+      <c r="N8" s="298"/>
+      <c r="O8" s="316"/>
+      <c r="P8" s="317"/>
+      <c r="Q8" s="317"/>
+      <c r="R8" s="317"/>
+      <c r="S8" s="317"/>
+      <c r="T8" s="317"/>
+      <c r="U8" s="317"/>
+      <c r="V8" s="318"/>
+      <c r="W8" s="298"/>
+      <c r="X8" s="298"/>
+      <c r="Y8" s="298"/>
+      <c r="Z8" s="298"/>
+      <c r="AA8" s="298"/>
+      <c r="AB8" s="298"/>
+      <c r="AC8" s="319"/>
+      <c r="AD8" s="321"/>
+      <c r="AE8" s="298"/>
+      <c r="AF8" s="327"/>
+      <c r="AG8" s="327"/>
+      <c r="AH8" s="328"/>
+      <c r="AI8" s="327"/>
+      <c r="AJ8" s="298"/>
+      <c r="AK8" s="297"/>
+      <c r="AL8" s="298"/>
+      <c r="AM8" s="303"/>
+      <c r="AN8" s="312"/>
     </row>
     <row r="9" spans="1:43" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="302"/>
-      <c r="B9" s="336"/>
-      <c r="C9" s="322"/>
-      <c r="D9" s="302"/>
-      <c r="E9" s="302"/>
-      <c r="F9" s="302"/>
-      <c r="G9" s="302"/>
-      <c r="H9" s="302"/>
-      <c r="I9" s="302"/>
-      <c r="J9" s="302"/>
-      <c r="K9" s="302"/>
-      <c r="L9" s="302"/>
-      <c r="M9" s="302"/>
-      <c r="N9" s="302"/>
-      <c r="O9" s="317"/>
-      <c r="P9" s="318"/>
-      <c r="Q9" s="318"/>
-      <c r="R9" s="318"/>
-      <c r="S9" s="318"/>
-      <c r="T9" s="318"/>
-      <c r="U9" s="318"/>
-      <c r="V9" s="319"/>
-      <c r="W9" s="302"/>
-      <c r="X9" s="302"/>
-      <c r="Y9" s="302"/>
-      <c r="Z9" s="302"/>
-      <c r="AA9" s="302"/>
-      <c r="AB9" s="302"/>
+      <c r="A9" s="298"/>
+      <c r="B9" s="337"/>
+      <c r="C9" s="324"/>
+      <c r="D9" s="298"/>
+      <c r="E9" s="298"/>
+      <c r="F9" s="298"/>
+      <c r="G9" s="298"/>
+      <c r="H9" s="298"/>
+      <c r="I9" s="298"/>
+      <c r="J9" s="298"/>
+      <c r="K9" s="298"/>
+      <c r="L9" s="298"/>
+      <c r="M9" s="298"/>
+      <c r="N9" s="298"/>
+      <c r="O9" s="319"/>
+      <c r="P9" s="320"/>
+      <c r="Q9" s="320"/>
+      <c r="R9" s="320"/>
+      <c r="S9" s="320"/>
+      <c r="T9" s="320"/>
+      <c r="U9" s="320"/>
+      <c r="V9" s="321"/>
+      <c r="W9" s="298"/>
+      <c r="X9" s="298"/>
+      <c r="Y9" s="298"/>
+      <c r="Z9" s="298"/>
+      <c r="AA9" s="298"/>
+      <c r="AB9" s="298"/>
       <c r="AC9" s="201" t="s">
         <v>153</v>
       </c>
       <c r="AD9" s="178" t="s">
         <v>154</v>
       </c>
-      <c r="AE9" s="302"/>
-      <c r="AF9" s="299"/>
-      <c r="AG9" s="299"/>
-      <c r="AH9" s="300"/>
-      <c r="AI9" s="299"/>
-      <c r="AJ9" s="302"/>
-      <c r="AK9" s="301"/>
-      <c r="AL9" s="302"/>
-      <c r="AM9" s="296"/>
-      <c r="AN9" s="297"/>
+      <c r="AE9" s="298"/>
+      <c r="AF9" s="327"/>
+      <c r="AG9" s="327"/>
+      <c r="AH9" s="328"/>
+      <c r="AI9" s="327"/>
+      <c r="AJ9" s="298"/>
+      <c r="AK9" s="297"/>
+      <c r="AL9" s="298"/>
+      <c r="AM9" s="303"/>
+      <c r="AN9" s="312"/>
       <c r="AO9">
         <f>Z11/W11</f>
         <v>0.50320398224028773</v>
@@ -22364,27 +22368,6 @@
   </sheetData>
   <autoFilter ref="A10:AQ73" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AD8"/>
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A2:AB2"/>
@@ -22401,6 +22384,27 @@
     <mergeCell ref="H7:H9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:J9"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AD8"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
   </mergeCells>
   <pageMargins left="0.17" right="0.15748031496062992" top="0.41" bottom="0.23622047244094491" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
@@ -22414,8 +22418,8 @@
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
     <col min="2" max="2" width="35.5703125" style="252" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" style="224" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="268" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" style="224" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" style="266" customWidth="1"/>
     <col min="5" max="5" width="13.140625" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" customWidth="1"/>
     <col min="7" max="7" width="10.5703125" customWidth="1"/>
@@ -22425,13 +22429,13 @@
     <col min="11" max="11" width="11.140625" customWidth="1"/>
     <col min="12" max="12" width="10.42578125" customWidth="1"/>
     <col min="13" max="13" width="10.5703125" customWidth="1"/>
-    <col min="14" max="14" width="10" style="214" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" style="214" customWidth="1"/>
     <col min="15" max="15" width="11.28515625" style="214" customWidth="1"/>
-    <col min="16" max="16" width="13.140625" style="214" customWidth="1"/>
+    <col min="16" max="16" width="10.7109375" style="214" customWidth="1"/>
     <col min="17" max="17" width="11.28515625" customWidth="1"/>
     <col min="18" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" style="102" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" style="102" customWidth="1"/>
+    <col min="19" max="19" width="10.28515625" style="102" customWidth="1"/>
+    <col min="20" max="20" width="10.85546875" style="102" customWidth="1"/>
     <col min="21" max="21" width="11.42578125" style="102" customWidth="1"/>
     <col min="22" max="23" width="17.28515625" style="102" customWidth="1"/>
     <col min="24" max="24" width="9.5703125" customWidth="1"/>
@@ -22441,38 +22445,38 @@
     <col min="29" max="29" width="12.140625" customWidth="1"/>
     <col min="30" max="30" width="17.5703125" customWidth="1"/>
     <col min="31" max="31" width="12.28515625" customWidth="1"/>
-    <col min="32" max="33" width="12.42578125" customWidth="1"/>
-    <col min="34" max="34" width="13.140625" customWidth="1"/>
+    <col min="32" max="33" width="11.85546875" customWidth="1"/>
+    <col min="34" max="34" width="11.28515625" customWidth="1"/>
     <col min="35" max="37" width="0" hidden="1" customWidth="1"/>
     <col min="40" max="40" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="303" t="s">
+      <c r="A1" s="304" t="s">
         <v>206</v>
       </c>
-      <c r="B1" s="304"/>
-      <c r="C1" s="305"/>
-      <c r="D1" s="304"/>
-      <c r="E1" s="304"/>
-      <c r="F1" s="304"/>
-      <c r="G1" s="304"/>
-      <c r="H1" s="304"/>
-      <c r="I1" s="304"/>
-      <c r="J1" s="304"/>
-      <c r="K1" s="304"/>
-      <c r="L1" s="304"/>
-      <c r="M1" s="304"/>
-      <c r="N1" s="304"/>
-      <c r="O1" s="304"/>
-      <c r="P1" s="304"/>
-      <c r="Q1" s="304"/>
-      <c r="R1" s="306"/>
-      <c r="S1" s="262"/>
-      <c r="T1" s="262"/>
-      <c r="U1" s="262"/>
-      <c r="V1" s="262"/>
-      <c r="W1" s="262"/>
+      <c r="B1" s="305"/>
+      <c r="C1" s="306"/>
+      <c r="D1" s="305"/>
+      <c r="E1" s="305"/>
+      <c r="F1" s="305"/>
+      <c r="G1" s="305"/>
+      <c r="H1" s="305"/>
+      <c r="I1" s="305"/>
+      <c r="J1" s="305"/>
+      <c r="K1" s="305"/>
+      <c r="L1" s="305"/>
+      <c r="M1" s="305"/>
+      <c r="N1" s="305"/>
+      <c r="O1" s="305"/>
+      <c r="P1" s="305"/>
+      <c r="Q1" s="305"/>
+      <c r="R1" s="307"/>
+      <c r="S1" s="261"/>
+      <c r="T1" s="261"/>
+      <c r="U1" s="261"/>
+      <c r="V1" s="261"/>
+      <c r="W1" s="261"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
@@ -22488,31 +22492,31 @@
       <c r="AH1" s="160"/>
     </row>
     <row r="2" spans="1:40" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="307" t="s">
+      <c r="A2" s="308" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="304"/>
-      <c r="C2" s="305"/>
-      <c r="D2" s="304"/>
-      <c r="E2" s="304"/>
-      <c r="F2" s="304"/>
-      <c r="G2" s="304"/>
-      <c r="H2" s="304"/>
-      <c r="I2" s="304"/>
-      <c r="J2" s="304"/>
-      <c r="K2" s="304"/>
-      <c r="L2" s="304"/>
-      <c r="M2" s="304"/>
-      <c r="N2" s="304"/>
-      <c r="O2" s="304"/>
-      <c r="P2" s="304"/>
-      <c r="Q2" s="304"/>
-      <c r="R2" s="306"/>
-      <c r="S2" s="262"/>
-      <c r="T2" s="262"/>
-      <c r="U2" s="262"/>
-      <c r="V2" s="262"/>
-      <c r="W2" s="262"/>
+      <c r="B2" s="305"/>
+      <c r="C2" s="306"/>
+      <c r="D2" s="305"/>
+      <c r="E2" s="305"/>
+      <c r="F2" s="305"/>
+      <c r="G2" s="305"/>
+      <c r="H2" s="305"/>
+      <c r="I2" s="305"/>
+      <c r="J2" s="305"/>
+      <c r="K2" s="305"/>
+      <c r="L2" s="305"/>
+      <c r="M2" s="305"/>
+      <c r="N2" s="305"/>
+      <c r="O2" s="305"/>
+      <c r="P2" s="305"/>
+      <c r="Q2" s="305"/>
+      <c r="R2" s="307"/>
+      <c r="S2" s="261"/>
+      <c r="T2" s="261"/>
+      <c r="U2" s="261"/>
+      <c r="V2" s="261"/>
+      <c r="W2" s="261"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
@@ -22562,80 +22566,80 @@
       <c r="AH3" s="160"/>
     </row>
     <row r="4" spans="1:40" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="308" t="s">
+      <c r="A4" s="309" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="304"/>
-      <c r="C4" s="305"/>
-      <c r="D4" s="304"/>
-      <c r="E4" s="304"/>
-      <c r="F4" s="304"/>
-      <c r="G4" s="304"/>
-      <c r="H4" s="304"/>
-      <c r="I4" s="304"/>
-      <c r="J4" s="304"/>
-      <c r="K4" s="304"/>
-      <c r="L4" s="304"/>
-      <c r="M4" s="304"/>
-      <c r="N4" s="304"/>
-      <c r="O4" s="304"/>
-      <c r="P4" s="304"/>
-      <c r="Q4" s="304"/>
-      <c r="R4" s="304"/>
-      <c r="S4" s="305"/>
-      <c r="T4" s="305"/>
-      <c r="U4" s="305"/>
-      <c r="V4" s="305"/>
-      <c r="W4" s="305"/>
-      <c r="X4" s="304"/>
-      <c r="Y4" s="304"/>
-      <c r="Z4" s="305"/>
-      <c r="AA4" s="305"/>
-      <c r="AB4" s="304"/>
-      <c r="AC4" s="305"/>
-      <c r="AD4" s="305"/>
-      <c r="AE4" s="304"/>
-      <c r="AF4" s="305"/>
-      <c r="AG4" s="305"/>
-      <c r="AH4" s="306"/>
+      <c r="B4" s="305"/>
+      <c r="C4" s="306"/>
+      <c r="D4" s="305"/>
+      <c r="E4" s="305"/>
+      <c r="F4" s="305"/>
+      <c r="G4" s="305"/>
+      <c r="H4" s="305"/>
+      <c r="I4" s="305"/>
+      <c r="J4" s="305"/>
+      <c r="K4" s="305"/>
+      <c r="L4" s="305"/>
+      <c r="M4" s="305"/>
+      <c r="N4" s="305"/>
+      <c r="O4" s="305"/>
+      <c r="P4" s="305"/>
+      <c r="Q4" s="305"/>
+      <c r="R4" s="305"/>
+      <c r="S4" s="306"/>
+      <c r="T4" s="306"/>
+      <c r="U4" s="306"/>
+      <c r="V4" s="306"/>
+      <c r="W4" s="306"/>
+      <c r="X4" s="305"/>
+      <c r="Y4" s="305"/>
+      <c r="Z4" s="306"/>
+      <c r="AA4" s="306"/>
+      <c r="AB4" s="305"/>
+      <c r="AC4" s="306"/>
+      <c r="AD4" s="306"/>
+      <c r="AE4" s="305"/>
+      <c r="AF4" s="306"/>
+      <c r="AG4" s="306"/>
+      <c r="AH4" s="307"/>
     </row>
-    <row r="5" spans="1:40" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="309" t="s">
-        <v>228</v>
-      </c>
-      <c r="B5" s="304"/>
-      <c r="C5" s="305"/>
-      <c r="D5" s="304"/>
-      <c r="E5" s="304"/>
-      <c r="F5" s="304"/>
-      <c r="G5" s="304"/>
-      <c r="H5" s="304"/>
-      <c r="I5" s="304"/>
-      <c r="J5" s="304"/>
-      <c r="K5" s="304"/>
-      <c r="L5" s="304"/>
-      <c r="M5" s="304"/>
-      <c r="N5" s="304"/>
-      <c r="O5" s="304"/>
-      <c r="P5" s="304"/>
-      <c r="Q5" s="304"/>
-      <c r="R5" s="304"/>
-      <c r="S5" s="305"/>
-      <c r="T5" s="305"/>
-      <c r="U5" s="305"/>
-      <c r="V5" s="305"/>
-      <c r="W5" s="305"/>
-      <c r="X5" s="304"/>
-      <c r="Y5" s="304"/>
-      <c r="Z5" s="305"/>
-      <c r="AA5" s="305"/>
-      <c r="AB5" s="304"/>
-      <c r="AC5" s="305"/>
-      <c r="AD5" s="305"/>
-      <c r="AE5" s="304"/>
-      <c r="AF5" s="305"/>
-      <c r="AG5" s="305"/>
-      <c r="AH5" s="306"/>
+    <row r="5" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="310" t="s">
+        <v>229</v>
+      </c>
+      <c r="B5" s="310"/>
+      <c r="C5" s="310"/>
+      <c r="D5" s="310"/>
+      <c r="E5" s="310"/>
+      <c r="F5" s="310"/>
+      <c r="G5" s="310"/>
+      <c r="H5" s="310"/>
+      <c r="I5" s="310"/>
+      <c r="J5" s="310"/>
+      <c r="K5" s="310"/>
+      <c r="L5" s="310"/>
+      <c r="M5" s="310"/>
+      <c r="N5" s="310"/>
+      <c r="O5" s="310"/>
+      <c r="P5" s="310"/>
+      <c r="Q5" s="310"/>
+      <c r="R5" s="310"/>
+      <c r="S5" s="310"/>
+      <c r="T5" s="310"/>
+      <c r="U5" s="310"/>
+      <c r="V5" s="310"/>
+      <c r="W5" s="310"/>
+      <c r="X5" s="310"/>
+      <c r="Y5" s="310"/>
+      <c r="Z5" s="310"/>
+      <c r="AA5" s="310"/>
+      <c r="AB5" s="310"/>
+      <c r="AC5" s="310"/>
+      <c r="AD5" s="310"/>
+      <c r="AE5" s="310"/>
+      <c r="AF5" s="310"/>
+      <c r="AG5" s="343"/>
+      <c r="AH5" s="310"/>
     </row>
     <row r="6" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -22660,192 +22664,195 @@
       <c r="R6" s="11"/>
       <c r="S6" s="11"/>
       <c r="T6" s="11"/>
-      <c r="U6" s="320" t="s">
+      <c r="U6" s="322" t="s">
         <v>151</v>
       </c>
-      <c r="V6" s="320"/>
-      <c r="W6" s="320"/>
-      <c r="X6" s="320"/>
-      <c r="Y6" s="320"/>
-      <c r="Z6" s="320"/>
-      <c r="AA6" s="320"/>
-      <c r="AB6" s="320"/>
-      <c r="AC6" s="320"/>
-      <c r="AD6" s="320"/>
-      <c r="AE6" s="320"/>
-      <c r="AF6" s="320"/>
-      <c r="AG6" s="320"/>
-      <c r="AH6" s="320"/>
+      <c r="V6" s="322"/>
+      <c r="W6" s="322"/>
+      <c r="X6" s="322"/>
+      <c r="Y6" s="322"/>
+      <c r="Z6" s="322"/>
+      <c r="AA6" s="322"/>
+      <c r="AB6" s="322"/>
+      <c r="AC6" s="322"/>
+      <c r="AD6" s="322"/>
+      <c r="AE6" s="322"/>
+      <c r="AF6" s="322"/>
+      <c r="AG6" s="322"/>
+      <c r="AH6" s="322"/>
     </row>
     <row r="7" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="296" t="s">
+      <c r="A7" s="303" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="296" t="s">
+      <c r="B7" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="322" t="s">
+      <c r="C7" s="324" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="296" t="s">
+      <c r="D7" s="303" t="s">
         <v>140</v>
       </c>
-      <c r="E7" s="311" t="s">
+      <c r="E7" s="313" t="s">
         <v>138</v>
       </c>
-      <c r="F7" s="312"/>
-      <c r="G7" s="312"/>
-      <c r="H7" s="312"/>
-      <c r="I7" s="312"/>
-      <c r="J7" s="312"/>
-      <c r="K7" s="312"/>
-      <c r="L7" s="313"/>
-      <c r="M7" s="296" t="s">
+      <c r="F7" s="314"/>
+      <c r="G7" s="314"/>
+      <c r="H7" s="314"/>
+      <c r="I7" s="314"/>
+      <c r="J7" s="314"/>
+      <c r="K7" s="314"/>
+      <c r="L7" s="315"/>
+      <c r="M7" s="303" t="s">
         <v>202</v>
       </c>
-      <c r="N7" s="310" t="s">
+      <c r="N7" s="311" t="s">
         <v>13</v>
       </c>
-      <c r="O7" s="310" t="s">
+      <c r="O7" s="311" t="s">
+        <v>224</v>
+      </c>
+      <c r="P7" s="325" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q7" s="303" t="s">
+        <v>15</v>
+      </c>
+      <c r="R7" s="303" t="s">
+        <v>16</v>
+      </c>
+      <c r="S7" s="299" t="s">
         <v>227</v>
       </c>
-      <c r="P7" s="323" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q7" s="296" t="s">
-        <v>15</v>
-      </c>
-      <c r="R7" s="296" t="s">
-        <v>16</v>
-      </c>
-      <c r="S7" s="324" t="s">
-        <v>211</v>
-      </c>
-      <c r="T7" s="324"/>
-      <c r="U7" s="324"/>
-      <c r="V7" s="325" t="s">
-        <v>215</v>
-      </c>
-      <c r="W7" s="325" t="s">
-        <v>219</v>
-      </c>
-      <c r="X7" s="301" t="s">
+      <c r="T7" s="299"/>
+      <c r="U7" s="299"/>
+      <c r="V7" s="300" t="s">
+        <v>212</v>
+      </c>
+      <c r="W7" s="300" t="s">
+        <v>216</v>
+      </c>
+      <c r="X7" s="297" t="s">
         <v>17</v>
       </c>
-      <c r="Y7" s="298" t="s">
+      <c r="Y7" s="326" t="s">
         <v>107</v>
       </c>
-      <c r="Z7" s="298" t="s">
+      <c r="Z7" s="326" t="s">
         <v>108</v>
       </c>
-      <c r="AA7" s="298" t="s">
+      <c r="AA7" s="326" t="s">
         <v>106</v>
       </c>
-      <c r="AB7" s="300" t="s">
+      <c r="AB7" s="328" t="s">
         <v>147</v>
       </c>
-      <c r="AC7" s="301" t="s">
+      <c r="AC7" s="297" t="s">
         <v>136</v>
       </c>
-      <c r="AD7" s="301" t="s">
+      <c r="AD7" s="297" t="s">
         <v>137</v>
       </c>
-      <c r="AE7" s="296" t="s">
+      <c r="AE7" s="303" t="s">
         <v>135</v>
       </c>
-      <c r="AF7" s="296" t="s">
+      <c r="AF7" s="303" t="s">
         <v>146</v>
       </c>
-      <c r="AG7" s="296" t="s">
-        <v>230</v>
-      </c>
-      <c r="AH7" s="296" t="s">
+      <c r="AG7" s="303" t="s">
+        <v>231</v>
+      </c>
+      <c r="AH7" s="303" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="302"/>
-      <c r="B8" s="321"/>
-      <c r="C8" s="322"/>
-      <c r="D8" s="297"/>
-      <c r="E8" s="314"/>
-      <c r="F8" s="315"/>
-      <c r="G8" s="315"/>
-      <c r="H8" s="315"/>
-      <c r="I8" s="315"/>
-      <c r="J8" s="315"/>
-      <c r="K8" s="315"/>
-      <c r="L8" s="316"/>
-      <c r="M8" s="302"/>
-      <c r="N8" s="302"/>
-      <c r="O8" s="302"/>
-      <c r="P8" s="302"/>
-      <c r="Q8" s="302"/>
-      <c r="R8" s="302"/>
-      <c r="S8" s="324"/>
-      <c r="T8" s="324"/>
-      <c r="U8" s="324"/>
-      <c r="V8" s="326"/>
-      <c r="W8" s="326"/>
-      <c r="X8" s="302"/>
-      <c r="Y8" s="299"/>
-      <c r="Z8" s="299"/>
-      <c r="AA8" s="300"/>
-      <c r="AB8" s="299"/>
-      <c r="AC8" s="302"/>
-      <c r="AD8" s="301"/>
-      <c r="AE8" s="302"/>
-      <c r="AF8" s="296"/>
-      <c r="AG8" s="296"/>
-      <c r="AH8" s="297"/>
+      <c r="A8" s="298"/>
+      <c r="B8" s="323"/>
+      <c r="C8" s="324"/>
+      <c r="D8" s="312"/>
+      <c r="E8" s="316"/>
+      <c r="F8" s="317"/>
+      <c r="G8" s="317"/>
+      <c r="H8" s="317"/>
+      <c r="I8" s="317"/>
+      <c r="J8" s="317"/>
+      <c r="K8" s="317"/>
+      <c r="L8" s="318"/>
+      <c r="M8" s="298"/>
+      <c r="N8" s="298"/>
+      <c r="O8" s="298"/>
+      <c r="P8" s="298"/>
+      <c r="Q8" s="298"/>
+      <c r="R8" s="298"/>
+      <c r="S8" s="299"/>
+      <c r="T8" s="299"/>
+      <c r="U8" s="299"/>
+      <c r="V8" s="301"/>
+      <c r="W8" s="301"/>
+      <c r="X8" s="298"/>
+      <c r="Y8" s="327"/>
+      <c r="Z8" s="327"/>
+      <c r="AA8" s="328"/>
+      <c r="AB8" s="327"/>
+      <c r="AC8" s="298"/>
+      <c r="AD8" s="297"/>
+      <c r="AE8" s="298"/>
+      <c r="AF8" s="303"/>
+      <c r="AG8" s="303"/>
+      <c r="AH8" s="312"/>
     </row>
     <row r="9" spans="1:40" ht="104.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="302"/>
-      <c r="B9" s="321"/>
-      <c r="C9" s="322"/>
-      <c r="D9" s="297"/>
-      <c r="E9" s="317"/>
-      <c r="F9" s="318"/>
-      <c r="G9" s="318"/>
-      <c r="H9" s="318"/>
-      <c r="I9" s="318"/>
-      <c r="J9" s="318"/>
-      <c r="K9" s="318"/>
-      <c r="L9" s="319"/>
-      <c r="M9" s="302"/>
-      <c r="N9" s="302"/>
-      <c r="O9" s="302"/>
-      <c r="P9" s="302"/>
-      <c r="Q9" s="302"/>
-      <c r="R9" s="302"/>
-      <c r="S9" s="265" t="s">
-        <v>212</v>
-      </c>
-      <c r="T9" s="265" t="s">
-        <v>214</v>
-      </c>
-      <c r="U9" s="265" t="s">
-        <v>213</v>
-      </c>
-      <c r="V9" s="327"/>
-      <c r="W9" s="327"/>
-      <c r="X9" s="302"/>
-      <c r="Y9" s="299"/>
-      <c r="Z9" s="299"/>
-      <c r="AA9" s="300"/>
-      <c r="AB9" s="299"/>
-      <c r="AC9" s="302"/>
-      <c r="AD9" s="301"/>
-      <c r="AE9" s="302"/>
-      <c r="AF9" s="296"/>
-      <c r="AG9" s="296"/>
-      <c r="AH9" s="297"/>
+      <c r="A9" s="298"/>
+      <c r="B9" s="323"/>
+      <c r="C9" s="324"/>
+      <c r="D9" s="312"/>
+      <c r="E9" s="319"/>
+      <c r="F9" s="320"/>
+      <c r="G9" s="320"/>
+      <c r="H9" s="320"/>
+      <c r="I9" s="320"/>
+      <c r="J9" s="320"/>
+      <c r="K9" s="320"/>
+      <c r="L9" s="321"/>
+      <c r="M9" s="298"/>
+      <c r="N9" s="298"/>
+      <c r="O9" s="298"/>
+      <c r="P9" s="298"/>
+      <c r="Q9" s="298"/>
+      <c r="R9" s="298"/>
+      <c r="S9" s="263" t="s">
+        <v>225</v>
+      </c>
+      <c r="T9" s="263" t="s">
+        <v>226</v>
+      </c>
+      <c r="U9" s="263" t="s">
+        <v>211</v>
+      </c>
+      <c r="V9" s="302"/>
+      <c r="W9" s="302"/>
+      <c r="X9" s="298"/>
+      <c r="Y9" s="327"/>
+      <c r="Z9" s="327"/>
+      <c r="AA9" s="328"/>
+      <c r="AB9" s="327"/>
+      <c r="AC9" s="298"/>
+      <c r="AD9" s="297"/>
+      <c r="AE9" s="298"/>
+      <c r="AF9" s="303"/>
+      <c r="AG9" s="303"/>
+      <c r="AH9" s="312"/>
       <c r="AI9">
         <f>P12/M12</f>
-        <v>0.75397648211812751</v>
+        <v>0.75409626603409796</v>
       </c>
       <c r="AK9">
         <v>27</v>
+      </c>
+      <c r="AM9">
+        <v>730212</v>
       </c>
     </row>
     <row r="10" spans="1:40" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -22883,7 +22890,7 @@
         <v>209</v>
       </c>
       <c r="L10" s="129" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="M10" s="28">
         <v>5</v>
@@ -22899,17 +22906,17 @@
       <c r="R10" s="28">
         <v>8</v>
       </c>
-      <c r="S10" s="263">
+      <c r="S10" s="262">
         <v>9</v>
       </c>
-      <c r="T10" s="263">
+      <c r="T10" s="262">
         <v>10</v>
       </c>
-      <c r="U10" s="263">
+      <c r="U10" s="262">
         <v>11</v>
       </c>
-      <c r="V10" s="263"/>
-      <c r="W10" s="263"/>
+      <c r="V10" s="262"/>
+      <c r="W10" s="262"/>
       <c r="X10" s="243">
         <v>12</v>
       </c>
@@ -22928,79 +22935,85 @@
       <c r="AK10">
         <v>1</v>
       </c>
+      <c r="AM10">
+        <v>730160</v>
+      </c>
     </row>
     <row r="11" spans="1:40" ht="28.15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28"/>
-      <c r="B11" s="281" t="s">
-        <v>221</v>
+      <c r="B11" s="275" t="s">
+        <v>218</v>
       </c>
       <c r="C11" s="103"/>
-      <c r="D11" s="286">
+      <c r="D11" s="280">
         <f>D12</f>
         <v>890720</v>
       </c>
-      <c r="E11" s="287"/>
-      <c r="F11" s="288"/>
-      <c r="G11" s="288"/>
-      <c r="H11" s="288"/>
-      <c r="I11" s="288"/>
-      <c r="J11" s="288"/>
-      <c r="K11" s="288"/>
-      <c r="L11" s="288"/>
-      <c r="M11" s="286">
+      <c r="E11" s="281"/>
+      <c r="F11" s="282"/>
+      <c r="G11" s="282"/>
+      <c r="H11" s="282"/>
+      <c r="I11" s="282"/>
+      <c r="J11" s="282"/>
+      <c r="K11" s="282"/>
+      <c r="L11" s="282"/>
+      <c r="M11" s="280">
         <f>M12+39020</f>
         <v>1007347</v>
       </c>
-      <c r="N11" s="289"/>
-      <c r="O11" s="289"/>
-      <c r="P11" s="290">
+      <c r="N11" s="283">
+        <v>730211.77500000002</v>
+      </c>
+      <c r="O11" s="283">
+        <f>O12</f>
+        <v>0</v>
+      </c>
+      <c r="P11" s="283">
         <f>P12</f>
-        <v>730095.78500000003</v>
-      </c>
-      <c r="Q11" s="291">
+        <v>730211.77500000002</v>
+      </c>
+      <c r="Q11" s="284">
         <f>P11/M11</f>
-        <v>0.72477089324731203</v>
-      </c>
-      <c r="R11" s="292">
+        <v>0.72488603728407397</v>
+      </c>
+      <c r="R11" s="285">
         <f>R12</f>
-        <v>0.81966923949164727</v>
-      </c>
-      <c r="S11" s="293">
+        <v>0.81979945998742598</v>
+      </c>
+      <c r="S11" s="286">
         <f>S12</f>
-        <v>57013</v>
-      </c>
-      <c r="T11" s="293">
-        <f>T12</f>
-        <v>67533.5</v>
-      </c>
-      <c r="U11" s="293">
+        <v>25834</v>
+      </c>
+      <c r="T11" s="286"/>
+      <c r="U11" s="286">
         <f>U12</f>
-        <v>-10520.5</v>
-      </c>
-      <c r="V11" s="282"/>
-      <c r="W11" s="282"/>
-      <c r="X11" s="283"/>
-      <c r="Y11" s="280"/>
-      <c r="Z11" s="280"/>
-      <c r="AA11" s="280"/>
-      <c r="AB11" s="284"/>
-      <c r="AC11" s="280"/>
-      <c r="AD11" s="280"/>
-      <c r="AE11" s="280"/>
-      <c r="AF11" s="280"/>
-      <c r="AG11" s="280"/>
-      <c r="AH11" s="280"/>
-      <c r="AL11">
-        <v>721480</v>
+        <v>25834</v>
+      </c>
+      <c r="V11" s="276"/>
+      <c r="W11" s="276"/>
+      <c r="X11" s="277"/>
+      <c r="Y11" s="274"/>
+      <c r="Z11" s="274"/>
+      <c r="AA11" s="274"/>
+      <c r="AB11" s="278"/>
+      <c r="AC11" s="274"/>
+      <c r="AD11" s="274"/>
+      <c r="AE11" s="274"/>
+      <c r="AF11" s="274"/>
+      <c r="AG11" s="274"/>
+      <c r="AH11" s="274"/>
+      <c r="AL11" s="19">
+        <f>S11+P11</f>
+        <v>756045.77500000002</v>
       </c>
     </row>
     <row r="12" spans="1:40" s="102" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="96"/>
-      <c r="B12" s="337" t="s">
-        <v>222</v>
+      <c r="B12" s="275" t="s">
+        <v>219</v>
       </c>
       <c r="C12" s="104"/>
-      <c r="D12" s="266">
+      <c r="D12" s="264">
         <f>SUBTOTAL(9,D13:D74)</f>
         <v>890720</v>
       </c>
@@ -23041,35 +23054,35 @@
         <v>968327</v>
       </c>
       <c r="N12" s="98">
-        <v>721569.28500000003</v>
+        <v>730211.77500000002</v>
       </c>
       <c r="O12" s="98">
         <f>SUM(O13:O77)</f>
-        <v>8525.5</v>
-      </c>
-      <c r="P12" s="295">
+        <v>0</v>
+      </c>
+      <c r="P12" s="288">
         <f>SUBTOTAL(9,P13:P74)</f>
-        <v>730095.78500000003</v>
+        <v>730211.77500000002</v>
       </c>
       <c r="Q12" s="101">
         <f>P12/M12</f>
-        <v>0.75397648211812751</v>
+        <v>0.75409626603409796</v>
       </c>
       <c r="R12" s="101">
         <f>P12/D12</f>
-        <v>0.81966923949164727</v>
-      </c>
-      <c r="S12" s="115">
-        <f>SUM(S13:S74)</f>
-        <v>57013</v>
+        <v>0.81979945998742598</v>
+      </c>
+      <c r="S12" s="292">
+        <f>SUM(S13:S77)</f>
+        <v>25834</v>
       </c>
       <c r="T12" s="115">
-        <f>SUM(T13:T74)</f>
-        <v>67533.5</v>
+        <f>SUM(T13:T77)</f>
+        <v>0</v>
       </c>
       <c r="U12" s="115">
         <f>S12-T12</f>
-        <v>-10520.5</v>
+        <v>25834</v>
       </c>
       <c r="V12" s="115"/>
       <c r="W12" s="115">
@@ -23078,19 +23091,19 @@
       </c>
       <c r="X12" s="98">
         <f>M12-P12</f>
-        <v>238231.21499999997</v>
+        <v>238115.22499999998</v>
       </c>
       <c r="Y12" s="98">
         <f>N12-Q12</f>
-        <v>721568.53102351795</v>
+        <v>730211.02090373402</v>
       </c>
       <c r="Z12" s="98">
         <f>O12-R12</f>
-        <v>8524.6803307605078</v>
+        <v>-0.81979945998742598</v>
       </c>
       <c r="AA12" s="98">
         <f>P12-S12</f>
-        <v>673082.78500000003</v>
+        <v>704377.77500000002</v>
       </c>
       <c r="AB12" s="159">
         <f>SUM(AB13:AB67)</f>
@@ -23098,16 +23111,16 @@
       </c>
       <c r="AC12" s="125">
         <f t="shared" ref="AC12:AC22" si="1">M12-P12-AB12</f>
-        <v>-86528.785000000033</v>
+        <v>-86644.775000000023</v>
       </c>
       <c r="AD12" s="126">
         <f>(P12+AB12)/M12</f>
-        <v>1.0893590543277221</v>
+        <v>1.0894788382436924</v>
       </c>
       <c r="AE12" s="101"/>
       <c r="AF12" s="115">
         <f>SUM(AF13:AF67)</f>
-        <v>146793.70300000004</v>
+        <v>146700.94300000003</v>
       </c>
       <c r="AG12" s="136"/>
       <c r="AH12" s="175" t="s">
@@ -23115,15 +23128,16 @@
       </c>
       <c r="AI12" s="117">
         <f>M12-P12</f>
-        <v>238231.21499999997</v>
+        <v>238115.22499999998</v>
       </c>
       <c r="AJ12" s="119">
         <f>P12+S12</f>
-        <v>787108.78500000003</v>
-      </c>
-      <c r="AL12" s="119">
-        <f>M12*3%</f>
-        <v>29049.809999999998</v>
+        <v>756045.77500000002</v>
+      </c>
+      <c r="AL12" s="291"/>
+      <c r="AM12" s="102">
+        <f>AM9-AM10</f>
+        <v>52</v>
       </c>
       <c r="AN12" s="119">
         <f>M12*70%</f>
@@ -23151,7 +23165,7 @@
         <f>I13+J13+K13+L13</f>
         <v>0</v>
       </c>
-      <c r="N13" s="207">
+      <c r="N13" s="289">
         <v>0</v>
       </c>
       <c r="O13" s="208"/>
@@ -23161,7 +23175,7 @@
       </c>
       <c r="Q13" s="39"/>
       <c r="R13" s="56"/>
-      <c r="S13" s="56"/>
+      <c r="S13" s="293"/>
       <c r="T13" s="177"/>
       <c r="U13" s="56"/>
       <c r="V13" s="56"/>
@@ -23185,15 +23199,15 @@
       <c r="AH13" s="162"/>
       <c r="AI13" s="19">
         <f>P12+AB12</f>
-        <v>1054855.7850000001</v>
+        <v>1054971.7749999999</v>
       </c>
       <c r="AL13" s="19">
         <f>AL12-D12</f>
-        <v>-861670.19</v>
+        <v>-890720</v>
       </c>
       <c r="AN13" s="19">
         <f>AN12-P12</f>
-        <v>-52266.885000000126</v>
+        <v>-52382.875000000116</v>
       </c>
     </row>
     <row r="14" spans="1:40" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -23225,7 +23239,7 @@
         <f>SUM(E14:L14)</f>
         <v>0</v>
       </c>
-      <c r="N14" s="210">
+      <c r="N14" s="273">
         <v>0</v>
       </c>
       <c r="O14" s="210"/>
@@ -23239,16 +23253,14 @@
       <c r="R14" s="63">
         <v>0</v>
       </c>
-      <c r="S14" s="270"/>
-      <c r="T14" s="177">
-        <v>0</v>
-      </c>
-      <c r="U14" s="270">
+      <c r="S14" s="294"/>
+      <c r="T14" s="177"/>
+      <c r="U14" s="268">
         <f>S14-T14</f>
         <v>0</v>
       </c>
-      <c r="V14" s="270"/>
-      <c r="W14" s="270"/>
+      <c r="V14" s="268"/>
+      <c r="W14" s="268"/>
       <c r="X14" s="33">
         <f>M14-P14</f>
         <v>0</v>
@@ -23274,14 +23286,14 @@
         <v>0</v>
       </c>
       <c r="AG14" s="338" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AH14" s="141" t="s">
         <v>27</v>
       </c>
       <c r="AI14" s="120">
         <f>P12/M12</f>
-        <v>0.75397648211812751</v>
+        <v>0.75409626603409796</v>
       </c>
       <c r="AK14">
         <v>2</v>
@@ -23294,7 +23306,7 @@
         <v>7264685000</v>
       </c>
     </row>
-    <row r="15" spans="1:40" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" ht="63" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>2</v>
       </c>
@@ -23326,7 +23338,7 @@
         <f>SUM(E15:L15)</f>
         <v>0</v>
       </c>
-      <c r="N15" s="210">
+      <c r="N15" s="273">
         <v>0</v>
       </c>
       <c r="O15" s="210"/>
@@ -23341,16 +23353,14 @@
         <f>0%</f>
         <v>0</v>
       </c>
-      <c r="S15" s="270"/>
-      <c r="T15" s="177">
-        <v>0</v>
-      </c>
-      <c r="U15" s="270">
+      <c r="S15" s="294"/>
+      <c r="T15" s="177"/>
+      <c r="U15" s="268">
         <f t="shared" ref="U15:U74" si="4">S15-T15</f>
         <v>0</v>
       </c>
-      <c r="V15" s="270"/>
-      <c r="W15" s="270"/>
+      <c r="V15" s="268"/>
+      <c r="W15" s="268"/>
       <c r="X15" s="33">
         <f>M15-P15</f>
         <v>0</v>
@@ -23375,7 +23385,7 @@
         <v>0</v>
       </c>
       <c r="AG15" s="338" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AH15" s="141" t="s">
         <v>29</v>
@@ -23411,7 +23421,7 @@
         <f t="shared" ref="M16:M77" si="5">SUM(E16:L16)</f>
         <v>0</v>
       </c>
-      <c r="N16" s="210">
+      <c r="N16" s="273">
         <v>0</v>
       </c>
       <c r="O16" s="210"/>
@@ -23421,14 +23431,14 @@
       </c>
       <c r="Q16" s="154"/>
       <c r="R16" s="63"/>
-      <c r="S16" s="270"/>
+      <c r="S16" s="294"/>
       <c r="T16" s="177"/>
-      <c r="U16" s="270">
+      <c r="U16" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V16" s="270"/>
-      <c r="W16" s="270"/>
+      <c r="V16" s="268"/>
+      <c r="W16" s="268"/>
       <c r="X16" s="33">
         <f>M16-P16</f>
         <v>0</v>
@@ -23485,7 +23495,7 @@
         <f>SUM(E17:L17)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="210">
+      <c r="N17" s="273">
         <v>0</v>
       </c>
       <c r="O17" s="210"/>
@@ -23501,14 +23511,14 @@
         <f>0%</f>
         <v>0</v>
       </c>
-      <c r="S17" s="270"/>
+      <c r="S17" s="294"/>
       <c r="T17" s="177"/>
-      <c r="U17" s="270">
+      <c r="U17" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V17" s="270"/>
-      <c r="W17" s="270"/>
+      <c r="V17" s="268"/>
+      <c r="W17" s="268"/>
       <c r="X17" s="33">
         <f>M17-P17</f>
         <v>0</v>
@@ -23534,7 +23544,7 @@
         <v>0</v>
       </c>
       <c r="AG17" s="339" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH17" s="144" t="s">
         <v>39</v>
@@ -23558,7 +23568,7 @@
       <c r="K18" s="35"/>
       <c r="L18" s="35"/>
       <c r="M18" s="32"/>
-      <c r="N18" s="210">
+      <c r="N18" s="273">
         <v>0</v>
       </c>
       <c r="O18" s="210"/>
@@ -23568,14 +23578,14 @@
       </c>
       <c r="Q18" s="63"/>
       <c r="R18" s="63"/>
-      <c r="S18" s="270"/>
+      <c r="S18" s="294"/>
       <c r="T18" s="177"/>
-      <c r="U18" s="270">
+      <c r="U18" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V18" s="270"/>
-      <c r="W18" s="270"/>
+      <c r="V18" s="268"/>
+      <c r="W18" s="268"/>
       <c r="X18" s="33"/>
       <c r="Y18" s="64"/>
       <c r="Z18" s="64"/>
@@ -23623,7 +23633,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="N19" s="210">
+      <c r="N19" s="273">
         <v>50</v>
       </c>
       <c r="O19" s="210"/>
@@ -23639,18 +23649,16 @@
         <f>P19/D19</f>
         <v>1</v>
       </c>
-      <c r="S19" s="270"/>
-      <c r="T19" s="177">
-        <v>50</v>
-      </c>
-      <c r="U19" s="270">
+      <c r="S19" s="294"/>
+      <c r="T19" s="177"/>
+      <c r="U19" s="268">
         <f t="shared" si="4"/>
-        <v>-50</v>
-      </c>
-      <c r="V19" s="270" t="s">
-        <v>216</v>
-      </c>
-      <c r="W19" s="270">
+        <v>0</v>
+      </c>
+      <c r="V19" s="268" t="s">
+        <v>213</v>
+      </c>
+      <c r="W19" s="268">
         <v>50</v>
       </c>
       <c r="X19" s="33">
@@ -23678,7 +23686,7 @@
         <v>0</v>
       </c>
       <c r="AG19" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH19" s="166"/>
     </row>
@@ -23713,7 +23721,7 @@
         <f t="shared" si="5"/>
         <v>15711</v>
       </c>
-      <c r="N20" s="210">
+      <c r="N20" s="273">
         <v>3885.6019999999999</v>
       </c>
       <c r="O20" s="210"/>
@@ -23729,20 +23737,16 @@
         <f>P20/M20</f>
         <v>0.24731729361593788</v>
       </c>
-      <c r="S20" s="270">
-        <v>1600</v>
-      </c>
-      <c r="T20" s="177">
-        <v>1639</v>
-      </c>
-      <c r="U20" s="270">
+      <c r="S20" s="294"/>
+      <c r="T20" s="177"/>
+      <c r="U20" s="268">
         <f t="shared" si="4"/>
-        <v>-39</v>
-      </c>
-      <c r="V20" s="270" t="s">
-        <v>217</v>
-      </c>
-      <c r="W20" s="270">
+        <v>0</v>
+      </c>
+      <c r="V20" s="268" t="s">
+        <v>214</v>
+      </c>
+      <c r="W20" s="268">
         <v>1600</v>
       </c>
       <c r="X20" s="33">
@@ -23772,7 +23776,7 @@
         <v>11825.398000000001</v>
       </c>
       <c r="AG20" s="339" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH20" s="147" t="s">
         <v>61</v>
@@ -23805,68 +23809,68 @@
         <f t="shared" si="5"/>
         <v>36800</v>
       </c>
-      <c r="N21" s="210">
-        <v>29633.066999999999</v>
+      <c r="N21" s="273">
+        <v>29673.066999999999</v>
       </c>
       <c r="O21" s="210"/>
       <c r="P21" s="209">
         <f t="shared" si="2"/>
-        <v>29633.066999999999</v>
+        <v>29673.066999999999</v>
       </c>
       <c r="Q21" s="63">
         <f>P21/M21</f>
-        <v>0.80524638586956521</v>
+        <v>0.80633334239130428</v>
       </c>
       <c r="R21" s="63">
         <f>P21/D21</f>
-        <v>0.80524638586956521</v>
-      </c>
-      <c r="S21" s="270">
-        <v>0</v>
-      </c>
-      <c r="T21" s="177">
-        <f>100+3017</f>
-        <v>3117</v>
-      </c>
-      <c r="U21" s="270">
+        <v>0.80633334239130428</v>
+      </c>
+      <c r="S21" s="294">
+        <v>3805</v>
+      </c>
+      <c r="T21" s="177"/>
+      <c r="U21" s="268">
         <f t="shared" si="4"/>
-        <v>-3117</v>
-      </c>
-      <c r="V21" s="270"/>
-      <c r="W21" s="270"/>
+        <v>3805</v>
+      </c>
+      <c r="V21" s="268"/>
+      <c r="W21" s="268"/>
       <c r="X21" s="33">
         <f t="shared" si="6"/>
-        <v>7166.9330000000009</v>
+        <v>7126.9330000000009</v>
       </c>
       <c r="Y21" s="64"/>
       <c r="Z21" s="64"/>
       <c r="AA21" s="41">
         <f t="shared" si="3"/>
-        <v>7166.9330000000009</v>
+        <v>7126.9330000000009</v>
       </c>
       <c r="AB21" s="123">
         <v>20000</v>
       </c>
       <c r="AC21" s="125">
         <f t="shared" si="1"/>
-        <v>-12833.066999999999</v>
+        <v>-12873.066999999999</v>
       </c>
       <c r="AD21" s="126">
         <f>(P21+AB21)/M21</f>
-        <v>1.3487246467391303</v>
+        <v>1.3498116032608694</v>
       </c>
       <c r="AE21" s="77"/>
       <c r="AF21" s="157">
         <f>M21-P21</f>
-        <v>7166.9330000000009</v>
+        <v>7126.9330000000009</v>
       </c>
       <c r="AG21" s="339" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH21" s="169"/>
       <c r="AJ21" s="18">
         <f>P21-24656</f>
-        <v>4977.0669999999991</v>
+        <v>5017.0669999999991</v>
+      </c>
+      <c r="AL21">
+        <v>33478</v>
       </c>
     </row>
     <row r="22" spans="1:40" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -23896,7 +23900,7 @@
         <f t="shared" si="5"/>
         <v>3288</v>
       </c>
-      <c r="N22" s="210">
+      <c r="N22" s="273">
         <v>3155.66</v>
       </c>
       <c r="O22" s="210"/>
@@ -23912,20 +23916,16 @@
         <f>P22/D22</f>
         <v>0.95975060827250602</v>
       </c>
-      <c r="S22" s="270">
-        <v>863</v>
-      </c>
-      <c r="T22" s="177">
-        <v>863</v>
-      </c>
-      <c r="U22" s="270">
+      <c r="S22" s="294"/>
+      <c r="T22" s="177"/>
+      <c r="U22" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V22" s="270" t="s">
-        <v>217</v>
-      </c>
-      <c r="W22" s="270">
+      <c r="V22" s="268" t="s">
+        <v>214</v>
+      </c>
+      <c r="W22" s="268">
         <v>863</v>
       </c>
       <c r="X22" s="33">
@@ -23955,7 +23955,7 @@
         <v>132.34000000000015</v>
       </c>
       <c r="AG22" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH22" s="167"/>
       <c r="AI22" s="18">
@@ -23964,6 +23964,10 @@
       </c>
       <c r="AK22">
         <v>4</v>
+      </c>
+      <c r="AL22" s="18">
+        <f>AL21-P21</f>
+        <v>3804.9330000000009</v>
       </c>
     </row>
     <row r="23" spans="1:40" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -23997,7 +24001,7 @@
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="N23" s="210">
+      <c r="N23" s="273">
         <v>0</v>
       </c>
       <c r="O23" s="210"/>
@@ -24007,14 +24011,16 @@
       </c>
       <c r="Q23" s="63"/>
       <c r="R23" s="63"/>
-      <c r="S23" s="271"/>
+      <c r="S23" s="295">
+        <v>6</v>
+      </c>
       <c r="T23" s="177"/>
-      <c r="U23" s="270">
+      <c r="U23" s="268">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V23" s="270"/>
-      <c r="W23" s="270"/>
+        <v>6</v>
+      </c>
+      <c r="V23" s="268"/>
+      <c r="W23" s="268"/>
       <c r="X23" s="33">
         <f t="shared" si="6"/>
         <v>6</v>
@@ -24028,7 +24034,7 @@
       <c r="AE23" s="77"/>
       <c r="AF23" s="157"/>
       <c r="AG23" s="122" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH23" s="167"/>
       <c r="AI23" s="18"/>
@@ -24064,7 +24070,7 @@
         <f t="shared" si="5"/>
         <v>23</v>
       </c>
-      <c r="N24" s="210">
+      <c r="N24" s="273">
         <v>0</v>
       </c>
       <c r="O24" s="210"/>
@@ -24074,14 +24080,16 @@
       </c>
       <c r="Q24" s="63"/>
       <c r="R24" s="63"/>
-      <c r="S24" s="271"/>
+      <c r="S24" s="295">
+        <v>23</v>
+      </c>
       <c r="T24" s="177"/>
-      <c r="U24" s="270">
+      <c r="U24" s="268">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V24" s="270"/>
-      <c r="W24" s="270"/>
+        <v>23</v>
+      </c>
+      <c r="V24" s="268"/>
+      <c r="W24" s="268"/>
       <c r="X24" s="33">
         <f t="shared" si="6"/>
         <v>23</v>
@@ -24095,7 +24103,7 @@
       <c r="AE24" s="77"/>
       <c r="AF24" s="157"/>
       <c r="AG24" s="122" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH24" s="167"/>
       <c r="AI24" s="18"/>
@@ -24127,7 +24135,7 @@
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="N25" s="277">
+      <c r="N25" s="273">
         <v>3.2639999999999998</v>
       </c>
       <c r="O25" s="210"/>
@@ -24137,18 +24145,14 @@
       </c>
       <c r="Q25" s="63"/>
       <c r="R25" s="63"/>
-      <c r="S25" s="271">
-        <v>4</v>
-      </c>
-      <c r="T25" s="210">
-        <v>4</v>
-      </c>
-      <c r="U25" s="270">
+      <c r="S25" s="295"/>
+      <c r="T25" s="210"/>
+      <c r="U25" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V25" s="270"/>
-      <c r="W25" s="270"/>
+      <c r="V25" s="268"/>
+      <c r="W25" s="268"/>
       <c r="X25" s="33">
         <f t="shared" si="6"/>
         <v>0.73600000000000021</v>
@@ -24162,7 +24166,7 @@
       <c r="AE25" s="77"/>
       <c r="AF25" s="157"/>
       <c r="AG25" s="122" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AH25" s="167"/>
       <c r="AI25" s="18"/>
@@ -24194,7 +24198,7 @@
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="N26" s="210">
+      <c r="N26" s="273">
         <v>5.54</v>
       </c>
       <c r="O26" s="210"/>
@@ -24204,18 +24208,14 @@
       </c>
       <c r="Q26" s="63"/>
       <c r="R26" s="63"/>
-      <c r="S26" s="271">
-        <v>1</v>
-      </c>
-      <c r="T26" s="210">
-        <v>0.5</v>
-      </c>
-      <c r="U26" s="270">
+      <c r="S26" s="295"/>
+      <c r="T26" s="210"/>
+      <c r="U26" s="268">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-      <c r="V26" s="270"/>
-      <c r="W26" s="270"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="268"/>
+      <c r="W26" s="268"/>
       <c r="X26" s="33">
         <f t="shared" si="6"/>
         <v>0.45999999999999996</v>
@@ -24229,7 +24229,7 @@
       <c r="AE26" s="77"/>
       <c r="AF26" s="157"/>
       <c r="AG26" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH26" s="167"/>
       <c r="AI26" s="18"/>
@@ -24261,7 +24261,7 @@
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="N27" s="277">
+      <c r="N27" s="273">
         <v>5.1639999999999997</v>
       </c>
       <c r="O27" s="210"/>
@@ -24271,18 +24271,14 @@
       </c>
       <c r="Q27" s="63"/>
       <c r="R27" s="63"/>
-      <c r="S27" s="271">
-        <v>6</v>
-      </c>
-      <c r="T27" s="210">
-        <v>6</v>
-      </c>
-      <c r="U27" s="270">
+      <c r="S27" s="295"/>
+      <c r="T27" s="210"/>
+      <c r="U27" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V27" s="270"/>
-      <c r="W27" s="270"/>
+      <c r="V27" s="268"/>
+      <c r="W27" s="268"/>
       <c r="X27" s="33">
         <f t="shared" si="6"/>
         <v>0.8360000000000003</v>
@@ -24296,7 +24292,7 @@
       <c r="AE27" s="77"/>
       <c r="AF27" s="157"/>
       <c r="AG27" s="122" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AH27" s="167"/>
       <c r="AI27" s="18"/>
@@ -24328,7 +24324,7 @@
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="N28" s="278">
+      <c r="N28" s="273">
         <v>3.97</v>
       </c>
       <c r="O28" s="210"/>
@@ -24338,18 +24334,14 @@
       </c>
       <c r="Q28" s="63"/>
       <c r="R28" s="63"/>
-      <c r="S28" s="271">
-        <v>1</v>
-      </c>
-      <c r="T28" s="279">
-        <v>1</v>
-      </c>
-      <c r="U28" s="270">
+      <c r="S28" s="295"/>
+      <c r="T28" s="273"/>
+      <c r="U28" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V28" s="270"/>
-      <c r="W28" s="270"/>
+      <c r="V28" s="268"/>
+      <c r="W28" s="268"/>
       <c r="X28" s="33">
         <f t="shared" si="6"/>
         <v>2.9999999999999805E-2</v>
@@ -24363,7 +24355,7 @@
       <c r="AE28" s="77"/>
       <c r="AF28" s="157"/>
       <c r="AG28" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH28" s="167"/>
       <c r="AI28" s="18"/>
@@ -24378,7 +24370,7 @@
       <c r="C29" s="221" t="s">
         <v>117</v>
       </c>
-      <c r="D29" s="285">
+      <c r="D29" s="279">
         <v>43</v>
       </c>
       <c r="E29" s="35"/>
@@ -24395,7 +24387,7 @@
         <f t="shared" si="5"/>
         <v>43</v>
       </c>
-      <c r="N29" s="276">
+      <c r="N29" s="273">
         <v>42.15</v>
       </c>
       <c r="O29" s="210"/>
@@ -24405,18 +24397,14 @@
       </c>
       <c r="Q29" s="63"/>
       <c r="R29" s="63"/>
-      <c r="S29" s="271">
-        <v>36</v>
-      </c>
-      <c r="T29" s="210">
-        <v>36</v>
-      </c>
-      <c r="U29" s="270">
+      <c r="S29" s="295"/>
+      <c r="T29" s="210"/>
+      <c r="U29" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V29" s="270"/>
-      <c r="W29" s="270"/>
+      <c r="V29" s="268"/>
+      <c r="W29" s="268"/>
       <c r="X29" s="33">
         <f t="shared" si="6"/>
         <v>0.85000000000000142</v>
@@ -24430,11 +24418,11 @@
       <c r="AE29" s="77"/>
       <c r="AF29" s="157"/>
       <c r="AG29" s="338" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AH29" s="167"/>
       <c r="AI29" s="18"/>
-      <c r="AN29" s="269"/>
+      <c r="AN29" s="267"/>
     </row>
     <row r="30" spans="1:40" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="30">
@@ -24463,7 +24451,7 @@
         <f t="shared" si="5"/>
         <v>45</v>
       </c>
-      <c r="N30" s="210">
+      <c r="N30" s="273">
         <v>44.32</v>
       </c>
       <c r="O30" s="210"/>
@@ -24473,18 +24461,14 @@
       </c>
       <c r="Q30" s="63"/>
       <c r="R30" s="63"/>
-      <c r="S30" s="271">
-        <v>45</v>
-      </c>
-      <c r="T30" s="210">
-        <v>44.32</v>
-      </c>
-      <c r="U30" s="270">
+      <c r="S30" s="295"/>
+      <c r="T30" s="210"/>
+      <c r="U30" s="268">
         <f t="shared" si="4"/>
-        <v>0.67999999999999972</v>
-      </c>
-      <c r="V30" s="270"/>
-      <c r="W30" s="270"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="268"/>
+      <c r="W30" s="268"/>
       <c r="X30" s="33">
         <f t="shared" si="6"/>
         <v>0.67999999999999972</v>
@@ -24498,7 +24482,7 @@
       <c r="AE30" s="77"/>
       <c r="AF30" s="157"/>
       <c r="AG30" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH30" s="167"/>
       <c r="AI30" s="18"/>
@@ -24530,7 +24514,7 @@
         <f t="shared" si="5"/>
         <v>74</v>
       </c>
-      <c r="N31" s="210">
+      <c r="N31" s="273">
         <v>73.800000000000011</v>
       </c>
       <c r="O31" s="210"/>
@@ -24540,18 +24524,14 @@
       </c>
       <c r="Q31" s="63"/>
       <c r="R31" s="63"/>
-      <c r="S31" s="271">
-        <v>37</v>
-      </c>
-      <c r="T31" s="210">
-        <v>36.700000000000003</v>
-      </c>
-      <c r="U31" s="270">
+      <c r="S31" s="295"/>
+      <c r="T31" s="210"/>
+      <c r="U31" s="268">
         <f t="shared" si="4"/>
-        <v>0.29999999999999716</v>
-      </c>
-      <c r="V31" s="270"/>
-      <c r="W31" s="270"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="268"/>
+      <c r="W31" s="268"/>
       <c r="X31" s="33">
         <f t="shared" si="6"/>
         <v>0.19999999999998863</v>
@@ -24565,7 +24545,7 @@
       <c r="AE31" s="77"/>
       <c r="AF31" s="157"/>
       <c r="AG31" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH31" s="167"/>
       <c r="AI31" s="18"/>
@@ -24597,7 +24577,7 @@
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="N32" s="277">
+      <c r="N32" s="273">
         <v>3.28</v>
       </c>
       <c r="O32" s="210"/>
@@ -24607,18 +24587,14 @@
       </c>
       <c r="Q32" s="63"/>
       <c r="R32" s="63"/>
-      <c r="S32" s="271">
-        <v>4</v>
-      </c>
-      <c r="T32" s="210">
-        <v>3.28</v>
-      </c>
-      <c r="U32" s="270">
+      <c r="S32" s="295"/>
+      <c r="T32" s="210"/>
+      <c r="U32" s="268">
         <f t="shared" si="4"/>
-        <v>0.7200000000000002</v>
-      </c>
-      <c r="V32" s="270"/>
-      <c r="W32" s="270"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="268"/>
+      <c r="W32" s="268"/>
       <c r="X32" s="33">
         <f t="shared" si="6"/>
         <v>0.7200000000000002</v>
@@ -24632,12 +24608,12 @@
       <c r="AE32" s="77"/>
       <c r="AF32" s="157"/>
       <c r="AG32" s="122" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH32" s="167"/>
       <c r="AI32" s="18"/>
     </row>
-    <row r="33" spans="1:38" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="30">
         <v>18</v>
       </c>
@@ -24664,7 +24640,7 @@
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="N33" s="210">
+      <c r="N33" s="273">
         <v>8.6999999999999993</v>
       </c>
       <c r="O33" s="210"/>
@@ -24674,18 +24650,14 @@
       </c>
       <c r="Q33" s="63"/>
       <c r="R33" s="63"/>
-      <c r="S33" s="271">
-        <v>9</v>
-      </c>
-      <c r="T33" s="210">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="U33" s="270">
+      <c r="S33" s="295"/>
+      <c r="T33" s="210"/>
+      <c r="U33" s="268">
         <f t="shared" si="4"/>
-        <v>0.30000000000000071</v>
-      </c>
-      <c r="V33" s="270"/>
-      <c r="W33" s="270"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="268"/>
+      <c r="W33" s="268"/>
       <c r="X33" s="33">
         <f t="shared" si="6"/>
         <v>0.30000000000000071</v>
@@ -24699,12 +24671,12 @@
       <c r="AE33" s="77"/>
       <c r="AF33" s="157"/>
       <c r="AG33" s="122" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AH33" s="167"/>
       <c r="AI33" s="18"/>
     </row>
-    <row r="34" spans="1:38" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="30">
         <v>19</v>
       </c>
@@ -24731,7 +24703,7 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="N34" s="210">
+      <c r="N34" s="273">
         <v>9</v>
       </c>
       <c r="O34" s="210"/>
@@ -24741,18 +24713,14 @@
       </c>
       <c r="Q34" s="63"/>
       <c r="R34" s="63"/>
-      <c r="S34" s="271">
-        <v>2</v>
-      </c>
-      <c r="T34" s="210">
-        <v>1</v>
-      </c>
-      <c r="U34" s="270">
+      <c r="S34" s="295"/>
+      <c r="T34" s="210"/>
+      <c r="U34" s="268">
         <f>S34-T34</f>
-        <v>1</v>
-      </c>
-      <c r="V34" s="270"/>
-      <c r="W34" s="270"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="268"/>
+      <c r="W34" s="268"/>
       <c r="X34" s="33">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -24766,12 +24734,12 @@
       <c r="AE34" s="77"/>
       <c r="AF34" s="157"/>
       <c r="AG34" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH34" s="167"/>
       <c r="AI34" s="18"/>
     </row>
-    <row r="35" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="51" t="s">
         <v>182</v>
       </c>
@@ -24789,7 +24757,7 @@
       <c r="K35" s="35"/>
       <c r="L35" s="35"/>
       <c r="M35" s="32"/>
-      <c r="N35" s="210">
+      <c r="N35" s="273">
         <v>0</v>
       </c>
       <c r="O35" s="210"/>
@@ -24799,14 +24767,14 @@
       </c>
       <c r="Q35" s="63"/>
       <c r="R35" s="63"/>
-      <c r="S35" s="271"/>
+      <c r="S35" s="295"/>
       <c r="T35" s="177"/>
-      <c r="U35" s="270">
+      <c r="U35" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V35" s="270"/>
-      <c r="W35" s="270"/>
+      <c r="V35" s="268"/>
+      <c r="W35" s="268"/>
       <c r="X35" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -24828,7 +24796,7 @@
       <c r="AG35" s="341"/>
       <c r="AH35" s="170"/>
     </row>
-    <row r="36" spans="1:38" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="30">
         <v>20</v>
       </c>
@@ -24859,68 +24827,66 @@
         <f t="shared" si="5"/>
         <v>6515</v>
       </c>
-      <c r="N36" s="210">
-        <v>6454.44</v>
+      <c r="N36" s="273">
+        <v>6453</v>
       </c>
       <c r="O36" s="210"/>
       <c r="P36" s="209">
-        <f>SUM(N36:O36)+1</f>
-        <v>6455.44</v>
+        <f>SUM(N36:O36)</f>
+        <v>6453</v>
       </c>
       <c r="Q36" s="63">
         <f t="shared" ref="Q36:Q43" si="8">P36/M36</f>
-        <v>0.9908580199539524</v>
+        <v>0.99048349961627014</v>
       </c>
       <c r="R36" s="63">
         <f t="shared" ref="R36:R43" si="9">P36/D36</f>
-        <v>0.9908580199539524</v>
-      </c>
-      <c r="S36" s="271"/>
-      <c r="T36" s="177">
-        <v>450</v>
-      </c>
-      <c r="U36" s="270">
+        <v>0.99048349961627014</v>
+      </c>
+      <c r="S36" s="295"/>
+      <c r="T36" s="177"/>
+      <c r="U36" s="268">
         <f t="shared" si="4"/>
-        <v>-450</v>
-      </c>
-      <c r="V36" s="270"/>
-      <c r="W36" s="270"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="268"/>
+      <c r="W36" s="268"/>
       <c r="X36" s="33">
         <f t="shared" si="6"/>
-        <v>59.5600000000004</v>
+        <v>62</v>
       </c>
       <c r="Y36" s="64"/>
       <c r="Z36" s="64"/>
       <c r="AA36" s="41">
         <f t="shared" si="3"/>
-        <v>59.5600000000004</v>
+        <v>62</v>
       </c>
       <c r="AB36" s="65">
         <v>110</v>
       </c>
       <c r="AC36" s="125">
         <f t="shared" si="7"/>
-        <v>-50.4399999999996</v>
+        <v>-48</v>
       </c>
       <c r="AD36" s="126">
         <f t="shared" ref="AD36:AD62" si="10">(P36+AB36)/M36</f>
-        <v>1.0077421335379892</v>
+        <v>1.0073676132003069</v>
       </c>
       <c r="AE36" s="64"/>
       <c r="AF36" s="64">
         <f t="shared" ref="AF36:AF62" si="11">M36-P36</f>
-        <v>59.5600000000004</v>
+        <v>62</v>
       </c>
       <c r="AG36" s="339" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH36" s="168"/>
       <c r="AL36" s="18">
-        <f>P36-6078</f>
-        <v>377.4399999999996</v>
+        <f>6515</f>
+        <v>6515</v>
       </c>
     </row>
-    <row r="37" spans="1:38" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="30">
         <v>21</v>
       </c>
@@ -24947,7 +24913,7 @@
         <f t="shared" si="5"/>
         <v>1208</v>
       </c>
-      <c r="N37" s="210">
+      <c r="N37" s="273">
         <v>936.10699999999997</v>
       </c>
       <c r="O37" s="210"/>
@@ -24963,14 +24929,14 @@
         <f t="shared" si="9"/>
         <v>0.7749230132450331</v>
       </c>
-      <c r="S37" s="271"/>
+      <c r="S37" s="295"/>
       <c r="T37" s="177"/>
-      <c r="U37" s="270">
+      <c r="U37" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V37" s="270"/>
-      <c r="W37" s="270"/>
+      <c r="V37" s="268"/>
+      <c r="W37" s="268"/>
       <c r="X37" s="33">
         <f t="shared" si="6"/>
         <v>271.89300000000003</v>
@@ -24996,15 +24962,19 @@
         <v>271.89300000000003</v>
       </c>
       <c r="AG37" s="338" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AH37" s="169"/>
       <c r="AJ37" s="19">
         <f>N37-261</f>
         <v>675.10699999999997</v>
       </c>
+      <c r="AL37" s="18">
+        <f>AL36-P36</f>
+        <v>62</v>
+      </c>
     </row>
-    <row r="38" spans="1:38" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="30">
         <v>22</v>
       </c>
@@ -25035,7 +25005,7 @@
         <f t="shared" si="5"/>
         <v>14500</v>
       </c>
-      <c r="N38" s="210">
+      <c r="N38" s="273">
         <v>9665.2000000000007</v>
       </c>
       <c r="O38" s="210"/>
@@ -25051,16 +25021,16 @@
         <f t="shared" si="9"/>
         <v>0.77321600000000001</v>
       </c>
-      <c r="S38" s="271">
-        <v>3500</v>
+      <c r="S38" s="295">
+        <v>2835</v>
       </c>
       <c r="T38" s="177"/>
-      <c r="U38" s="270">
+      <c r="U38" s="268">
         <f t="shared" si="4"/>
-        <v>3500</v>
-      </c>
-      <c r="V38" s="270"/>
-      <c r="W38" s="270"/>
+        <v>2835</v>
+      </c>
+      <c r="V38" s="268"/>
+      <c r="W38" s="268"/>
       <c r="X38" s="33">
         <f t="shared" si="6"/>
         <v>4834.7999999999993</v>
@@ -25088,13 +25058,21 @@
         <v>4834.7999999999993</v>
       </c>
       <c r="AG38" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH38" s="167"/>
       <c r="AI38" s="22"/>
       <c r="AJ38" s="19"/>
+      <c r="AL38" s="19">
+        <f>S38+N38</f>
+        <v>12500.2</v>
+      </c>
+      <c r="AM38" s="19">
+        <f>M38-P38</f>
+        <v>4834.7999999999993</v>
+      </c>
     </row>
-    <row r="39" spans="1:38" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="30">
         <v>23</v>
       </c>
@@ -25123,13 +25101,10 @@
         <f t="shared" si="5"/>
         <v>39097</v>
       </c>
-      <c r="N39" s="210">
-        <v>28818.329999999998</v>
-      </c>
-      <c r="O39" s="210">
-        <f>4874.4+374.9+7.5+108.3+1</f>
-        <v>5366.0999999999995</v>
-      </c>
+      <c r="N39" s="273">
+        <v>34184.43</v>
+      </c>
+      <c r="O39" s="210"/>
       <c r="P39" s="209">
         <f t="shared" si="12"/>
         <v>34184.43</v>
@@ -25142,22 +25117,16 @@
         <f t="shared" si="9"/>
         <v>0.77485844459052067</v>
       </c>
-      <c r="S39" s="271">
-        <f>7900</f>
-        <v>7900</v>
-      </c>
-      <c r="T39" s="177">
-        <f>7931+148+200</f>
-        <v>8279</v>
-      </c>
-      <c r="U39" s="270">
+      <c r="S39" s="295"/>
+      <c r="T39" s="177"/>
+      <c r="U39" s="268">
         <f t="shared" si="4"/>
-        <v>-379</v>
-      </c>
-      <c r="V39" s="270" t="s">
-        <v>220</v>
-      </c>
-      <c r="W39" s="270">
+        <v>0</v>
+      </c>
+      <c r="V39" s="268" t="s">
+        <v>217</v>
+      </c>
+      <c r="W39" s="268">
         <v>148</v>
       </c>
       <c r="X39" s="33">
@@ -25187,12 +25156,16 @@
         <v>4912.57</v>
       </c>
       <c r="AG39" s="338" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AH39" s="166"/>
       <c r="AJ39" s="19"/>
+      <c r="AL39" s="23">
+        <f>AL38-N38</f>
+        <v>2835</v>
+      </c>
     </row>
-    <row r="40" spans="1:38" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="30">
         <v>24</v>
       </c>
@@ -25219,12 +25192,10 @@
         <f t="shared" si="5"/>
         <v>50419</v>
       </c>
-      <c r="N40" s="210">
-        <v>33629.99</v>
-      </c>
-      <c r="O40" s="210">
-        <v>751</v>
-      </c>
+      <c r="N40" s="273">
+        <v>34380.99</v>
+      </c>
+      <c r="O40" s="210"/>
       <c r="P40" s="209">
         <f t="shared" si="12"/>
         <v>34380.99</v>
@@ -25237,21 +25208,18 @@
         <f t="shared" si="9"/>
         <v>0.70569982963525524</v>
       </c>
-      <c r="S40" s="271">
-        <v>10000</v>
-      </c>
-      <c r="T40" s="177">
-        <f>80+11394</f>
-        <v>11474</v>
-      </c>
-      <c r="U40" s="270">
+      <c r="S40" s="295">
+        <v>2158</v>
+      </c>
+      <c r="T40" s="177"/>
+      <c r="U40" s="268">
         <f t="shared" si="4"/>
-        <v>-1474</v>
-      </c>
-      <c r="V40" s="270" t="s">
-        <v>218</v>
-      </c>
-      <c r="W40" s="270">
+        <v>2158</v>
+      </c>
+      <c r="V40" s="268" t="s">
+        <v>215</v>
+      </c>
+      <c r="W40" s="268">
         <v>11382</v>
       </c>
       <c r="X40" s="33">
@@ -25281,15 +25249,14 @@
         <v>16038.010000000002</v>
       </c>
       <c r="AG40" s="122" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AH40" s="169"/>
       <c r="AL40">
-        <f>154.8+595.5</f>
-        <v>750.3</v>
+        <v>36539</v>
       </c>
     </row>
-    <row r="41" spans="1:38" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="30">
         <v>25</v>
       </c>
@@ -25320,13 +25287,10 @@
         <f t="shared" si="5"/>
         <v>60438</v>
       </c>
-      <c r="N41" s="210">
-        <v>48007.9</v>
-      </c>
-      <c r="O41" s="210">
-        <f>116+75+260.6+20.8+1936</f>
-        <v>2408.4</v>
-      </c>
+      <c r="N41" s="273">
+        <v>50416.3</v>
+      </c>
+      <c r="O41" s="210"/>
       <c r="P41" s="209">
         <f t="shared" si="12"/>
         <v>50416.3</v>
@@ -25339,19 +25303,14 @@
         <f t="shared" si="9"/>
         <v>0.83418213706608435</v>
       </c>
-      <c r="S41" s="271">
-        <v>10000</v>
-      </c>
-      <c r="T41" s="177">
-        <f>10933+300</f>
-        <v>11233</v>
-      </c>
-      <c r="U41" s="270">
+      <c r="S41" s="295"/>
+      <c r="T41" s="177"/>
+      <c r="U41" s="268">
         <f t="shared" si="4"/>
-        <v>-1233</v>
-      </c>
-      <c r="V41" s="270"/>
-      <c r="W41" s="270"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="268"/>
+      <c r="W41" s="268"/>
       <c r="X41" s="33">
         <f t="shared" si="6"/>
         <v>10021.699999999997</v>
@@ -25379,15 +25338,15 @@
         <v>10021.699999999997</v>
       </c>
       <c r="AG41" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH41" s="169"/>
       <c r="AL41" s="18">
-        <f>16055-7000</f>
-        <v>9055</v>
+        <f>AL40-P40</f>
+        <v>2158.010000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:38" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="30">
         <v>26</v>
       </c>
@@ -25416,7 +25375,7 @@
         <f t="shared" si="5"/>
         <v>420</v>
       </c>
-      <c r="N42" s="210">
+      <c r="N42" s="273">
         <v>0</v>
       </c>
       <c r="O42" s="210"/>
@@ -25432,14 +25391,14 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S42" s="271"/>
+      <c r="S42" s="295"/>
       <c r="T42" s="177"/>
-      <c r="U42" s="270">
+      <c r="U42" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V42" s="270"/>
-      <c r="W42" s="270"/>
+      <c r="V42" s="268"/>
+      <c r="W42" s="268"/>
       <c r="X42" s="33">
         <f t="shared" si="6"/>
         <v>420</v>
@@ -25465,18 +25424,19 @@
         <v>420</v>
       </c>
       <c r="AG42" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH42" s="169"/>
       <c r="AI42" s="18">
         <f>AI41-P41</f>
         <v>-50416.3</v>
       </c>
-      <c r="AL42">
-        <v>1473</v>
+      <c r="AL42" s="18">
+        <f>AL41-P41</f>
+        <v>-48258.29</v>
       </c>
     </row>
-    <row r="43" spans="1:38" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="30">
         <v>27</v>
       </c>
@@ -25503,7 +25463,7 @@
         <f t="shared" si="5"/>
         <v>125</v>
       </c>
-      <c r="N43" s="210">
+      <c r="N43" s="273">
         <v>0</v>
       </c>
       <c r="O43" s="210"/>
@@ -25519,14 +25479,14 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S43" s="271"/>
+      <c r="S43" s="295"/>
       <c r="T43" s="177"/>
-      <c r="U43" s="270">
+      <c r="U43" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V43" s="270"/>
-      <c r="W43" s="270"/>
+      <c r="V43" s="268"/>
+      <c r="W43" s="268"/>
       <c r="X43" s="33">
         <f t="shared" si="6"/>
         <v>125</v>
@@ -25552,7 +25512,7 @@
         <v>125</v>
       </c>
       <c r="AG43" s="122" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AH43" s="167"/>
       <c r="AI43" s="18">
@@ -25564,7 +25524,7 @@
         <v>13104</v>
       </c>
     </row>
-    <row r="44" spans="1:38" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="30">
         <v>28</v>
       </c>
@@ -25593,7 +25553,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N44" s="210">
+      <c r="N44" s="273">
         <v>0</v>
       </c>
       <c r="O44" s="210"/>
@@ -25607,14 +25567,14 @@
       <c r="R44" s="63">
         <v>0</v>
       </c>
-      <c r="S44" s="271"/>
+      <c r="S44" s="295"/>
       <c r="T44" s="177"/>
-      <c r="U44" s="270">
+      <c r="U44" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V44" s="270"/>
-      <c r="W44" s="270"/>
+      <c r="V44" s="268"/>
+      <c r="W44" s="268"/>
       <c r="X44" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -25640,7 +25600,7 @@
         <v>0</v>
       </c>
       <c r="AG44" s="339" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH44" s="174" t="s">
         <v>74</v>
@@ -25650,7 +25610,7 @@
         <v>13104</v>
       </c>
     </row>
-    <row r="45" spans="1:38" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="30">
         <v>29</v>
       </c>
@@ -25679,7 +25639,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N45" s="210">
+      <c r="N45" s="273">
         <v>0</v>
       </c>
       <c r="O45" s="210"/>
@@ -25694,14 +25654,14 @@
         <f t="shared" ref="R45:R59" si="13">P45/D45</f>
         <v>0</v>
       </c>
-      <c r="S45" s="271"/>
+      <c r="S45" s="295"/>
       <c r="T45" s="177"/>
-      <c r="U45" s="270">
+      <c r="U45" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V45" s="270"/>
-      <c r="W45" s="270"/>
+      <c r="V45" s="268"/>
+      <c r="W45" s="268"/>
       <c r="X45" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -25727,14 +25687,14 @@
         <v>0</v>
       </c>
       <c r="AG45" s="338" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AH45" s="166"/>
       <c r="AI45">
         <v>24869</v>
       </c>
     </row>
-    <row r="46" spans="1:38" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="30">
         <v>30</v>
       </c>
@@ -25763,7 +25723,7 @@
         <f t="shared" si="5"/>
         <v>191</v>
       </c>
-      <c r="N46" s="210">
+      <c r="N46" s="273">
         <v>0</v>
       </c>
       <c r="O46" s="210"/>
@@ -25779,14 +25739,14 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S46" s="271"/>
+      <c r="S46" s="295"/>
       <c r="T46" s="177"/>
-      <c r="U46" s="270">
+      <c r="U46" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V46" s="270"/>
-      <c r="W46" s="270"/>
+      <c r="V46" s="268"/>
+      <c r="W46" s="268"/>
       <c r="X46" s="33">
         <f t="shared" si="6"/>
         <v>191</v>
@@ -25812,7 +25772,7 @@
         <v>191</v>
       </c>
       <c r="AG46" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH46" s="167"/>
       <c r="AI46" s="19">
@@ -25823,7 +25783,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="47" spans="1:38" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="30">
         <v>31</v>
       </c>
@@ -25850,7 +25810,7 @@
         <f t="shared" si="5"/>
         <v>33</v>
       </c>
-      <c r="N47" s="210">
+      <c r="N47" s="273">
         <v>0</v>
       </c>
       <c r="O47" s="210"/>
@@ -25866,14 +25826,14 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S47" s="271"/>
+      <c r="S47" s="295"/>
       <c r="T47" s="177"/>
-      <c r="U47" s="270">
+      <c r="U47" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V47" s="270"/>
-      <c r="W47" s="270"/>
+      <c r="V47" s="268"/>
+      <c r="W47" s="268"/>
       <c r="X47" s="33">
         <f t="shared" si="6"/>
         <v>33</v>
@@ -25899,14 +25859,14 @@
         <v>33</v>
       </c>
       <c r="AG47" s="122" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH47" s="166"/>
       <c r="AK47">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:38" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="30">
         <v>32</v>
       </c>
@@ -25933,7 +25893,7 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="N48" s="210">
+      <c r="N48" s="273">
         <v>0</v>
       </c>
       <c r="O48" s="210"/>
@@ -25949,14 +25909,14 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S48" s="270"/>
+      <c r="S48" s="294"/>
       <c r="T48" s="177"/>
-      <c r="U48" s="270">
+      <c r="U48" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V48" s="270"/>
-      <c r="W48" s="270"/>
+      <c r="V48" s="268"/>
+      <c r="W48" s="268"/>
       <c r="X48" s="33">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -25982,7 +25942,7 @@
         <v>10</v>
       </c>
       <c r="AG48" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH48" s="166"/>
     </row>
@@ -26013,7 +25973,7 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="N49" s="210">
+      <c r="N49" s="273">
         <v>0</v>
       </c>
       <c r="O49" s="210"/>
@@ -26029,14 +25989,14 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S49" s="270"/>
+      <c r="S49" s="294"/>
       <c r="T49" s="177"/>
-      <c r="U49" s="270">
+      <c r="U49" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V49" s="270"/>
-      <c r="W49" s="270"/>
+      <c r="V49" s="268"/>
+      <c r="W49" s="268"/>
       <c r="X49" s="33">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -26062,7 +26022,7 @@
         <v>10</v>
       </c>
       <c r="AG49" s="122" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AH49" s="166"/>
     </row>
@@ -26093,7 +26053,7 @@
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="N50" s="210">
+      <c r="N50" s="273">
         <v>0</v>
       </c>
       <c r="O50" s="210"/>
@@ -26109,14 +26069,14 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S50" s="270"/>
+      <c r="S50" s="294"/>
       <c r="T50" s="177"/>
-      <c r="U50" s="270">
+      <c r="U50" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V50" s="270"/>
-      <c r="W50" s="270"/>
+      <c r="V50" s="268"/>
+      <c r="W50" s="268"/>
       <c r="X50" s="33">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -26142,7 +26102,7 @@
         <v>20</v>
       </c>
       <c r="AG50" s="338" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AH50" s="166"/>
     </row>
@@ -26173,7 +26133,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="N51" s="210">
+      <c r="N51" s="273">
         <v>0</v>
       </c>
       <c r="O51" s="210"/>
@@ -26189,14 +26149,14 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S51" s="270"/>
+      <c r="S51" s="294"/>
       <c r="T51" s="177"/>
-      <c r="U51" s="270">
+      <c r="U51" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V51" s="270"/>
-      <c r="W51" s="270"/>
+      <c r="V51" s="268"/>
+      <c r="W51" s="268"/>
       <c r="X51" s="33">
         <f t="shared" ref="X51:X74" si="15">M51-P51</f>
         <v>50</v>
@@ -26222,7 +26182,7 @@
         <v>50</v>
       </c>
       <c r="AG51" s="338" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AH51" s="166"/>
     </row>
@@ -26253,7 +26213,7 @@
         <f>SUM(E52:L52)</f>
         <v>50</v>
       </c>
-      <c r="N52" s="210">
+      <c r="N52" s="273">
         <v>0</v>
       </c>
       <c r="O52" s="210"/>
@@ -26269,16 +26229,14 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S52" s="270"/>
-      <c r="T52" s="177">
-        <v>0</v>
-      </c>
-      <c r="U52" s="270">
+      <c r="S52" s="294"/>
+      <c r="T52" s="177"/>
+      <c r="U52" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V52" s="270"/>
-      <c r="W52" s="270"/>
+      <c r="V52" s="268"/>
+      <c r="W52" s="268"/>
       <c r="X52" s="33">
         <f t="shared" si="15"/>
         <v>50</v>
@@ -26304,7 +26262,7 @@
         <v>50</v>
       </c>
       <c r="AG52" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH52" s="171"/>
       <c r="AN52" s="176">
@@ -26339,7 +26297,7 @@
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="N53" s="210">
+      <c r="N53" s="273">
         <v>0</v>
       </c>
       <c r="O53" s="210"/>
@@ -26355,14 +26313,14 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S53" s="270"/>
+      <c r="S53" s="294"/>
       <c r="T53" s="177"/>
-      <c r="U53" s="270">
+      <c r="U53" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V53" s="270"/>
-      <c r="W53" s="270"/>
+      <c r="V53" s="268"/>
+      <c r="W53" s="268"/>
       <c r="X53" s="33">
         <f t="shared" si="15"/>
         <v>15</v>
@@ -26388,7 +26346,7 @@
         <v>15</v>
       </c>
       <c r="AG53" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH53" s="167"/>
       <c r="AN53" s="176">
@@ -26423,7 +26381,7 @@
         <f t="shared" si="5"/>
         <v>33</v>
       </c>
-      <c r="N54" s="210">
+      <c r="N54" s="273">
         <v>0</v>
       </c>
       <c r="O54" s="210"/>
@@ -26439,14 +26397,14 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S54" s="270"/>
+      <c r="S54" s="294"/>
       <c r="T54" s="177"/>
-      <c r="U54" s="270">
+      <c r="U54" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V54" s="270"/>
-      <c r="W54" s="270"/>
+      <c r="V54" s="268"/>
+      <c r="W54" s="268"/>
       <c r="X54" s="33">
         <f t="shared" si="15"/>
         <v>33</v>
@@ -26472,7 +26430,7 @@
         <v>33</v>
       </c>
       <c r="AG54" s="122" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH54" s="167"/>
     </row>
@@ -26503,7 +26461,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="N55" s="210">
+      <c r="N55" s="273">
         <v>0</v>
       </c>
       <c r="O55" s="210"/>
@@ -26519,14 +26477,14 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S55" s="270"/>
+      <c r="S55" s="294"/>
       <c r="T55" s="177"/>
-      <c r="U55" s="270">
+      <c r="U55" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V55" s="270"/>
-      <c r="W55" s="270"/>
+      <c r="V55" s="268"/>
+      <c r="W55" s="268"/>
       <c r="X55" s="33">
         <f t="shared" si="15"/>
         <v>50</v>
@@ -26552,7 +26510,7 @@
         <v>50</v>
       </c>
       <c r="AG55" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH55" s="167"/>
     </row>
@@ -26583,7 +26541,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="N56" s="210">
+      <c r="N56" s="273">
         <v>0</v>
       </c>
       <c r="O56" s="210"/>
@@ -26599,14 +26557,14 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S56" s="270"/>
+      <c r="S56" s="294"/>
       <c r="T56" s="177"/>
-      <c r="U56" s="270">
+      <c r="U56" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V56" s="270"/>
-      <c r="W56" s="270"/>
+      <c r="V56" s="268"/>
+      <c r="W56" s="268"/>
       <c r="X56" s="33">
         <f t="shared" si="15"/>
         <v>50</v>
@@ -26632,7 +26590,7 @@
         <v>50</v>
       </c>
       <c r="AG56" s="338" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AH56" s="167"/>
     </row>
@@ -26663,7 +26621,7 @@
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="N57" s="210">
+      <c r="N57" s="273">
         <v>0</v>
       </c>
       <c r="O57" s="210"/>
@@ -26679,14 +26637,14 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S57" s="270"/>
+      <c r="S57" s="294"/>
       <c r="T57" s="177"/>
-      <c r="U57" s="270">
+      <c r="U57" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V57" s="270"/>
-      <c r="W57" s="270"/>
+      <c r="V57" s="268"/>
+      <c r="W57" s="268"/>
       <c r="X57" s="33">
         <f t="shared" si="15"/>
         <v>6</v>
@@ -26712,7 +26670,7 @@
         <v>6</v>
       </c>
       <c r="AG57" s="122" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AH57" s="167"/>
     </row>
@@ -26743,7 +26701,7 @@
         <f t="shared" si="5"/>
         <v>23</v>
       </c>
-      <c r="N58" s="210">
+      <c r="N58" s="273">
         <v>0</v>
       </c>
       <c r="O58" s="210"/>
@@ -26759,14 +26717,14 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S58" s="270"/>
+      <c r="S58" s="294"/>
       <c r="T58" s="177"/>
-      <c r="U58" s="270">
+      <c r="U58" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V58" s="270"/>
-      <c r="W58" s="270"/>
+      <c r="V58" s="268"/>
+      <c r="W58" s="268"/>
       <c r="X58" s="33">
         <f t="shared" si="15"/>
         <v>23</v>
@@ -26792,7 +26750,7 @@
         <v>23</v>
       </c>
       <c r="AG58" s="122" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH58" s="167"/>
     </row>
@@ -26823,7 +26781,7 @@
         <f t="shared" si="5"/>
         <v>25</v>
       </c>
-      <c r="N59" s="210">
+      <c r="N59" s="273">
         <v>0</v>
       </c>
       <c r="O59" s="210"/>
@@ -26839,14 +26797,14 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S59" s="270"/>
+      <c r="S59" s="294"/>
       <c r="T59" s="177"/>
-      <c r="U59" s="270">
+      <c r="U59" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V59" s="270"/>
-      <c r="W59" s="270"/>
+      <c r="V59" s="268"/>
+      <c r="W59" s="268"/>
       <c r="X59" s="33">
         <f t="shared" si="15"/>
         <v>25</v>
@@ -26872,7 +26830,7 @@
         <v>25</v>
       </c>
       <c r="AG59" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH59" s="167"/>
     </row>
@@ -26903,7 +26861,7 @@
         <f t="shared" si="5"/>
         <v>265</v>
       </c>
-      <c r="N60" s="210">
+      <c r="N60" s="273">
         <v>0</v>
       </c>
       <c r="O60" s="210"/>
@@ -26917,14 +26875,16 @@
       <c r="R60" s="63">
         <v>0</v>
       </c>
-      <c r="S60" s="270"/>
+      <c r="S60" s="294">
+        <v>265</v>
+      </c>
       <c r="T60" s="177"/>
-      <c r="U60" s="270">
+      <c r="U60" s="268">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V60" s="270"/>
-      <c r="W60" s="270">
+        <v>265</v>
+      </c>
+      <c r="V60" s="268"/>
+      <c r="W60" s="268">
         <v>265</v>
       </c>
       <c r="X60" s="33">
@@ -26952,7 +26912,7 @@
         <v>265</v>
       </c>
       <c r="AG60" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH60" s="167"/>
       <c r="AL60">
@@ -26987,69 +26947,70 @@
         <f t="shared" si="5"/>
         <v>61775</v>
       </c>
-      <c r="N61" s="210">
-        <v>33820.960999999996</v>
+      <c r="N61" s="273">
+        <v>33876.160999999993</v>
       </c>
       <c r="O61" s="210"/>
       <c r="P61" s="209">
         <f t="shared" si="12"/>
-        <v>33820.960999999996</v>
+        <v>33876.160999999993</v>
       </c>
       <c r="Q61" s="63">
         <f>P61/M61</f>
-        <v>0.54748621610683923</v>
+        <v>0.54837978146499378</v>
       </c>
       <c r="R61" s="63">
         <f>P61/D61</f>
-        <v>0.54748621610683923</v>
-      </c>
-      <c r="S61" s="270">
-        <v>6000</v>
-      </c>
-      <c r="T61" s="177">
-        <v>5458</v>
-      </c>
-      <c r="U61" s="270">
+        <v>0.54837978146499378</v>
+      </c>
+      <c r="S61" s="294">
+        <v>10000</v>
+      </c>
+      <c r="T61" s="177"/>
+      <c r="U61" s="268">
         <f t="shared" si="4"/>
-        <v>542</v>
-      </c>
-      <c r="V61" s="270"/>
-      <c r="W61" s="270"/>
+        <v>10000</v>
+      </c>
+      <c r="V61" s="268"/>
+      <c r="W61" s="268"/>
       <c r="X61" s="33">
         <f t="shared" si="15"/>
-        <v>27954.039000000004</v>
+        <v>27898.839000000007</v>
       </c>
       <c r="Y61" s="64"/>
       <c r="Z61" s="64"/>
       <c r="AA61" s="41">
         <f t="shared" si="3"/>
-        <v>27954.039000000004</v>
+        <v>27898.839000000007</v>
       </c>
       <c r="AB61" s="65">
         <v>10000</v>
       </c>
       <c r="AC61" s="125">
         <f t="shared" si="7"/>
-        <v>17954.039000000004</v>
+        <v>17898.839000000007</v>
       </c>
       <c r="AD61" s="126">
         <f t="shared" si="10"/>
-        <v>0.70936399838122211</v>
+        <v>0.71025756373937665</v>
       </c>
       <c r="AE61" s="67"/>
       <c r="AF61" s="64">
         <f t="shared" si="11"/>
-        <v>27954.039000000004</v>
+        <v>27898.839000000007</v>
       </c>
       <c r="AG61" s="338" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AH61" s="167"/>
+      <c r="AL61">
+        <v>49420</v>
+      </c>
       <c r="AM61">
         <v>37065</v>
       </c>
     </row>
-    <row r="62" spans="1:40" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:40" ht="60" x14ac:dyDescent="0.25">
       <c r="A62" s="30">
         <v>46</v>
       </c>
@@ -27080,7 +27041,7 @@
         <f t="shared" si="5"/>
         <v>559984</v>
       </c>
-      <c r="N62" s="210">
+      <c r="N62" s="273">
         <v>497783.54</v>
       </c>
       <c r="O62" s="210"/>
@@ -27096,14 +27057,14 @@
         <f>P62/D62</f>
         <v>0.98030568115576699</v>
       </c>
-      <c r="S62" s="270"/>
+      <c r="S62" s="294"/>
       <c r="T62" s="177"/>
-      <c r="U62" s="270">
+      <c r="U62" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V62" s="270"/>
-      <c r="W62" s="270"/>
+      <c r="V62" s="268"/>
+      <c r="W62" s="268"/>
       <c r="X62" s="33">
         <f t="shared" si="15"/>
         <v>62200.460000000021</v>
@@ -27131,7 +27092,7 @@
         <v>62200.460000000021</v>
       </c>
       <c r="AG62" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH62" s="147" t="s">
         <v>152</v>
@@ -27142,9 +27103,13 @@
       <c r="AK62" s="22">
         <v>167340</v>
       </c>
+      <c r="AL62" s="18">
+        <f>507784-P62</f>
+        <v>10000.460000000021</v>
+      </c>
       <c r="AM62" s="18">
         <f>AM61-P61</f>
-        <v>3244.0390000000043</v>
+        <v>3188.8390000000072</v>
       </c>
     </row>
     <row r="63" spans="1:40" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -27168,7 +27133,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N63" s="210">
+      <c r="N63" s="273">
         <v>0</v>
       </c>
       <c r="O63" s="210"/>
@@ -27178,14 +27143,14 @@
       </c>
       <c r="Q63" s="63"/>
       <c r="R63" s="63"/>
-      <c r="S63" s="270"/>
+      <c r="S63" s="294"/>
       <c r="T63" s="114"/>
-      <c r="U63" s="270">
+      <c r="U63" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V63" s="270"/>
-      <c r="W63" s="270"/>
+      <c r="V63" s="268"/>
+      <c r="W63" s="268"/>
       <c r="X63" s="33">
         <f t="shared" si="15"/>
         <v>0</v>
@@ -27215,7 +27180,7 @@
         <v>-330443.53999999998</v>
       </c>
     </row>
-    <row r="64" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="30">
         <v>1</v>
       </c>
@@ -27246,56 +27211,52 @@
         <f t="shared" si="5"/>
         <v>6792</v>
       </c>
-      <c r="N64" s="210">
-        <v>3567</v>
+      <c r="N64" s="273">
+        <v>3576.73</v>
       </c>
       <c r="O64" s="210"/>
       <c r="P64" s="209">
         <f t="shared" si="12"/>
-        <v>3567</v>
+        <v>3576.73</v>
       </c>
       <c r="Q64" s="186">
         <f t="shared" ref="Q64:Q71" si="16">P64/M64</f>
-        <v>0.52517667844522964</v>
+        <v>0.52660924617196703</v>
       </c>
       <c r="R64" s="63">
         <v>0</v>
       </c>
-      <c r="S64" s="270">
-        <v>3000</v>
-      </c>
-      <c r="T64" s="270">
-        <v>3467</v>
-      </c>
-      <c r="U64" s="270">
+      <c r="S64" s="294"/>
+      <c r="T64" s="268"/>
+      <c r="U64" s="268">
         <f t="shared" si="4"/>
-        <v>-467</v>
-      </c>
-      <c r="V64" s="270"/>
-      <c r="W64" s="270"/>
+        <v>0</v>
+      </c>
+      <c r="V64" s="268"/>
+      <c r="W64" s="268"/>
       <c r="X64" s="33">
         <f t="shared" si="15"/>
-        <v>3225</v>
+        <v>3215.27</v>
       </c>
       <c r="Y64" s="64"/>
       <c r="Z64" s="64"/>
       <c r="AA64" s="41">
         <f t="shared" si="3"/>
-        <v>3225</v>
+        <v>3215.27</v>
       </c>
       <c r="AB64" s="65"/>
       <c r="AC64" s="125">
         <f t="shared" si="7"/>
-        <v>3225</v>
+        <v>3215.27</v>
       </c>
       <c r="AD64" s="126">
         <f>(P64+AB64)/M64</f>
-        <v>0.52517667844522964</v>
+        <v>0.52660924617196703</v>
       </c>
       <c r="AE64" s="67"/>
       <c r="AF64" s="67"/>
       <c r="AG64" s="173" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AH64" s="173"/>
       <c r="AK64" s="24">
@@ -27334,7 +27295,7 @@
         <f t="shared" si="5"/>
         <v>4100</v>
       </c>
-      <c r="N65" s="210">
+      <c r="N65" s="273">
         <v>3484</v>
       </c>
       <c r="O65" s="210"/>
@@ -27349,19 +27310,16 @@
       <c r="R65" s="63">
         <v>0</v>
       </c>
-      <c r="S65" s="270">
-        <f>423+37</f>
-        <v>460</v>
-      </c>
-      <c r="T65" s="270">
-        <v>3384</v>
-      </c>
-      <c r="U65" s="270">
+      <c r="S65" s="294">
+        <v>1316</v>
+      </c>
+      <c r="T65" s="268"/>
+      <c r="U65" s="268">
         <f t="shared" si="4"/>
-        <v>-2924</v>
-      </c>
-      <c r="V65" s="270"/>
-      <c r="W65" s="270"/>
+        <v>1316</v>
+      </c>
+      <c r="V65" s="268"/>
+      <c r="W65" s="268"/>
       <c r="X65" s="33">
         <f t="shared" si="15"/>
         <v>616</v>
@@ -27384,9 +27342,12 @@
       <c r="AE65" s="67"/>
       <c r="AF65" s="67"/>
       <c r="AG65" s="173" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH65" s="173"/>
+      <c r="AL65">
+        <v>4800</v>
+      </c>
     </row>
     <row r="66" spans="1:38" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="30">
@@ -27419,7 +27380,7 @@
         <f t="shared" si="5"/>
         <v>10200</v>
       </c>
-      <c r="N66" s="210">
+      <c r="N66" s="273">
         <v>574.29999999999995</v>
       </c>
       <c r="O66" s="210"/>
@@ -27434,19 +27395,16 @@
       <c r="R66" s="63">
         <v>0</v>
       </c>
-      <c r="S66" s="270">
-        <f>448+26</f>
-        <v>474</v>
-      </c>
-      <c r="T66" s="270">
-        <v>474</v>
-      </c>
-      <c r="U66" s="270">
+      <c r="S66" s="294">
+        <v>5426</v>
+      </c>
+      <c r="T66" s="268"/>
+      <c r="U66" s="268">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V66" s="270"/>
-      <c r="W66" s="270"/>
+        <v>5426</v>
+      </c>
+      <c r="V66" s="268"/>
+      <c r="W66" s="268"/>
       <c r="X66" s="33">
         <f t="shared" si="15"/>
         <v>9625.7000000000007</v>
@@ -27469,9 +27427,13 @@
       <c r="AE66" s="64"/>
       <c r="AF66" s="64"/>
       <c r="AG66" s="173" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH66" s="173"/>
+      <c r="AL66" s="18">
+        <f>6000-P66</f>
+        <v>5425.7</v>
+      </c>
     </row>
     <row r="67" spans="1:38" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="30">
@@ -27507,7 +27469,7 @@
         <f t="shared" si="5"/>
         <v>12500</v>
       </c>
-      <c r="N67" s="210">
+      <c r="N67" s="273">
         <v>684</v>
       </c>
       <c r="O67" s="210"/>
@@ -27522,16 +27484,14 @@
       <c r="R67" s="63">
         <v>0</v>
       </c>
-      <c r="S67" s="270"/>
-      <c r="T67" s="270">
-        <v>584</v>
-      </c>
-      <c r="U67" s="270">
+      <c r="S67" s="294"/>
+      <c r="T67" s="268"/>
+      <c r="U67" s="268">
         <f t="shared" si="4"/>
-        <v>-584</v>
-      </c>
-      <c r="V67" s="270"/>
-      <c r="W67" s="270"/>
+        <v>0</v>
+      </c>
+      <c r="V67" s="268"/>
+      <c r="W67" s="268"/>
       <c r="X67" s="33">
         <f t="shared" si="15"/>
         <v>11816</v>
@@ -27554,7 +27514,7 @@
       <c r="AE67" s="67"/>
       <c r="AF67" s="67"/>
       <c r="AG67" s="338" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AH67" s="173"/>
     </row>
@@ -27581,7 +27541,7 @@
       </c>
       <c r="I68" s="179"/>
       <c r="J68" s="179"/>
-      <c r="K68" s="272">
+      <c r="K68" s="269">
         <v>4250</v>
       </c>
       <c r="L68" s="179"/>
@@ -27589,36 +27549,32 @@
         <f t="shared" si="5"/>
         <v>4600</v>
       </c>
-      <c r="N68" s="210">
-        <v>2100.6</v>
+      <c r="N68" s="273">
+        <v>2114.1</v>
       </c>
       <c r="O68" s="211"/>
       <c r="P68" s="209">
         <f t="shared" si="12"/>
-        <v>2100.6</v>
+        <v>2114.1</v>
       </c>
       <c r="Q68" s="187">
         <f t="shared" si="16"/>
-        <v>0.45665217391304347</v>
+        <v>0.45958695652173909</v>
       </c>
       <c r="R68" s="63">
         <v>0</v>
       </c>
-      <c r="S68" s="270">
-        <v>320</v>
-      </c>
-      <c r="T68" s="270">
-        <v>2001</v>
-      </c>
-      <c r="U68" s="270">
+      <c r="S68" s="294"/>
+      <c r="T68" s="268"/>
+      <c r="U68" s="268">
         <f t="shared" si="4"/>
-        <v>-1681</v>
-      </c>
-      <c r="V68" s="270"/>
-      <c r="W68" s="270"/>
+        <v>0</v>
+      </c>
+      <c r="V68" s="268"/>
+      <c r="W68" s="268"/>
       <c r="X68" s="33">
         <f t="shared" si="15"/>
-        <v>2499.4</v>
+        <v>2485.9</v>
       </c>
       <c r="Y68" s="179"/>
       <c r="Z68" s="179"/>
@@ -27626,21 +27582,21 @@
       <c r="AB68" s="179"/>
       <c r="AC68" s="179">
         <f t="shared" si="7"/>
-        <v>2499.4</v>
+        <v>2485.9</v>
       </c>
       <c r="AD68" s="179">
         <f>(P68+AB68)/M68</f>
-        <v>0.45665217391304347</v>
+        <v>0.45958695652173909</v>
       </c>
       <c r="AE68" s="179"/>
       <c r="AF68" s="179"/>
       <c r="AG68" s="173" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AH68" s="173"/>
       <c r="AL68">
         <f>470-P68</f>
-        <v>-1630.6</v>
+        <v>-1644.1</v>
       </c>
     </row>
     <row r="69" spans="1:38" ht="135.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -27666,7 +27622,7 @@
       </c>
       <c r="I69" s="181"/>
       <c r="J69" s="181"/>
-      <c r="K69" s="273">
+      <c r="K69" s="270">
         <v>10700</v>
       </c>
       <c r="L69" s="181"/>
@@ -27674,7 +27630,7 @@
         <f t="shared" si="5"/>
         <v>11400</v>
       </c>
-      <c r="N69" s="210">
+      <c r="N69" s="273">
         <v>5777.4</v>
       </c>
       <c r="O69" s="212"/>
@@ -27689,18 +27645,14 @@
       <c r="R69" s="198">
         <v>0</v>
       </c>
-      <c r="S69" s="270">
-        <v>4500</v>
-      </c>
-      <c r="T69" s="270">
-        <v>5677</v>
-      </c>
-      <c r="U69" s="270">
+      <c r="S69" s="294"/>
+      <c r="T69" s="268"/>
+      <c r="U69" s="268">
         <f t="shared" si="4"/>
-        <v>-1177</v>
-      </c>
-      <c r="V69" s="270"/>
-      <c r="W69" s="270"/>
+        <v>0</v>
+      </c>
+      <c r="V69" s="268"/>
+      <c r="W69" s="268"/>
       <c r="X69" s="33">
         <f t="shared" si="15"/>
         <v>5622.6</v>
@@ -27714,7 +27666,7 @@
       <c r="AE69" s="179"/>
       <c r="AF69" s="179"/>
       <c r="AG69" s="339" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH69" s="200"/>
     </row>
@@ -27741,7 +27693,7 @@
       </c>
       <c r="I70" s="182"/>
       <c r="J70" s="182"/>
-      <c r="K70" s="274">
+      <c r="K70" s="271">
         <v>10267</v>
       </c>
       <c r="L70" s="182"/>
@@ -27749,7 +27701,7 @@
         <f t="shared" si="5"/>
         <v>10967</v>
       </c>
-      <c r="N70" s="210">
+      <c r="N70" s="273">
         <v>5391</v>
       </c>
       <c r="O70" s="211"/>
@@ -27764,18 +27716,14 @@
       <c r="R70" s="63">
         <v>0</v>
       </c>
-      <c r="S70" s="270">
-        <v>4300</v>
-      </c>
-      <c r="T70" s="270">
-        <v>5291</v>
-      </c>
-      <c r="U70" s="270">
+      <c r="S70" s="294"/>
+      <c r="T70" s="268"/>
+      <c r="U70" s="268">
         <f t="shared" si="4"/>
-        <v>-991</v>
-      </c>
-      <c r="V70" s="270"/>
-      <c r="W70" s="270"/>
+        <v>0</v>
+      </c>
+      <c r="V70" s="268"/>
+      <c r="W70" s="268"/>
       <c r="X70" s="33">
         <f t="shared" si="15"/>
         <v>5576</v>
@@ -27789,7 +27737,7 @@
       <c r="AE70" s="184"/>
       <c r="AF70" s="184"/>
       <c r="AG70" s="339" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH70" s="173"/>
     </row>
@@ -27816,7 +27764,7 @@
       </c>
       <c r="I71" s="181"/>
       <c r="J71" s="181"/>
-      <c r="K71" s="274">
+      <c r="K71" s="271">
         <v>6523</v>
       </c>
       <c r="L71" s="181"/>
@@ -27824,7 +27772,7 @@
         <f t="shared" si="5"/>
         <v>7073</v>
       </c>
-      <c r="N71" s="210">
+      <c r="N71" s="273">
         <v>3951</v>
       </c>
       <c r="O71" s="213"/>
@@ -27839,18 +27787,14 @@
       <c r="R71" s="63">
         <v>0</v>
       </c>
-      <c r="S71" s="270">
-        <v>3951</v>
-      </c>
-      <c r="T71" s="270">
-        <v>3951</v>
-      </c>
-      <c r="U71" s="270">
+      <c r="S71" s="294"/>
+      <c r="T71" s="268"/>
+      <c r="U71" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V71" s="270"/>
-      <c r="W71" s="270"/>
+      <c r="V71" s="268"/>
+      <c r="W71" s="268"/>
       <c r="X71" s="33">
         <f t="shared" si="15"/>
         <v>3122</v>
@@ -27864,7 +27808,7 @@
       <c r="AE71" s="179"/>
       <c r="AF71" s="179"/>
       <c r="AG71" s="173" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AH71" s="173"/>
     </row>
@@ -27889,30 +27833,30 @@
       </c>
       <c r="I72" s="258"/>
       <c r="J72" s="258"/>
-      <c r="K72" s="275"/>
+      <c r="K72" s="272"/>
       <c r="L72" s="258"/>
       <c r="M72" s="32">
         <f t="shared" si="5"/>
         <v>600</v>
       </c>
-      <c r="N72" s="259">
-        <v>0</v>
-      </c>
-      <c r="O72" s="260"/>
+      <c r="N72" s="290">
+        <v>0</v>
+      </c>
+      <c r="O72" s="259"/>
       <c r="P72" s="209">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Q72" s="261"/>
+      <c r="Q72" s="260"/>
       <c r="R72" s="63"/>
-      <c r="S72" s="270"/>
-      <c r="T72" s="270"/>
-      <c r="U72" s="270">
+      <c r="S72" s="294"/>
+      <c r="T72" s="268"/>
+      <c r="U72" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V72" s="270"/>
-      <c r="W72" s="270"/>
+      <c r="V72" s="268"/>
+      <c r="W72" s="268"/>
       <c r="X72" s="33">
         <f t="shared" si="15"/>
         <v>600</v>
@@ -27926,7 +27870,7 @@
       <c r="AE72" s="256"/>
       <c r="AF72" s="256"/>
       <c r="AG72" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH72" s="173"/>
     </row>
@@ -27951,30 +27895,30 @@
       </c>
       <c r="I73" s="258"/>
       <c r="J73" s="258"/>
-      <c r="K73" s="275"/>
+      <c r="K73" s="272"/>
       <c r="L73" s="258"/>
       <c r="M73" s="32">
         <f t="shared" si="5"/>
         <v>800</v>
       </c>
-      <c r="N73" s="259">
-        <v>0</v>
-      </c>
-      <c r="O73" s="260"/>
+      <c r="N73" s="290">
+        <v>0</v>
+      </c>
+      <c r="O73" s="259"/>
       <c r="P73" s="209">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Q73" s="261"/>
+      <c r="Q73" s="260"/>
       <c r="R73" s="63"/>
-      <c r="S73" s="270"/>
-      <c r="T73" s="270"/>
-      <c r="U73" s="270">
+      <c r="S73" s="294"/>
+      <c r="T73" s="268"/>
+      <c r="U73" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V73" s="270"/>
-      <c r="W73" s="270"/>
+      <c r="V73" s="268"/>
+      <c r="W73" s="268"/>
       <c r="X73" s="33">
         <f t="shared" si="15"/>
         <v>800</v>
@@ -27988,7 +27932,7 @@
       <c r="AE73" s="256"/>
       <c r="AF73" s="256"/>
       <c r="AG73" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH73" s="173"/>
     </row>
@@ -28013,30 +27957,30 @@
       </c>
       <c r="I74" s="258"/>
       <c r="J74" s="258"/>
-      <c r="K74" s="275"/>
+      <c r="K74" s="272"/>
       <c r="L74" s="258"/>
       <c r="M74" s="32">
         <f t="shared" si="5"/>
         <v>1000</v>
       </c>
-      <c r="N74" s="259">
-        <v>0</v>
-      </c>
-      <c r="O74" s="260"/>
+      <c r="N74" s="290">
+        <v>0</v>
+      </c>
+      <c r="O74" s="259"/>
       <c r="P74" s="209">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Q74" s="261"/>
+      <c r="Q74" s="260"/>
       <c r="R74" s="63"/>
-      <c r="S74" s="270"/>
-      <c r="T74" s="270"/>
-      <c r="U74" s="270">
+      <c r="S74" s="294"/>
+      <c r="T74" s="268"/>
+      <c r="U74" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V74" s="270"/>
-      <c r="W74" s="270"/>
+      <c r="V74" s="268"/>
+      <c r="W74" s="268"/>
       <c r="X74" s="33">
         <f t="shared" si="15"/>
         <v>1000</v>
@@ -28050,7 +27994,7 @@
       <c r="AE74" s="256"/>
       <c r="AF74" s="256"/>
       <c r="AG74" s="340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AH74" s="173"/>
     </row>
@@ -28059,10 +28003,10 @@
         <v>12</v>
       </c>
       <c r="B75" s="254" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C75" s="255" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D75" s="59"/>
       <c r="E75" s="257"/>
@@ -28071,24 +28015,24 @@
       <c r="H75" s="35"/>
       <c r="I75" s="258"/>
       <c r="J75" s="258"/>
-      <c r="K75" s="275"/>
-      <c r="L75" s="294">
+      <c r="K75" s="272"/>
+      <c r="L75" s="287">
         <v>26900</v>
       </c>
       <c r="M75" s="32">
         <f t="shared" si="5"/>
         <v>26900</v>
       </c>
-      <c r="N75" s="259"/>
-      <c r="O75" s="260"/>
+      <c r="N75" s="290"/>
+      <c r="O75" s="259"/>
       <c r="P75" s="209"/>
-      <c r="Q75" s="261"/>
+      <c r="Q75" s="260"/>
       <c r="R75" s="63"/>
-      <c r="S75" s="270"/>
-      <c r="T75" s="270"/>
-      <c r="U75" s="270"/>
-      <c r="V75" s="270"/>
-      <c r="W75" s="270"/>
+      <c r="S75" s="294"/>
+      <c r="T75" s="268"/>
+      <c r="U75" s="268"/>
+      <c r="V75" s="268"/>
+      <c r="W75" s="268"/>
       <c r="X75" s="33"/>
       <c r="Y75" s="256"/>
       <c r="Z75" s="256"/>
@@ -28106,9 +28050,11 @@
         <v>13</v>
       </c>
       <c r="B76" s="254" t="s">
-        <v>226</v>
-      </c>
-      <c r="C76" s="255"/>
+        <v>223</v>
+      </c>
+      <c r="C76" s="255" t="s">
+        <v>228</v>
+      </c>
       <c r="D76" s="59"/>
       <c r="E76" s="257"/>
       <c r="F76" s="35"/>
@@ -28116,24 +28062,24 @@
       <c r="H76" s="35"/>
       <c r="I76" s="258"/>
       <c r="J76" s="258"/>
-      <c r="K76" s="275"/>
-      <c r="L76" s="294">
+      <c r="K76" s="272"/>
+      <c r="L76" s="287">
         <v>20000</v>
       </c>
       <c r="M76" s="32">
         <f t="shared" si="5"/>
         <v>20000</v>
       </c>
-      <c r="N76" s="259"/>
-      <c r="O76" s="260"/>
+      <c r="N76" s="290"/>
+      <c r="O76" s="259"/>
       <c r="P76" s="209"/>
-      <c r="Q76" s="261"/>
+      <c r="Q76" s="260"/>
       <c r="R76" s="63"/>
-      <c r="S76" s="270"/>
-      <c r="T76" s="270"/>
-      <c r="U76" s="270"/>
-      <c r="V76" s="270"/>
-      <c r="W76" s="270"/>
+      <c r="S76" s="294"/>
+      <c r="T76" s="268"/>
+      <c r="U76" s="268"/>
+      <c r="V76" s="268"/>
+      <c r="W76" s="268"/>
       <c r="X76" s="33"/>
       <c r="Y76" s="256"/>
       <c r="Z76" s="256"/>
@@ -28150,7 +28096,7 @@
       <c r="A77" s="179"/>
       <c r="B77" s="251"/>
       <c r="C77" s="226"/>
-      <c r="D77" s="267"/>
+      <c r="D77" s="265"/>
       <c r="E77" s="179"/>
       <c r="F77" s="179"/>
       <c r="G77" s="179"/>
@@ -28168,7 +28114,7 @@
       <c r="P77" s="213"/>
       <c r="Q77" s="179"/>
       <c r="R77" s="179"/>
-      <c r="S77" s="264"/>
+      <c r="S77" s="296"/>
       <c r="T77" s="256"/>
       <c r="U77" s="256"/>
       <c r="V77" s="256"/>
@@ -29101,13 +29047,17 @@
     <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A10:AK74" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A10:AK77" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="30">
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="S7:U8"/>
-    <mergeCell ref="V7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AC9"/>
+    <mergeCell ref="AD7:AD9"/>
+    <mergeCell ref="AF7:AF9"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A4:AH4"/>
@@ -29124,15 +29074,11 @@
     <mergeCell ref="P7:P9"/>
     <mergeCell ref="Q7:Q9"/>
     <mergeCell ref="R7:R9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AC9"/>
-    <mergeCell ref="AD7:AD9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="S7:U8"/>
+    <mergeCell ref="V7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="AE7:AE9"/>
   </mergeCells>
   <pageMargins left="0.55000000000000004" right="0.15748031496062992" top="0.39370078740157483" bottom="0.23622047244094491" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" r:id="rId1"/>

--- a/report/bao-cao.xlsx
+++ b/report/bao-cao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HXuan\BaocaoGiaingan\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72CDCCF-E769-4CB6-AED7-BC6811B5E1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CC5902-6939-4B8E-A8F7-86369AD55D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,17 +16,17 @@
     <sheet name="bc" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="BAO CAO 30-06 (2)" sheetId="3" state="hidden" r:id="rId2"/>
     <sheet name="BAO CAO 30-06 (KHV mới)" sheetId="4" state="hidden" r:id="rId3"/>
-    <sheet name="BAO CAO 01-10-2026" sheetId="5" r:id="rId4"/>
+    <sheet name="BAO CAO 12-10-2026" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BAO CAO 01-10-2026'!$A$10:$AK$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BAO CAO 12-10-2026'!$A$10:$AK$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BAO CAO 30-06 (2)'!$A$10:$AQ$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BAO CAO 30-06 (KHV mới)'!$A$10:$AQ$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">bc!$A$10:$AP$80</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'BAO CAO 01-10-2026'!$A$1:$AH$77</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'BAO CAO 12-10-2026'!$A$1:$AH$77</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'BAO CAO 30-06 (2)'!$A$1:$AN$58</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'BAO CAO 30-06 (KHV mới)'!$A$1:$AN$79</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'BAO CAO 01-10-2026'!$7:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'BAO CAO 12-10-2026'!$7:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'BAO CAO 30-06 (2)'!$7:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'BAO CAO 30-06 (KHV mới)'!$7:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">bc!$7:$9</definedName>
@@ -707,9 +707,6 @@
     <t>QĐ 5545 ngày 25/08/2028</t>
   </si>
   <si>
-    <t>Số còn chi trong tháng 09/2026</t>
-  </si>
-  <si>
     <t>Hồ sơ A/C KT gửi thanh toán</t>
   </si>
   <si>
@@ -746,10 +743,6 @@
     <t>Dự án Bồi thường giải phóng mặt bằng để thực hiện dự án Xây dựng cầu sắt Bình Lợi trên địa bàn Quận Bình Thạnh</t>
   </si>
   <si>
-    <t>Số giải ngân
-trong tuần (từ ngày 01/10/2026 đến 04/10/2026</t>
-  </si>
-  <si>
     <t>Ước chi tháng 10/2026</t>
   </si>
   <si>
@@ -760,12 +753,6 @@
   </si>
   <si>
     <t>7507257</t>
-  </si>
-  <si>
-    <t>(Tính đến ngày 06/10/2026)</t>
-  </si>
-  <si>
-    <t>TỔNG SỐ GIẢI NGÂN ĐẾN NGÀY BÁO CÁO NGÀY 06/10/2026</t>
   </si>
   <si>
     <t>Cán bộ Kỹ thuật</t>
@@ -790,6 +777,19 @@
   </si>
   <si>
     <t>Nguyễn Phi Hoàng</t>
+  </si>
+  <si>
+    <t>(Tính đến ngày 12/10/2026)</t>
+  </si>
+  <si>
+    <t>Số giải ngân
+trong tuần (từ ngày 06/10/2026 đến 12/10/2026</t>
+  </si>
+  <si>
+    <t>TỔNG SỐ GIẢI NGÂN ĐẾN NGÀY BÁO CÁO NGÀY 12/10/2026</t>
+  </si>
+  <si>
+    <t>Số còn chi trong tháng 10/2026</t>
   </si>
 </sst>
 </file>
@@ -2429,25 +2429,36 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="1" fontId="47" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="54" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="167" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="77" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2463,10 +2474,12 @@
     <xf numFmtId="0" fontId="59" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="59" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2506,27 +2519,32 @@
     <xf numFmtId="167" fontId="63" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2537,24 +2555,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="47" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2808,36 +2808,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="329" t="s">
+      <c r="A1" s="338" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="305"/>
-      <c r="C1" s="306"/>
-      <c r="D1" s="305"/>
-      <c r="E1" s="305"/>
-      <c r="F1" s="305"/>
-      <c r="G1" s="305"/>
-      <c r="H1" s="305"/>
-      <c r="I1" s="305"/>
-      <c r="J1" s="305"/>
-      <c r="K1" s="305"/>
-      <c r="L1" s="305"/>
-      <c r="M1" s="305"/>
-      <c r="N1" s="305"/>
-      <c r="O1" s="305"/>
-      <c r="P1" s="305"/>
-      <c r="Q1" s="305"/>
-      <c r="R1" s="305"/>
-      <c r="S1" s="305"/>
-      <c r="T1" s="305"/>
-      <c r="U1" s="305"/>
-      <c r="V1" s="305"/>
-      <c r="W1" s="305"/>
-      <c r="X1" s="305"/>
-      <c r="Y1" s="305"/>
-      <c r="Z1" s="305"/>
-      <c r="AA1" s="305"/>
-      <c r="AB1" s="307"/>
+      <c r="B1" s="310"/>
+      <c r="C1" s="311"/>
+      <c r="D1" s="310"/>
+      <c r="E1" s="310"/>
+      <c r="F1" s="310"/>
+      <c r="G1" s="310"/>
+      <c r="H1" s="310"/>
+      <c r="I1" s="310"/>
+      <c r="J1" s="310"/>
+      <c r="K1" s="310"/>
+      <c r="L1" s="310"/>
+      <c r="M1" s="310"/>
+      <c r="N1" s="310"/>
+      <c r="O1" s="310"/>
+      <c r="P1" s="310"/>
+      <c r="Q1" s="310"/>
+      <c r="R1" s="310"/>
+      <c r="S1" s="310"/>
+      <c r="T1" s="310"/>
+      <c r="U1" s="310"/>
+      <c r="V1" s="310"/>
+      <c r="W1" s="310"/>
+      <c r="X1" s="310"/>
+      <c r="Y1" s="310"/>
+      <c r="Z1" s="310"/>
+      <c r="AA1" s="310"/>
+      <c r="AB1" s="312"/>
       <c r="AC1" s="17"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="2"/>
@@ -2853,36 +2853,36 @@
       <c r="AM1" s="3"/>
     </row>
     <row r="2" spans="1:42" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="308" t="s">
+      <c r="A2" s="313" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="305"/>
-      <c r="C2" s="306"/>
-      <c r="D2" s="305"/>
-      <c r="E2" s="305"/>
-      <c r="F2" s="305"/>
-      <c r="G2" s="305"/>
-      <c r="H2" s="305"/>
-      <c r="I2" s="305"/>
-      <c r="J2" s="305"/>
-      <c r="K2" s="305"/>
-      <c r="L2" s="305"/>
-      <c r="M2" s="305"/>
-      <c r="N2" s="305"/>
-      <c r="O2" s="305"/>
-      <c r="P2" s="305"/>
-      <c r="Q2" s="305"/>
-      <c r="R2" s="305"/>
-      <c r="S2" s="305"/>
-      <c r="T2" s="305"/>
-      <c r="U2" s="305"/>
-      <c r="V2" s="305"/>
-      <c r="W2" s="305"/>
-      <c r="X2" s="305"/>
-      <c r="Y2" s="305"/>
-      <c r="Z2" s="305"/>
-      <c r="AA2" s="305"/>
-      <c r="AB2" s="307"/>
+      <c r="B2" s="310"/>
+      <c r="C2" s="311"/>
+      <c r="D2" s="310"/>
+      <c r="E2" s="310"/>
+      <c r="F2" s="310"/>
+      <c r="G2" s="310"/>
+      <c r="H2" s="310"/>
+      <c r="I2" s="310"/>
+      <c r="J2" s="310"/>
+      <c r="K2" s="310"/>
+      <c r="L2" s="310"/>
+      <c r="M2" s="310"/>
+      <c r="N2" s="310"/>
+      <c r="O2" s="310"/>
+      <c r="P2" s="310"/>
+      <c r="Q2" s="310"/>
+      <c r="R2" s="310"/>
+      <c r="S2" s="310"/>
+      <c r="T2" s="310"/>
+      <c r="U2" s="310"/>
+      <c r="V2" s="310"/>
+      <c r="W2" s="310"/>
+      <c r="X2" s="310"/>
+      <c r="Y2" s="310"/>
+      <c r="Z2" s="310"/>
+      <c r="AA2" s="310"/>
+      <c r="AB2" s="312"/>
       <c r="AC2" s="17"/>
       <c r="AD2" s="1"/>
       <c r="AE2" s="2"/>
@@ -2937,90 +2937,90 @@
       <c r="AM3" s="3"/>
     </row>
     <row r="4" spans="1:42" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="309" t="s">
+      <c r="A4" s="314" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="305"/>
-      <c r="C4" s="306"/>
-      <c r="D4" s="305"/>
-      <c r="E4" s="305"/>
-      <c r="F4" s="305"/>
-      <c r="G4" s="305"/>
-      <c r="H4" s="305"/>
-      <c r="I4" s="305"/>
-      <c r="J4" s="305"/>
-      <c r="K4" s="305"/>
-      <c r="L4" s="305"/>
-      <c r="M4" s="305"/>
-      <c r="N4" s="305"/>
-      <c r="O4" s="305"/>
-      <c r="P4" s="305"/>
-      <c r="Q4" s="305"/>
-      <c r="R4" s="305"/>
-      <c r="S4" s="305"/>
-      <c r="T4" s="305"/>
-      <c r="U4" s="305"/>
-      <c r="V4" s="305"/>
-      <c r="W4" s="305"/>
-      <c r="X4" s="305"/>
-      <c r="Y4" s="305"/>
-      <c r="Z4" s="305"/>
-      <c r="AA4" s="305"/>
-      <c r="AB4" s="305"/>
-      <c r="AC4" s="306"/>
-      <c r="AD4" s="305"/>
-      <c r="AE4" s="305"/>
-      <c r="AF4" s="306"/>
-      <c r="AG4" s="306"/>
-      <c r="AH4" s="305"/>
-      <c r="AI4" s="306"/>
-      <c r="AJ4" s="306"/>
-      <c r="AK4" s="305"/>
-      <c r="AL4" s="306"/>
-      <c r="AM4" s="307"/>
+      <c r="B4" s="310"/>
+      <c r="C4" s="311"/>
+      <c r="D4" s="310"/>
+      <c r="E4" s="310"/>
+      <c r="F4" s="310"/>
+      <c r="G4" s="310"/>
+      <c r="H4" s="310"/>
+      <c r="I4" s="310"/>
+      <c r="J4" s="310"/>
+      <c r="K4" s="310"/>
+      <c r="L4" s="310"/>
+      <c r="M4" s="310"/>
+      <c r="N4" s="310"/>
+      <c r="O4" s="310"/>
+      <c r="P4" s="310"/>
+      <c r="Q4" s="310"/>
+      <c r="R4" s="310"/>
+      <c r="S4" s="310"/>
+      <c r="T4" s="310"/>
+      <c r="U4" s="310"/>
+      <c r="V4" s="310"/>
+      <c r="W4" s="310"/>
+      <c r="X4" s="310"/>
+      <c r="Y4" s="310"/>
+      <c r="Z4" s="310"/>
+      <c r="AA4" s="310"/>
+      <c r="AB4" s="310"/>
+      <c r="AC4" s="311"/>
+      <c r="AD4" s="310"/>
+      <c r="AE4" s="310"/>
+      <c r="AF4" s="311"/>
+      <c r="AG4" s="311"/>
+      <c r="AH4" s="310"/>
+      <c r="AI4" s="311"/>
+      <c r="AJ4" s="311"/>
+      <c r="AK4" s="310"/>
+      <c r="AL4" s="311"/>
+      <c r="AM4" s="312"/>
     </row>
     <row r="5" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="310" t="s">
+      <c r="A5" s="315" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="305"/>
-      <c r="C5" s="306"/>
-      <c r="D5" s="305"/>
-      <c r="E5" s="305"/>
-      <c r="F5" s="305"/>
-      <c r="G5" s="305"/>
-      <c r="H5" s="305"/>
-      <c r="I5" s="305"/>
-      <c r="J5" s="305"/>
-      <c r="K5" s="305"/>
-      <c r="L5" s="305"/>
-      <c r="M5" s="305"/>
-      <c r="N5" s="305"/>
-      <c r="O5" s="305"/>
-      <c r="P5" s="305"/>
-      <c r="Q5" s="305"/>
-      <c r="R5" s="305"/>
-      <c r="S5" s="305"/>
-      <c r="T5" s="305"/>
-      <c r="U5" s="305"/>
-      <c r="V5" s="305"/>
-      <c r="W5" s="305"/>
-      <c r="X5" s="305"/>
-      <c r="Y5" s="305"/>
-      <c r="Z5" s="305"/>
-      <c r="AA5" s="305"/>
-      <c r="AB5" s="305"/>
-      <c r="AC5" s="306"/>
-      <c r="AD5" s="305"/>
-      <c r="AE5" s="305"/>
-      <c r="AF5" s="306"/>
-      <c r="AG5" s="306"/>
-      <c r="AH5" s="305"/>
-      <c r="AI5" s="306"/>
-      <c r="AJ5" s="306"/>
-      <c r="AK5" s="305"/>
-      <c r="AL5" s="306"/>
-      <c r="AM5" s="307"/>
+      <c r="B5" s="310"/>
+      <c r="C5" s="311"/>
+      <c r="D5" s="310"/>
+      <c r="E5" s="310"/>
+      <c r="F5" s="310"/>
+      <c r="G5" s="310"/>
+      <c r="H5" s="310"/>
+      <c r="I5" s="310"/>
+      <c r="J5" s="310"/>
+      <c r="K5" s="310"/>
+      <c r="L5" s="310"/>
+      <c r="M5" s="310"/>
+      <c r="N5" s="310"/>
+      <c r="O5" s="310"/>
+      <c r="P5" s="310"/>
+      <c r="Q5" s="310"/>
+      <c r="R5" s="310"/>
+      <c r="S5" s="310"/>
+      <c r="T5" s="310"/>
+      <c r="U5" s="310"/>
+      <c r="V5" s="310"/>
+      <c r="W5" s="310"/>
+      <c r="X5" s="310"/>
+      <c r="Y5" s="310"/>
+      <c r="Z5" s="310"/>
+      <c r="AA5" s="310"/>
+      <c r="AB5" s="310"/>
+      <c r="AC5" s="311"/>
+      <c r="AD5" s="310"/>
+      <c r="AE5" s="310"/>
+      <c r="AF5" s="311"/>
+      <c r="AG5" s="311"/>
+      <c r="AH5" s="310"/>
+      <c r="AI5" s="311"/>
+      <c r="AJ5" s="311"/>
+      <c r="AK5" s="310"/>
+      <c r="AL5" s="311"/>
+      <c r="AM5" s="312"/>
     </row>
     <row r="6" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -3054,203 +3054,203 @@
       <c r="AA6" s="16"/>
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
-      <c r="AD6" s="331"/>
-      <c r="AE6" s="306"/>
-      <c r="AF6" s="306"/>
-      <c r="AG6" s="306"/>
-      <c r="AH6" s="306"/>
-      <c r="AI6" s="306"/>
-      <c r="AJ6" s="306"/>
-      <c r="AK6" s="306"/>
-      <c r="AL6" s="306"/>
-      <c r="AM6" s="306"/>
+      <c r="AD6" s="339"/>
+      <c r="AE6" s="311"/>
+      <c r="AF6" s="311"/>
+      <c r="AG6" s="311"/>
+      <c r="AH6" s="311"/>
+      <c r="AI6" s="311"/>
+      <c r="AJ6" s="311"/>
+      <c r="AK6" s="311"/>
+      <c r="AL6" s="311"/>
+      <c r="AM6" s="311"/>
     </row>
     <row r="7" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="303" t="s">
+      <c r="A7" s="302" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="303" t="s">
+      <c r="B7" s="302" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="324" t="s">
+      <c r="C7" s="329" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="303" t="s">
+      <c r="D7" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="303" t="s">
+      <c r="E7" s="302" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="303" t="s">
+      <c r="F7" s="302" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="303" t="s">
+      <c r="G7" s="302" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="303" t="s">
+      <c r="H7" s="302" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="303" t="s">
+      <c r="I7" s="302" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="303" t="s">
+      <c r="J7" s="302" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="303" t="s">
+      <c r="K7" s="302" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="333" t="s">
+      <c r="L7" s="336" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="303" t="s">
+      <c r="M7" s="302" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="303" t="s">
+      <c r="N7" s="302" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="313" t="s">
+      <c r="O7" s="318" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="314"/>
-      <c r="Q7" s="314"/>
-      <c r="R7" s="314"/>
-      <c r="S7" s="314"/>
-      <c r="T7" s="314"/>
-      <c r="U7" s="314"/>
-      <c r="V7" s="315"/>
-      <c r="W7" s="303" t="s">
+      <c r="P7" s="319"/>
+      <c r="Q7" s="319"/>
+      <c r="R7" s="319"/>
+      <c r="S7" s="319"/>
+      <c r="T7" s="319"/>
+      <c r="U7" s="319"/>
+      <c r="V7" s="320"/>
+      <c r="W7" s="302" t="s">
         <v>139</v>
       </c>
-      <c r="X7" s="330" t="s">
+      <c r="X7" s="337" t="s">
         <v>13</v>
       </c>
-      <c r="Y7" s="330" t="s">
+      <c r="Y7" s="337" t="s">
         <v>14</v>
       </c>
-      <c r="Z7" s="297" t="s">
+      <c r="Z7" s="307" t="s">
         <v>150</v>
       </c>
-      <c r="AA7" s="303" t="s">
+      <c r="AA7" s="302" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="303" t="s">
+      <c r="AB7" s="302" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="303" t="s">
+      <c r="AC7" s="302" t="s">
         <v>134</v>
       </c>
-      <c r="AD7" s="297" t="s">
+      <c r="AD7" s="307" t="s">
         <v>17</v>
       </c>
-      <c r="AE7" s="326" t="s">
+      <c r="AE7" s="304" t="s">
         <v>107</v>
       </c>
-      <c r="AF7" s="326" t="s">
+      <c r="AF7" s="304" t="s">
         <v>108</v>
       </c>
-      <c r="AG7" s="326" t="s">
+      <c r="AG7" s="304" t="s">
         <v>106</v>
       </c>
-      <c r="AH7" s="328" t="s">
+      <c r="AH7" s="306" t="s">
         <v>147</v>
       </c>
-      <c r="AI7" s="297" t="s">
+      <c r="AI7" s="307" t="s">
         <v>136</v>
       </c>
-      <c r="AJ7" s="297" t="s">
+      <c r="AJ7" s="307" t="s">
         <v>137</v>
       </c>
-      <c r="AK7" s="303" t="s">
+      <c r="AK7" s="302" t="s">
         <v>135</v>
       </c>
-      <c r="AL7" s="303" t="s">
+      <c r="AL7" s="302" t="s">
         <v>146</v>
       </c>
-      <c r="AM7" s="303" t="s">
+      <c r="AM7" s="302" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="298"/>
-      <c r="B8" s="298"/>
-      <c r="C8" s="324"/>
-      <c r="D8" s="298"/>
-      <c r="E8" s="298"/>
-      <c r="F8" s="298"/>
-      <c r="G8" s="298"/>
-      <c r="H8" s="298"/>
-      <c r="I8" s="298"/>
-      <c r="J8" s="298"/>
-      <c r="K8" s="298"/>
-      <c r="L8" s="298"/>
-      <c r="M8" s="298"/>
-      <c r="N8" s="298"/>
-      <c r="O8" s="316"/>
-      <c r="P8" s="317"/>
-      <c r="Q8" s="317"/>
-      <c r="R8" s="317"/>
-      <c r="S8" s="317"/>
-      <c r="T8" s="317"/>
-      <c r="U8" s="317"/>
-      <c r="V8" s="318"/>
-      <c r="W8" s="298"/>
-      <c r="X8" s="298"/>
-      <c r="Y8" s="298"/>
-      <c r="Z8" s="298"/>
-      <c r="AA8" s="298"/>
-      <c r="AB8" s="298"/>
-      <c r="AC8" s="303"/>
-      <c r="AD8" s="298"/>
-      <c r="AE8" s="327"/>
-      <c r="AF8" s="327"/>
-      <c r="AG8" s="328"/>
-      <c r="AH8" s="327"/>
-      <c r="AI8" s="298"/>
-      <c r="AJ8" s="297"/>
-      <c r="AK8" s="298"/>
-      <c r="AL8" s="303"/>
-      <c r="AM8" s="298"/>
+      <c r="A8" s="308"/>
+      <c r="B8" s="308"/>
+      <c r="C8" s="329"/>
+      <c r="D8" s="308"/>
+      <c r="E8" s="308"/>
+      <c r="F8" s="308"/>
+      <c r="G8" s="308"/>
+      <c r="H8" s="308"/>
+      <c r="I8" s="308"/>
+      <c r="J8" s="308"/>
+      <c r="K8" s="308"/>
+      <c r="L8" s="308"/>
+      <c r="M8" s="308"/>
+      <c r="N8" s="308"/>
+      <c r="O8" s="321"/>
+      <c r="P8" s="322"/>
+      <c r="Q8" s="322"/>
+      <c r="R8" s="322"/>
+      <c r="S8" s="322"/>
+      <c r="T8" s="322"/>
+      <c r="U8" s="322"/>
+      <c r="V8" s="323"/>
+      <c r="W8" s="308"/>
+      <c r="X8" s="308"/>
+      <c r="Y8" s="308"/>
+      <c r="Z8" s="308"/>
+      <c r="AA8" s="308"/>
+      <c r="AB8" s="308"/>
+      <c r="AC8" s="302"/>
+      <c r="AD8" s="308"/>
+      <c r="AE8" s="305"/>
+      <c r="AF8" s="305"/>
+      <c r="AG8" s="306"/>
+      <c r="AH8" s="305"/>
+      <c r="AI8" s="308"/>
+      <c r="AJ8" s="307"/>
+      <c r="AK8" s="308"/>
+      <c r="AL8" s="302"/>
+      <c r="AM8" s="308"/>
     </row>
     <row r="9" spans="1:42" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="298"/>
-      <c r="B9" s="298"/>
-      <c r="C9" s="324"/>
-      <c r="D9" s="298"/>
-      <c r="E9" s="298"/>
-      <c r="F9" s="298"/>
-      <c r="G9" s="298"/>
-      <c r="H9" s="298"/>
-      <c r="I9" s="298"/>
-      <c r="J9" s="298"/>
-      <c r="K9" s="298"/>
-      <c r="L9" s="298"/>
-      <c r="M9" s="298"/>
-      <c r="N9" s="298"/>
-      <c r="O9" s="319"/>
-      <c r="P9" s="320"/>
-      <c r="Q9" s="320"/>
-      <c r="R9" s="320"/>
-      <c r="S9" s="320"/>
-      <c r="T9" s="320"/>
-      <c r="U9" s="320"/>
-      <c r="V9" s="321"/>
-      <c r="W9" s="298"/>
-      <c r="X9" s="298"/>
-      <c r="Y9" s="298"/>
-      <c r="Z9" s="298"/>
-      <c r="AA9" s="298"/>
-      <c r="AB9" s="298"/>
-      <c r="AC9" s="303"/>
-      <c r="AD9" s="298"/>
-      <c r="AE9" s="327"/>
-      <c r="AF9" s="327"/>
-      <c r="AG9" s="328"/>
-      <c r="AH9" s="327"/>
-      <c r="AI9" s="298"/>
-      <c r="AJ9" s="297"/>
-      <c r="AK9" s="298"/>
-      <c r="AL9" s="303"/>
-      <c r="AM9" s="298"/>
+      <c r="A9" s="308"/>
+      <c r="B9" s="308"/>
+      <c r="C9" s="329"/>
+      <c r="D9" s="308"/>
+      <c r="E9" s="308"/>
+      <c r="F9" s="308"/>
+      <c r="G9" s="308"/>
+      <c r="H9" s="308"/>
+      <c r="I9" s="308"/>
+      <c r="J9" s="308"/>
+      <c r="K9" s="308"/>
+      <c r="L9" s="308"/>
+      <c r="M9" s="308"/>
+      <c r="N9" s="308"/>
+      <c r="O9" s="324"/>
+      <c r="P9" s="325"/>
+      <c r="Q9" s="325"/>
+      <c r="R9" s="325"/>
+      <c r="S9" s="325"/>
+      <c r="T9" s="325"/>
+      <c r="U9" s="325"/>
+      <c r="V9" s="326"/>
+      <c r="W9" s="308"/>
+      <c r="X9" s="308"/>
+      <c r="Y9" s="308"/>
+      <c r="Z9" s="308"/>
+      <c r="AA9" s="308"/>
+      <c r="AB9" s="308"/>
+      <c r="AC9" s="302"/>
+      <c r="AD9" s="308"/>
+      <c r="AE9" s="305"/>
+      <c r="AF9" s="305"/>
+      <c r="AG9" s="306"/>
+      <c r="AH9" s="305"/>
+      <c r="AI9" s="308"/>
+      <c r="AJ9" s="307"/>
+      <c r="AK9" s="308"/>
+      <c r="AL9" s="302"/>
+      <c r="AM9" s="308"/>
       <c r="AP9">
         <v>27</v>
       </c>
@@ -8699,47 +8699,47 @@
       </c>
     </row>
     <row r="77" spans="1:42" ht="29.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="332" t="s">
+      <c r="A77" s="335" t="s">
         <v>145</v>
       </c>
-      <c r="B77" s="298"/>
-      <c r="C77" s="298"/>
-      <c r="D77" s="298"/>
-      <c r="E77" s="298"/>
-      <c r="F77" s="298"/>
-      <c r="G77" s="298"/>
-      <c r="H77" s="298"/>
-      <c r="I77" s="298"/>
-      <c r="J77" s="298"/>
-      <c r="K77" s="298"/>
-      <c r="L77" s="298"/>
-      <c r="M77" s="298"/>
-      <c r="N77" s="298"/>
-      <c r="O77" s="298"/>
-      <c r="P77" s="298"/>
-      <c r="Q77" s="298"/>
-      <c r="R77" s="298"/>
-      <c r="S77" s="298"/>
-      <c r="T77" s="298"/>
-      <c r="U77" s="298"/>
-      <c r="V77" s="298"/>
-      <c r="W77" s="298"/>
-      <c r="X77" s="298"/>
-      <c r="Y77" s="298"/>
-      <c r="Z77" s="298"/>
-      <c r="AA77" s="298"/>
-      <c r="AB77" s="298"/>
-      <c r="AC77" s="298"/>
-      <c r="AD77" s="298"/>
-      <c r="AE77" s="298"/>
-      <c r="AF77" s="298"/>
-      <c r="AG77" s="298"/>
-      <c r="AH77" s="298"/>
-      <c r="AI77" s="298"/>
-      <c r="AJ77" s="298"/>
-      <c r="AK77" s="298"/>
-      <c r="AL77" s="298"/>
-      <c r="AM77" s="298"/>
+      <c r="B77" s="308"/>
+      <c r="C77" s="308"/>
+      <c r="D77" s="308"/>
+      <c r="E77" s="308"/>
+      <c r="F77" s="308"/>
+      <c r="G77" s="308"/>
+      <c r="H77" s="308"/>
+      <c r="I77" s="308"/>
+      <c r="J77" s="308"/>
+      <c r="K77" s="308"/>
+      <c r="L77" s="308"/>
+      <c r="M77" s="308"/>
+      <c r="N77" s="308"/>
+      <c r="O77" s="308"/>
+      <c r="P77" s="308"/>
+      <c r="Q77" s="308"/>
+      <c r="R77" s="308"/>
+      <c r="S77" s="308"/>
+      <c r="T77" s="308"/>
+      <c r="U77" s="308"/>
+      <c r="V77" s="308"/>
+      <c r="W77" s="308"/>
+      <c r="X77" s="308"/>
+      <c r="Y77" s="308"/>
+      <c r="Z77" s="308"/>
+      <c r="AA77" s="308"/>
+      <c r="AB77" s="308"/>
+      <c r="AC77" s="308"/>
+      <c r="AD77" s="308"/>
+      <c r="AE77" s="308"/>
+      <c r="AF77" s="308"/>
+      <c r="AG77" s="308"/>
+      <c r="AH77" s="308"/>
+      <c r="AI77" s="308"/>
+      <c r="AJ77" s="308"/>
+      <c r="AK77" s="308"/>
+      <c r="AL77" s="308"/>
+      <c r="AM77" s="308"/>
     </row>
     <row r="78" spans="1:42" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="81"/>
@@ -9839,6 +9839,28 @@
   </sheetData>
   <autoFilter ref="A10:AP80" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="38">
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AC9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="A2:AB2"/>
+    <mergeCell ref="A4:AM4"/>
+    <mergeCell ref="A5:AM5"/>
+    <mergeCell ref="AD7:AD9"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="AD6:AM6"/>
     <mergeCell ref="A77:AM77"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="D7:D9"/>
@@ -9855,28 +9877,6 @@
     <mergeCell ref="AI7:AI9"/>
     <mergeCell ref="AJ7:AJ9"/>
     <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="A2:AB2"/>
-    <mergeCell ref="A4:AM4"/>
-    <mergeCell ref="A5:AM5"/>
-    <mergeCell ref="AD7:AD9"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="AD6:AM6"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AC9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="O7:V9"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.27559055118110237" top="0.47244094488188981" bottom="0.31496062992125984" header="0" footer="0"/>
   <pageSetup scale="80" orientation="landscape" r:id="rId1"/>
@@ -9925,36 +9925,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="329" t="s">
+      <c r="A1" s="338" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="305"/>
-      <c r="C1" s="306"/>
-      <c r="D1" s="305"/>
-      <c r="E1" s="305"/>
-      <c r="F1" s="305"/>
-      <c r="G1" s="305"/>
-      <c r="H1" s="305"/>
-      <c r="I1" s="305"/>
-      <c r="J1" s="305"/>
-      <c r="K1" s="305"/>
-      <c r="L1" s="305"/>
-      <c r="M1" s="305"/>
-      <c r="N1" s="305"/>
-      <c r="O1" s="305"/>
-      <c r="P1" s="305"/>
-      <c r="Q1" s="305"/>
-      <c r="R1" s="305"/>
-      <c r="S1" s="305"/>
-      <c r="T1" s="305"/>
-      <c r="U1" s="305"/>
-      <c r="V1" s="305"/>
-      <c r="W1" s="305"/>
-      <c r="X1" s="305"/>
-      <c r="Y1" s="305"/>
-      <c r="Z1" s="305"/>
-      <c r="AA1" s="305"/>
-      <c r="AB1" s="307"/>
+      <c r="B1" s="310"/>
+      <c r="C1" s="311"/>
+      <c r="D1" s="310"/>
+      <c r="E1" s="310"/>
+      <c r="F1" s="310"/>
+      <c r="G1" s="310"/>
+      <c r="H1" s="310"/>
+      <c r="I1" s="310"/>
+      <c r="J1" s="310"/>
+      <c r="K1" s="310"/>
+      <c r="L1" s="310"/>
+      <c r="M1" s="310"/>
+      <c r="N1" s="310"/>
+      <c r="O1" s="310"/>
+      <c r="P1" s="310"/>
+      <c r="Q1" s="310"/>
+      <c r="R1" s="310"/>
+      <c r="S1" s="310"/>
+      <c r="T1" s="310"/>
+      <c r="U1" s="310"/>
+      <c r="V1" s="310"/>
+      <c r="W1" s="310"/>
+      <c r="X1" s="310"/>
+      <c r="Y1" s="310"/>
+      <c r="Z1" s="310"/>
+      <c r="AA1" s="310"/>
+      <c r="AB1" s="312"/>
       <c r="AC1" s="17"/>
       <c r="AD1" s="17"/>
       <c r="AE1" s="1"/>
@@ -9971,36 +9971,36 @@
       <c r="AN1" s="160"/>
     </row>
     <row r="2" spans="1:43" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="308" t="s">
+      <c r="A2" s="313" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="305"/>
-      <c r="C2" s="306"/>
-      <c r="D2" s="305"/>
-      <c r="E2" s="305"/>
-      <c r="F2" s="305"/>
-      <c r="G2" s="305"/>
-      <c r="H2" s="305"/>
-      <c r="I2" s="305"/>
-      <c r="J2" s="305"/>
-      <c r="K2" s="305"/>
-      <c r="L2" s="305"/>
-      <c r="M2" s="305"/>
-      <c r="N2" s="305"/>
-      <c r="O2" s="305"/>
-      <c r="P2" s="305"/>
-      <c r="Q2" s="305"/>
-      <c r="R2" s="305"/>
-      <c r="S2" s="305"/>
-      <c r="T2" s="305"/>
-      <c r="U2" s="305"/>
-      <c r="V2" s="305"/>
-      <c r="W2" s="305"/>
-      <c r="X2" s="305"/>
-      <c r="Y2" s="305"/>
-      <c r="Z2" s="305"/>
-      <c r="AA2" s="305"/>
-      <c r="AB2" s="307"/>
+      <c r="B2" s="310"/>
+      <c r="C2" s="311"/>
+      <c r="D2" s="310"/>
+      <c r="E2" s="310"/>
+      <c r="F2" s="310"/>
+      <c r="G2" s="310"/>
+      <c r="H2" s="310"/>
+      <c r="I2" s="310"/>
+      <c r="J2" s="310"/>
+      <c r="K2" s="310"/>
+      <c r="L2" s="310"/>
+      <c r="M2" s="310"/>
+      <c r="N2" s="310"/>
+      <c r="O2" s="310"/>
+      <c r="P2" s="310"/>
+      <c r="Q2" s="310"/>
+      <c r="R2" s="310"/>
+      <c r="S2" s="310"/>
+      <c r="T2" s="310"/>
+      <c r="U2" s="310"/>
+      <c r="V2" s="310"/>
+      <c r="W2" s="310"/>
+      <c r="X2" s="310"/>
+      <c r="Y2" s="310"/>
+      <c r="Z2" s="310"/>
+      <c r="AA2" s="310"/>
+      <c r="AB2" s="312"/>
       <c r="AC2" s="17"/>
       <c r="AD2" s="17"/>
       <c r="AE2" s="1"/>
@@ -10057,92 +10057,92 @@
       <c r="AN3" s="160"/>
     </row>
     <row r="4" spans="1:43" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="309" t="s">
+      <c r="A4" s="314" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="305"/>
-      <c r="C4" s="306"/>
-      <c r="D4" s="305"/>
-      <c r="E4" s="305"/>
-      <c r="F4" s="305"/>
-      <c r="G4" s="305"/>
-      <c r="H4" s="305"/>
-      <c r="I4" s="305"/>
-      <c r="J4" s="305"/>
-      <c r="K4" s="305"/>
-      <c r="L4" s="305"/>
-      <c r="M4" s="305"/>
-      <c r="N4" s="305"/>
-      <c r="O4" s="305"/>
-      <c r="P4" s="305"/>
-      <c r="Q4" s="305"/>
-      <c r="R4" s="305"/>
-      <c r="S4" s="305"/>
-      <c r="T4" s="305"/>
-      <c r="U4" s="305"/>
-      <c r="V4" s="305"/>
-      <c r="W4" s="305"/>
-      <c r="X4" s="305"/>
-      <c r="Y4" s="305"/>
-      <c r="Z4" s="305"/>
-      <c r="AA4" s="305"/>
-      <c r="AB4" s="305"/>
-      <c r="AC4" s="306"/>
-      <c r="AD4" s="306"/>
-      <c r="AE4" s="305"/>
-      <c r="AF4" s="305"/>
-      <c r="AG4" s="306"/>
-      <c r="AH4" s="306"/>
-      <c r="AI4" s="305"/>
-      <c r="AJ4" s="306"/>
-      <c r="AK4" s="306"/>
-      <c r="AL4" s="305"/>
-      <c r="AM4" s="306"/>
-      <c r="AN4" s="307"/>
+      <c r="B4" s="310"/>
+      <c r="C4" s="311"/>
+      <c r="D4" s="310"/>
+      <c r="E4" s="310"/>
+      <c r="F4" s="310"/>
+      <c r="G4" s="310"/>
+      <c r="H4" s="310"/>
+      <c r="I4" s="310"/>
+      <c r="J4" s="310"/>
+      <c r="K4" s="310"/>
+      <c r="L4" s="310"/>
+      <c r="M4" s="310"/>
+      <c r="N4" s="310"/>
+      <c r="O4" s="310"/>
+      <c r="P4" s="310"/>
+      <c r="Q4" s="310"/>
+      <c r="R4" s="310"/>
+      <c r="S4" s="310"/>
+      <c r="T4" s="310"/>
+      <c r="U4" s="310"/>
+      <c r="V4" s="310"/>
+      <c r="W4" s="310"/>
+      <c r="X4" s="310"/>
+      <c r="Y4" s="310"/>
+      <c r="Z4" s="310"/>
+      <c r="AA4" s="310"/>
+      <c r="AB4" s="310"/>
+      <c r="AC4" s="311"/>
+      <c r="AD4" s="311"/>
+      <c r="AE4" s="310"/>
+      <c r="AF4" s="310"/>
+      <c r="AG4" s="311"/>
+      <c r="AH4" s="311"/>
+      <c r="AI4" s="310"/>
+      <c r="AJ4" s="311"/>
+      <c r="AK4" s="311"/>
+      <c r="AL4" s="310"/>
+      <c r="AM4" s="311"/>
+      <c r="AN4" s="312"/>
     </row>
     <row r="5" spans="1:43" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="310" t="s">
+      <c r="A5" s="315" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="305"/>
-      <c r="C5" s="306"/>
-      <c r="D5" s="305"/>
-      <c r="E5" s="305"/>
-      <c r="F5" s="305"/>
-      <c r="G5" s="305"/>
-      <c r="H5" s="305"/>
-      <c r="I5" s="305"/>
-      <c r="J5" s="305"/>
-      <c r="K5" s="305"/>
-      <c r="L5" s="305"/>
-      <c r="M5" s="305"/>
-      <c r="N5" s="305"/>
-      <c r="O5" s="305"/>
-      <c r="P5" s="305"/>
-      <c r="Q5" s="305"/>
-      <c r="R5" s="305"/>
-      <c r="S5" s="305"/>
-      <c r="T5" s="305"/>
-      <c r="U5" s="305"/>
-      <c r="V5" s="305"/>
-      <c r="W5" s="305"/>
-      <c r="X5" s="305"/>
-      <c r="Y5" s="305"/>
-      <c r="Z5" s="305"/>
-      <c r="AA5" s="305"/>
-      <c r="AB5" s="305"/>
-      <c r="AC5" s="306"/>
-      <c r="AD5" s="306"/>
-      <c r="AE5" s="305"/>
-      <c r="AF5" s="305"/>
-      <c r="AG5" s="306"/>
-      <c r="AH5" s="306"/>
-      <c r="AI5" s="305"/>
-      <c r="AJ5" s="306"/>
-      <c r="AK5" s="306"/>
-      <c r="AL5" s="305"/>
-      <c r="AM5" s="306"/>
-      <c r="AN5" s="307"/>
+      <c r="B5" s="310"/>
+      <c r="C5" s="311"/>
+      <c r="D5" s="310"/>
+      <c r="E5" s="310"/>
+      <c r="F5" s="310"/>
+      <c r="G5" s="310"/>
+      <c r="H5" s="310"/>
+      <c r="I5" s="310"/>
+      <c r="J5" s="310"/>
+      <c r="K5" s="310"/>
+      <c r="L5" s="310"/>
+      <c r="M5" s="310"/>
+      <c r="N5" s="310"/>
+      <c r="O5" s="310"/>
+      <c r="P5" s="310"/>
+      <c r="Q5" s="310"/>
+      <c r="R5" s="310"/>
+      <c r="S5" s="310"/>
+      <c r="T5" s="310"/>
+      <c r="U5" s="310"/>
+      <c r="V5" s="310"/>
+      <c r="W5" s="310"/>
+      <c r="X5" s="310"/>
+      <c r="Y5" s="310"/>
+      <c r="Z5" s="310"/>
+      <c r="AA5" s="310"/>
+      <c r="AB5" s="310"/>
+      <c r="AC5" s="311"/>
+      <c r="AD5" s="311"/>
+      <c r="AE5" s="310"/>
+      <c r="AF5" s="310"/>
+      <c r="AG5" s="311"/>
+      <c r="AH5" s="311"/>
+      <c r="AI5" s="310"/>
+      <c r="AJ5" s="311"/>
+      <c r="AK5" s="311"/>
+      <c r="AL5" s="310"/>
+      <c r="AM5" s="311"/>
+      <c r="AN5" s="312"/>
     </row>
     <row r="6" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -10177,212 +10177,212 @@
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
       <c r="AD6" s="11"/>
-      <c r="AE6" s="334" t="s">
+      <c r="AE6" s="340" t="s">
         <v>151</v>
       </c>
-      <c r="AF6" s="335"/>
-      <c r="AG6" s="335"/>
-      <c r="AH6" s="335"/>
-      <c r="AI6" s="335"/>
-      <c r="AJ6" s="335"/>
-      <c r="AK6" s="335"/>
-      <c r="AL6" s="335"/>
-      <c r="AM6" s="335"/>
-      <c r="AN6" s="335"/>
+      <c r="AF6" s="341"/>
+      <c r="AG6" s="341"/>
+      <c r="AH6" s="341"/>
+      <c r="AI6" s="341"/>
+      <c r="AJ6" s="341"/>
+      <c r="AK6" s="341"/>
+      <c r="AL6" s="341"/>
+      <c r="AM6" s="341"/>
+      <c r="AN6" s="341"/>
     </row>
     <row r="7" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="303" t="s">
+      <c r="A7" s="302" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="303" t="s">
+      <c r="B7" s="302" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="324" t="s">
+      <c r="C7" s="329" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="303" t="s">
+      <c r="D7" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="303" t="s">
+      <c r="E7" s="302" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="303" t="s">
+      <c r="F7" s="302" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="303" t="s">
+      <c r="G7" s="302" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="303" t="s">
+      <c r="H7" s="302" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="303" t="s">
+      <c r="I7" s="302" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="303" t="s">
+      <c r="J7" s="302" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="303" t="s">
+      <c r="K7" s="302" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="333" t="s">
+      <c r="L7" s="336" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="303" t="s">
+      <c r="M7" s="302" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="303" t="s">
+      <c r="N7" s="302" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="313" t="s">
+      <c r="O7" s="318" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="314"/>
-      <c r="Q7" s="314"/>
-      <c r="R7" s="314"/>
-      <c r="S7" s="314"/>
-      <c r="T7" s="314"/>
-      <c r="U7" s="314"/>
-      <c r="V7" s="315"/>
-      <c r="W7" s="303" t="s">
+      <c r="P7" s="319"/>
+      <c r="Q7" s="319"/>
+      <c r="R7" s="319"/>
+      <c r="S7" s="319"/>
+      <c r="T7" s="319"/>
+      <c r="U7" s="319"/>
+      <c r="V7" s="320"/>
+      <c r="W7" s="302" t="s">
         <v>139</v>
       </c>
-      <c r="X7" s="311" t="s">
+      <c r="X7" s="317" t="s">
         <v>13</v>
       </c>
-      <c r="Y7" s="311" t="s">
+      <c r="Y7" s="317" t="s">
         <v>184</v>
       </c>
-      <c r="Z7" s="325" t="s">
+      <c r="Z7" s="330" t="s">
         <v>175</v>
       </c>
-      <c r="AA7" s="303" t="s">
+      <c r="AA7" s="302" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="303" t="s">
+      <c r="AB7" s="302" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="313" t="s">
+      <c r="AC7" s="318" t="s">
         <v>155</v>
       </c>
-      <c r="AD7" s="315"/>
-      <c r="AE7" s="297" t="s">
+      <c r="AD7" s="320"/>
+      <c r="AE7" s="307" t="s">
         <v>17</v>
       </c>
-      <c r="AF7" s="326" t="s">
+      <c r="AF7" s="304" t="s">
         <v>107</v>
       </c>
-      <c r="AG7" s="326" t="s">
+      <c r="AG7" s="304" t="s">
         <v>108</v>
       </c>
-      <c r="AH7" s="326" t="s">
+      <c r="AH7" s="304" t="s">
         <v>106</v>
       </c>
-      <c r="AI7" s="328" t="s">
+      <c r="AI7" s="306" t="s">
         <v>147</v>
       </c>
-      <c r="AJ7" s="297" t="s">
+      <c r="AJ7" s="307" t="s">
         <v>136</v>
       </c>
-      <c r="AK7" s="297" t="s">
+      <c r="AK7" s="307" t="s">
         <v>137</v>
       </c>
-      <c r="AL7" s="303" t="s">
+      <c r="AL7" s="302" t="s">
         <v>135</v>
       </c>
-      <c r="AM7" s="303" t="s">
+      <c r="AM7" s="302" t="s">
         <v>146</v>
       </c>
-      <c r="AN7" s="303" t="s">
+      <c r="AN7" s="302" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="298"/>
-      <c r="B8" s="298"/>
-      <c r="C8" s="324"/>
-      <c r="D8" s="298"/>
-      <c r="E8" s="298"/>
-      <c r="F8" s="298"/>
-      <c r="G8" s="298"/>
-      <c r="H8" s="298"/>
-      <c r="I8" s="298"/>
-      <c r="J8" s="298"/>
-      <c r="K8" s="298"/>
-      <c r="L8" s="298"/>
-      <c r="M8" s="298"/>
-      <c r="N8" s="298"/>
-      <c r="O8" s="316"/>
-      <c r="P8" s="317"/>
-      <c r="Q8" s="317"/>
-      <c r="R8" s="317"/>
-      <c r="S8" s="317"/>
-      <c r="T8" s="317"/>
-      <c r="U8" s="317"/>
-      <c r="V8" s="318"/>
-      <c r="W8" s="298"/>
-      <c r="X8" s="298"/>
-      <c r="Y8" s="298"/>
-      <c r="Z8" s="298"/>
-      <c r="AA8" s="298"/>
-      <c r="AB8" s="298"/>
-      <c r="AC8" s="319"/>
-      <c r="AD8" s="321"/>
-      <c r="AE8" s="298"/>
-      <c r="AF8" s="327"/>
-      <c r="AG8" s="327"/>
-      <c r="AH8" s="328"/>
-      <c r="AI8" s="327"/>
-      <c r="AJ8" s="298"/>
-      <c r="AK8" s="297"/>
-      <c r="AL8" s="298"/>
-      <c r="AM8" s="303"/>
-      <c r="AN8" s="312"/>
+      <c r="A8" s="308"/>
+      <c r="B8" s="308"/>
+      <c r="C8" s="329"/>
+      <c r="D8" s="308"/>
+      <c r="E8" s="308"/>
+      <c r="F8" s="308"/>
+      <c r="G8" s="308"/>
+      <c r="H8" s="308"/>
+      <c r="I8" s="308"/>
+      <c r="J8" s="308"/>
+      <c r="K8" s="308"/>
+      <c r="L8" s="308"/>
+      <c r="M8" s="308"/>
+      <c r="N8" s="308"/>
+      <c r="O8" s="321"/>
+      <c r="P8" s="322"/>
+      <c r="Q8" s="322"/>
+      <c r="R8" s="322"/>
+      <c r="S8" s="322"/>
+      <c r="T8" s="322"/>
+      <c r="U8" s="322"/>
+      <c r="V8" s="323"/>
+      <c r="W8" s="308"/>
+      <c r="X8" s="308"/>
+      <c r="Y8" s="308"/>
+      <c r="Z8" s="308"/>
+      <c r="AA8" s="308"/>
+      <c r="AB8" s="308"/>
+      <c r="AC8" s="324"/>
+      <c r="AD8" s="326"/>
+      <c r="AE8" s="308"/>
+      <c r="AF8" s="305"/>
+      <c r="AG8" s="305"/>
+      <c r="AH8" s="306"/>
+      <c r="AI8" s="305"/>
+      <c r="AJ8" s="308"/>
+      <c r="AK8" s="307"/>
+      <c r="AL8" s="308"/>
+      <c r="AM8" s="302"/>
+      <c r="AN8" s="303"/>
     </row>
     <row r="9" spans="1:43" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="298"/>
-      <c r="B9" s="298"/>
-      <c r="C9" s="324"/>
-      <c r="D9" s="298"/>
-      <c r="E9" s="298"/>
-      <c r="F9" s="298"/>
-      <c r="G9" s="298"/>
-      <c r="H9" s="298"/>
-      <c r="I9" s="298"/>
-      <c r="J9" s="298"/>
-      <c r="K9" s="298"/>
-      <c r="L9" s="298"/>
-      <c r="M9" s="298"/>
-      <c r="N9" s="298"/>
-      <c r="O9" s="319"/>
-      <c r="P9" s="320"/>
-      <c r="Q9" s="320"/>
-      <c r="R9" s="320"/>
-      <c r="S9" s="320"/>
-      <c r="T9" s="320"/>
-      <c r="U9" s="320"/>
-      <c r="V9" s="321"/>
-      <c r="W9" s="298"/>
-      <c r="X9" s="298"/>
-      <c r="Y9" s="298"/>
-      <c r="Z9" s="298"/>
-      <c r="AA9" s="298"/>
-      <c r="AB9" s="298"/>
+      <c r="A9" s="308"/>
+      <c r="B9" s="308"/>
+      <c r="C9" s="329"/>
+      <c r="D9" s="308"/>
+      <c r="E9" s="308"/>
+      <c r="F9" s="308"/>
+      <c r="G9" s="308"/>
+      <c r="H9" s="308"/>
+      <c r="I9" s="308"/>
+      <c r="J9" s="308"/>
+      <c r="K9" s="308"/>
+      <c r="L9" s="308"/>
+      <c r="M9" s="308"/>
+      <c r="N9" s="308"/>
+      <c r="O9" s="324"/>
+      <c r="P9" s="325"/>
+      <c r="Q9" s="325"/>
+      <c r="R9" s="325"/>
+      <c r="S9" s="325"/>
+      <c r="T9" s="325"/>
+      <c r="U9" s="325"/>
+      <c r="V9" s="326"/>
+      <c r="W9" s="308"/>
+      <c r="X9" s="308"/>
+      <c r="Y9" s="308"/>
+      <c r="Z9" s="308"/>
+      <c r="AA9" s="308"/>
+      <c r="AB9" s="308"/>
       <c r="AC9" s="201" t="s">
         <v>153</v>
       </c>
       <c r="AD9" s="178" t="s">
         <v>154</v>
       </c>
-      <c r="AE9" s="298"/>
-      <c r="AF9" s="327"/>
-      <c r="AG9" s="327"/>
-      <c r="AH9" s="328"/>
-      <c r="AI9" s="327"/>
-      <c r="AJ9" s="298"/>
-      <c r="AK9" s="297"/>
-      <c r="AL9" s="298"/>
-      <c r="AM9" s="303"/>
-      <c r="AN9" s="312"/>
+      <c r="AE9" s="308"/>
+      <c r="AF9" s="305"/>
+      <c r="AG9" s="305"/>
+      <c r="AH9" s="306"/>
+      <c r="AI9" s="305"/>
+      <c r="AJ9" s="308"/>
+      <c r="AK9" s="307"/>
+      <c r="AL9" s="308"/>
+      <c r="AM9" s="302"/>
+      <c r="AN9" s="303"/>
       <c r="AO9">
         <f>Z11/W11</f>
         <v>0.50632226325372287</v>
@@ -15652,27 +15652,6 @@
   </sheetData>
   <autoFilter ref="A10:AQ54" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AD8"/>
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A2:AB2"/>
@@ -15689,6 +15668,27 @@
     <mergeCell ref="H7:H9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:J9"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AD8"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
   </mergeCells>
   <pageMargins left="0.17" right="0.15748031496062992" top="0.41" bottom="0.23622047244094491" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
@@ -15737,36 +15737,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="329" t="s">
+      <c r="A1" s="338" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="305"/>
-      <c r="C1" s="306"/>
-      <c r="D1" s="305"/>
-      <c r="E1" s="305"/>
-      <c r="F1" s="305"/>
-      <c r="G1" s="305"/>
-      <c r="H1" s="305"/>
-      <c r="I1" s="305"/>
-      <c r="J1" s="305"/>
-      <c r="K1" s="305"/>
-      <c r="L1" s="305"/>
-      <c r="M1" s="305"/>
-      <c r="N1" s="305"/>
-      <c r="O1" s="305"/>
-      <c r="P1" s="305"/>
-      <c r="Q1" s="305"/>
-      <c r="R1" s="305"/>
-      <c r="S1" s="305"/>
-      <c r="T1" s="305"/>
-      <c r="U1" s="305"/>
-      <c r="V1" s="305"/>
-      <c r="W1" s="305"/>
-      <c r="X1" s="305"/>
-      <c r="Y1" s="305"/>
-      <c r="Z1" s="305"/>
-      <c r="AA1" s="305"/>
-      <c r="AB1" s="307"/>
+      <c r="B1" s="310"/>
+      <c r="C1" s="311"/>
+      <c r="D1" s="310"/>
+      <c r="E1" s="310"/>
+      <c r="F1" s="310"/>
+      <c r="G1" s="310"/>
+      <c r="H1" s="310"/>
+      <c r="I1" s="310"/>
+      <c r="J1" s="310"/>
+      <c r="K1" s="310"/>
+      <c r="L1" s="310"/>
+      <c r="M1" s="310"/>
+      <c r="N1" s="310"/>
+      <c r="O1" s="310"/>
+      <c r="P1" s="310"/>
+      <c r="Q1" s="310"/>
+      <c r="R1" s="310"/>
+      <c r="S1" s="310"/>
+      <c r="T1" s="310"/>
+      <c r="U1" s="310"/>
+      <c r="V1" s="310"/>
+      <c r="W1" s="310"/>
+      <c r="X1" s="310"/>
+      <c r="Y1" s="310"/>
+      <c r="Z1" s="310"/>
+      <c r="AA1" s="310"/>
+      <c r="AB1" s="312"/>
       <c r="AC1" s="17"/>
       <c r="AD1" s="17"/>
       <c r="AE1" s="1"/>
@@ -15783,36 +15783,36 @@
       <c r="AN1" s="160"/>
     </row>
     <row r="2" spans="1:43" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="308" t="s">
+      <c r="A2" s="313" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="305"/>
-      <c r="C2" s="306"/>
-      <c r="D2" s="305"/>
-      <c r="E2" s="305"/>
-      <c r="F2" s="305"/>
-      <c r="G2" s="305"/>
-      <c r="H2" s="305"/>
-      <c r="I2" s="305"/>
-      <c r="J2" s="305"/>
-      <c r="K2" s="305"/>
-      <c r="L2" s="305"/>
-      <c r="M2" s="305"/>
-      <c r="N2" s="305"/>
-      <c r="O2" s="305"/>
-      <c r="P2" s="305"/>
-      <c r="Q2" s="305"/>
-      <c r="R2" s="305"/>
-      <c r="S2" s="305"/>
-      <c r="T2" s="305"/>
-      <c r="U2" s="305"/>
-      <c r="V2" s="305"/>
-      <c r="W2" s="305"/>
-      <c r="X2" s="305"/>
-      <c r="Y2" s="305"/>
-      <c r="Z2" s="305"/>
-      <c r="AA2" s="305"/>
-      <c r="AB2" s="307"/>
+      <c r="B2" s="310"/>
+      <c r="C2" s="311"/>
+      <c r="D2" s="310"/>
+      <c r="E2" s="310"/>
+      <c r="F2" s="310"/>
+      <c r="G2" s="310"/>
+      <c r="H2" s="310"/>
+      <c r="I2" s="310"/>
+      <c r="J2" s="310"/>
+      <c r="K2" s="310"/>
+      <c r="L2" s="310"/>
+      <c r="M2" s="310"/>
+      <c r="N2" s="310"/>
+      <c r="O2" s="310"/>
+      <c r="P2" s="310"/>
+      <c r="Q2" s="310"/>
+      <c r="R2" s="310"/>
+      <c r="S2" s="310"/>
+      <c r="T2" s="310"/>
+      <c r="U2" s="310"/>
+      <c r="V2" s="310"/>
+      <c r="W2" s="310"/>
+      <c r="X2" s="310"/>
+      <c r="Y2" s="310"/>
+      <c r="Z2" s="310"/>
+      <c r="AA2" s="310"/>
+      <c r="AB2" s="312"/>
       <c r="AC2" s="17"/>
       <c r="AD2" s="17"/>
       <c r="AE2" s="1"/>
@@ -15869,92 +15869,92 @@
       <c r="AN3" s="160"/>
     </row>
     <row r="4" spans="1:43" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="309" t="s">
+      <c r="A4" s="314" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="305"/>
-      <c r="C4" s="306"/>
-      <c r="D4" s="305"/>
-      <c r="E4" s="305"/>
-      <c r="F4" s="305"/>
-      <c r="G4" s="305"/>
-      <c r="H4" s="305"/>
-      <c r="I4" s="305"/>
-      <c r="J4" s="305"/>
-      <c r="K4" s="305"/>
-      <c r="L4" s="305"/>
-      <c r="M4" s="305"/>
-      <c r="N4" s="305"/>
-      <c r="O4" s="305"/>
-      <c r="P4" s="305"/>
-      <c r="Q4" s="305"/>
-      <c r="R4" s="305"/>
-      <c r="S4" s="305"/>
-      <c r="T4" s="305"/>
-      <c r="U4" s="305"/>
-      <c r="V4" s="305"/>
-      <c r="W4" s="305"/>
-      <c r="X4" s="305"/>
-      <c r="Y4" s="305"/>
-      <c r="Z4" s="305"/>
-      <c r="AA4" s="305"/>
-      <c r="AB4" s="305"/>
-      <c r="AC4" s="306"/>
-      <c r="AD4" s="306"/>
-      <c r="AE4" s="305"/>
-      <c r="AF4" s="305"/>
-      <c r="AG4" s="306"/>
-      <c r="AH4" s="306"/>
-      <c r="AI4" s="305"/>
-      <c r="AJ4" s="306"/>
-      <c r="AK4" s="306"/>
-      <c r="AL4" s="305"/>
-      <c r="AM4" s="306"/>
-      <c r="AN4" s="307"/>
+      <c r="B4" s="310"/>
+      <c r="C4" s="311"/>
+      <c r="D4" s="310"/>
+      <c r="E4" s="310"/>
+      <c r="F4" s="310"/>
+      <c r="G4" s="310"/>
+      <c r="H4" s="310"/>
+      <c r="I4" s="310"/>
+      <c r="J4" s="310"/>
+      <c r="K4" s="310"/>
+      <c r="L4" s="310"/>
+      <c r="M4" s="310"/>
+      <c r="N4" s="310"/>
+      <c r="O4" s="310"/>
+      <c r="P4" s="310"/>
+      <c r="Q4" s="310"/>
+      <c r="R4" s="310"/>
+      <c r="S4" s="310"/>
+      <c r="T4" s="310"/>
+      <c r="U4" s="310"/>
+      <c r="V4" s="310"/>
+      <c r="W4" s="310"/>
+      <c r="X4" s="310"/>
+      <c r="Y4" s="310"/>
+      <c r="Z4" s="310"/>
+      <c r="AA4" s="310"/>
+      <c r="AB4" s="310"/>
+      <c r="AC4" s="311"/>
+      <c r="AD4" s="311"/>
+      <c r="AE4" s="310"/>
+      <c r="AF4" s="310"/>
+      <c r="AG4" s="311"/>
+      <c r="AH4" s="311"/>
+      <c r="AI4" s="310"/>
+      <c r="AJ4" s="311"/>
+      <c r="AK4" s="311"/>
+      <c r="AL4" s="310"/>
+      <c r="AM4" s="311"/>
+      <c r="AN4" s="312"/>
     </row>
     <row r="5" spans="1:43" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="310" t="s">
+      <c r="A5" s="315" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="305"/>
-      <c r="C5" s="306"/>
-      <c r="D5" s="305"/>
-      <c r="E5" s="305"/>
-      <c r="F5" s="305"/>
-      <c r="G5" s="305"/>
-      <c r="H5" s="305"/>
-      <c r="I5" s="305"/>
-      <c r="J5" s="305"/>
-      <c r="K5" s="305"/>
-      <c r="L5" s="305"/>
-      <c r="M5" s="305"/>
-      <c r="N5" s="305"/>
-      <c r="O5" s="305"/>
-      <c r="P5" s="305"/>
-      <c r="Q5" s="305"/>
-      <c r="R5" s="305"/>
-      <c r="S5" s="305"/>
-      <c r="T5" s="305"/>
-      <c r="U5" s="305"/>
-      <c r="V5" s="305"/>
-      <c r="W5" s="305"/>
-      <c r="X5" s="305"/>
-      <c r="Y5" s="305"/>
-      <c r="Z5" s="305"/>
-      <c r="AA5" s="305"/>
-      <c r="AB5" s="305"/>
-      <c r="AC5" s="306"/>
-      <c r="AD5" s="306"/>
-      <c r="AE5" s="305"/>
-      <c r="AF5" s="305"/>
-      <c r="AG5" s="306"/>
-      <c r="AH5" s="306"/>
-      <c r="AI5" s="305"/>
-      <c r="AJ5" s="306"/>
-      <c r="AK5" s="306"/>
-      <c r="AL5" s="305"/>
-      <c r="AM5" s="306"/>
-      <c r="AN5" s="307"/>
+      <c r="B5" s="310"/>
+      <c r="C5" s="311"/>
+      <c r="D5" s="310"/>
+      <c r="E5" s="310"/>
+      <c r="F5" s="310"/>
+      <c r="G5" s="310"/>
+      <c r="H5" s="310"/>
+      <c r="I5" s="310"/>
+      <c r="J5" s="310"/>
+      <c r="K5" s="310"/>
+      <c r="L5" s="310"/>
+      <c r="M5" s="310"/>
+      <c r="N5" s="310"/>
+      <c r="O5" s="310"/>
+      <c r="P5" s="310"/>
+      <c r="Q5" s="310"/>
+      <c r="R5" s="310"/>
+      <c r="S5" s="310"/>
+      <c r="T5" s="310"/>
+      <c r="U5" s="310"/>
+      <c r="V5" s="310"/>
+      <c r="W5" s="310"/>
+      <c r="X5" s="310"/>
+      <c r="Y5" s="310"/>
+      <c r="Z5" s="310"/>
+      <c r="AA5" s="310"/>
+      <c r="AB5" s="310"/>
+      <c r="AC5" s="311"/>
+      <c r="AD5" s="311"/>
+      <c r="AE5" s="310"/>
+      <c r="AF5" s="310"/>
+      <c r="AG5" s="311"/>
+      <c r="AH5" s="311"/>
+      <c r="AI5" s="310"/>
+      <c r="AJ5" s="311"/>
+      <c r="AK5" s="311"/>
+      <c r="AL5" s="310"/>
+      <c r="AM5" s="311"/>
+      <c r="AN5" s="312"/>
     </row>
     <row r="6" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -15989,212 +15989,212 @@
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
       <c r="AD6" s="11"/>
-      <c r="AE6" s="334" t="s">
+      <c r="AE6" s="340" t="s">
         <v>151</v>
       </c>
-      <c r="AF6" s="335"/>
-      <c r="AG6" s="335"/>
-      <c r="AH6" s="335"/>
-      <c r="AI6" s="335"/>
-      <c r="AJ6" s="335"/>
-      <c r="AK6" s="335"/>
-      <c r="AL6" s="335"/>
-      <c r="AM6" s="335"/>
-      <c r="AN6" s="335"/>
+      <c r="AF6" s="341"/>
+      <c r="AG6" s="341"/>
+      <c r="AH6" s="341"/>
+      <c r="AI6" s="341"/>
+      <c r="AJ6" s="341"/>
+      <c r="AK6" s="341"/>
+      <c r="AL6" s="341"/>
+      <c r="AM6" s="341"/>
+      <c r="AN6" s="341"/>
     </row>
     <row r="7" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="303" t="s">
+      <c r="A7" s="302" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="336" t="s">
+      <c r="B7" s="342" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="324" t="s">
+      <c r="C7" s="329" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="303" t="s">
+      <c r="D7" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="303" t="s">
+      <c r="E7" s="302" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="303" t="s">
+      <c r="F7" s="302" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="303" t="s">
+      <c r="G7" s="302" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="303" t="s">
+      <c r="H7" s="302" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="303" t="s">
+      <c r="I7" s="302" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="303" t="s">
+      <c r="J7" s="302" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="303" t="s">
+      <c r="K7" s="302" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="333" t="s">
+      <c r="L7" s="336" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="303" t="s">
+      <c r="M7" s="302" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="303" t="s">
+      <c r="N7" s="302" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="313" t="s">
+      <c r="O7" s="318" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="314"/>
-      <c r="Q7" s="314"/>
-      <c r="R7" s="314"/>
-      <c r="S7" s="314"/>
-      <c r="T7" s="314"/>
-      <c r="U7" s="314"/>
-      <c r="V7" s="315"/>
-      <c r="W7" s="303" t="s">
+      <c r="P7" s="319"/>
+      <c r="Q7" s="319"/>
+      <c r="R7" s="319"/>
+      <c r="S7" s="319"/>
+      <c r="T7" s="319"/>
+      <c r="U7" s="319"/>
+      <c r="V7" s="320"/>
+      <c r="W7" s="302" t="s">
         <v>139</v>
       </c>
-      <c r="X7" s="311" t="s">
+      <c r="X7" s="317" t="s">
         <v>13</v>
       </c>
-      <c r="Y7" s="311" t="s">
+      <c r="Y7" s="317" t="s">
         <v>184</v>
       </c>
-      <c r="Z7" s="325" t="s">
+      <c r="Z7" s="330" t="s">
         <v>175</v>
       </c>
-      <c r="AA7" s="303" t="s">
+      <c r="AA7" s="302" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="303" t="s">
+      <c r="AB7" s="302" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="313" t="s">
+      <c r="AC7" s="318" t="s">
         <v>155</v>
       </c>
-      <c r="AD7" s="315"/>
-      <c r="AE7" s="297" t="s">
+      <c r="AD7" s="320"/>
+      <c r="AE7" s="307" t="s">
         <v>17</v>
       </c>
-      <c r="AF7" s="326" t="s">
+      <c r="AF7" s="304" t="s">
         <v>107</v>
       </c>
-      <c r="AG7" s="326" t="s">
+      <c r="AG7" s="304" t="s">
         <v>108</v>
       </c>
-      <c r="AH7" s="326" t="s">
+      <c r="AH7" s="304" t="s">
         <v>106</v>
       </c>
-      <c r="AI7" s="328" t="s">
+      <c r="AI7" s="306" t="s">
         <v>147</v>
       </c>
-      <c r="AJ7" s="297" t="s">
+      <c r="AJ7" s="307" t="s">
         <v>136</v>
       </c>
-      <c r="AK7" s="297" t="s">
+      <c r="AK7" s="307" t="s">
         <v>137</v>
       </c>
-      <c r="AL7" s="303" t="s">
+      <c r="AL7" s="302" t="s">
         <v>135</v>
       </c>
-      <c r="AM7" s="303" t="s">
+      <c r="AM7" s="302" t="s">
         <v>146</v>
       </c>
-      <c r="AN7" s="303" t="s">
+      <c r="AN7" s="302" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="298"/>
-      <c r="B8" s="337"/>
-      <c r="C8" s="324"/>
-      <c r="D8" s="298"/>
-      <c r="E8" s="298"/>
-      <c r="F8" s="298"/>
-      <c r="G8" s="298"/>
-      <c r="H8" s="298"/>
-      <c r="I8" s="298"/>
-      <c r="J8" s="298"/>
-      <c r="K8" s="298"/>
-      <c r="L8" s="298"/>
-      <c r="M8" s="298"/>
-      <c r="N8" s="298"/>
-      <c r="O8" s="316"/>
-      <c r="P8" s="317"/>
-      <c r="Q8" s="317"/>
-      <c r="R8" s="317"/>
-      <c r="S8" s="317"/>
-      <c r="T8" s="317"/>
-      <c r="U8" s="317"/>
-      <c r="V8" s="318"/>
-      <c r="W8" s="298"/>
-      <c r="X8" s="298"/>
-      <c r="Y8" s="298"/>
-      <c r="Z8" s="298"/>
-      <c r="AA8" s="298"/>
-      <c r="AB8" s="298"/>
-      <c r="AC8" s="319"/>
-      <c r="AD8" s="321"/>
-      <c r="AE8" s="298"/>
-      <c r="AF8" s="327"/>
-      <c r="AG8" s="327"/>
-      <c r="AH8" s="328"/>
-      <c r="AI8" s="327"/>
-      <c r="AJ8" s="298"/>
-      <c r="AK8" s="297"/>
-      <c r="AL8" s="298"/>
-      <c r="AM8" s="303"/>
-      <c r="AN8" s="312"/>
+      <c r="A8" s="308"/>
+      <c r="B8" s="343"/>
+      <c r="C8" s="329"/>
+      <c r="D8" s="308"/>
+      <c r="E8" s="308"/>
+      <c r="F8" s="308"/>
+      <c r="G8" s="308"/>
+      <c r="H8" s="308"/>
+      <c r="I8" s="308"/>
+      <c r="J8" s="308"/>
+      <c r="K8" s="308"/>
+      <c r="L8" s="308"/>
+      <c r="M8" s="308"/>
+      <c r="N8" s="308"/>
+      <c r="O8" s="321"/>
+      <c r="P8" s="322"/>
+      <c r="Q8" s="322"/>
+      <c r="R8" s="322"/>
+      <c r="S8" s="322"/>
+      <c r="T8" s="322"/>
+      <c r="U8" s="322"/>
+      <c r="V8" s="323"/>
+      <c r="W8" s="308"/>
+      <c r="X8" s="308"/>
+      <c r="Y8" s="308"/>
+      <c r="Z8" s="308"/>
+      <c r="AA8" s="308"/>
+      <c r="AB8" s="308"/>
+      <c r="AC8" s="324"/>
+      <c r="AD8" s="326"/>
+      <c r="AE8" s="308"/>
+      <c r="AF8" s="305"/>
+      <c r="AG8" s="305"/>
+      <c r="AH8" s="306"/>
+      <c r="AI8" s="305"/>
+      <c r="AJ8" s="308"/>
+      <c r="AK8" s="307"/>
+      <c r="AL8" s="308"/>
+      <c r="AM8" s="302"/>
+      <c r="AN8" s="303"/>
     </row>
     <row r="9" spans="1:43" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="298"/>
-      <c r="B9" s="337"/>
-      <c r="C9" s="324"/>
-      <c r="D9" s="298"/>
-      <c r="E9" s="298"/>
-      <c r="F9" s="298"/>
-      <c r="G9" s="298"/>
-      <c r="H9" s="298"/>
-      <c r="I9" s="298"/>
-      <c r="J9" s="298"/>
-      <c r="K9" s="298"/>
-      <c r="L9" s="298"/>
-      <c r="M9" s="298"/>
-      <c r="N9" s="298"/>
-      <c r="O9" s="319"/>
-      <c r="P9" s="320"/>
-      <c r="Q9" s="320"/>
-      <c r="R9" s="320"/>
-      <c r="S9" s="320"/>
-      <c r="T9" s="320"/>
-      <c r="U9" s="320"/>
-      <c r="V9" s="321"/>
-      <c r="W9" s="298"/>
-      <c r="X9" s="298"/>
-      <c r="Y9" s="298"/>
-      <c r="Z9" s="298"/>
-      <c r="AA9" s="298"/>
-      <c r="AB9" s="298"/>
+      <c r="A9" s="308"/>
+      <c r="B9" s="343"/>
+      <c r="C9" s="329"/>
+      <c r="D9" s="308"/>
+      <c r="E9" s="308"/>
+      <c r="F9" s="308"/>
+      <c r="G9" s="308"/>
+      <c r="H9" s="308"/>
+      <c r="I9" s="308"/>
+      <c r="J9" s="308"/>
+      <c r="K9" s="308"/>
+      <c r="L9" s="308"/>
+      <c r="M9" s="308"/>
+      <c r="N9" s="308"/>
+      <c r="O9" s="324"/>
+      <c r="P9" s="325"/>
+      <c r="Q9" s="325"/>
+      <c r="R9" s="325"/>
+      <c r="S9" s="325"/>
+      <c r="T9" s="325"/>
+      <c r="U9" s="325"/>
+      <c r="V9" s="326"/>
+      <c r="W9" s="308"/>
+      <c r="X9" s="308"/>
+      <c r="Y9" s="308"/>
+      <c r="Z9" s="308"/>
+      <c r="AA9" s="308"/>
+      <c r="AB9" s="308"/>
       <c r="AC9" s="201" t="s">
         <v>153</v>
       </c>
       <c r="AD9" s="178" t="s">
         <v>154</v>
       </c>
-      <c r="AE9" s="298"/>
-      <c r="AF9" s="327"/>
-      <c r="AG9" s="327"/>
-      <c r="AH9" s="328"/>
-      <c r="AI9" s="327"/>
-      <c r="AJ9" s="298"/>
-      <c r="AK9" s="297"/>
-      <c r="AL9" s="298"/>
-      <c r="AM9" s="303"/>
-      <c r="AN9" s="312"/>
+      <c r="AE9" s="308"/>
+      <c r="AF9" s="305"/>
+      <c r="AG9" s="305"/>
+      <c r="AH9" s="306"/>
+      <c r="AI9" s="305"/>
+      <c r="AJ9" s="308"/>
+      <c r="AK9" s="307"/>
+      <c r="AL9" s="308"/>
+      <c r="AM9" s="302"/>
+      <c r="AN9" s="303"/>
       <c r="AO9">
         <f>Z11/W11</f>
         <v>0.50320398224028773</v>
@@ -22368,6 +22368,27 @@
   </sheetData>
   <autoFilter ref="A10:AQ73" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="37">
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AD8"/>
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A2:AB2"/>
@@ -22384,27 +22405,6 @@
     <mergeCell ref="H7:H9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:J9"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AD8"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
   </mergeCells>
   <pageMargins left="0.17" right="0.15748031496062992" top="0.41" bottom="0.23622047244094491" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
@@ -22452,26 +22452,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="304" t="s">
+      <c r="A1" s="309" t="s">
         <v>206</v>
       </c>
-      <c r="B1" s="305"/>
-      <c r="C1" s="306"/>
-      <c r="D1" s="305"/>
-      <c r="E1" s="305"/>
-      <c r="F1" s="305"/>
-      <c r="G1" s="305"/>
-      <c r="H1" s="305"/>
-      <c r="I1" s="305"/>
-      <c r="J1" s="305"/>
-      <c r="K1" s="305"/>
-      <c r="L1" s="305"/>
-      <c r="M1" s="305"/>
-      <c r="N1" s="305"/>
-      <c r="O1" s="305"/>
-      <c r="P1" s="305"/>
-      <c r="Q1" s="305"/>
-      <c r="R1" s="307"/>
+      <c r="B1" s="310"/>
+      <c r="C1" s="311"/>
+      <c r="D1" s="310"/>
+      <c r="E1" s="310"/>
+      <c r="F1" s="310"/>
+      <c r="G1" s="310"/>
+      <c r="H1" s="310"/>
+      <c r="I1" s="310"/>
+      <c r="J1" s="310"/>
+      <c r="K1" s="310"/>
+      <c r="L1" s="310"/>
+      <c r="M1" s="310"/>
+      <c r="N1" s="310"/>
+      <c r="O1" s="310"/>
+      <c r="P1" s="310"/>
+      <c r="Q1" s="310"/>
+      <c r="R1" s="312"/>
       <c r="S1" s="261"/>
       <c r="T1" s="261"/>
       <c r="U1" s="261"/>
@@ -22492,26 +22492,26 @@
       <c r="AH1" s="160"/>
     </row>
     <row r="2" spans="1:40" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="308" t="s">
+      <c r="A2" s="313" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="305"/>
-      <c r="C2" s="306"/>
-      <c r="D2" s="305"/>
-      <c r="E2" s="305"/>
-      <c r="F2" s="305"/>
-      <c r="G2" s="305"/>
-      <c r="H2" s="305"/>
-      <c r="I2" s="305"/>
-      <c r="J2" s="305"/>
-      <c r="K2" s="305"/>
-      <c r="L2" s="305"/>
-      <c r="M2" s="305"/>
-      <c r="N2" s="305"/>
-      <c r="O2" s="305"/>
-      <c r="P2" s="305"/>
-      <c r="Q2" s="305"/>
-      <c r="R2" s="307"/>
+      <c r="B2" s="310"/>
+      <c r="C2" s="311"/>
+      <c r="D2" s="310"/>
+      <c r="E2" s="310"/>
+      <c r="F2" s="310"/>
+      <c r="G2" s="310"/>
+      <c r="H2" s="310"/>
+      <c r="I2" s="310"/>
+      <c r="J2" s="310"/>
+      <c r="K2" s="310"/>
+      <c r="L2" s="310"/>
+      <c r="M2" s="310"/>
+      <c r="N2" s="310"/>
+      <c r="O2" s="310"/>
+      <c r="P2" s="310"/>
+      <c r="Q2" s="310"/>
+      <c r="R2" s="312"/>
       <c r="S2" s="261"/>
       <c r="T2" s="261"/>
       <c r="U2" s="261"/>
@@ -22566,80 +22566,80 @@
       <c r="AH3" s="160"/>
     </row>
     <row r="4" spans="1:40" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="309" t="s">
+      <c r="A4" s="314" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="305"/>
-      <c r="C4" s="306"/>
-      <c r="D4" s="305"/>
-      <c r="E4" s="305"/>
-      <c r="F4" s="305"/>
-      <c r="G4" s="305"/>
-      <c r="H4" s="305"/>
-      <c r="I4" s="305"/>
-      <c r="J4" s="305"/>
-      <c r="K4" s="305"/>
-      <c r="L4" s="305"/>
-      <c r="M4" s="305"/>
-      <c r="N4" s="305"/>
-      <c r="O4" s="305"/>
-      <c r="P4" s="305"/>
-      <c r="Q4" s="305"/>
-      <c r="R4" s="305"/>
-      <c r="S4" s="306"/>
-      <c r="T4" s="306"/>
-      <c r="U4" s="306"/>
-      <c r="V4" s="306"/>
-      <c r="W4" s="306"/>
-      <c r="X4" s="305"/>
-      <c r="Y4" s="305"/>
-      <c r="Z4" s="306"/>
-      <c r="AA4" s="306"/>
-      <c r="AB4" s="305"/>
-      <c r="AC4" s="306"/>
-      <c r="AD4" s="306"/>
-      <c r="AE4" s="305"/>
-      <c r="AF4" s="306"/>
-      <c r="AG4" s="306"/>
-      <c r="AH4" s="307"/>
+      <c r="B4" s="310"/>
+      <c r="C4" s="311"/>
+      <c r="D4" s="310"/>
+      <c r="E4" s="310"/>
+      <c r="F4" s="310"/>
+      <c r="G4" s="310"/>
+      <c r="H4" s="310"/>
+      <c r="I4" s="310"/>
+      <c r="J4" s="310"/>
+      <c r="K4" s="310"/>
+      <c r="L4" s="310"/>
+      <c r="M4" s="310"/>
+      <c r="N4" s="310"/>
+      <c r="O4" s="310"/>
+      <c r="P4" s="310"/>
+      <c r="Q4" s="310"/>
+      <c r="R4" s="310"/>
+      <c r="S4" s="311"/>
+      <c r="T4" s="311"/>
+      <c r="U4" s="311"/>
+      <c r="V4" s="311"/>
+      <c r="W4" s="311"/>
+      <c r="X4" s="310"/>
+      <c r="Y4" s="310"/>
+      <c r="Z4" s="311"/>
+      <c r="AA4" s="311"/>
+      <c r="AB4" s="310"/>
+      <c r="AC4" s="311"/>
+      <c r="AD4" s="311"/>
+      <c r="AE4" s="310"/>
+      <c r="AF4" s="311"/>
+      <c r="AG4" s="311"/>
+      <c r="AH4" s="312"/>
     </row>
     <row r="5" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="310" t="s">
-        <v>229</v>
-      </c>
-      <c r="B5" s="310"/>
-      <c r="C5" s="310"/>
-      <c r="D5" s="310"/>
-      <c r="E5" s="310"/>
-      <c r="F5" s="310"/>
-      <c r="G5" s="310"/>
-      <c r="H5" s="310"/>
-      <c r="I5" s="310"/>
-      <c r="J5" s="310"/>
-      <c r="K5" s="310"/>
-      <c r="L5" s="310"/>
-      <c r="M5" s="310"/>
-      <c r="N5" s="310"/>
-      <c r="O5" s="310"/>
-      <c r="P5" s="310"/>
-      <c r="Q5" s="310"/>
-      <c r="R5" s="310"/>
-      <c r="S5" s="310"/>
-      <c r="T5" s="310"/>
-      <c r="U5" s="310"/>
-      <c r="V5" s="310"/>
-      <c r="W5" s="310"/>
-      <c r="X5" s="310"/>
-      <c r="Y5" s="310"/>
-      <c r="Z5" s="310"/>
-      <c r="AA5" s="310"/>
-      <c r="AB5" s="310"/>
-      <c r="AC5" s="310"/>
-      <c r="AD5" s="310"/>
-      <c r="AE5" s="310"/>
-      <c r="AF5" s="310"/>
-      <c r="AG5" s="343"/>
-      <c r="AH5" s="310"/>
+      <c r="A5" s="315" t="s">
+        <v>235</v>
+      </c>
+      <c r="B5" s="315"/>
+      <c r="C5" s="315"/>
+      <c r="D5" s="315"/>
+      <c r="E5" s="315"/>
+      <c r="F5" s="315"/>
+      <c r="G5" s="315"/>
+      <c r="H5" s="315"/>
+      <c r="I5" s="315"/>
+      <c r="J5" s="315"/>
+      <c r="K5" s="315"/>
+      <c r="L5" s="315"/>
+      <c r="M5" s="315"/>
+      <c r="N5" s="315"/>
+      <c r="O5" s="315"/>
+      <c r="P5" s="315"/>
+      <c r="Q5" s="315"/>
+      <c r="R5" s="315"/>
+      <c r="S5" s="315"/>
+      <c r="T5" s="315"/>
+      <c r="U5" s="315"/>
+      <c r="V5" s="315"/>
+      <c r="W5" s="315"/>
+      <c r="X5" s="315"/>
+      <c r="Y5" s="315"/>
+      <c r="Z5" s="315"/>
+      <c r="AA5" s="315"/>
+      <c r="AB5" s="315"/>
+      <c r="AC5" s="315"/>
+      <c r="AD5" s="315"/>
+      <c r="AE5" s="315"/>
+      <c r="AF5" s="315"/>
+      <c r="AG5" s="316"/>
+      <c r="AH5" s="315"/>
     </row>
     <row r="6" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -22664,186 +22664,186 @@
       <c r="R6" s="11"/>
       <c r="S6" s="11"/>
       <c r="T6" s="11"/>
-      <c r="U6" s="322" t="s">
+      <c r="U6" s="327" t="s">
         <v>151</v>
       </c>
-      <c r="V6" s="322"/>
-      <c r="W6" s="322"/>
-      <c r="X6" s="322"/>
-      <c r="Y6" s="322"/>
-      <c r="Z6" s="322"/>
-      <c r="AA6" s="322"/>
-      <c r="AB6" s="322"/>
-      <c r="AC6" s="322"/>
-      <c r="AD6" s="322"/>
-      <c r="AE6" s="322"/>
-      <c r="AF6" s="322"/>
-      <c r="AG6" s="322"/>
-      <c r="AH6" s="322"/>
+      <c r="V6" s="327"/>
+      <c r="W6" s="327"/>
+      <c r="X6" s="327"/>
+      <c r="Y6" s="327"/>
+      <c r="Z6" s="327"/>
+      <c r="AA6" s="327"/>
+      <c r="AB6" s="327"/>
+      <c r="AC6" s="327"/>
+      <c r="AD6" s="327"/>
+      <c r="AE6" s="327"/>
+      <c r="AF6" s="327"/>
+      <c r="AG6" s="327"/>
+      <c r="AH6" s="327"/>
     </row>
     <row r="7" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="303" t="s">
+      <c r="A7" s="302" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="303" t="s">
+      <c r="B7" s="302" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="324" t="s">
+      <c r="C7" s="329" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="303" t="s">
+      <c r="D7" s="302" t="s">
         <v>140</v>
       </c>
-      <c r="E7" s="313" t="s">
+      <c r="E7" s="318" t="s">
         <v>138</v>
       </c>
-      <c r="F7" s="314"/>
-      <c r="G7" s="314"/>
-      <c r="H7" s="314"/>
-      <c r="I7" s="314"/>
-      <c r="J7" s="314"/>
-      <c r="K7" s="314"/>
-      <c r="L7" s="315"/>
-      <c r="M7" s="303" t="s">
+      <c r="F7" s="319"/>
+      <c r="G7" s="319"/>
+      <c r="H7" s="319"/>
+      <c r="I7" s="319"/>
+      <c r="J7" s="319"/>
+      <c r="K7" s="319"/>
+      <c r="L7" s="320"/>
+      <c r="M7" s="302" t="s">
         <v>202</v>
       </c>
-      <c r="N7" s="311" t="s">
+      <c r="N7" s="317" t="s">
         <v>13</v>
       </c>
-      <c r="O7" s="311" t="s">
-        <v>224</v>
-      </c>
-      <c r="P7" s="325" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q7" s="303" t="s">
+      <c r="O7" s="317" t="s">
+        <v>236</v>
+      </c>
+      <c r="P7" s="330" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q7" s="302" t="s">
         <v>15</v>
       </c>
-      <c r="R7" s="303" t="s">
+      <c r="R7" s="302" t="s">
         <v>16</v>
       </c>
-      <c r="S7" s="299" t="s">
+      <c r="S7" s="331" t="s">
+        <v>225</v>
+      </c>
+      <c r="T7" s="331"/>
+      <c r="U7" s="331"/>
+      <c r="V7" s="332" t="s">
+        <v>211</v>
+      </c>
+      <c r="W7" s="332" t="s">
+        <v>215</v>
+      </c>
+      <c r="X7" s="307" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="304" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z7" s="304" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA7" s="304" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB7" s="306" t="s">
+        <v>147</v>
+      </c>
+      <c r="AC7" s="307" t="s">
+        <v>136</v>
+      </c>
+      <c r="AD7" s="307" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE7" s="302" t="s">
+        <v>135</v>
+      </c>
+      <c r="AF7" s="302" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG7" s="302" t="s">
         <v>227</v>
       </c>
-      <c r="T7" s="299"/>
-      <c r="U7" s="299"/>
-      <c r="V7" s="300" t="s">
-        <v>212</v>
-      </c>
-      <c r="W7" s="300" t="s">
-        <v>216</v>
-      </c>
-      <c r="X7" s="297" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y7" s="326" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z7" s="326" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA7" s="326" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB7" s="328" t="s">
-        <v>147</v>
-      </c>
-      <c r="AC7" s="297" t="s">
-        <v>136</v>
-      </c>
-      <c r="AD7" s="297" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE7" s="303" t="s">
-        <v>135</v>
-      </c>
-      <c r="AF7" s="303" t="s">
-        <v>146</v>
-      </c>
-      <c r="AG7" s="303" t="s">
-        <v>231</v>
-      </c>
-      <c r="AH7" s="303" t="s">
+      <c r="AH7" s="302" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="298"/>
-      <c r="B8" s="323"/>
-      <c r="C8" s="324"/>
-      <c r="D8" s="312"/>
-      <c r="E8" s="316"/>
-      <c r="F8" s="317"/>
-      <c r="G8" s="317"/>
-      <c r="H8" s="317"/>
-      <c r="I8" s="317"/>
-      <c r="J8" s="317"/>
-      <c r="K8" s="317"/>
-      <c r="L8" s="318"/>
-      <c r="M8" s="298"/>
-      <c r="N8" s="298"/>
-      <c r="O8" s="298"/>
-      <c r="P8" s="298"/>
-      <c r="Q8" s="298"/>
-      <c r="R8" s="298"/>
-      <c r="S8" s="299"/>
-      <c r="T8" s="299"/>
-      <c r="U8" s="299"/>
-      <c r="V8" s="301"/>
-      <c r="W8" s="301"/>
-      <c r="X8" s="298"/>
-      <c r="Y8" s="327"/>
-      <c r="Z8" s="327"/>
-      <c r="AA8" s="328"/>
-      <c r="AB8" s="327"/>
-      <c r="AC8" s="298"/>
-      <c r="AD8" s="297"/>
-      <c r="AE8" s="298"/>
-      <c r="AF8" s="303"/>
-      <c r="AG8" s="303"/>
-      <c r="AH8" s="312"/>
+      <c r="A8" s="308"/>
+      <c r="B8" s="328"/>
+      <c r="C8" s="329"/>
+      <c r="D8" s="303"/>
+      <c r="E8" s="321"/>
+      <c r="F8" s="322"/>
+      <c r="G8" s="322"/>
+      <c r="H8" s="322"/>
+      <c r="I8" s="322"/>
+      <c r="J8" s="322"/>
+      <c r="K8" s="322"/>
+      <c r="L8" s="323"/>
+      <c r="M8" s="308"/>
+      <c r="N8" s="308"/>
+      <c r="O8" s="308"/>
+      <c r="P8" s="308"/>
+      <c r="Q8" s="308"/>
+      <c r="R8" s="308"/>
+      <c r="S8" s="331"/>
+      <c r="T8" s="331"/>
+      <c r="U8" s="331"/>
+      <c r="V8" s="333"/>
+      <c r="W8" s="333"/>
+      <c r="X8" s="308"/>
+      <c r="Y8" s="305"/>
+      <c r="Z8" s="305"/>
+      <c r="AA8" s="306"/>
+      <c r="AB8" s="305"/>
+      <c r="AC8" s="308"/>
+      <c r="AD8" s="307"/>
+      <c r="AE8" s="308"/>
+      <c r="AF8" s="302"/>
+      <c r="AG8" s="302"/>
+      <c r="AH8" s="303"/>
     </row>
     <row r="9" spans="1:40" ht="104.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="298"/>
-      <c r="B9" s="323"/>
-      <c r="C9" s="324"/>
-      <c r="D9" s="312"/>
-      <c r="E9" s="319"/>
-      <c r="F9" s="320"/>
-      <c r="G9" s="320"/>
-      <c r="H9" s="320"/>
-      <c r="I9" s="320"/>
-      <c r="J9" s="320"/>
-      <c r="K9" s="320"/>
-      <c r="L9" s="321"/>
-      <c r="M9" s="298"/>
-      <c r="N9" s="298"/>
-      <c r="O9" s="298"/>
-      <c r="P9" s="298"/>
-      <c r="Q9" s="298"/>
-      <c r="R9" s="298"/>
+      <c r="A9" s="308"/>
+      <c r="B9" s="328"/>
+      <c r="C9" s="329"/>
+      <c r="D9" s="303"/>
+      <c r="E9" s="324"/>
+      <c r="F9" s="325"/>
+      <c r="G9" s="325"/>
+      <c r="H9" s="325"/>
+      <c r="I9" s="325"/>
+      <c r="J9" s="325"/>
+      <c r="K9" s="325"/>
+      <c r="L9" s="326"/>
+      <c r="M9" s="308"/>
+      <c r="N9" s="308"/>
+      <c r="O9" s="308"/>
+      <c r="P9" s="308"/>
+      <c r="Q9" s="308"/>
+      <c r="R9" s="308"/>
       <c r="S9" s="263" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="T9" s="263" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="U9" s="263" t="s">
-        <v>211</v>
-      </c>
-      <c r="V9" s="302"/>
-      <c r="W9" s="302"/>
-      <c r="X9" s="298"/>
-      <c r="Y9" s="327"/>
-      <c r="Z9" s="327"/>
-      <c r="AA9" s="328"/>
-      <c r="AB9" s="327"/>
-      <c r="AC9" s="298"/>
-      <c r="AD9" s="297"/>
-      <c r="AE9" s="298"/>
-      <c r="AF9" s="303"/>
-      <c r="AG9" s="303"/>
-      <c r="AH9" s="312"/>
+        <v>238</v>
+      </c>
+      <c r="V9" s="334"/>
+      <c r="W9" s="334"/>
+      <c r="X9" s="308"/>
+      <c r="Y9" s="305"/>
+      <c r="Z9" s="305"/>
+      <c r="AA9" s="306"/>
+      <c r="AB9" s="305"/>
+      <c r="AC9" s="308"/>
+      <c r="AD9" s="307"/>
+      <c r="AE9" s="308"/>
+      <c r="AF9" s="302"/>
+      <c r="AG9" s="302"/>
+      <c r="AH9" s="303"/>
       <c r="AI9">
         <f>P12/M12</f>
         <v>0.75409626603409796</v>
@@ -22890,7 +22890,7 @@
         <v>209</v>
       </c>
       <c r="L10" s="129" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M10" s="28">
         <v>5</v>
@@ -22942,7 +22942,7 @@
     <row r="11" spans="1:40" ht="28.15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28"/>
       <c r="B11" s="275" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C11" s="103"/>
       <c r="D11" s="280">
@@ -23010,7 +23010,7 @@
     <row r="12" spans="1:40" s="102" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="96"/>
       <c r="B12" s="275" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C12" s="104"/>
       <c r="D12" s="264">
@@ -23285,8 +23285,8 @@
         <f>M14-P14</f>
         <v>0</v>
       </c>
-      <c r="AG14" s="338" t="s">
-        <v>232</v>
+      <c r="AG14" s="297" t="s">
+        <v>228</v>
       </c>
       <c r="AH14" s="141" t="s">
         <v>27</v>
@@ -23384,8 +23384,8 @@
         <f>M15-P15</f>
         <v>0</v>
       </c>
-      <c r="AG15" s="338" t="s">
-        <v>232</v>
+      <c r="AG15" s="297" t="s">
+        <v>228</v>
       </c>
       <c r="AH15" s="141" t="s">
         <v>29</v>
@@ -23543,8 +23543,8 @@
         <f>M17-P17</f>
         <v>0</v>
       </c>
-      <c r="AG17" s="339" t="s">
-        <v>233</v>
+      <c r="AG17" s="298" t="s">
+        <v>229</v>
       </c>
       <c r="AH17" s="144" t="s">
         <v>39</v>
@@ -23656,7 +23656,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="268" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="W19" s="268">
         <v>50</v>
@@ -23685,8 +23685,8 @@
         <f>M19-P19</f>
         <v>0</v>
       </c>
-      <c r="AG19" s="340" t="s">
-        <v>234</v>
+      <c r="AG19" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH19" s="166"/>
     </row>
@@ -23744,7 +23744,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="268" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="W20" s="268">
         <v>1600</v>
@@ -23775,8 +23775,8 @@
         <f>M20-P20</f>
         <v>11825.398000000001</v>
       </c>
-      <c r="AG20" s="339" t="s">
-        <v>233</v>
+      <c r="AG20" s="298" t="s">
+        <v>229</v>
       </c>
       <c r="AH20" s="147" t="s">
         <v>61</v>
@@ -23861,8 +23861,8 @@
         <f>M21-P21</f>
         <v>7126.9330000000009</v>
       </c>
-      <c r="AG21" s="339" t="s">
-        <v>233</v>
+      <c r="AG21" s="298" t="s">
+        <v>229</v>
       </c>
       <c r="AH21" s="169"/>
       <c r="AJ21" s="18">
@@ -23923,7 +23923,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="268" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="W22" s="268">
         <v>863</v>
@@ -23954,8 +23954,8 @@
         <f>M22-P22</f>
         <v>132.34000000000015</v>
       </c>
-      <c r="AG22" s="340" t="s">
-        <v>234</v>
+      <c r="AG22" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH22" s="167"/>
       <c r="AI22" s="18">
@@ -24034,7 +24034,7 @@
       <c r="AE23" s="77"/>
       <c r="AF23" s="157"/>
       <c r="AG23" s="122" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AH23" s="167"/>
       <c r="AI23" s="18"/>
@@ -24103,7 +24103,7 @@
       <c r="AE24" s="77"/>
       <c r="AF24" s="157"/>
       <c r="AG24" s="122" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AH24" s="167"/>
       <c r="AI24" s="18"/>
@@ -24166,7 +24166,7 @@
       <c r="AE25" s="77"/>
       <c r="AF25" s="157"/>
       <c r="AG25" s="122" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AH25" s="167"/>
       <c r="AI25" s="18"/>
@@ -24228,8 +24228,8 @@
       <c r="AD26" s="126"/>
       <c r="AE26" s="77"/>
       <c r="AF26" s="157"/>
-      <c r="AG26" s="340" t="s">
-        <v>234</v>
+      <c r="AG26" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH26" s="167"/>
       <c r="AI26" s="18"/>
@@ -24292,7 +24292,7 @@
       <c r="AE27" s="77"/>
       <c r="AF27" s="157"/>
       <c r="AG27" s="122" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AH27" s="167"/>
       <c r="AI27" s="18"/>
@@ -24354,8 +24354,8 @@
       <c r="AD28" s="126"/>
       <c r="AE28" s="77"/>
       <c r="AF28" s="157"/>
-      <c r="AG28" s="340" t="s">
-        <v>234</v>
+      <c r="AG28" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH28" s="167"/>
       <c r="AI28" s="18"/>
@@ -24417,8 +24417,8 @@
       <c r="AD29" s="126"/>
       <c r="AE29" s="77"/>
       <c r="AF29" s="157"/>
-      <c r="AG29" s="338" t="s">
-        <v>232</v>
+      <c r="AG29" s="297" t="s">
+        <v>228</v>
       </c>
       <c r="AH29" s="167"/>
       <c r="AI29" s="18"/>
@@ -24481,8 +24481,8 @@
       <c r="AD30" s="126"/>
       <c r="AE30" s="77"/>
       <c r="AF30" s="157"/>
-      <c r="AG30" s="340" t="s">
-        <v>234</v>
+      <c r="AG30" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH30" s="167"/>
       <c r="AI30" s="18"/>
@@ -24544,8 +24544,8 @@
       <c r="AD31" s="126"/>
       <c r="AE31" s="77"/>
       <c r="AF31" s="157"/>
-      <c r="AG31" s="340" t="s">
-        <v>234</v>
+      <c r="AG31" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH31" s="167"/>
       <c r="AI31" s="18"/>
@@ -24608,7 +24608,7 @@
       <c r="AE32" s="77"/>
       <c r="AF32" s="157"/>
       <c r="AG32" s="122" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AH32" s="167"/>
       <c r="AI32" s="18"/>
@@ -24671,7 +24671,7 @@
       <c r="AE33" s="77"/>
       <c r="AF33" s="157"/>
       <c r="AG33" s="122" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AH33" s="167"/>
       <c r="AI33" s="18"/>
@@ -24733,8 +24733,8 @@
       <c r="AD34" s="126"/>
       <c r="AE34" s="77"/>
       <c r="AF34" s="157"/>
-      <c r="AG34" s="340" t="s">
-        <v>234</v>
+      <c r="AG34" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH34" s="167"/>
       <c r="AI34" s="18"/>
@@ -24793,7 +24793,7 @@
       <c r="AD35" s="126"/>
       <c r="AE35" s="67"/>
       <c r="AF35" s="64"/>
-      <c r="AG35" s="341"/>
+      <c r="AG35" s="300"/>
       <c r="AH35" s="170"/>
     </row>
     <row r="36" spans="1:39" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -24877,8 +24877,8 @@
         <f t="shared" ref="AF36:AF62" si="11">M36-P36</f>
         <v>62</v>
       </c>
-      <c r="AG36" s="339" t="s">
-        <v>233</v>
+      <c r="AG36" s="298" t="s">
+        <v>229</v>
       </c>
       <c r="AH36" s="168"/>
       <c r="AL36" s="18">
@@ -24961,8 +24961,8 @@
         <f t="shared" si="11"/>
         <v>271.89300000000003</v>
       </c>
-      <c r="AG37" s="338" t="s">
-        <v>232</v>
+      <c r="AG37" s="297" t="s">
+        <v>228</v>
       </c>
       <c r="AH37" s="169"/>
       <c r="AJ37" s="19">
@@ -25057,8 +25057,8 @@
         <f t="shared" si="11"/>
         <v>4834.7999999999993</v>
       </c>
-      <c r="AG38" s="340" t="s">
-        <v>234</v>
+      <c r="AG38" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH38" s="167"/>
       <c r="AI38" s="22"/>
@@ -25124,7 +25124,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="268" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="W39" s="268">
         <v>148</v>
@@ -25155,8 +25155,8 @@
         <f t="shared" si="11"/>
         <v>4912.57</v>
       </c>
-      <c r="AG39" s="338" t="s">
-        <v>232</v>
+      <c r="AG39" s="297" t="s">
+        <v>228</v>
       </c>
       <c r="AH39" s="166"/>
       <c r="AJ39" s="19"/>
@@ -25217,7 +25217,7 @@
         <v>2158</v>
       </c>
       <c r="V40" s="268" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="W40" s="268">
         <v>11382</v>
@@ -25249,7 +25249,7 @@
         <v>16038.010000000002</v>
       </c>
       <c r="AG40" s="122" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AH40" s="169"/>
       <c r="AL40">
@@ -25337,8 +25337,8 @@
         <f t="shared" si="11"/>
         <v>10021.699999999997</v>
       </c>
-      <c r="AG41" s="340" t="s">
-        <v>234</v>
+      <c r="AG41" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH41" s="169"/>
       <c r="AL41" s="18">
@@ -25423,8 +25423,8 @@
         <f t="shared" si="11"/>
         <v>420</v>
       </c>
-      <c r="AG42" s="340" t="s">
-        <v>234</v>
+      <c r="AG42" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH42" s="169"/>
       <c r="AI42" s="18">
@@ -25512,7 +25512,7 @@
         <v>125</v>
       </c>
       <c r="AG43" s="122" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AH43" s="167"/>
       <c r="AI43" s="18">
@@ -25599,8 +25599,8 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AG44" s="339" t="s">
-        <v>233</v>
+      <c r="AG44" s="298" t="s">
+        <v>229</v>
       </c>
       <c r="AH44" s="174" t="s">
         <v>74</v>
@@ -25686,8 +25686,8 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AG45" s="338" t="s">
-        <v>232</v>
+      <c r="AG45" s="297" t="s">
+        <v>228</v>
       </c>
       <c r="AH45" s="166"/>
       <c r="AI45">
@@ -25771,8 +25771,8 @@
         <f t="shared" si="11"/>
         <v>191</v>
       </c>
-      <c r="AG46" s="340" t="s">
-        <v>234</v>
+      <c r="AG46" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH46" s="167"/>
       <c r="AI46" s="19">
@@ -25859,7 +25859,7 @@
         <v>33</v>
       </c>
       <c r="AG47" s="122" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AH47" s="166"/>
       <c r="AK47">
@@ -25941,8 +25941,8 @@
         <f t="shared" si="11"/>
         <v>10</v>
       </c>
-      <c r="AG48" s="340" t="s">
-        <v>234</v>
+      <c r="AG48" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH48" s="166"/>
     </row>
@@ -26022,7 +26022,7 @@
         <v>10</v>
       </c>
       <c r="AG49" s="122" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AH49" s="166"/>
     </row>
@@ -26101,8 +26101,8 @@
         <f t="shared" si="11"/>
         <v>20</v>
       </c>
-      <c r="AG50" s="338" t="s">
-        <v>232</v>
+      <c r="AG50" s="297" t="s">
+        <v>228</v>
       </c>
       <c r="AH50" s="166"/>
     </row>
@@ -26181,8 +26181,8 @@
         <f t="shared" si="11"/>
         <v>50</v>
       </c>
-      <c r="AG51" s="338" t="s">
-        <v>232</v>
+      <c r="AG51" s="297" t="s">
+        <v>228</v>
       </c>
       <c r="AH51" s="166"/>
     </row>
@@ -26261,8 +26261,8 @@
         <f t="shared" si="11"/>
         <v>50</v>
       </c>
-      <c r="AG52" s="340" t="s">
-        <v>234</v>
+      <c r="AG52" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH52" s="171"/>
       <c r="AN52" s="176">
@@ -26345,8 +26345,8 @@
         <f t="shared" si="11"/>
         <v>15</v>
       </c>
-      <c r="AG53" s="340" t="s">
-        <v>234</v>
+      <c r="AG53" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH53" s="167"/>
       <c r="AN53" s="176">
@@ -26430,7 +26430,7 @@
         <v>33</v>
       </c>
       <c r="AG54" s="122" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AH54" s="167"/>
     </row>
@@ -26509,8 +26509,8 @@
         <f t="shared" si="11"/>
         <v>50</v>
       </c>
-      <c r="AG55" s="340" t="s">
-        <v>234</v>
+      <c r="AG55" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH55" s="167"/>
     </row>
@@ -26589,8 +26589,8 @@
         <f t="shared" si="11"/>
         <v>50</v>
       </c>
-      <c r="AG56" s="338" t="s">
-        <v>232</v>
+      <c r="AG56" s="297" t="s">
+        <v>228</v>
       </c>
       <c r="AH56" s="167"/>
     </row>
@@ -26670,7 +26670,7 @@
         <v>6</v>
       </c>
       <c r="AG57" s="122" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AH57" s="167"/>
     </row>
@@ -26750,7 +26750,7 @@
         <v>23</v>
       </c>
       <c r="AG58" s="122" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AH58" s="167"/>
     </row>
@@ -26829,8 +26829,8 @@
         <f t="shared" si="11"/>
         <v>25</v>
       </c>
-      <c r="AG59" s="340" t="s">
-        <v>234</v>
+      <c r="AG59" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH59" s="167"/>
     </row>
@@ -26911,8 +26911,8 @@
         <f t="shared" si="11"/>
         <v>265</v>
       </c>
-      <c r="AG60" s="340" t="s">
-        <v>234</v>
+      <c r="AG60" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH60" s="167"/>
       <c r="AL60">
@@ -26999,8 +26999,8 @@
         <f t="shared" si="11"/>
         <v>27898.839000000007</v>
       </c>
-      <c r="AG61" s="338" t="s">
-        <v>232</v>
+      <c r="AG61" s="297" t="s">
+        <v>228</v>
       </c>
       <c r="AH61" s="167"/>
       <c r="AL61">
@@ -27091,8 +27091,8 @@
         <f t="shared" si="11"/>
         <v>62200.460000000021</v>
       </c>
-      <c r="AG62" s="340" t="s">
-        <v>234</v>
+      <c r="AG62" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH62" s="147" t="s">
         <v>152</v>
@@ -27169,7 +27169,7 @@
       <c r="AD63" s="126"/>
       <c r="AE63" s="67"/>
       <c r="AF63" s="67"/>
-      <c r="AG63" s="342"/>
+      <c r="AG63" s="301"/>
       <c r="AH63" s="172"/>
       <c r="AJ63" s="21">
         <f>AJ62-P62</f>
@@ -27256,7 +27256,7 @@
       <c r="AE64" s="67"/>
       <c r="AF64" s="67"/>
       <c r="AG64" s="173" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="AH64" s="173"/>
       <c r="AK64" s="24">
@@ -27342,7 +27342,7 @@
       <c r="AE65" s="67"/>
       <c r="AF65" s="67"/>
       <c r="AG65" s="173" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AH65" s="173"/>
       <c r="AL65">
@@ -27427,7 +27427,7 @@
       <c r="AE66" s="64"/>
       <c r="AF66" s="64"/>
       <c r="AG66" s="173" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AH66" s="173"/>
       <c r="AL66" s="18">
@@ -27513,8 +27513,8 @@
       </c>
       <c r="AE67" s="67"/>
       <c r="AF67" s="67"/>
-      <c r="AG67" s="338" t="s">
-        <v>232</v>
+      <c r="AG67" s="297" t="s">
+        <v>228</v>
       </c>
       <c r="AH67" s="173"/>
     </row>
@@ -27591,7 +27591,7 @@
       <c r="AE68" s="179"/>
       <c r="AF68" s="179"/>
       <c r="AG68" s="173" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="AH68" s="173"/>
       <c r="AL68">
@@ -27665,8 +27665,8 @@
       <c r="AD69" s="179"/>
       <c r="AE69" s="179"/>
       <c r="AF69" s="179"/>
-      <c r="AG69" s="339" t="s">
-        <v>233</v>
+      <c r="AG69" s="298" t="s">
+        <v>229</v>
       </c>
       <c r="AH69" s="200"/>
     </row>
@@ -27736,8 +27736,8 @@
       <c r="AD70" s="184"/>
       <c r="AE70" s="184"/>
       <c r="AF70" s="184"/>
-      <c r="AG70" s="339" t="s">
-        <v>233</v>
+      <c r="AG70" s="298" t="s">
+        <v>229</v>
       </c>
       <c r="AH70" s="173"/>
     </row>
@@ -27808,7 +27808,7 @@
       <c r="AE71" s="179"/>
       <c r="AF71" s="179"/>
       <c r="AG71" s="173" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AH71" s="173"/>
     </row>
@@ -27869,8 +27869,8 @@
       <c r="AD72" s="256"/>
       <c r="AE72" s="256"/>
       <c r="AF72" s="256"/>
-      <c r="AG72" s="340" t="s">
-        <v>234</v>
+      <c r="AG72" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH72" s="173"/>
     </row>
@@ -27931,8 +27931,8 @@
       <c r="AD73" s="256"/>
       <c r="AE73" s="256"/>
       <c r="AF73" s="256"/>
-      <c r="AG73" s="340" t="s">
-        <v>234</v>
+      <c r="AG73" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH73" s="173"/>
     </row>
@@ -27993,8 +27993,8 @@
       <c r="AD74" s="256"/>
       <c r="AE74" s="256"/>
       <c r="AF74" s="256"/>
-      <c r="AG74" s="340" t="s">
-        <v>234</v>
+      <c r="AG74" s="299" t="s">
+        <v>230</v>
       </c>
       <c r="AH74" s="173"/>
     </row>
@@ -28003,10 +28003,10 @@
         <v>12</v>
       </c>
       <c r="B75" s="254" t="s">
+        <v>220</v>
+      </c>
+      <c r="C75" s="255" t="s">
         <v>221</v>
-      </c>
-      <c r="C75" s="255" t="s">
-        <v>222</v>
       </c>
       <c r="D75" s="59"/>
       <c r="E75" s="257"/>
@@ -28050,10 +28050,10 @@
         <v>13</v>
       </c>
       <c r="B76" s="254" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C76" s="255" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D76" s="59"/>
       <c r="E76" s="257"/>
@@ -29049,15 +29049,11 @@
   </sheetData>
   <autoFilter ref="A10:AK77" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="30">
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AC9"/>
-    <mergeCell ref="AD7:AD9"/>
-    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="S7:U8"/>
+    <mergeCell ref="V7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="AE7:AE9"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A4:AH4"/>
@@ -29074,11 +29070,15 @@
     <mergeCell ref="P7:P9"/>
     <mergeCell ref="Q7:Q9"/>
     <mergeCell ref="R7:R9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="S7:U8"/>
-    <mergeCell ref="V7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AC9"/>
+    <mergeCell ref="AD7:AD9"/>
+    <mergeCell ref="AF7:AF9"/>
   </mergeCells>
   <pageMargins left="0.55000000000000004" right="0.15748031496062992" top="0.39370078740157483" bottom="0.23622047244094491" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" r:id="rId1"/>

--- a/report/bao-cao.xlsx
+++ b/report/bao-cao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HXuan\BaocaoGiaingan\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CC5902-6939-4B8E-A8F7-86369AD55D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF136ABB-F198-41DB-832E-71F03BA04BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,17 +16,17 @@
     <sheet name="bc" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="BAO CAO 30-06 (2)" sheetId="3" state="hidden" r:id="rId2"/>
     <sheet name="BAO CAO 30-06 (KHV mới)" sheetId="4" state="hidden" r:id="rId3"/>
-    <sheet name="BAO CAO 12-10-2026" sheetId="5" r:id="rId4"/>
+    <sheet name="BAO CAO 17-10-2026" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BAO CAO 12-10-2026'!$A$10:$AK$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BAO CAO 17-10-2026'!$A$10:$AK$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BAO CAO 30-06 (2)'!$A$10:$AQ$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BAO CAO 30-06 (KHV mới)'!$A$10:$AQ$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">bc!$A$10:$AP$80</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'BAO CAO 12-10-2026'!$A$1:$AH$77</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'BAO CAO 17-10-2026'!$A$1:$AH$77</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'BAO CAO 30-06 (2)'!$A$1:$AN$58</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'BAO CAO 30-06 (KHV mới)'!$A$1:$AN$79</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'BAO CAO 12-10-2026'!$7:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'BAO CAO 17-10-2026'!$7:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'BAO CAO 30-06 (2)'!$7:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'BAO CAO 30-06 (KHV mới)'!$7:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">bc!$7:$9</definedName>
@@ -755,6 +755,19 @@
     <t>7507257</t>
   </si>
   <si>
+    <t>Số còn chi trong tháng 10/2026</t>
+  </si>
+  <si>
+    <t>(Tính đến ngày 17/10/2026)</t>
+  </si>
+  <si>
+    <t>Số giải ngân
+trong tuần (từ ngày 12/10/2026 đến 17/10/2026</t>
+  </si>
+  <si>
+    <t>TỔNG SỐ GIẢI NGÂN ĐẾN NGÀY BÁO CÁO NGÀY 17/10/2026</t>
+  </si>
+  <si>
     <t>Cán bộ Kỹ thuật</t>
   </si>
   <si>
@@ -777,19 +790,6 @@
   </si>
   <si>
     <t>Nguyễn Phi Hoàng</t>
-  </si>
-  <si>
-    <t>(Tính đến ngày 12/10/2026)</t>
-  </si>
-  <si>
-    <t>Số giải ngân
-trong tuần (từ ngày 06/10/2026 đến 12/10/2026</t>
-  </si>
-  <si>
-    <t>TỔNG SỐ GIẢI NGÂN ĐẾN NGÀY BÁO CÁO NGÀY 12/10/2026</t>
-  </si>
-  <si>
-    <t>Số còn chi trong tháng 10/2026</t>
   </si>
 </sst>
 </file>
@@ -1655,7 +1655,7 @@
     <xf numFmtId="164" fontId="60" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="60" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="344">
+  <cellXfs count="347">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2414,51 +2414,50 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="28" fillId="12" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="29" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="70" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="42" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="70" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="29" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="70" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="70" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="29" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="29" fillId="9" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="29" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="47" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="54" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="77" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2474,12 +2473,10 @@
     <xf numFmtId="0" fontId="59" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2519,32 +2516,27 @@
     <xf numFmtId="167" fontId="63" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2555,6 +2547,21 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="47" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2808,36 +2815,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="338" t="s">
+      <c r="A1" s="333" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="310"/>
-      <c r="C1" s="311"/>
-      <c r="D1" s="310"/>
-      <c r="E1" s="310"/>
-      <c r="F1" s="310"/>
-      <c r="G1" s="310"/>
-      <c r="H1" s="310"/>
-      <c r="I1" s="310"/>
-      <c r="J1" s="310"/>
-      <c r="K1" s="310"/>
-      <c r="L1" s="310"/>
-      <c r="M1" s="310"/>
-      <c r="N1" s="310"/>
-      <c r="O1" s="310"/>
-      <c r="P1" s="310"/>
-      <c r="Q1" s="310"/>
-      <c r="R1" s="310"/>
-      <c r="S1" s="310"/>
-      <c r="T1" s="310"/>
-      <c r="U1" s="310"/>
-      <c r="V1" s="310"/>
-      <c r="W1" s="310"/>
-      <c r="X1" s="310"/>
-      <c r="Y1" s="310"/>
-      <c r="Z1" s="310"/>
-      <c r="AA1" s="310"/>
-      <c r="AB1" s="312"/>
+      <c r="B1" s="309"/>
+      <c r="C1" s="310"/>
+      <c r="D1" s="309"/>
+      <c r="E1" s="309"/>
+      <c r="F1" s="309"/>
+      <c r="G1" s="309"/>
+      <c r="H1" s="309"/>
+      <c r="I1" s="309"/>
+      <c r="J1" s="309"/>
+      <c r="K1" s="309"/>
+      <c r="L1" s="309"/>
+      <c r="M1" s="309"/>
+      <c r="N1" s="309"/>
+      <c r="O1" s="309"/>
+      <c r="P1" s="309"/>
+      <c r="Q1" s="309"/>
+      <c r="R1" s="309"/>
+      <c r="S1" s="309"/>
+      <c r="T1" s="309"/>
+      <c r="U1" s="309"/>
+      <c r="V1" s="309"/>
+      <c r="W1" s="309"/>
+      <c r="X1" s="309"/>
+      <c r="Y1" s="309"/>
+      <c r="Z1" s="309"/>
+      <c r="AA1" s="309"/>
+      <c r="AB1" s="311"/>
       <c r="AC1" s="17"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="2"/>
@@ -2853,36 +2860,36 @@
       <c r="AM1" s="3"/>
     </row>
     <row r="2" spans="1:42" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="313" t="s">
+      <c r="A2" s="312" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="310"/>
-      <c r="C2" s="311"/>
-      <c r="D2" s="310"/>
-      <c r="E2" s="310"/>
-      <c r="F2" s="310"/>
-      <c r="G2" s="310"/>
-      <c r="H2" s="310"/>
-      <c r="I2" s="310"/>
-      <c r="J2" s="310"/>
-      <c r="K2" s="310"/>
-      <c r="L2" s="310"/>
-      <c r="M2" s="310"/>
-      <c r="N2" s="310"/>
-      <c r="O2" s="310"/>
-      <c r="P2" s="310"/>
-      <c r="Q2" s="310"/>
-      <c r="R2" s="310"/>
-      <c r="S2" s="310"/>
-      <c r="T2" s="310"/>
-      <c r="U2" s="310"/>
-      <c r="V2" s="310"/>
-      <c r="W2" s="310"/>
-      <c r="X2" s="310"/>
-      <c r="Y2" s="310"/>
-      <c r="Z2" s="310"/>
-      <c r="AA2" s="310"/>
-      <c r="AB2" s="312"/>
+      <c r="B2" s="309"/>
+      <c r="C2" s="310"/>
+      <c r="D2" s="309"/>
+      <c r="E2" s="309"/>
+      <c r="F2" s="309"/>
+      <c r="G2" s="309"/>
+      <c r="H2" s="309"/>
+      <c r="I2" s="309"/>
+      <c r="J2" s="309"/>
+      <c r="K2" s="309"/>
+      <c r="L2" s="309"/>
+      <c r="M2" s="309"/>
+      <c r="N2" s="309"/>
+      <c r="O2" s="309"/>
+      <c r="P2" s="309"/>
+      <c r="Q2" s="309"/>
+      <c r="R2" s="309"/>
+      <c r="S2" s="309"/>
+      <c r="T2" s="309"/>
+      <c r="U2" s="309"/>
+      <c r="V2" s="309"/>
+      <c r="W2" s="309"/>
+      <c r="X2" s="309"/>
+      <c r="Y2" s="309"/>
+      <c r="Z2" s="309"/>
+      <c r="AA2" s="309"/>
+      <c r="AB2" s="311"/>
       <c r="AC2" s="17"/>
       <c r="AD2" s="1"/>
       <c r="AE2" s="2"/>
@@ -2937,90 +2944,90 @@
       <c r="AM3" s="3"/>
     </row>
     <row r="4" spans="1:42" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="314" t="s">
+      <c r="A4" s="313" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="310"/>
-      <c r="C4" s="311"/>
-      <c r="D4" s="310"/>
-      <c r="E4" s="310"/>
-      <c r="F4" s="310"/>
-      <c r="G4" s="310"/>
-      <c r="H4" s="310"/>
-      <c r="I4" s="310"/>
-      <c r="J4" s="310"/>
-      <c r="K4" s="310"/>
-      <c r="L4" s="310"/>
-      <c r="M4" s="310"/>
-      <c r="N4" s="310"/>
-      <c r="O4" s="310"/>
-      <c r="P4" s="310"/>
-      <c r="Q4" s="310"/>
-      <c r="R4" s="310"/>
-      <c r="S4" s="310"/>
-      <c r="T4" s="310"/>
-      <c r="U4" s="310"/>
-      <c r="V4" s="310"/>
-      <c r="W4" s="310"/>
-      <c r="X4" s="310"/>
-      <c r="Y4" s="310"/>
-      <c r="Z4" s="310"/>
-      <c r="AA4" s="310"/>
-      <c r="AB4" s="310"/>
-      <c r="AC4" s="311"/>
-      <c r="AD4" s="310"/>
-      <c r="AE4" s="310"/>
-      <c r="AF4" s="311"/>
-      <c r="AG4" s="311"/>
-      <c r="AH4" s="310"/>
-      <c r="AI4" s="311"/>
-      <c r="AJ4" s="311"/>
-      <c r="AK4" s="310"/>
-      <c r="AL4" s="311"/>
-      <c r="AM4" s="312"/>
+      <c r="B4" s="309"/>
+      <c r="C4" s="310"/>
+      <c r="D4" s="309"/>
+      <c r="E4" s="309"/>
+      <c r="F4" s="309"/>
+      <c r="G4" s="309"/>
+      <c r="H4" s="309"/>
+      <c r="I4" s="309"/>
+      <c r="J4" s="309"/>
+      <c r="K4" s="309"/>
+      <c r="L4" s="309"/>
+      <c r="M4" s="309"/>
+      <c r="N4" s="309"/>
+      <c r="O4" s="309"/>
+      <c r="P4" s="309"/>
+      <c r="Q4" s="309"/>
+      <c r="R4" s="309"/>
+      <c r="S4" s="309"/>
+      <c r="T4" s="309"/>
+      <c r="U4" s="309"/>
+      <c r="V4" s="309"/>
+      <c r="W4" s="309"/>
+      <c r="X4" s="309"/>
+      <c r="Y4" s="309"/>
+      <c r="Z4" s="309"/>
+      <c r="AA4" s="309"/>
+      <c r="AB4" s="309"/>
+      <c r="AC4" s="310"/>
+      <c r="AD4" s="309"/>
+      <c r="AE4" s="309"/>
+      <c r="AF4" s="310"/>
+      <c r="AG4" s="310"/>
+      <c r="AH4" s="309"/>
+      <c r="AI4" s="310"/>
+      <c r="AJ4" s="310"/>
+      <c r="AK4" s="309"/>
+      <c r="AL4" s="310"/>
+      <c r="AM4" s="311"/>
     </row>
     <row r="5" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="315" t="s">
+      <c r="A5" s="314" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="310"/>
-      <c r="C5" s="311"/>
-      <c r="D5" s="310"/>
-      <c r="E5" s="310"/>
-      <c r="F5" s="310"/>
-      <c r="G5" s="310"/>
-      <c r="H5" s="310"/>
-      <c r="I5" s="310"/>
-      <c r="J5" s="310"/>
-      <c r="K5" s="310"/>
-      <c r="L5" s="310"/>
-      <c r="M5" s="310"/>
-      <c r="N5" s="310"/>
-      <c r="O5" s="310"/>
-      <c r="P5" s="310"/>
-      <c r="Q5" s="310"/>
-      <c r="R5" s="310"/>
-      <c r="S5" s="310"/>
-      <c r="T5" s="310"/>
-      <c r="U5" s="310"/>
-      <c r="V5" s="310"/>
-      <c r="W5" s="310"/>
-      <c r="X5" s="310"/>
-      <c r="Y5" s="310"/>
-      <c r="Z5" s="310"/>
-      <c r="AA5" s="310"/>
-      <c r="AB5" s="310"/>
-      <c r="AC5" s="311"/>
-      <c r="AD5" s="310"/>
-      <c r="AE5" s="310"/>
-      <c r="AF5" s="311"/>
-      <c r="AG5" s="311"/>
-      <c r="AH5" s="310"/>
-      <c r="AI5" s="311"/>
-      <c r="AJ5" s="311"/>
-      <c r="AK5" s="310"/>
-      <c r="AL5" s="311"/>
-      <c r="AM5" s="312"/>
+      <c r="B5" s="309"/>
+      <c r="C5" s="310"/>
+      <c r="D5" s="309"/>
+      <c r="E5" s="309"/>
+      <c r="F5" s="309"/>
+      <c r="G5" s="309"/>
+      <c r="H5" s="309"/>
+      <c r="I5" s="309"/>
+      <c r="J5" s="309"/>
+      <c r="K5" s="309"/>
+      <c r="L5" s="309"/>
+      <c r="M5" s="309"/>
+      <c r="N5" s="309"/>
+      <c r="O5" s="309"/>
+      <c r="P5" s="309"/>
+      <c r="Q5" s="309"/>
+      <c r="R5" s="309"/>
+      <c r="S5" s="309"/>
+      <c r="T5" s="309"/>
+      <c r="U5" s="309"/>
+      <c r="V5" s="309"/>
+      <c r="W5" s="309"/>
+      <c r="X5" s="309"/>
+      <c r="Y5" s="309"/>
+      <c r="Z5" s="309"/>
+      <c r="AA5" s="309"/>
+      <c r="AB5" s="309"/>
+      <c r="AC5" s="310"/>
+      <c r="AD5" s="309"/>
+      <c r="AE5" s="309"/>
+      <c r="AF5" s="310"/>
+      <c r="AG5" s="310"/>
+      <c r="AH5" s="309"/>
+      <c r="AI5" s="310"/>
+      <c r="AJ5" s="310"/>
+      <c r="AK5" s="309"/>
+      <c r="AL5" s="310"/>
+      <c r="AM5" s="311"/>
     </row>
     <row r="6" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -3054,203 +3061,203 @@
       <c r="AA6" s="16"/>
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
-      <c r="AD6" s="339"/>
-      <c r="AE6" s="311"/>
-      <c r="AF6" s="311"/>
-      <c r="AG6" s="311"/>
-      <c r="AH6" s="311"/>
-      <c r="AI6" s="311"/>
-      <c r="AJ6" s="311"/>
-      <c r="AK6" s="311"/>
-      <c r="AL6" s="311"/>
-      <c r="AM6" s="311"/>
+      <c r="AD6" s="335"/>
+      <c r="AE6" s="310"/>
+      <c r="AF6" s="310"/>
+      <c r="AG6" s="310"/>
+      <c r="AH6" s="310"/>
+      <c r="AI6" s="310"/>
+      <c r="AJ6" s="310"/>
+      <c r="AK6" s="310"/>
+      <c r="AL6" s="310"/>
+      <c r="AM6" s="310"/>
     </row>
     <row r="7" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="302" t="s">
+      <c r="A7" s="307" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="302" t="s">
+      <c r="B7" s="307" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="329" t="s">
+      <c r="C7" s="328" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="302" t="s">
+      <c r="D7" s="307" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="302" t="s">
+      <c r="E7" s="307" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="302" t="s">
+      <c r="F7" s="307" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="302" t="s">
+      <c r="G7" s="307" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="302" t="s">
+      <c r="H7" s="307" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="302" t="s">
+      <c r="I7" s="307" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="302" t="s">
+      <c r="J7" s="307" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="302" t="s">
+      <c r="K7" s="307" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="336" t="s">
+      <c r="L7" s="337" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="302" t="s">
+      <c r="M7" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="302" t="s">
+      <c r="N7" s="307" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="318" t="s">
+      <c r="O7" s="317" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="319"/>
-      <c r="Q7" s="319"/>
-      <c r="R7" s="319"/>
-      <c r="S7" s="319"/>
-      <c r="T7" s="319"/>
-      <c r="U7" s="319"/>
-      <c r="V7" s="320"/>
-      <c r="W7" s="302" t="s">
+      <c r="P7" s="318"/>
+      <c r="Q7" s="318"/>
+      <c r="R7" s="318"/>
+      <c r="S7" s="318"/>
+      <c r="T7" s="318"/>
+      <c r="U7" s="318"/>
+      <c r="V7" s="319"/>
+      <c r="W7" s="307" t="s">
         <v>139</v>
       </c>
-      <c r="X7" s="337" t="s">
+      <c r="X7" s="334" t="s">
         <v>13</v>
       </c>
-      <c r="Y7" s="337" t="s">
+      <c r="Y7" s="334" t="s">
         <v>14</v>
       </c>
-      <c r="Z7" s="307" t="s">
+      <c r="Z7" s="301" t="s">
         <v>150</v>
       </c>
-      <c r="AA7" s="302" t="s">
+      <c r="AA7" s="307" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="302" t="s">
+      <c r="AB7" s="307" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="302" t="s">
+      <c r="AC7" s="307" t="s">
         <v>134</v>
       </c>
-      <c r="AD7" s="307" t="s">
+      <c r="AD7" s="301" t="s">
         <v>17</v>
       </c>
-      <c r="AE7" s="304" t="s">
+      <c r="AE7" s="330" t="s">
         <v>107</v>
       </c>
-      <c r="AF7" s="304" t="s">
+      <c r="AF7" s="330" t="s">
         <v>108</v>
       </c>
-      <c r="AG7" s="304" t="s">
+      <c r="AG7" s="330" t="s">
         <v>106</v>
       </c>
-      <c r="AH7" s="306" t="s">
+      <c r="AH7" s="332" t="s">
         <v>147</v>
       </c>
-      <c r="AI7" s="307" t="s">
+      <c r="AI7" s="301" t="s">
         <v>136</v>
       </c>
-      <c r="AJ7" s="307" t="s">
+      <c r="AJ7" s="301" t="s">
         <v>137</v>
       </c>
-      <c r="AK7" s="302" t="s">
+      <c r="AK7" s="307" t="s">
         <v>135</v>
       </c>
-      <c r="AL7" s="302" t="s">
+      <c r="AL7" s="307" t="s">
         <v>146</v>
       </c>
-      <c r="AM7" s="302" t="s">
+      <c r="AM7" s="307" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="308"/>
-      <c r="B8" s="308"/>
-      <c r="C8" s="329"/>
-      <c r="D8" s="308"/>
-      <c r="E8" s="308"/>
-      <c r="F8" s="308"/>
-      <c r="G8" s="308"/>
-      <c r="H8" s="308"/>
-      <c r="I8" s="308"/>
-      <c r="J8" s="308"/>
-      <c r="K8" s="308"/>
-      <c r="L8" s="308"/>
-      <c r="M8" s="308"/>
-      <c r="N8" s="308"/>
-      <c r="O8" s="321"/>
-      <c r="P8" s="322"/>
-      <c r="Q8" s="322"/>
-      <c r="R8" s="322"/>
-      <c r="S8" s="322"/>
-      <c r="T8" s="322"/>
-      <c r="U8" s="322"/>
-      <c r="V8" s="323"/>
-      <c r="W8" s="308"/>
-      <c r="X8" s="308"/>
-      <c r="Y8" s="308"/>
-      <c r="Z8" s="308"/>
-      <c r="AA8" s="308"/>
-      <c r="AB8" s="308"/>
-      <c r="AC8" s="302"/>
-      <c r="AD8" s="308"/>
-      <c r="AE8" s="305"/>
-      <c r="AF8" s="305"/>
-      <c r="AG8" s="306"/>
-      <c r="AH8" s="305"/>
-      <c r="AI8" s="308"/>
-      <c r="AJ8" s="307"/>
-      <c r="AK8" s="308"/>
-      <c r="AL8" s="302"/>
-      <c r="AM8" s="308"/>
+      <c r="A8" s="302"/>
+      <c r="B8" s="302"/>
+      <c r="C8" s="328"/>
+      <c r="D8" s="302"/>
+      <c r="E8" s="302"/>
+      <c r="F8" s="302"/>
+      <c r="G8" s="302"/>
+      <c r="H8" s="302"/>
+      <c r="I8" s="302"/>
+      <c r="J8" s="302"/>
+      <c r="K8" s="302"/>
+      <c r="L8" s="302"/>
+      <c r="M8" s="302"/>
+      <c r="N8" s="302"/>
+      <c r="O8" s="320"/>
+      <c r="P8" s="321"/>
+      <c r="Q8" s="321"/>
+      <c r="R8" s="321"/>
+      <c r="S8" s="321"/>
+      <c r="T8" s="321"/>
+      <c r="U8" s="321"/>
+      <c r="V8" s="322"/>
+      <c r="W8" s="302"/>
+      <c r="X8" s="302"/>
+      <c r="Y8" s="302"/>
+      <c r="Z8" s="302"/>
+      <c r="AA8" s="302"/>
+      <c r="AB8" s="302"/>
+      <c r="AC8" s="307"/>
+      <c r="AD8" s="302"/>
+      <c r="AE8" s="331"/>
+      <c r="AF8" s="331"/>
+      <c r="AG8" s="332"/>
+      <c r="AH8" s="331"/>
+      <c r="AI8" s="302"/>
+      <c r="AJ8" s="301"/>
+      <c r="AK8" s="302"/>
+      <c r="AL8" s="307"/>
+      <c r="AM8" s="302"/>
     </row>
     <row r="9" spans="1:42" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="308"/>
-      <c r="B9" s="308"/>
-      <c r="C9" s="329"/>
-      <c r="D9" s="308"/>
-      <c r="E9" s="308"/>
-      <c r="F9" s="308"/>
-      <c r="G9" s="308"/>
-      <c r="H9" s="308"/>
-      <c r="I9" s="308"/>
-      <c r="J9" s="308"/>
-      <c r="K9" s="308"/>
-      <c r="L9" s="308"/>
-      <c r="M9" s="308"/>
-      <c r="N9" s="308"/>
-      <c r="O9" s="324"/>
-      <c r="P9" s="325"/>
-      <c r="Q9" s="325"/>
-      <c r="R9" s="325"/>
-      <c r="S9" s="325"/>
-      <c r="T9" s="325"/>
-      <c r="U9" s="325"/>
-      <c r="V9" s="326"/>
-      <c r="W9" s="308"/>
-      <c r="X9" s="308"/>
-      <c r="Y9" s="308"/>
-      <c r="Z9" s="308"/>
-      <c r="AA9" s="308"/>
-      <c r="AB9" s="308"/>
-      <c r="AC9" s="302"/>
-      <c r="AD9" s="308"/>
-      <c r="AE9" s="305"/>
-      <c r="AF9" s="305"/>
-      <c r="AG9" s="306"/>
-      <c r="AH9" s="305"/>
-      <c r="AI9" s="308"/>
-      <c r="AJ9" s="307"/>
-      <c r="AK9" s="308"/>
-      <c r="AL9" s="302"/>
-      <c r="AM9" s="308"/>
+      <c r="A9" s="302"/>
+      <c r="B9" s="302"/>
+      <c r="C9" s="328"/>
+      <c r="D9" s="302"/>
+      <c r="E9" s="302"/>
+      <c r="F9" s="302"/>
+      <c r="G9" s="302"/>
+      <c r="H9" s="302"/>
+      <c r="I9" s="302"/>
+      <c r="J9" s="302"/>
+      <c r="K9" s="302"/>
+      <c r="L9" s="302"/>
+      <c r="M9" s="302"/>
+      <c r="N9" s="302"/>
+      <c r="O9" s="323"/>
+      <c r="P9" s="324"/>
+      <c r="Q9" s="324"/>
+      <c r="R9" s="324"/>
+      <c r="S9" s="324"/>
+      <c r="T9" s="324"/>
+      <c r="U9" s="324"/>
+      <c r="V9" s="325"/>
+      <c r="W9" s="302"/>
+      <c r="X9" s="302"/>
+      <c r="Y9" s="302"/>
+      <c r="Z9" s="302"/>
+      <c r="AA9" s="302"/>
+      <c r="AB9" s="302"/>
+      <c r="AC9" s="307"/>
+      <c r="AD9" s="302"/>
+      <c r="AE9" s="331"/>
+      <c r="AF9" s="331"/>
+      <c r="AG9" s="332"/>
+      <c r="AH9" s="331"/>
+      <c r="AI9" s="302"/>
+      <c r="AJ9" s="301"/>
+      <c r="AK9" s="302"/>
+      <c r="AL9" s="307"/>
+      <c r="AM9" s="302"/>
       <c r="AP9">
         <v>27</v>
       </c>
@@ -8699,47 +8706,47 @@
       </c>
     </row>
     <row r="77" spans="1:42" ht="29.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="335" t="s">
+      <c r="A77" s="336" t="s">
         <v>145</v>
       </c>
-      <c r="B77" s="308"/>
-      <c r="C77" s="308"/>
-      <c r="D77" s="308"/>
-      <c r="E77" s="308"/>
-      <c r="F77" s="308"/>
-      <c r="G77" s="308"/>
-      <c r="H77" s="308"/>
-      <c r="I77" s="308"/>
-      <c r="J77" s="308"/>
-      <c r="K77" s="308"/>
-      <c r="L77" s="308"/>
-      <c r="M77" s="308"/>
-      <c r="N77" s="308"/>
-      <c r="O77" s="308"/>
-      <c r="P77" s="308"/>
-      <c r="Q77" s="308"/>
-      <c r="R77" s="308"/>
-      <c r="S77" s="308"/>
-      <c r="T77" s="308"/>
-      <c r="U77" s="308"/>
-      <c r="V77" s="308"/>
-      <c r="W77" s="308"/>
-      <c r="X77" s="308"/>
-      <c r="Y77" s="308"/>
-      <c r="Z77" s="308"/>
-      <c r="AA77" s="308"/>
-      <c r="AB77" s="308"/>
-      <c r="AC77" s="308"/>
-      <c r="AD77" s="308"/>
-      <c r="AE77" s="308"/>
-      <c r="AF77" s="308"/>
-      <c r="AG77" s="308"/>
-      <c r="AH77" s="308"/>
-      <c r="AI77" s="308"/>
-      <c r="AJ77" s="308"/>
-      <c r="AK77" s="308"/>
-      <c r="AL77" s="308"/>
-      <c r="AM77" s="308"/>
+      <c r="B77" s="302"/>
+      <c r="C77" s="302"/>
+      <c r="D77" s="302"/>
+      <c r="E77" s="302"/>
+      <c r="F77" s="302"/>
+      <c r="G77" s="302"/>
+      <c r="H77" s="302"/>
+      <c r="I77" s="302"/>
+      <c r="J77" s="302"/>
+      <c r="K77" s="302"/>
+      <c r="L77" s="302"/>
+      <c r="M77" s="302"/>
+      <c r="N77" s="302"/>
+      <c r="O77" s="302"/>
+      <c r="P77" s="302"/>
+      <c r="Q77" s="302"/>
+      <c r="R77" s="302"/>
+      <c r="S77" s="302"/>
+      <c r="T77" s="302"/>
+      <c r="U77" s="302"/>
+      <c r="V77" s="302"/>
+      <c r="W77" s="302"/>
+      <c r="X77" s="302"/>
+      <c r="Y77" s="302"/>
+      <c r="Z77" s="302"/>
+      <c r="AA77" s="302"/>
+      <c r="AB77" s="302"/>
+      <c r="AC77" s="302"/>
+      <c r="AD77" s="302"/>
+      <c r="AE77" s="302"/>
+      <c r="AF77" s="302"/>
+      <c r="AG77" s="302"/>
+      <c r="AH77" s="302"/>
+      <c r="AI77" s="302"/>
+      <c r="AJ77" s="302"/>
+      <c r="AK77" s="302"/>
+      <c r="AL77" s="302"/>
+      <c r="AM77" s="302"/>
     </row>
     <row r="78" spans="1:42" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="81"/>
@@ -9839,12 +9846,22 @@
   </sheetData>
   <autoFilter ref="A10:AP80" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="38">
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AC9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="A77:AM77"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:J9"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="A7:A9"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A2:AB2"/>
     <mergeCell ref="A4:AM4"/>
@@ -9861,22 +9878,12 @@
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="X7:X9"/>
     <mergeCell ref="AD6:AM6"/>
-    <mergeCell ref="A77:AM77"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:J9"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AC9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="O7:V9"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.27559055118110237" top="0.47244094488188981" bottom="0.31496062992125984" header="0" footer="0"/>
   <pageSetup scale="80" orientation="landscape" r:id="rId1"/>
@@ -9925,36 +9932,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="338" t="s">
+      <c r="A1" s="333" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="310"/>
-      <c r="C1" s="311"/>
-      <c r="D1" s="310"/>
-      <c r="E1" s="310"/>
-      <c r="F1" s="310"/>
-      <c r="G1" s="310"/>
-      <c r="H1" s="310"/>
-      <c r="I1" s="310"/>
-      <c r="J1" s="310"/>
-      <c r="K1" s="310"/>
-      <c r="L1" s="310"/>
-      <c r="M1" s="310"/>
-      <c r="N1" s="310"/>
-      <c r="O1" s="310"/>
-      <c r="P1" s="310"/>
-      <c r="Q1" s="310"/>
-      <c r="R1" s="310"/>
-      <c r="S1" s="310"/>
-      <c r="T1" s="310"/>
-      <c r="U1" s="310"/>
-      <c r="V1" s="310"/>
-      <c r="W1" s="310"/>
-      <c r="X1" s="310"/>
-      <c r="Y1" s="310"/>
-      <c r="Z1" s="310"/>
-      <c r="AA1" s="310"/>
-      <c r="AB1" s="312"/>
+      <c r="B1" s="309"/>
+      <c r="C1" s="310"/>
+      <c r="D1" s="309"/>
+      <c r="E1" s="309"/>
+      <c r="F1" s="309"/>
+      <c r="G1" s="309"/>
+      <c r="H1" s="309"/>
+      <c r="I1" s="309"/>
+      <c r="J1" s="309"/>
+      <c r="K1" s="309"/>
+      <c r="L1" s="309"/>
+      <c r="M1" s="309"/>
+      <c r="N1" s="309"/>
+      <c r="O1" s="309"/>
+      <c r="P1" s="309"/>
+      <c r="Q1" s="309"/>
+      <c r="R1" s="309"/>
+      <c r="S1" s="309"/>
+      <c r="T1" s="309"/>
+      <c r="U1" s="309"/>
+      <c r="V1" s="309"/>
+      <c r="W1" s="309"/>
+      <c r="X1" s="309"/>
+      <c r="Y1" s="309"/>
+      <c r="Z1" s="309"/>
+      <c r="AA1" s="309"/>
+      <c r="AB1" s="311"/>
       <c r="AC1" s="17"/>
       <c r="AD1" s="17"/>
       <c r="AE1" s="1"/>
@@ -9971,36 +9978,36 @@
       <c r="AN1" s="160"/>
     </row>
     <row r="2" spans="1:43" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="313" t="s">
+      <c r="A2" s="312" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="310"/>
-      <c r="C2" s="311"/>
-      <c r="D2" s="310"/>
-      <c r="E2" s="310"/>
-      <c r="F2" s="310"/>
-      <c r="G2" s="310"/>
-      <c r="H2" s="310"/>
-      <c r="I2" s="310"/>
-      <c r="J2" s="310"/>
-      <c r="K2" s="310"/>
-      <c r="L2" s="310"/>
-      <c r="M2" s="310"/>
-      <c r="N2" s="310"/>
-      <c r="O2" s="310"/>
-      <c r="P2" s="310"/>
-      <c r="Q2" s="310"/>
-      <c r="R2" s="310"/>
-      <c r="S2" s="310"/>
-      <c r="T2" s="310"/>
-      <c r="U2" s="310"/>
-      <c r="V2" s="310"/>
-      <c r="W2" s="310"/>
-      <c r="X2" s="310"/>
-      <c r="Y2" s="310"/>
-      <c r="Z2" s="310"/>
-      <c r="AA2" s="310"/>
-      <c r="AB2" s="312"/>
+      <c r="B2" s="309"/>
+      <c r="C2" s="310"/>
+      <c r="D2" s="309"/>
+      <c r="E2" s="309"/>
+      <c r="F2" s="309"/>
+      <c r="G2" s="309"/>
+      <c r="H2" s="309"/>
+      <c r="I2" s="309"/>
+      <c r="J2" s="309"/>
+      <c r="K2" s="309"/>
+      <c r="L2" s="309"/>
+      <c r="M2" s="309"/>
+      <c r="N2" s="309"/>
+      <c r="O2" s="309"/>
+      <c r="P2" s="309"/>
+      <c r="Q2" s="309"/>
+      <c r="R2" s="309"/>
+      <c r="S2" s="309"/>
+      <c r="T2" s="309"/>
+      <c r="U2" s="309"/>
+      <c r="V2" s="309"/>
+      <c r="W2" s="309"/>
+      <c r="X2" s="309"/>
+      <c r="Y2" s="309"/>
+      <c r="Z2" s="309"/>
+      <c r="AA2" s="309"/>
+      <c r="AB2" s="311"/>
       <c r="AC2" s="17"/>
       <c r="AD2" s="17"/>
       <c r="AE2" s="1"/>
@@ -10057,92 +10064,92 @@
       <c r="AN3" s="160"/>
     </row>
     <row r="4" spans="1:43" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="314" t="s">
+      <c r="A4" s="313" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="310"/>
-      <c r="C4" s="311"/>
-      <c r="D4" s="310"/>
-      <c r="E4" s="310"/>
-      <c r="F4" s="310"/>
-      <c r="G4" s="310"/>
-      <c r="H4" s="310"/>
-      <c r="I4" s="310"/>
-      <c r="J4" s="310"/>
-      <c r="K4" s="310"/>
-      <c r="L4" s="310"/>
-      <c r="M4" s="310"/>
-      <c r="N4" s="310"/>
-      <c r="O4" s="310"/>
-      <c r="P4" s="310"/>
-      <c r="Q4" s="310"/>
-      <c r="R4" s="310"/>
-      <c r="S4" s="310"/>
-      <c r="T4" s="310"/>
-      <c r="U4" s="310"/>
-      <c r="V4" s="310"/>
-      <c r="W4" s="310"/>
-      <c r="X4" s="310"/>
-      <c r="Y4" s="310"/>
-      <c r="Z4" s="310"/>
-      <c r="AA4" s="310"/>
-      <c r="AB4" s="310"/>
-      <c r="AC4" s="311"/>
-      <c r="AD4" s="311"/>
-      <c r="AE4" s="310"/>
-      <c r="AF4" s="310"/>
-      <c r="AG4" s="311"/>
-      <c r="AH4" s="311"/>
-      <c r="AI4" s="310"/>
-      <c r="AJ4" s="311"/>
-      <c r="AK4" s="311"/>
-      <c r="AL4" s="310"/>
-      <c r="AM4" s="311"/>
-      <c r="AN4" s="312"/>
+      <c r="B4" s="309"/>
+      <c r="C4" s="310"/>
+      <c r="D4" s="309"/>
+      <c r="E4" s="309"/>
+      <c r="F4" s="309"/>
+      <c r="G4" s="309"/>
+      <c r="H4" s="309"/>
+      <c r="I4" s="309"/>
+      <c r="J4" s="309"/>
+      <c r="K4" s="309"/>
+      <c r="L4" s="309"/>
+      <c r="M4" s="309"/>
+      <c r="N4" s="309"/>
+      <c r="O4" s="309"/>
+      <c r="P4" s="309"/>
+      <c r="Q4" s="309"/>
+      <c r="R4" s="309"/>
+      <c r="S4" s="309"/>
+      <c r="T4" s="309"/>
+      <c r="U4" s="309"/>
+      <c r="V4" s="309"/>
+      <c r="W4" s="309"/>
+      <c r="X4" s="309"/>
+      <c r="Y4" s="309"/>
+      <c r="Z4" s="309"/>
+      <c r="AA4" s="309"/>
+      <c r="AB4" s="309"/>
+      <c r="AC4" s="310"/>
+      <c r="AD4" s="310"/>
+      <c r="AE4" s="309"/>
+      <c r="AF4" s="309"/>
+      <c r="AG4" s="310"/>
+      <c r="AH4" s="310"/>
+      <c r="AI4" s="309"/>
+      <c r="AJ4" s="310"/>
+      <c r="AK4" s="310"/>
+      <c r="AL4" s="309"/>
+      <c r="AM4" s="310"/>
+      <c r="AN4" s="311"/>
     </row>
     <row r="5" spans="1:43" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="315" t="s">
+      <c r="A5" s="314" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="310"/>
-      <c r="C5" s="311"/>
-      <c r="D5" s="310"/>
-      <c r="E5" s="310"/>
-      <c r="F5" s="310"/>
-      <c r="G5" s="310"/>
-      <c r="H5" s="310"/>
-      <c r="I5" s="310"/>
-      <c r="J5" s="310"/>
-      <c r="K5" s="310"/>
-      <c r="L5" s="310"/>
-      <c r="M5" s="310"/>
-      <c r="N5" s="310"/>
-      <c r="O5" s="310"/>
-      <c r="P5" s="310"/>
-      <c r="Q5" s="310"/>
-      <c r="R5" s="310"/>
-      <c r="S5" s="310"/>
-      <c r="T5" s="310"/>
-      <c r="U5" s="310"/>
-      <c r="V5" s="310"/>
-      <c r="W5" s="310"/>
-      <c r="X5" s="310"/>
-      <c r="Y5" s="310"/>
-      <c r="Z5" s="310"/>
-      <c r="AA5" s="310"/>
-      <c r="AB5" s="310"/>
-      <c r="AC5" s="311"/>
-      <c r="AD5" s="311"/>
-      <c r="AE5" s="310"/>
-      <c r="AF5" s="310"/>
-      <c r="AG5" s="311"/>
-      <c r="AH5" s="311"/>
-      <c r="AI5" s="310"/>
-      <c r="AJ5" s="311"/>
-      <c r="AK5" s="311"/>
-      <c r="AL5" s="310"/>
-      <c r="AM5" s="311"/>
-      <c r="AN5" s="312"/>
+      <c r="B5" s="309"/>
+      <c r="C5" s="310"/>
+      <c r="D5" s="309"/>
+      <c r="E5" s="309"/>
+      <c r="F5" s="309"/>
+      <c r="G5" s="309"/>
+      <c r="H5" s="309"/>
+      <c r="I5" s="309"/>
+      <c r="J5" s="309"/>
+      <c r="K5" s="309"/>
+      <c r="L5" s="309"/>
+      <c r="M5" s="309"/>
+      <c r="N5" s="309"/>
+      <c r="O5" s="309"/>
+      <c r="P5" s="309"/>
+      <c r="Q5" s="309"/>
+      <c r="R5" s="309"/>
+      <c r="S5" s="309"/>
+      <c r="T5" s="309"/>
+      <c r="U5" s="309"/>
+      <c r="V5" s="309"/>
+      <c r="W5" s="309"/>
+      <c r="X5" s="309"/>
+      <c r="Y5" s="309"/>
+      <c r="Z5" s="309"/>
+      <c r="AA5" s="309"/>
+      <c r="AB5" s="309"/>
+      <c r="AC5" s="310"/>
+      <c r="AD5" s="310"/>
+      <c r="AE5" s="309"/>
+      <c r="AF5" s="309"/>
+      <c r="AG5" s="310"/>
+      <c r="AH5" s="310"/>
+      <c r="AI5" s="309"/>
+      <c r="AJ5" s="310"/>
+      <c r="AK5" s="310"/>
+      <c r="AL5" s="309"/>
+      <c r="AM5" s="310"/>
+      <c r="AN5" s="311"/>
     </row>
     <row r="6" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -10177,212 +10184,212 @@
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
       <c r="AD6" s="11"/>
-      <c r="AE6" s="340" t="s">
+      <c r="AE6" s="338" t="s">
         <v>151</v>
       </c>
-      <c r="AF6" s="341"/>
-      <c r="AG6" s="341"/>
-      <c r="AH6" s="341"/>
-      <c r="AI6" s="341"/>
-      <c r="AJ6" s="341"/>
-      <c r="AK6" s="341"/>
-      <c r="AL6" s="341"/>
-      <c r="AM6" s="341"/>
-      <c r="AN6" s="341"/>
+      <c r="AF6" s="339"/>
+      <c r="AG6" s="339"/>
+      <c r="AH6" s="339"/>
+      <c r="AI6" s="339"/>
+      <c r="AJ6" s="339"/>
+      <c r="AK6" s="339"/>
+      <c r="AL6" s="339"/>
+      <c r="AM6" s="339"/>
+      <c r="AN6" s="339"/>
     </row>
     <row r="7" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="302" t="s">
+      <c r="A7" s="307" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="302" t="s">
+      <c r="B7" s="307" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="329" t="s">
+      <c r="C7" s="328" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="302" t="s">
+      <c r="D7" s="307" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="302" t="s">
+      <c r="E7" s="307" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="302" t="s">
+      <c r="F7" s="307" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="302" t="s">
+      <c r="G7" s="307" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="302" t="s">
+      <c r="H7" s="307" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="302" t="s">
+      <c r="I7" s="307" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="302" t="s">
+      <c r="J7" s="307" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="302" t="s">
+      <c r="K7" s="307" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="336" t="s">
+      <c r="L7" s="337" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="302" t="s">
+      <c r="M7" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="302" t="s">
+      <c r="N7" s="307" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="318" t="s">
+      <c r="O7" s="317" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="319"/>
-      <c r="Q7" s="319"/>
-      <c r="R7" s="319"/>
-      <c r="S7" s="319"/>
-      <c r="T7" s="319"/>
-      <c r="U7" s="319"/>
-      <c r="V7" s="320"/>
-      <c r="W7" s="302" t="s">
+      <c r="P7" s="318"/>
+      <c r="Q7" s="318"/>
+      <c r="R7" s="318"/>
+      <c r="S7" s="318"/>
+      <c r="T7" s="318"/>
+      <c r="U7" s="318"/>
+      <c r="V7" s="319"/>
+      <c r="W7" s="307" t="s">
         <v>139</v>
       </c>
-      <c r="X7" s="317" t="s">
+      <c r="X7" s="315" t="s">
         <v>13</v>
       </c>
-      <c r="Y7" s="317" t="s">
+      <c r="Y7" s="315" t="s">
         <v>184</v>
       </c>
-      <c r="Z7" s="330" t="s">
+      <c r="Z7" s="329" t="s">
         <v>175</v>
       </c>
-      <c r="AA7" s="302" t="s">
+      <c r="AA7" s="307" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="302" t="s">
+      <c r="AB7" s="307" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="318" t="s">
+      <c r="AC7" s="317" t="s">
         <v>155</v>
       </c>
-      <c r="AD7" s="320"/>
-      <c r="AE7" s="307" t="s">
+      <c r="AD7" s="319"/>
+      <c r="AE7" s="301" t="s">
         <v>17</v>
       </c>
-      <c r="AF7" s="304" t="s">
+      <c r="AF7" s="330" t="s">
         <v>107</v>
       </c>
-      <c r="AG7" s="304" t="s">
+      <c r="AG7" s="330" t="s">
         <v>108</v>
       </c>
-      <c r="AH7" s="304" t="s">
+      <c r="AH7" s="330" t="s">
         <v>106</v>
       </c>
-      <c r="AI7" s="306" t="s">
+      <c r="AI7" s="332" t="s">
         <v>147</v>
       </c>
-      <c r="AJ7" s="307" t="s">
+      <c r="AJ7" s="301" t="s">
         <v>136</v>
       </c>
-      <c r="AK7" s="307" t="s">
+      <c r="AK7" s="301" t="s">
         <v>137</v>
       </c>
-      <c r="AL7" s="302" t="s">
+      <c r="AL7" s="307" t="s">
         <v>135</v>
       </c>
-      <c r="AM7" s="302" t="s">
+      <c r="AM7" s="307" t="s">
         <v>146</v>
       </c>
-      <c r="AN7" s="302" t="s">
+      <c r="AN7" s="307" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="308"/>
-      <c r="B8" s="308"/>
-      <c r="C8" s="329"/>
-      <c r="D8" s="308"/>
-      <c r="E8" s="308"/>
-      <c r="F8" s="308"/>
-      <c r="G8" s="308"/>
-      <c r="H8" s="308"/>
-      <c r="I8" s="308"/>
-      <c r="J8" s="308"/>
-      <c r="K8" s="308"/>
-      <c r="L8" s="308"/>
-      <c r="M8" s="308"/>
-      <c r="N8" s="308"/>
-      <c r="O8" s="321"/>
-      <c r="P8" s="322"/>
-      <c r="Q8" s="322"/>
-      <c r="R8" s="322"/>
-      <c r="S8" s="322"/>
-      <c r="T8" s="322"/>
-      <c r="U8" s="322"/>
-      <c r="V8" s="323"/>
-      <c r="W8" s="308"/>
-      <c r="X8" s="308"/>
-      <c r="Y8" s="308"/>
-      <c r="Z8" s="308"/>
-      <c r="AA8" s="308"/>
-      <c r="AB8" s="308"/>
-      <c r="AC8" s="324"/>
-      <c r="AD8" s="326"/>
-      <c r="AE8" s="308"/>
-      <c r="AF8" s="305"/>
-      <c r="AG8" s="305"/>
-      <c r="AH8" s="306"/>
-      <c r="AI8" s="305"/>
-      <c r="AJ8" s="308"/>
-      <c r="AK8" s="307"/>
-      <c r="AL8" s="308"/>
-      <c r="AM8" s="302"/>
-      <c r="AN8" s="303"/>
+      <c r="A8" s="302"/>
+      <c r="B8" s="302"/>
+      <c r="C8" s="328"/>
+      <c r="D8" s="302"/>
+      <c r="E8" s="302"/>
+      <c r="F8" s="302"/>
+      <c r="G8" s="302"/>
+      <c r="H8" s="302"/>
+      <c r="I8" s="302"/>
+      <c r="J8" s="302"/>
+      <c r="K8" s="302"/>
+      <c r="L8" s="302"/>
+      <c r="M8" s="302"/>
+      <c r="N8" s="302"/>
+      <c r="O8" s="320"/>
+      <c r="P8" s="321"/>
+      <c r="Q8" s="321"/>
+      <c r="R8" s="321"/>
+      <c r="S8" s="321"/>
+      <c r="T8" s="321"/>
+      <c r="U8" s="321"/>
+      <c r="V8" s="322"/>
+      <c r="W8" s="302"/>
+      <c r="X8" s="302"/>
+      <c r="Y8" s="302"/>
+      <c r="Z8" s="302"/>
+      <c r="AA8" s="302"/>
+      <c r="AB8" s="302"/>
+      <c r="AC8" s="323"/>
+      <c r="AD8" s="325"/>
+      <c r="AE8" s="302"/>
+      <c r="AF8" s="331"/>
+      <c r="AG8" s="331"/>
+      <c r="AH8" s="332"/>
+      <c r="AI8" s="331"/>
+      <c r="AJ8" s="302"/>
+      <c r="AK8" s="301"/>
+      <c r="AL8" s="302"/>
+      <c r="AM8" s="307"/>
+      <c r="AN8" s="316"/>
     </row>
     <row r="9" spans="1:43" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="308"/>
-      <c r="B9" s="308"/>
-      <c r="C9" s="329"/>
-      <c r="D9" s="308"/>
-      <c r="E9" s="308"/>
-      <c r="F9" s="308"/>
-      <c r="G9" s="308"/>
-      <c r="H9" s="308"/>
-      <c r="I9" s="308"/>
-      <c r="J9" s="308"/>
-      <c r="K9" s="308"/>
-      <c r="L9" s="308"/>
-      <c r="M9" s="308"/>
-      <c r="N9" s="308"/>
-      <c r="O9" s="324"/>
-      <c r="P9" s="325"/>
-      <c r="Q9" s="325"/>
-      <c r="R9" s="325"/>
-      <c r="S9" s="325"/>
-      <c r="T9" s="325"/>
-      <c r="U9" s="325"/>
-      <c r="V9" s="326"/>
-      <c r="W9" s="308"/>
-      <c r="X9" s="308"/>
-      <c r="Y9" s="308"/>
-      <c r="Z9" s="308"/>
-      <c r="AA9" s="308"/>
-      <c r="AB9" s="308"/>
+      <c r="A9" s="302"/>
+      <c r="B9" s="302"/>
+      <c r="C9" s="328"/>
+      <c r="D9" s="302"/>
+      <c r="E9" s="302"/>
+      <c r="F9" s="302"/>
+      <c r="G9" s="302"/>
+      <c r="H9" s="302"/>
+      <c r="I9" s="302"/>
+      <c r="J9" s="302"/>
+      <c r="K9" s="302"/>
+      <c r="L9" s="302"/>
+      <c r="M9" s="302"/>
+      <c r="N9" s="302"/>
+      <c r="O9" s="323"/>
+      <c r="P9" s="324"/>
+      <c r="Q9" s="324"/>
+      <c r="R9" s="324"/>
+      <c r="S9" s="324"/>
+      <c r="T9" s="324"/>
+      <c r="U9" s="324"/>
+      <c r="V9" s="325"/>
+      <c r="W9" s="302"/>
+      <c r="X9" s="302"/>
+      <c r="Y9" s="302"/>
+      <c r="Z9" s="302"/>
+      <c r="AA9" s="302"/>
+      <c r="AB9" s="302"/>
       <c r="AC9" s="201" t="s">
         <v>153</v>
       </c>
       <c r="AD9" s="178" t="s">
         <v>154</v>
       </c>
-      <c r="AE9" s="308"/>
-      <c r="AF9" s="305"/>
-      <c r="AG9" s="305"/>
-      <c r="AH9" s="306"/>
-      <c r="AI9" s="305"/>
-      <c r="AJ9" s="308"/>
-      <c r="AK9" s="307"/>
-      <c r="AL9" s="308"/>
-      <c r="AM9" s="302"/>
-      <c r="AN9" s="303"/>
+      <c r="AE9" s="302"/>
+      <c r="AF9" s="331"/>
+      <c r="AG9" s="331"/>
+      <c r="AH9" s="332"/>
+      <c r="AI9" s="331"/>
+      <c r="AJ9" s="302"/>
+      <c r="AK9" s="301"/>
+      <c r="AL9" s="302"/>
+      <c r="AM9" s="307"/>
+      <c r="AN9" s="316"/>
       <c r="AO9">
         <f>Z11/W11</f>
         <v>0.50632226325372287</v>
@@ -15652,6 +15659,27 @@
   </sheetData>
   <autoFilter ref="A10:AQ54" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="37">
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AD8"/>
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A2:AB2"/>
@@ -15668,27 +15696,6 @@
     <mergeCell ref="H7:H9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:J9"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AD8"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
   </mergeCells>
   <pageMargins left="0.17" right="0.15748031496062992" top="0.41" bottom="0.23622047244094491" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
@@ -15737,36 +15744,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="338" t="s">
+      <c r="A1" s="333" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="310"/>
-      <c r="C1" s="311"/>
-      <c r="D1" s="310"/>
-      <c r="E1" s="310"/>
-      <c r="F1" s="310"/>
-      <c r="G1" s="310"/>
-      <c r="H1" s="310"/>
-      <c r="I1" s="310"/>
-      <c r="J1" s="310"/>
-      <c r="K1" s="310"/>
-      <c r="L1" s="310"/>
-      <c r="M1" s="310"/>
-      <c r="N1" s="310"/>
-      <c r="O1" s="310"/>
-      <c r="P1" s="310"/>
-      <c r="Q1" s="310"/>
-      <c r="R1" s="310"/>
-      <c r="S1" s="310"/>
-      <c r="T1" s="310"/>
-      <c r="U1" s="310"/>
-      <c r="V1" s="310"/>
-      <c r="W1" s="310"/>
-      <c r="X1" s="310"/>
-      <c r="Y1" s="310"/>
-      <c r="Z1" s="310"/>
-      <c r="AA1" s="310"/>
-      <c r="AB1" s="312"/>
+      <c r="B1" s="309"/>
+      <c r="C1" s="310"/>
+      <c r="D1" s="309"/>
+      <c r="E1" s="309"/>
+      <c r="F1" s="309"/>
+      <c r="G1" s="309"/>
+      <c r="H1" s="309"/>
+      <c r="I1" s="309"/>
+      <c r="J1" s="309"/>
+      <c r="K1" s="309"/>
+      <c r="L1" s="309"/>
+      <c r="M1" s="309"/>
+      <c r="N1" s="309"/>
+      <c r="O1" s="309"/>
+      <c r="P1" s="309"/>
+      <c r="Q1" s="309"/>
+      <c r="R1" s="309"/>
+      <c r="S1" s="309"/>
+      <c r="T1" s="309"/>
+      <c r="U1" s="309"/>
+      <c r="V1" s="309"/>
+      <c r="W1" s="309"/>
+      <c r="X1" s="309"/>
+      <c r="Y1" s="309"/>
+      <c r="Z1" s="309"/>
+      <c r="AA1" s="309"/>
+      <c r="AB1" s="311"/>
       <c r="AC1" s="17"/>
       <c r="AD1" s="17"/>
       <c r="AE1" s="1"/>
@@ -15783,36 +15790,36 @@
       <c r="AN1" s="160"/>
     </row>
     <row r="2" spans="1:43" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="313" t="s">
+      <c r="A2" s="312" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="310"/>
-      <c r="C2" s="311"/>
-      <c r="D2" s="310"/>
-      <c r="E2" s="310"/>
-      <c r="F2" s="310"/>
-      <c r="G2" s="310"/>
-      <c r="H2" s="310"/>
-      <c r="I2" s="310"/>
-      <c r="J2" s="310"/>
-      <c r="K2" s="310"/>
-      <c r="L2" s="310"/>
-      <c r="M2" s="310"/>
-      <c r="N2" s="310"/>
-      <c r="O2" s="310"/>
-      <c r="P2" s="310"/>
-      <c r="Q2" s="310"/>
-      <c r="R2" s="310"/>
-      <c r="S2" s="310"/>
-      <c r="T2" s="310"/>
-      <c r="U2" s="310"/>
-      <c r="V2" s="310"/>
-      <c r="W2" s="310"/>
-      <c r="X2" s="310"/>
-      <c r="Y2" s="310"/>
-      <c r="Z2" s="310"/>
-      <c r="AA2" s="310"/>
-      <c r="AB2" s="312"/>
+      <c r="B2" s="309"/>
+      <c r="C2" s="310"/>
+      <c r="D2" s="309"/>
+      <c r="E2" s="309"/>
+      <c r="F2" s="309"/>
+      <c r="G2" s="309"/>
+      <c r="H2" s="309"/>
+      <c r="I2" s="309"/>
+      <c r="J2" s="309"/>
+      <c r="K2" s="309"/>
+      <c r="L2" s="309"/>
+      <c r="M2" s="309"/>
+      <c r="N2" s="309"/>
+      <c r="O2" s="309"/>
+      <c r="P2" s="309"/>
+      <c r="Q2" s="309"/>
+      <c r="R2" s="309"/>
+      <c r="S2" s="309"/>
+      <c r="T2" s="309"/>
+      <c r="U2" s="309"/>
+      <c r="V2" s="309"/>
+      <c r="W2" s="309"/>
+      <c r="X2" s="309"/>
+      <c r="Y2" s="309"/>
+      <c r="Z2" s="309"/>
+      <c r="AA2" s="309"/>
+      <c r="AB2" s="311"/>
       <c r="AC2" s="17"/>
       <c r="AD2" s="17"/>
       <c r="AE2" s="1"/>
@@ -15869,92 +15876,92 @@
       <c r="AN3" s="160"/>
     </row>
     <row r="4" spans="1:43" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="314" t="s">
+      <c r="A4" s="313" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="310"/>
-      <c r="C4" s="311"/>
-      <c r="D4" s="310"/>
-      <c r="E4" s="310"/>
-      <c r="F4" s="310"/>
-      <c r="G4" s="310"/>
-      <c r="H4" s="310"/>
-      <c r="I4" s="310"/>
-      <c r="J4" s="310"/>
-      <c r="K4" s="310"/>
-      <c r="L4" s="310"/>
-      <c r="M4" s="310"/>
-      <c r="N4" s="310"/>
-      <c r="O4" s="310"/>
-      <c r="P4" s="310"/>
-      <c r="Q4" s="310"/>
-      <c r="R4" s="310"/>
-      <c r="S4" s="310"/>
-      <c r="T4" s="310"/>
-      <c r="U4" s="310"/>
-      <c r="V4" s="310"/>
-      <c r="W4" s="310"/>
-      <c r="X4" s="310"/>
-      <c r="Y4" s="310"/>
-      <c r="Z4" s="310"/>
-      <c r="AA4" s="310"/>
-      <c r="AB4" s="310"/>
-      <c r="AC4" s="311"/>
-      <c r="AD4" s="311"/>
-      <c r="AE4" s="310"/>
-      <c r="AF4" s="310"/>
-      <c r="AG4" s="311"/>
-      <c r="AH4" s="311"/>
-      <c r="AI4" s="310"/>
-      <c r="AJ4" s="311"/>
-      <c r="AK4" s="311"/>
-      <c r="AL4" s="310"/>
-      <c r="AM4" s="311"/>
-      <c r="AN4" s="312"/>
+      <c r="B4" s="309"/>
+      <c r="C4" s="310"/>
+      <c r="D4" s="309"/>
+      <c r="E4" s="309"/>
+      <c r="F4" s="309"/>
+      <c r="G4" s="309"/>
+      <c r="H4" s="309"/>
+      <c r="I4" s="309"/>
+      <c r="J4" s="309"/>
+      <c r="K4" s="309"/>
+      <c r="L4" s="309"/>
+      <c r="M4" s="309"/>
+      <c r="N4" s="309"/>
+      <c r="O4" s="309"/>
+      <c r="P4" s="309"/>
+      <c r="Q4" s="309"/>
+      <c r="R4" s="309"/>
+      <c r="S4" s="309"/>
+      <c r="T4" s="309"/>
+      <c r="U4" s="309"/>
+      <c r="V4" s="309"/>
+      <c r="W4" s="309"/>
+      <c r="X4" s="309"/>
+      <c r="Y4" s="309"/>
+      <c r="Z4" s="309"/>
+      <c r="AA4" s="309"/>
+      <c r="AB4" s="309"/>
+      <c r="AC4" s="310"/>
+      <c r="AD4" s="310"/>
+      <c r="AE4" s="309"/>
+      <c r="AF4" s="309"/>
+      <c r="AG4" s="310"/>
+      <c r="AH4" s="310"/>
+      <c r="AI4" s="309"/>
+      <c r="AJ4" s="310"/>
+      <c r="AK4" s="310"/>
+      <c r="AL4" s="309"/>
+      <c r="AM4" s="310"/>
+      <c r="AN4" s="311"/>
     </row>
     <row r="5" spans="1:43" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="315" t="s">
+      <c r="A5" s="314" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="310"/>
-      <c r="C5" s="311"/>
-      <c r="D5" s="310"/>
-      <c r="E5" s="310"/>
-      <c r="F5" s="310"/>
-      <c r="G5" s="310"/>
-      <c r="H5" s="310"/>
-      <c r="I5" s="310"/>
-      <c r="J5" s="310"/>
-      <c r="K5" s="310"/>
-      <c r="L5" s="310"/>
-      <c r="M5" s="310"/>
-      <c r="N5" s="310"/>
-      <c r="O5" s="310"/>
-      <c r="P5" s="310"/>
-      <c r="Q5" s="310"/>
-      <c r="R5" s="310"/>
-      <c r="S5" s="310"/>
-      <c r="T5" s="310"/>
-      <c r="U5" s="310"/>
-      <c r="V5" s="310"/>
-      <c r="W5" s="310"/>
-      <c r="X5" s="310"/>
-      <c r="Y5" s="310"/>
-      <c r="Z5" s="310"/>
-      <c r="AA5" s="310"/>
-      <c r="AB5" s="310"/>
-      <c r="AC5" s="311"/>
-      <c r="AD5" s="311"/>
-      <c r="AE5" s="310"/>
-      <c r="AF5" s="310"/>
-      <c r="AG5" s="311"/>
-      <c r="AH5" s="311"/>
-      <c r="AI5" s="310"/>
-      <c r="AJ5" s="311"/>
-      <c r="AK5" s="311"/>
-      <c r="AL5" s="310"/>
-      <c r="AM5" s="311"/>
-      <c r="AN5" s="312"/>
+      <c r="B5" s="309"/>
+      <c r="C5" s="310"/>
+      <c r="D5" s="309"/>
+      <c r="E5" s="309"/>
+      <c r="F5" s="309"/>
+      <c r="G5" s="309"/>
+      <c r="H5" s="309"/>
+      <c r="I5" s="309"/>
+      <c r="J5" s="309"/>
+      <c r="K5" s="309"/>
+      <c r="L5" s="309"/>
+      <c r="M5" s="309"/>
+      <c r="N5" s="309"/>
+      <c r="O5" s="309"/>
+      <c r="P5" s="309"/>
+      <c r="Q5" s="309"/>
+      <c r="R5" s="309"/>
+      <c r="S5" s="309"/>
+      <c r="T5" s="309"/>
+      <c r="U5" s="309"/>
+      <c r="V5" s="309"/>
+      <c r="W5" s="309"/>
+      <c r="X5" s="309"/>
+      <c r="Y5" s="309"/>
+      <c r="Z5" s="309"/>
+      <c r="AA5" s="309"/>
+      <c r="AB5" s="309"/>
+      <c r="AC5" s="310"/>
+      <c r="AD5" s="310"/>
+      <c r="AE5" s="309"/>
+      <c r="AF5" s="309"/>
+      <c r="AG5" s="310"/>
+      <c r="AH5" s="310"/>
+      <c r="AI5" s="309"/>
+      <c r="AJ5" s="310"/>
+      <c r="AK5" s="310"/>
+      <c r="AL5" s="309"/>
+      <c r="AM5" s="310"/>
+      <c r="AN5" s="311"/>
     </row>
     <row r="6" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -15989,212 +15996,212 @@
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
       <c r="AD6" s="11"/>
-      <c r="AE6" s="340" t="s">
+      <c r="AE6" s="338" t="s">
         <v>151</v>
       </c>
-      <c r="AF6" s="341"/>
-      <c r="AG6" s="341"/>
-      <c r="AH6" s="341"/>
-      <c r="AI6" s="341"/>
-      <c r="AJ6" s="341"/>
-      <c r="AK6" s="341"/>
-      <c r="AL6" s="341"/>
-      <c r="AM6" s="341"/>
-      <c r="AN6" s="341"/>
+      <c r="AF6" s="339"/>
+      <c r="AG6" s="339"/>
+      <c r="AH6" s="339"/>
+      <c r="AI6" s="339"/>
+      <c r="AJ6" s="339"/>
+      <c r="AK6" s="339"/>
+      <c r="AL6" s="339"/>
+      <c r="AM6" s="339"/>
+      <c r="AN6" s="339"/>
     </row>
     <row r="7" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="302" t="s">
+      <c r="A7" s="307" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="342" t="s">
+      <c r="B7" s="340" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="329" t="s">
+      <c r="C7" s="328" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="302" t="s">
+      <c r="D7" s="307" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="302" t="s">
+      <c r="E7" s="307" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="302" t="s">
+      <c r="F7" s="307" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="302" t="s">
+      <c r="G7" s="307" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="302" t="s">
+      <c r="H7" s="307" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="302" t="s">
+      <c r="I7" s="307" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="302" t="s">
+      <c r="J7" s="307" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="302" t="s">
+      <c r="K7" s="307" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="336" t="s">
+      <c r="L7" s="337" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="302" t="s">
+      <c r="M7" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="302" t="s">
+      <c r="N7" s="307" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="318" t="s">
+      <c r="O7" s="317" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="319"/>
-      <c r="Q7" s="319"/>
-      <c r="R7" s="319"/>
-      <c r="S7" s="319"/>
-      <c r="T7" s="319"/>
-      <c r="U7" s="319"/>
-      <c r="V7" s="320"/>
-      <c r="W7" s="302" t="s">
+      <c r="P7" s="318"/>
+      <c r="Q7" s="318"/>
+      <c r="R7" s="318"/>
+      <c r="S7" s="318"/>
+      <c r="T7" s="318"/>
+      <c r="U7" s="318"/>
+      <c r="V7" s="319"/>
+      <c r="W7" s="307" t="s">
         <v>139</v>
       </c>
-      <c r="X7" s="317" t="s">
+      <c r="X7" s="315" t="s">
         <v>13</v>
       </c>
-      <c r="Y7" s="317" t="s">
+      <c r="Y7" s="315" t="s">
         <v>184</v>
       </c>
-      <c r="Z7" s="330" t="s">
+      <c r="Z7" s="329" t="s">
         <v>175</v>
       </c>
-      <c r="AA7" s="302" t="s">
+      <c r="AA7" s="307" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="302" t="s">
+      <c r="AB7" s="307" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="318" t="s">
+      <c r="AC7" s="317" t="s">
         <v>155</v>
       </c>
-      <c r="AD7" s="320"/>
-      <c r="AE7" s="307" t="s">
+      <c r="AD7" s="319"/>
+      <c r="AE7" s="301" t="s">
         <v>17</v>
       </c>
-      <c r="AF7" s="304" t="s">
+      <c r="AF7" s="330" t="s">
         <v>107</v>
       </c>
-      <c r="AG7" s="304" t="s">
+      <c r="AG7" s="330" t="s">
         <v>108</v>
       </c>
-      <c r="AH7" s="304" t="s">
+      <c r="AH7" s="330" t="s">
         <v>106</v>
       </c>
-      <c r="AI7" s="306" t="s">
+      <c r="AI7" s="332" t="s">
         <v>147</v>
       </c>
-      <c r="AJ7" s="307" t="s">
+      <c r="AJ7" s="301" t="s">
         <v>136</v>
       </c>
-      <c r="AK7" s="307" t="s">
+      <c r="AK7" s="301" t="s">
         <v>137</v>
       </c>
-      <c r="AL7" s="302" t="s">
+      <c r="AL7" s="307" t="s">
         <v>135</v>
       </c>
-      <c r="AM7" s="302" t="s">
+      <c r="AM7" s="307" t="s">
         <v>146</v>
       </c>
-      <c r="AN7" s="302" t="s">
+      <c r="AN7" s="307" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="308"/>
-      <c r="B8" s="343"/>
-      <c r="C8" s="329"/>
-      <c r="D8" s="308"/>
-      <c r="E8" s="308"/>
-      <c r="F8" s="308"/>
-      <c r="G8" s="308"/>
-      <c r="H8" s="308"/>
-      <c r="I8" s="308"/>
-      <c r="J8" s="308"/>
-      <c r="K8" s="308"/>
-      <c r="L8" s="308"/>
-      <c r="M8" s="308"/>
-      <c r="N8" s="308"/>
-      <c r="O8" s="321"/>
-      <c r="P8" s="322"/>
-      <c r="Q8" s="322"/>
-      <c r="R8" s="322"/>
-      <c r="S8" s="322"/>
-      <c r="T8" s="322"/>
-      <c r="U8" s="322"/>
-      <c r="V8" s="323"/>
-      <c r="W8" s="308"/>
-      <c r="X8" s="308"/>
-      <c r="Y8" s="308"/>
-      <c r="Z8" s="308"/>
-      <c r="AA8" s="308"/>
-      <c r="AB8" s="308"/>
-      <c r="AC8" s="324"/>
-      <c r="AD8" s="326"/>
-      <c r="AE8" s="308"/>
-      <c r="AF8" s="305"/>
-      <c r="AG8" s="305"/>
-      <c r="AH8" s="306"/>
-      <c r="AI8" s="305"/>
-      <c r="AJ8" s="308"/>
-      <c r="AK8" s="307"/>
-      <c r="AL8" s="308"/>
-      <c r="AM8" s="302"/>
-      <c r="AN8" s="303"/>
+      <c r="A8" s="302"/>
+      <c r="B8" s="341"/>
+      <c r="C8" s="328"/>
+      <c r="D8" s="302"/>
+      <c r="E8" s="302"/>
+      <c r="F8" s="302"/>
+      <c r="G8" s="302"/>
+      <c r="H8" s="302"/>
+      <c r="I8" s="302"/>
+      <c r="J8" s="302"/>
+      <c r="K8" s="302"/>
+      <c r="L8" s="302"/>
+      <c r="M8" s="302"/>
+      <c r="N8" s="302"/>
+      <c r="O8" s="320"/>
+      <c r="P8" s="321"/>
+      <c r="Q8" s="321"/>
+      <c r="R8" s="321"/>
+      <c r="S8" s="321"/>
+      <c r="T8" s="321"/>
+      <c r="U8" s="321"/>
+      <c r="V8" s="322"/>
+      <c r="W8" s="302"/>
+      <c r="X8" s="302"/>
+      <c r="Y8" s="302"/>
+      <c r="Z8" s="302"/>
+      <c r="AA8" s="302"/>
+      <c r="AB8" s="302"/>
+      <c r="AC8" s="323"/>
+      <c r="AD8" s="325"/>
+      <c r="AE8" s="302"/>
+      <c r="AF8" s="331"/>
+      <c r="AG8" s="331"/>
+      <c r="AH8" s="332"/>
+      <c r="AI8" s="331"/>
+      <c r="AJ8" s="302"/>
+      <c r="AK8" s="301"/>
+      <c r="AL8" s="302"/>
+      <c r="AM8" s="307"/>
+      <c r="AN8" s="316"/>
     </row>
     <row r="9" spans="1:43" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="308"/>
-      <c r="B9" s="343"/>
-      <c r="C9" s="329"/>
-      <c r="D9" s="308"/>
-      <c r="E9" s="308"/>
-      <c r="F9" s="308"/>
-      <c r="G9" s="308"/>
-      <c r="H9" s="308"/>
-      <c r="I9" s="308"/>
-      <c r="J9" s="308"/>
-      <c r="K9" s="308"/>
-      <c r="L9" s="308"/>
-      <c r="M9" s="308"/>
-      <c r="N9" s="308"/>
-      <c r="O9" s="324"/>
-      <c r="P9" s="325"/>
-      <c r="Q9" s="325"/>
-      <c r="R9" s="325"/>
-      <c r="S9" s="325"/>
-      <c r="T9" s="325"/>
-      <c r="U9" s="325"/>
-      <c r="V9" s="326"/>
-      <c r="W9" s="308"/>
-      <c r="X9" s="308"/>
-      <c r="Y9" s="308"/>
-      <c r="Z9" s="308"/>
-      <c r="AA9" s="308"/>
-      <c r="AB9" s="308"/>
+      <c r="A9" s="302"/>
+      <c r="B9" s="341"/>
+      <c r="C9" s="328"/>
+      <c r="D9" s="302"/>
+      <c r="E9" s="302"/>
+      <c r="F9" s="302"/>
+      <c r="G9" s="302"/>
+      <c r="H9" s="302"/>
+      <c r="I9" s="302"/>
+      <c r="J9" s="302"/>
+      <c r="K9" s="302"/>
+      <c r="L9" s="302"/>
+      <c r="M9" s="302"/>
+      <c r="N9" s="302"/>
+      <c r="O9" s="323"/>
+      <c r="P9" s="324"/>
+      <c r="Q9" s="324"/>
+      <c r="R9" s="324"/>
+      <c r="S9" s="324"/>
+      <c r="T9" s="324"/>
+      <c r="U9" s="324"/>
+      <c r="V9" s="325"/>
+      <c r="W9" s="302"/>
+      <c r="X9" s="302"/>
+      <c r="Y9" s="302"/>
+      <c r="Z9" s="302"/>
+      <c r="AA9" s="302"/>
+      <c r="AB9" s="302"/>
       <c r="AC9" s="201" t="s">
         <v>153</v>
       </c>
       <c r="AD9" s="178" t="s">
         <v>154</v>
       </c>
-      <c r="AE9" s="308"/>
-      <c r="AF9" s="305"/>
-      <c r="AG9" s="305"/>
-      <c r="AH9" s="306"/>
-      <c r="AI9" s="305"/>
-      <c r="AJ9" s="308"/>
-      <c r="AK9" s="307"/>
-      <c r="AL9" s="308"/>
-      <c r="AM9" s="302"/>
-      <c r="AN9" s="303"/>
+      <c r="AE9" s="302"/>
+      <c r="AF9" s="331"/>
+      <c r="AG9" s="331"/>
+      <c r="AH9" s="332"/>
+      <c r="AI9" s="331"/>
+      <c r="AJ9" s="302"/>
+      <c r="AK9" s="301"/>
+      <c r="AL9" s="302"/>
+      <c r="AM9" s="307"/>
+      <c r="AN9" s="316"/>
       <c r="AO9">
         <f>Z11/W11</f>
         <v>0.50320398224028773</v>
@@ -22368,27 +22375,6 @@
   </sheetData>
   <autoFilter ref="A10:AQ73" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AD8"/>
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A2:AB2"/>
@@ -22405,6 +22391,27 @@
     <mergeCell ref="H7:H9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:J9"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AD8"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
   </mergeCells>
   <pageMargins left="0.17" right="0.15748031496062992" top="0.41" bottom="0.23622047244094491" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
@@ -22432,11 +22439,10 @@
     <col min="14" max="14" width="12.140625" style="214" customWidth="1"/>
     <col min="15" max="15" width="11.28515625" style="214" customWidth="1"/>
     <col min="16" max="16" width="10.7109375" style="214" customWidth="1"/>
-    <col min="17" max="17" width="11.28515625" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="10.28515625" style="102" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" style="102" customWidth="1"/>
-    <col min="21" max="21" width="11.42578125" style="102" customWidth="1"/>
+    <col min="17" max="18" width="9" customWidth="1"/>
+    <col min="19" max="19" width="10.42578125" style="102" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" style="102" customWidth="1"/>
+    <col min="21" max="21" width="9.85546875" style="102" customWidth="1"/>
     <col min="22" max="23" width="17.28515625" style="102" customWidth="1"/>
     <col min="24" max="24" width="9.5703125" customWidth="1"/>
     <col min="25" max="26" width="14.7109375" customWidth="1"/>
@@ -22445,33 +22451,33 @@
     <col min="29" max="29" width="12.140625" customWidth="1"/>
     <col min="30" max="30" width="17.5703125" customWidth="1"/>
     <col min="31" max="31" width="12.28515625" customWidth="1"/>
-    <col min="32" max="33" width="11.85546875" customWidth="1"/>
-    <col min="34" max="34" width="11.28515625" customWidth="1"/>
-    <col min="35" max="37" width="0" hidden="1" customWidth="1"/>
+    <col min="32" max="33" width="11.28515625" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" customWidth="1"/>
+    <col min="35" max="37" width="14.42578125" customWidth="1"/>
     <col min="40" max="40" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="309" t="s">
+      <c r="A1" s="308" t="s">
         <v>206</v>
       </c>
-      <c r="B1" s="310"/>
-      <c r="C1" s="311"/>
-      <c r="D1" s="310"/>
-      <c r="E1" s="310"/>
-      <c r="F1" s="310"/>
-      <c r="G1" s="310"/>
-      <c r="H1" s="310"/>
-      <c r="I1" s="310"/>
-      <c r="J1" s="310"/>
-      <c r="K1" s="310"/>
-      <c r="L1" s="310"/>
-      <c r="M1" s="310"/>
-      <c r="N1" s="310"/>
-      <c r="O1" s="310"/>
-      <c r="P1" s="310"/>
-      <c r="Q1" s="310"/>
-      <c r="R1" s="312"/>
+      <c r="B1" s="309"/>
+      <c r="C1" s="310"/>
+      <c r="D1" s="309"/>
+      <c r="E1" s="309"/>
+      <c r="F1" s="309"/>
+      <c r="G1" s="309"/>
+      <c r="H1" s="309"/>
+      <c r="I1" s="309"/>
+      <c r="J1" s="309"/>
+      <c r="K1" s="309"/>
+      <c r="L1" s="309"/>
+      <c r="M1" s="309"/>
+      <c r="N1" s="309"/>
+      <c r="O1" s="309"/>
+      <c r="P1" s="309"/>
+      <c r="Q1" s="309"/>
+      <c r="R1" s="311"/>
       <c r="S1" s="261"/>
       <c r="T1" s="261"/>
       <c r="U1" s="261"/>
@@ -22492,26 +22498,26 @@
       <c r="AH1" s="160"/>
     </row>
     <row r="2" spans="1:40" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="313" t="s">
+      <c r="A2" s="312" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="310"/>
-      <c r="C2" s="311"/>
-      <c r="D2" s="310"/>
-      <c r="E2" s="310"/>
-      <c r="F2" s="310"/>
-      <c r="G2" s="310"/>
-      <c r="H2" s="310"/>
-      <c r="I2" s="310"/>
-      <c r="J2" s="310"/>
-      <c r="K2" s="310"/>
-      <c r="L2" s="310"/>
-      <c r="M2" s="310"/>
-      <c r="N2" s="310"/>
-      <c r="O2" s="310"/>
-      <c r="P2" s="310"/>
-      <c r="Q2" s="310"/>
-      <c r="R2" s="312"/>
+      <c r="B2" s="309"/>
+      <c r="C2" s="310"/>
+      <c r="D2" s="309"/>
+      <c r="E2" s="309"/>
+      <c r="F2" s="309"/>
+      <c r="G2" s="309"/>
+      <c r="H2" s="309"/>
+      <c r="I2" s="309"/>
+      <c r="J2" s="309"/>
+      <c r="K2" s="309"/>
+      <c r="L2" s="309"/>
+      <c r="M2" s="309"/>
+      <c r="N2" s="309"/>
+      <c r="O2" s="309"/>
+      <c r="P2" s="309"/>
+      <c r="Q2" s="309"/>
+      <c r="R2" s="311"/>
       <c r="S2" s="261"/>
       <c r="T2" s="261"/>
       <c r="U2" s="261"/>
@@ -22566,80 +22572,80 @@
       <c r="AH3" s="160"/>
     </row>
     <row r="4" spans="1:40" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="314" t="s">
+      <c r="A4" s="313" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="310"/>
-      <c r="C4" s="311"/>
-      <c r="D4" s="310"/>
-      <c r="E4" s="310"/>
-      <c r="F4" s="310"/>
-      <c r="G4" s="310"/>
-      <c r="H4" s="310"/>
-      <c r="I4" s="310"/>
-      <c r="J4" s="310"/>
-      <c r="K4" s="310"/>
-      <c r="L4" s="310"/>
-      <c r="M4" s="310"/>
-      <c r="N4" s="310"/>
-      <c r="O4" s="310"/>
-      <c r="P4" s="310"/>
-      <c r="Q4" s="310"/>
-      <c r="R4" s="310"/>
-      <c r="S4" s="311"/>
-      <c r="T4" s="311"/>
-      <c r="U4" s="311"/>
-      <c r="V4" s="311"/>
-      <c r="W4" s="311"/>
-      <c r="X4" s="310"/>
-      <c r="Y4" s="310"/>
-      <c r="Z4" s="311"/>
-      <c r="AA4" s="311"/>
-      <c r="AB4" s="310"/>
-      <c r="AC4" s="311"/>
-      <c r="AD4" s="311"/>
-      <c r="AE4" s="310"/>
-      <c r="AF4" s="311"/>
-      <c r="AG4" s="311"/>
-      <c r="AH4" s="312"/>
+      <c r="B4" s="309"/>
+      <c r="C4" s="310"/>
+      <c r="D4" s="309"/>
+      <c r="E4" s="309"/>
+      <c r="F4" s="309"/>
+      <c r="G4" s="309"/>
+      <c r="H4" s="309"/>
+      <c r="I4" s="309"/>
+      <c r="J4" s="309"/>
+      <c r="K4" s="309"/>
+      <c r="L4" s="309"/>
+      <c r="M4" s="309"/>
+      <c r="N4" s="309"/>
+      <c r="O4" s="309"/>
+      <c r="P4" s="309"/>
+      <c r="Q4" s="309"/>
+      <c r="R4" s="309"/>
+      <c r="S4" s="310"/>
+      <c r="T4" s="310"/>
+      <c r="U4" s="310"/>
+      <c r="V4" s="310"/>
+      <c r="W4" s="310"/>
+      <c r="X4" s="309"/>
+      <c r="Y4" s="309"/>
+      <c r="Z4" s="310"/>
+      <c r="AA4" s="310"/>
+      <c r="AB4" s="309"/>
+      <c r="AC4" s="310"/>
+      <c r="AD4" s="310"/>
+      <c r="AE4" s="309"/>
+      <c r="AF4" s="310"/>
+      <c r="AG4" s="310"/>
+      <c r="AH4" s="311"/>
     </row>
-    <row r="5" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="315" t="s">
-        <v>235</v>
-      </c>
-      <c r="B5" s="315"/>
-      <c r="C5" s="315"/>
-      <c r="D5" s="315"/>
-      <c r="E5" s="315"/>
-      <c r="F5" s="315"/>
-      <c r="G5" s="315"/>
-      <c r="H5" s="315"/>
-      <c r="I5" s="315"/>
-      <c r="J5" s="315"/>
-      <c r="K5" s="315"/>
-      <c r="L5" s="315"/>
-      <c r="M5" s="315"/>
-      <c r="N5" s="315"/>
-      <c r="O5" s="315"/>
-      <c r="P5" s="315"/>
-      <c r="Q5" s="315"/>
-      <c r="R5" s="315"/>
-      <c r="S5" s="315"/>
-      <c r="T5" s="315"/>
-      <c r="U5" s="315"/>
-      <c r="V5" s="315"/>
-      <c r="W5" s="315"/>
-      <c r="X5" s="315"/>
-      <c r="Y5" s="315"/>
-      <c r="Z5" s="315"/>
-      <c r="AA5" s="315"/>
-      <c r="AB5" s="315"/>
-      <c r="AC5" s="315"/>
-      <c r="AD5" s="315"/>
-      <c r="AE5" s="315"/>
-      <c r="AF5" s="315"/>
-      <c r="AG5" s="316"/>
-      <c r="AH5" s="315"/>
+    <row r="5" spans="1:40" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A5" s="314" t="s">
+        <v>228</v>
+      </c>
+      <c r="B5" s="309"/>
+      <c r="C5" s="310"/>
+      <c r="D5" s="309"/>
+      <c r="E5" s="309"/>
+      <c r="F5" s="309"/>
+      <c r="G5" s="309"/>
+      <c r="H5" s="309"/>
+      <c r="I5" s="309"/>
+      <c r="J5" s="309"/>
+      <c r="K5" s="309"/>
+      <c r="L5" s="309"/>
+      <c r="M5" s="309"/>
+      <c r="N5" s="309"/>
+      <c r="O5" s="309"/>
+      <c r="P5" s="309"/>
+      <c r="Q5" s="309"/>
+      <c r="R5" s="309"/>
+      <c r="S5" s="310"/>
+      <c r="T5" s="310"/>
+      <c r="U5" s="310"/>
+      <c r="V5" s="310"/>
+      <c r="W5" s="310"/>
+      <c r="X5" s="309"/>
+      <c r="Y5" s="309"/>
+      <c r="Z5" s="310"/>
+      <c r="AA5" s="310"/>
+      <c r="AB5" s="309"/>
+      <c r="AC5" s="310"/>
+      <c r="AD5" s="310"/>
+      <c r="AE5" s="309"/>
+      <c r="AF5" s="310"/>
+      <c r="AG5" s="310"/>
+      <c r="AH5" s="311"/>
     </row>
     <row r="6" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -22664,164 +22670,164 @@
       <c r="R6" s="11"/>
       <c r="S6" s="11"/>
       <c r="T6" s="11"/>
-      <c r="U6" s="327" t="s">
+      <c r="U6" s="326" t="s">
         <v>151</v>
       </c>
-      <c r="V6" s="327"/>
-      <c r="W6" s="327"/>
-      <c r="X6" s="327"/>
-      <c r="Y6" s="327"/>
-      <c r="Z6" s="327"/>
-      <c r="AA6" s="327"/>
-      <c r="AB6" s="327"/>
-      <c r="AC6" s="327"/>
-      <c r="AD6" s="327"/>
-      <c r="AE6" s="327"/>
-      <c r="AF6" s="327"/>
-      <c r="AG6" s="327"/>
-      <c r="AH6" s="327"/>
+      <c r="V6" s="326"/>
+      <c r="W6" s="326"/>
+      <c r="X6" s="326"/>
+      <c r="Y6" s="326"/>
+      <c r="Z6" s="326"/>
+      <c r="AA6" s="326"/>
+      <c r="AB6" s="326"/>
+      <c r="AC6" s="326"/>
+      <c r="AD6" s="326"/>
+      <c r="AE6" s="326"/>
+      <c r="AF6" s="326"/>
+      <c r="AG6" s="326"/>
+      <c r="AH6" s="326"/>
     </row>
     <row r="7" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="302" t="s">
+      <c r="A7" s="307" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="302" t="s">
+      <c r="B7" s="307" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="329" t="s">
+      <c r="C7" s="328" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="302" t="s">
+      <c r="D7" s="307" t="s">
         <v>140</v>
       </c>
-      <c r="E7" s="318" t="s">
+      <c r="E7" s="317" t="s">
         <v>138</v>
       </c>
-      <c r="F7" s="319"/>
-      <c r="G7" s="319"/>
-      <c r="H7" s="319"/>
-      <c r="I7" s="319"/>
-      <c r="J7" s="319"/>
-      <c r="K7" s="319"/>
-      <c r="L7" s="320"/>
-      <c r="M7" s="302" t="s">
+      <c r="F7" s="318"/>
+      <c r="G7" s="318"/>
+      <c r="H7" s="318"/>
+      <c r="I7" s="318"/>
+      <c r="J7" s="318"/>
+      <c r="K7" s="318"/>
+      <c r="L7" s="319"/>
+      <c r="M7" s="307" t="s">
         <v>202</v>
       </c>
-      <c r="N7" s="317" t="s">
+      <c r="N7" s="315" t="s">
         <v>13</v>
       </c>
-      <c r="O7" s="317" t="s">
-        <v>236</v>
-      </c>
-      <c r="P7" s="330" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q7" s="302" t="s">
+      <c r="O7" s="315" t="s">
+        <v>229</v>
+      </c>
+      <c r="P7" s="329" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q7" s="307" t="s">
         <v>15</v>
       </c>
-      <c r="R7" s="302" t="s">
+      <c r="R7" s="307" t="s">
         <v>16</v>
       </c>
-      <c r="S7" s="331" t="s">
+      <c r="S7" s="303" t="s">
         <v>225</v>
       </c>
-      <c r="T7" s="331"/>
-      <c r="U7" s="331"/>
-      <c r="V7" s="332" t="s">
+      <c r="T7" s="303"/>
+      <c r="U7" s="303"/>
+      <c r="V7" s="304" t="s">
         <v>211</v>
       </c>
-      <c r="W7" s="332" t="s">
+      <c r="W7" s="304" t="s">
         <v>215</v>
       </c>
-      <c r="X7" s="307" t="s">
+      <c r="X7" s="301" t="s">
         <v>17</v>
       </c>
-      <c r="Y7" s="304" t="s">
+      <c r="Y7" s="330" t="s">
         <v>107</v>
       </c>
-      <c r="Z7" s="304" t="s">
+      <c r="Z7" s="330" t="s">
         <v>108</v>
       </c>
-      <c r="AA7" s="304" t="s">
+      <c r="AA7" s="330" t="s">
         <v>106</v>
       </c>
-      <c r="AB7" s="306" t="s">
+      <c r="AB7" s="332" t="s">
         <v>147</v>
       </c>
-      <c r="AC7" s="307" t="s">
+      <c r="AC7" s="301" t="s">
         <v>136</v>
       </c>
-      <c r="AD7" s="307" t="s">
+      <c r="AD7" s="301" t="s">
         <v>137</v>
       </c>
-      <c r="AE7" s="302" t="s">
+      <c r="AE7" s="307" t="s">
         <v>135</v>
       </c>
-      <c r="AF7" s="302" t="s">
+      <c r="AF7" s="307" t="s">
         <v>146</v>
       </c>
-      <c r="AG7" s="302" t="s">
-        <v>227</v>
-      </c>
-      <c r="AH7" s="302" t="s">
+      <c r="AG7" s="307" t="s">
+        <v>231</v>
+      </c>
+      <c r="AH7" s="307" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="308"/>
-      <c r="B8" s="328"/>
-      <c r="C8" s="329"/>
-      <c r="D8" s="303"/>
-      <c r="E8" s="321"/>
-      <c r="F8" s="322"/>
-      <c r="G8" s="322"/>
-      <c r="H8" s="322"/>
-      <c r="I8" s="322"/>
-      <c r="J8" s="322"/>
-      <c r="K8" s="322"/>
-      <c r="L8" s="323"/>
-      <c r="M8" s="308"/>
-      <c r="N8" s="308"/>
-      <c r="O8" s="308"/>
-      <c r="P8" s="308"/>
-      <c r="Q8" s="308"/>
-      <c r="R8" s="308"/>
-      <c r="S8" s="331"/>
-      <c r="T8" s="331"/>
-      <c r="U8" s="331"/>
-      <c r="V8" s="333"/>
-      <c r="W8" s="333"/>
-      <c r="X8" s="308"/>
-      <c r="Y8" s="305"/>
-      <c r="Z8" s="305"/>
-      <c r="AA8" s="306"/>
-      <c r="AB8" s="305"/>
-      <c r="AC8" s="308"/>
-      <c r="AD8" s="307"/>
-      <c r="AE8" s="308"/>
-      <c r="AF8" s="302"/>
-      <c r="AG8" s="302"/>
-      <c r="AH8" s="303"/>
+      <c r="A8" s="302"/>
+      <c r="B8" s="327"/>
+      <c r="C8" s="328"/>
+      <c r="D8" s="316"/>
+      <c r="E8" s="320"/>
+      <c r="F8" s="321"/>
+      <c r="G8" s="321"/>
+      <c r="H8" s="321"/>
+      <c r="I8" s="321"/>
+      <c r="J8" s="321"/>
+      <c r="K8" s="321"/>
+      <c r="L8" s="322"/>
+      <c r="M8" s="302"/>
+      <c r="N8" s="302"/>
+      <c r="O8" s="302"/>
+      <c r="P8" s="302"/>
+      <c r="Q8" s="302"/>
+      <c r="R8" s="302"/>
+      <c r="S8" s="303"/>
+      <c r="T8" s="303"/>
+      <c r="U8" s="303"/>
+      <c r="V8" s="305"/>
+      <c r="W8" s="305"/>
+      <c r="X8" s="302"/>
+      <c r="Y8" s="331"/>
+      <c r="Z8" s="331"/>
+      <c r="AA8" s="332"/>
+      <c r="AB8" s="331"/>
+      <c r="AC8" s="302"/>
+      <c r="AD8" s="301"/>
+      <c r="AE8" s="302"/>
+      <c r="AF8" s="307"/>
+      <c r="AG8" s="307"/>
+      <c r="AH8" s="316"/>
     </row>
     <row r="9" spans="1:40" ht="104.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="308"/>
-      <c r="B9" s="328"/>
-      <c r="C9" s="329"/>
-      <c r="D9" s="303"/>
-      <c r="E9" s="324"/>
-      <c r="F9" s="325"/>
-      <c r="G9" s="325"/>
-      <c r="H9" s="325"/>
-      <c r="I9" s="325"/>
-      <c r="J9" s="325"/>
-      <c r="K9" s="325"/>
-      <c r="L9" s="326"/>
-      <c r="M9" s="308"/>
-      <c r="N9" s="308"/>
-      <c r="O9" s="308"/>
-      <c r="P9" s="308"/>
-      <c r="Q9" s="308"/>
-      <c r="R9" s="308"/>
+      <c r="A9" s="302"/>
+      <c r="B9" s="327"/>
+      <c r="C9" s="328"/>
+      <c r="D9" s="316"/>
+      <c r="E9" s="323"/>
+      <c r="F9" s="324"/>
+      <c r="G9" s="324"/>
+      <c r="H9" s="324"/>
+      <c r="I9" s="324"/>
+      <c r="J9" s="324"/>
+      <c r="K9" s="324"/>
+      <c r="L9" s="325"/>
+      <c r="M9" s="302"/>
+      <c r="N9" s="302"/>
+      <c r="O9" s="302"/>
+      <c r="P9" s="302"/>
+      <c r="Q9" s="302"/>
+      <c r="R9" s="302"/>
       <c r="S9" s="263" t="s">
         <v>223</v>
       </c>
@@ -22829,24 +22835,24 @@
         <v>224</v>
       </c>
       <c r="U9" s="263" t="s">
-        <v>238</v>
-      </c>
-      <c r="V9" s="334"/>
-      <c r="W9" s="334"/>
-      <c r="X9" s="308"/>
-      <c r="Y9" s="305"/>
-      <c r="Z9" s="305"/>
-      <c r="AA9" s="306"/>
-      <c r="AB9" s="305"/>
-      <c r="AC9" s="308"/>
-      <c r="AD9" s="307"/>
-      <c r="AE9" s="308"/>
-      <c r="AF9" s="302"/>
-      <c r="AG9" s="302"/>
-      <c r="AH9" s="303"/>
+        <v>227</v>
+      </c>
+      <c r="V9" s="306"/>
+      <c r="W9" s="306"/>
+      <c r="X9" s="302"/>
+      <c r="Y9" s="331"/>
+      <c r="Z9" s="331"/>
+      <c r="AA9" s="332"/>
+      <c r="AB9" s="331"/>
+      <c r="AC9" s="302"/>
+      <c r="AD9" s="301"/>
+      <c r="AE9" s="302"/>
+      <c r="AF9" s="307"/>
+      <c r="AG9" s="307"/>
+      <c r="AH9" s="316"/>
       <c r="AI9">
         <f>P12/M12</f>
-        <v>0.75409626603409796</v>
+        <v>0.75445795170433128</v>
       </c>
       <c r="AK9">
         <v>27</v>
@@ -22939,7 +22945,7 @@
         <v>730160</v>
       </c>
     </row>
-    <row r="11" spans="1:40" ht="28.15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28"/>
       <c r="B11" s="275" t="s">
         <v>217</v>
@@ -22966,19 +22972,19 @@
       </c>
       <c r="O11" s="283">
         <f>O12</f>
-        <v>0</v>
+        <v>350.23</v>
       </c>
       <c r="P11" s="283">
         <f>P12</f>
-        <v>730211.77500000002</v>
+        <v>730562.005</v>
       </c>
       <c r="Q11" s="284">
         <f>P11/M11</f>
-        <v>0.72488603728407397</v>
+        <v>0.72523371291124117</v>
       </c>
       <c r="R11" s="285">
         <f>R12</f>
-        <v>0.81979945998742598</v>
+        <v>0.8201926587479792</v>
       </c>
       <c r="S11" s="286">
         <f>S12</f>
@@ -22987,7 +22993,7 @@
       <c r="T11" s="286"/>
       <c r="U11" s="286">
         <f>U12</f>
-        <v>25834</v>
+        <v>25483.77</v>
       </c>
       <c r="V11" s="276"/>
       <c r="W11" s="276"/>
@@ -23004,7 +23010,7 @@
       <c r="AH11" s="274"/>
       <c r="AL11" s="19">
         <f>S11+P11</f>
-        <v>756045.77500000002</v>
+        <v>756396.005</v>
       </c>
     </row>
     <row r="12" spans="1:40" s="102" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -23058,31 +23064,31 @@
       </c>
       <c r="O12" s="98">
         <f>SUM(O13:O77)</f>
-        <v>0</v>
+        <v>350.23</v>
       </c>
       <c r="P12" s="288">
         <f>SUBTOTAL(9,P13:P74)</f>
-        <v>730211.77500000002</v>
+        <v>730562.005</v>
       </c>
       <c r="Q12" s="101">
         <f>P12/M12</f>
-        <v>0.75409626603409796</v>
+        <v>0.75445795170433128</v>
       </c>
       <c r="R12" s="101">
         <f>P12/D12</f>
-        <v>0.81979945998742598</v>
-      </c>
-      <c r="S12" s="292">
+        <v>0.8201926587479792</v>
+      </c>
+      <c r="S12" s="115">
         <f>SUM(S13:S77)</f>
         <v>25834</v>
       </c>
       <c r="T12" s="115">
         <f>SUM(T13:T77)</f>
-        <v>0</v>
+        <v>350.22999999999996</v>
       </c>
       <c r="U12" s="115">
         <f>S12-T12</f>
-        <v>25834</v>
+        <v>25483.77</v>
       </c>
       <c r="V12" s="115"/>
       <c r="W12" s="115">
@@ -23091,19 +23097,19 @@
       </c>
       <c r="X12" s="98">
         <f>M12-P12</f>
-        <v>238115.22499999998</v>
+        <v>237764.995</v>
       </c>
       <c r="Y12" s="98">
         <f>N12-Q12</f>
-        <v>730211.02090373402</v>
+        <v>730211.02054204827</v>
       </c>
       <c r="Z12" s="98">
         <f>O12-R12</f>
-        <v>-0.81979945998742598</v>
+        <v>349.40980734125202</v>
       </c>
       <c r="AA12" s="98">
         <f>P12-S12</f>
-        <v>704377.77500000002</v>
+        <v>704728.005</v>
       </c>
       <c r="AB12" s="159">
         <f>SUM(AB13:AB67)</f>
@@ -23111,11 +23117,11 @@
       </c>
       <c r="AC12" s="125">
         <f t="shared" ref="AC12:AC22" si="1">M12-P12-AB12</f>
-        <v>-86644.775000000023</v>
+        <v>-86995.005000000005</v>
       </c>
       <c r="AD12" s="126">
         <f>(P12+AB12)/M12</f>
-        <v>1.0894788382436924</v>
+        <v>1.0898405239139257</v>
       </c>
       <c r="AE12" s="101"/>
       <c r="AF12" s="115">
@@ -23128,11 +23134,11 @@
       </c>
       <c r="AI12" s="117">
         <f>M12-P12</f>
-        <v>238115.22499999998</v>
+        <v>237764.995</v>
       </c>
       <c r="AJ12" s="119">
         <f>P12+S12</f>
-        <v>756045.77500000002</v>
+        <v>756396.005</v>
       </c>
       <c r="AL12" s="291"/>
       <c r="AM12" s="102">
@@ -23144,7 +23150,7 @@
         <v>677828.89999999991</v>
       </c>
     </row>
-    <row r="13" spans="1:40" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="51" t="s">
         <v>24</v>
       </c>
@@ -23175,7 +23181,7 @@
       </c>
       <c r="Q13" s="39"/>
       <c r="R13" s="56"/>
-      <c r="S13" s="293"/>
+      <c r="S13" s="56"/>
       <c r="T13" s="177"/>
       <c r="U13" s="56"/>
       <c r="V13" s="56"/>
@@ -23199,7 +23205,7 @@
       <c r="AH13" s="162"/>
       <c r="AI13" s="19">
         <f>P12+AB12</f>
-        <v>1054971.7749999999</v>
+        <v>1055322.0049999999</v>
       </c>
       <c r="AL13" s="19">
         <f>AL12-D12</f>
@@ -23207,7 +23213,7 @@
       </c>
       <c r="AN13" s="19">
         <f>AN12-P12</f>
-        <v>-52382.875000000116</v>
+        <v>-52733.105000000098</v>
       </c>
     </row>
     <row r="14" spans="1:40" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -23253,7 +23259,7 @@
       <c r="R14" s="63">
         <v>0</v>
       </c>
-      <c r="S14" s="294"/>
+      <c r="S14" s="268"/>
       <c r="T14" s="177"/>
       <c r="U14" s="268">
         <f>S14-T14</f>
@@ -23285,15 +23291,15 @@
         <f>M14-P14</f>
         <v>0</v>
       </c>
-      <c r="AG14" s="297" t="s">
-        <v>228</v>
+      <c r="AG14" s="342" t="s">
+        <v>232</v>
       </c>
       <c r="AH14" s="141" t="s">
         <v>27</v>
       </c>
       <c r="AI14" s="120">
         <f>P12/M12</f>
-        <v>0.75409626603409796</v>
+        <v>0.75445795170433128</v>
       </c>
       <c r="AK14">
         <v>2</v>
@@ -23306,7 +23312,7 @@
         <v>7264685000</v>
       </c>
     </row>
-    <row r="15" spans="1:40" ht="63" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>2</v>
       </c>
@@ -23353,7 +23359,7 @@
         <f>0%</f>
         <v>0</v>
       </c>
-      <c r="S15" s="294"/>
+      <c r="S15" s="268"/>
       <c r="T15" s="177"/>
       <c r="U15" s="268">
         <f t="shared" ref="U15:U74" si="4">S15-T15</f>
@@ -23384,8 +23390,8 @@
         <f>M15-P15</f>
         <v>0</v>
       </c>
-      <c r="AG15" s="297" t="s">
-        <v>228</v>
+      <c r="AG15" s="342" t="s">
+        <v>232</v>
       </c>
       <c r="AH15" s="141" t="s">
         <v>29</v>
@@ -23431,7 +23437,7 @@
       </c>
       <c r="Q16" s="154"/>
       <c r="R16" s="63"/>
-      <c r="S16" s="294"/>
+      <c r="S16" s="268"/>
       <c r="T16" s="177"/>
       <c r="U16" s="268">
         <f t="shared" si="4"/>
@@ -23511,7 +23517,7 @@
         <f>0%</f>
         <v>0</v>
       </c>
-      <c r="S17" s="294"/>
+      <c r="S17" s="268"/>
       <c r="T17" s="177"/>
       <c r="U17" s="268">
         <f t="shared" si="4"/>
@@ -23543,8 +23549,8 @@
         <f>M17-P17</f>
         <v>0</v>
       </c>
-      <c r="AG17" s="298" t="s">
-        <v>229</v>
+      <c r="AG17" s="343" t="s">
+        <v>233</v>
       </c>
       <c r="AH17" s="144" t="s">
         <v>39</v>
@@ -23578,7 +23584,7 @@
       </c>
       <c r="Q18" s="63"/>
       <c r="R18" s="63"/>
-      <c r="S18" s="294"/>
+      <c r="S18" s="268"/>
       <c r="T18" s="177"/>
       <c r="U18" s="268">
         <f t="shared" si="4"/>
@@ -23649,7 +23655,7 @@
         <f>P19/D19</f>
         <v>1</v>
       </c>
-      <c r="S19" s="294"/>
+      <c r="S19" s="268"/>
       <c r="T19" s="177"/>
       <c r="U19" s="268">
         <f t="shared" si="4"/>
@@ -23685,8 +23691,8 @@
         <f>M19-P19</f>
         <v>0</v>
       </c>
-      <c r="AG19" s="299" t="s">
-        <v>230</v>
+      <c r="AG19" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH19" s="166"/>
     </row>
@@ -23737,7 +23743,7 @@
         <f>P20/M20</f>
         <v>0.24731729361593788</v>
       </c>
-      <c r="S20" s="294"/>
+      <c r="S20" s="268"/>
       <c r="T20" s="177"/>
       <c r="U20" s="268">
         <f t="shared" si="4"/>
@@ -23775,8 +23781,8 @@
         <f>M20-P20</f>
         <v>11825.398000000001</v>
       </c>
-      <c r="AG20" s="298" t="s">
-        <v>229</v>
+      <c r="AG20" s="343" t="s">
+        <v>233</v>
       </c>
       <c r="AH20" s="147" t="s">
         <v>61</v>
@@ -23825,7 +23831,7 @@
         <f>P21/D21</f>
         <v>0.80633334239130428</v>
       </c>
-      <c r="S21" s="294">
+      <c r="S21" s="268">
         <v>3805</v>
       </c>
       <c r="T21" s="177"/>
@@ -23861,8 +23867,8 @@
         <f>M21-P21</f>
         <v>7126.9330000000009</v>
       </c>
-      <c r="AG21" s="298" t="s">
-        <v>229</v>
+      <c r="AG21" s="343" t="s">
+        <v>233</v>
       </c>
       <c r="AH21" s="169"/>
       <c r="AJ21" s="18">
@@ -23916,7 +23922,7 @@
         <f>P22/D22</f>
         <v>0.95975060827250602</v>
       </c>
-      <c r="S22" s="294"/>
+      <c r="S22" s="268"/>
       <c r="T22" s="177"/>
       <c r="U22" s="268">
         <f t="shared" si="4"/>
@@ -23954,8 +23960,8 @@
         <f>M22-P22</f>
         <v>132.34000000000015</v>
       </c>
-      <c r="AG22" s="299" t="s">
-        <v>230</v>
+      <c r="AG22" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH22" s="167"/>
       <c r="AI22" s="18">
@@ -24004,26 +24010,30 @@
       <c r="N23" s="273">
         <v>0</v>
       </c>
-      <c r="O23" s="210"/>
+      <c r="O23" s="210">
+        <v>5.5</v>
+      </c>
       <c r="P23" s="209">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q23" s="63"/>
       <c r="R23" s="63"/>
-      <c r="S23" s="295">
+      <c r="S23" s="292">
         <v>6</v>
       </c>
-      <c r="T23" s="177"/>
+      <c r="T23" s="177">
+        <v>5.5</v>
+      </c>
       <c r="U23" s="268">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="V23" s="268"/>
       <c r="W23" s="268"/>
       <c r="X23" s="33">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="Y23" s="64"/>
       <c r="Z23" s="64"/>
@@ -24034,7 +24044,7 @@
       <c r="AE23" s="77"/>
       <c r="AF23" s="157"/>
       <c r="AG23" s="122" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AH23" s="167"/>
       <c r="AI23" s="18"/>
@@ -24073,26 +24083,30 @@
       <c r="N24" s="273">
         <v>0</v>
       </c>
-      <c r="O24" s="210"/>
+      <c r="O24" s="210">
+        <v>22.6</v>
+      </c>
       <c r="P24" s="209">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>22.6</v>
       </c>
       <c r="Q24" s="63"/>
       <c r="R24" s="63"/>
-      <c r="S24" s="295">
+      <c r="S24" s="292">
         <v>23</v>
       </c>
-      <c r="T24" s="177"/>
+      <c r="T24" s="177">
+        <v>22.6</v>
+      </c>
       <c r="U24" s="268">
         <f t="shared" si="4"/>
-        <v>23</v>
+        <v>0.39999999999999858</v>
       </c>
       <c r="V24" s="268"/>
       <c r="W24" s="268"/>
       <c r="X24" s="33">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>0.39999999999999858</v>
       </c>
       <c r="Y24" s="64"/>
       <c r="Z24" s="64"/>
@@ -24103,12 +24117,12 @@
       <c r="AE24" s="77"/>
       <c r="AF24" s="157"/>
       <c r="AG24" s="122" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AH24" s="167"/>
       <c r="AI24" s="18"/>
     </row>
-    <row r="25" spans="1:40" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:40" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="30">
         <v>10</v>
       </c>
@@ -24145,8 +24159,8 @@
       </c>
       <c r="Q25" s="63"/>
       <c r="R25" s="63"/>
-      <c r="S25" s="295"/>
-      <c r="T25" s="210"/>
+      <c r="S25" s="292"/>
+      <c r="T25" s="297"/>
       <c r="U25" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24166,7 +24180,7 @@
       <c r="AE25" s="77"/>
       <c r="AF25" s="157"/>
       <c r="AG25" s="122" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AH25" s="167"/>
       <c r="AI25" s="18"/>
@@ -24208,8 +24222,8 @@
       </c>
       <c r="Q26" s="63"/>
       <c r="R26" s="63"/>
-      <c r="S26" s="295"/>
-      <c r="T26" s="210"/>
+      <c r="S26" s="292"/>
+      <c r="T26" s="297"/>
       <c r="U26" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24228,8 +24242,8 @@
       <c r="AD26" s="126"/>
       <c r="AE26" s="77"/>
       <c r="AF26" s="157"/>
-      <c r="AG26" s="299" t="s">
-        <v>230</v>
+      <c r="AG26" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH26" s="167"/>
       <c r="AI26" s="18"/>
@@ -24271,8 +24285,8 @@
       </c>
       <c r="Q27" s="63"/>
       <c r="R27" s="63"/>
-      <c r="S27" s="295"/>
-      <c r="T27" s="210"/>
+      <c r="S27" s="292"/>
+      <c r="T27" s="297"/>
       <c r="U27" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24292,7 +24306,7 @@
       <c r="AE27" s="77"/>
       <c r="AF27" s="157"/>
       <c r="AG27" s="122" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AH27" s="167"/>
       <c r="AI27" s="18"/>
@@ -24334,8 +24348,8 @@
       </c>
       <c r="Q28" s="63"/>
       <c r="R28" s="63"/>
-      <c r="S28" s="295"/>
-      <c r="T28" s="273"/>
+      <c r="S28" s="292"/>
+      <c r="T28" s="298"/>
       <c r="U28" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24354,8 +24368,8 @@
       <c r="AD28" s="126"/>
       <c r="AE28" s="77"/>
       <c r="AF28" s="157"/>
-      <c r="AG28" s="299" t="s">
-        <v>230</v>
+      <c r="AG28" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH28" s="167"/>
       <c r="AI28" s="18"/>
@@ -24397,8 +24411,8 @@
       </c>
       <c r="Q29" s="63"/>
       <c r="R29" s="63"/>
-      <c r="S29" s="295"/>
-      <c r="T29" s="210"/>
+      <c r="S29" s="292"/>
+      <c r="T29" s="297"/>
       <c r="U29" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24417,8 +24431,8 @@
       <c r="AD29" s="126"/>
       <c r="AE29" s="77"/>
       <c r="AF29" s="157"/>
-      <c r="AG29" s="297" t="s">
-        <v>228</v>
+      <c r="AG29" s="342" t="s">
+        <v>232</v>
       </c>
       <c r="AH29" s="167"/>
       <c r="AI29" s="18"/>
@@ -24461,8 +24475,8 @@
       </c>
       <c r="Q30" s="63"/>
       <c r="R30" s="63"/>
-      <c r="S30" s="295"/>
-      <c r="T30" s="210"/>
+      <c r="S30" s="292"/>
+      <c r="T30" s="297"/>
       <c r="U30" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24481,8 +24495,8 @@
       <c r="AD30" s="126"/>
       <c r="AE30" s="77"/>
       <c r="AF30" s="157"/>
-      <c r="AG30" s="299" t="s">
-        <v>230</v>
+      <c r="AG30" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH30" s="167"/>
       <c r="AI30" s="18"/>
@@ -24524,8 +24538,8 @@
       </c>
       <c r="Q31" s="63"/>
       <c r="R31" s="63"/>
-      <c r="S31" s="295"/>
-      <c r="T31" s="210"/>
+      <c r="S31" s="292"/>
+      <c r="T31" s="297"/>
       <c r="U31" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24544,8 +24558,8 @@
       <c r="AD31" s="126"/>
       <c r="AE31" s="77"/>
       <c r="AF31" s="157"/>
-      <c r="AG31" s="299" t="s">
-        <v>230</v>
+      <c r="AG31" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH31" s="167"/>
       <c r="AI31" s="18"/>
@@ -24587,8 +24601,8 @@
       </c>
       <c r="Q32" s="63"/>
       <c r="R32" s="63"/>
-      <c r="S32" s="295"/>
-      <c r="T32" s="210"/>
+      <c r="S32" s="292"/>
+      <c r="T32" s="297"/>
       <c r="U32" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24608,7 +24622,7 @@
       <c r="AE32" s="77"/>
       <c r="AF32" s="157"/>
       <c r="AG32" s="122" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AH32" s="167"/>
       <c r="AI32" s="18"/>
@@ -24650,8 +24664,8 @@
       </c>
       <c r="Q33" s="63"/>
       <c r="R33" s="63"/>
-      <c r="S33" s="295"/>
-      <c r="T33" s="210"/>
+      <c r="S33" s="292"/>
+      <c r="T33" s="297"/>
       <c r="U33" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24671,7 +24685,7 @@
       <c r="AE33" s="77"/>
       <c r="AF33" s="157"/>
       <c r="AG33" s="122" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AH33" s="167"/>
       <c r="AI33" s="18"/>
@@ -24713,8 +24727,8 @@
       </c>
       <c r="Q34" s="63"/>
       <c r="R34" s="63"/>
-      <c r="S34" s="295"/>
-      <c r="T34" s="210"/>
+      <c r="S34" s="292"/>
+      <c r="T34" s="297"/>
       <c r="U34" s="268">
         <f>S34-T34</f>
         <v>0</v>
@@ -24733,8 +24747,8 @@
       <c r="AD34" s="126"/>
       <c r="AE34" s="77"/>
       <c r="AF34" s="157"/>
-      <c r="AG34" s="299" t="s">
-        <v>230</v>
+      <c r="AG34" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH34" s="167"/>
       <c r="AI34" s="18"/>
@@ -24767,8 +24781,8 @@
       </c>
       <c r="Q35" s="63"/>
       <c r="R35" s="63"/>
-      <c r="S35" s="295"/>
-      <c r="T35" s="177"/>
+      <c r="S35" s="292"/>
+      <c r="T35" s="296"/>
       <c r="U35" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24793,7 +24807,7 @@
       <c r="AD35" s="126"/>
       <c r="AE35" s="67"/>
       <c r="AF35" s="64"/>
-      <c r="AG35" s="300"/>
+      <c r="AG35" s="345"/>
       <c r="AH35" s="170"/>
     </row>
     <row r="36" spans="1:39" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -24843,8 +24857,8 @@
         <f t="shared" ref="R36:R43" si="9">P36/D36</f>
         <v>0.99048349961627014</v>
       </c>
-      <c r="S36" s="295"/>
-      <c r="T36" s="177"/>
+      <c r="S36" s="292"/>
+      <c r="T36" s="296"/>
       <c r="U36" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24877,8 +24891,8 @@
         <f t="shared" ref="AF36:AF62" si="11">M36-P36</f>
         <v>62</v>
       </c>
-      <c r="AG36" s="298" t="s">
-        <v>229</v>
+      <c r="AG36" s="343" t="s">
+        <v>233</v>
       </c>
       <c r="AH36" s="168"/>
       <c r="AL36" s="18">
@@ -24929,8 +24943,8 @@
         <f t="shared" si="9"/>
         <v>0.7749230132450331</v>
       </c>
-      <c r="S37" s="295"/>
-      <c r="T37" s="177"/>
+      <c r="S37" s="292"/>
+      <c r="T37" s="296"/>
       <c r="U37" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24961,8 +24975,8 @@
         <f t="shared" si="11"/>
         <v>271.89300000000003</v>
       </c>
-      <c r="AG37" s="297" t="s">
-        <v>228</v>
+      <c r="AG37" s="342" t="s">
+        <v>232</v>
       </c>
       <c r="AH37" s="169"/>
       <c r="AJ37" s="19">
@@ -25021,10 +25035,10 @@
         <f t="shared" si="9"/>
         <v>0.77321600000000001</v>
       </c>
-      <c r="S38" s="295">
+      <c r="S38" s="292">
         <v>2835</v>
       </c>
-      <c r="T38" s="177"/>
+      <c r="T38" s="296"/>
       <c r="U38" s="268">
         <f t="shared" si="4"/>
         <v>2835</v>
@@ -25057,8 +25071,8 @@
         <f t="shared" si="11"/>
         <v>4834.7999999999993</v>
       </c>
-      <c r="AG38" s="299" t="s">
-        <v>230</v>
+      <c r="AG38" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH38" s="167"/>
       <c r="AI38" s="22"/>
@@ -25117,8 +25131,8 @@
         <f t="shared" si="9"/>
         <v>0.77485844459052067</v>
       </c>
-      <c r="S39" s="295"/>
-      <c r="T39" s="177"/>
+      <c r="S39" s="292"/>
+      <c r="T39" s="296"/>
       <c r="U39" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -25155,8 +25169,8 @@
         <f t="shared" si="11"/>
         <v>4912.57</v>
       </c>
-      <c r="AG39" s="297" t="s">
-        <v>228</v>
+      <c r="AG39" s="342" t="s">
+        <v>232</v>
       </c>
       <c r="AH39" s="166"/>
       <c r="AJ39" s="19"/>
@@ -25208,10 +25222,10 @@
         <f t="shared" si="9"/>
         <v>0.70569982963525524</v>
       </c>
-      <c r="S40" s="295">
+      <c r="S40" s="292">
         <v>2158</v>
       </c>
-      <c r="T40" s="177"/>
+      <c r="T40" s="296"/>
       <c r="U40" s="268">
         <f t="shared" si="4"/>
         <v>2158</v>
@@ -25249,7 +25263,7 @@
         <v>16038.010000000002</v>
       </c>
       <c r="AG40" s="122" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AH40" s="169"/>
       <c r="AL40">
@@ -25303,8 +25317,8 @@
         <f t="shared" si="9"/>
         <v>0.83418213706608435</v>
       </c>
-      <c r="S41" s="295"/>
-      <c r="T41" s="177"/>
+      <c r="S41" s="292"/>
+      <c r="T41" s="296"/>
       <c r="U41" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -25337,8 +25351,8 @@
         <f t="shared" si="11"/>
         <v>10021.699999999997</v>
       </c>
-      <c r="AG41" s="299" t="s">
-        <v>230</v>
+      <c r="AG41" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH41" s="169"/>
       <c r="AL41" s="18">
@@ -25391,8 +25405,8 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S42" s="295"/>
-      <c r="T42" s="177"/>
+      <c r="S42" s="292"/>
+      <c r="T42" s="296"/>
       <c r="U42" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -25423,8 +25437,8 @@
         <f t="shared" si="11"/>
         <v>420</v>
       </c>
-      <c r="AG42" s="299" t="s">
-        <v>230</v>
+      <c r="AG42" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH42" s="169"/>
       <c r="AI42" s="18">
@@ -25479,8 +25493,8 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S43" s="295"/>
-      <c r="T43" s="177"/>
+      <c r="S43" s="292"/>
+      <c r="T43" s="296"/>
       <c r="U43" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -25512,7 +25526,7 @@
         <v>125</v>
       </c>
       <c r="AG43" s="122" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AH43" s="167"/>
       <c r="AI43" s="18">
@@ -25567,8 +25581,8 @@
       <c r="R44" s="63">
         <v>0</v>
       </c>
-      <c r="S44" s="295"/>
-      <c r="T44" s="177"/>
+      <c r="S44" s="292"/>
+      <c r="T44" s="296"/>
       <c r="U44" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -25599,8 +25613,8 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AG44" s="298" t="s">
-        <v>229</v>
+      <c r="AG44" s="343" t="s">
+        <v>233</v>
       </c>
       <c r="AH44" s="174" t="s">
         <v>74</v>
@@ -25654,8 +25668,8 @@
         <f t="shared" ref="R45:R59" si="13">P45/D45</f>
         <v>0</v>
       </c>
-      <c r="S45" s="295"/>
-      <c r="T45" s="177"/>
+      <c r="S45" s="292"/>
+      <c r="T45" s="296"/>
       <c r="U45" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -25686,8 +25700,8 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AG45" s="297" t="s">
-        <v>228</v>
+      <c r="AG45" s="342" t="s">
+        <v>232</v>
       </c>
       <c r="AH45" s="166"/>
       <c r="AI45">
@@ -25739,8 +25753,8 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S46" s="295"/>
-      <c r="T46" s="177"/>
+      <c r="S46" s="292"/>
+      <c r="T46" s="296"/>
       <c r="U46" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -25771,8 +25785,8 @@
         <f t="shared" si="11"/>
         <v>191</v>
       </c>
-      <c r="AG46" s="299" t="s">
-        <v>230</v>
+      <c r="AG46" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH46" s="167"/>
       <c r="AI46" s="19">
@@ -25826,8 +25840,8 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S47" s="295"/>
-      <c r="T47" s="177"/>
+      <c r="S47" s="292"/>
+      <c r="T47" s="296"/>
       <c r="U47" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -25859,7 +25873,7 @@
         <v>33</v>
       </c>
       <c r="AG47" s="122" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AH47" s="166"/>
       <c r="AK47">
@@ -25909,8 +25923,8 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S48" s="294"/>
-      <c r="T48" s="177"/>
+      <c r="S48" s="268"/>
+      <c r="T48" s="296"/>
       <c r="U48" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -25941,8 +25955,8 @@
         <f t="shared" si="11"/>
         <v>10</v>
       </c>
-      <c r="AG48" s="299" t="s">
-        <v>230</v>
+      <c r="AG48" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH48" s="166"/>
     </row>
@@ -25989,8 +26003,8 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S49" s="294"/>
-      <c r="T49" s="177"/>
+      <c r="S49" s="268"/>
+      <c r="T49" s="296"/>
       <c r="U49" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26022,7 +26036,7 @@
         <v>10</v>
       </c>
       <c r="AG49" s="122" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AH49" s="166"/>
     </row>
@@ -26069,8 +26083,8 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S50" s="294"/>
-      <c r="T50" s="177"/>
+      <c r="S50" s="268"/>
+      <c r="T50" s="296"/>
       <c r="U50" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26101,8 +26115,8 @@
         <f t="shared" si="11"/>
         <v>20</v>
       </c>
-      <c r="AG50" s="297" t="s">
-        <v>228</v>
+      <c r="AG50" s="342" t="s">
+        <v>232</v>
       </c>
       <c r="AH50" s="166"/>
     </row>
@@ -26149,8 +26163,8 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S51" s="294"/>
-      <c r="T51" s="177"/>
+      <c r="S51" s="268"/>
+      <c r="T51" s="296"/>
       <c r="U51" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26181,8 +26195,8 @@
         <f t="shared" si="11"/>
         <v>50</v>
       </c>
-      <c r="AG51" s="297" t="s">
-        <v>228</v>
+      <c r="AG51" s="342" t="s">
+        <v>232</v>
       </c>
       <c r="AH51" s="166"/>
     </row>
@@ -26229,8 +26243,8 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S52" s="294"/>
-      <c r="T52" s="177"/>
+      <c r="S52" s="268"/>
+      <c r="T52" s="296"/>
       <c r="U52" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26261,8 +26275,8 @@
         <f t="shared" si="11"/>
         <v>50</v>
       </c>
-      <c r="AG52" s="299" t="s">
-        <v>230</v>
+      <c r="AG52" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH52" s="171"/>
       <c r="AN52" s="176">
@@ -26313,8 +26327,8 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S53" s="294"/>
-      <c r="T53" s="177"/>
+      <c r="S53" s="268"/>
+      <c r="T53" s="296"/>
       <c r="U53" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26345,8 +26359,8 @@
         <f t="shared" si="11"/>
         <v>15</v>
       </c>
-      <c r="AG53" s="299" t="s">
-        <v>230</v>
+      <c r="AG53" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH53" s="167"/>
       <c r="AN53" s="176">
@@ -26397,8 +26411,8 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S54" s="294"/>
-      <c r="T54" s="177"/>
+      <c r="S54" s="268"/>
+      <c r="T54" s="296"/>
       <c r="U54" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26430,7 +26444,7 @@
         <v>33</v>
       </c>
       <c r="AG54" s="122" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AH54" s="167"/>
     </row>
@@ -26477,8 +26491,8 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S55" s="294"/>
-      <c r="T55" s="177"/>
+      <c r="S55" s="268"/>
+      <c r="T55" s="296"/>
       <c r="U55" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26509,8 +26523,8 @@
         <f t="shared" si="11"/>
         <v>50</v>
       </c>
-      <c r="AG55" s="299" t="s">
-        <v>230</v>
+      <c r="AG55" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH55" s="167"/>
     </row>
@@ -26557,8 +26571,8 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S56" s="294"/>
-      <c r="T56" s="177"/>
+      <c r="S56" s="268"/>
+      <c r="T56" s="296"/>
       <c r="U56" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26589,8 +26603,8 @@
         <f t="shared" si="11"/>
         <v>50</v>
       </c>
-      <c r="AG56" s="297" t="s">
-        <v>228</v>
+      <c r="AG56" s="342" t="s">
+        <v>232</v>
       </c>
       <c r="AH56" s="167"/>
     </row>
@@ -26637,8 +26651,8 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S57" s="294"/>
-      <c r="T57" s="177"/>
+      <c r="S57" s="268"/>
+      <c r="T57" s="296"/>
       <c r="U57" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26670,7 +26684,7 @@
         <v>6</v>
       </c>
       <c r="AG57" s="122" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AH57" s="167"/>
     </row>
@@ -26717,8 +26731,8 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S58" s="294"/>
-      <c r="T58" s="177"/>
+      <c r="S58" s="268"/>
+      <c r="T58" s="296"/>
       <c r="U58" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26750,7 +26764,7 @@
         <v>23</v>
       </c>
       <c r="AG58" s="122" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AH58" s="167"/>
     </row>
@@ -26797,8 +26811,8 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S59" s="294"/>
-      <c r="T59" s="177"/>
+      <c r="S59" s="268"/>
+      <c r="T59" s="296"/>
       <c r="U59" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26829,8 +26843,8 @@
         <f t="shared" si="11"/>
         <v>25</v>
       </c>
-      <c r="AG59" s="299" t="s">
-        <v>230</v>
+      <c r="AG59" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH59" s="167"/>
     </row>
@@ -26875,10 +26889,10 @@
       <c r="R60" s="63">
         <v>0</v>
       </c>
-      <c r="S60" s="294">
+      <c r="S60" s="268">
         <v>265</v>
       </c>
-      <c r="T60" s="177"/>
+      <c r="T60" s="296"/>
       <c r="U60" s="268">
         <f t="shared" si="4"/>
         <v>265</v>
@@ -26911,8 +26925,8 @@
         <f t="shared" si="11"/>
         <v>265</v>
       </c>
-      <c r="AG60" s="299" t="s">
-        <v>230</v>
+      <c r="AG60" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH60" s="167"/>
       <c r="AL60">
@@ -26963,10 +26977,10 @@
         <f>P61/D61</f>
         <v>0.54837978146499378</v>
       </c>
-      <c r="S61" s="294">
+      <c r="S61" s="268">
         <v>10000</v>
       </c>
-      <c r="T61" s="177"/>
+      <c r="T61" s="296"/>
       <c r="U61" s="268">
         <f t="shared" si="4"/>
         <v>10000</v>
@@ -26999,8 +27013,8 @@
         <f t="shared" si="11"/>
         <v>27898.839000000007</v>
       </c>
-      <c r="AG61" s="297" t="s">
-        <v>228</v>
+      <c r="AG61" s="342" t="s">
+        <v>232</v>
       </c>
       <c r="AH61" s="167"/>
       <c r="AL61">
@@ -27010,7 +27024,7 @@
         <v>37065</v>
       </c>
     </row>
-    <row r="62" spans="1:40" ht="60" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="30">
         <v>46</v>
       </c>
@@ -27057,8 +27071,8 @@
         <f>P62/D62</f>
         <v>0.98030568115576699</v>
       </c>
-      <c r="S62" s="294"/>
-      <c r="T62" s="177"/>
+      <c r="S62" s="268"/>
+      <c r="T62" s="296"/>
       <c r="U62" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -27091,8 +27105,8 @@
         <f t="shared" si="11"/>
         <v>62200.460000000021</v>
       </c>
-      <c r="AG62" s="299" t="s">
-        <v>230</v>
+      <c r="AG62" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH62" s="147" t="s">
         <v>152</v>
@@ -27143,8 +27157,8 @@
       </c>
       <c r="Q63" s="63"/>
       <c r="R63" s="63"/>
-      <c r="S63" s="294"/>
-      <c r="T63" s="114"/>
+      <c r="S63" s="268"/>
+      <c r="T63" s="113"/>
       <c r="U63" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -27169,7 +27183,7 @@
       <c r="AD63" s="126"/>
       <c r="AE63" s="67"/>
       <c r="AF63" s="67"/>
-      <c r="AG63" s="301"/>
+      <c r="AG63" s="346"/>
       <c r="AH63" s="172"/>
       <c r="AJ63" s="21">
         <f>AJ62-P62</f>
@@ -27179,8 +27193,11 @@
         <f>AK62-P62</f>
         <v>-330443.53999999998</v>
       </c>
+      <c r="AM63">
+        <v>20</v>
+      </c>
     </row>
-    <row r="64" spans="1:40" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="30">
         <v>1</v>
       </c>
@@ -27214,57 +27231,65 @@
       <c r="N64" s="273">
         <v>3576.73</v>
       </c>
-      <c r="O64" s="210"/>
+      <c r="O64" s="294">
+        <f>19.75+42.64+0.67</f>
+        <v>63.06</v>
+      </c>
       <c r="P64" s="209">
         <f t="shared" si="12"/>
-        <v>3576.73</v>
+        <v>3639.79</v>
       </c>
       <c r="Q64" s="186">
         <f t="shared" ref="Q64:Q71" si="16">P64/M64</f>
-        <v>0.52660924617196703</v>
+        <v>0.53589369846878676</v>
       </c>
       <c r="R64" s="63">
         <v>0</v>
       </c>
-      <c r="S64" s="294"/>
-      <c r="T64" s="268"/>
+      <c r="S64" s="268"/>
+      <c r="T64" s="299">
+        <v>63.06</v>
+      </c>
       <c r="U64" s="268">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-63.06</v>
       </c>
       <c r="V64" s="268"/>
       <c r="W64" s="268"/>
       <c r="X64" s="33">
         <f t="shared" si="15"/>
-        <v>3215.27</v>
+        <v>3152.21</v>
       </c>
       <c r="Y64" s="64"/>
       <c r="Z64" s="64"/>
       <c r="AA64" s="41">
         <f t="shared" si="3"/>
-        <v>3215.27</v>
+        <v>3152.21</v>
       </c>
       <c r="AB64" s="65"/>
       <c r="AC64" s="125">
         <f t="shared" si="7"/>
-        <v>3215.27</v>
+        <v>3152.21</v>
       </c>
       <c r="AD64" s="126">
         <f>(P64+AB64)/M64</f>
-        <v>0.52660924617196703</v>
+        <v>0.53589369846878676</v>
       </c>
       <c r="AE64" s="67"/>
       <c r="AF64" s="67"/>
       <c r="AG64" s="173" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AH64" s="173"/>
       <c r="AK64" s="24">
         <f>383-60</f>
         <v>323</v>
       </c>
+      <c r="AM64">
+        <v>43</v>
+      </c>
     </row>
-    <row r="65" spans="1:38" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:40" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="30">
         <v>2</v>
       </c>
@@ -27298,58 +27323,66 @@
       <c r="N65" s="273">
         <v>3484</v>
       </c>
-      <c r="O65" s="210"/>
+      <c r="O65" s="294">
+        <f>23.57+18.54+0.83</f>
+        <v>42.94</v>
+      </c>
       <c r="P65" s="209">
         <f t="shared" si="12"/>
-        <v>3484</v>
+        <v>3526.94</v>
       </c>
       <c r="Q65" s="186">
         <f t="shared" si="16"/>
-        <v>0.84975609756097559</v>
+        <v>0.86022926829268298</v>
       </c>
       <c r="R65" s="63">
         <v>0</v>
       </c>
-      <c r="S65" s="294">
+      <c r="S65" s="268">
         <v>1316</v>
       </c>
-      <c r="T65" s="268"/>
+      <c r="T65" s="299">
+        <v>42.94</v>
+      </c>
       <c r="U65" s="268">
         <f t="shared" si="4"/>
-        <v>1316</v>
+        <v>1273.06</v>
       </c>
       <c r="V65" s="268"/>
       <c r="W65" s="268"/>
       <c r="X65" s="33">
         <f t="shared" si="15"/>
-        <v>616</v>
+        <v>573.05999999999995</v>
       </c>
       <c r="Y65" s="64"/>
       <c r="Z65" s="64"/>
       <c r="AA65" s="41">
         <f t="shared" si="3"/>
-        <v>616</v>
+        <v>573.05999999999995</v>
       </c>
       <c r="AB65" s="65"/>
       <c r="AC65" s="125">
         <f t="shared" si="7"/>
-        <v>616</v>
+        <v>573.05999999999995</v>
       </c>
       <c r="AD65" s="126">
         <f>(P65+AB65)/M65</f>
-        <v>0.84975609756097559</v>
+        <v>0.86022926829268298</v>
       </c>
       <c r="AE65" s="67"/>
       <c r="AF65" s="67"/>
       <c r="AG65" s="173" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AH65" s="173"/>
       <c r="AL65">
         <v>4800</v>
       </c>
+      <c r="AM65">
+        <v>0.7</v>
+      </c>
     </row>
-    <row r="66" spans="1:38" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:40" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="30">
         <v>3</v>
       </c>
@@ -27395,10 +27428,10 @@
       <c r="R66" s="63">
         <v>0</v>
       </c>
-      <c r="S66" s="294">
+      <c r="S66" s="268">
         <v>5426</v>
       </c>
-      <c r="T66" s="268"/>
+      <c r="T66" s="299"/>
       <c r="U66" s="268">
         <f t="shared" si="4"/>
         <v>5426</v>
@@ -27427,7 +27460,7 @@
       <c r="AE66" s="64"/>
       <c r="AF66" s="64"/>
       <c r="AG66" s="173" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AH66" s="173"/>
       <c r="AL66" s="18">
@@ -27435,7 +27468,7 @@
         <v>5425.7</v>
       </c>
     </row>
-    <row r="67" spans="1:38" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:40" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="30">
         <v>4</v>
       </c>
@@ -27472,53 +27505,57 @@
       <c r="N67" s="273">
         <v>684</v>
       </c>
-      <c r="O67" s="210"/>
+      <c r="O67" s="295">
+        <v>1.76</v>
+      </c>
       <c r="P67" s="209">
         <f t="shared" si="12"/>
-        <v>684</v>
+        <v>685.76</v>
       </c>
       <c r="Q67" s="186">
         <f t="shared" si="16"/>
-        <v>5.4719999999999998E-2</v>
+        <v>5.4860800000000001E-2</v>
       </c>
       <c r="R67" s="63">
         <v>0</v>
       </c>
-      <c r="S67" s="294"/>
-      <c r="T67" s="268"/>
+      <c r="S67" s="268"/>
+      <c r="T67" s="299">
+        <v>1.76</v>
+      </c>
       <c r="U67" s="268">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-1.76</v>
       </c>
       <c r="V67" s="268"/>
       <c r="W67" s="268"/>
       <c r="X67" s="33">
         <f t="shared" si="15"/>
-        <v>11816</v>
+        <v>11814.24</v>
       </c>
       <c r="Y67" s="64"/>
       <c r="Z67" s="64"/>
       <c r="AA67" s="41">
         <f t="shared" si="3"/>
-        <v>11816</v>
+        <v>11814.24</v>
       </c>
       <c r="AB67" s="65"/>
       <c r="AC67" s="125">
         <f t="shared" si="7"/>
-        <v>11816</v>
+        <v>11814.24</v>
       </c>
       <c r="AD67" s="126">
         <f>(P67+AB67)/M67</f>
-        <v>5.4719999999999998E-2</v>
+        <v>5.4860800000000001E-2</v>
       </c>
       <c r="AE67" s="67"/>
       <c r="AF67" s="67"/>
-      <c r="AG67" s="297" t="s">
-        <v>228</v>
+      <c r="AG67" s="342" t="s">
+        <v>232</v>
       </c>
       <c r="AH67" s="173"/>
     </row>
-    <row r="68" spans="1:38" ht="61.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:40" ht="61.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="30">
         <v>5</v>
       </c>
@@ -27552,29 +27589,34 @@
       <c r="N68" s="273">
         <v>2114.1</v>
       </c>
-      <c r="O68" s="211"/>
+      <c r="O68" s="211">
+        <f>10.68+18.49+0.5</f>
+        <v>29.669999999999998</v>
+      </c>
       <c r="P68" s="209">
         <f t="shared" si="12"/>
-        <v>2114.1</v>
+        <v>2143.77</v>
       </c>
       <c r="Q68" s="187">
         <f t="shared" si="16"/>
-        <v>0.45958695652173909</v>
+        <v>0.46603695652173915</v>
       </c>
       <c r="R68" s="63">
         <v>0</v>
       </c>
-      <c r="S68" s="294"/>
-      <c r="T68" s="268"/>
+      <c r="S68" s="268"/>
+      <c r="T68" s="299">
+        <v>29.67</v>
+      </c>
       <c r="U68" s="268">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-29.67</v>
       </c>
       <c r="V68" s="268"/>
       <c r="W68" s="268"/>
       <c r="X68" s="33">
         <f t="shared" si="15"/>
-        <v>2485.9</v>
+        <v>2456.23</v>
       </c>
       <c r="Y68" s="179"/>
       <c r="Z68" s="179"/>
@@ -27582,24 +27624,24 @@
       <c r="AB68" s="179"/>
       <c r="AC68" s="179">
         <f t="shared" si="7"/>
-        <v>2485.9</v>
+        <v>2456.23</v>
       </c>
       <c r="AD68" s="179">
         <f>(P68+AB68)/M68</f>
-        <v>0.45958695652173909</v>
+        <v>0.46603695652173915</v>
       </c>
       <c r="AE68" s="179"/>
       <c r="AF68" s="179"/>
       <c r="AG68" s="173" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AH68" s="173"/>
       <c r="AL68">
         <f>470-P68</f>
-        <v>-1644.1</v>
+        <v>-1673.77</v>
       </c>
     </row>
-    <row r="69" spans="1:38" ht="135.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:40" ht="135.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="30">
         <v>6</v>
       </c>
@@ -27633,29 +27675,34 @@
       <c r="N69" s="273">
         <v>5777.4</v>
       </c>
-      <c r="O69" s="212"/>
+      <c r="O69" s="212">
+        <f>31.8+46.76+40.49+1.28</f>
+        <v>120.33000000000001</v>
+      </c>
       <c r="P69" s="209">
         <f t="shared" si="12"/>
-        <v>5777.4</v>
+        <v>5897.73</v>
       </c>
       <c r="Q69" s="197">
         <f t="shared" si="16"/>
-        <v>0.50678947368421046</v>
+        <v>0.51734473684210525</v>
       </c>
       <c r="R69" s="198">
         <v>0</v>
       </c>
-      <c r="S69" s="294"/>
-      <c r="T69" s="268"/>
+      <c r="S69" s="268"/>
+      <c r="T69" s="299">
+        <v>120.33</v>
+      </c>
       <c r="U69" s="268">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-120.33</v>
       </c>
       <c r="V69" s="268"/>
       <c r="W69" s="268"/>
       <c r="X69" s="33">
         <f t="shared" si="15"/>
-        <v>5622.6</v>
+        <v>5502.27</v>
       </c>
       <c r="Y69" s="179"/>
       <c r="Z69" s="179"/>
@@ -27665,12 +27712,16 @@
       <c r="AD69" s="179"/>
       <c r="AE69" s="179"/>
       <c r="AF69" s="179"/>
-      <c r="AG69" s="298" t="s">
-        <v>229</v>
+      <c r="AG69" s="343" t="s">
+        <v>233</v>
       </c>
       <c r="AH69" s="200"/>
+      <c r="AN69">
+        <f>77+40+1.2</f>
+        <v>118.2</v>
+      </c>
     </row>
-    <row r="70" spans="1:38" s="20" customFormat="1" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:40" s="20" customFormat="1" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="30">
         <v>7</v>
       </c>
@@ -27704,29 +27755,34 @@
       <c r="N70" s="273">
         <v>5391</v>
       </c>
-      <c r="O70" s="211"/>
+      <c r="O70" s="211">
+        <f>37.2+1.23</f>
+        <v>38.43</v>
+      </c>
       <c r="P70" s="209">
         <f t="shared" si="12"/>
-        <v>5391</v>
+        <v>5429.43</v>
       </c>
       <c r="Q70" s="189">
         <f t="shared" si="16"/>
-        <v>0.49156560590863502</v>
+        <v>0.49506975471870157</v>
       </c>
       <c r="R70" s="63">
         <v>0</v>
       </c>
-      <c r="S70" s="294"/>
-      <c r="T70" s="268"/>
+      <c r="S70" s="268"/>
+      <c r="T70" s="299">
+        <v>38.43</v>
+      </c>
       <c r="U70" s="268">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-38.43</v>
       </c>
       <c r="V70" s="268"/>
       <c r="W70" s="268"/>
       <c r="X70" s="33">
         <f t="shared" si="15"/>
-        <v>5576</v>
+        <v>5537.57</v>
       </c>
       <c r="Y70" s="184"/>
       <c r="Z70" s="184"/>
@@ -27736,12 +27792,12 @@
       <c r="AD70" s="184"/>
       <c r="AE70" s="184"/>
       <c r="AF70" s="184"/>
-      <c r="AG70" s="298" t="s">
-        <v>229</v>
+      <c r="AG70" s="343" t="s">
+        <v>233</v>
       </c>
       <c r="AH70" s="173"/>
     </row>
-    <row r="71" spans="1:38" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:40" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="30">
         <v>8</v>
       </c>
@@ -27775,29 +27831,34 @@
       <c r="N71" s="273">
         <v>3951</v>
       </c>
-      <c r="O71" s="213"/>
+      <c r="O71" s="213">
+        <f>24.6+1.34</f>
+        <v>25.94</v>
+      </c>
       <c r="P71" s="209">
         <f t="shared" si="12"/>
-        <v>3951</v>
+        <v>3976.94</v>
       </c>
       <c r="Q71" s="189">
         <f t="shared" si="16"/>
-        <v>0.55860313869645128</v>
+        <v>0.56227060653188177</v>
       </c>
       <c r="R71" s="63">
         <v>0</v>
       </c>
-      <c r="S71" s="294"/>
-      <c r="T71" s="268"/>
+      <c r="S71" s="268"/>
+      <c r="T71" s="299">
+        <v>25.94</v>
+      </c>
       <c r="U71" s="268">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-25.94</v>
       </c>
       <c r="V71" s="268"/>
       <c r="W71" s="268"/>
       <c r="X71" s="33">
         <f t="shared" si="15"/>
-        <v>3122</v>
+        <v>3096.06</v>
       </c>
       <c r="Y71" s="179"/>
       <c r="Z71" s="179"/>
@@ -27808,11 +27869,11 @@
       <c r="AE71" s="179"/>
       <c r="AF71" s="179"/>
       <c r="AG71" s="173" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AH71" s="173"/>
     </row>
-    <row r="72" spans="1:38" s="241" customFormat="1" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:40" s="241" customFormat="1" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="30">
         <v>9</v>
       </c>
@@ -27849,8 +27910,8 @@
       </c>
       <c r="Q72" s="260"/>
       <c r="R72" s="63"/>
-      <c r="S72" s="294"/>
-      <c r="T72" s="268"/>
+      <c r="S72" s="268"/>
+      <c r="T72" s="299"/>
       <c r="U72" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -27869,12 +27930,12 @@
       <c r="AD72" s="256"/>
       <c r="AE72" s="256"/>
       <c r="AF72" s="256"/>
-      <c r="AG72" s="299" t="s">
-        <v>230</v>
+      <c r="AG72" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH72" s="173"/>
     </row>
-    <row r="73" spans="1:38" s="241" customFormat="1" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:40" s="241" customFormat="1" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="30">
         <v>10</v>
       </c>
@@ -27911,8 +27972,8 @@
       </c>
       <c r="Q73" s="260"/>
       <c r="R73" s="63"/>
-      <c r="S73" s="294"/>
-      <c r="T73" s="268"/>
+      <c r="S73" s="268"/>
+      <c r="T73" s="299"/>
       <c r="U73" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -27931,12 +27992,12 @@
       <c r="AD73" s="256"/>
       <c r="AE73" s="256"/>
       <c r="AF73" s="256"/>
-      <c r="AG73" s="299" t="s">
-        <v>230</v>
+      <c r="AG73" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH73" s="173"/>
     </row>
-    <row r="74" spans="1:38" s="241" customFormat="1" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:40" s="241" customFormat="1" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="30">
         <v>11</v>
       </c>
@@ -27973,8 +28034,8 @@
       </c>
       <c r="Q74" s="260"/>
       <c r="R74" s="63"/>
-      <c r="S74" s="294"/>
-      <c r="T74" s="268"/>
+      <c r="S74" s="268"/>
+      <c r="T74" s="299"/>
       <c r="U74" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -27993,12 +28054,12 @@
       <c r="AD74" s="256"/>
       <c r="AE74" s="256"/>
       <c r="AF74" s="256"/>
-      <c r="AG74" s="299" t="s">
-        <v>230</v>
+      <c r="AG74" s="344" t="s">
+        <v>234</v>
       </c>
       <c r="AH74" s="173"/>
     </row>
-    <row r="75" spans="1:38" s="241" customFormat="1" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:40" s="241" customFormat="1" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="30">
         <v>12</v>
       </c>
@@ -28028,8 +28089,8 @@
       <c r="P75" s="209"/>
       <c r="Q75" s="260"/>
       <c r="R75" s="63"/>
-      <c r="S75" s="294"/>
-      <c r="T75" s="268"/>
+      <c r="S75" s="268"/>
+      <c r="T75" s="299"/>
       <c r="U75" s="268"/>
       <c r="V75" s="268"/>
       <c r="W75" s="268"/>
@@ -28045,7 +28106,7 @@
       <c r="AG75" s="256"/>
       <c r="AH75" s="173"/>
     </row>
-    <row r="76" spans="1:38" s="241" customFormat="1" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:40" s="241" customFormat="1" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="30">
         <v>13</v>
       </c>
@@ -28075,8 +28136,8 @@
       <c r="P76" s="209"/>
       <c r="Q76" s="260"/>
       <c r="R76" s="63"/>
-      <c r="S76" s="294"/>
-      <c r="T76" s="268"/>
+      <c r="S76" s="268"/>
+      <c r="T76" s="299"/>
       <c r="U76" s="268"/>
       <c r="V76" s="268"/>
       <c r="W76" s="268"/>
@@ -28092,7 +28153,7 @@
       <c r="AG76" s="256"/>
       <c r="AH76" s="173"/>
     </row>
-    <row r="77" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="179"/>
       <c r="B77" s="251"/>
       <c r="C77" s="226"/>
@@ -28114,8 +28175,8 @@
       <c r="P77" s="213"/>
       <c r="Q77" s="179"/>
       <c r="R77" s="179"/>
-      <c r="S77" s="296"/>
-      <c r="T77" s="256"/>
+      <c r="S77" s="293"/>
+      <c r="T77" s="300"/>
       <c r="U77" s="256"/>
       <c r="V77" s="256"/>
       <c r="W77" s="256"/>
@@ -28131,30 +28192,25 @@
       <c r="AG77" s="179"/>
       <c r="AH77" s="179"/>
     </row>
-    <row r="78" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="13:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M81">
-        <f>1233824-2400</f>
-        <v>1231424</v>
-      </c>
-    </row>
-    <row r="82" spans="13:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="13:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="13:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="13:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="13:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="13:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="13:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="13:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="13:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="13:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="13:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="13:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="13:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="13:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="13:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -29049,11 +29105,15 @@
   </sheetData>
   <autoFilter ref="A10:AK77" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="30">
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="S7:U8"/>
-    <mergeCell ref="V7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AC9"/>
+    <mergeCell ref="AD7:AD9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A4:AH4"/>
@@ -29070,15 +29130,11 @@
     <mergeCell ref="P7:P9"/>
     <mergeCell ref="Q7:Q9"/>
     <mergeCell ref="R7:R9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AC9"/>
-    <mergeCell ref="AD7:AD9"/>
-    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="S7:U8"/>
+    <mergeCell ref="V7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="AE7:AE9"/>
   </mergeCells>
   <pageMargins left="0.55000000000000004" right="0.15748031496062992" top="0.39370078740157483" bottom="0.23622047244094491" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" r:id="rId1"/>

--- a/report/bao-cao.xlsx
+++ b/report/bao-cao.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HXuan\BaocaoGiaingan\report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HXuan\uonlyliv3own\BaocaoGiaingan\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF136ABB-F198-41DB-832E-71F03BA04BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0975E01D-C7F5-4B35-8D04-38F483223A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,17 +16,17 @@
     <sheet name="bc" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="BAO CAO 30-06 (2)" sheetId="3" state="hidden" r:id="rId2"/>
     <sheet name="BAO CAO 30-06 (KHV mới)" sheetId="4" state="hidden" r:id="rId3"/>
-    <sheet name="BAO CAO 17-10-2026" sheetId="5" r:id="rId4"/>
+    <sheet name="BAO CAO 26-10-2026" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BAO CAO 17-10-2026'!$A$10:$AK$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BAO CAO 26-10-2026'!$A$10:$AK$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BAO CAO 30-06 (2)'!$A$10:$AQ$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BAO CAO 30-06 (KHV mới)'!$A$10:$AQ$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">bc!$A$10:$AP$80</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'BAO CAO 17-10-2026'!$A$1:$AH$77</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'BAO CAO 26-10-2026'!$A$1:$AH$77</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'BAO CAO 30-06 (2)'!$A$1:$AN$58</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'BAO CAO 30-06 (KHV mới)'!$A$1:$AN$79</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'BAO CAO 17-10-2026'!$7:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'BAO CAO 26-10-2026'!$7:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'BAO CAO 30-06 (2)'!$7:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'BAO CAO 30-06 (KHV mới)'!$7:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">bc!$7:$9</definedName>
@@ -758,14 +758,14 @@
     <t>Số còn chi trong tháng 10/2026</t>
   </si>
   <si>
-    <t>(Tính đến ngày 17/10/2026)</t>
+    <t>(Tính đến ngày 26/10/2026)</t>
+  </si>
+  <si>
+    <t>TỔNG SỐ GIẢI NGÂN ĐẾN NGÀY BÁO CÁO NGÀY 26/10/2026</t>
   </si>
   <si>
     <t>Số giải ngân
-trong tuần (từ ngày 12/10/2026 đến 17/10/2026</t>
-  </si>
-  <si>
-    <t>TỔNG SỐ GIẢI NGÂN ĐẾN NGÀY BÁO CÁO NGÀY 17/10/2026</t>
+trong tuần (từ ngày 19/10/2026 đến 24/10/2026</t>
   </si>
   <si>
     <t>Cán bộ Kỹ thuật</t>
@@ -2414,9 +2414,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="29" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2439,25 +2436,24 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="172" fontId="0" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="29" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="54" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="77" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2476,7 +2472,6 @@
     <xf numFmtId="0" fontId="64" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2516,27 +2511,32 @@
     <xf numFmtId="167" fontId="63" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2815,7 +2815,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="333" t="s">
+      <c r="A1" s="336" t="s">
         <v>142</v>
       </c>
       <c r="B1" s="309"/>
@@ -3061,7 +3061,7 @@
       <c r="AA6" s="16"/>
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
-      <c r="AD6" s="335"/>
+      <c r="AD6" s="337"/>
       <c r="AE6" s="310"/>
       <c r="AF6" s="310"/>
       <c r="AG6" s="310"/>
@@ -3073,191 +3073,191 @@
       <c r="AM6" s="310"/>
     </row>
     <row r="7" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="307" t="s">
+      <c r="A7" s="301" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="307" t="s">
+      <c r="B7" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="328" t="s">
+      <c r="C7" s="327" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="307" t="s">
+      <c r="D7" s="301" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="307" t="s">
+      <c r="E7" s="301" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="307" t="s">
+      <c r="F7" s="301" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="307" t="s">
+      <c r="G7" s="301" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="307" t="s">
+      <c r="H7" s="301" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="307" t="s">
+      <c r="I7" s="301" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="307" t="s">
+      <c r="J7" s="301" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="307" t="s">
+      <c r="K7" s="301" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="337" t="s">
+      <c r="L7" s="334" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="307" t="s">
+      <c r="M7" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="307" t="s">
+      <c r="N7" s="301" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="317" t="s">
+      <c r="O7" s="316" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="318"/>
-      <c r="Q7" s="318"/>
-      <c r="R7" s="318"/>
-      <c r="S7" s="318"/>
-      <c r="T7" s="318"/>
-      <c r="U7" s="318"/>
-      <c r="V7" s="319"/>
-      <c r="W7" s="307" t="s">
+      <c r="P7" s="317"/>
+      <c r="Q7" s="317"/>
+      <c r="R7" s="317"/>
+      <c r="S7" s="317"/>
+      <c r="T7" s="317"/>
+      <c r="U7" s="317"/>
+      <c r="V7" s="318"/>
+      <c r="W7" s="301" t="s">
         <v>139</v>
       </c>
-      <c r="X7" s="334" t="s">
+      <c r="X7" s="335" t="s">
         <v>13</v>
       </c>
-      <c r="Y7" s="334" t="s">
+      <c r="Y7" s="335" t="s">
         <v>14</v>
       </c>
-      <c r="Z7" s="301" t="s">
+      <c r="Z7" s="306" t="s">
         <v>150</v>
       </c>
-      <c r="AA7" s="307" t="s">
+      <c r="AA7" s="301" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="307" t="s">
+      <c r="AB7" s="301" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="307" t="s">
+      <c r="AC7" s="301" t="s">
         <v>134</v>
       </c>
-      <c r="AD7" s="301" t="s">
+      <c r="AD7" s="306" t="s">
         <v>17</v>
       </c>
-      <c r="AE7" s="330" t="s">
+      <c r="AE7" s="303" t="s">
         <v>107</v>
       </c>
-      <c r="AF7" s="330" t="s">
+      <c r="AF7" s="303" t="s">
         <v>108</v>
       </c>
-      <c r="AG7" s="330" t="s">
+      <c r="AG7" s="303" t="s">
         <v>106</v>
       </c>
-      <c r="AH7" s="332" t="s">
+      <c r="AH7" s="305" t="s">
         <v>147</v>
       </c>
-      <c r="AI7" s="301" t="s">
+      <c r="AI7" s="306" t="s">
         <v>136</v>
       </c>
-      <c r="AJ7" s="301" t="s">
+      <c r="AJ7" s="306" t="s">
         <v>137</v>
       </c>
-      <c r="AK7" s="307" t="s">
+      <c r="AK7" s="301" t="s">
         <v>135</v>
       </c>
-      <c r="AL7" s="307" t="s">
+      <c r="AL7" s="301" t="s">
         <v>146</v>
       </c>
-      <c r="AM7" s="307" t="s">
+      <c r="AM7" s="301" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="302"/>
-      <c r="B8" s="302"/>
-      <c r="C8" s="328"/>
-      <c r="D8" s="302"/>
-      <c r="E8" s="302"/>
-      <c r="F8" s="302"/>
-      <c r="G8" s="302"/>
-      <c r="H8" s="302"/>
-      <c r="I8" s="302"/>
-      <c r="J8" s="302"/>
-      <c r="K8" s="302"/>
-      <c r="L8" s="302"/>
-      <c r="M8" s="302"/>
-      <c r="N8" s="302"/>
-      <c r="O8" s="320"/>
-      <c r="P8" s="321"/>
-      <c r="Q8" s="321"/>
-      <c r="R8" s="321"/>
-      <c r="S8" s="321"/>
-      <c r="T8" s="321"/>
-      <c r="U8" s="321"/>
-      <c r="V8" s="322"/>
-      <c r="W8" s="302"/>
-      <c r="X8" s="302"/>
-      <c r="Y8" s="302"/>
-      <c r="Z8" s="302"/>
-      <c r="AA8" s="302"/>
-      <c r="AB8" s="302"/>
-      <c r="AC8" s="307"/>
-      <c r="AD8" s="302"/>
-      <c r="AE8" s="331"/>
-      <c r="AF8" s="331"/>
-      <c r="AG8" s="332"/>
-      <c r="AH8" s="331"/>
-      <c r="AI8" s="302"/>
-      <c r="AJ8" s="301"/>
-      <c r="AK8" s="302"/>
-      <c r="AL8" s="307"/>
-      <c r="AM8" s="302"/>
+      <c r="A8" s="307"/>
+      <c r="B8" s="307"/>
+      <c r="C8" s="327"/>
+      <c r="D8" s="307"/>
+      <c r="E8" s="307"/>
+      <c r="F8" s="307"/>
+      <c r="G8" s="307"/>
+      <c r="H8" s="307"/>
+      <c r="I8" s="307"/>
+      <c r="J8" s="307"/>
+      <c r="K8" s="307"/>
+      <c r="L8" s="307"/>
+      <c r="M8" s="307"/>
+      <c r="N8" s="307"/>
+      <c r="O8" s="319"/>
+      <c r="P8" s="320"/>
+      <c r="Q8" s="320"/>
+      <c r="R8" s="320"/>
+      <c r="S8" s="320"/>
+      <c r="T8" s="320"/>
+      <c r="U8" s="320"/>
+      <c r="V8" s="321"/>
+      <c r="W8" s="307"/>
+      <c r="X8" s="307"/>
+      <c r="Y8" s="307"/>
+      <c r="Z8" s="307"/>
+      <c r="AA8" s="307"/>
+      <c r="AB8" s="307"/>
+      <c r="AC8" s="301"/>
+      <c r="AD8" s="307"/>
+      <c r="AE8" s="304"/>
+      <c r="AF8" s="304"/>
+      <c r="AG8" s="305"/>
+      <c r="AH8" s="304"/>
+      <c r="AI8" s="307"/>
+      <c r="AJ8" s="306"/>
+      <c r="AK8" s="307"/>
+      <c r="AL8" s="301"/>
+      <c r="AM8" s="307"/>
     </row>
     <row r="9" spans="1:42" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="302"/>
-      <c r="B9" s="302"/>
-      <c r="C9" s="328"/>
-      <c r="D9" s="302"/>
-      <c r="E9" s="302"/>
-      <c r="F9" s="302"/>
-      <c r="G9" s="302"/>
-      <c r="H9" s="302"/>
-      <c r="I9" s="302"/>
-      <c r="J9" s="302"/>
-      <c r="K9" s="302"/>
-      <c r="L9" s="302"/>
-      <c r="M9" s="302"/>
-      <c r="N9" s="302"/>
-      <c r="O9" s="323"/>
-      <c r="P9" s="324"/>
-      <c r="Q9" s="324"/>
-      <c r="R9" s="324"/>
-      <c r="S9" s="324"/>
-      <c r="T9" s="324"/>
-      <c r="U9" s="324"/>
-      <c r="V9" s="325"/>
-      <c r="W9" s="302"/>
-      <c r="X9" s="302"/>
-      <c r="Y9" s="302"/>
-      <c r="Z9" s="302"/>
-      <c r="AA9" s="302"/>
-      <c r="AB9" s="302"/>
-      <c r="AC9" s="307"/>
-      <c r="AD9" s="302"/>
-      <c r="AE9" s="331"/>
-      <c r="AF9" s="331"/>
-      <c r="AG9" s="332"/>
-      <c r="AH9" s="331"/>
-      <c r="AI9" s="302"/>
-      <c r="AJ9" s="301"/>
-      <c r="AK9" s="302"/>
-      <c r="AL9" s="307"/>
-      <c r="AM9" s="302"/>
+      <c r="A9" s="307"/>
+      <c r="B9" s="307"/>
+      <c r="C9" s="327"/>
+      <c r="D9" s="307"/>
+      <c r="E9" s="307"/>
+      <c r="F9" s="307"/>
+      <c r="G9" s="307"/>
+      <c r="H9" s="307"/>
+      <c r="I9" s="307"/>
+      <c r="J9" s="307"/>
+      <c r="K9" s="307"/>
+      <c r="L9" s="307"/>
+      <c r="M9" s="307"/>
+      <c r="N9" s="307"/>
+      <c r="O9" s="322"/>
+      <c r="P9" s="323"/>
+      <c r="Q9" s="323"/>
+      <c r="R9" s="323"/>
+      <c r="S9" s="323"/>
+      <c r="T9" s="323"/>
+      <c r="U9" s="323"/>
+      <c r="V9" s="324"/>
+      <c r="W9" s="307"/>
+      <c r="X9" s="307"/>
+      <c r="Y9" s="307"/>
+      <c r="Z9" s="307"/>
+      <c r="AA9" s="307"/>
+      <c r="AB9" s="307"/>
+      <c r="AC9" s="301"/>
+      <c r="AD9" s="307"/>
+      <c r="AE9" s="304"/>
+      <c r="AF9" s="304"/>
+      <c r="AG9" s="305"/>
+      <c r="AH9" s="304"/>
+      <c r="AI9" s="307"/>
+      <c r="AJ9" s="306"/>
+      <c r="AK9" s="307"/>
+      <c r="AL9" s="301"/>
+      <c r="AM9" s="307"/>
       <c r="AP9">
         <v>27</v>
       </c>
@@ -8706,47 +8706,47 @@
       </c>
     </row>
     <row r="77" spans="1:42" ht="29.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="336" t="s">
+      <c r="A77" s="333" t="s">
         <v>145</v>
       </c>
-      <c r="B77" s="302"/>
-      <c r="C77" s="302"/>
-      <c r="D77" s="302"/>
-      <c r="E77" s="302"/>
-      <c r="F77" s="302"/>
-      <c r="G77" s="302"/>
-      <c r="H77" s="302"/>
-      <c r="I77" s="302"/>
-      <c r="J77" s="302"/>
-      <c r="K77" s="302"/>
-      <c r="L77" s="302"/>
-      <c r="M77" s="302"/>
-      <c r="N77" s="302"/>
-      <c r="O77" s="302"/>
-      <c r="P77" s="302"/>
-      <c r="Q77" s="302"/>
-      <c r="R77" s="302"/>
-      <c r="S77" s="302"/>
-      <c r="T77" s="302"/>
-      <c r="U77" s="302"/>
-      <c r="V77" s="302"/>
-      <c r="W77" s="302"/>
-      <c r="X77" s="302"/>
-      <c r="Y77" s="302"/>
-      <c r="Z77" s="302"/>
-      <c r="AA77" s="302"/>
-      <c r="AB77" s="302"/>
-      <c r="AC77" s="302"/>
-      <c r="AD77" s="302"/>
-      <c r="AE77" s="302"/>
-      <c r="AF77" s="302"/>
-      <c r="AG77" s="302"/>
-      <c r="AH77" s="302"/>
-      <c r="AI77" s="302"/>
-      <c r="AJ77" s="302"/>
-      <c r="AK77" s="302"/>
-      <c r="AL77" s="302"/>
-      <c r="AM77" s="302"/>
+      <c r="B77" s="307"/>
+      <c r="C77" s="307"/>
+      <c r="D77" s="307"/>
+      <c r="E77" s="307"/>
+      <c r="F77" s="307"/>
+      <c r="G77" s="307"/>
+      <c r="H77" s="307"/>
+      <c r="I77" s="307"/>
+      <c r="J77" s="307"/>
+      <c r="K77" s="307"/>
+      <c r="L77" s="307"/>
+      <c r="M77" s="307"/>
+      <c r="N77" s="307"/>
+      <c r="O77" s="307"/>
+      <c r="P77" s="307"/>
+      <c r="Q77" s="307"/>
+      <c r="R77" s="307"/>
+      <c r="S77" s="307"/>
+      <c r="T77" s="307"/>
+      <c r="U77" s="307"/>
+      <c r="V77" s="307"/>
+      <c r="W77" s="307"/>
+      <c r="X77" s="307"/>
+      <c r="Y77" s="307"/>
+      <c r="Z77" s="307"/>
+      <c r="AA77" s="307"/>
+      <c r="AB77" s="307"/>
+      <c r="AC77" s="307"/>
+      <c r="AD77" s="307"/>
+      <c r="AE77" s="307"/>
+      <c r="AF77" s="307"/>
+      <c r="AG77" s="307"/>
+      <c r="AH77" s="307"/>
+      <c r="AI77" s="307"/>
+      <c r="AJ77" s="307"/>
+      <c r="AK77" s="307"/>
+      <c r="AL77" s="307"/>
+      <c r="AM77" s="307"/>
     </row>
     <row r="78" spans="1:42" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="81"/>
@@ -9846,6 +9846,28 @@
   </sheetData>
   <autoFilter ref="A10:AP80" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="38">
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AC9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="A2:AB2"/>
+    <mergeCell ref="A4:AM4"/>
+    <mergeCell ref="A5:AM5"/>
+    <mergeCell ref="AD7:AD9"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="AD6:AM6"/>
     <mergeCell ref="A77:AM77"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="D7:D9"/>
@@ -9862,28 +9884,6 @@
     <mergeCell ref="AI7:AI9"/>
     <mergeCell ref="AJ7:AJ9"/>
     <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="A2:AB2"/>
-    <mergeCell ref="A4:AM4"/>
-    <mergeCell ref="A5:AM5"/>
-    <mergeCell ref="AD7:AD9"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="AD6:AM6"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AC9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="O7:V9"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.27559055118110237" top="0.47244094488188981" bottom="0.31496062992125984" header="0" footer="0"/>
   <pageSetup scale="80" orientation="landscape" r:id="rId1"/>
@@ -9932,7 +9932,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="333" t="s">
+      <c r="A1" s="336" t="s">
         <v>142</v>
       </c>
       <c r="B1" s="309"/>
@@ -10198,59 +10198,59 @@
       <c r="AN6" s="339"/>
     </row>
     <row r="7" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="307" t="s">
+      <c r="A7" s="301" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="307" t="s">
+      <c r="B7" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="328" t="s">
+      <c r="C7" s="327" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="307" t="s">
+      <c r="D7" s="301" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="307" t="s">
+      <c r="E7" s="301" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="307" t="s">
+      <c r="F7" s="301" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="307" t="s">
+      <c r="G7" s="301" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="307" t="s">
+      <c r="H7" s="301" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="307" t="s">
+      <c r="I7" s="301" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="307" t="s">
+      <c r="J7" s="301" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="307" t="s">
+      <c r="K7" s="301" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="337" t="s">
+      <c r="L7" s="334" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="307" t="s">
+      <c r="M7" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="307" t="s">
+      <c r="N7" s="301" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="317" t="s">
+      <c r="O7" s="316" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="318"/>
-      <c r="Q7" s="318"/>
-      <c r="R7" s="318"/>
-      <c r="S7" s="318"/>
-      <c r="T7" s="318"/>
-      <c r="U7" s="318"/>
-      <c r="V7" s="319"/>
-      <c r="W7" s="307" t="s">
+      <c r="P7" s="317"/>
+      <c r="Q7" s="317"/>
+      <c r="R7" s="317"/>
+      <c r="S7" s="317"/>
+      <c r="T7" s="317"/>
+      <c r="U7" s="317"/>
+      <c r="V7" s="318"/>
+      <c r="W7" s="301" t="s">
         <v>139</v>
       </c>
       <c r="X7" s="315" t="s">
@@ -10259,137 +10259,137 @@
       <c r="Y7" s="315" t="s">
         <v>184</v>
       </c>
-      <c r="Z7" s="329" t="s">
+      <c r="Z7" s="328" t="s">
         <v>175</v>
       </c>
-      <c r="AA7" s="307" t="s">
+      <c r="AA7" s="301" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="307" t="s">
+      <c r="AB7" s="301" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="317" t="s">
+      <c r="AC7" s="316" t="s">
         <v>155</v>
       </c>
-      <c r="AD7" s="319"/>
-      <c r="AE7" s="301" t="s">
+      <c r="AD7" s="318"/>
+      <c r="AE7" s="306" t="s">
         <v>17</v>
       </c>
-      <c r="AF7" s="330" t="s">
+      <c r="AF7" s="303" t="s">
         <v>107</v>
       </c>
-      <c r="AG7" s="330" t="s">
+      <c r="AG7" s="303" t="s">
         <v>108</v>
       </c>
-      <c r="AH7" s="330" t="s">
+      <c r="AH7" s="303" t="s">
         <v>106</v>
       </c>
-      <c r="AI7" s="332" t="s">
+      <c r="AI7" s="305" t="s">
         <v>147</v>
       </c>
-      <c r="AJ7" s="301" t="s">
+      <c r="AJ7" s="306" t="s">
         <v>136</v>
       </c>
-      <c r="AK7" s="301" t="s">
+      <c r="AK7" s="306" t="s">
         <v>137</v>
       </c>
-      <c r="AL7" s="307" t="s">
+      <c r="AL7" s="301" t="s">
         <v>135</v>
       </c>
-      <c r="AM7" s="307" t="s">
+      <c r="AM7" s="301" t="s">
         <v>146</v>
       </c>
-      <c r="AN7" s="307" t="s">
+      <c r="AN7" s="301" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="302"/>
-      <c r="B8" s="302"/>
-      <c r="C8" s="328"/>
-      <c r="D8" s="302"/>
-      <c r="E8" s="302"/>
-      <c r="F8" s="302"/>
-      <c r="G8" s="302"/>
-      <c r="H8" s="302"/>
-      <c r="I8" s="302"/>
-      <c r="J8" s="302"/>
-      <c r="K8" s="302"/>
-      <c r="L8" s="302"/>
-      <c r="M8" s="302"/>
-      <c r="N8" s="302"/>
-      <c r="O8" s="320"/>
-      <c r="P8" s="321"/>
-      <c r="Q8" s="321"/>
-      <c r="R8" s="321"/>
-      <c r="S8" s="321"/>
-      <c r="T8" s="321"/>
-      <c r="U8" s="321"/>
-      <c r="V8" s="322"/>
-      <c r="W8" s="302"/>
-      <c r="X8" s="302"/>
-      <c r="Y8" s="302"/>
-      <c r="Z8" s="302"/>
-      <c r="AA8" s="302"/>
-      <c r="AB8" s="302"/>
-      <c r="AC8" s="323"/>
-      <c r="AD8" s="325"/>
-      <c r="AE8" s="302"/>
-      <c r="AF8" s="331"/>
-      <c r="AG8" s="331"/>
-      <c r="AH8" s="332"/>
-      <c r="AI8" s="331"/>
-      <c r="AJ8" s="302"/>
-      <c r="AK8" s="301"/>
-      <c r="AL8" s="302"/>
-      <c r="AM8" s="307"/>
-      <c r="AN8" s="316"/>
+      <c r="A8" s="307"/>
+      <c r="B8" s="307"/>
+      <c r="C8" s="327"/>
+      <c r="D8" s="307"/>
+      <c r="E8" s="307"/>
+      <c r="F8" s="307"/>
+      <c r="G8" s="307"/>
+      <c r="H8" s="307"/>
+      <c r="I8" s="307"/>
+      <c r="J8" s="307"/>
+      <c r="K8" s="307"/>
+      <c r="L8" s="307"/>
+      <c r="M8" s="307"/>
+      <c r="N8" s="307"/>
+      <c r="O8" s="319"/>
+      <c r="P8" s="320"/>
+      <c r="Q8" s="320"/>
+      <c r="R8" s="320"/>
+      <c r="S8" s="320"/>
+      <c r="T8" s="320"/>
+      <c r="U8" s="320"/>
+      <c r="V8" s="321"/>
+      <c r="W8" s="307"/>
+      <c r="X8" s="307"/>
+      <c r="Y8" s="307"/>
+      <c r="Z8" s="307"/>
+      <c r="AA8" s="307"/>
+      <c r="AB8" s="307"/>
+      <c r="AC8" s="322"/>
+      <c r="AD8" s="324"/>
+      <c r="AE8" s="307"/>
+      <c r="AF8" s="304"/>
+      <c r="AG8" s="304"/>
+      <c r="AH8" s="305"/>
+      <c r="AI8" s="304"/>
+      <c r="AJ8" s="307"/>
+      <c r="AK8" s="306"/>
+      <c r="AL8" s="307"/>
+      <c r="AM8" s="301"/>
+      <c r="AN8" s="302"/>
     </row>
     <row r="9" spans="1:43" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="302"/>
-      <c r="B9" s="302"/>
-      <c r="C9" s="328"/>
-      <c r="D9" s="302"/>
-      <c r="E9" s="302"/>
-      <c r="F9" s="302"/>
-      <c r="G9" s="302"/>
-      <c r="H9" s="302"/>
-      <c r="I9" s="302"/>
-      <c r="J9" s="302"/>
-      <c r="K9" s="302"/>
-      <c r="L9" s="302"/>
-      <c r="M9" s="302"/>
-      <c r="N9" s="302"/>
-      <c r="O9" s="323"/>
-      <c r="P9" s="324"/>
-      <c r="Q9" s="324"/>
-      <c r="R9" s="324"/>
-      <c r="S9" s="324"/>
-      <c r="T9" s="324"/>
-      <c r="U9" s="324"/>
-      <c r="V9" s="325"/>
-      <c r="W9" s="302"/>
-      <c r="X9" s="302"/>
-      <c r="Y9" s="302"/>
-      <c r="Z9" s="302"/>
-      <c r="AA9" s="302"/>
-      <c r="AB9" s="302"/>
+      <c r="A9" s="307"/>
+      <c r="B9" s="307"/>
+      <c r="C9" s="327"/>
+      <c r="D9" s="307"/>
+      <c r="E9" s="307"/>
+      <c r="F9" s="307"/>
+      <c r="G9" s="307"/>
+      <c r="H9" s="307"/>
+      <c r="I9" s="307"/>
+      <c r="J9" s="307"/>
+      <c r="K9" s="307"/>
+      <c r="L9" s="307"/>
+      <c r="M9" s="307"/>
+      <c r="N9" s="307"/>
+      <c r="O9" s="322"/>
+      <c r="P9" s="323"/>
+      <c r="Q9" s="323"/>
+      <c r="R9" s="323"/>
+      <c r="S9" s="323"/>
+      <c r="T9" s="323"/>
+      <c r="U9" s="323"/>
+      <c r="V9" s="324"/>
+      <c r="W9" s="307"/>
+      <c r="X9" s="307"/>
+      <c r="Y9" s="307"/>
+      <c r="Z9" s="307"/>
+      <c r="AA9" s="307"/>
+      <c r="AB9" s="307"/>
       <c r="AC9" s="201" t="s">
         <v>153</v>
       </c>
       <c r="AD9" s="178" t="s">
         <v>154</v>
       </c>
-      <c r="AE9" s="302"/>
-      <c r="AF9" s="331"/>
-      <c r="AG9" s="331"/>
-      <c r="AH9" s="332"/>
-      <c r="AI9" s="331"/>
-      <c r="AJ9" s="302"/>
-      <c r="AK9" s="301"/>
-      <c r="AL9" s="302"/>
-      <c r="AM9" s="307"/>
-      <c r="AN9" s="316"/>
+      <c r="AE9" s="307"/>
+      <c r="AF9" s="304"/>
+      <c r="AG9" s="304"/>
+      <c r="AH9" s="305"/>
+      <c r="AI9" s="304"/>
+      <c r="AJ9" s="307"/>
+      <c r="AK9" s="306"/>
+      <c r="AL9" s="307"/>
+      <c r="AM9" s="301"/>
+      <c r="AN9" s="302"/>
       <c r="AO9">
         <f>Z11/W11</f>
         <v>0.50632226325372287</v>
@@ -15659,27 +15659,6 @@
   </sheetData>
   <autoFilter ref="A10:AQ54" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AD8"/>
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A2:AB2"/>
@@ -15696,6 +15675,27 @@
     <mergeCell ref="H7:H9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:J9"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AD8"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
   </mergeCells>
   <pageMargins left="0.17" right="0.15748031496062992" top="0.41" bottom="0.23622047244094491" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
@@ -15744,7 +15744,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="333" t="s">
+      <c r="A1" s="336" t="s">
         <v>142</v>
       </c>
       <c r="B1" s="309"/>
@@ -16010,59 +16010,59 @@
       <c r="AN6" s="339"/>
     </row>
     <row r="7" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="307" t="s">
+      <c r="A7" s="301" t="s">
         <v>1</v>
       </c>
       <c r="B7" s="340" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="328" t="s">
+      <c r="C7" s="327" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="307" t="s">
+      <c r="D7" s="301" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="307" t="s">
+      <c r="E7" s="301" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="307" t="s">
+      <c r="F7" s="301" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="307" t="s">
+      <c r="G7" s="301" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="307" t="s">
+      <c r="H7" s="301" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="307" t="s">
+      <c r="I7" s="301" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="307" t="s">
+      <c r="J7" s="301" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="307" t="s">
+      <c r="K7" s="301" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="337" t="s">
+      <c r="L7" s="334" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="307" t="s">
+      <c r="M7" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="307" t="s">
+      <c r="N7" s="301" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="317" t="s">
+      <c r="O7" s="316" t="s">
         <v>138</v>
       </c>
-      <c r="P7" s="318"/>
-      <c r="Q7" s="318"/>
-      <c r="R7" s="318"/>
-      <c r="S7" s="318"/>
-      <c r="T7" s="318"/>
-      <c r="U7" s="318"/>
-      <c r="V7" s="319"/>
-      <c r="W7" s="307" t="s">
+      <c r="P7" s="317"/>
+      <c r="Q7" s="317"/>
+      <c r="R7" s="317"/>
+      <c r="S7" s="317"/>
+      <c r="T7" s="317"/>
+      <c r="U7" s="317"/>
+      <c r="V7" s="318"/>
+      <c r="W7" s="301" t="s">
         <v>139</v>
       </c>
       <c r="X7" s="315" t="s">
@@ -16071,137 +16071,137 @@
       <c r="Y7" s="315" t="s">
         <v>184</v>
       </c>
-      <c r="Z7" s="329" t="s">
+      <c r="Z7" s="328" t="s">
         <v>175</v>
       </c>
-      <c r="AA7" s="307" t="s">
+      <c r="AA7" s="301" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="307" t="s">
+      <c r="AB7" s="301" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="317" t="s">
+      <c r="AC7" s="316" t="s">
         <v>155</v>
       </c>
-      <c r="AD7" s="319"/>
-      <c r="AE7" s="301" t="s">
+      <c r="AD7" s="318"/>
+      <c r="AE7" s="306" t="s">
         <v>17</v>
       </c>
-      <c r="AF7" s="330" t="s">
+      <c r="AF7" s="303" t="s">
         <v>107</v>
       </c>
-      <c r="AG7" s="330" t="s">
+      <c r="AG7" s="303" t="s">
         <v>108</v>
       </c>
-      <c r="AH7" s="330" t="s">
+      <c r="AH7" s="303" t="s">
         <v>106</v>
       </c>
-      <c r="AI7" s="332" t="s">
+      <c r="AI7" s="305" t="s">
         <v>147</v>
       </c>
-      <c r="AJ7" s="301" t="s">
+      <c r="AJ7" s="306" t="s">
         <v>136</v>
       </c>
-      <c r="AK7" s="301" t="s">
+      <c r="AK7" s="306" t="s">
         <v>137</v>
       </c>
-      <c r="AL7" s="307" t="s">
+      <c r="AL7" s="301" t="s">
         <v>135</v>
       </c>
-      <c r="AM7" s="307" t="s">
+      <c r="AM7" s="301" t="s">
         <v>146</v>
       </c>
-      <c r="AN7" s="307" t="s">
+      <c r="AN7" s="301" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="302"/>
+      <c r="A8" s="307"/>
       <c r="B8" s="341"/>
-      <c r="C8" s="328"/>
-      <c r="D8" s="302"/>
-      <c r="E8" s="302"/>
-      <c r="F8" s="302"/>
-      <c r="G8" s="302"/>
-      <c r="H8" s="302"/>
-      <c r="I8" s="302"/>
-      <c r="J8" s="302"/>
-      <c r="K8" s="302"/>
-      <c r="L8" s="302"/>
-      <c r="M8" s="302"/>
-      <c r="N8" s="302"/>
-      <c r="O8" s="320"/>
-      <c r="P8" s="321"/>
-      <c r="Q8" s="321"/>
-      <c r="R8" s="321"/>
-      <c r="S8" s="321"/>
-      <c r="T8" s="321"/>
-      <c r="U8" s="321"/>
-      <c r="V8" s="322"/>
-      <c r="W8" s="302"/>
-      <c r="X8" s="302"/>
-      <c r="Y8" s="302"/>
-      <c r="Z8" s="302"/>
-      <c r="AA8" s="302"/>
-      <c r="AB8" s="302"/>
-      <c r="AC8" s="323"/>
-      <c r="AD8" s="325"/>
-      <c r="AE8" s="302"/>
-      <c r="AF8" s="331"/>
-      <c r="AG8" s="331"/>
-      <c r="AH8" s="332"/>
-      <c r="AI8" s="331"/>
-      <c r="AJ8" s="302"/>
-      <c r="AK8" s="301"/>
-      <c r="AL8" s="302"/>
-      <c r="AM8" s="307"/>
-      <c r="AN8" s="316"/>
+      <c r="C8" s="327"/>
+      <c r="D8" s="307"/>
+      <c r="E8" s="307"/>
+      <c r="F8" s="307"/>
+      <c r="G8" s="307"/>
+      <c r="H8" s="307"/>
+      <c r="I8" s="307"/>
+      <c r="J8" s="307"/>
+      <c r="K8" s="307"/>
+      <c r="L8" s="307"/>
+      <c r="M8" s="307"/>
+      <c r="N8" s="307"/>
+      <c r="O8" s="319"/>
+      <c r="P8" s="320"/>
+      <c r="Q8" s="320"/>
+      <c r="R8" s="320"/>
+      <c r="S8" s="320"/>
+      <c r="T8" s="320"/>
+      <c r="U8" s="320"/>
+      <c r="V8" s="321"/>
+      <c r="W8" s="307"/>
+      <c r="X8" s="307"/>
+      <c r="Y8" s="307"/>
+      <c r="Z8" s="307"/>
+      <c r="AA8" s="307"/>
+      <c r="AB8" s="307"/>
+      <c r="AC8" s="322"/>
+      <c r="AD8" s="324"/>
+      <c r="AE8" s="307"/>
+      <c r="AF8" s="304"/>
+      <c r="AG8" s="304"/>
+      <c r="AH8" s="305"/>
+      <c r="AI8" s="304"/>
+      <c r="AJ8" s="307"/>
+      <c r="AK8" s="306"/>
+      <c r="AL8" s="307"/>
+      <c r="AM8" s="301"/>
+      <c r="AN8" s="302"/>
     </row>
     <row r="9" spans="1:43" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="302"/>
+      <c r="A9" s="307"/>
       <c r="B9" s="341"/>
-      <c r="C9" s="328"/>
-      <c r="D9" s="302"/>
-      <c r="E9" s="302"/>
-      <c r="F9" s="302"/>
-      <c r="G9" s="302"/>
-      <c r="H9" s="302"/>
-      <c r="I9" s="302"/>
-      <c r="J9" s="302"/>
-      <c r="K9" s="302"/>
-      <c r="L9" s="302"/>
-      <c r="M9" s="302"/>
-      <c r="N9" s="302"/>
-      <c r="O9" s="323"/>
-      <c r="P9" s="324"/>
-      <c r="Q9" s="324"/>
-      <c r="R9" s="324"/>
-      <c r="S9" s="324"/>
-      <c r="T9" s="324"/>
-      <c r="U9" s="324"/>
-      <c r="V9" s="325"/>
-      <c r="W9" s="302"/>
-      <c r="X9" s="302"/>
-      <c r="Y9" s="302"/>
-      <c r="Z9" s="302"/>
-      <c r="AA9" s="302"/>
-      <c r="AB9" s="302"/>
+      <c r="C9" s="327"/>
+      <c r="D9" s="307"/>
+      <c r="E9" s="307"/>
+      <c r="F9" s="307"/>
+      <c r="G9" s="307"/>
+      <c r="H9" s="307"/>
+      <c r="I9" s="307"/>
+      <c r="J9" s="307"/>
+      <c r="K9" s="307"/>
+      <c r="L9" s="307"/>
+      <c r="M9" s="307"/>
+      <c r="N9" s="307"/>
+      <c r="O9" s="322"/>
+      <c r="P9" s="323"/>
+      <c r="Q9" s="323"/>
+      <c r="R9" s="323"/>
+      <c r="S9" s="323"/>
+      <c r="T9" s="323"/>
+      <c r="U9" s="323"/>
+      <c r="V9" s="324"/>
+      <c r="W9" s="307"/>
+      <c r="X9" s="307"/>
+      <c r="Y9" s="307"/>
+      <c r="Z9" s="307"/>
+      <c r="AA9" s="307"/>
+      <c r="AB9" s="307"/>
       <c r="AC9" s="201" t="s">
         <v>153</v>
       </c>
       <c r="AD9" s="178" t="s">
         <v>154</v>
       </c>
-      <c r="AE9" s="302"/>
-      <c r="AF9" s="331"/>
-      <c r="AG9" s="331"/>
-      <c r="AH9" s="332"/>
-      <c r="AI9" s="331"/>
-      <c r="AJ9" s="302"/>
-      <c r="AK9" s="301"/>
-      <c r="AL9" s="302"/>
-      <c r="AM9" s="307"/>
-      <c r="AN9" s="316"/>
+      <c r="AE9" s="307"/>
+      <c r="AF9" s="304"/>
+      <c r="AG9" s="304"/>
+      <c r="AH9" s="305"/>
+      <c r="AI9" s="304"/>
+      <c r="AJ9" s="307"/>
+      <c r="AK9" s="306"/>
+      <c r="AL9" s="307"/>
+      <c r="AM9" s="301"/>
+      <c r="AN9" s="302"/>
       <c r="AO9">
         <f>Z11/W11</f>
         <v>0.50320398224028773</v>
@@ -22375,6 +22375,27 @@
   </sheetData>
   <autoFilter ref="A10:AQ73" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="37">
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AD8"/>
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="A2:AB2"/>
@@ -22391,27 +22412,6 @@
     <mergeCell ref="H7:H9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:J9"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AD8"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
   </mergeCells>
   <pageMargins left="0.17" right="0.15748031496062992" top="0.41" bottom="0.23622047244094491" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
@@ -22437,7 +22437,7 @@
     <col min="12" max="12" width="10.42578125" customWidth="1"/>
     <col min="13" max="13" width="10.5703125" customWidth="1"/>
     <col min="14" max="14" width="12.140625" style="214" customWidth="1"/>
-    <col min="15" max="15" width="11.28515625" style="214" customWidth="1"/>
+    <col min="15" max="15" width="9.28515625" style="214" customWidth="1"/>
     <col min="16" max="16" width="10.7109375" style="214" customWidth="1"/>
     <col min="17" max="18" width="9" customWidth="1"/>
     <col min="19" max="19" width="10.42578125" style="102" customWidth="1"/>
@@ -22451,8 +22451,8 @@
     <col min="29" max="29" width="12.140625" customWidth="1"/>
     <col min="30" max="30" width="17.5703125" customWidth="1"/>
     <col min="31" max="31" width="12.28515625" customWidth="1"/>
-    <col min="32" max="33" width="11.28515625" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" customWidth="1"/>
+    <col min="32" max="33" width="11.42578125" customWidth="1"/>
+    <col min="34" max="34" width="19.28515625" customWidth="1"/>
     <col min="35" max="37" width="14.42578125" customWidth="1"/>
     <col min="40" max="40" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -22670,164 +22670,164 @@
       <c r="R6" s="11"/>
       <c r="S6" s="11"/>
       <c r="T6" s="11"/>
-      <c r="U6" s="326" t="s">
+      <c r="U6" s="325" t="s">
         <v>151</v>
       </c>
-      <c r="V6" s="326"/>
-      <c r="W6" s="326"/>
-      <c r="X6" s="326"/>
-      <c r="Y6" s="326"/>
-      <c r="Z6" s="326"/>
-      <c r="AA6" s="326"/>
-      <c r="AB6" s="326"/>
-      <c r="AC6" s="326"/>
-      <c r="AD6" s="326"/>
-      <c r="AE6" s="326"/>
-      <c r="AF6" s="326"/>
-      <c r="AG6" s="326"/>
-      <c r="AH6" s="326"/>
+      <c r="V6" s="325"/>
+      <c r="W6" s="325"/>
+      <c r="X6" s="325"/>
+      <c r="Y6" s="325"/>
+      <c r="Z6" s="325"/>
+      <c r="AA6" s="325"/>
+      <c r="AB6" s="325"/>
+      <c r="AC6" s="325"/>
+      <c r="AD6" s="325"/>
+      <c r="AE6" s="325"/>
+      <c r="AF6" s="325"/>
+      <c r="AG6" s="325"/>
+      <c r="AH6" s="325"/>
     </row>
     <row r="7" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="307" t="s">
+      <c r="A7" s="301" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="307" t="s">
+      <c r="B7" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="328" t="s">
+      <c r="C7" s="327" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="307" t="s">
+      <c r="D7" s="301" t="s">
         <v>140</v>
       </c>
-      <c r="E7" s="317" t="s">
+      <c r="E7" s="316" t="s">
         <v>138</v>
       </c>
-      <c r="F7" s="318"/>
-      <c r="G7" s="318"/>
-      <c r="H7" s="318"/>
-      <c r="I7" s="318"/>
-      <c r="J7" s="318"/>
-      <c r="K7" s="318"/>
-      <c r="L7" s="319"/>
-      <c r="M7" s="307" t="s">
+      <c r="F7" s="317"/>
+      <c r="G7" s="317"/>
+      <c r="H7" s="317"/>
+      <c r="I7" s="317"/>
+      <c r="J7" s="317"/>
+      <c r="K7" s="317"/>
+      <c r="L7" s="318"/>
+      <c r="M7" s="301" t="s">
         <v>202</v>
       </c>
       <c r="N7" s="315" t="s">
         <v>13</v>
       </c>
       <c r="O7" s="315" t="s">
+        <v>230</v>
+      </c>
+      <c r="P7" s="328" t="s">
         <v>229</v>
       </c>
-      <c r="P7" s="329" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q7" s="307" t="s">
+      <c r="Q7" s="301" t="s">
         <v>15</v>
       </c>
-      <c r="R7" s="307" t="s">
+      <c r="R7" s="301" t="s">
         <v>16</v>
       </c>
-      <c r="S7" s="303" t="s">
+      <c r="S7" s="329" t="s">
         <v>225</v>
       </c>
-      <c r="T7" s="303"/>
-      <c r="U7" s="303"/>
-      <c r="V7" s="304" t="s">
+      <c r="T7" s="329"/>
+      <c r="U7" s="329"/>
+      <c r="V7" s="330" t="s">
         <v>211</v>
       </c>
-      <c r="W7" s="304" t="s">
+      <c r="W7" s="330" t="s">
         <v>215</v>
       </c>
-      <c r="X7" s="301" t="s">
+      <c r="X7" s="306" t="s">
         <v>17</v>
       </c>
-      <c r="Y7" s="330" t="s">
+      <c r="Y7" s="303" t="s">
         <v>107</v>
       </c>
-      <c r="Z7" s="330" t="s">
+      <c r="Z7" s="303" t="s">
         <v>108</v>
       </c>
-      <c r="AA7" s="330" t="s">
+      <c r="AA7" s="303" t="s">
         <v>106</v>
       </c>
-      <c r="AB7" s="332" t="s">
+      <c r="AB7" s="305" t="s">
         <v>147</v>
       </c>
-      <c r="AC7" s="301" t="s">
+      <c r="AC7" s="306" t="s">
         <v>136</v>
       </c>
-      <c r="AD7" s="301" t="s">
+      <c r="AD7" s="306" t="s">
         <v>137</v>
       </c>
-      <c r="AE7" s="307" t="s">
+      <c r="AE7" s="301" t="s">
         <v>135</v>
       </c>
-      <c r="AF7" s="307" t="s">
+      <c r="AF7" s="301" t="s">
         <v>146</v>
       </c>
-      <c r="AG7" s="307" t="s">
+      <c r="AG7" s="301" t="s">
         <v>231</v>
       </c>
-      <c r="AH7" s="307" t="s">
+      <c r="AH7" s="301" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="302"/>
-      <c r="B8" s="327"/>
-      <c r="C8" s="328"/>
-      <c r="D8" s="316"/>
-      <c r="E8" s="320"/>
-      <c r="F8" s="321"/>
-      <c r="G8" s="321"/>
-      <c r="H8" s="321"/>
-      <c r="I8" s="321"/>
-      <c r="J8" s="321"/>
-      <c r="K8" s="321"/>
-      <c r="L8" s="322"/>
-      <c r="M8" s="302"/>
-      <c r="N8" s="302"/>
-      <c r="O8" s="302"/>
-      <c r="P8" s="302"/>
-      <c r="Q8" s="302"/>
-      <c r="R8" s="302"/>
-      <c r="S8" s="303"/>
-      <c r="T8" s="303"/>
-      <c r="U8" s="303"/>
-      <c r="V8" s="305"/>
-      <c r="W8" s="305"/>
-      <c r="X8" s="302"/>
-      <c r="Y8" s="331"/>
-      <c r="Z8" s="331"/>
-      <c r="AA8" s="332"/>
-      <c r="AB8" s="331"/>
-      <c r="AC8" s="302"/>
-      <c r="AD8" s="301"/>
-      <c r="AE8" s="302"/>
-      <c r="AF8" s="307"/>
-      <c r="AG8" s="307"/>
-      <c r="AH8" s="316"/>
+      <c r="A8" s="307"/>
+      <c r="B8" s="326"/>
+      <c r="C8" s="327"/>
+      <c r="D8" s="302"/>
+      <c r="E8" s="319"/>
+      <c r="F8" s="320"/>
+      <c r="G8" s="320"/>
+      <c r="H8" s="320"/>
+      <c r="I8" s="320"/>
+      <c r="J8" s="320"/>
+      <c r="K8" s="320"/>
+      <c r="L8" s="321"/>
+      <c r="M8" s="307"/>
+      <c r="N8" s="307"/>
+      <c r="O8" s="307"/>
+      <c r="P8" s="307"/>
+      <c r="Q8" s="307"/>
+      <c r="R8" s="307"/>
+      <c r="S8" s="329"/>
+      <c r="T8" s="329"/>
+      <c r="U8" s="329"/>
+      <c r="V8" s="331"/>
+      <c r="W8" s="331"/>
+      <c r="X8" s="307"/>
+      <c r="Y8" s="304"/>
+      <c r="Z8" s="304"/>
+      <c r="AA8" s="305"/>
+      <c r="AB8" s="304"/>
+      <c r="AC8" s="307"/>
+      <c r="AD8" s="306"/>
+      <c r="AE8" s="307"/>
+      <c r="AF8" s="301"/>
+      <c r="AG8" s="301"/>
+      <c r="AH8" s="302"/>
     </row>
     <row r="9" spans="1:40" ht="104.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="302"/>
-      <c r="B9" s="327"/>
-      <c r="C9" s="328"/>
-      <c r="D9" s="316"/>
-      <c r="E9" s="323"/>
-      <c r="F9" s="324"/>
-      <c r="G9" s="324"/>
-      <c r="H9" s="324"/>
-      <c r="I9" s="324"/>
-      <c r="J9" s="324"/>
-      <c r="K9" s="324"/>
-      <c r="L9" s="325"/>
-      <c r="M9" s="302"/>
-      <c r="N9" s="302"/>
-      <c r="O9" s="302"/>
-      <c r="P9" s="302"/>
-      <c r="Q9" s="302"/>
-      <c r="R9" s="302"/>
+      <c r="A9" s="307"/>
+      <c r="B9" s="326"/>
+      <c r="C9" s="327"/>
+      <c r="D9" s="302"/>
+      <c r="E9" s="322"/>
+      <c r="F9" s="323"/>
+      <c r="G9" s="323"/>
+      <c r="H9" s="323"/>
+      <c r="I9" s="323"/>
+      <c r="J9" s="323"/>
+      <c r="K9" s="323"/>
+      <c r="L9" s="324"/>
+      <c r="M9" s="307"/>
+      <c r="N9" s="307"/>
+      <c r="O9" s="307"/>
+      <c r="P9" s="307"/>
+      <c r="Q9" s="307"/>
+      <c r="R9" s="307"/>
       <c r="S9" s="263" t="s">
         <v>223</v>
       </c>
@@ -22837,22 +22837,22 @@
       <c r="U9" s="263" t="s">
         <v>227</v>
       </c>
-      <c r="V9" s="306"/>
-      <c r="W9" s="306"/>
-      <c r="X9" s="302"/>
-      <c r="Y9" s="331"/>
-      <c r="Z9" s="331"/>
-      <c r="AA9" s="332"/>
-      <c r="AB9" s="331"/>
-      <c r="AC9" s="302"/>
-      <c r="AD9" s="301"/>
-      <c r="AE9" s="302"/>
-      <c r="AF9" s="307"/>
-      <c r="AG9" s="307"/>
-      <c r="AH9" s="316"/>
+      <c r="V9" s="332"/>
+      <c r="W9" s="332"/>
+      <c r="X9" s="307"/>
+      <c r="Y9" s="304"/>
+      <c r="Z9" s="304"/>
+      <c r="AA9" s="305"/>
+      <c r="AB9" s="304"/>
+      <c r="AC9" s="307"/>
+      <c r="AD9" s="306"/>
+      <c r="AE9" s="307"/>
+      <c r="AF9" s="301"/>
+      <c r="AG9" s="301"/>
+      <c r="AH9" s="302"/>
       <c r="AI9">
         <f>P12/M12</f>
-        <v>0.75445795170433128</v>
+        <v>0.75467915797039631</v>
       </c>
       <c r="AK9">
         <v>27</v>
@@ -22972,28 +22972,28 @@
       </c>
       <c r="O11" s="283">
         <f>O12</f>
-        <v>350.23</v>
+        <v>214.2</v>
       </c>
       <c r="P11" s="283">
         <f>P12</f>
-        <v>730562.005</v>
+        <v>730776.20499999996</v>
       </c>
       <c r="Q11" s="284">
         <f>P11/M11</f>
-        <v>0.72523371291124117</v>
+        <v>0.7254463506616885</v>
       </c>
       <c r="R11" s="285">
         <f>R12</f>
-        <v>0.8201926587479792</v>
+        <v>0.82043313835997844</v>
       </c>
       <c r="S11" s="286">
         <f>S12</f>
-        <v>25834</v>
+        <v>15440</v>
       </c>
       <c r="T11" s="286"/>
       <c r="U11" s="286">
         <f>U12</f>
-        <v>25483.77</v>
+        <v>14918.77</v>
       </c>
       <c r="V11" s="276"/>
       <c r="W11" s="276"/>
@@ -23010,7 +23010,7 @@
       <c r="AH11" s="274"/>
       <c r="AL11" s="19">
         <f>S11+P11</f>
-        <v>756396.005</v>
+        <v>746216.20499999996</v>
       </c>
     </row>
     <row r="12" spans="1:40" s="102" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -23060,35 +23060,35 @@
         <v>968327</v>
       </c>
       <c r="N12" s="98">
-        <v>730211.77500000002</v>
+        <v>730562.005</v>
       </c>
       <c r="O12" s="98">
         <f>SUM(O13:O77)</f>
-        <v>350.23</v>
+        <v>214.2</v>
       </c>
       <c r="P12" s="288">
         <f>SUBTOTAL(9,P13:P74)</f>
-        <v>730562.005</v>
+        <v>730776.20499999996</v>
       </c>
       <c r="Q12" s="101">
         <f>P12/M12</f>
-        <v>0.75445795170433128</v>
+        <v>0.75467915797039631</v>
       </c>
       <c r="R12" s="101">
         <f>P12/D12</f>
-        <v>0.8201926587479792</v>
+        <v>0.82043313835997844</v>
       </c>
       <c r="S12" s="115">
         <f>SUM(S13:S77)</f>
-        <v>25834</v>
+        <v>15440</v>
       </c>
       <c r="T12" s="115">
         <f>SUM(T13:T77)</f>
-        <v>350.22999999999996</v>
+        <v>521.23</v>
       </c>
       <c r="U12" s="115">
         <f>S12-T12</f>
-        <v>25483.77</v>
+        <v>14918.77</v>
       </c>
       <c r="V12" s="115"/>
       <c r="W12" s="115">
@@ -23097,19 +23097,19 @@
       </c>
       <c r="X12" s="98">
         <f>M12-P12</f>
-        <v>237764.995</v>
+        <v>237550.79500000004</v>
       </c>
       <c r="Y12" s="98">
         <f>N12-Q12</f>
-        <v>730211.02054204827</v>
+        <v>730561.25032084202</v>
       </c>
       <c r="Z12" s="98">
         <f>O12-R12</f>
-        <v>349.40980734125202</v>
+        <v>213.37956686164</v>
       </c>
       <c r="AA12" s="98">
         <f>P12-S12</f>
-        <v>704728.005</v>
+        <v>715336.20499999996</v>
       </c>
       <c r="AB12" s="159">
         <f>SUM(AB13:AB67)</f>
@@ -23117,16 +23117,16 @@
       </c>
       <c r="AC12" s="125">
         <f t="shared" ref="AC12:AC22" si="1">M12-P12-AB12</f>
-        <v>-86995.005000000005</v>
+        <v>-87209.204999999958</v>
       </c>
       <c r="AD12" s="126">
         <f>(P12+AB12)/M12</f>
-        <v>1.0898405239139257</v>
+        <v>1.0900617301799909</v>
       </c>
       <c r="AE12" s="101"/>
       <c r="AF12" s="115">
         <f>SUM(AF13:AF67)</f>
-        <v>146700.94300000003</v>
+        <v>146657.57300000003</v>
       </c>
       <c r="AG12" s="136"/>
       <c r="AH12" s="175" t="s">
@@ -23134,11 +23134,11 @@
       </c>
       <c r="AI12" s="117">
         <f>M12-P12</f>
-        <v>237764.995</v>
+        <v>237550.79500000004</v>
       </c>
       <c r="AJ12" s="119">
         <f>P12+S12</f>
-        <v>756396.005</v>
+        <v>746216.20499999996</v>
       </c>
       <c r="AL12" s="291"/>
       <c r="AM12" s="102">
@@ -23205,7 +23205,7 @@
       <c r="AH13" s="162"/>
       <c r="AI13" s="19">
         <f>P12+AB12</f>
-        <v>1055322.0049999999</v>
+        <v>1055536.2050000001</v>
       </c>
       <c r="AL13" s="19">
         <f>AL12-D12</f>
@@ -23213,7 +23213,7 @@
       </c>
       <c r="AN13" s="19">
         <f>AN12-P12</f>
-        <v>-52733.105000000098</v>
+        <v>-52947.305000000051</v>
       </c>
     </row>
     <row r="14" spans="1:40" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -23299,7 +23299,7 @@
       </c>
       <c r="AI14" s="120">
         <f>P12/M12</f>
-        <v>0.75445795170433128</v>
+        <v>0.75467915797039631</v>
       </c>
       <c r="AK14">
         <v>2</v>
@@ -23312,7 +23312,7 @@
         <v>7264685000</v>
       </c>
     </row>
-    <row r="15" spans="1:40" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>2</v>
       </c>
@@ -23730,18 +23730,20 @@
       <c r="N20" s="273">
         <v>3885.6019999999999</v>
       </c>
-      <c r="O20" s="210"/>
+      <c r="O20" s="210">
+        <v>43.37</v>
+      </c>
       <c r="P20" s="209">
         <f t="shared" si="2"/>
-        <v>3885.6019999999999</v>
+        <v>3928.9719999999998</v>
       </c>
       <c r="Q20" s="63">
         <f>P20/M20</f>
-        <v>0.24731729361593788</v>
+        <v>0.25007777989943353</v>
       </c>
       <c r="R20" s="63">
         <f>P20/M20</f>
-        <v>0.24731729361593788</v>
+        <v>0.25007777989943353</v>
       </c>
       <c r="S20" s="268"/>
       <c r="T20" s="177"/>
@@ -23757,29 +23759,29 @@
       </c>
       <c r="X20" s="33">
         <f t="shared" si="6"/>
-        <v>11825.398000000001</v>
+        <v>11782.028</v>
       </c>
       <c r="Y20" s="64"/>
       <c r="Z20" s="64"/>
       <c r="AA20" s="41">
         <f t="shared" si="3"/>
-        <v>11825.398000000001</v>
+        <v>11782.028</v>
       </c>
       <c r="AB20" s="73" t="s">
         <v>148</v>
       </c>
       <c r="AC20" s="125">
         <f t="shared" si="1"/>
-        <v>8825.398000000001</v>
+        <v>8782.0280000000002</v>
       </c>
       <c r="AD20" s="126">
         <f>(P20+AB20)/M20</f>
-        <v>0.43826631022850232</v>
+        <v>0.44102679651199794</v>
       </c>
       <c r="AE20" s="74"/>
       <c r="AF20" s="157">
         <f>M20-P20</f>
-        <v>11825.398000000001</v>
+        <v>11782.028</v>
       </c>
       <c r="AG20" s="343" t="s">
         <v>233</v>
@@ -23832,12 +23834,12 @@
         <v>0.80633334239130428</v>
       </c>
       <c r="S21" s="268">
-        <v>3805</v>
+        <v>0</v>
       </c>
       <c r="T21" s="177"/>
       <c r="U21" s="268">
         <f t="shared" si="4"/>
-        <v>3805</v>
+        <v>0</v>
       </c>
       <c r="V21" s="268"/>
       <c r="W21" s="268"/>
@@ -24008,18 +24010,16 @@
         <v>6</v>
       </c>
       <c r="N23" s="273">
-        <v>0</v>
-      </c>
-      <c r="O23" s="210">
         <v>5.5</v>
       </c>
+      <c r="O23" s="210"/>
       <c r="P23" s="209">
         <f t="shared" si="2"/>
         <v>5.5</v>
       </c>
       <c r="Q23" s="63"/>
       <c r="R23" s="63"/>
-      <c r="S23" s="292">
+      <c r="S23" s="300">
         <v>6</v>
       </c>
       <c r="T23" s="177">
@@ -24081,18 +24081,16 @@
         <v>23</v>
       </c>
       <c r="N24" s="273">
-        <v>0</v>
-      </c>
-      <c r="O24" s="210">
         <v>22.6</v>
       </c>
+      <c r="O24" s="210"/>
       <c r="P24" s="209">
         <f t="shared" si="2"/>
         <v>22.6</v>
       </c>
       <c r="Q24" s="63"/>
       <c r="R24" s="63"/>
-      <c r="S24" s="292">
+      <c r="S24" s="300">
         <v>23</v>
       </c>
       <c r="T24" s="177">
@@ -24159,8 +24157,8 @@
       </c>
       <c r="Q25" s="63"/>
       <c r="R25" s="63"/>
-      <c r="S25" s="292"/>
-      <c r="T25" s="297"/>
+      <c r="S25" s="300"/>
+      <c r="T25" s="296"/>
       <c r="U25" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24222,8 +24220,8 @@
       </c>
       <c r="Q26" s="63"/>
       <c r="R26" s="63"/>
-      <c r="S26" s="292"/>
-      <c r="T26" s="297"/>
+      <c r="S26" s="300"/>
+      <c r="T26" s="296"/>
       <c r="U26" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24285,8 +24283,8 @@
       </c>
       <c r="Q27" s="63"/>
       <c r="R27" s="63"/>
-      <c r="S27" s="292"/>
-      <c r="T27" s="297"/>
+      <c r="S27" s="300"/>
+      <c r="T27" s="296"/>
       <c r="U27" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24348,8 +24346,8 @@
       </c>
       <c r="Q28" s="63"/>
       <c r="R28" s="63"/>
-      <c r="S28" s="292"/>
-      <c r="T28" s="298"/>
+      <c r="S28" s="300"/>
+      <c r="T28" s="297"/>
       <c r="U28" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24411,8 +24409,8 @@
       </c>
       <c r="Q29" s="63"/>
       <c r="R29" s="63"/>
-      <c r="S29" s="292"/>
-      <c r="T29" s="297"/>
+      <c r="S29" s="300"/>
+      <c r="T29" s="296"/>
       <c r="U29" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24475,8 +24473,8 @@
       </c>
       <c r="Q30" s="63"/>
       <c r="R30" s="63"/>
-      <c r="S30" s="292"/>
-      <c r="T30" s="297"/>
+      <c r="S30" s="300"/>
+      <c r="T30" s="296"/>
       <c r="U30" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24538,8 +24536,8 @@
       </c>
       <c r="Q31" s="63"/>
       <c r="R31" s="63"/>
-      <c r="S31" s="292"/>
-      <c r="T31" s="297"/>
+      <c r="S31" s="300"/>
+      <c r="T31" s="296"/>
       <c r="U31" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24601,8 +24599,8 @@
       </c>
       <c r="Q32" s="63"/>
       <c r="R32" s="63"/>
-      <c r="S32" s="292"/>
-      <c r="T32" s="297"/>
+      <c r="S32" s="300"/>
+      <c r="T32" s="296"/>
       <c r="U32" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24664,8 +24662,8 @@
       </c>
       <c r="Q33" s="63"/>
       <c r="R33" s="63"/>
-      <c r="S33" s="292"/>
-      <c r="T33" s="297"/>
+      <c r="S33" s="300"/>
+      <c r="T33" s="296"/>
       <c r="U33" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24727,8 +24725,8 @@
       </c>
       <c r="Q34" s="63"/>
       <c r="R34" s="63"/>
-      <c r="S34" s="292"/>
-      <c r="T34" s="297"/>
+      <c r="S34" s="300"/>
+      <c r="T34" s="296"/>
       <c r="U34" s="268">
         <f>S34-T34</f>
         <v>0</v>
@@ -24781,8 +24779,8 @@
       </c>
       <c r="Q35" s="63"/>
       <c r="R35" s="63"/>
-      <c r="S35" s="292"/>
-      <c r="T35" s="296"/>
+      <c r="S35" s="300"/>
+      <c r="T35" s="295"/>
       <c r="U35" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24857,8 +24855,8 @@
         <f t="shared" ref="R36:R43" si="9">P36/D36</f>
         <v>0.99048349961627014</v>
       </c>
-      <c r="S36" s="292"/>
-      <c r="T36" s="296"/>
+      <c r="S36" s="300"/>
+      <c r="T36" s="295"/>
       <c r="U36" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -24943,8 +24941,8 @@
         <f t="shared" si="9"/>
         <v>0.7749230132450331</v>
       </c>
-      <c r="S37" s="292"/>
-      <c r="T37" s="296"/>
+      <c r="S37" s="300"/>
+      <c r="T37" s="295"/>
       <c r="U37" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -25035,10 +25033,10 @@
         <f t="shared" si="9"/>
         <v>0.77321600000000001</v>
       </c>
-      <c r="S38" s="292">
+      <c r="S38" s="300">
         <v>2835</v>
       </c>
-      <c r="T38" s="296"/>
+      <c r="T38" s="295"/>
       <c r="U38" s="268">
         <f t="shared" si="4"/>
         <v>2835</v>
@@ -25131,11 +25129,13 @@
         <f t="shared" si="9"/>
         <v>0.77485844459052067</v>
       </c>
-      <c r="S39" s="292"/>
-      <c r="T39" s="296"/>
+      <c r="S39" s="300">
+        <v>150</v>
+      </c>
+      <c r="T39" s="295"/>
       <c r="U39" s="268">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="V39" s="268" t="s">
         <v>216</v>
@@ -25222,13 +25222,11 @@
         <f t="shared" si="9"/>
         <v>0.70569982963525524</v>
       </c>
-      <c r="S40" s="292">
-        <v>2158</v>
-      </c>
-      <c r="T40" s="296"/>
+      <c r="S40" s="300"/>
+      <c r="T40" s="295"/>
       <c r="U40" s="268">
         <f t="shared" si="4"/>
-        <v>2158</v>
+        <v>0</v>
       </c>
       <c r="V40" s="268" t="s">
         <v>214</v>
@@ -25317,8 +25315,8 @@
         <f t="shared" si="9"/>
         <v>0.83418213706608435</v>
       </c>
-      <c r="S41" s="292"/>
-      <c r="T41" s="296"/>
+      <c r="S41" s="300"/>
+      <c r="T41" s="295"/>
       <c r="U41" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -25405,8 +25403,8 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S42" s="292"/>
-      <c r="T42" s="296"/>
+      <c r="S42" s="300"/>
+      <c r="T42" s="295"/>
       <c r="U42" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -25493,8 +25491,8 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S43" s="292"/>
-      <c r="T43" s="296"/>
+      <c r="S43" s="300"/>
+      <c r="T43" s="295"/>
       <c r="U43" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -25581,8 +25579,8 @@
       <c r="R44" s="63">
         <v>0</v>
       </c>
-      <c r="S44" s="292"/>
-      <c r="T44" s="296"/>
+      <c r="S44" s="300"/>
+      <c r="T44" s="295"/>
       <c r="U44" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -25668,8 +25666,8 @@
         <f t="shared" ref="R45:R59" si="13">P45/D45</f>
         <v>0</v>
       </c>
-      <c r="S45" s="292"/>
-      <c r="T45" s="296"/>
+      <c r="S45" s="300"/>
+      <c r="T45" s="295"/>
       <c r="U45" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -25753,8 +25751,8 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S46" s="292"/>
-      <c r="T46" s="296"/>
+      <c r="S46" s="300"/>
+      <c r="T46" s="295"/>
       <c r="U46" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -25840,8 +25838,8 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S47" s="292"/>
-      <c r="T47" s="296"/>
+      <c r="S47" s="300"/>
+      <c r="T47" s="295"/>
       <c r="U47" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -25924,7 +25922,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="268"/>
-      <c r="T48" s="296"/>
+      <c r="T48" s="295"/>
       <c r="U48" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26004,7 +26002,7 @@
         <v>0</v>
       </c>
       <c r="S49" s="268"/>
-      <c r="T49" s="296"/>
+      <c r="T49" s="295"/>
       <c r="U49" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26084,7 +26082,7 @@
         <v>0</v>
       </c>
       <c r="S50" s="268"/>
-      <c r="T50" s="296"/>
+      <c r="T50" s="295"/>
       <c r="U50" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26164,7 +26162,7 @@
         <v>0</v>
       </c>
       <c r="S51" s="268"/>
-      <c r="T51" s="296"/>
+      <c r="T51" s="295"/>
       <c r="U51" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26244,7 +26242,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="268"/>
-      <c r="T52" s="296"/>
+      <c r="T52" s="295"/>
       <c r="U52" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26328,7 +26326,7 @@
         <v>0</v>
       </c>
       <c r="S53" s="268"/>
-      <c r="T53" s="296"/>
+      <c r="T53" s="295"/>
       <c r="U53" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26412,7 +26410,7 @@
         <v>0</v>
       </c>
       <c r="S54" s="268"/>
-      <c r="T54" s="296"/>
+      <c r="T54" s="295"/>
       <c r="U54" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26492,7 +26490,7 @@
         <v>0</v>
       </c>
       <c r="S55" s="268"/>
-      <c r="T55" s="296"/>
+      <c r="T55" s="295"/>
       <c r="U55" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26572,7 +26570,7 @@
         <v>0</v>
       </c>
       <c r="S56" s="268"/>
-      <c r="T56" s="296"/>
+      <c r="T56" s="295"/>
       <c r="U56" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26652,7 +26650,7 @@
         <v>0</v>
       </c>
       <c r="S57" s="268"/>
-      <c r="T57" s="296"/>
+      <c r="T57" s="295"/>
       <c r="U57" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26732,7 +26730,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="268"/>
-      <c r="T58" s="296"/>
+      <c r="T58" s="295"/>
       <c r="U58" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26812,7 +26810,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="268"/>
-      <c r="T59" s="296"/>
+      <c r="T59" s="295"/>
       <c r="U59" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -26889,13 +26887,13 @@
       <c r="R60" s="63">
         <v>0</v>
       </c>
-      <c r="S60" s="268">
-        <v>265</v>
-      </c>
-      <c r="T60" s="296"/>
+      <c r="S60" s="268"/>
+      <c r="T60" s="295">
+        <v>0</v>
+      </c>
       <c r="U60" s="268">
         <f t="shared" si="4"/>
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="V60" s="268"/>
       <c r="W60" s="268">
@@ -26978,12 +26976,12 @@
         <v>0.54837978146499378</v>
       </c>
       <c r="S61" s="268">
-        <v>10000</v>
-      </c>
-      <c r="T61" s="296"/>
+        <v>0</v>
+      </c>
+      <c r="T61" s="295"/>
       <c r="U61" s="268">
         <f t="shared" si="4"/>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V61" s="268"/>
       <c r="W61" s="268"/>
@@ -27024,7 +27022,7 @@
         <v>37065</v>
       </c>
     </row>
-    <row r="62" spans="1:40" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:40" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="30">
         <v>46</v>
       </c>
@@ -27072,7 +27070,7 @@
         <v>0.98030568115576699</v>
       </c>
       <c r="S62" s="268"/>
-      <c r="T62" s="296"/>
+      <c r="T62" s="295"/>
       <c r="U62" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -27229,12 +27227,9 @@
         <v>6792</v>
       </c>
       <c r="N64" s="273">
-        <v>3576.73</v>
-      </c>
-      <c r="O64" s="294">
-        <f>19.75+42.64+0.67</f>
-        <v>63.06</v>
-      </c>
+        <v>3639.79</v>
+      </c>
+      <c r="O64" s="293"/>
       <c r="P64" s="209">
         <f t="shared" si="12"/>
         <v>3639.79</v>
@@ -27247,7 +27242,7 @@
         <v>0</v>
       </c>
       <c r="S64" s="268"/>
-      <c r="T64" s="299">
+      <c r="T64" s="268">
         <v>63.06</v>
       </c>
       <c r="U64" s="268">
@@ -27321,53 +27316,53 @@
         <v>4100</v>
       </c>
       <c r="N65" s="273">
-        <v>3484</v>
-      </c>
-      <c r="O65" s="294">
-        <f>23.57+18.54+0.83</f>
-        <v>42.94</v>
+        <v>3526.94</v>
+      </c>
+      <c r="O65" s="273">
+        <v>32</v>
       </c>
       <c r="P65" s="209">
         <f t="shared" si="12"/>
-        <v>3526.94</v>
+        <v>3558.94</v>
       </c>
       <c r="Q65" s="186">
         <f t="shared" si="16"/>
-        <v>0.86022926829268298</v>
+        <v>0.86803414634146348</v>
       </c>
       <c r="R65" s="63">
         <v>0</v>
       </c>
       <c r="S65" s="268">
-        <v>1316</v>
-      </c>
-      <c r="T65" s="299">
-        <v>42.94</v>
+        <v>0</v>
+      </c>
+      <c r="T65" s="268">
+        <f>42.94+32</f>
+        <v>74.94</v>
       </c>
       <c r="U65" s="268">
         <f t="shared" si="4"/>
-        <v>1273.06</v>
+        <v>-74.94</v>
       </c>
       <c r="V65" s="268"/>
       <c r="W65" s="268"/>
       <c r="X65" s="33">
         <f t="shared" si="15"/>
-        <v>573.05999999999995</v>
+        <v>541.05999999999995</v>
       </c>
       <c r="Y65" s="64"/>
       <c r="Z65" s="64"/>
       <c r="AA65" s="41">
         <f t="shared" si="3"/>
-        <v>573.05999999999995</v>
+        <v>541.05999999999995</v>
       </c>
       <c r="AB65" s="65"/>
       <c r="AC65" s="125">
         <f t="shared" si="7"/>
-        <v>573.05999999999995</v>
+        <v>541.05999999999995</v>
       </c>
       <c r="AD65" s="126">
         <f>(P65+AB65)/M65</f>
-        <v>0.86022926829268298</v>
+        <v>0.86803414634146348</v>
       </c>
       <c r="AE65" s="67"/>
       <c r="AF65" s="67"/>
@@ -27416,14 +27411,16 @@
       <c r="N66" s="273">
         <v>574.29999999999995</v>
       </c>
-      <c r="O66" s="210"/>
+      <c r="O66" s="210">
+        <v>1.56</v>
+      </c>
       <c r="P66" s="209">
         <f t="shared" si="12"/>
-        <v>574.29999999999995</v>
+        <v>575.8599999999999</v>
       </c>
       <c r="Q66" s="186">
         <f t="shared" si="16"/>
-        <v>5.6303921568627444E-2</v>
+        <v>5.6456862745098028E-2</v>
       </c>
       <c r="R66" s="63">
         <v>0</v>
@@ -27431,31 +27428,33 @@
       <c r="S66" s="268">
         <v>5426</v>
       </c>
-      <c r="T66" s="299"/>
+      <c r="T66" s="298">
+        <v>2</v>
+      </c>
       <c r="U66" s="268">
         <f t="shared" si="4"/>
-        <v>5426</v>
+        <v>5424</v>
       </c>
       <c r="V66" s="268"/>
       <c r="W66" s="268"/>
       <c r="X66" s="33">
         <f t="shared" si="15"/>
-        <v>9625.7000000000007</v>
+        <v>9624.14</v>
       </c>
       <c r="Y66" s="64"/>
       <c r="Z66" s="64"/>
       <c r="AA66" s="41">
         <f t="shared" si="3"/>
-        <v>9625.7000000000007</v>
+        <v>9624.14</v>
       </c>
       <c r="AB66" s="65"/>
       <c r="AC66" s="125">
         <f t="shared" si="7"/>
-        <v>9625.7000000000007</v>
+        <v>9624.14</v>
       </c>
       <c r="AD66" s="126">
         <f>(P66+AB66)/M66</f>
-        <v>5.6303921568627444E-2</v>
+        <v>5.6456862745098028E-2</v>
       </c>
       <c r="AE66" s="64"/>
       <c r="AF66" s="64"/>
@@ -27465,7 +27464,7 @@
       <c r="AH66" s="173"/>
       <c r="AL66" s="18">
         <f>6000-P66</f>
-        <v>5425.7</v>
+        <v>5424.14</v>
       </c>
     </row>
     <row r="67" spans="1:40" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -27503,11 +27502,9 @@
         <v>12500</v>
       </c>
       <c r="N67" s="273">
-        <v>684</v>
-      </c>
-      <c r="O67" s="295">
-        <v>1.76</v>
-      </c>
+        <v>685.76</v>
+      </c>
+      <c r="O67" s="294"/>
       <c r="P67" s="209">
         <f t="shared" si="12"/>
         <v>685.76</v>
@@ -27519,13 +27516,15 @@
       <c r="R67" s="63">
         <v>0</v>
       </c>
-      <c r="S67" s="268"/>
-      <c r="T67" s="299">
+      <c r="S67" s="268">
+        <v>7000</v>
+      </c>
+      <c r="T67" s="298">
         <v>1.76</v>
       </c>
       <c r="U67" s="268">
         <f t="shared" si="4"/>
-        <v>-1.76</v>
+        <v>6998.24</v>
       </c>
       <c r="V67" s="268"/>
       <c r="W67" s="268"/>
@@ -27587,12 +27586,9 @@
         <v>4600</v>
       </c>
       <c r="N68" s="273">
-        <v>2114.1</v>
-      </c>
-      <c r="O68" s="211">
-        <f>10.68+18.49+0.5</f>
-        <v>29.669999999999998</v>
-      </c>
+        <v>2143.77</v>
+      </c>
+      <c r="O68" s="211"/>
       <c r="P68" s="209">
         <f t="shared" si="12"/>
         <v>2143.77</v>
@@ -27605,7 +27601,7 @@
         <v>0</v>
       </c>
       <c r="S68" s="268"/>
-      <c r="T68" s="299">
+      <c r="T68" s="268">
         <v>29.67</v>
       </c>
       <c r="U68" s="268">
@@ -27673,12 +27669,9 @@
         <v>11400</v>
       </c>
       <c r="N69" s="273">
-        <v>5777.4</v>
-      </c>
-      <c r="O69" s="212">
-        <f>31.8+46.76+40.49+1.28</f>
-        <v>120.33000000000001</v>
-      </c>
+        <v>5897.73</v>
+      </c>
+      <c r="O69" s="212"/>
       <c r="P69" s="209">
         <f t="shared" si="12"/>
         <v>5897.73</v>
@@ -27691,12 +27684,13 @@
         <v>0</v>
       </c>
       <c r="S69" s="268"/>
-      <c r="T69" s="299">
-        <v>120.33</v>
+      <c r="T69" s="268">
+        <f>120.33+74.23</f>
+        <v>194.56</v>
       </c>
       <c r="U69" s="268">
         <f t="shared" si="4"/>
-        <v>-120.33</v>
+        <v>-194.56</v>
       </c>
       <c r="V69" s="268"/>
       <c r="W69" s="268"/>
@@ -27753,25 +27747,25 @@
         <v>10967</v>
       </c>
       <c r="N70" s="273">
-        <v>5391</v>
+        <v>5429.43</v>
       </c>
       <c r="O70" s="211">
-        <f>37.2+1.23</f>
-        <v>38.43</v>
+        <f>45+29.5</f>
+        <v>74.5</v>
       </c>
       <c r="P70" s="209">
         <f t="shared" si="12"/>
-        <v>5429.43</v>
+        <v>5503.93</v>
       </c>
       <c r="Q70" s="189">
         <f t="shared" si="16"/>
-        <v>0.49506975471870157</v>
+        <v>0.50186286131120639</v>
       </c>
       <c r="R70" s="63">
         <v>0</v>
       </c>
       <c r="S70" s="268"/>
-      <c r="T70" s="299">
+      <c r="T70" s="298">
         <v>38.43</v>
       </c>
       <c r="U70" s="268">
@@ -27782,7 +27776,7 @@
       <c r="W70" s="268"/>
       <c r="X70" s="33">
         <f t="shared" si="15"/>
-        <v>5537.57</v>
+        <v>5463.07</v>
       </c>
       <c r="Y70" s="184"/>
       <c r="Z70" s="184"/>
@@ -27829,36 +27823,37 @@
         <v>7073</v>
       </c>
       <c r="N71" s="273">
-        <v>3951</v>
-      </c>
-      <c r="O71" s="213">
-        <f>24.6+1.34</f>
-        <v>25.94</v>
+        <v>3976.94</v>
+      </c>
+      <c r="O71" s="211">
+        <f>48.98+13.79</f>
+        <v>62.769999999999996</v>
       </c>
       <c r="P71" s="209">
         <f t="shared" si="12"/>
-        <v>3976.94</v>
+        <v>4039.71</v>
       </c>
       <c r="Q71" s="189">
         <f t="shared" si="16"/>
-        <v>0.56227060653188177</v>
+        <v>0.57114520005655312</v>
       </c>
       <c r="R71" s="63">
         <v>0</v>
       </c>
       <c r="S71" s="268"/>
-      <c r="T71" s="299">
-        <v>25.94</v>
+      <c r="T71" s="268">
+        <f>25.94+62.77</f>
+        <v>88.710000000000008</v>
       </c>
       <c r="U71" s="268">
         <f t="shared" si="4"/>
-        <v>-25.94</v>
+        <v>-88.710000000000008</v>
       </c>
       <c r="V71" s="268"/>
       <c r="W71" s="268"/>
       <c r="X71" s="33">
         <f t="shared" si="15"/>
-        <v>3096.06</v>
+        <v>3033.29</v>
       </c>
       <c r="Y71" s="179"/>
       <c r="Z71" s="179"/>
@@ -27911,7 +27906,7 @@
       <c r="Q72" s="260"/>
       <c r="R72" s="63"/>
       <c r="S72" s="268"/>
-      <c r="T72" s="299"/>
+      <c r="T72" s="298"/>
       <c r="U72" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -27973,7 +27968,7 @@
       <c r="Q73" s="260"/>
       <c r="R73" s="63"/>
       <c r="S73" s="268"/>
-      <c r="T73" s="299"/>
+      <c r="T73" s="298"/>
       <c r="U73" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -28035,7 +28030,7 @@
       <c r="Q74" s="260"/>
       <c r="R74" s="63"/>
       <c r="S74" s="268"/>
-      <c r="T74" s="299"/>
+      <c r="T74" s="298"/>
       <c r="U74" s="268">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -28090,7 +28085,7 @@
       <c r="Q75" s="260"/>
       <c r="R75" s="63"/>
       <c r="S75" s="268"/>
-      <c r="T75" s="299"/>
+      <c r="T75" s="298"/>
       <c r="U75" s="268"/>
       <c r="V75" s="268"/>
       <c r="W75" s="268"/>
@@ -28137,7 +28132,7 @@
       <c r="Q76" s="260"/>
       <c r="R76" s="63"/>
       <c r="S76" s="268"/>
-      <c r="T76" s="299"/>
+      <c r="T76" s="298"/>
       <c r="U76" s="268"/>
       <c r="V76" s="268"/>
       <c r="W76" s="268"/>
@@ -28175,8 +28170,8 @@
       <c r="P77" s="213"/>
       <c r="Q77" s="179"/>
       <c r="R77" s="179"/>
-      <c r="S77" s="293"/>
-      <c r="T77" s="300"/>
+      <c r="S77" s="292"/>
+      <c r="T77" s="299"/>
       <c r="U77" s="256"/>
       <c r="V77" s="256"/>
       <c r="W77" s="256"/>
@@ -29105,15 +29100,11 @@
   </sheetData>
   <autoFilter ref="A10:AK77" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="30">
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AC9"/>
-    <mergeCell ref="AD7:AD9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="S7:U8"/>
+    <mergeCell ref="V7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="AE7:AE9"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A4:AH4"/>
@@ -29130,11 +29121,15 @@
     <mergeCell ref="P7:P9"/>
     <mergeCell ref="Q7:Q9"/>
     <mergeCell ref="R7:R9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="S7:U8"/>
-    <mergeCell ref="V7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AC9"/>
+    <mergeCell ref="AD7:AD9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
   </mergeCells>
   <pageMargins left="0.55000000000000004" right="0.15748031496062992" top="0.39370078740157483" bottom="0.23622047244094491" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" r:id="rId1"/>
